--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10530" uniqueCount="3686">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10563" uniqueCount="3695">
   <si>
     <t>Ņ</t>
   </si>
@@ -11072,9 +11072,6 @@
     <t>Nailgun</t>
   </si>
   <si>
-    <t>[o]</t>
-  </si>
-  <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1482693706472751124/id_Ty.png?ex=69b7e19e&amp;is=69b6901e&amp;hm=3102c5618f3f3480ed32aabf1938343ecd97850aec11f51e0049a0c2bf2d3a02</t>
   </si>
   <si>
@@ -11085,6 +11082,36 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1482693892280287312/id_T1.png?ex=69b7e1cb&amp;is=69b6904b&amp;hm=65dca87c374ffe1a76cffb85176b68c7493dedae2a79086bec5d932463ee6c76</t>
+  </si>
+  <si>
+    <t>T2</t>
+  </si>
+  <si>
+    <t>berreez</t>
+  </si>
+  <si>
+    <t>T3</t>
+  </si>
+  <si>
+    <t>T4</t>
+  </si>
+  <si>
+    <t>T5</t>
+  </si>
+  <si>
+    <t>Exorcistor/Summoner</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1483769478981619843/id_T2.png?ex=69bbcb82&amp;is=69ba7a02&amp;hm=307ee8406bbe2a715c8a08bd853a4a46bdabe7ed021d191e8eda71882181792a</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1483769526482112592/id_T3.png?ex=69bbcb8e&amp;is=69ba7a0e&amp;hm=56a1d96c566e357b71616fbfb661b1b5c0620eff854e8b5e09dfe1b8ededcbea</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1483769573877616650/id_T4.jpg?ex=69bbcb99&amp;is=69ba7a19&amp;hm=13cfcd9d4b3df81670c9726df7b063ecf59a73496ba6c2a6c3a9b97c614deb14</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1483769620375666789/id_T5.jpg?ex=69bbcba4&amp;is=69ba7a24&amp;hm=df4574ef9fae77d586b80333ff2de81ca6f9880d41cc0466a3cc8b56ed676fce</t>
   </si>
 </sst>
 </file>
@@ -11096,18 +11123,11 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="83" x14ac:knownFonts="1">
+  <fonts count="82" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -11710,119 +11730,118 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="62" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="77" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="69" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="70" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="59" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="46" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -11831,18 +11850,18 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -11856,8 +11875,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -12075,7 +12094,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1268"/>
+  <dimension ref="A1:O1276"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -64726,11 +64745,11 @@
       <c r="K1265">
         <v>1266</v>
       </c>
-      <c r="M1265" s="131" t="s">
+      <c r="M1265" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1265" t="s">
         <v>3681</v>
-      </c>
-      <c r="N1265" t="s">
-        <v>3682</v>
       </c>
     </row>
     <row r="1266" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64767,11 +64786,11 @@
       <c r="K1266">
         <v>1267</v>
       </c>
-      <c r="M1266" s="131" t="s">
-        <v>3681</v>
+      <c r="M1266" s="57" t="s">
+        <v>861</v>
       </c>
       <c r="N1266" t="s">
-        <v>3683</v>
+        <v>3682</v>
       </c>
     </row>
     <row r="1267" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64808,11 +64827,11 @@
       <c r="K1267">
         <v>1268</v>
       </c>
-      <c r="M1267" s="131" t="s">
-        <v>3681</v>
+      <c r="M1267" s="57" t="s">
+        <v>861</v>
       </c>
       <c r="N1267" t="s">
-        <v>3684</v>
+        <v>3683</v>
       </c>
     </row>
     <row r="1268" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64849,11 +64868,195 @@
       <c r="K1268">
         <v>1269</v>
       </c>
-      <c r="M1268" s="131" t="s">
-        <v>3681</v>
+      <c r="M1268" s="57" t="s">
+        <v>861</v>
       </c>
       <c r="N1268" t="s">
+        <v>3684</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1269">
+        <v>56</v>
+      </c>
+      <c r="B1269" s="7">
+        <v>13897219</v>
+      </c>
+      <c r="C1269" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1269" t="s">
+        <v>336</v>
+      </c>
+      <c r="E1269" t="s">
+        <v>3439</v>
+      </c>
+      <c r="F1269" s="29">
+        <v>46098</v>
+      </c>
+      <c r="G1269" s="56">
+        <v>0.15327546296296296</v>
+      </c>
+      <c r="H1269" t="s">
+        <v>1329</v>
+      </c>
+      <c r="I1269" t="s">
+        <v>293</v>
+      </c>
+      <c r="J1269" s="63" t="s">
         <v>3685</v>
+      </c>
+      <c r="K1269">
+        <v>1270</v>
+      </c>
+      <c r="M1269" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1269" t="s">
+        <v>3691</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1270">
+        <v>56</v>
+      </c>
+      <c r="B1270" s="7">
+        <v>12357428</v>
+      </c>
+      <c r="C1270" t="s">
+        <v>3686</v>
+      </c>
+      <c r="D1270" t="s">
+        <v>286</v>
+      </c>
+      <c r="E1270" t="s">
+        <v>3686</v>
+      </c>
+      <c r="F1270" s="29">
+        <v>46098</v>
+      </c>
+      <c r="G1270" s="56" t="s">
+        <v>507</v>
+      </c>
+      <c r="H1270" t="s">
+        <v>837</v>
+      </c>
+      <c r="I1270" t="s">
+        <v>293</v>
+      </c>
+      <c r="J1270" s="63" t="s">
+        <v>3687</v>
+      </c>
+      <c r="K1270">
+        <v>1271</v>
+      </c>
+      <c r="M1270" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1270" t="s">
+        <v>3692</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1271">
+        <v>56</v>
+      </c>
+      <c r="B1271" s="7">
+        <v>17640029</v>
+      </c>
+      <c r="C1271" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1271" t="s">
+        <v>536</v>
+      </c>
+      <c r="E1271" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1271" s="29">
+        <v>46098</v>
+      </c>
+      <c r="G1271" s="56">
+        <v>0.20313657407407407</v>
+      </c>
+      <c r="H1271" t="s">
+        <v>1268</v>
+      </c>
+      <c r="I1271" t="s">
+        <v>293</v>
+      </c>
+      <c r="J1271" s="63" t="s">
+        <v>3688</v>
+      </c>
+      <c r="K1271">
+        <v>1272</v>
+      </c>
+      <c r="M1271" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1271" t="s">
+        <v>3693</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1272">
+        <v>56</v>
+      </c>
+      <c r="B1272" s="7">
+        <v>20655781</v>
+      </c>
+      <c r="C1272" t="s">
+        <v>3544</v>
+      </c>
+      <c r="D1272" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1272" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1272" s="29">
+        <v>46099</v>
+      </c>
+      <c r="G1272" s="56">
+        <v>0.11376157407407407</v>
+      </c>
+      <c r="H1272" t="s">
+        <v>3690</v>
+      </c>
+      <c r="I1272" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1272" s="63" t="s">
+        <v>3689</v>
+      </c>
+      <c r="K1272">
+        <v>1273</v>
+      </c>
+      <c r="M1272" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1272" t="s">
+        <v>3694</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1273">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1274">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1275">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1276">
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10563" uniqueCount="3695">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10620" uniqueCount="3711">
   <si>
     <t>Ņ</t>
   </si>
@@ -11112,6 +11112,54 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1483769620375666789/id_T5.jpg?ex=69bbcba4&amp;is=69ba7a24&amp;hm=df4574ef9fae77d586b80333ff2de81ca6f9880d41cc0466a3cc8b56ed676fce</t>
+  </si>
+  <si>
+    <t>past life regression (z)</t>
+  </si>
+  <si>
+    <t>T6</t>
+  </si>
+  <si>
+    <t>T7</t>
+  </si>
+  <si>
+    <t>T8</t>
+  </si>
+  <si>
+    <t>T9</t>
+  </si>
+  <si>
+    <t>T(</t>
+  </si>
+  <si>
+    <t>T)</t>
+  </si>
+  <si>
+    <t>UA</t>
+  </si>
+  <si>
+    <t>Ragnarok/Kronos/Summoner</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1484248080063660173/id_T6.png?ex=69bd893e&amp;is=69bc37be&amp;hm=b2ab5e049c0cca56f3953aa85e8b030eabb06b9a5e09b77645269c174eb6784d</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1484248143594913813/id_T7.jpg?ex=69bd894d&amp;is=69bc37cd&amp;hm=43f491ae24b7692ec00bbc168ad0d1e7d01b82f1a12b84539024b2414d5e0530</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1484248197424611508/id_T8.jpg?ex=69bd895a&amp;is=69bc37da&amp;hm=dd804ad570c0ad89692ca6c0b99514778d3d43d06181ed4cccbf7222c10b2880</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1484248257570799746/id_T9.jpg?ex=69bd8968&amp;is=69bc37e8&amp;hm=ffa9a5eb18520402b411b91653713f9abd25bc1d41c0c488ee3097aa41872918</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1484248329394065589/id_T.jpg?ex=69bd8979&amp;is=69bc37f9&amp;hm=220f5a0f2fc36dfc90da6c7645b04cef33bf0ef2c54be119b0d5c32d1cdf9526</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1484248422860066907/id_T.jpg?ex=69bd8990&amp;is=69bc3810&amp;hm=a9d6f99c3ad460b381e050a5379eef0ceb4a2af15f2e4f40c02cd950b1546c45</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1484248484340305930/id_UA.jpg?ex=69bd899e&amp;is=69bc381e&amp;hm=f741b800322ea86697f5f57ad843185b6aecb251b8ae655e5bd833d514df4f66</t>
   </si>
 </sst>
 </file>
@@ -12094,7 +12142,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1276"/>
+  <dimension ref="A1:O1279"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -65043,20 +65091,287 @@
       <c r="A1273">
         <v>56</v>
       </c>
+      <c r="B1273" s="7">
+        <v>15637601</v>
+      </c>
+      <c r="C1273" t="s">
+        <v>3695</v>
+      </c>
+      <c r="D1273" t="s">
+        <v>367</v>
+      </c>
+      <c r="E1273" t="s">
+        <v>701</v>
+      </c>
+      <c r="F1273" s="29">
+        <v>46099</v>
+      </c>
+      <c r="G1273" s="56">
+        <v>9.2476851851851852E-2</v>
+      </c>
+      <c r="H1273" t="s">
+        <v>892</v>
+      </c>
+      <c r="I1273" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1273" s="63" t="s">
+        <v>3696</v>
+      </c>
+      <c r="K1273">
+        <v>1274</v>
+      </c>
+      <c r="M1273" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1273" t="s">
+        <v>3704</v>
+      </c>
     </row>
     <row r="1274" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1274">
         <v>56</v>
       </c>
+      <c r="B1274" s="7">
+        <v>10418104</v>
+      </c>
+      <c r="C1274" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1274" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1274" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1274" s="29">
+        <v>45584</v>
+      </c>
+      <c r="G1274" s="56">
+        <v>6.0937499999999999E-2</v>
+      </c>
+      <c r="H1274" t="s">
+        <v>842</v>
+      </c>
+      <c r="I1274" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1274" s="63" t="s">
+        <v>3697</v>
+      </c>
+      <c r="K1274">
+        <v>1275</v>
+      </c>
+      <c r="M1274" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1274" t="s">
+        <v>3705</v>
+      </c>
     </row>
     <row r="1275" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1275">
         <v>56</v>
       </c>
+      <c r="B1275" s="7">
+        <v>10019685</v>
+      </c>
+      <c r="C1275" t="s">
+        <v>3544</v>
+      </c>
+      <c r="D1275" t="s">
+        <v>467</v>
+      </c>
+      <c r="E1275" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1275" s="29">
+        <v>46099</v>
+      </c>
+      <c r="G1275" s="56">
+        <v>6.6157407407407401E-2</v>
+      </c>
+      <c r="H1275" t="s">
+        <v>812</v>
+      </c>
+      <c r="I1275" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1275" s="63" t="s">
+        <v>3698</v>
+      </c>
+      <c r="K1275">
+        <v>1276</v>
+      </c>
+      <c r="M1275" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1275" t="s">
+        <v>3706</v>
+      </c>
     </row>
     <row r="1276" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1276">
         <v>56</v>
+      </c>
+      <c r="B1276" s="7">
+        <v>24416863</v>
+      </c>
+      <c r="C1276" t="s">
+        <v>3544</v>
+      </c>
+      <c r="D1276" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1276" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1276" s="29">
+        <v>46099</v>
+      </c>
+      <c r="G1276" s="56">
+        <v>0.14564814814814817</v>
+      </c>
+      <c r="H1276" t="s">
+        <v>892</v>
+      </c>
+      <c r="I1276" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1276" s="63" t="s">
+        <v>3699</v>
+      </c>
+      <c r="K1276">
+        <v>1277</v>
+      </c>
+      <c r="M1276" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1276" t="s">
+        <v>3707</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1277">
+        <v>56</v>
+      </c>
+      <c r="B1277" s="7">
+        <v>20390911</v>
+      </c>
+      <c r="C1277" t="s">
+        <v>3544</v>
+      </c>
+      <c r="D1277" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1277" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1277" s="29">
+        <v>46100</v>
+      </c>
+      <c r="G1277" s="56" t="s">
+        <v>507</v>
+      </c>
+      <c r="H1277" t="s">
+        <v>824</v>
+      </c>
+      <c r="I1277" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1277" s="63" t="s">
+        <v>3700</v>
+      </c>
+      <c r="K1277">
+        <v>1278</v>
+      </c>
+      <c r="M1277" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1277" t="s">
+        <v>3708</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1278">
+        <v>56</v>
+      </c>
+      <c r="B1278" s="7">
+        <v>36572979</v>
+      </c>
+      <c r="C1278" t="s">
+        <v>3544</v>
+      </c>
+      <c r="D1278" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1278" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1278" s="29">
+        <v>46100</v>
+      </c>
+      <c r="G1278" s="56">
+        <v>0.25368055555555552</v>
+      </c>
+      <c r="H1278" t="s">
+        <v>832</v>
+      </c>
+      <c r="I1278" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1278" s="63" t="s">
+        <v>3701</v>
+      </c>
+      <c r="K1278">
+        <v>1279</v>
+      </c>
+      <c r="M1278" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1278" t="s">
+        <v>3709</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1279">
+        <v>56</v>
+      </c>
+      <c r="B1279" s="7">
+        <v>11688943</v>
+      </c>
+      <c r="C1279" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1279" t="s">
+        <v>619</v>
+      </c>
+      <c r="E1279" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1279" s="29">
+        <v>46046</v>
+      </c>
+      <c r="G1279" s="56">
+        <v>8.5636574074074087E-2</v>
+      </c>
+      <c r="H1279" t="s">
+        <v>3703</v>
+      </c>
+      <c r="I1279" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1279" s="63" t="s">
+        <v>3702</v>
+      </c>
+      <c r="K1279">
+        <v>1280</v>
+      </c>
+      <c r="M1279" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1279" t="s">
+        <v>3710</v>
       </c>
     </row>
   </sheetData>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10620" uniqueCount="3711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10736" uniqueCount="3752">
   <si>
     <t>Ņ</t>
   </si>
@@ -11160,6 +11160,129 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1484248484340305930/id_UA.jpg?ex=69bd899e&amp;is=69bc381e&amp;hm=f741b800322ea86697f5f57ad843185b6aecb251b8ae655e5bd833d514df4f66</t>
+  </si>
+  <si>
+    <t>UB</t>
+  </si>
+  <si>
+    <t>UC</t>
+  </si>
+  <si>
+    <t>UD</t>
+  </si>
+  <si>
+    <t>UE</t>
+  </si>
+  <si>
+    <t>UF</t>
+  </si>
+  <si>
+    <t>Ransacker</t>
+  </si>
+  <si>
+    <t>the bare minimum</t>
+  </si>
+  <si>
+    <t>nerf's pillow</t>
+  </si>
+  <si>
+    <t>[KPK] [VN] [base]</t>
+  </si>
+  <si>
+    <t>stay safe (z)</t>
+  </si>
+  <si>
+    <t>48.7 reminder</t>
+  </si>
+  <si>
+    <t>UG</t>
+  </si>
+  <si>
+    <t>UH</t>
+  </si>
+  <si>
+    <t>UI</t>
+  </si>
+  <si>
+    <t>Grape</t>
+  </si>
+  <si>
+    <t>Nyx/Elite Skimmer</t>
+  </si>
+  <si>
+    <t>UJ</t>
+  </si>
+  <si>
+    <t>UK</t>
+  </si>
+  <si>
+    <t>Overthrower</t>
+  </si>
+  <si>
+    <t>UL</t>
+  </si>
+  <si>
+    <t>UM</t>
+  </si>
+  <si>
+    <t>UN</t>
+  </si>
+  <si>
+    <t>Auto-7</t>
+  </si>
+  <si>
+    <t>Reset</t>
+  </si>
+  <si>
+    <t>356/39294</t>
+  </si>
+  <si>
+    <t>Ares/Freyja</t>
+  </si>
+  <si>
+    <t>UO</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1485171918020808725/id_UB.png?ex=69c0e5a2&amp;is=69bf9422&amp;hm=fd778ef137f9895fb6a5d9a254df79c920e0640e1431e5d17849e4d7185aeac0</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1485171976254525471/id_UC.jpg?ex=69c0e5b0&amp;is=69bf9430&amp;hm=17c84de61cef832d0186e7923651f7bd90f41b5e3f56827923d90a88948ec71e</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1485172036585259110/id_UD.png?ex=69c0e5be&amp;is=69bf943e&amp;hm=4494de47466daab921110d8561d739254c25964032fe4d5a82e7ded1696c8e54</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1485172274511216690/id_UE.png?ex=69c0e5f7&amp;is=69bf9477&amp;hm=433bb63a78fd6c4b093c98e1e8287868e3ccbbd7766305343c45ef3768a4a748</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1485172326503940147/id_UF.png?ex=69c0e603&amp;is=69bf9483&amp;hm=66c19c39813e15b42ed185dcb70183217ee6b422b534df27423093b3e4b65f58</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1485172378165186570/id_UG.png?ex=69c0e610&amp;is=69bf9490&amp;hm=a6f576624298d9f4f53a3eeedcef88314d815f5b50f9a87b4a25f707626fb7d6</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1485172482813071530/id_UH.png?ex=69c0e629&amp;is=69bf94a9&amp;hm=2cec6bb66fe45dea2b71f1ba47e5a1c46c69dcaa21f7f3a100fd08ae8f5303a6</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1485172528916857042/id_UI.png?ex=69c0e634&amp;is=69bf94b4&amp;hm=87de073ef49bd6ddb5b2e2c6982b49a2d5bb026730ad24293757798b19dd94ff</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1485172595438653491/id_UJ.png?ex=69c0e643&amp;is=69bf94c3&amp;hm=a57f50e1dcf2a907196be2b4cdfcdb0c0ef4f55c8e5737eae7c1e93f79e6dc47</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1485172647095435417/id_UK.png?ex=69c0e650&amp;is=69bf94d0&amp;hm=bcd4fd33d20dac1e37e95b5760589b0689d654f20b5eea209403f44f3543a8d3</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1485172723880693790/id_UL.jpg?ex=69c0e662&amp;is=69bf94e2&amp;hm=91e831a3102931eb961aaf547ca9395147407652eee8951bc3220f11f7a23147</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1485172769053212804/id_UM.jpg?ex=69c0e66d&amp;is=69bf94ed&amp;hm=5bacf4d85dc6d79110bf85221add57faacabd646a65a50bc12e7b189ee0ce9cb</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1485172811646505000/id_UN.jpg?ex=69c0e677&amp;is=69bf94f7&amp;hm=ac2b209b48ccb0cc5cca44691a33bd340365e1bb833916ea616377becd485c33</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1485172856798318654/id_UO.jpg?ex=69c0e682&amp;is=69bf9502&amp;hm=3ec1edec93dc12d221be943c2446b9beb22bc65fbc48387fbfcfa95840e2bd3b</t>
   </si>
 </sst>
 </file>
@@ -11171,11 +11294,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="82" x14ac:knownFonts="1">
+  <fonts count="83" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -11778,118 +11908,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="62" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="77" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="69" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="70" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="59" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -11898,18 +12029,18 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -11923,8 +12054,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -12142,7 +12273,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1279"/>
+  <dimension ref="A1:O1293"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -21756,8 +21887,8 @@
       <c r="H224" t="s">
         <v>822</v>
       </c>
-      <c r="I224" s="91" t="s">
-        <v>813</v>
+      <c r="I224" s="131" t="s">
+        <v>820</v>
       </c>
       <c r="J224" s="63" t="s">
         <v>1325</v>
@@ -23702,8 +23833,8 @@
       <c r="H270" t="s">
         <v>1430</v>
       </c>
-      <c r="I270" s="94" t="s">
-        <v>813</v>
+      <c r="I270" s="131" t="s">
+        <v>820</v>
       </c>
       <c r="J270" s="63" t="s">
         <v>1426</v>
@@ -56197,8 +56328,8 @@
       <c r="D1056" s="37" t="s">
         <v>685</v>
       </c>
-      <c r="E1056" s="37" t="s">
-        <v>684</v>
+      <c r="E1056" s="131" t="s">
+        <v>3686</v>
       </c>
       <c r="F1056" s="29">
         <v>46020</v>
@@ -65154,7 +65285,7 @@
         <v>842</v>
       </c>
       <c r="I1274" t="s">
-        <v>813</v>
+        <v>820</v>
       </c>
       <c r="J1274" s="63" t="s">
         <v>3697</v>
@@ -65372,6 +65503,580 @@
       </c>
       <c r="N1279" t="s">
         <v>3710</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1280">
+        <v>56</v>
+      </c>
+      <c r="B1280" s="7">
+        <v>2459104</v>
+      </c>
+      <c r="C1280" t="s">
+        <v>3717</v>
+      </c>
+      <c r="D1280" t="s">
+        <v>3716</v>
+      </c>
+      <c r="E1280" t="s">
+        <v>3686</v>
+      </c>
+      <c r="F1280" s="29">
+        <v>46102</v>
+      </c>
+      <c r="G1280" s="56">
+        <v>4.4513888888888888E-2</v>
+      </c>
+      <c r="H1280" t="s">
+        <v>892</v>
+      </c>
+      <c r="I1280" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1280" s="63" t="s">
+        <v>3711</v>
+      </c>
+      <c r="K1280">
+        <v>1281</v>
+      </c>
+      <c r="M1280" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1280" t="s">
+        <v>3738</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1281">
+        <v>56</v>
+      </c>
+      <c r="B1281" s="7">
+        <v>5022558</v>
+      </c>
+      <c r="C1281" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1281" t="s">
+        <v>3716</v>
+      </c>
+      <c r="E1281" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1281" s="29">
+        <v>46102</v>
+      </c>
+      <c r="G1281" s="56">
+        <v>4.6192129629629632E-2</v>
+      </c>
+      <c r="H1281" t="s">
+        <v>3690</v>
+      </c>
+      <c r="I1281" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1281" s="63" t="s">
+        <v>3712</v>
+      </c>
+      <c r="K1281">
+        <v>1282</v>
+      </c>
+      <c r="M1281" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1281" t="s">
+        <v>3739</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1282">
+        <v>56</v>
+      </c>
+      <c r="B1282" s="7">
+        <v>38584884</v>
+      </c>
+      <c r="C1282" t="s">
+        <v>3718</v>
+      </c>
+      <c r="D1282" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1282" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1282" s="29">
+        <v>46102</v>
+      </c>
+      <c r="G1282" s="56">
+        <v>0.23178240740740741</v>
+      </c>
+      <c r="H1282" t="s">
+        <v>1115</v>
+      </c>
+      <c r="I1282" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1282" s="63" t="s">
+        <v>3713</v>
+      </c>
+      <c r="K1282">
+        <v>1283</v>
+      </c>
+      <c r="M1282" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1282" t="s">
+        <v>3740</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1283">
+        <v>56</v>
+      </c>
+      <c r="B1283" s="7">
+        <v>20008060</v>
+      </c>
+      <c r="C1283" t="s">
+        <v>3719</v>
+      </c>
+      <c r="D1283" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1283" t="s">
+        <v>113</v>
+      </c>
+      <c r="F1283" s="29">
+        <v>46101</v>
+      </c>
+      <c r="G1283" s="56" t="s">
+        <v>507</v>
+      </c>
+      <c r="H1283" t="s">
+        <v>847</v>
+      </c>
+      <c r="I1283" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1283" s="63" t="s">
+        <v>3714</v>
+      </c>
+      <c r="K1283">
+        <v>1284</v>
+      </c>
+      <c r="M1283" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1283" t="s">
+        <v>3741</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1284">
+        <v>56</v>
+      </c>
+      <c r="B1284" s="7">
+        <v>6665326</v>
+      </c>
+      <c r="C1284" t="s">
+        <v>3720</v>
+      </c>
+      <c r="D1284" t="s">
+        <v>341</v>
+      </c>
+      <c r="E1284" t="s">
+        <v>701</v>
+      </c>
+      <c r="F1284" s="29">
+        <v>46101</v>
+      </c>
+      <c r="G1284" s="56" t="s">
+        <v>507</v>
+      </c>
+      <c r="H1284" t="s">
+        <v>2040</v>
+      </c>
+      <c r="I1284" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1284" s="63" t="s">
+        <v>3715</v>
+      </c>
+      <c r="K1284">
+        <v>1285</v>
+      </c>
+      <c r="M1284" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1284" t="s">
+        <v>3742</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1285">
+        <v>56</v>
+      </c>
+      <c r="B1285" s="7">
+        <v>14678575</v>
+      </c>
+      <c r="C1285" t="s">
+        <v>3721</v>
+      </c>
+      <c r="D1285" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1285" t="s">
+        <v>237</v>
+      </c>
+      <c r="F1285" s="29">
+        <v>46102</v>
+      </c>
+      <c r="G1285" s="56">
+        <v>0.11765046296296296</v>
+      </c>
+      <c r="H1285" t="s">
+        <v>812</v>
+      </c>
+      <c r="I1285" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1285" s="63" t="s">
+        <v>3722</v>
+      </c>
+      <c r="K1285">
+        <v>1286</v>
+      </c>
+      <c r="M1285" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1285" t="s">
+        <v>3743</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1286">
+        <v>56</v>
+      </c>
+      <c r="B1286" s="7">
+        <v>22217879</v>
+      </c>
+      <c r="C1286" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1286" t="s">
+        <v>428</v>
+      </c>
+      <c r="E1286" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1286" s="29">
+        <v>46102</v>
+      </c>
+      <c r="G1286" s="56">
+        <v>0.10060185185185185</v>
+      </c>
+      <c r="H1286" t="s">
+        <v>839</v>
+      </c>
+      <c r="I1286" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1286" s="63" t="s">
+        <v>3723</v>
+      </c>
+      <c r="K1286">
+        <v>1287</v>
+      </c>
+      <c r="M1286" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1286" t="s">
+        <v>3744</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1287">
+        <v>56</v>
+      </c>
+      <c r="B1287" s="7">
+        <v>15035249</v>
+      </c>
+      <c r="C1287" t="s">
+        <v>3725</v>
+      </c>
+      <c r="D1287" t="s">
+        <v>449</v>
+      </c>
+      <c r="E1287" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1287" s="29">
+        <v>46101</v>
+      </c>
+      <c r="G1287" s="56">
+        <v>8.895833333333332E-2</v>
+      </c>
+      <c r="H1287" t="s">
+        <v>892</v>
+      </c>
+      <c r="I1287" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1287" s="63" t="s">
+        <v>3724</v>
+      </c>
+      <c r="K1287">
+        <v>1288</v>
+      </c>
+      <c r="M1287" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1287" t="s">
+        <v>3745</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1288">
+        <v>56</v>
+      </c>
+      <c r="B1288" s="7">
+        <v>4777323</v>
+      </c>
+      <c r="C1288" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1288" t="s">
+        <v>249</v>
+      </c>
+      <c r="E1288" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1288" s="29">
+        <v>46059</v>
+      </c>
+      <c r="G1288" s="56">
+        <v>0.1292939814814815</v>
+      </c>
+      <c r="H1288" t="s">
+        <v>3726</v>
+      </c>
+      <c r="I1288" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1288" s="63" t="s">
+        <v>3727</v>
+      </c>
+      <c r="K1288">
+        <v>1289</v>
+      </c>
+      <c r="M1288" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1288" t="s">
+        <v>3746</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1289">
+        <v>56</v>
+      </c>
+      <c r="B1289" s="7">
+        <v>6350136</v>
+      </c>
+      <c r="C1289" t="s">
+        <v>215</v>
+      </c>
+      <c r="D1289" t="s">
+        <v>3729</v>
+      </c>
+      <c r="E1289" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1289" s="29">
+        <v>46102</v>
+      </c>
+      <c r="G1289" s="56">
+        <v>3.8692129629629632E-2</v>
+      </c>
+      <c r="H1289" t="s">
+        <v>812</v>
+      </c>
+      <c r="I1289" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1289" s="63" t="s">
+        <v>3728</v>
+      </c>
+      <c r="K1289">
+        <v>1290</v>
+      </c>
+      <c r="M1289" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1289" t="s">
+        <v>3747</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1290">
+        <v>56</v>
+      </c>
+      <c r="B1290" s="7">
+        <v>10070998</v>
+      </c>
+      <c r="C1290" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1290" t="s">
+        <v>3733</v>
+      </c>
+      <c r="E1290" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1290" s="29">
+        <v>46102</v>
+      </c>
+      <c r="G1290" s="56">
+        <v>5.752314814814815E-2</v>
+      </c>
+      <c r="H1290" t="s">
+        <v>818</v>
+      </c>
+      <c r="I1290" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1290" s="63" t="s">
+        <v>3730</v>
+      </c>
+      <c r="K1290">
+        <v>1291</v>
+      </c>
+      <c r="M1290" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1290" t="s">
+        <v>3748</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1291">
+        <v>56</v>
+      </c>
+      <c r="B1291" s="7">
+        <v>16795093</v>
+      </c>
+      <c r="C1291" t="s">
+        <v>532</v>
+      </c>
+      <c r="D1291" t="s">
+        <v>156</v>
+      </c>
+      <c r="E1291" t="s">
+        <v>532</v>
+      </c>
+      <c r="F1291" s="29">
+        <v>46101</v>
+      </c>
+      <c r="G1291" s="56" t="s">
+        <v>507</v>
+      </c>
+      <c r="H1291" t="s">
+        <v>824</v>
+      </c>
+      <c r="I1291" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1291" s="63" t="s">
+        <v>3731</v>
+      </c>
+      <c r="K1291">
+        <v>1292</v>
+      </c>
+      <c r="M1291" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1291" t="s">
+        <v>3749</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1292">
+        <v>56</v>
+      </c>
+      <c r="B1292" s="7">
+        <v>18118243</v>
+      </c>
+      <c r="C1292" t="s">
+        <v>532</v>
+      </c>
+      <c r="D1292" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1292" t="s">
+        <v>532</v>
+      </c>
+      <c r="F1292" s="29">
+        <v>46102</v>
+      </c>
+      <c r="G1292" s="56" t="s">
+        <v>507</v>
+      </c>
+      <c r="H1292" t="s">
+        <v>3734</v>
+      </c>
+      <c r="I1292" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1292" s="63" t="s">
+        <v>3732</v>
+      </c>
+      <c r="K1292">
+        <v>1293</v>
+      </c>
+      <c r="M1292" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1292" t="s">
+        <v>3750</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1293">
+        <v>56</v>
+      </c>
+      <c r="B1293" s="7">
+        <v>6886047</v>
+      </c>
+      <c r="C1293" t="s">
+        <v>3735</v>
+      </c>
+      <c r="D1293" t="s">
+        <v>3729</v>
+      </c>
+      <c r="E1293" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1293" s="29">
+        <v>46102</v>
+      </c>
+      <c r="G1293" s="56">
+        <v>4.3784722222222218E-2</v>
+      </c>
+      <c r="H1293" t="s">
+        <v>3736</v>
+      </c>
+      <c r="I1293" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1293" s="63" t="s">
+        <v>3737</v>
+      </c>
+      <c r="K1293">
+        <v>1294</v>
+      </c>
+      <c r="M1293" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1293" t="s">
+        <v>3751</v>
       </c>
     </row>
   </sheetData>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10736" uniqueCount="3752">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10744" uniqueCount="3758">
   <si>
     <t>Ņ</t>
   </si>
@@ -11283,6 +11283,24 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1485172856798318654/id_UO.jpg?ex=69c0e682&amp;is=69bf9502&amp;hm=3ec1edec93dc12d221be943c2446b9beb22bc65fbc48387fbfcfa95840e2bd3b</t>
+  </si>
+  <si>
+    <t>LeBen</t>
+  </si>
+  <si>
+    <t>UP</t>
+  </si>
+  <si>
+    <t>yt(10m hexer?)</t>
+  </si>
+  <si>
+    <t>Hexer</t>
+  </si>
+  <si>
+    <t>Ares/Theia/Selene</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1485201000452325478/id_UP.png?ex=69c100b8&amp;is=69bfaf38&amp;hm=f53202dbe178fca599fcc42d6411535b3be3a3442714508941447c954a40c36d</t>
   </si>
 </sst>
 </file>
@@ -12273,7 +12291,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1293"/>
+  <dimension ref="A1:O1294"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -65519,7 +65537,7 @@
         <v>3716</v>
       </c>
       <c r="E1280" t="s">
-        <v>3686</v>
+        <v>3752</v>
       </c>
       <c r="F1280" s="29">
         <v>46102</v>
@@ -66077,6 +66095,47 @@
       </c>
       <c r="N1293" t="s">
         <v>3751</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1294">
+        <v>56</v>
+      </c>
+      <c r="B1294" s="7">
+        <v>1778128</v>
+      </c>
+      <c r="C1294" t="s">
+        <v>3754</v>
+      </c>
+      <c r="D1294" t="s">
+        <v>3755</v>
+      </c>
+      <c r="E1294" t="s">
+        <v>219</v>
+      </c>
+      <c r="F1294" s="29">
+        <v>46103</v>
+      </c>
+      <c r="G1294" s="56">
+        <v>6.6203703703703709E-2</v>
+      </c>
+      <c r="H1294" t="s">
+        <v>3756</v>
+      </c>
+      <c r="I1294" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1294" s="63" t="s">
+        <v>3753</v>
+      </c>
+      <c r="K1294">
+        <v>1295</v>
+      </c>
+      <c r="M1294" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1294" t="s">
+        <v>3757</v>
       </c>
     </row>
   </sheetData>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10744" uniqueCount="3758">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10784" uniqueCount="3772">
   <si>
     <t>Ņ</t>
   </si>
@@ -11301,6 +11301,48 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1485201000452325478/id_UP.png?ex=69c100b8&amp;is=69bfaf38&amp;hm=f53202dbe178fca599fcc42d6411535b3be3a3442714508941447c954a40c36d</t>
+  </si>
+  <si>
+    <t>UQ</t>
+  </si>
+  <si>
+    <t>Crank</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1485270745721340075/id_UQ.png?ex=69c141ac&amp;is=69bff02c&amp;hm=06817434216c5c5b2327d6dc9815ab2026ce64483cfaabf8421446b69a9025e9</t>
+  </si>
+  <si>
+    <t>Supplant</t>
+  </si>
+  <si>
+    <t>UR</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>Nest Guardian/Summoner/Elite Crasher</t>
+  </si>
+  <si>
+    <t>Nest Warden/Paladin</t>
+  </si>
+  <si>
+    <t>UT</t>
+  </si>
+  <si>
+    <t>UU</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1485582086487277568/id_UR.png?ex=69c263a2&amp;is=69c11222&amp;hm=1d71aed3bcc45d1d02750fc7388c2fd00266f72cbec46cacbf43fdc67fdd11a8</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1485582152736440361/id_US.png?ex=69c263b1&amp;is=69c11231&amp;hm=f1f4da98bc8e1aa248349e4fcc1bd70f6c824febd341e1e49984adf3b2de4b22</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1485582261536686100/id_UT.png?ex=69c263cb&amp;is=69c1124b&amp;hm=a399ef131f3e77950ba058c22aa182a722fa8bb23367a690bb45e25ae8f5db4b</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1485582309775114253/id_UU.jpg?ex=69c263d7&amp;is=69c11257&amp;hm=7a9a1255dde91dd7c285cba390233e6259deddcf863ea8814999e44d9565e635</t>
   </si>
 </sst>
 </file>
@@ -11312,11 +11354,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="83" x14ac:knownFonts="1">
+  <fonts count="84" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -11926,118 +11975,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="70" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="71" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="48" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -12046,18 +12096,18 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -12071,8 +12121,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
@@ -12291,7 +12341,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1294"/>
+  <dimension ref="A1:O1299"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -25285,7 +25335,7 @@
       <c r="B305" s="7">
         <v>18377129</v>
       </c>
-      <c r="C305" s="14" t="s">
+      <c r="C305" s="132" t="s">
         <v>444</v>
       </c>
       <c r="D305" s="16" t="s">
@@ -66136,6 +66186,211 @@
       </c>
       <c r="N1294" t="s">
         <v>3757</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1295">
+        <v>56</v>
+      </c>
+      <c r="B1295" s="7">
+        <v>3257914</v>
+      </c>
+      <c r="C1295" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1295" t="s">
+        <v>3759</v>
+      </c>
+      <c r="E1295" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1295" s="29">
+        <v>46102</v>
+      </c>
+      <c r="G1295" s="56">
+        <v>6.7465277777777777E-2</v>
+      </c>
+      <c r="H1295" t="s">
+        <v>1870</v>
+      </c>
+      <c r="I1295" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1295" s="63" t="s">
+        <v>3758</v>
+      </c>
+      <c r="K1295">
+        <v>1296</v>
+      </c>
+      <c r="M1295" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1295" t="s">
+        <v>3760</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1296">
+        <v>56</v>
+      </c>
+      <c r="B1296" s="7">
+        <v>3783921</v>
+      </c>
+      <c r="C1296" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1296" t="s">
+        <v>3761</v>
+      </c>
+      <c r="E1296" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1296" s="29">
+        <v>46103</v>
+      </c>
+      <c r="G1296" s="56">
+        <v>4.9733796296296297E-2</v>
+      </c>
+      <c r="H1296" t="s">
+        <v>2832</v>
+      </c>
+      <c r="I1296" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1296" s="63" t="s">
+        <v>3762</v>
+      </c>
+      <c r="K1296">
+        <v>1297</v>
+      </c>
+      <c r="M1296" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1296" t="s">
+        <v>3768</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1297">
+        <v>56</v>
+      </c>
+      <c r="B1297" s="7">
+        <v>1939606</v>
+      </c>
+      <c r="C1297" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1297" t="s">
+        <v>691</v>
+      </c>
+      <c r="E1297" t="s">
+        <v>437</v>
+      </c>
+      <c r="F1297" s="29">
+        <v>46104</v>
+      </c>
+      <c r="G1297" s="56">
+        <v>3.6064814814814813E-2</v>
+      </c>
+      <c r="H1297" t="s">
+        <v>3764</v>
+      </c>
+      <c r="I1297" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1297" s="63" t="s">
+        <v>3763</v>
+      </c>
+      <c r="K1297">
+        <v>1298</v>
+      </c>
+      <c r="M1297" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1297" t="s">
+        <v>3769</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1298">
+        <v>56</v>
+      </c>
+      <c r="B1298" s="7">
+        <v>13166025</v>
+      </c>
+      <c r="C1298" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D1298" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1298" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1298" s="29">
+        <v>46104</v>
+      </c>
+      <c r="G1298" s="56">
+        <v>9.1122685185185182E-2</v>
+      </c>
+      <c r="H1298" t="s">
+        <v>3765</v>
+      </c>
+      <c r="I1298" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1298" s="63" t="s">
+        <v>3766</v>
+      </c>
+      <c r="K1298">
+        <v>1299</v>
+      </c>
+      <c r="M1298" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1298" t="s">
+        <v>3770</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1299">
+        <v>56</v>
+      </c>
+      <c r="B1299" s="7">
+        <v>25358803</v>
+      </c>
+      <c r="C1299" t="s">
+        <v>3544</v>
+      </c>
+      <c r="D1299" t="s">
+        <v>428</v>
+      </c>
+      <c r="E1299" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1299" s="29">
+        <v>46104</v>
+      </c>
+      <c r="G1299" s="56">
+        <v>0.13155092592592593</v>
+      </c>
+      <c r="H1299" t="s">
+        <v>2468</v>
+      </c>
+      <c r="I1299" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1299" s="63" t="s">
+        <v>3767</v>
+      </c>
+      <c r="K1299">
+        <v>1300</v>
+      </c>
+      <c r="M1299" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1299" t="s">
+        <v>3771</v>
       </c>
     </row>
   </sheetData>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10784" uniqueCount="3772">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10808" uniqueCount="3784">
   <si>
     <t>Ņ</t>
   </si>
@@ -11343,6 +11343,42 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1485582309775114253/id_UU.jpg?ex=69c263d7&amp;is=69c11257&amp;hm=7a9a1255dde91dd7c285cba390233e6259deddcf863ea8814999e44d9565e635</t>
+  </si>
+  <si>
+    <t>Elite Crasher/Freyja</t>
+  </si>
+  <si>
+    <t>UV</t>
+  </si>
+  <si>
+    <t>UW</t>
+  </si>
+  <si>
+    <t>UX</t>
+  </si>
+  <si>
+    <t>Rifle</t>
+  </si>
+  <si>
+    <t>Hunter</t>
+  </si>
+  <si>
+    <t>Assassin</t>
+  </si>
+  <si>
+    <t>Elite Crasher/Ragnarok/Freyja</t>
+  </si>
+  <si>
+    <t>[o]</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1486032558490648636/id_UV.png?ex=69c4072b&amp;is=69c2b5ab&amp;hm=73aae71e30c63234bfd187b535e03661f174e6952b79f80e90794c14b16f1b26</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1486032639566676038/id_UW.png?ex=69c4073e&amp;is=69c2b5be&amp;hm=294889b483ea1c9a85d47e17f2c3f8a0f6deb1c630b6f1e5611165977cdd3fbe</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1486032699398426845/id_UX.png?ex=69c4074c&amp;is=69c2b5cc&amp;hm=f109d19e803f55e8e5309196307ac13d77327319b784901726b59e83855e21de</t>
   </si>
 </sst>
 </file>
@@ -11354,11 +11390,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="84" x14ac:knownFonts="1">
+  <fonts count="85" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -11975,118 +12018,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="134">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="81" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="71" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="72" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="66" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="62" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="48" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="49" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -12095,18 +12139,18 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -12120,8 +12164,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -12341,7 +12385,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1299"/>
+  <dimension ref="A1:O1302"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -66393,6 +66437,129 @@
         <v>3771</v>
       </c>
     </row>
+    <row r="1300" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1300">
+        <v>56</v>
+      </c>
+      <c r="B1300" s="7">
+        <v>4897611</v>
+      </c>
+      <c r="C1300" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1300" t="s">
+        <v>3776</v>
+      </c>
+      <c r="E1300" t="s">
+        <v>437</v>
+      </c>
+      <c r="F1300" s="29">
+        <v>46105</v>
+      </c>
+      <c r="G1300" s="56">
+        <v>6.4432870370370363E-2</v>
+      </c>
+      <c r="H1300" t="s">
+        <v>3772</v>
+      </c>
+      <c r="I1300" t="s">
+        <v>293</v>
+      </c>
+      <c r="J1300" s="63" t="s">
+        <v>3773</v>
+      </c>
+      <c r="K1300">
+        <v>1301</v>
+      </c>
+      <c r="M1300" s="133" t="s">
+        <v>3780</v>
+      </c>
+      <c r="N1300" t="s">
+        <v>3781</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1301">
+        <v>56</v>
+      </c>
+      <c r="B1301" s="7">
+        <v>2093108</v>
+      </c>
+      <c r="C1301" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1301" t="s">
+        <v>3777</v>
+      </c>
+      <c r="E1301" t="s">
+        <v>437</v>
+      </c>
+      <c r="F1301" s="29">
+        <v>46105</v>
+      </c>
+      <c r="G1301" s="56">
+        <v>4.6724537037037044E-2</v>
+      </c>
+      <c r="H1301" t="s">
+        <v>944</v>
+      </c>
+      <c r="I1301" t="s">
+        <v>293</v>
+      </c>
+      <c r="J1301" s="63" t="s">
+        <v>3774</v>
+      </c>
+      <c r="K1301">
+        <v>1302</v>
+      </c>
+      <c r="M1301" s="133" t="s">
+        <v>3780</v>
+      </c>
+      <c r="N1301" t="s">
+        <v>3782</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1302">
+        <v>56</v>
+      </c>
+      <c r="B1302" s="7">
+        <v>3365501</v>
+      </c>
+      <c r="C1302" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1302" t="s">
+        <v>3778</v>
+      </c>
+      <c r="E1302" t="s">
+        <v>437</v>
+      </c>
+      <c r="F1302" s="29">
+        <v>46105</v>
+      </c>
+      <c r="G1302" s="56">
+        <v>5.5960648148148141E-2</v>
+      </c>
+      <c r="H1302" t="s">
+        <v>3779</v>
+      </c>
+      <c r="I1302" t="s">
+        <v>293</v>
+      </c>
+      <c r="J1302" s="63" t="s">
+        <v>3775</v>
+      </c>
+      <c r="K1302">
+        <v>1303</v>
+      </c>
+      <c r="M1302" s="133" t="s">
+        <v>3780</v>
+      </c>
+      <c r="N1302" t="s">
+        <v>3783</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N1">
     <sortState ref="A2:N1264">

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10808" uniqueCount="3784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10872" uniqueCount="3806">
   <si>
     <t>Ņ</t>
   </si>
@@ -11369,9 +11369,6 @@
     <t>Elite Crasher/Ragnarok/Freyja</t>
   </si>
   <si>
-    <t>[o]</t>
-  </si>
-  <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1486032558490648636/id_UV.png?ex=69c4072b&amp;is=69c2b5ab&amp;hm=73aae71e30c63234bfd187b535e03661f174e6952b79f80e90794c14b16f1b26</t>
   </si>
   <si>
@@ -11379,6 +11376,75 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1486032699398426845/id_UX.png?ex=69c4074c&amp;is=69c2b5cc&amp;hm=f109d19e803f55e8e5309196307ac13d77327319b784901726b59e83855e21de</t>
+  </si>
+  <si>
+    <t>UY</t>
+  </si>
+  <si>
+    <t>UZ</t>
+  </si>
+  <si>
+    <t>Ua</t>
+  </si>
+  <si>
+    <t>Ub</t>
+  </si>
+  <si>
+    <t>Uc</t>
+  </si>
+  <si>
+    <t>Mortar</t>
+  </si>
+  <si>
+    <t>Nimrod</t>
+  </si>
+  <si>
+    <t>Falcon</t>
+  </si>
+  <si>
+    <t>[note][arowy]heart[star][something]</t>
+  </si>
+  <si>
+    <t>Ud</t>
+  </si>
+  <si>
+    <t>Ue</t>
+  </si>
+  <si>
+    <t>Deadeye</t>
+  </si>
+  <si>
+    <t>Ranger</t>
+  </si>
+  <si>
+    <t>Selene/Ezekiel</t>
+  </si>
+  <si>
+    <t>Uf</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1486429418430664876/id_UY.png?ex=69c578c5&amp;is=69c42745&amp;hm=e98d66b59a8d227dbe5e7a988286fc75a95a85a52e2f91331fce2544f26bf7cd</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1486429487166918686/id_UZ.png?ex=69c578d6&amp;is=69c42756&amp;hm=8cefe405a02382b788b713584b0edb71952bf55582c8dc8d25294cc9720d3a41</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1486429639655161986/id_Ua.png?ex=69c578fa&amp;is=69c4277a&amp;hm=34e255909935467e936d4c448e9fa8d38107641c9e3c1ab58c5c09d61102b1f0</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1486431586038710525/id_Ub.png?ex=69c57aca&amp;is=69c4294a&amp;hm=de61363a3e2f0833822d1117a456d2381c7a0961035315f98ba43515ee6c0a4b</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1486431636307447950/id_Uc.jpg?ex=69c57ad6&amp;is=69c42956&amp;hm=b441b930bcb5b35942671d9323a4081186eb726c28d15f5bab4f81e63cdfc30e</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1486431696009302096/id_Ud.png?ex=69c57ae4&amp;is=69c42964&amp;hm=d16baf427a3aacf80ad6a7263d9c2756f09ebb699217560d87528d33f1eff26b</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1486431764158218321/id_Ue.png?ex=69c57af5&amp;is=69c42975&amp;hm=78dcacae1bc63291228fff349d7ff21ef9c7ff7a0bf0f8bdcaca32775abcda90</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1486431823151108137/id_Uf.png?ex=69c57b03&amp;is=69c42983&amp;hm=ed458a1dd0b4e27de51aef72675e87e99add56c939d9555d25e4e6d0321c9f6d</t>
   </si>
 </sst>
 </file>
@@ -11390,18 +11456,11 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="85" x14ac:knownFonts="1">
+  <fonts count="84" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -12018,119 +12077,118 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="134">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="81" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="71" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="72" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="66" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="62" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="49" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="48" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -12139,18 +12197,18 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -12164,8 +12222,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -12385,7 +12443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1302"/>
+  <dimension ref="A1:O1310"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -66471,11 +66529,11 @@
       <c r="K1300">
         <v>1301</v>
       </c>
-      <c r="M1300" s="133" t="s">
+      <c r="M1300" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1300" t="s">
         <v>3780</v>
-      </c>
-      <c r="N1300" t="s">
-        <v>3781</v>
       </c>
     </row>
     <row r="1301" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66512,11 +66570,11 @@
       <c r="K1301">
         <v>1302</v>
       </c>
-      <c r="M1301" s="133" t="s">
-        <v>3780</v>
+      <c r="M1301" s="57" t="s">
+        <v>861</v>
       </c>
       <c r="N1301" t="s">
-        <v>3782</v>
+        <v>3781</v>
       </c>
     </row>
     <row r="1302" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66553,11 +66611,339 @@
       <c r="K1302">
         <v>1303</v>
       </c>
-      <c r="M1302" s="133" t="s">
-        <v>3780</v>
+      <c r="M1302" s="57" t="s">
+        <v>861</v>
       </c>
       <c r="N1302" t="s">
+        <v>3782</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1303">
+        <v>56</v>
+      </c>
+      <c r="B1303" s="7">
+        <v>6170578</v>
+      </c>
+      <c r="C1303" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1303" t="s">
+        <v>3788</v>
+      </c>
+      <c r="E1303">
+        <v>44100</v>
+      </c>
+      <c r="F1303" s="29">
+        <v>46105</v>
+      </c>
+      <c r="G1303" s="56">
+        <v>5.6134259259259266E-2</v>
+      </c>
+      <c r="H1303" t="s">
+        <v>949</v>
+      </c>
+      <c r="I1303" t="s">
+        <v>293</v>
+      </c>
+      <c r="J1303" s="63" t="s">
         <v>3783</v>
+      </c>
+      <c r="K1303">
+        <v>1304</v>
+      </c>
+      <c r="M1303" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1303" t="s">
+        <v>3798</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1304">
+        <v>56</v>
+      </c>
+      <c r="B1304" s="7">
+        <v>2194932</v>
+      </c>
+      <c r="C1304" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1304" t="s">
+        <v>3789</v>
+      </c>
+      <c r="E1304" t="s">
+        <v>437</v>
+      </c>
+      <c r="F1304" s="29">
+        <v>46106</v>
+      </c>
+      <c r="G1304" s="56">
+        <v>2.3715277777777776E-2</v>
+      </c>
+      <c r="H1304" t="s">
+        <v>840</v>
+      </c>
+      <c r="I1304" t="s">
+        <v>293</v>
+      </c>
+      <c r="J1304" s="63" t="s">
+        <v>3784</v>
+      </c>
+      <c r="K1304">
+        <v>1305</v>
+      </c>
+      <c r="M1304" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1304" t="s">
+        <v>3799</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1305">
+        <v>56</v>
+      </c>
+      <c r="B1305" s="7">
+        <v>2297567</v>
+      </c>
+      <c r="C1305" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1305" t="s">
+        <v>3790</v>
+      </c>
+      <c r="E1305" t="s">
+        <v>437</v>
+      </c>
+      <c r="F1305" s="29">
+        <v>46106</v>
+      </c>
+      <c r="G1305" s="56">
+        <v>2.0208333333333335E-2</v>
+      </c>
+      <c r="H1305" t="s">
+        <v>839</v>
+      </c>
+      <c r="I1305" t="s">
+        <v>293</v>
+      </c>
+      <c r="J1305" s="63" t="s">
+        <v>3785</v>
+      </c>
+      <c r="K1305">
+        <v>1306</v>
+      </c>
+      <c r="M1305" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1305" t="s">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1306">
+        <v>56</v>
+      </c>
+      <c r="B1306" s="7">
+        <v>9033862</v>
+      </c>
+      <c r="C1306" t="s">
+        <v>3791</v>
+      </c>
+      <c r="D1306" t="s">
+        <v>409</v>
+      </c>
+      <c r="E1306" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1306" s="29">
+        <v>46106</v>
+      </c>
+      <c r="G1306" s="56">
+        <v>6.6458333333333341E-2</v>
+      </c>
+      <c r="H1306" t="s">
+        <v>812</v>
+      </c>
+      <c r="I1306" t="s">
+        <v>293</v>
+      </c>
+      <c r="J1306" s="63" t="s">
+        <v>3786</v>
+      </c>
+      <c r="K1306">
+        <v>1307</v>
+      </c>
+      <c r="M1306" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1306" t="s">
+        <v>3801</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1307">
+        <v>56</v>
+      </c>
+      <c r="B1307" s="7">
+        <v>12760795</v>
+      </c>
+      <c r="C1307" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1307" t="s">
+        <v>375</v>
+      </c>
+      <c r="E1307" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1307" s="29">
+        <v>46106</v>
+      </c>
+      <c r="G1307" s="56">
+        <v>0.1007986111111111</v>
+      </c>
+      <c r="H1307" t="s">
+        <v>2466</v>
+      </c>
+      <c r="I1307" t="s">
+        <v>293</v>
+      </c>
+      <c r="J1307" s="63" t="s">
+        <v>3787</v>
+      </c>
+      <c r="K1307">
+        <v>1308</v>
+      </c>
+      <c r="M1307" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1307" t="s">
+        <v>3802</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1308">
+        <v>56</v>
+      </c>
+      <c r="B1308" s="7">
+        <v>4186799</v>
+      </c>
+      <c r="C1308" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1308" t="s">
+        <v>3794</v>
+      </c>
+      <c r="E1308" t="s">
+        <v>437</v>
+      </c>
+      <c r="F1308" s="29">
+        <v>46106</v>
+      </c>
+      <c r="G1308" s="56">
+        <v>5.935185185185185E-2</v>
+      </c>
+      <c r="H1308" t="s">
+        <v>818</v>
+      </c>
+      <c r="I1308" t="s">
+        <v>293</v>
+      </c>
+      <c r="J1308" s="63" t="s">
+        <v>3792</v>
+      </c>
+      <c r="K1308">
+        <v>1309</v>
+      </c>
+      <c r="M1308" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1308" t="s">
+        <v>3803</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1309">
+        <v>56</v>
+      </c>
+      <c r="B1309" s="7">
+        <v>2748550</v>
+      </c>
+      <c r="C1309" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1309" t="s">
+        <v>3795</v>
+      </c>
+      <c r="E1309" t="s">
+        <v>437</v>
+      </c>
+      <c r="F1309" s="29">
+        <v>46106</v>
+      </c>
+      <c r="G1309" s="56">
+        <v>4.2546296296296297E-2</v>
+      </c>
+      <c r="H1309" t="s">
+        <v>3796</v>
+      </c>
+      <c r="I1309" t="s">
+        <v>293</v>
+      </c>
+      <c r="J1309" s="63" t="s">
+        <v>3793</v>
+      </c>
+      <c r="K1309">
+        <v>1310</v>
+      </c>
+      <c r="M1309" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1309" t="s">
+        <v>3804</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1310">
+        <v>56</v>
+      </c>
+      <c r="B1310" s="7">
+        <v>17210000</v>
+      </c>
+      <c r="C1310" t="s">
+        <v>1738</v>
+      </c>
+      <c r="D1310" t="s">
+        <v>451</v>
+      </c>
+      <c r="E1310" t="s">
+        <v>178</v>
+      </c>
+      <c r="F1310" s="29">
+        <v>45839</v>
+      </c>
+      <c r="G1310" s="56" t="s">
+        <v>507</v>
+      </c>
+      <c r="H1310" t="s">
+        <v>507</v>
+      </c>
+      <c r="I1310" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1310" s="63" t="s">
+        <v>3797</v>
+      </c>
+      <c r="K1310">
+        <v>1311</v>
+      </c>
+      <c r="M1310" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1310" t="s">
+        <v>3805</v>
       </c>
     </row>
   </sheetData>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10872" uniqueCount="3806">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10904" uniqueCount="3815">
   <si>
     <t>Ņ</t>
   </si>
@@ -11445,6 +11445,33 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1486431823151108137/id_Uf.png?ex=69c57b03&amp;is=69c42983&amp;hm=ed458a1dd0b4e27de51aef72675e87e99add56c939d9555d25e4e6d0321c9f6d</t>
+  </si>
+  <si>
+    <t>Ug</t>
+  </si>
+  <si>
+    <t>Uh</t>
+  </si>
+  <si>
+    <t>Ui</t>
+  </si>
+  <si>
+    <t>miyaka .:</t>
+  </si>
+  <si>
+    <t>Uj</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1487022214589972510/id_Ug.png?ex=69c7a0db&amp;is=69c64f5b&amp;hm=33a22e9947ff5ac6aa1f2b73368ce7bf7893b643967224914229a72270859cb5</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1487022273998356520/id_Uh.jpg?ex=69c7a0e9&amp;is=69c64f69&amp;hm=cac610ab910555de32398c9e4fa43c0ce66345defa914f37d83ef26b1056e09b</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1487022333104488582/id_Ui.png?ex=69c7a0f7&amp;is=69c64f77&amp;hm=33a199e6222ae2a44b48d0ae8b29e79302429c6c38abc8126c9283f2900de29e</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1487022394290737333/id_Uj.jpg?ex=69c7a106&amp;is=69c64f86&amp;hm=5f1337d00354c7f792d1e864848c51de60dd07e853d0419ab5711ba8cb61ce95</t>
   </si>
 </sst>
 </file>
@@ -12443,7 +12470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1310"/>
+  <dimension ref="A1:O1314"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -66946,6 +66973,170 @@
         <v>3805</v>
       </c>
     </row>
+    <row r="1311" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1311">
+        <v>56</v>
+      </c>
+      <c r="B1311" s="7">
+        <v>3158962</v>
+      </c>
+      <c r="C1311" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1311" t="s">
+        <v>666</v>
+      </c>
+      <c r="E1311" t="s">
+        <v>654</v>
+      </c>
+      <c r="F1311" s="29">
+        <v>46108</v>
+      </c>
+      <c r="G1311" s="56">
+        <v>1.5219907407407409E-2</v>
+      </c>
+      <c r="H1311" t="s">
+        <v>892</v>
+      </c>
+      <c r="I1311" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1311" s="63" t="s">
+        <v>3806</v>
+      </c>
+      <c r="K1311">
+        <v>1312</v>
+      </c>
+      <c r="M1311" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1311" t="s">
+        <v>3811</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1312">
+        <v>56</v>
+      </c>
+      <c r="B1312" s="7">
+        <v>37031763</v>
+      </c>
+      <c r="C1312" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1312" t="s">
+        <v>449</v>
+      </c>
+      <c r="E1312" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1312" s="29">
+        <v>46108</v>
+      </c>
+      <c r="G1312" s="56">
+        <v>0.21887731481481479</v>
+      </c>
+      <c r="H1312" t="s">
+        <v>822</v>
+      </c>
+      <c r="I1312" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1312" s="63" t="s">
+        <v>3807</v>
+      </c>
+      <c r="K1312">
+        <v>1313</v>
+      </c>
+      <c r="M1312" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1312" t="s">
+        <v>3812</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1313">
+        <v>56</v>
+      </c>
+      <c r="B1313" s="7">
+        <v>15142034</v>
+      </c>
+      <c r="C1313" t="s">
+        <v>3809</v>
+      </c>
+      <c r="D1313" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1313" t="s">
+        <v>737</v>
+      </c>
+      <c r="F1313" s="29">
+        <v>46108</v>
+      </c>
+      <c r="G1313" s="56">
+        <v>6.293981481481481E-2</v>
+      </c>
+      <c r="H1313" t="s">
+        <v>812</v>
+      </c>
+      <c r="I1313" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1313" s="63" t="s">
+        <v>3808</v>
+      </c>
+      <c r="K1313">
+        <v>1314</v>
+      </c>
+      <c r="M1313" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1313" t="s">
+        <v>3813</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1314">
+        <v>56</v>
+      </c>
+      <c r="B1314" s="7">
+        <v>28555960</v>
+      </c>
+      <c r="C1314" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1314" t="s">
+        <v>333</v>
+      </c>
+      <c r="E1314" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1314" s="29">
+        <v>46108</v>
+      </c>
+      <c r="G1314" s="56">
+        <v>0.19980324074074074</v>
+      </c>
+      <c r="H1314" t="s">
+        <v>812</v>
+      </c>
+      <c r="I1314" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1314" s="63" t="s">
+        <v>3810</v>
+      </c>
+      <c r="K1314">
+        <v>1315</v>
+      </c>
+      <c r="M1314" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1314" t="s">
+        <v>3814</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N1">
     <sortState ref="A2:N1264">

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10904" uniqueCount="3815">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11023" uniqueCount="3840">
   <si>
     <t>Ņ</t>
   </si>
@@ -11472,6 +11472,81 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1487022394290737333/id_Uj.jpg?ex=69c7a106&amp;is=69c64f86&amp;hm=5f1337d00354c7f792d1e864848c51de60dd07e853d0419ab5711ba8cb61ce95</t>
+  </si>
+  <si>
+    <t>Uk</t>
+  </si>
+  <si>
+    <t>Ul</t>
+  </si>
+  <si>
+    <t>snowblind</t>
+  </si>
+  <si>
+    <t>Um</t>
+  </si>
+  <si>
+    <t>Un</t>
+  </si>
+  <si>
+    <t>Triple Auto-Artillery</t>
+  </si>
+  <si>
+    <t>Uo</t>
+  </si>
+  <si>
+    <t>Up</t>
+  </si>
+  <si>
+    <t>Uq</t>
+  </si>
+  <si>
+    <t>Ur</t>
+  </si>
+  <si>
+    <t>Us</t>
+  </si>
+  <si>
+    <t>Ut</t>
+  </si>
+  <si>
+    <t>Uu</t>
+  </si>
+  <si>
+    <t>Triple Auto-Doper</t>
+  </si>
+  <si>
+    <t>Uv</t>
+  </si>
+  <si>
+    <t>Uw</t>
+  </si>
+  <si>
+    <t>Ux</t>
+  </si>
+  <si>
+    <t>Uy</t>
+  </si>
+  <si>
+    <t>Uz</t>
+  </si>
+  <si>
+    <t>Eliete Crasher/Nest Warden</t>
+  </si>
+  <si>
+    <t>U0</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>ƒ(x) = ax+b A</t>
+  </si>
+  <si>
+    <t>ƒ(x) = ax+b</t>
+  </si>
+  <si>
+    <t>U2</t>
   </si>
 </sst>
 </file>
@@ -11483,11 +11558,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="84" x14ac:knownFonts="1">
+  <fonts count="85" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -12104,118 +12186,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="81" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="71" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="72" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="66" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="62" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="48" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="49" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -12224,18 +12307,18 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -12249,11 +12332,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -12470,7 +12554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1314"/>
+  <dimension ref="A1:O1333"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -23649,7 +23733,7 @@
         <v>0.20160879629629633</v>
       </c>
       <c r="H261" t="s">
-        <v>1477</v>
+        <v>1329</v>
       </c>
       <c r="I261" s="94" t="s">
         <v>813</v>
@@ -67135,6 +67219,671 @@
       </c>
       <c r="N1314" t="s">
         <v>3814</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1315">
+        <v>47</v>
+      </c>
+      <c r="B1315" s="7">
+        <v>25850000</v>
+      </c>
+      <c r="C1315" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1315" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1315" t="s">
+        <v>113</v>
+      </c>
+      <c r="F1315" s="29">
+        <v>46110</v>
+      </c>
+      <c r="G1315" s="56" t="s">
+        <v>507</v>
+      </c>
+      <c r="H1315" t="s">
+        <v>507</v>
+      </c>
+      <c r="I1315" t="s">
+        <v>813</v>
+      </c>
+      <c r="K1315">
+        <v>1316</v>
+      </c>
+      <c r="M1315" s="63" t="s">
+        <v>3815</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1316">
+        <v>47</v>
+      </c>
+      <c r="B1316" s="7">
+        <v>19610000</v>
+      </c>
+      <c r="C1316" t="s">
+        <v>712</v>
+      </c>
+      <c r="D1316" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1316" t="s">
+        <v>712</v>
+      </c>
+      <c r="F1316" s="29">
+        <v>46110</v>
+      </c>
+      <c r="G1316" s="56" t="s">
+        <v>507</v>
+      </c>
+      <c r="H1316" t="s">
+        <v>507</v>
+      </c>
+      <c r="I1316" t="s">
+        <v>813</v>
+      </c>
+      <c r="K1316">
+        <v>1317</v>
+      </c>
+      <c r="M1316" s="63" t="s">
+        <v>3816</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1317">
+        <v>47</v>
+      </c>
+      <c r="B1317" s="7">
+        <v>61493897</v>
+      </c>
+      <c r="C1317" t="s">
+        <v>3817</v>
+      </c>
+      <c r="D1317" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1317" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1317" s="29">
+        <v>46110</v>
+      </c>
+      <c r="G1317" s="56">
+        <v>0.55304398148148148</v>
+      </c>
+      <c r="H1317" t="s">
+        <v>812</v>
+      </c>
+      <c r="I1317" t="s">
+        <v>813</v>
+      </c>
+      <c r="K1317">
+        <v>1318</v>
+      </c>
+      <c r="M1317" s="63" t="s">
+        <v>3818</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1318">
+        <v>47</v>
+      </c>
+      <c r="B1318" s="7">
+        <v>20384040</v>
+      </c>
+      <c r="C1318" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1318" t="s">
+        <v>3820</v>
+      </c>
+      <c r="E1318" t="s">
+        <v>3439</v>
+      </c>
+      <c r="F1318" s="29">
+        <v>46109</v>
+      </c>
+      <c r="G1318" s="56">
+        <v>0.13681712962962964</v>
+      </c>
+      <c r="H1318" t="s">
+        <v>972</v>
+      </c>
+      <c r="I1318" t="s">
+        <v>813</v>
+      </c>
+      <c r="K1318">
+        <v>1319</v>
+      </c>
+      <c r="M1318" s="63" t="s">
+        <v>3819</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1319">
+        <v>47</v>
+      </c>
+      <c r="B1319" s="7">
+        <v>9444194</v>
+      </c>
+      <c r="C1319" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1319" t="s">
+        <v>673</v>
+      </c>
+      <c r="E1319" t="s">
+        <v>701</v>
+      </c>
+      <c r="F1319" s="29">
+        <v>46109</v>
+      </c>
+      <c r="G1319" s="56">
+        <v>9.087962962962963E-2</v>
+      </c>
+      <c r="H1319" t="s">
+        <v>839</v>
+      </c>
+      <c r="I1319" t="s">
+        <v>813</v>
+      </c>
+      <c r="K1319">
+        <v>1320</v>
+      </c>
+      <c r="M1319" s="63" t="s">
+        <v>3821</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1320">
+        <v>47</v>
+      </c>
+      <c r="B1320" s="7">
+        <v>12003090</v>
+      </c>
+      <c r="C1320" t="s">
+        <v>237</v>
+      </c>
+      <c r="D1320" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1320" t="s">
+        <v>237</v>
+      </c>
+      <c r="F1320" s="29">
+        <v>46109</v>
+      </c>
+      <c r="G1320" s="56">
+        <v>9.555555555555556E-2</v>
+      </c>
+      <c r="H1320" t="s">
+        <v>822</v>
+      </c>
+      <c r="I1320" t="s">
+        <v>813</v>
+      </c>
+      <c r="K1320">
+        <v>1321</v>
+      </c>
+      <c r="M1320" s="63" t="s">
+        <v>3822</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1321">
+        <v>47</v>
+      </c>
+      <c r="B1321" s="7">
+        <v>18665009</v>
+      </c>
+      <c r="C1321" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1321" t="s">
+        <v>405</v>
+      </c>
+      <c r="E1321" t="s">
+        <v>701</v>
+      </c>
+      <c r="F1321" s="29">
+        <v>46109</v>
+      </c>
+      <c r="G1321" s="56">
+        <v>0.23525462962962962</v>
+      </c>
+      <c r="H1321" t="s">
+        <v>822</v>
+      </c>
+      <c r="I1321" t="s">
+        <v>813</v>
+      </c>
+      <c r="K1321">
+        <v>1322</v>
+      </c>
+      <c r="M1321" s="63" t="s">
+        <v>3823</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1322">
+        <v>47</v>
+      </c>
+      <c r="B1322" s="7">
+        <v>5124009</v>
+      </c>
+      <c r="C1322" t="s">
+        <v>237</v>
+      </c>
+      <c r="D1322" t="s">
+        <v>569</v>
+      </c>
+      <c r="E1322" t="s">
+        <v>237</v>
+      </c>
+      <c r="F1322" s="29">
+        <v>46109</v>
+      </c>
+      <c r="G1322" s="56">
+        <v>6.025462962962963E-2</v>
+      </c>
+      <c r="H1322" t="s">
+        <v>822</v>
+      </c>
+      <c r="I1322" t="s">
+        <v>813</v>
+      </c>
+      <c r="K1322">
+        <v>1323</v>
+      </c>
+      <c r="M1322" s="63" t="s">
+        <v>3824</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1323">
+        <v>47</v>
+      </c>
+      <c r="B1323" s="7">
+        <v>22119141</v>
+      </c>
+      <c r="C1323" t="s">
+        <v>237</v>
+      </c>
+      <c r="D1323" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1323" t="s">
+        <v>237</v>
+      </c>
+      <c r="F1323" s="29">
+        <v>46110</v>
+      </c>
+      <c r="G1323" s="56">
+        <v>0.16976851851851851</v>
+      </c>
+      <c r="H1323" t="s">
+        <v>822</v>
+      </c>
+      <c r="I1323" t="s">
+        <v>813</v>
+      </c>
+      <c r="K1323">
+        <v>1324</v>
+      </c>
+      <c r="M1323" s="63" t="s">
+        <v>3825</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1324">
+        <v>47</v>
+      </c>
+      <c r="B1324" s="7">
+        <v>7127015</v>
+      </c>
+      <c r="C1324" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1324" t="s">
+        <v>3828</v>
+      </c>
+      <c r="E1324" t="s">
+        <v>701</v>
+      </c>
+      <c r="F1324" s="29">
+        <v>46110</v>
+      </c>
+      <c r="G1324" s="56">
+        <v>8.7986111111111112E-2</v>
+      </c>
+      <c r="H1324" t="s">
+        <v>822</v>
+      </c>
+      <c r="I1324" t="s">
+        <v>813</v>
+      </c>
+      <c r="K1324">
+        <v>1325</v>
+      </c>
+      <c r="M1324" s="63" t="s">
+        <v>3826</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1325">
+        <v>47</v>
+      </c>
+      <c r="B1325" s="7">
+        <v>8540141</v>
+      </c>
+      <c r="C1325" t="s">
+        <v>3791</v>
+      </c>
+      <c r="D1325" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1325" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1325" s="29">
+        <v>46109</v>
+      </c>
+      <c r="G1325" s="56">
+        <v>4.1886574074074069E-2</v>
+      </c>
+      <c r="H1325" t="s">
+        <v>842</v>
+      </c>
+      <c r="I1325" t="s">
+        <v>813</v>
+      </c>
+      <c r="K1325">
+        <v>1326</v>
+      </c>
+      <c r="M1325" s="63" t="s">
+        <v>3827</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1326">
+        <v>47</v>
+      </c>
+      <c r="B1326" s="7">
+        <v>10616401</v>
+      </c>
+      <c r="C1326" t="s">
+        <v>660</v>
+      </c>
+      <c r="D1326" t="s">
+        <v>367</v>
+      </c>
+      <c r="E1326" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1326" s="29">
+        <v>46109</v>
+      </c>
+      <c r="G1326" s="56" t="s">
+        <v>507</v>
+      </c>
+      <c r="H1326" t="s">
+        <v>847</v>
+      </c>
+      <c r="I1326" t="s">
+        <v>813</v>
+      </c>
+      <c r="K1326">
+        <v>1327</v>
+      </c>
+      <c r="M1326" s="63" t="s">
+        <v>3829</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1327">
+        <v>47</v>
+      </c>
+      <c r="B1327" s="7">
+        <v>23564087</v>
+      </c>
+      <c r="C1327" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1327" t="s">
+        <v>450</v>
+      </c>
+      <c r="E1327" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1327" s="29">
+        <v>46110</v>
+      </c>
+      <c r="G1327" s="56">
+        <v>0.14083333333333334</v>
+      </c>
+      <c r="H1327" t="s">
+        <v>3834</v>
+      </c>
+      <c r="I1327" t="s">
+        <v>813</v>
+      </c>
+      <c r="K1327">
+        <v>1328</v>
+      </c>
+      <c r="M1327" s="63" t="s">
+        <v>3830</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1328">
+        <v>47</v>
+      </c>
+      <c r="B1328" s="7">
+        <v>10136663</v>
+      </c>
+      <c r="C1328" t="s">
+        <v>660</v>
+      </c>
+      <c r="D1328" t="s">
+        <v>477</v>
+      </c>
+      <c r="E1328" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1328" s="29">
+        <v>46109</v>
+      </c>
+      <c r="G1328" s="56" t="s">
+        <v>507</v>
+      </c>
+      <c r="H1328" t="s">
+        <v>847</v>
+      </c>
+      <c r="I1328" t="s">
+        <v>813</v>
+      </c>
+      <c r="K1328">
+        <v>1329</v>
+      </c>
+      <c r="M1328" s="63" t="s">
+        <v>3831</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1329">
+        <v>47</v>
+      </c>
+      <c r="B1329" s="7">
+        <v>17347531</v>
+      </c>
+      <c r="C1329" t="s">
+        <v>660</v>
+      </c>
+      <c r="D1329" t="s">
+        <v>451</v>
+      </c>
+      <c r="E1329" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1329" s="29">
+        <v>46110</v>
+      </c>
+      <c r="G1329" s="56">
+        <v>0.10208333333333335</v>
+      </c>
+      <c r="H1329" t="s">
+        <v>839</v>
+      </c>
+      <c r="I1329" t="s">
+        <v>813</v>
+      </c>
+      <c r="K1329">
+        <v>1330</v>
+      </c>
+      <c r="M1329" s="63" t="s">
+        <v>3832</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1330">
+        <v>47</v>
+      </c>
+      <c r="B1330" s="7">
+        <v>10009336</v>
+      </c>
+      <c r="C1330" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1330" t="s">
+        <v>565</v>
+      </c>
+      <c r="E1330" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1330" s="29">
+        <v>46101</v>
+      </c>
+      <c r="G1330" s="56" t="s">
+        <v>507</v>
+      </c>
+      <c r="H1330" t="s">
+        <v>2040</v>
+      </c>
+      <c r="I1330" t="s">
+        <v>813</v>
+      </c>
+      <c r="K1330">
+        <v>1331</v>
+      </c>
+      <c r="M1330" s="63" t="s">
+        <v>3833</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1331">
+        <v>47</v>
+      </c>
+      <c r="B1331" s="7">
+        <v>2003504</v>
+      </c>
+      <c r="C1331" t="s">
+        <v>507</v>
+      </c>
+      <c r="D1331" t="s">
+        <v>3759</v>
+      </c>
+      <c r="E1331" t="s">
+        <v>210</v>
+      </c>
+      <c r="F1331" s="29">
+        <v>46104</v>
+      </c>
+      <c r="G1331" s="56">
+        <v>2.7222222222222228E-2</v>
+      </c>
+      <c r="H1331" t="s">
+        <v>832</v>
+      </c>
+      <c r="I1331" t="s">
+        <v>813</v>
+      </c>
+      <c r="K1331">
+        <v>1332</v>
+      </c>
+      <c r="M1331" s="63" t="s">
+        <v>3835</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1332">
+        <v>47</v>
+      </c>
+      <c r="B1332" s="7">
+        <v>6455802</v>
+      </c>
+      <c r="C1332" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1332" t="s">
+        <v>357</v>
+      </c>
+      <c r="E1332" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1332" s="29">
+        <v>46109</v>
+      </c>
+      <c r="G1332" s="56">
+        <v>4.7766203703703707E-2</v>
+      </c>
+      <c r="H1332" t="s">
+        <v>844</v>
+      </c>
+      <c r="I1332" t="s">
+        <v>813</v>
+      </c>
+      <c r="K1332">
+        <v>1333</v>
+      </c>
+      <c r="M1332" s="63" t="s">
+        <v>3836</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1333">
+        <v>47</v>
+      </c>
+      <c r="B1333" s="7">
+        <v>13298242</v>
+      </c>
+      <c r="C1333" t="s">
+        <v>3837</v>
+      </c>
+      <c r="D1333" s="133" t="s">
+        <v>2003</v>
+      </c>
+      <c r="E1333" s="133" t="s">
+        <v>3838</v>
+      </c>
+      <c r="F1333" s="29">
+        <v>46110</v>
+      </c>
+      <c r="G1333" s="56">
+        <v>0.13412037037037036</v>
+      </c>
+      <c r="H1333" s="133" t="s">
+        <v>812</v>
+      </c>
+      <c r="I1333" s="133" t="s">
+        <v>813</v>
+      </c>
+      <c r="K1333">
+        <v>1334</v>
+      </c>
+      <c r="M1333" s="134" t="s">
+        <v>3839</v>
       </c>
     </row>
   </sheetData>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11023" uniqueCount="3840">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11069" uniqueCount="3863">
   <si>
     <t>Ņ</t>
   </si>
@@ -11547,6 +11547,75 @@
   </si>
   <si>
     <t>U2</t>
+  </si>
+  <si>
+    <t>U3</t>
+  </si>
+  <si>
+    <t>Shopper</t>
+  </si>
+  <si>
+    <t>[o]</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1488124176152924250/id_Uk.png?ex=69cba323&amp;is=69ca51a3&amp;hm=4ed98b080fd5b6c7fcba062a4595e1d89a60f90fdf5efcc6b1ea7837d2c99255</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1488124232776024115/id_Ul.png?ex=69cba331&amp;is=69ca51b1&amp;hm=aee9602b2846137a260db6d4eb1607e057e722dea3a166cc766338c669b48ada</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1488124300526620743/id_Um.png?ex=69cba341&amp;is=69ca51c1&amp;hm=cad217fd4112874963e9cbd64e4abf01480936d743fab386a1ab4af650d8a264</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1488124354276491394/id_Un.png?ex=69cba34e&amp;is=69ca51ce&amp;hm=7c3d0881051ee706bb61d982d03f83db08c121271d7369784b504c76fe50bb2e</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1488124409779585134/id_Uo.png?ex=69cba35b&amp;is=69ca51db&amp;hm=7d0a2e987da1118311084c732bc652ffe3c7ca020211875764a94a15f451db6d</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1488124851125358653/id_Up.png?ex=69cba3c4&amp;is=69ca5244&amp;hm=7e5e3a1aaf67b9098d6dfafe123ad09630684fd346a44b7ef2d06cced86923cf</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1488124913939386388/id_Uq.png?ex=69cba3d3&amp;is=69ca5253&amp;hm=af5c2d453e98b553e2f05e385a2bff71a8418923d427ff656e5eb3590db929f6</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1488124966158471268/id_Ur.png?ex=69cba3df&amp;is=69ca525f&amp;hm=b614b05a5ac8a0ad0bd6256e5b65ca68dfc88b51696c553cd73b02702cad8ea1</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1488125018352123954/id_Us.png?ex=69cba3ec&amp;is=69ca526c&amp;hm=b212ebda43b4d83fceaf7ea8443845b24a08447e08c8a77fd885349a611c5740</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1488125074002415747/id_Ut.png?ex=69cba3f9&amp;is=69ca5279&amp;hm=92a658fe7e892659d9bb6206128b1282336a588797bfdbeedfb59ebe1974573d</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1488125147855720470/id_Uu.jpg?ex=69cba40b&amp;is=69ca528b&amp;hm=2683861cb15ac3f53659c9f4f2f94018099a4197767cf02ae9bae69a7a3ead42</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1488125255489687673/id_Uv.png?ex=69cba424&amp;is=69ca52a4&amp;hm=4c7283328abeff80042baecec00340e35ecf0a23d143021b4dbb29b828d5db95</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1488125486810005605/id_Uw.jpg?ex=69cba45c&amp;is=69ca52dc&amp;hm=5fa14c1583dfbfd41c894782eb912f20986c0f8ca6fdb7cf49b56a9aed45d435</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1488125564618539111/id_Ux.png?ex=69cba46e&amp;is=69ca52ee&amp;hm=eb4d9ffec78bf83ff3e8b42ef399709246282b7373442eb09307c0e101c6e2df</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1488125664153309184/id_Uy.png?ex=69cba486&amp;is=69ca5306&amp;hm=17b374fa337b652038829b51129a8013338ee7ffdec526b9903f82084ff32123</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1488125713964863598/id_Uz.jpg?ex=69cba492&amp;is=69ca5312&amp;hm=d4ddbd499307942ea002a2593c9fb42e4b1573f724f172e63a882a5cbfb7497b</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1488125796429332480/id_U0.jpg?ex=69cba4a5&amp;is=69ca5325&amp;hm=6cd446c61930ac7a8770797034228d95ddf56ca37f790e663f73a21f1f976c41</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1488125885101113484/id_U1.jpg?ex=69cba4bb&amp;is=69ca533b&amp;hm=85743bddfeeee2be54352a63721afb955eab3ee77b204a55fbddb88f81c62a24</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1488125955783266427/id_U2.png?ex=69cba4cb&amp;is=69ca534b&amp;hm=39263531a00cc5b10583c6bceae68ba5bb0d609a41128eae82c42b281e729a72</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1488126003267113154/id_U3.jpg?ex=69cba4d7&amp;is=69ca5357&amp;hm=8059e2b84f8697efa5481de8d6452136bc11d7e9099499b729a22582095fbaef</t>
   </si>
 </sst>
 </file>
@@ -11558,11 +11627,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="85" x14ac:knownFonts="1">
+  <fonts count="86" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -12186,118 +12262,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="82" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="66" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="81" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="72" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="66" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="73" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="67" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="62" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="49" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="50" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -12306,18 +12383,18 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -12331,11 +12408,12 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
@@ -12554,7 +12632,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1333"/>
+  <dimension ref="A1:O1334"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -67249,11 +67327,17 @@
       <c r="I1315" t="s">
         <v>813</v>
       </c>
+      <c r="J1315" s="63" t="s">
+        <v>3815</v>
+      </c>
       <c r="K1315">
         <v>1316</v>
       </c>
-      <c r="M1315" s="63" t="s">
-        <v>3815</v>
+      <c r="M1315" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1315" t="s">
+        <v>3843</v>
       </c>
     </row>
     <row r="1316" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67284,11 +67368,17 @@
       <c r="I1316" t="s">
         <v>813</v>
       </c>
+      <c r="J1316" s="63" t="s">
+        <v>3816</v>
+      </c>
       <c r="K1316">
         <v>1317</v>
       </c>
-      <c r="M1316" s="63" t="s">
-        <v>3816</v>
+      <c r="M1316" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1316" t="s">
+        <v>3844</v>
       </c>
     </row>
     <row r="1317" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67319,11 +67409,17 @@
       <c r="I1317" t="s">
         <v>813</v>
       </c>
+      <c r="J1317" s="63" t="s">
+        <v>3818</v>
+      </c>
       <c r="K1317">
         <v>1318</v>
       </c>
-      <c r="M1317" s="63" t="s">
-        <v>3818</v>
+      <c r="M1317" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1317" t="s">
+        <v>3845</v>
       </c>
     </row>
     <row r="1318" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67354,11 +67450,17 @@
       <c r="I1318" t="s">
         <v>813</v>
       </c>
+      <c r="J1318" s="63" t="s">
+        <v>3819</v>
+      </c>
       <c r="K1318">
         <v>1319</v>
       </c>
-      <c r="M1318" s="63" t="s">
-        <v>3819</v>
+      <c r="M1318" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1318" t="s">
+        <v>3846</v>
       </c>
     </row>
     <row r="1319" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67389,11 +67491,17 @@
       <c r="I1319" t="s">
         <v>813</v>
       </c>
+      <c r="J1319" s="63" t="s">
+        <v>3821</v>
+      </c>
       <c r="K1319">
         <v>1320</v>
       </c>
-      <c r="M1319" s="63" t="s">
-        <v>3821</v>
+      <c r="M1319" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1319" t="s">
+        <v>3847</v>
       </c>
     </row>
     <row r="1320" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67424,11 +67532,17 @@
       <c r="I1320" t="s">
         <v>813</v>
       </c>
+      <c r="J1320" s="63" t="s">
+        <v>3822</v>
+      </c>
       <c r="K1320">
         <v>1321</v>
       </c>
-      <c r="M1320" s="63" t="s">
-        <v>3822</v>
+      <c r="M1320" s="135" t="s">
+        <v>3842</v>
+      </c>
+      <c r="N1320" t="s">
+        <v>3848</v>
       </c>
     </row>
     <row r="1321" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67459,11 +67573,17 @@
       <c r="I1321" t="s">
         <v>813</v>
       </c>
+      <c r="J1321" s="63" t="s">
+        <v>3823</v>
+      </c>
       <c r="K1321">
         <v>1322</v>
       </c>
-      <c r="M1321" s="63" t="s">
-        <v>3823</v>
+      <c r="M1321" s="135" t="s">
+        <v>3842</v>
+      </c>
+      <c r="N1321" t="s">
+        <v>3849</v>
       </c>
     </row>
     <row r="1322" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67494,11 +67614,17 @@
       <c r="I1322" t="s">
         <v>813</v>
       </c>
+      <c r="J1322" s="63" t="s">
+        <v>3824</v>
+      </c>
       <c r="K1322">
         <v>1323</v>
       </c>
-      <c r="M1322" s="63" t="s">
-        <v>3824</v>
+      <c r="M1322" s="135" t="s">
+        <v>3842</v>
+      </c>
+      <c r="N1322" t="s">
+        <v>3850</v>
       </c>
     </row>
     <row r="1323" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67529,11 +67655,17 @@
       <c r="I1323" t="s">
         <v>813</v>
       </c>
+      <c r="J1323" s="63" t="s">
+        <v>3825</v>
+      </c>
       <c r="K1323">
         <v>1324</v>
       </c>
-      <c r="M1323" s="63" t="s">
-        <v>3825</v>
+      <c r="M1323" s="135" t="s">
+        <v>3842</v>
+      </c>
+      <c r="N1323" t="s">
+        <v>3851</v>
       </c>
     </row>
     <row r="1324" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67564,11 +67696,17 @@
       <c r="I1324" t="s">
         <v>813</v>
       </c>
+      <c r="J1324" s="63" t="s">
+        <v>3826</v>
+      </c>
       <c r="K1324">
         <v>1325</v>
       </c>
-      <c r="M1324" s="63" t="s">
-        <v>3826</v>
+      <c r="M1324" s="135" t="s">
+        <v>3842</v>
+      </c>
+      <c r="N1324" t="s">
+        <v>3852</v>
       </c>
     </row>
     <row r="1325" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67599,11 +67737,17 @@
       <c r="I1325" t="s">
         <v>813</v>
       </c>
+      <c r="J1325" s="63" t="s">
+        <v>3827</v>
+      </c>
       <c r="K1325">
         <v>1326</v>
       </c>
-      <c r="M1325" s="63" t="s">
-        <v>3827</v>
+      <c r="M1325" s="135" t="s">
+        <v>3842</v>
+      </c>
+      <c r="N1325" t="s">
+        <v>3853</v>
       </c>
     </row>
     <row r="1326" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67634,11 +67778,17 @@
       <c r="I1326" t="s">
         <v>813</v>
       </c>
+      <c r="J1326" s="63" t="s">
+        <v>3829</v>
+      </c>
       <c r="K1326">
         <v>1327</v>
       </c>
-      <c r="M1326" s="63" t="s">
-        <v>3829</v>
+      <c r="M1326" s="135" t="s">
+        <v>3842</v>
+      </c>
+      <c r="N1326" t="s">
+        <v>3854</v>
       </c>
     </row>
     <row r="1327" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67669,11 +67819,17 @@
       <c r="I1327" t="s">
         <v>813</v>
       </c>
+      <c r="J1327" s="63" t="s">
+        <v>3830</v>
+      </c>
       <c r="K1327">
         <v>1328</v>
       </c>
-      <c r="M1327" s="63" t="s">
-        <v>3830</v>
+      <c r="M1327" s="135" t="s">
+        <v>3842</v>
+      </c>
+      <c r="N1327" t="s">
+        <v>3855</v>
       </c>
     </row>
     <row r="1328" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67704,14 +67860,20 @@
       <c r="I1328" t="s">
         <v>813</v>
       </c>
+      <c r="J1328" s="63" t="s">
+        <v>3831</v>
+      </c>
       <c r="K1328">
         <v>1329</v>
       </c>
-      <c r="M1328" s="63" t="s">
-        <v>3831</v>
-      </c>
-    </row>
-    <row r="1329" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M1328" s="135" t="s">
+        <v>3842</v>
+      </c>
+      <c r="N1328" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1329">
         <v>47</v>
       </c>
@@ -67739,14 +67901,20 @@
       <c r="I1329" t="s">
         <v>813</v>
       </c>
+      <c r="J1329" s="63" t="s">
+        <v>3832</v>
+      </c>
       <c r="K1329">
         <v>1330</v>
       </c>
-      <c r="M1329" s="63" t="s">
-        <v>3832</v>
-      </c>
-    </row>
-    <row r="1330" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M1329" s="135" t="s">
+        <v>3842</v>
+      </c>
+      <c r="N1329" t="s">
+        <v>3857</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1330">
         <v>47</v>
       </c>
@@ -67774,14 +67942,20 @@
       <c r="I1330" t="s">
         <v>813</v>
       </c>
+      <c r="J1330" s="63" t="s">
+        <v>3833</v>
+      </c>
       <c r="K1330">
         <v>1331</v>
       </c>
-      <c r="M1330" s="63" t="s">
-        <v>3833</v>
-      </c>
-    </row>
-    <row r="1331" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M1330" s="135" t="s">
+        <v>3842</v>
+      </c>
+      <c r="N1330" t="s">
+        <v>3858</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1331">
         <v>47</v>
       </c>
@@ -67809,14 +67983,20 @@
       <c r="I1331" t="s">
         <v>813</v>
       </c>
+      <c r="J1331" s="63" t="s">
+        <v>3835</v>
+      </c>
       <c r="K1331">
         <v>1332</v>
       </c>
-      <c r="M1331" s="63" t="s">
-        <v>3835</v>
-      </c>
-    </row>
-    <row r="1332" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M1331" s="135" t="s">
+        <v>3842</v>
+      </c>
+      <c r="N1331" t="s">
+        <v>3859</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1332">
         <v>47</v>
       </c>
@@ -67844,14 +68024,20 @@
       <c r="I1332" t="s">
         <v>813</v>
       </c>
+      <c r="J1332" s="63" t="s">
+        <v>3836</v>
+      </c>
       <c r="K1332">
         <v>1333</v>
       </c>
-      <c r="M1332" s="63" t="s">
-        <v>3836</v>
-      </c>
-    </row>
-    <row r="1333" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M1332" s="135" t="s">
+        <v>3842</v>
+      </c>
+      <c r="N1332" t="s">
+        <v>3860</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1333">
         <v>47</v>
       </c>
@@ -67879,11 +68065,58 @@
       <c r="I1333" s="133" t="s">
         <v>813</v>
       </c>
+      <c r="J1333" s="134" t="s">
+        <v>3839</v>
+      </c>
       <c r="K1333">
         <v>1334</v>
       </c>
-      <c r="M1333" s="134" t="s">
-        <v>3839</v>
+      <c r="M1333" s="135" t="s">
+        <v>3842</v>
+      </c>
+      <c r="N1333" t="s">
+        <v>3861</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1334">
+        <v>47</v>
+      </c>
+      <c r="B1334" s="7">
+        <v>3645993</v>
+      </c>
+      <c r="C1334" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1334" s="135" t="s">
+        <v>3841</v>
+      </c>
+      <c r="E1334" s="135" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1334" s="29">
+        <v>46111</v>
+      </c>
+      <c r="G1334" s="56">
+        <v>4.0648148148148149E-2</v>
+      </c>
+      <c r="H1334" s="135" t="s">
+        <v>1329</v>
+      </c>
+      <c r="I1334" s="135" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1334" s="136" t="s">
+        <v>3840</v>
+      </c>
+      <c r="K1334">
+        <v>1335</v>
+      </c>
+      <c r="M1334" s="135" t="s">
+        <v>3842</v>
+      </c>
+      <c r="N1334" t="s">
+        <v>3862</v>
       </c>
     </row>
   </sheetData>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11069" uniqueCount="3863">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11078" uniqueCount="3867">
   <si>
     <t>Ņ</t>
   </si>
@@ -11543,9 +11543,6 @@
     <t>ƒ(x) = ax+b A</t>
   </si>
   <si>
-    <t>ƒ(x) = ax+b</t>
-  </si>
-  <si>
     <t>U2</t>
   </si>
   <si>
@@ -11555,9 +11552,6 @@
     <t>Shopper</t>
   </si>
   <si>
-    <t>[o]</t>
-  </si>
-  <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1488124176152924250/id_Uk.png?ex=69cba323&amp;is=69ca51a3&amp;hm=4ed98b080fd5b6c7fcba062a4595e1d89a60f90fdf5efcc6b1ea7837d2c99255</t>
   </si>
   <si>
@@ -11616,6 +11610,24 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1488126003267113154/id_U3.jpg?ex=69cba4d7&amp;is=69ca5357&amp;hm=8059e2b84f8697efa5481de8d6452136bc11d7e9099499b729a22582095fbaef</t>
+  </si>
+  <si>
+    <t>[FR] La Defénse</t>
+  </si>
+  <si>
+    <t>the wave 11 pali run (to 73)</t>
+  </si>
+  <si>
+    <t>U4</t>
+  </si>
+  <si>
+    <t>Paladin/Ragnarok</t>
+  </si>
+  <si>
+    <t>meow meow catgirl power!</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1488410297197789264/id_U4.png?ex=69ccad9c&amp;is=69cb5c1c&amp;hm=6f1b076cb50f2de4943742bb2e6d49125fb910243a765546d3fd035d20a8c31f</t>
   </si>
 </sst>
 </file>
@@ -11627,11 +11639,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="86" x14ac:knownFonts="1">
+  <fonts count="87" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -12262,118 +12281,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="137">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="83" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="67" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="82" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="66" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="81" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="73" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="67" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="74" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="68" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="50" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="51" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -12382,18 +12402,18 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -12407,15 +12427,15 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -12632,7 +12652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1334"/>
+  <dimension ref="A1:O1335"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -67337,7 +67357,7 @@
         <v>861</v>
       </c>
       <c r="N1315" t="s">
-        <v>3843</v>
+        <v>3841</v>
       </c>
     </row>
     <row r="1316" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67378,7 +67398,7 @@
         <v>861</v>
       </c>
       <c r="N1316" t="s">
-        <v>3844</v>
+        <v>3842</v>
       </c>
     </row>
     <row r="1317" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67419,7 +67439,7 @@
         <v>861</v>
       </c>
       <c r="N1317" t="s">
-        <v>3845</v>
+        <v>3843</v>
       </c>
     </row>
     <row r="1318" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67460,7 +67480,7 @@
         <v>861</v>
       </c>
       <c r="N1318" t="s">
-        <v>3846</v>
+        <v>3844</v>
       </c>
     </row>
     <row r="1319" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67501,7 +67521,7 @@
         <v>861</v>
       </c>
       <c r="N1319" t="s">
-        <v>3847</v>
+        <v>3845</v>
       </c>
     </row>
     <row r="1320" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67538,11 +67558,11 @@
       <c r="K1320">
         <v>1321</v>
       </c>
-      <c r="M1320" s="135" t="s">
-        <v>3842</v>
+      <c r="M1320" s="57" t="s">
+        <v>861</v>
       </c>
       <c r="N1320" t="s">
-        <v>3848</v>
+        <v>3846</v>
       </c>
     </row>
     <row r="1321" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67579,11 +67599,11 @@
       <c r="K1321">
         <v>1322</v>
       </c>
-      <c r="M1321" s="135" t="s">
-        <v>3842</v>
+      <c r="M1321" s="57" t="s">
+        <v>861</v>
       </c>
       <c r="N1321" t="s">
-        <v>3849</v>
+        <v>3847</v>
       </c>
     </row>
     <row r="1322" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67620,11 +67640,11 @@
       <c r="K1322">
         <v>1323</v>
       </c>
-      <c r="M1322" s="135" t="s">
-        <v>3842</v>
+      <c r="M1322" s="57" t="s">
+        <v>861</v>
       </c>
       <c r="N1322" t="s">
-        <v>3850</v>
+        <v>3848</v>
       </c>
     </row>
     <row r="1323" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67661,11 +67681,11 @@
       <c r="K1323">
         <v>1324</v>
       </c>
-      <c r="M1323" s="135" t="s">
-        <v>3842</v>
+      <c r="M1323" s="57" t="s">
+        <v>861</v>
       </c>
       <c r="N1323" t="s">
-        <v>3851</v>
+        <v>3849</v>
       </c>
     </row>
     <row r="1324" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67702,11 +67722,11 @@
       <c r="K1324">
         <v>1325</v>
       </c>
-      <c r="M1324" s="135" t="s">
-        <v>3842</v>
+      <c r="M1324" s="57" t="s">
+        <v>861</v>
       </c>
       <c r="N1324" t="s">
-        <v>3852</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="1325" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67743,11 +67763,11 @@
       <c r="K1325">
         <v>1326</v>
       </c>
-      <c r="M1325" s="135" t="s">
-        <v>3842</v>
+      <c r="M1325" s="57" t="s">
+        <v>861</v>
       </c>
       <c r="N1325" t="s">
-        <v>3853</v>
+        <v>3851</v>
       </c>
     </row>
     <row r="1326" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67784,11 +67804,11 @@
       <c r="K1326">
         <v>1327</v>
       </c>
-      <c r="M1326" s="135" t="s">
-        <v>3842</v>
+      <c r="M1326" s="57" t="s">
+        <v>861</v>
       </c>
       <c r="N1326" t="s">
-        <v>3854</v>
+        <v>3852</v>
       </c>
     </row>
     <row r="1327" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67825,11 +67845,11 @@
       <c r="K1327">
         <v>1328</v>
       </c>
-      <c r="M1327" s="135" t="s">
-        <v>3842</v>
+      <c r="M1327" s="57" t="s">
+        <v>861</v>
       </c>
       <c r="N1327" t="s">
-        <v>3855</v>
+        <v>3853</v>
       </c>
     </row>
     <row r="1328" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67866,11 +67886,11 @@
       <c r="K1328">
         <v>1329</v>
       </c>
-      <c r="M1328" s="135" t="s">
-        <v>3842</v>
+      <c r="M1328" s="57" t="s">
+        <v>861</v>
       </c>
       <c r="N1328" t="s">
-        <v>3856</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="1329" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67907,11 +67927,11 @@
       <c r="K1329">
         <v>1330</v>
       </c>
-      <c r="M1329" s="135" t="s">
-        <v>3842</v>
+      <c r="M1329" s="57" t="s">
+        <v>861</v>
       </c>
       <c r="N1329" t="s">
-        <v>3857</v>
+        <v>3855</v>
       </c>
     </row>
     <row r="1330" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67948,11 +67968,11 @@
       <c r="K1330">
         <v>1331</v>
       </c>
-      <c r="M1330" s="135" t="s">
-        <v>3842</v>
+      <c r="M1330" s="57" t="s">
+        <v>861</v>
       </c>
       <c r="N1330" t="s">
-        <v>3858</v>
+        <v>3856</v>
       </c>
     </row>
     <row r="1331" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67989,11 +68009,11 @@
       <c r="K1331">
         <v>1332</v>
       </c>
-      <c r="M1331" s="135" t="s">
-        <v>3842</v>
+      <c r="M1331" s="57" t="s">
+        <v>861</v>
       </c>
       <c r="N1331" t="s">
-        <v>3859</v>
+        <v>3857</v>
       </c>
     </row>
     <row r="1332" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68030,11 +68050,11 @@
       <c r="K1332">
         <v>1333</v>
       </c>
-      <c r="M1332" s="135" t="s">
-        <v>3842</v>
+      <c r="M1332" s="57" t="s">
+        <v>861</v>
       </c>
       <c r="N1332" t="s">
-        <v>3860</v>
+        <v>3858</v>
       </c>
     </row>
     <row r="1333" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68050,8 +68070,8 @@
       <c r="D1333" s="133" t="s">
         <v>2003</v>
       </c>
-      <c r="E1333" s="133" t="s">
-        <v>3838</v>
+      <c r="E1333" s="137" t="s">
+        <v>3861</v>
       </c>
       <c r="F1333" s="29">
         <v>46110</v>
@@ -68066,16 +68086,16 @@
         <v>813</v>
       </c>
       <c r="J1333" s="134" t="s">
-        <v>3839</v>
+        <v>3838</v>
       </c>
       <c r="K1333">
         <v>1334</v>
       </c>
-      <c r="M1333" s="135" t="s">
-        <v>3842</v>
+      <c r="M1333" s="57" t="s">
+        <v>861</v>
       </c>
       <c r="N1333" t="s">
-        <v>3861</v>
+        <v>3859</v>
       </c>
     </row>
     <row r="1334" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68089,7 +68109,7 @@
         <v>17</v>
       </c>
       <c r="D1334" s="135" t="s">
-        <v>3841</v>
+        <v>3840</v>
       </c>
       <c r="E1334" s="135" t="s">
         <v>18</v>
@@ -68107,16 +68127,60 @@
         <v>813</v>
       </c>
       <c r="J1334" s="136" t="s">
-        <v>3840</v>
+        <v>3839</v>
       </c>
       <c r="K1334">
         <v>1335</v>
       </c>
-      <c r="M1334" s="135" t="s">
-        <v>3842</v>
+      <c r="M1334" s="57" t="s">
+        <v>861</v>
       </c>
       <c r="N1334" t="s">
+        <v>3860</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1335">
+        <v>50</v>
+      </c>
+      <c r="B1335" s="7">
+        <v>14527446</v>
+      </c>
+      <c r="C1335" t="s">
+        <v>3865</v>
+      </c>
+      <c r="D1335" s="137" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1335" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1335" s="29">
+        <v>46111</v>
+      </c>
+      <c r="G1335" s="56">
+        <v>8.4050925925925932E-2</v>
+      </c>
+      <c r="H1335" s="137" t="s">
+        <v>3864</v>
+      </c>
+      <c r="I1335" s="137" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1335" s="63" t="s">
+        <v>3863</v>
+      </c>
+      <c r="K1335">
+        <v>1336</v>
+      </c>
+      <c r="L1335" t="s">
         <v>3862</v>
+      </c>
+      <c r="M1335" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1335" t="s">
+        <v>3866</v>
       </c>
     </row>
   </sheetData>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11078" uniqueCount="3867">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11142" uniqueCount="3888">
   <si>
     <t>Ņ</t>
   </si>
@@ -11628,6 +11628,69 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1488410297197789264/id_U4.png?ex=69ccad9c&amp;is=69cb5c1c&amp;hm=6f1b076cb50f2de4943742bb2e6d49125fb910243a765546d3fd035d20a8c31f</t>
+  </si>
+  <si>
+    <t>TejmQman77_The_Aprilian</t>
+  </si>
+  <si>
+    <t>Examiner</t>
+  </si>
+  <si>
+    <t>U5</t>
+  </si>
+  <si>
+    <t>cobblerdrive</t>
+  </si>
+  <si>
+    <t>U6</t>
+  </si>
+  <si>
+    <t>U7</t>
+  </si>
+  <si>
+    <t>[]Hakuryu</t>
+  </si>
+  <si>
+    <t>U8</t>
+  </si>
+  <si>
+    <t>Triple Auto-Gunner</t>
+  </si>
+  <si>
+    <t>U9</t>
+  </si>
+  <si>
+    <t>U(</t>
+  </si>
+  <si>
+    <t>U)</t>
+  </si>
+  <si>
+    <t>VA</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1489308525413798129/id_U5.png?ex=69cff226&amp;is=69cea0a6&amp;hm=0e84577aeda5cbbfd3edee41ea7e789bdf9584ef95fd921390e014b6ab524fd1</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1489308584943681757/id_U6.png?ex=69cff234&amp;is=69cea0b4&amp;hm=e9959c35a2dc0966fc572e347e7484ea09f8a89930d438329c841b49b64d5d44</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1489308665977639022/id_U7.png?ex=69cff247&amp;is=69cea0c7&amp;hm=a4517b45c740fe14de4d48af4f84bba4f1dc014d8dae521c43ab698c0efc1c28</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1489308750509641748/id_U8.png?ex=69cff25c&amp;is=69cea0dc&amp;hm=d5747144f07bff2f84779d72bbc74a02904b8226e5bce3a45800734300f7c272</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1489308907007381656/id_U9.png?ex=69cff281&amp;is=69cea101&amp;hm=ccb248e7875a46f42899bbbaf1e6c3067d4debdf817f0b7f2b8c6aadffa76d2f</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1489308964494643311/id_U.png?ex=69cff28f&amp;is=69cea10f&amp;hm=96e55235b6e217ea9ecf7bca252f9742fa543cbd1c9c864fd7c87ea4eab175b2</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1489309020819947601/id_U.png?ex=69cff29c&amp;is=69cea11c&amp;hm=41833a3053f8a8badfacc56e6835522f0bb320aac4790af74a963355af4a9442</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1489309069926727910/id_VA.jpg?ex=69cff2a8&amp;is=69cea128&amp;hm=82d83720c52cd9748a9161fc866fc91960b02c0b3a8c267a57d7e6f333fd6687</t>
   </si>
 </sst>
 </file>
@@ -11639,11 +11702,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="87" x14ac:knownFonts="1">
+  <fonts count="88" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -12281,118 +12351,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="139">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="84" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="68" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="83" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="67" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="82" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="74" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="68" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="75" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="69" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="52" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="52" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="52" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="52" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="51" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="52" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -12401,18 +12472,18 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -12426,15 +12497,15 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -12652,7 +12723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1335"/>
+  <dimension ref="A1:O1343"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -67506,7 +67577,7 @@
         <v>9.087962962962963E-2</v>
       </c>
       <c r="H1319" t="s">
-        <v>839</v>
+        <v>822</v>
       </c>
       <c r="I1319" t="s">
         <v>813</v>
@@ -68181,6 +68252,334 @@
       </c>
       <c r="N1335" t="s">
         <v>3866</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1336">
+        <v>52</v>
+      </c>
+      <c r="B1336" s="7">
+        <v>5081926</v>
+      </c>
+      <c r="C1336" t="s">
+        <v>3867</v>
+      </c>
+      <c r="D1336" s="138" t="s">
+        <v>3868</v>
+      </c>
+      <c r="E1336" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1336" s="29">
+        <v>46113</v>
+      </c>
+      <c r="G1336" s="56">
+        <v>0.11712962962962963</v>
+      </c>
+      <c r="H1336" s="138" t="s">
+        <v>822</v>
+      </c>
+      <c r="I1336" s="138" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1336" s="63" t="s">
+        <v>3869</v>
+      </c>
+      <c r="K1336">
+        <v>1337</v>
+      </c>
+      <c r="M1336" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1336" t="s">
+        <v>3880</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1337">
+        <v>52</v>
+      </c>
+      <c r="B1337" s="7">
+        <v>11643533</v>
+      </c>
+      <c r="C1337" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1337" s="138" t="s">
+        <v>3870</v>
+      </c>
+      <c r="E1337" t="s">
+        <v>3439</v>
+      </c>
+      <c r="F1337" s="29">
+        <v>46113</v>
+      </c>
+      <c r="G1337" s="56">
+        <v>0.12475694444444445</v>
+      </c>
+      <c r="H1337" s="138" t="s">
+        <v>2466</v>
+      </c>
+      <c r="I1337" s="138" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1337" s="63" t="s">
+        <v>3871</v>
+      </c>
+      <c r="K1337">
+        <v>1338</v>
+      </c>
+      <c r="M1337" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1337" t="s">
+        <v>3881</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1338">
+        <v>52</v>
+      </c>
+      <c r="B1338" s="7">
+        <v>30358417</v>
+      </c>
+      <c r="C1338" t="s">
+        <v>3873</v>
+      </c>
+      <c r="D1338" s="138" t="s">
+        <v>428</v>
+      </c>
+      <c r="E1338" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1338" s="29">
+        <v>46113</v>
+      </c>
+      <c r="G1338" s="56">
+        <v>0.1675925925925926</v>
+      </c>
+      <c r="H1338" s="138" t="s">
+        <v>842</v>
+      </c>
+      <c r="I1338" s="138" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1338" s="63" t="s">
+        <v>3872</v>
+      </c>
+      <c r="K1338">
+        <v>1339</v>
+      </c>
+      <c r="M1338" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1338" t="s">
+        <v>3882</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1339">
+        <v>52</v>
+      </c>
+      <c r="B1339" s="7">
+        <v>4541678</v>
+      </c>
+      <c r="C1339" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1339" s="138" t="s">
+        <v>129</v>
+      </c>
+      <c r="E1339" t="s">
+        <v>654</v>
+      </c>
+      <c r="F1339" s="29">
+        <v>46113</v>
+      </c>
+      <c r="G1339" s="56">
+        <v>2.8784722222222225E-2</v>
+      </c>
+      <c r="H1339" s="138" t="s">
+        <v>842</v>
+      </c>
+      <c r="I1339" s="138" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1339" s="63" t="s">
+        <v>3874</v>
+      </c>
+      <c r="K1339">
+        <v>1340</v>
+      </c>
+      <c r="M1339" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1339" t="s">
+        <v>3883</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1340">
+        <v>52</v>
+      </c>
+      <c r="B1340" s="7">
+        <v>7687947</v>
+      </c>
+      <c r="C1340" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1340" s="138" t="s">
+        <v>3875</v>
+      </c>
+      <c r="E1340" t="s">
+        <v>654</v>
+      </c>
+      <c r="F1340" s="29">
+        <v>46113</v>
+      </c>
+      <c r="G1340" s="56">
+        <v>5.4652777777777772E-2</v>
+      </c>
+      <c r="H1340" s="138" t="s">
+        <v>832</v>
+      </c>
+      <c r="I1340" s="138" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1340" s="63" t="s">
+        <v>3876</v>
+      </c>
+      <c r="K1340">
+        <v>1341</v>
+      </c>
+      <c r="M1340" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1340" t="s">
+        <v>3884</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1341">
+        <v>52</v>
+      </c>
+      <c r="B1341" s="7">
+        <v>7143774</v>
+      </c>
+      <c r="C1341" t="s">
+        <v>660</v>
+      </c>
+      <c r="D1341" s="138" t="s">
+        <v>545</v>
+      </c>
+      <c r="E1341" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1341" s="29">
+        <v>46112</v>
+      </c>
+      <c r="G1341" s="56">
+        <v>6.385416666666667E-2</v>
+      </c>
+      <c r="H1341" s="138" t="s">
+        <v>812</v>
+      </c>
+      <c r="I1341" s="138" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1341" s="63" t="s">
+        <v>3877</v>
+      </c>
+      <c r="K1341">
+        <v>1342</v>
+      </c>
+      <c r="M1341" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1341" t="s">
+        <v>3885</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1342">
+        <v>52</v>
+      </c>
+      <c r="B1342" s="7">
+        <v>11089001</v>
+      </c>
+      <c r="C1342" t="s">
+        <v>660</v>
+      </c>
+      <c r="D1342" s="138" t="s">
+        <v>341</v>
+      </c>
+      <c r="E1342" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1342" s="29">
+        <v>46112</v>
+      </c>
+      <c r="G1342" s="56">
+        <v>0.11258101851851852</v>
+      </c>
+      <c r="H1342" s="138" t="s">
+        <v>945</v>
+      </c>
+      <c r="I1342" s="138" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1342" s="63" t="s">
+        <v>3878</v>
+      </c>
+      <c r="K1342">
+        <v>1343</v>
+      </c>
+      <c r="M1342" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1342" t="s">
+        <v>3886</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1343">
+        <v>52</v>
+      </c>
+      <c r="B1343" s="7">
+        <v>11636542</v>
+      </c>
+      <c r="C1343" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1343" s="138" t="s">
+        <v>89</v>
+      </c>
+      <c r="E1343" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1343" s="29">
+        <v>46113</v>
+      </c>
+      <c r="G1343" s="56">
+        <v>6.9201388888888882E-2</v>
+      </c>
+      <c r="H1343" s="138" t="s">
+        <v>1115</v>
+      </c>
+      <c r="I1343" s="138" t="s">
+        <v>813</v>
+      </c>
+      <c r="J1343" s="63" t="s">
+        <v>3879</v>
+      </c>
+      <c r="K1343">
+        <v>1344</v>
+      </c>
+      <c r="M1343" s="57" t="s">
+        <v>861</v>
+      </c>
+      <c r="N1343" t="s">
+        <v>3887</v>
       </c>
     </row>
   </sheetData>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11208" uniqueCount="3905">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11257" uniqueCount="3924">
   <si>
     <t>Ņ</t>
   </si>
@@ -11684,9 +11684,6 @@
     <t>TEAᯓ directive</t>
   </si>
   <si>
-    <t>M13 [M\*st*k idi Nyx]</t>
-  </si>
-  <si>
     <t>VB</t>
   </si>
   <si>
@@ -11742,6 +11739,66 @@
   </si>
   <si>
     <t>()\_+KMMYYPPR&lt;[L0R0s]</t>
+  </si>
+  <si>
+    <t>M13 [M\*st\*k idi Nyx]</t>
+  </si>
+  <si>
+    <t>(p.-.)&gt;.D</t>
+  </si>
+  <si>
+    <t>VJ</t>
+  </si>
+  <si>
+    <t>VK</t>
+  </si>
+  <si>
+    <t>VL</t>
+  </si>
+  <si>
+    <t>Auto-Spawner</t>
+  </si>
+  <si>
+    <t>Tejm the Aprilian</t>
+  </si>
+  <si>
+    <t>Theia/Ezekiel</t>
+  </si>
+  <si>
+    <t>Crop Duster</t>
+  </si>
+  <si>
+    <t>Ik neem jouw ballen &lt;3</t>
+  </si>
+  <si>
+    <t>VM</t>
+  </si>
+  <si>
+    <t>VN</t>
+  </si>
+  <si>
+    <t>VO</t>
+  </si>
+  <si>
+    <t>Medic</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1491084505933676768/id_VJ.png?ex=69d66829&amp;is=69d516a9&amp;hm=7a7f8e8da986d69386bf6aad93bf5f6f88f5da99172c61be6ebecdf36d1d8a99</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1491084569116414082/id_VK.png?ex=69d66838&amp;is=69d516b8&amp;hm=6e07700efe8408d1beb329656f81eb739f55501dee0e61c27dc593eee982e943</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1491084620572131468/id_VL.png?ex=69d66844&amp;is=69d516c4&amp;hm=e4b9dd6a27175fec31b3ced0a119559f9f5800332bac811885dfe61080bda88a</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1491084679799902349/id_VM.png?ex=69d66852&amp;is=69d516d2&amp;hm=7e7677cb72201a548504a86dcfd36fc2006ef0df952a78adb34020c61b9a19e9</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1491084734858530976/id_VN.png?ex=69d6685f&amp;is=69d516df&amp;hm=4ef337bbd24159ff451b44ca75e84818a5443569d9ae6bfec4ac521d5694cd0b</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1491084778508648558/id_VO.jpg?ex=69d6686a&amp;is=69d516ea&amp;hm=6d42c28d469b5d3a5b38102ad555a7417c0c7bdf06410ccbaece45d0e6c6f533</t>
   </si>
 </sst>
 </file>
@@ -11753,11 +11810,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="90" x14ac:knownFonts="1">
+  <fonts count="91" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -12416,118 +12480,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="141">
+  <cellXfs count="142">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="87" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="71" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="86" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="70" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="85" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="77" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="71" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="72" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="68" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="67" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="52" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="52" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="54" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="55" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -12536,18 +12601,18 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -12561,15 +12626,15 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -12790,7 +12855,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1351"/>
+  <dimension ref="A1:O1357"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -16387,7 +16452,7 @@
         <v>30380000</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>3904</v>
+        <v>3903</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>5</v>
@@ -18063,7 +18128,7 @@
         <v>26686674</v>
       </c>
       <c r="C123" t="s">
-        <v>3885</v>
+        <v>3904</v>
       </c>
       <c r="D123" t="s">
         <v>7</v>
@@ -68678,7 +68743,7 @@
         <v>292</v>
       </c>
       <c r="J1344" s="63" t="s">
-        <v>3886</v>
+        <v>3885</v>
       </c>
       <c r="K1344">
         <v>1345</v>
@@ -68687,7 +68752,7 @@
         <v>859</v>
       </c>
       <c r="N1344" t="s">
-        <v>3896</v>
+        <v>3895</v>
       </c>
     </row>
     <row r="1345" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68719,7 +68784,7 @@
         <v>292</v>
       </c>
       <c r="J1345" s="63" t="s">
-        <v>3887</v>
+        <v>3886</v>
       </c>
       <c r="K1345">
         <v>1346</v>
@@ -68728,7 +68793,7 @@
         <v>859</v>
       </c>
       <c r="N1345" t="s">
-        <v>3897</v>
+        <v>3896</v>
       </c>
     </row>
     <row r="1346" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68739,7 +68804,7 @@
         <v>4196788</v>
       </c>
       <c r="C1346" t="s">
-        <v>3889</v>
+        <v>3888</v>
       </c>
       <c r="D1346" s="140" t="s">
         <v>444</v>
@@ -68760,7 +68825,7 @@
         <v>292</v>
       </c>
       <c r="J1346" s="63" t="s">
-        <v>3888</v>
+        <v>3887</v>
       </c>
       <c r="K1346">
         <v>1347</v>
@@ -68769,7 +68834,7 @@
         <v>859</v>
       </c>
       <c r="N1346" t="s">
-        <v>3898</v>
+        <v>3897</v>
       </c>
     </row>
     <row r="1347" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68780,7 +68845,7 @@
         <v>11596975</v>
       </c>
       <c r="C1347" t="s">
-        <v>3890</v>
+        <v>3889</v>
       </c>
       <c r="D1347" s="140" t="s">
         <v>374</v>
@@ -68801,7 +68866,7 @@
         <v>292</v>
       </c>
       <c r="J1347" s="63" t="s">
-        <v>3891</v>
+        <v>3890</v>
       </c>
       <c r="K1347">
         <v>1348</v>
@@ -68810,7 +68875,7 @@
         <v>859</v>
       </c>
       <c r="N1347" t="s">
-        <v>3899</v>
+        <v>3898</v>
       </c>
     </row>
     <row r="1348" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68842,7 +68907,7 @@
         <v>811</v>
       </c>
       <c r="J1348" s="63" t="s">
-        <v>3892</v>
+        <v>3891</v>
       </c>
       <c r="K1348">
         <v>1349</v>
@@ -68851,7 +68916,7 @@
         <v>859</v>
       </c>
       <c r="N1348" t="s">
-        <v>3900</v>
+        <v>3899</v>
       </c>
     </row>
     <row r="1349" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68883,7 +68948,7 @@
         <v>811</v>
       </c>
       <c r="J1349" s="63" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
       <c r="K1349">
         <v>1350</v>
@@ -68892,7 +68957,7 @@
         <v>859</v>
       </c>
       <c r="N1349" t="s">
-        <v>3901</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="1350" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68924,7 +68989,7 @@
         <v>292</v>
       </c>
       <c r="J1350" s="63" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
       <c r="K1350">
         <v>1351</v>
@@ -68933,7 +68998,7 @@
         <v>859</v>
       </c>
       <c r="N1350" t="s">
-        <v>3902</v>
+        <v>3901</v>
       </c>
     </row>
     <row r="1351" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68965,7 +69030,7 @@
         <v>292</v>
       </c>
       <c r="J1351" s="63" t="s">
-        <v>3895</v>
+        <v>3894</v>
       </c>
       <c r="K1351">
         <v>1352</v>
@@ -68974,7 +69039,253 @@
         <v>859</v>
       </c>
       <c r="N1351" t="s">
-        <v>3903</v>
+        <v>3902</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1352">
+        <v>59</v>
+      </c>
+      <c r="B1352" s="7">
+        <v>6980000</v>
+      </c>
+      <c r="C1352" t="s">
+        <v>3905</v>
+      </c>
+      <c r="D1352" s="141" t="s">
+        <v>3909</v>
+      </c>
+      <c r="E1352" t="s">
+        <v>368</v>
+      </c>
+      <c r="F1352" s="29">
+        <v>46117</v>
+      </c>
+      <c r="G1352" s="56" t="s">
+        <v>505</v>
+      </c>
+      <c r="H1352" s="141" t="s">
+        <v>505</v>
+      </c>
+      <c r="I1352" s="141" t="s">
+        <v>292</v>
+      </c>
+      <c r="J1352" s="63" t="s">
+        <v>3906</v>
+      </c>
+      <c r="K1352">
+        <v>1353</v>
+      </c>
+      <c r="M1352" s="57" t="s">
+        <v>859</v>
+      </c>
+      <c r="N1352" t="s">
+        <v>3918</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1353">
+        <v>59</v>
+      </c>
+      <c r="B1353" s="7">
+        <v>4892080</v>
+      </c>
+      <c r="C1353" t="s">
+        <v>3910</v>
+      </c>
+      <c r="D1353" s="141" t="s">
+        <v>650</v>
+      </c>
+      <c r="E1353" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1353" s="29">
+        <v>46117</v>
+      </c>
+      <c r="G1353" s="56">
+        <v>4.6365740740740742E-2</v>
+      </c>
+      <c r="H1353" s="141" t="s">
+        <v>3911</v>
+      </c>
+      <c r="I1353" s="141" t="s">
+        <v>292</v>
+      </c>
+      <c r="J1353" s="63" t="s">
+        <v>3907</v>
+      </c>
+      <c r="K1353">
+        <v>1354</v>
+      </c>
+      <c r="M1353" s="57" t="s">
+        <v>859</v>
+      </c>
+      <c r="N1353" t="s">
+        <v>3919</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1354">
+        <v>59</v>
+      </c>
+      <c r="B1354" s="7">
+        <v>2082487</v>
+      </c>
+      <c r="C1354" t="s">
+        <v>443</v>
+      </c>
+      <c r="D1354" t="s">
+        <v>3912</v>
+      </c>
+      <c r="E1354" t="s">
+        <v>436</v>
+      </c>
+      <c r="F1354" s="29">
+        <v>46119</v>
+      </c>
+      <c r="G1354" s="56">
+        <v>2.7893518518518515E-2</v>
+      </c>
+      <c r="H1354" s="141" t="s">
+        <v>820</v>
+      </c>
+      <c r="I1354" s="141" t="s">
+        <v>292</v>
+      </c>
+      <c r="J1354" s="63" t="s">
+        <v>3908</v>
+      </c>
+      <c r="K1354">
+        <v>1355</v>
+      </c>
+      <c r="M1354" s="57" t="s">
+        <v>859</v>
+      </c>
+      <c r="N1354" t="s">
+        <v>3920</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1355">
+        <v>59</v>
+      </c>
+      <c r="B1355" s="7">
+        <v>4255101</v>
+      </c>
+      <c r="C1355" t="s">
+        <v>3913</v>
+      </c>
+      <c r="D1355" t="s">
+        <v>374</v>
+      </c>
+      <c r="E1355" t="s">
+        <v>652</v>
+      </c>
+      <c r="F1355" s="29">
+        <v>46119</v>
+      </c>
+      <c r="G1355" s="56">
+        <v>3.7256944444444447E-2</v>
+      </c>
+      <c r="H1355" s="141" t="s">
+        <v>1393</v>
+      </c>
+      <c r="I1355" s="141" t="s">
+        <v>292</v>
+      </c>
+      <c r="J1355" s="63" t="s">
+        <v>3914</v>
+      </c>
+      <c r="K1355">
+        <v>1356</v>
+      </c>
+      <c r="M1355" s="57" t="s">
+        <v>859</v>
+      </c>
+      <c r="N1355" t="s">
+        <v>3921</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1356">
+        <v>59</v>
+      </c>
+      <c r="B1356" s="7">
+        <v>2750955</v>
+      </c>
+      <c r="C1356" t="s">
+        <v>209</v>
+      </c>
+      <c r="D1356" t="s">
+        <v>3917</v>
+      </c>
+      <c r="E1356" t="s">
+        <v>209</v>
+      </c>
+      <c r="F1356" s="29">
+        <v>46118</v>
+      </c>
+      <c r="G1356" s="56">
+        <v>4.2696759259259261E-2</v>
+      </c>
+      <c r="H1356" s="141" t="s">
+        <v>835</v>
+      </c>
+      <c r="I1356" s="141" t="s">
+        <v>292</v>
+      </c>
+      <c r="J1356" s="63" t="s">
+        <v>3915</v>
+      </c>
+      <c r="K1356">
+        <v>1357</v>
+      </c>
+      <c r="M1356" s="57" t="s">
+        <v>859</v>
+      </c>
+      <c r="N1356" t="s">
+        <v>3922</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1357">
+        <v>59</v>
+      </c>
+      <c r="B1357" s="7">
+        <v>11549451</v>
+      </c>
+      <c r="C1357" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1357" t="s">
+        <v>357</v>
+      </c>
+      <c r="E1357" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1357" s="29">
+        <v>46119</v>
+      </c>
+      <c r="G1357" s="56">
+        <v>0.10803240740740742</v>
+      </c>
+      <c r="H1357" s="141" t="s">
+        <v>890</v>
+      </c>
+      <c r="I1357" s="141" t="s">
+        <v>292</v>
+      </c>
+      <c r="J1357" s="63" t="s">
+        <v>3916</v>
+      </c>
+      <c r="K1357">
+        <v>1358</v>
+      </c>
+      <c r="M1357" s="57" t="s">
+        <v>859</v>
+      </c>
+      <c r="N1357" t="s">
+        <v>3923</v>
       </c>
     </row>
   </sheetData>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11321" uniqueCount="3946">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11329" uniqueCount="3948">
   <si>
     <t>Ņ</t>
   </si>
@@ -11865,6 +11865,12 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1491475222388539623/id_VW.jpg?ex=69d7d40b&amp;is=69d6828b&amp;hm=0ad16e45a41442d342152e0e4c5dd85c84cf308a79e71d1eb02a90a45993d4ca</t>
+  </si>
+  <si>
+    <t>VX</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1491491244076040202/id_VX.jpg?ex=69d7e2f7&amp;is=69d69177&amp;hm=79c796e51d9710a6cbe21e2ff9c7066692d1a0ab4dd565b28f65540ac619b5f3</t>
   </si>
 </sst>
 </file>
@@ -11876,11 +11882,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="93" x14ac:knownFonts="1">
+  <fonts count="94" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -12560,118 +12573,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="144">
+  <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="90" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="74" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="89" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="73" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="88" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="74" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="81" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="75" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="71" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="70" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="57" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="57" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="57" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="57" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="57" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="58" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="53" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="52" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -12680,18 +12694,18 @@
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="28" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -12705,15 +12719,15 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -12937,7 +12951,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1365"/>
+  <dimension ref="A1:O1366"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -69698,6 +69712,47 @@
         <v>3945</v>
       </c>
     </row>
+    <row r="1366" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1366">
+        <v>60</v>
+      </c>
+      <c r="B1366" s="7">
+        <v>10080590</v>
+      </c>
+      <c r="C1366" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1366" t="s">
+        <v>79</v>
+      </c>
+      <c r="E1366" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1366" s="29">
+        <v>46120</v>
+      </c>
+      <c r="G1366" s="56">
+        <v>4.6307870370370374E-2</v>
+      </c>
+      <c r="H1366" s="144" t="s">
+        <v>1110</v>
+      </c>
+      <c r="I1366" s="144" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1366" s="63" t="s">
+        <v>3946</v>
+      </c>
+      <c r="K1366">
+        <v>1367</v>
+      </c>
+      <c r="M1366" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1366" t="s">
+        <v>3947</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N1">
     <sortState ref="A2:N1357">

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11329" uniqueCount="3948">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11362" uniqueCount="3959">
   <si>
     <t>Ņ</t>
   </si>
@@ -11871,6 +11871,39 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1491491244076040202/id_VX.jpg?ex=69d7e2f7&amp;is=69d69177&amp;hm=79c796e51d9710a6cbe21e2ff9c7066692d1a0ab4dd565b28f65540ac619b5f3</t>
+  </si>
+  <si>
+    <t>obunga's bait</t>
+  </si>
+  <si>
+    <t>Nyx/Enchantress</t>
+  </si>
+  <si>
+    <t>VY</t>
+  </si>
+  <si>
+    <t>VZ</t>
+  </si>
+  <si>
+    <t>Va</t>
+  </si>
+  <si>
+    <t>Vb</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1491820739441987735/id_VY.png?ex=69d915d4&amp;is=69d7c454&amp;hm=3e26b0bcc2cd1f85bf8f04d0f27148158d2100d923cf1868f06c6264dfc72196</t>
+  </si>
+  <si>
+    <t>[o]</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1491820855208968263/id_VZ.jpg?ex=69d915f0&amp;is=69d7c470&amp;hm=00d173fd79df36b59d98e215e045e9c45b6798a163e2e1103cc5fb289c7a66cb</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1491820934812795031/id_Va.png?ex=69d91603&amp;is=69d7c483&amp;hm=6a5028c249f3579ffda9b301c3229dde3bf986242ff4075c3147abf456653c08</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1491821125829656738/id_Vb.jpg?ex=69d91631&amp;is=69d7c4b1&amp;hm=7e1da7dc50df6173832f1dd6a597e59c092a91d8afc6063fd6895a0c21a3a98c</t>
   </si>
 </sst>
 </file>
@@ -11882,11 +11915,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="94" x14ac:knownFonts="1">
+  <fonts count="95" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -12573,118 +12613,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="91" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="75" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="90" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="74" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="89" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="81" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="75" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="82" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="76" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="72" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="71" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="59" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="59" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="59" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="59" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="58" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="59" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="53" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="52" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="52" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -12693,18 +12734,18 @@
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="28" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="29" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -12718,15 +12759,15 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -12951,7 +12992,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1366"/>
+  <dimension ref="A1:O1370"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -69753,6 +69794,170 @@
         <v>3947</v>
       </c>
     </row>
+    <row r="1367" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1367">
+        <v>61</v>
+      </c>
+      <c r="B1367" s="7">
+        <v>25352781</v>
+      </c>
+      <c r="C1367" t="s">
+        <v>3948</v>
+      </c>
+      <c r="D1367" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1367" t="s">
+        <v>113</v>
+      </c>
+      <c r="F1367" s="29">
+        <v>46120</v>
+      </c>
+      <c r="G1367" s="56" t="s">
+        <v>504</v>
+      </c>
+      <c r="H1367" s="145" t="s">
+        <v>3949</v>
+      </c>
+      <c r="I1367" s="145" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1367" s="63" t="s">
+        <v>3950</v>
+      </c>
+      <c r="K1367">
+        <v>1368</v>
+      </c>
+      <c r="M1367" s="145" t="s">
+        <v>3955</v>
+      </c>
+      <c r="N1367" t="s">
+        <v>3954</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1368">
+        <v>61</v>
+      </c>
+      <c r="B1368" s="7">
+        <v>3050392</v>
+      </c>
+      <c r="C1368" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1368" t="s">
+        <v>470</v>
+      </c>
+      <c r="E1368" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1368" s="29">
+        <v>46121</v>
+      </c>
+      <c r="G1368" s="56">
+        <v>3.1041666666666665E-2</v>
+      </c>
+      <c r="H1368" s="145" t="s">
+        <v>840</v>
+      </c>
+      <c r="I1368" s="145" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1368" s="63" t="s">
+        <v>3951</v>
+      </c>
+      <c r="K1368">
+        <v>1369</v>
+      </c>
+      <c r="M1368" s="145" t="s">
+        <v>3955</v>
+      </c>
+      <c r="N1368" t="s">
+        <v>3956</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1369">
+        <v>61</v>
+      </c>
+      <c r="B1369" s="7">
+        <v>10476636</v>
+      </c>
+      <c r="C1369" t="s">
+        <v>3934</v>
+      </c>
+      <c r="D1369" t="s">
+        <v>3723</v>
+      </c>
+      <c r="E1369" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1369" s="29">
+        <v>46121</v>
+      </c>
+      <c r="G1369" s="56">
+        <v>5.9467592592592593E-2</v>
+      </c>
+      <c r="H1369" s="145" t="s">
+        <v>808</v>
+      </c>
+      <c r="I1369" s="145" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1369" s="63" t="s">
+        <v>3952</v>
+      </c>
+      <c r="K1369">
+        <v>1370</v>
+      </c>
+      <c r="M1369" s="145" t="s">
+        <v>3955</v>
+      </c>
+      <c r="N1369" t="s">
+        <v>3957</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1370">
+        <v>61</v>
+      </c>
+      <c r="B1370" s="7">
+        <v>14560807</v>
+      </c>
+      <c r="C1370" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1370" t="s">
+        <v>356</v>
+      </c>
+      <c r="E1370" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1370" s="29">
+        <v>46120</v>
+      </c>
+      <c r="G1370" s="56">
+        <v>0.10738425925925926</v>
+      </c>
+      <c r="H1370" s="145" t="s">
+        <v>808</v>
+      </c>
+      <c r="I1370" s="145" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1370" s="63" t="s">
+        <v>3953</v>
+      </c>
+      <c r="K1370">
+        <v>1371</v>
+      </c>
+      <c r="M1370" s="145" t="s">
+        <v>3955</v>
+      </c>
+      <c r="N1370" t="s">
+        <v>3958</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N1">
     <sortState ref="A2:N1357">

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11362" uniqueCount="3959">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11469" uniqueCount="3997">
   <si>
     <t>Ņ</t>
   </si>
@@ -11894,9 +11894,6 @@
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1491820739441987735/id_VY.png?ex=69d915d4&amp;is=69d7c454&amp;hm=3e26b0bcc2cd1f85bf8f04d0f27148158d2100d923cf1868f06c6264dfc72196</t>
   </si>
   <si>
-    <t>[o]</t>
-  </si>
-  <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1491820855208968263/id_VZ.jpg?ex=69d915f0&amp;is=69d7c470&amp;hm=00d173fd79df36b59d98e215e045e9c45b6798a163e2e1103cc5fb289c7a66cb</t>
   </si>
   <si>
@@ -11904,6 +11901,123 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1491821125829656738/id_Vb.jpg?ex=69d91631&amp;is=69d7c4b1&amp;hm=7e1da7dc50df6173832f1dd6a597e59c092a91d8afc6063fd6895a0c21a3a98c</t>
+  </si>
+  <si>
+    <t>Vc</t>
+  </si>
+  <si>
+    <t>life's scat porn</t>
+  </si>
+  <si>
+    <t>Vd</t>
+  </si>
+  <si>
+    <t>Elite Crashe/LC/Ares</t>
+  </si>
+  <si>
+    <t>Ve</t>
+  </si>
+  <si>
+    <t>FallenDemoin</t>
+  </si>
+  <si>
+    <t>Vf</t>
+  </si>
+  <si>
+    <t>DemoinDiciple</t>
+  </si>
+  <si>
+    <t>Vg</t>
+  </si>
+  <si>
+    <t>Nyx/Kronos</t>
+  </si>
+  <si>
+    <t>Vh</t>
+  </si>
+  <si>
+    <t>Ragnarok/LC/Kronos</t>
+  </si>
+  <si>
+    <t>I wanna surpass OGRE's</t>
+  </si>
+  <si>
+    <t>Hakuryu</t>
+  </si>
+  <si>
+    <t>Vi</t>
+  </si>
+  <si>
+    <t>Vj</t>
+  </si>
+  <si>
+    <t>Vk</t>
+  </si>
+  <si>
+    <t>Vl</t>
+  </si>
+  <si>
+    <t>POKOLIAN</t>
+  </si>
+  <si>
+    <t>Vm</t>
+  </si>
+  <si>
+    <t>Paladin/Ares</t>
+  </si>
+  <si>
+    <t>Vn</t>
+  </si>
+  <si>
+    <t>Vo</t>
+  </si>
+  <si>
+    <t>warrior2902</t>
+  </si>
+  <si>
+    <t>Stary kurczak &lt;3</t>
+  </si>
+  <si>
+    <t>Ragnarok/Nest Warden/Elite Crasher</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1492090478022361239/id_Vc.png?ex=69da110b&amp;is=69d8bf8b&amp;hm=99f6e398e28ff867b9de33ac4d35648cd5ebb671e2c56fce9ebb9fc183dc894c</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1492090559399985252/id_Vd.png?ex=69da111f&amp;is=69d8bf9f&amp;hm=657540de3e799141c09c1909f1de1e811e0500e8927f13fa966344812593a52f</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1492090619605160066/id_Ve.png?ex=69da112d&amp;is=69d8bfad&amp;hm=d81152a37600fd9327cc18d095c94886877e6ed42189c959cc8fdba5f220a7c2</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1492090679189307412/id_Vf.png?ex=69da113b&amp;is=69d8bfbb&amp;hm=f27c60acad8696edd5801b8e4cc4ad1cbf5d92a0c9addc6b7ee10908777f7354</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1492090730473193502/id_Vg.png?ex=69da1147&amp;is=69d8bfc7&amp;hm=b55a1c43216947a583886b2df33679a8fe1d9c603095996ffa6f0955a88b09ac</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1492090791902843021/id_Vh.png?ex=69da1156&amp;is=69d8bfd6&amp;hm=7b9608e44cddae029a7da2349c4565de7ffd283aff962917828ebcf6768a30b9</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1492090841009754132/id_Vi.png?ex=69da1162&amp;is=69d8bfe2&amp;hm=1274fb296934fd544c379dfcf240a65a240cd99fca96750715651f0e5896f53b</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1492090893644337222/id_Vj.png?ex=69da116e&amp;is=69d8bfee&amp;hm=d45a5cb248dbf1b50832409c89b6745d42a84acebf5a79cdba729f01c2ba3926</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1492090941274591334/id_Vk.png?ex=69da117a&amp;is=69d8bffa&amp;hm=b091c50b73d1d568fca43dd5f9db030b7efd11a3e9ef237c722d2f935e9c3137</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1492090989710540840/id_Vl.png?ex=69da1185&amp;is=69d8c005&amp;hm=ebd70f5abc6b739b8ba8e1b8b9a7629863a51df574126084c91a0f7fbb8d0bf2</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1492091037496119368/id_Vm.png?ex=69da1191&amp;is=69d8c011&amp;hm=b46d74c55241764c0cee8b066ecbe9774497a9662554778599e600edbfa6da40</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1492091083524407426/id_Vn.png?ex=69da119c&amp;is=69d8c01c&amp;hm=3b2ef5311644da4fdb4368ac9c7067f17c5105f60dd36520a0a3a35e70efdbad</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1492091135357616311/id_Vo.png?ex=69da11a8&amp;is=69d8c028&amp;hm=d71bfddea344fc744879c0e748c5acde2955159b317169a0fa852d1a6fb7fa10</t>
   </si>
 </sst>
 </file>
@@ -11915,11 +12029,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="95" x14ac:knownFonts="1">
+  <fonts count="96" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -12613,118 +12734,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="92" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="76" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="91" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="75" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="90" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="82" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="76" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="83" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="77" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="73" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="72" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="59" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="59" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="59" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="59" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="57" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="57" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="59" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="60" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="53" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="53" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="52" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="52" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -12733,18 +12855,18 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="29" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="30" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -12758,15 +12880,15 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -12992,7 +13114,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1370"/>
+  <dimension ref="A1:O1383"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -69828,8 +69950,8 @@
       <c r="K1367">
         <v>1368</v>
       </c>
-      <c r="M1367" s="145" t="s">
-        <v>3955</v>
+      <c r="M1367" s="57" t="s">
+        <v>857</v>
       </c>
       <c r="N1367" t="s">
         <v>3954</v>
@@ -69869,11 +69991,11 @@
       <c r="K1368">
         <v>1369</v>
       </c>
-      <c r="M1368" s="145" t="s">
+      <c r="M1368" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1368" t="s">
         <v>3955</v>
-      </c>
-      <c r="N1368" t="s">
-        <v>3956</v>
       </c>
     </row>
     <row r="1369" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69910,11 +70032,11 @@
       <c r="K1369">
         <v>1370</v>
       </c>
-      <c r="M1369" s="145" t="s">
-        <v>3955</v>
+      <c r="M1369" s="57" t="s">
+        <v>857</v>
       </c>
       <c r="N1369" t="s">
-        <v>3957</v>
+        <v>3956</v>
       </c>
     </row>
     <row r="1370" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69951,11 +70073,544 @@
       <c r="K1370">
         <v>1371</v>
       </c>
-      <c r="M1370" s="145" t="s">
-        <v>3955</v>
+      <c r="M1370" s="57" t="s">
+        <v>857</v>
       </c>
       <c r="N1370" t="s">
+        <v>3957</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1371">
+        <v>62</v>
+      </c>
+      <c r="B1371" s="7">
+        <v>43719222</v>
+      </c>
+      <c r="C1371" t="s">
+        <v>3959</v>
+      </c>
+      <c r="D1371" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1371" t="s">
+        <v>113</v>
+      </c>
+      <c r="F1371" s="29">
+        <v>46122</v>
+      </c>
+      <c r="G1371" s="56">
+        <v>0.20519675925925926</v>
+      </c>
+      <c r="H1371" s="146" t="s">
+        <v>838</v>
+      </c>
+      <c r="I1371" s="146" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1371" s="63" t="s">
         <v>3958</v>
+      </c>
+      <c r="K1371">
+        <v>1372</v>
+      </c>
+      <c r="M1371" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1371" t="s">
+        <v>3984</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1372">
+        <v>62</v>
+      </c>
+      <c r="B1372" s="7">
+        <v>10390275</v>
+      </c>
+      <c r="C1372" t="s">
+        <v>428</v>
+      </c>
+      <c r="D1372" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1372" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1372" s="29">
+        <v>45760</v>
+      </c>
+      <c r="G1372" s="56" t="s">
+        <v>504</v>
+      </c>
+      <c r="H1372" s="146" t="s">
+        <v>3961</v>
+      </c>
+      <c r="I1372" s="146" t="s">
+        <v>816</v>
+      </c>
+      <c r="J1372" s="63" t="s">
+        <v>3960</v>
+      </c>
+      <c r="K1372">
+        <v>1373</v>
+      </c>
+      <c r="M1372" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1372" t="s">
+        <v>3985</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1373">
+        <v>62</v>
+      </c>
+      <c r="B1373" s="7">
+        <v>4790253</v>
+      </c>
+      <c r="C1373" t="s">
+        <v>3963</v>
+      </c>
+      <c r="D1373" t="s">
+        <v>285</v>
+      </c>
+      <c r="E1373" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1373" s="29">
+        <v>45850</v>
+      </c>
+      <c r="G1373" s="56">
+        <v>5.8692129629629629E-2</v>
+      </c>
+      <c r="H1373" s="146" t="s">
+        <v>838</v>
+      </c>
+      <c r="I1373" s="146" t="s">
+        <v>292</v>
+      </c>
+      <c r="J1373" s="63" t="s">
+        <v>3962</v>
+      </c>
+      <c r="K1373">
+        <v>1374</v>
+      </c>
+      <c r="M1373" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1373" t="s">
+        <v>3986</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1374">
+        <v>62</v>
+      </c>
+      <c r="B1374" s="7">
+        <v>7656870</v>
+      </c>
+      <c r="C1374" t="s">
+        <v>3965</v>
+      </c>
+      <c r="D1374" t="s">
+        <v>128</v>
+      </c>
+      <c r="E1374" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1374" s="29">
+        <v>45950</v>
+      </c>
+      <c r="G1374" s="56">
+        <v>6.2395833333333338E-2</v>
+      </c>
+      <c r="H1374" s="146" t="s">
+        <v>1325</v>
+      </c>
+      <c r="I1374" s="146" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1374" s="63" t="s">
+        <v>3964</v>
+      </c>
+      <c r="K1374">
+        <v>1375</v>
+      </c>
+      <c r="M1374" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1374" t="s">
+        <v>3987</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1375">
+        <v>62</v>
+      </c>
+      <c r="B1375" s="7">
+        <v>8733988</v>
+      </c>
+      <c r="C1375" t="s">
+        <v>3965</v>
+      </c>
+      <c r="D1375" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1375" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1375" s="29">
+        <v>45956</v>
+      </c>
+      <c r="G1375" s="56">
+        <v>7.604166666666666E-2</v>
+      </c>
+      <c r="H1375" s="146" t="s">
+        <v>1111</v>
+      </c>
+      <c r="I1375" s="146" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1375" s="63" t="s">
+        <v>3966</v>
+      </c>
+      <c r="K1375">
+        <v>1376</v>
+      </c>
+      <c r="M1375" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1375" t="s">
+        <v>3988</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1376">
+        <v>62</v>
+      </c>
+      <c r="B1376" s="7">
+        <v>12284812</v>
+      </c>
+      <c r="C1376" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1376" t="s">
+        <v>96</v>
+      </c>
+      <c r="E1376" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1376" s="29">
+        <v>45964</v>
+      </c>
+      <c r="G1376" s="56">
+        <v>9.2604166666666668E-2</v>
+      </c>
+      <c r="H1376" s="146" t="s">
+        <v>3967</v>
+      </c>
+      <c r="I1376" s="146" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1376" s="63" t="s">
+        <v>3968</v>
+      </c>
+      <c r="K1376">
+        <v>1377</v>
+      </c>
+      <c r="M1376" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1376" t="s">
+        <v>3989</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1377">
+        <v>62</v>
+      </c>
+      <c r="B1377" s="7">
+        <v>14343403</v>
+      </c>
+      <c r="C1377" t="s">
+        <v>3970</v>
+      </c>
+      <c r="D1377" t="s">
+        <v>96</v>
+      </c>
+      <c r="E1377" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1377" s="29">
+        <v>45976</v>
+      </c>
+      <c r="G1377" s="56">
+        <v>0.10716435185185186</v>
+      </c>
+      <c r="H1377" s="146" t="s">
+        <v>3969</v>
+      </c>
+      <c r="I1377" s="146" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1377" s="63" t="s">
+        <v>3972</v>
+      </c>
+      <c r="K1377">
+        <v>1378</v>
+      </c>
+      <c r="M1377" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1377" t="s">
+        <v>3990</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1378">
+        <v>62</v>
+      </c>
+      <c r="B1378" s="7">
+        <v>12410166</v>
+      </c>
+      <c r="C1378" t="s">
+        <v>3971</v>
+      </c>
+      <c r="D1378" t="s">
+        <v>448</v>
+      </c>
+      <c r="E1378" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1378" s="29">
+        <v>46014</v>
+      </c>
+      <c r="G1378" s="56">
+        <v>7.3055555555555554E-2</v>
+      </c>
+      <c r="H1378" s="146" t="s">
+        <v>1280</v>
+      </c>
+      <c r="I1378" s="146" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1378" s="63" t="s">
+        <v>3973</v>
+      </c>
+      <c r="K1378">
+        <v>1379</v>
+      </c>
+      <c r="M1378" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1378" t="s">
+        <v>3991</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1379">
+        <v>62</v>
+      </c>
+      <c r="B1379" s="7">
+        <v>11173851</v>
+      </c>
+      <c r="C1379" t="s">
+        <v>428</v>
+      </c>
+      <c r="D1379" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1379" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1379" s="29">
+        <v>45704</v>
+      </c>
+      <c r="G1379" s="56">
+        <v>0.15314814814814814</v>
+      </c>
+      <c r="H1379" s="146" t="s">
+        <v>818</v>
+      </c>
+      <c r="I1379" s="146" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1379" s="63" t="s">
+        <v>3974</v>
+      </c>
+      <c r="K1379">
+        <v>1380</v>
+      </c>
+      <c r="M1379" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1379" t="s">
+        <v>3992</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1380">
+        <v>62</v>
+      </c>
+      <c r="B1380" s="7">
+        <v>34579941</v>
+      </c>
+      <c r="C1380" t="s">
+        <v>1107</v>
+      </c>
+      <c r="D1380" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1380" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1380" s="29">
+        <v>46109</v>
+      </c>
+      <c r="G1380" s="56" t="s">
+        <v>504</v>
+      </c>
+      <c r="H1380" s="146" t="s">
+        <v>3728</v>
+      </c>
+      <c r="I1380" s="146" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1380" s="63" t="s">
+        <v>3975</v>
+      </c>
+      <c r="K1380">
+        <v>1381</v>
+      </c>
+      <c r="M1380" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1380" t="s">
+        <v>3993</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1381">
+        <v>62</v>
+      </c>
+      <c r="B1381" s="7">
+        <v>9380000</v>
+      </c>
+      <c r="C1381" t="s">
+        <v>3976</v>
+      </c>
+      <c r="D1381" t="s">
+        <v>621</v>
+      </c>
+      <c r="E1381" t="s">
+        <v>3976</v>
+      </c>
+      <c r="F1381" s="29">
+        <v>46120</v>
+      </c>
+      <c r="G1381" s="56" t="s">
+        <v>504</v>
+      </c>
+      <c r="H1381" s="146" t="s">
+        <v>843</v>
+      </c>
+      <c r="I1381" s="146" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1381" s="63" t="s">
+        <v>3977</v>
+      </c>
+      <c r="K1381">
+        <v>1382</v>
+      </c>
+      <c r="M1381" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1381" t="s">
+        <v>3994</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1382">
+        <v>62</v>
+      </c>
+      <c r="B1382" s="7">
+        <v>18187409</v>
+      </c>
+      <c r="C1382" t="s">
+        <v>3981</v>
+      </c>
+      <c r="D1382" t="s">
+        <v>79</v>
+      </c>
+      <c r="E1382" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1382" s="29">
+        <v>46122</v>
+      </c>
+      <c r="G1382" s="56">
+        <v>0.11269675925925926</v>
+      </c>
+      <c r="H1382" s="146" t="s">
+        <v>3978</v>
+      </c>
+      <c r="I1382" s="146" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1382" s="63" t="s">
+        <v>3979</v>
+      </c>
+      <c r="K1382">
+        <v>1383</v>
+      </c>
+      <c r="M1382" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1382" t="s">
+        <v>3995</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1383">
+        <v>62</v>
+      </c>
+      <c r="B1383" s="7">
+        <v>9353760</v>
+      </c>
+      <c r="C1383" t="s">
+        <v>3982</v>
+      </c>
+      <c r="D1383" t="s">
+        <v>3868</v>
+      </c>
+      <c r="E1383" t="s">
+        <v>650</v>
+      </c>
+      <c r="F1383" s="29">
+        <v>46122</v>
+      </c>
+      <c r="G1383" s="56">
+        <v>4.7731481481481486E-2</v>
+      </c>
+      <c r="H1383" s="146" t="s">
+        <v>3983</v>
+      </c>
+      <c r="I1383" s="146" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1383" s="63" t="s">
+        <v>3980</v>
+      </c>
+      <c r="K1383">
+        <v>1384</v>
+      </c>
+      <c r="M1383" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1383" t="s">
+        <v>3996</v>
       </c>
     </row>
   </sheetData>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11469" uniqueCount="3997">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11510" uniqueCount="4011">
   <si>
     <t>Ņ</t>
   </si>
@@ -12018,6 +12018,48 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1492091135357616311/id_Vo.png?ex=69da11a8&amp;is=69d8c028&amp;hm=d71bfddea344fc744879c0e748c5acde2955159b317169a0fa852d1a6fb7fa10</t>
+  </si>
+  <si>
+    <t>Hazy Moon</t>
+  </si>
+  <si>
+    <t>Vp</t>
+  </si>
+  <si>
+    <t>Nest Guardian/Eris/Ragnarok</t>
+  </si>
+  <si>
+    <t>Vq</t>
+  </si>
+  <si>
+    <t>Vr</t>
+  </si>
+  <si>
+    <t>[] kiiro,celestialcat</t>
+  </si>
+  <si>
+    <t>Vs</t>
+  </si>
+  <si>
+    <t>LC/Paladin/Nest Warden</t>
+  </si>
+  <si>
+    <t>Vt</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1492458679574990909/id_Vp.png?ex=69db67f5&amp;is=69da1675&amp;hm=c50023aa4405d27b2f39c736ce3e99ea8ab41c10a5128217455670ff93b6457a</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1492458731701538846/id_Vq.png?ex=69db6802&amp;is=69da1682&amp;hm=1b31d249b2c581a8fe1b0f74a4aa786a3b7ddd08631af29cac3e47221da0a009</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1492458882558328832/id_Vr.png?ex=69db6826&amp;is=69da16a6&amp;hm=ccb9603dcd9e8e6f5fdfa3b07ce8905d43ddde5fa4056152526b0434fc4e9367</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1492458959934853180/id_Vs.png?ex=69db6838&amp;is=69da16b8&amp;hm=31a196535f3e2c0a93bf4771b37f17e2708ba72c53d7168e22eb47b53c4bbac0</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1492459010077491270/id_Vt.jpg?ex=69db6844&amp;is=69da16c4&amp;hm=a425fd4831173813253aafd2e53d950ac494efa52a8c009bc5e259c1c20bc712</t>
   </si>
 </sst>
 </file>
@@ -12029,11 +12071,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="96" x14ac:knownFonts="1">
+  <fonts count="97" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -12734,118 +12783,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="147">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="93" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="77" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="92" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="76" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="91" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="83" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="77" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="84" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="74" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="73" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="57" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="57" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="60" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="61" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="53" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="53" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -12854,18 +12904,18 @@
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="30" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="31" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -12879,15 +12929,15 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13114,7 +13164,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1383"/>
+  <dimension ref="A1:O1388"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -70613,6 +70663,211 @@
         <v>3996</v>
       </c>
     </row>
+    <row r="1384" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1384">
+        <v>63</v>
+      </c>
+      <c r="B1384" s="7">
+        <v>19970000</v>
+      </c>
+      <c r="C1384" t="s">
+        <v>120</v>
+      </c>
+      <c r="D1384" t="s">
+        <v>426</v>
+      </c>
+      <c r="E1384" t="s">
+        <v>3997</v>
+      </c>
+      <c r="F1384" s="29">
+        <v>46123</v>
+      </c>
+      <c r="G1384" s="56" t="s">
+        <v>504</v>
+      </c>
+      <c r="H1384" s="147" t="s">
+        <v>504</v>
+      </c>
+      <c r="I1384" s="147" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1384" s="63" t="s">
+        <v>3998</v>
+      </c>
+      <c r="K1384">
+        <v>1385</v>
+      </c>
+      <c r="M1384" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1384" t="s">
+        <v>4006</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1385">
+        <v>63</v>
+      </c>
+      <c r="B1385" s="7">
+        <v>5908296</v>
+      </c>
+      <c r="C1385" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1385" t="s">
+        <v>648</v>
+      </c>
+      <c r="E1385" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1385" s="29">
+        <v>46123</v>
+      </c>
+      <c r="G1385" s="56">
+        <v>0.11065972222222221</v>
+      </c>
+      <c r="H1385" s="147" t="s">
+        <v>3999</v>
+      </c>
+      <c r="I1385" s="147" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1385" s="63" t="s">
+        <v>4000</v>
+      </c>
+      <c r="K1385">
+        <v>1386</v>
+      </c>
+      <c r="M1385" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1385" t="s">
+        <v>4007</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1386">
+        <v>63</v>
+      </c>
+      <c r="B1386" s="7">
+        <v>14043248</v>
+      </c>
+      <c r="C1386" t="s">
+        <v>236</v>
+      </c>
+      <c r="D1386" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1386" t="s">
+        <v>236</v>
+      </c>
+      <c r="F1386" s="29">
+        <v>46123</v>
+      </c>
+      <c r="G1386" s="56">
+        <v>0.13692129629629629</v>
+      </c>
+      <c r="H1386" s="147" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1386" s="147" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1386" s="63" t="s">
+        <v>4001</v>
+      </c>
+      <c r="K1386">
+        <v>1387</v>
+      </c>
+      <c r="M1386" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1386" t="s">
+        <v>4008</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1387">
+        <v>63</v>
+      </c>
+      <c r="B1387" s="7">
+        <v>10483435</v>
+      </c>
+      <c r="C1387" t="s">
+        <v>4002</v>
+      </c>
+      <c r="D1387" t="s">
+        <v>401</v>
+      </c>
+      <c r="E1387" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1387" s="29">
+        <v>46123</v>
+      </c>
+      <c r="G1387" s="56">
+        <v>5.7592592592592591E-2</v>
+      </c>
+      <c r="H1387" s="147" t="s">
+        <v>1979</v>
+      </c>
+      <c r="I1387" s="147" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1387" s="63" t="s">
+        <v>4003</v>
+      </c>
+      <c r="K1387">
+        <v>1388</v>
+      </c>
+      <c r="M1387" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1387" t="s">
+        <v>4009</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1388">
+        <v>63</v>
+      </c>
+      <c r="B1388" s="7">
+        <v>11548314</v>
+      </c>
+      <c r="C1388" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1388" t="s">
+        <v>315</v>
+      </c>
+      <c r="E1388" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1388" s="29">
+        <v>46123</v>
+      </c>
+      <c r="G1388" s="56">
+        <v>6.3472222222222222E-2</v>
+      </c>
+      <c r="H1388" s="147" t="s">
+        <v>4004</v>
+      </c>
+      <c r="I1388" s="147" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1388" s="63" t="s">
+        <v>4005</v>
+      </c>
+      <c r="K1388">
+        <v>1389</v>
+      </c>
+      <c r="M1388" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1388" t="s">
+        <v>4010</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N1">
     <sortState ref="A2:N1357">

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11510" uniqueCount="4011">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11527" uniqueCount="4016">
   <si>
     <t>Ņ</t>
   </si>
@@ -12060,6 +12060,21 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1492459010077491270/id_Vt.jpg?ex=69db6844&amp;is=69da16c4&amp;hm=a425fd4831173813253aafd2e53d950ac494efa52a8c009bc5e259c1c20bc712</t>
+  </si>
+  <si>
+    <t>Förlorade i ljuset &lt;3</t>
+  </si>
+  <si>
+    <t>Vu</t>
+  </si>
+  <si>
+    <t>Vv</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1492536351763988672/id_Vu.png?ex=69dbb04c&amp;is=69da5ecc&amp;hm=99b6e7be25855e26091742eece8a114d4a5c68c81be4e50854c6e82714b4dd58</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1492536514515697744/id_Vv.png?ex=69dbb073&amp;is=69da5ef3&amp;hm=e12dd5696c6b34106be28e58d6611e71c94609e5448f6da5f50d6678f57e9a3f</t>
   </si>
 </sst>
 </file>
@@ -12071,11 +12086,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="97" x14ac:knownFonts="1">
+  <fonts count="98" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -12783,118 +12805,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="94" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="93" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="77" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="92" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="84" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="85" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="75" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="74" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="62" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="62" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="62" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="62" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="59" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="59" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="61" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="62" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="57" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -12903,18 +12926,18 @@
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="31" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -12928,15 +12951,15 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13164,7 +13187,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1388"/>
+  <dimension ref="A1:O1390"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -70868,6 +70891,88 @@
         <v>4010</v>
       </c>
     </row>
+    <row r="1389" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1389">
+        <v>63</v>
+      </c>
+      <c r="B1389" s="7">
+        <v>3935653</v>
+      </c>
+      <c r="C1389" t="s">
+        <v>4011</v>
+      </c>
+      <c r="D1389" t="s">
+        <v>615</v>
+      </c>
+      <c r="E1389" t="s">
+        <v>650</v>
+      </c>
+      <c r="F1389" s="29">
+        <v>46123</v>
+      </c>
+      <c r="G1389" s="56">
+        <v>3.9745370370370368E-2</v>
+      </c>
+      <c r="H1389" s="148" t="s">
+        <v>888</v>
+      </c>
+      <c r="I1389" s="148" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1389" s="63" t="s">
+        <v>4012</v>
+      </c>
+      <c r="K1389">
+        <v>1390</v>
+      </c>
+      <c r="M1389" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1389" t="s">
+        <v>4014</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1390">
+        <v>63</v>
+      </c>
+      <c r="B1390" s="7">
+        <v>8030000</v>
+      </c>
+      <c r="C1390" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1390" t="s">
+        <v>630</v>
+      </c>
+      <c r="E1390" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1390" s="29">
+        <v>46123</v>
+      </c>
+      <c r="G1390" s="56" t="s">
+        <v>504</v>
+      </c>
+      <c r="H1390" s="148" t="s">
+        <v>504</v>
+      </c>
+      <c r="I1390" s="148" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1390" s="63" t="s">
+        <v>4013</v>
+      </c>
+      <c r="K1390">
+        <v>1391</v>
+      </c>
+      <c r="M1390" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1390" t="s">
+        <v>4015</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N1">
     <sortState ref="A2:N1357">

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11527" uniqueCount="4016">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11561" uniqueCount="4026">
   <si>
     <t>Ņ</t>
   </si>
@@ -12075,6 +12075,36 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1492536514515697744/id_Vv.png?ex=69dbb073&amp;is=69da5ef3&amp;hm=e12dd5696c6b34106be28e58d6611e71c94609e5448f6da5f50d6678f57e9a3f</t>
+  </si>
+  <si>
+    <t>Spindle</t>
+  </si>
+  <si>
+    <t>Elite Crasher/Kronos/LC</t>
+  </si>
+  <si>
+    <t>Vw</t>
+  </si>
+  <si>
+    <t>Vx</t>
+  </si>
+  <si>
+    <t>Vy</t>
+  </si>
+  <si>
+    <t>Vz</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1492849996746326126/id_Vw.png?ex=69dcd467&amp;is=69db82e7&amp;hm=2a1778431bcb2d2606244548c2d678376df12e82a2efde7c4e5a8c83a895aec3</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1492850072973607014/id_Vx.png?ex=69dcd479&amp;is=69db82f9&amp;hm=13dcce3dd0a31b2610bde845389539e2eeb9de569a1afdf699bcf572edd23154</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1492850119693963344/id_Vy.jpg?ex=69dcd484&amp;is=69db8304&amp;hm=6c09997834447b5c6365f8d89ac8fcf43b34f605ad34fbd5d0aba1b1cae4995a</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1492850166619701309/id_Vz.png?ex=69dcd48f&amp;is=69db830f&amp;hm=91f76787e5f74de38736b05795ae0f934c5bf1f295970cac9bcbff717c5578c4</t>
   </si>
 </sst>
 </file>
@@ -12086,11 +12116,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="98" x14ac:knownFonts="1">
+  <fonts count="99" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -12805,118 +12842,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="149">
+  <cellXfs count="150">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="95" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="94" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="93" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="85" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="86" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="76" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="75" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="62" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="62" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="62" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="62" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="59" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="59" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="62" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="63" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="57" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -12925,18 +12963,18 @@
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="33" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -12950,15 +12988,15 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13187,7 +13225,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1390"/>
+  <dimension ref="A1:O1394"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -70954,8 +70992,8 @@
       <c r="G1390" s="56" t="s">
         <v>504</v>
       </c>
-      <c r="H1390" s="148" t="s">
-        <v>504</v>
+      <c r="H1390" s="149" t="s">
+        <v>843</v>
       </c>
       <c r="I1390" s="148" t="s">
         <v>809</v>
@@ -70971,6 +71009,170 @@
       </c>
       <c r="N1390" t="s">
         <v>4015</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1391">
+        <v>64</v>
+      </c>
+      <c r="B1391" s="7">
+        <v>6236778</v>
+      </c>
+      <c r="C1391" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1391" t="s">
+        <v>4016</v>
+      </c>
+      <c r="E1391" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1391" s="29">
+        <v>46124</v>
+      </c>
+      <c r="G1391" s="56">
+        <v>6.9641203703703705E-2</v>
+      </c>
+      <c r="H1391" s="149" t="s">
+        <v>4017</v>
+      </c>
+      <c r="I1391" s="149" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1391" s="63" t="s">
+        <v>4018</v>
+      </c>
+      <c r="K1391">
+        <v>1392</v>
+      </c>
+      <c r="M1391" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1391" t="s">
+        <v>4022</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1392">
+        <v>64</v>
+      </c>
+      <c r="B1392" s="7">
+        <v>10940000</v>
+      </c>
+      <c r="C1392" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1392" t="s">
+        <v>630</v>
+      </c>
+      <c r="E1392" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1392" s="29">
+        <v>46124</v>
+      </c>
+      <c r="G1392" s="56" t="s">
+        <v>504</v>
+      </c>
+      <c r="H1392" s="149" t="s">
+        <v>2035</v>
+      </c>
+      <c r="I1392" s="149" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1392" s="63" t="s">
+        <v>4019</v>
+      </c>
+      <c r="K1392">
+        <v>1393</v>
+      </c>
+      <c r="M1392" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1392" t="s">
+        <v>4023</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1393">
+        <v>64</v>
+      </c>
+      <c r="B1393" s="7">
+        <v>3087377</v>
+      </c>
+      <c r="C1393" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1393" t="s">
+        <v>470</v>
+      </c>
+      <c r="E1393" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1393" s="29">
+        <v>46124</v>
+      </c>
+      <c r="G1393" s="56">
+        <v>2.8472222222222222E-2</v>
+      </c>
+      <c r="H1393" s="149" t="s">
+        <v>838</v>
+      </c>
+      <c r="I1393" s="149" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1393" s="63" t="s">
+        <v>4020</v>
+      </c>
+      <c r="K1393">
+        <v>1394</v>
+      </c>
+      <c r="M1393" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1393" t="s">
+        <v>4024</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1394">
+        <v>64</v>
+      </c>
+      <c r="B1394" s="7">
+        <v>8459179</v>
+      </c>
+      <c r="C1394" t="s">
+        <v>3715</v>
+      </c>
+      <c r="D1394" t="s">
+        <v>395</v>
+      </c>
+      <c r="E1394" t="s">
+        <v>236</v>
+      </c>
+      <c r="F1394" s="29">
+        <v>46124</v>
+      </c>
+      <c r="G1394" s="56" t="s">
+        <v>504</v>
+      </c>
+      <c r="H1394" s="149" t="s">
+        <v>820</v>
+      </c>
+      <c r="I1394" s="149" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1394" s="63" t="s">
+        <v>4021</v>
+      </c>
+      <c r="K1394">
+        <v>1395</v>
+      </c>
+      <c r="M1394" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1394" t="s">
+        <v>4025</v>
       </c>
     </row>
   </sheetData>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11561" uniqueCount="4026">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11665" uniqueCount="4063">
   <si>
     <t>Ņ</t>
   </si>
@@ -12098,13 +12098,124 @@
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1492849996746326126/id_Vw.png?ex=69dcd467&amp;is=69db82e7&amp;hm=2a1778431bcb2d2606244548c2d678376df12e82a2efde7c4e5a8c83a895aec3</t>
   </si>
   <si>
-    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1492850072973607014/id_Vx.png?ex=69dcd479&amp;is=69db82f9&amp;hm=13dcce3dd0a31b2610bde845389539e2eeb9de569a1afdf699bcf572edd23154</t>
-  </si>
-  <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1492850119693963344/id_Vy.jpg?ex=69dcd484&amp;is=69db8304&amp;hm=6c09997834447b5c6365f8d89ac8fcf43b34f605ad34fbd5d0aba1b1cae4995a</t>
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1492850166619701309/id_Vz.png?ex=69dcd48f&amp;is=69db830f&amp;hm=91f76787e5f74de38736b05795ae0f934c5bf1f295970cac9bcbff717c5578c4</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>V0</t>
+  </si>
+  <si>
+    <t>roddarichard</t>
+  </si>
+  <si>
+    <t>im rusty</t>
+  </si>
+  <si>
+    <t>V2</t>
+  </si>
+  <si>
+    <t>V3</t>
+  </si>
+  <si>
+    <t>V4</t>
+  </si>
+  <si>
+    <t>V5</t>
+  </si>
+  <si>
+    <t>Elf Militia</t>
+  </si>
+  <si>
+    <t>e no 3m :cc</t>
+  </si>
+  <si>
+    <t>browskiwastaken</t>
+  </si>
+  <si>
+    <t>[PP-69/Sus-420] Copium 😔</t>
+  </si>
+  <si>
+    <t>browskiwastaken=redit</t>
+  </si>
+  <si>
+    <t>V6</t>
+  </si>
+  <si>
+    <t>V7</t>
+  </si>
+  <si>
+    <t>nerf nyx</t>
+  </si>
+  <si>
+    <t>Celestial</t>
+  </si>
+  <si>
+    <t>V8</t>
+  </si>
+  <si>
+    <t>V9</t>
+  </si>
+  <si>
+    <t>nerf nyx when</t>
+  </si>
+  <si>
+    <t>3m ambulance?</t>
+  </si>
+  <si>
+    <t>V(</t>
+  </si>
+  <si>
+    <t>V)</t>
+  </si>
+  <si>
+    <t>WA</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1471844339931021342/1493244877591285910/id_Vx.jpg?ex=69de4429&amp;is=69dcf2a9&amp;hm=ace429a9315eb9860896bf2fe8d94b9dd79e24a78d9d68c98f46e3c3ffa1b51b</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1493246224826892359/id_V0.png?ex=69de456b&amp;is=69dcf3eb&amp;hm=2aedb2e4d8a084ca2f28c352d70b466e76a8b1b26550b26d200771b2a1fd64f0</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1493246451923550300/id_V1.jpg?ex=69de45a1&amp;is=69dcf421&amp;hm=89288d0d2a9700e4b283eacba57885785736807d3c3a76550cfe22134eb4f9bc</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1493246501919391926/id_V2.jpg?ex=69de45ad&amp;is=69dcf42d&amp;hm=205638f2545e3fbb4ba13cf72ee641c6a3bf7a720a36d3e3c160e5a66813a558</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1493246545074589907/id_V3.jpg?ex=69de45b7&amp;is=69dcf437&amp;hm=9895530969feea85608b427980220621a301841a73c12898cb9fe9361ed09d25</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1493246603685793822/id_V4.jpg?ex=69de45c5&amp;is=69dcf445&amp;hm=5c97256a194d8933ad5d6f2fba31efaa571ca31847c7466d3540429b02342c35</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1493246648879681586/id_V5.jpg?ex=69de45d0&amp;is=69dcf450&amp;hm=4fbc445111ad2e66ce4ab345a81236217a63e258bf2aaa1deadc3aa24ddf6929</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1493246691980345567/id_V6.jpg?ex=69de45da&amp;is=69dcf45a&amp;hm=ec0560ffa5cdf21115aa4ad18c8673e26f10956b02a6dd30702b9d8c630239a0</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1493246732341874698/id_V7.jpg?ex=69de45e4&amp;is=69dcf464&amp;hm=d36f0d8175a76ee677c2cb8871a98724306caccb9219ecfce87777223204c8b6</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1493246772481622016/id_V8.jpg?ex=69de45ed&amp;is=69dcf46d&amp;hm=618578848c877fdb1848b494de6051a1df7648bbd7ebd8eb14f8fd780575c46d</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1493246842174181428/id_V9.png?ex=69de45fe&amp;is=69dcf47e&amp;hm=a731dbcde3b2bf7ac383a3c1b59c8f2a61e06b1cccf6ba3a7eff4d3d80040c31</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1493246934343876770/id_V.jpg?ex=69de4614&amp;is=69dcf494&amp;hm=1131f2114fc6ab5b4fbbba6984fe77c92d94465feb64abff193b7d59c3fca391</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1493246979201830943/id_V.png?ex=69de461f&amp;is=69dcf49f&amp;hm=699d3c2422cc22f886a2ef8020e8986abbbbe4fdddc56e524e17da600268a900</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1493247094830534676/id_WA.png?ex=69de463a&amp;is=69dcf4ba&amp;hm=507a87cc75b438acf40c8bd7e58795371ec058e888b8d1e5b3003ba58eb69102</t>
   </si>
 </sst>
 </file>
@@ -12116,11 +12227,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="99" x14ac:knownFonts="1">
+  <fonts count="100" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -12842,118 +12960,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="151">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="96" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="95" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="94" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="86" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="87" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="81" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="77" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="76" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="63" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="59" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="57" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="57" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -12962,18 +13081,18 @@
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="33" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="34" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -12987,15 +13106,15 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13225,7 +13344,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1394"/>
+  <dimension ref="A1:O1407"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -42312,7 +42431,7 @@
         <v>76</v>
       </c>
       <c r="E693" t="s">
-        <v>485</v>
+        <v>4027</v>
       </c>
       <c r="F693" s="29">
         <v>44676</v>
@@ -43300,7 +43419,7 @@
         <v>76</v>
       </c>
       <c r="E717" t="s">
-        <v>485</v>
+        <v>4027</v>
       </c>
       <c r="F717" s="29">
         <v>44676</v>
@@ -71057,7 +71176,7 @@
         <v>64</v>
       </c>
       <c r="B1392" s="7">
-        <v>10940000</v>
+        <v>10948283</v>
       </c>
       <c r="C1392" t="s">
         <v>17</v>
@@ -71090,7 +71209,7 @@
         <v>857</v>
       </c>
       <c r="N1392" t="s">
-        <v>4023</v>
+        <v>4049</v>
       </c>
     </row>
     <row r="1393" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71131,7 +71250,7 @@
         <v>857</v>
       </c>
       <c r="N1393" t="s">
-        <v>4024</v>
+        <v>4023</v>
       </c>
     </row>
     <row r="1394" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71172,7 +71291,540 @@
         <v>857</v>
       </c>
       <c r="N1394" t="s">
+        <v>4024</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1395">
+        <v>65</v>
+      </c>
+      <c r="B1395" s="7">
+        <v>21177695</v>
+      </c>
+      <c r="C1395" t="s">
+        <v>3689</v>
+      </c>
+      <c r="D1395" t="s">
+        <v>366</v>
+      </c>
+      <c r="E1395" t="s">
+        <v>697</v>
+      </c>
+      <c r="F1395" s="29">
+        <v>46100</v>
+      </c>
+      <c r="G1395" s="56">
+        <v>0.1496990740740741</v>
+      </c>
+      <c r="H1395" s="150" t="s">
+        <v>1630</v>
+      </c>
+      <c r="I1395" s="150" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1395" s="63" t="s">
+        <v>4026</v>
+      </c>
+      <c r="K1395">
+        <v>1396</v>
+      </c>
+      <c r="M1395" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1395" t="s">
+        <v>4050</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1396">
+        <v>65</v>
+      </c>
+      <c r="B1396" s="7">
+        <v>9514769</v>
+      </c>
+      <c r="C1396" t="s">
+        <v>4028</v>
+      </c>
+      <c r="D1396" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1396" t="s">
+        <v>4027</v>
+      </c>
+      <c r="F1396" s="29">
+        <v>44675</v>
+      </c>
+      <c r="G1396" s="56">
+        <v>4.612268518518519E-2</v>
+      </c>
+      <c r="H1396" s="150" t="s">
+        <v>1110</v>
+      </c>
+      <c r="I1396" s="150" t="s">
+        <v>816</v>
+      </c>
+      <c r="J1396" s="63" t="s">
         <v>4025</v>
+      </c>
+      <c r="K1396">
+        <v>1397</v>
+      </c>
+      <c r="M1396" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1396" t="s">
+        <v>4051</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1397">
+        <v>65</v>
+      </c>
+      <c r="B1397" s="7">
+        <v>11164114</v>
+      </c>
+      <c r="C1397" t="s">
+        <v>485</v>
+      </c>
+      <c r="D1397" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1397" t="s">
+        <v>4027</v>
+      </c>
+      <c r="F1397" s="29">
+        <v>44677</v>
+      </c>
+      <c r="G1397" s="56">
+        <v>6.8703703703703697E-2</v>
+      </c>
+      <c r="H1397" s="150" t="s">
+        <v>840</v>
+      </c>
+      <c r="I1397" s="150" t="s">
+        <v>816</v>
+      </c>
+      <c r="J1397" s="63" t="s">
+        <v>4029</v>
+      </c>
+      <c r="K1397">
+        <v>1398</v>
+      </c>
+      <c r="M1397" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1397" t="s">
+        <v>4052</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1398">
+        <v>65</v>
+      </c>
+      <c r="B1398" s="7">
+        <v>11319841</v>
+      </c>
+      <c r="C1398" t="s">
+        <v>869</v>
+      </c>
+      <c r="D1398" t="s">
+        <v>438</v>
+      </c>
+      <c r="E1398" t="s">
+        <v>4027</v>
+      </c>
+      <c r="F1398" s="29">
+        <v>44679</v>
+      </c>
+      <c r="G1398" s="56">
+        <v>3.107638888888889E-2</v>
+      </c>
+      <c r="H1398" s="150" t="s">
+        <v>968</v>
+      </c>
+      <c r="I1398" s="150" t="s">
+        <v>816</v>
+      </c>
+      <c r="J1398" s="63" t="s">
+        <v>4030</v>
+      </c>
+      <c r="K1398">
+        <v>1399</v>
+      </c>
+      <c r="M1398" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1398" t="s">
+        <v>4053</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1399">
+        <v>65</v>
+      </c>
+      <c r="B1399" s="7">
+        <v>3397005</v>
+      </c>
+      <c r="C1399" t="s">
+        <v>4034</v>
+      </c>
+      <c r="D1399" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1399" t="s">
+        <v>4027</v>
+      </c>
+      <c r="F1399" s="29">
+        <v>44556</v>
+      </c>
+      <c r="G1399" s="56">
+        <v>2.7152777777777779E-2</v>
+      </c>
+      <c r="H1399" s="150" t="s">
+        <v>4033</v>
+      </c>
+      <c r="I1399" s="150" t="s">
+        <v>816</v>
+      </c>
+      <c r="J1399" s="63" t="s">
+        <v>4031</v>
+      </c>
+      <c r="K1399">
+        <v>1400</v>
+      </c>
+      <c r="M1399" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1399" t="s">
+        <v>4054</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1400">
+        <v>65</v>
+      </c>
+      <c r="B1400" s="7">
+        <v>3817177</v>
+      </c>
+      <c r="C1400" t="s">
+        <v>4036</v>
+      </c>
+      <c r="D1400" t="s">
+        <v>3914</v>
+      </c>
+      <c r="E1400" t="s">
+        <v>4035</v>
+      </c>
+      <c r="F1400" s="29">
+        <v>44579</v>
+      </c>
+      <c r="G1400" s="56">
+        <v>5.2650462962962961E-2</v>
+      </c>
+      <c r="H1400" s="150" t="s">
+        <v>820</v>
+      </c>
+      <c r="I1400" s="150" t="s">
+        <v>816</v>
+      </c>
+      <c r="J1400" s="63" t="s">
+        <v>4032</v>
+      </c>
+      <c r="K1400">
+        <v>1401</v>
+      </c>
+      <c r="M1400" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1400" t="s">
+        <v>4055</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1401">
+        <v>65</v>
+      </c>
+      <c r="B1401" s="7">
+        <v>4527031</v>
+      </c>
+      <c r="C1401" t="s">
+        <v>4037</v>
+      </c>
+      <c r="D1401" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1401" t="s">
+        <v>4035</v>
+      </c>
+      <c r="F1401" s="29">
+        <v>44549</v>
+      </c>
+      <c r="G1401" s="56">
+        <v>6.3622685185185185E-2</v>
+      </c>
+      <c r="H1401" s="150" t="s">
+        <v>820</v>
+      </c>
+      <c r="I1401" s="150" t="s">
+        <v>816</v>
+      </c>
+      <c r="J1401" s="63" t="s">
+        <v>4038</v>
+      </c>
+      <c r="K1401">
+        <v>1402</v>
+      </c>
+      <c r="M1401" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1401" t="s">
+        <v>4056</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1402">
+        <v>65</v>
+      </c>
+      <c r="B1402" s="7">
+        <v>3055127</v>
+      </c>
+      <c r="C1402" t="s">
+        <v>4040</v>
+      </c>
+      <c r="D1402" t="s">
+        <v>203</v>
+      </c>
+      <c r="E1402" t="s">
+        <v>4027</v>
+      </c>
+      <c r="F1402" s="29">
+        <v>44563</v>
+      </c>
+      <c r="G1402" s="56">
+        <v>4.2222222222222223E-2</v>
+      </c>
+      <c r="H1402" s="150" t="s">
+        <v>4041</v>
+      </c>
+      <c r="I1402" s="150" t="s">
+        <v>292</v>
+      </c>
+      <c r="J1402" s="63" t="s">
+        <v>4039</v>
+      </c>
+      <c r="K1402">
+        <v>1403</v>
+      </c>
+      <c r="M1402" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1402" t="s">
+        <v>4057</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1403">
+        <v>65</v>
+      </c>
+      <c r="B1403" s="7">
+        <v>2745915</v>
+      </c>
+      <c r="C1403" t="s">
+        <v>4044</v>
+      </c>
+      <c r="D1403" t="s">
+        <v>489</v>
+      </c>
+      <c r="E1403" t="s">
+        <v>4027</v>
+      </c>
+      <c r="F1403" s="29">
+        <v>44582</v>
+      </c>
+      <c r="G1403" s="56">
+        <v>4.0543981481481479E-2</v>
+      </c>
+      <c r="H1403" s="150" t="s">
+        <v>1281</v>
+      </c>
+      <c r="I1403" s="150" t="s">
+        <v>816</v>
+      </c>
+      <c r="J1403" s="63" t="s">
+        <v>4042</v>
+      </c>
+      <c r="K1403">
+        <v>1404</v>
+      </c>
+      <c r="M1403" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1403" t="s">
+        <v>4058</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1404">
+        <v>65</v>
+      </c>
+      <c r="B1404" s="7">
+        <v>11625770</v>
+      </c>
+      <c r="C1404" t="s">
+        <v>182</v>
+      </c>
+      <c r="D1404" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1404" t="s">
+        <v>4027</v>
+      </c>
+      <c r="F1404" s="29">
+        <v>46142</v>
+      </c>
+      <c r="G1404" s="56">
+        <v>7.2013888888888891E-2</v>
+      </c>
+      <c r="H1404" s="150" t="s">
+        <v>820</v>
+      </c>
+      <c r="I1404" s="150" t="s">
+        <v>816</v>
+      </c>
+      <c r="J1404" s="63" t="s">
+        <v>4043</v>
+      </c>
+      <c r="K1404">
+        <v>1405</v>
+      </c>
+      <c r="M1404" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1404" t="s">
+        <v>4059</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1405">
+        <v>65</v>
+      </c>
+      <c r="B1405" s="7">
+        <v>3379190</v>
+      </c>
+      <c r="C1405" t="s">
+        <v>4045</v>
+      </c>
+      <c r="D1405" t="s">
+        <v>489</v>
+      </c>
+      <c r="E1405" t="s">
+        <v>4027</v>
+      </c>
+      <c r="F1405" s="29">
+        <v>44590</v>
+      </c>
+      <c r="G1405" s="56">
+        <v>4.4826388888888895E-2</v>
+      </c>
+      <c r="H1405" s="150" t="s">
+        <v>820</v>
+      </c>
+      <c r="I1405" s="150" t="s">
+        <v>816</v>
+      </c>
+      <c r="J1405" s="63" t="s">
+        <v>4046</v>
+      </c>
+      <c r="K1405">
+        <v>1406</v>
+      </c>
+      <c r="M1405" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1405" t="s">
+        <v>4060</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1406">
+        <v>65</v>
+      </c>
+      <c r="B1406" s="7">
+        <v>6209904</v>
+      </c>
+      <c r="C1406" t="s">
+        <v>478</v>
+      </c>
+      <c r="D1406" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1406" t="s">
+        <v>479</v>
+      </c>
+      <c r="F1406" s="29">
+        <v>44696</v>
+      </c>
+      <c r="G1406" s="56">
+        <v>5.6840277777777781E-2</v>
+      </c>
+      <c r="H1406" s="150" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1406" s="150" t="s">
+        <v>816</v>
+      </c>
+      <c r="J1406" s="63" t="s">
+        <v>4047</v>
+      </c>
+      <c r="K1406">
+        <v>1407</v>
+      </c>
+      <c r="M1406" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1406" t="s">
+        <v>4061</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1407">
+        <v>65</v>
+      </c>
+      <c r="B1407" s="7">
+        <v>5404191</v>
+      </c>
+      <c r="C1407" t="s">
+        <v>871</v>
+      </c>
+      <c r="D1407" t="s">
+        <v>489</v>
+      </c>
+      <c r="E1407" t="s">
+        <v>4027</v>
+      </c>
+      <c r="F1407" s="29">
+        <v>44680</v>
+      </c>
+      <c r="G1407" s="56">
+        <v>5.0219907407407414E-2</v>
+      </c>
+      <c r="H1407" s="150" t="s">
+        <v>820</v>
+      </c>
+      <c r="I1407" s="150" t="s">
+        <v>816</v>
+      </c>
+      <c r="J1407" s="63" t="s">
+        <v>4048</v>
+      </c>
+      <c r="K1407">
+        <v>1408</v>
+      </c>
+      <c r="M1407" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1407" t="s">
+        <v>4062</v>
       </c>
     </row>
   </sheetData>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11665" uniqueCount="4063">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11696" uniqueCount="4074">
   <si>
     <t>Ņ</t>
   </si>
@@ -10808,9 +10808,6 @@
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1480237970266259477/id_TU.png?ex=69aef289&amp;is=69ada109&amp;hm=0e268239c376476b592040d98594fff95e9e58b94cf5726e1357ee1981e1e105</t>
   </si>
   <si>
-    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1480238016097288306/id_TV.png?ex=69aef294&amp;is=69ada114&amp;hm=8ac4bd883f3eabe52081addcab4c7e5f5027807f13875791d27be01793391452</t>
-  </si>
-  <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1480238064608612473/id_TW.png?ex=69aef2a0&amp;is=69ada120&amp;hm=e3cfaa6801cbf77a1aaab3462b81870b1559568db094267ab6f084fbe026e9c2</t>
   </si>
   <si>
@@ -12216,6 +12213,42 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1493247094830534676/id_WA.png?ex=69de463a&amp;is=69dcf4ba&amp;hm=507a87cc75b438acf40c8bd7e58795371ec058e888b8d1e5b3003ba58eb69102</t>
+  </si>
+  <si>
+    <t>WB</t>
+  </si>
+  <si>
+    <t>FS⬆️</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1471844339931021342/1494590697292959846/id_TV.jpg?ex=69e3298e&amp;is=69e1d80e&amp;hm=37430cf5f0ca3c820fb1a7b4d27572ece8117d6c6702abc1e639beda41071bf9</t>
+  </si>
+  <si>
+    <t>WC</t>
+  </si>
+  <si>
+    <t>Nyx/Enchantress/Sorcerer</t>
+  </si>
+  <si>
+    <t>WD</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1494593655049289810/id_WB.jpg?ex=69e32c4f&amp;is=69e1dacf&amp;hm=345c058011c4ce06ad76ee8dc1f6c9e87e3702e9494762054b4de7ace4289d33</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1494593703958941786/id_WC.png?ex=69e32c5b&amp;is=69e1dadb&amp;hm=af2e0973c664c7b4fe6a3018aee898209a1bf3c1164888462b148d55b52fb911</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1494593751027290152/id_WD.png?ex=69e32c66&amp;is=69e1dae6&amp;hm=3fc0ea1c4ea4744a5a7a91ee9362c74a2998ba6f32f31e09d886425de7514d60</t>
+  </si>
+  <si>
+    <t>WE</t>
+  </si>
+  <si>
+    <t>Zaphkiel/Kronos</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1494594362443698286/id_WE.png?ex=69e32cf8&amp;is=69e1db78&amp;hm=8f2623622210c6789379d3dced64784b05736a8ebbade9bdd077a9a70e2c5fa5</t>
   </si>
 </sst>
 </file>
@@ -12227,11 +12260,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="100" x14ac:knownFonts="1">
+  <fonts count="101" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -12960,118 +13000,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="151">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="97" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="81" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="96" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="95" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="87" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="81" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="88" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="82" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="77" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="62" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="62" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="65" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="59" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="57" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="57" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13080,18 +13121,18 @@
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="34" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="35" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13105,15 +13146,15 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13344,7 +13385,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1407"/>
+  <dimension ref="A1:O1411"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -13494,7 +13535,7 @@
         <v>857</v>
       </c>
       <c r="N3" t="s">
-        <v>3645</v>
+        <v>3644</v>
       </c>
       <c r="O3" s="1"/>
     </row>
@@ -16941,7 +16982,7 @@
         <v>30380000</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>3900</v>
+        <v>3899</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>5</v>
@@ -18617,7 +18658,7 @@
         <v>26686674</v>
       </c>
       <c r="C123" t="s">
-        <v>3901</v>
+        <v>3900</v>
       </c>
       <c r="D123" t="s">
         <v>7</v>
@@ -27129,7 +27170,7 @@
         <v>17859596</v>
       </c>
       <c r="C324" t="s">
-        <v>3611</v>
+        <v>3610</v>
       </c>
       <c r="D324" t="s">
         <v>15</v>
@@ -36090,7 +36131,7 @@
         <v>9</v>
       </c>
       <c r="D540" s="142" t="s">
-        <v>3924</v>
+        <v>3923</v>
       </c>
       <c r="E540" t="s">
         <v>3434</v>
@@ -42431,7 +42472,7 @@
         <v>76</v>
       </c>
       <c r="E693" t="s">
-        <v>4027</v>
+        <v>4026</v>
       </c>
       <c r="F693" s="29">
         <v>44676</v>
@@ -43044,7 +43085,7 @@
         <v>409</v>
       </c>
       <c r="D708" t="s">
-        <v>3922</v>
+        <v>3921</v>
       </c>
       <c r="E708" t="s">
         <v>410</v>
@@ -43419,7 +43460,7 @@
         <v>76</v>
       </c>
       <c r="E717" t="s">
-        <v>4027</v>
+        <v>4026</v>
       </c>
       <c r="F717" s="29">
         <v>44676</v>
@@ -44824,7 +44865,7 @@
         <v>787</v>
       </c>
       <c r="D751" t="s">
-        <v>3924</v>
+        <v>3923</v>
       </c>
       <c r="E751" s="52" t="s">
         <v>441</v>
@@ -45978,7 +46019,7 @@
         <v>416</v>
       </c>
       <c r="D779" t="s">
-        <v>3923</v>
+        <v>3922</v>
       </c>
       <c r="E779" t="s">
         <v>8</v>
@@ -57400,7 +57441,7 @@
         <v>681</v>
       </c>
       <c r="E1056" s="131" t="s">
-        <v>3680</v>
+        <v>3679</v>
       </c>
       <c r="F1056" s="29">
         <v>46020</v>
@@ -60431,7 +60472,7 @@
         <v>3683365</v>
       </c>
       <c r="C1130" s="139" t="s">
-        <v>3881</v>
+        <v>3880</v>
       </c>
       <c r="D1130" s="103" t="s">
         <v>374</v>
@@ -60472,7 +60513,7 @@
         <v>16246656</v>
       </c>
       <c r="C1131" s="139" t="s">
-        <v>3881</v>
+        <v>3880</v>
       </c>
       <c r="D1131" s="103" t="s">
         <v>66</v>
@@ -60513,7 +60554,7 @@
         <v>7945684</v>
       </c>
       <c r="C1132" s="139" t="s">
-        <v>3881</v>
+        <v>3880</v>
       </c>
       <c r="D1132" s="103" t="s">
         <v>24</v>
@@ -61046,7 +61087,7 @@
         <v>31682775</v>
       </c>
       <c r="C1145" s="139" t="s">
-        <v>3881</v>
+        <v>3880</v>
       </c>
       <c r="D1145" s="105" t="s">
         <v>15</v>
@@ -61333,7 +61374,7 @@
         <v>39229228</v>
       </c>
       <c r="C1152" s="139" t="s">
-        <v>3881</v>
+        <v>3880</v>
       </c>
       <c r="D1152" s="109" t="s">
         <v>13</v>
@@ -64719,7 +64760,7 @@
         <v>809</v>
       </c>
       <c r="J1234" s="63" t="s">
-        <v>3601</v>
+        <v>3600</v>
       </c>
       <c r="K1234">
         <v>1235</v>
@@ -64736,7 +64777,7 @@
         <v>47</v>
       </c>
       <c r="B1235" s="7">
-        <v>41650000</v>
+        <v>41657675</v>
       </c>
       <c r="C1235" t="s">
         <v>3586</v>
@@ -64750,11 +64791,11 @@
       <c r="F1235" s="29">
         <v>46089</v>
       </c>
-      <c r="G1235" s="56" t="s">
-        <v>504</v>
+      <c r="G1235" s="56">
+        <v>0.29061342592592593</v>
       </c>
       <c r="H1235" t="s">
-        <v>888</v>
+        <v>2501</v>
       </c>
       <c r="I1235" t="s">
         <v>809</v>
@@ -64769,7 +64810,7 @@
         <v>857</v>
       </c>
       <c r="N1235" t="s">
-        <v>3593</v>
+        <v>4064</v>
       </c>
     </row>
     <row r="1236" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64810,7 +64851,7 @@
         <v>857</v>
       </c>
       <c r="N1236" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
     </row>
     <row r="1237" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64851,7 +64892,7 @@
         <v>857</v>
       </c>
       <c r="N1237" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
     </row>
     <row r="1238" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64892,7 +64933,7 @@
         <v>857</v>
       </c>
       <c r="N1238" t="s">
-        <v>3596</v>
+        <v>3595</v>
       </c>
     </row>
     <row r="1239" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64933,7 +64974,7 @@
         <v>857</v>
       </c>
       <c r="N1239" t="s">
-        <v>3606</v>
+        <v>3605</v>
       </c>
     </row>
     <row r="1240" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64944,7 +64985,7 @@
         <v>13795880</v>
       </c>
       <c r="C1240" t="s">
-        <v>3600</v>
+        <v>3599</v>
       </c>
       <c r="D1240" t="s">
         <v>66</v>
@@ -64959,13 +65000,13 @@
         <v>9.8101851851851843E-2</v>
       </c>
       <c r="H1240" t="s">
-        <v>3599</v>
+        <v>3598</v>
       </c>
       <c r="I1240" t="s">
         <v>809</v>
       </c>
       <c r="J1240" s="63" t="s">
-        <v>3597</v>
+        <v>3596</v>
       </c>
       <c r="K1240">
         <v>1241</v>
@@ -64974,7 +65015,7 @@
         <v>857</v>
       </c>
       <c r="N1240" t="s">
-        <v>3607</v>
+        <v>3606</v>
       </c>
     </row>
     <row r="1241" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64985,7 +65026,7 @@
         <v>34231677</v>
       </c>
       <c r="C1241" t="s">
-        <v>3602</v>
+        <v>3601</v>
       </c>
       <c r="D1241" t="s">
         <v>9</v>
@@ -65006,7 +65047,7 @@
         <v>809</v>
       </c>
       <c r="J1241" s="63" t="s">
-        <v>3598</v>
+        <v>3597</v>
       </c>
       <c r="K1241">
         <v>1242</v>
@@ -65015,7 +65056,7 @@
         <v>857</v>
       </c>
       <c r="N1241" t="s">
-        <v>3608</v>
+        <v>3607</v>
       </c>
     </row>
     <row r="1242" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65047,7 +65088,7 @@
         <v>809</v>
       </c>
       <c r="J1242" s="63" t="s">
-        <v>3603</v>
+        <v>3602</v>
       </c>
       <c r="K1242">
         <v>1243</v>
@@ -65056,7 +65097,7 @@
         <v>857</v>
       </c>
       <c r="N1242" t="s">
-        <v>3609</v>
+        <v>3608</v>
       </c>
     </row>
     <row r="1243" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65067,7 +65108,7 @@
         <v>11840108</v>
       </c>
       <c r="C1243" t="s">
-        <v>3604</v>
+        <v>3603</v>
       </c>
       <c r="D1243" t="s">
         <v>15</v>
@@ -65088,7 +65129,7 @@
         <v>809</v>
       </c>
       <c r="J1243" s="63" t="s">
-        <v>3605</v>
+        <v>3604</v>
       </c>
       <c r="K1243">
         <v>1244</v>
@@ -65097,7 +65138,7 @@
         <v>857</v>
       </c>
       <c r="N1243" t="s">
-        <v>3610</v>
+        <v>3609</v>
       </c>
     </row>
     <row r="1244" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65111,7 +65152,7 @@
         <v>25</v>
       </c>
       <c r="D1244" t="s">
-        <v>3612</v>
+        <v>3611</v>
       </c>
       <c r="E1244" t="s">
         <v>25</v>
@@ -65129,7 +65170,7 @@
         <v>809</v>
       </c>
       <c r="J1244" s="63" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
       <c r="K1244">
         <v>1245</v>
@@ -65138,7 +65179,7 @@
         <v>857</v>
       </c>
       <c r="N1244" t="s">
-        <v>3633</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="1245" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65170,7 +65211,7 @@
         <v>809</v>
       </c>
       <c r="J1245" s="63" t="s">
-        <v>3614</v>
+        <v>3613</v>
       </c>
       <c r="K1245">
         <v>1246</v>
@@ -65179,7 +65220,7 @@
         <v>857</v>
       </c>
       <c r="N1245" t="s">
-        <v>3634</v>
+        <v>3633</v>
       </c>
     </row>
     <row r="1246" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65211,7 +65252,7 @@
         <v>809</v>
       </c>
       <c r="J1246" s="63" t="s">
-        <v>3615</v>
+        <v>3614</v>
       </c>
       <c r="K1246">
         <v>1247</v>
@@ -65220,7 +65261,7 @@
         <v>857</v>
       </c>
       <c r="N1246" t="s">
-        <v>3635</v>
+        <v>3634</v>
       </c>
     </row>
     <row r="1247" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65231,7 +65272,7 @@
         <v>11950000</v>
       </c>
       <c r="C1247" t="s">
-        <v>3617</v>
+        <v>3616</v>
       </c>
       <c r="D1247" t="s">
         <v>13</v>
@@ -65252,7 +65293,7 @@
         <v>809</v>
       </c>
       <c r="J1247" s="63" t="s">
-        <v>3616</v>
+        <v>3615</v>
       </c>
       <c r="K1247">
         <v>1248</v>
@@ -65261,7 +65302,7 @@
         <v>857</v>
       </c>
       <c r="N1247" t="s">
-        <v>3636</v>
+        <v>3635</v>
       </c>
     </row>
     <row r="1248" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65293,7 +65334,7 @@
         <v>809</v>
       </c>
       <c r="J1248" s="63" t="s">
-        <v>3618</v>
+        <v>3617</v>
       </c>
       <c r="K1248">
         <v>1249</v>
@@ -65302,7 +65343,7 @@
         <v>857</v>
       </c>
       <c r="N1248" t="s">
-        <v>3637</v>
+        <v>3636</v>
       </c>
     </row>
     <row r="1249" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65313,7 +65354,7 @@
         <v>14403585</v>
       </c>
       <c r="C1249" t="s">
-        <v>3620</v>
+        <v>3619</v>
       </c>
       <c r="D1249" t="s">
         <v>426</v>
@@ -65334,7 +65375,7 @@
         <v>809</v>
       </c>
       <c r="J1249" s="63" t="s">
-        <v>3619</v>
+        <v>3618</v>
       </c>
       <c r="K1249">
         <v>1250</v>
@@ -65343,7 +65384,7 @@
         <v>857</v>
       </c>
       <c r="N1249" t="s">
-        <v>3638</v>
+        <v>3637</v>
       </c>
     </row>
     <row r="1250" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65354,7 +65395,7 @@
         <v>11846355</v>
       </c>
       <c r="C1250" t="s">
-        <v>3621</v>
+        <v>3620</v>
       </c>
       <c r="D1250" t="s">
         <v>35</v>
@@ -65369,13 +65410,13 @@
         <v>8.4108796296296293E-2</v>
       </c>
       <c r="H1250" t="s">
+        <v>3621</v>
+      </c>
+      <c r="I1250" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1250" s="63" t="s">
         <v>3622</v>
-      </c>
-      <c r="I1250" t="s">
-        <v>809</v>
-      </c>
-      <c r="J1250" s="63" t="s">
-        <v>3623</v>
       </c>
       <c r="K1250">
         <v>1251</v>
@@ -65384,7 +65425,7 @@
         <v>857</v>
       </c>
       <c r="N1250" t="s">
-        <v>3639</v>
+        <v>3638</v>
       </c>
     </row>
     <row r="1251" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65395,7 +65436,7 @@
         <v>26285296</v>
       </c>
       <c r="C1251" t="s">
-        <v>3625</v>
+        <v>3624</v>
       </c>
       <c r="D1251" t="s">
         <v>60</v>
@@ -65416,7 +65457,7 @@
         <v>809</v>
       </c>
       <c r="J1251" s="63" t="s">
-        <v>3624</v>
+        <v>3623</v>
       </c>
       <c r="K1251">
         <v>1252</v>
@@ -65425,7 +65466,7 @@
         <v>857</v>
       </c>
       <c r="N1251" t="s">
-        <v>3640</v>
+        <v>3639</v>
       </c>
     </row>
     <row r="1252" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65457,7 +65498,7 @@
         <v>809</v>
       </c>
       <c r="J1252" s="63" t="s">
-        <v>3626</v>
+        <v>3625</v>
       </c>
       <c r="K1252">
         <v>1253</v>
@@ -65466,7 +65507,7 @@
         <v>857</v>
       </c>
       <c r="N1252" t="s">
-        <v>3641</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="1253" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65492,13 +65533,13 @@
         <v>504</v>
       </c>
       <c r="H1253" t="s">
+        <v>3626</v>
+      </c>
+      <c r="I1253" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1253" s="63" t="s">
         <v>3627</v>
-      </c>
-      <c r="I1253" t="s">
-        <v>809</v>
-      </c>
-      <c r="J1253" s="63" t="s">
-        <v>3628</v>
       </c>
       <c r="K1253">
         <v>1254</v>
@@ -65507,7 +65548,7 @@
         <v>857</v>
       </c>
       <c r="N1253" t="s">
-        <v>3642</v>
+        <v>3641</v>
       </c>
     </row>
     <row r="1254" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65518,7 +65559,7 @@
         <v>10868943</v>
       </c>
       <c r="C1254" t="s">
-        <v>3630</v>
+        <v>3629</v>
       </c>
       <c r="D1254" t="s">
         <v>15</v>
@@ -65539,7 +65580,7 @@
         <v>809</v>
       </c>
       <c r="J1254" s="63" t="s">
-        <v>3629</v>
+        <v>3628</v>
       </c>
       <c r="K1254">
         <v>1255</v>
@@ -65548,7 +65589,7 @@
         <v>857</v>
       </c>
       <c r="N1254" t="s">
-        <v>3643</v>
+        <v>3642</v>
       </c>
     </row>
     <row r="1255" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65559,7 +65600,7 @@
         <v>11939361</v>
       </c>
       <c r="C1255" t="s">
-        <v>3632</v>
+        <v>3631</v>
       </c>
       <c r="D1255" t="s">
         <v>15</v>
@@ -65574,13 +65615,13 @@
         <v>0.11023148148148149</v>
       </c>
       <c r="H1255" t="s">
-        <v>3627</v>
+        <v>3626</v>
       </c>
       <c r="I1255" t="s">
         <v>809</v>
       </c>
       <c r="J1255" s="63" t="s">
-        <v>3631</v>
+        <v>3630</v>
       </c>
       <c r="K1255">
         <v>1256</v>
@@ -65589,7 +65630,7 @@
         <v>857</v>
       </c>
       <c r="N1255" t="s">
-        <v>3644</v>
+        <v>3643</v>
       </c>
     </row>
     <row r="1256" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65621,7 +65662,7 @@
         <v>809</v>
       </c>
       <c r="J1256" s="63" t="s">
-        <v>3646</v>
+        <v>3645</v>
       </c>
       <c r="K1256">
         <v>1257</v>
@@ -65630,7 +65671,7 @@
         <v>857</v>
       </c>
       <c r="N1256" t="s">
-        <v>3647</v>
+        <v>3646</v>
       </c>
     </row>
     <row r="1257" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65641,10 +65682,10 @@
         <v>3039493</v>
       </c>
       <c r="C1257" t="s">
-        <v>3600</v>
+        <v>3599</v>
       </c>
       <c r="D1257" t="s">
-        <v>3648</v>
+        <v>3647</v>
       </c>
       <c r="E1257" t="s">
         <v>435</v>
@@ -65662,7 +65703,7 @@
         <v>292</v>
       </c>
       <c r="J1257" s="63" t="s">
-        <v>3649</v>
+        <v>3648</v>
       </c>
       <c r="K1257">
         <v>1258</v>
@@ -65671,7 +65712,7 @@
         <v>857</v>
       </c>
       <c r="N1257" t="s">
-        <v>3661</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="1258" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65703,7 +65744,7 @@
         <v>292</v>
       </c>
       <c r="J1258" s="63" t="s">
-        <v>3650</v>
+        <v>3649</v>
       </c>
       <c r="K1258">
         <v>1259</v>
@@ -65712,7 +65753,7 @@
         <v>857</v>
       </c>
       <c r="N1258" t="s">
-        <v>3662</v>
+        <v>3661</v>
       </c>
     </row>
     <row r="1259" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65723,10 +65764,10 @@
         <v>2009695</v>
       </c>
       <c r="C1259" t="s">
-        <v>3600</v>
+        <v>3599</v>
       </c>
       <c r="D1259" t="s">
-        <v>3652</v>
+        <v>3651</v>
       </c>
       <c r="E1259" t="s">
         <v>435</v>
@@ -65744,7 +65785,7 @@
         <v>292</v>
       </c>
       <c r="J1259" s="63" t="s">
-        <v>3651</v>
+        <v>3650</v>
       </c>
       <c r="K1259">
         <v>1260</v>
@@ -65753,7 +65794,7 @@
         <v>857</v>
       </c>
       <c r="N1259" t="s">
-        <v>3663</v>
+        <v>3662</v>
       </c>
     </row>
     <row r="1260" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65764,7 +65805,7 @@
         <v>5275387</v>
       </c>
       <c r="C1260" t="s">
-        <v>3653</v>
+        <v>3652</v>
       </c>
       <c r="D1260" t="s">
         <v>1723</v>
@@ -65779,13 +65820,13 @@
         <v>5.4467592592592595E-2</v>
       </c>
       <c r="H1260" t="s">
-        <v>3654</v>
+        <v>3653</v>
       </c>
       <c r="I1260" t="s">
         <v>292</v>
       </c>
       <c r="J1260" s="63" t="s">
-        <v>3655</v>
+        <v>3654</v>
       </c>
       <c r="K1260">
         <v>1261</v>
@@ -65794,7 +65835,7 @@
         <v>857</v>
       </c>
       <c r="N1260" t="s">
-        <v>3664</v>
+        <v>3663</v>
       </c>
     </row>
     <row r="1261" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65805,13 +65846,13 @@
         <v>17490000</v>
       </c>
       <c r="C1261" t="s">
-        <v>3657</v>
+        <v>3656</v>
       </c>
       <c r="D1261" t="s">
         <v>54</v>
       </c>
       <c r="E1261" t="s">
-        <v>3657</v>
+        <v>3656</v>
       </c>
       <c r="F1261" s="29">
         <v>46090</v>
@@ -65826,7 +65867,7 @@
         <v>809</v>
       </c>
       <c r="J1261" s="63" t="s">
-        <v>3656</v>
+        <v>3655</v>
       </c>
       <c r="K1261">
         <v>1262</v>
@@ -65835,7 +65876,7 @@
         <v>857</v>
       </c>
       <c r="N1261" t="s">
-        <v>3665</v>
+        <v>3664</v>
       </c>
     </row>
     <row r="1262" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65867,7 +65908,7 @@
         <v>816</v>
       </c>
       <c r="J1262" s="63" t="s">
-        <v>3658</v>
+        <v>3657</v>
       </c>
       <c r="K1262">
         <v>1263</v>
@@ -65876,7 +65917,7 @@
         <v>857</v>
       </c>
       <c r="N1262" t="s">
-        <v>3666</v>
+        <v>3665</v>
       </c>
     </row>
     <row r="1263" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65908,7 +65949,7 @@
         <v>816</v>
       </c>
       <c r="J1263" s="63" t="s">
-        <v>3659</v>
+        <v>3658</v>
       </c>
       <c r="K1263">
         <v>1264</v>
@@ -65917,7 +65958,7 @@
         <v>857</v>
       </c>
       <c r="N1263" t="s">
-        <v>3667</v>
+        <v>3666</v>
       </c>
     </row>
     <row r="1264" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65949,7 +65990,7 @@
         <v>292</v>
       </c>
       <c r="J1264" s="63" t="s">
-        <v>3660</v>
+        <v>3659</v>
       </c>
       <c r="K1264">
         <v>1265</v>
@@ -65958,7 +65999,7 @@
         <v>857</v>
       </c>
       <c r="N1264" t="s">
-        <v>3668</v>
+        <v>3667</v>
       </c>
     </row>
     <row r="1265" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65984,13 +66025,13 @@
         <v>0.11001157407407407</v>
       </c>
       <c r="H1265" t="s">
-        <v>3673</v>
+        <v>3672</v>
       </c>
       <c r="I1265" t="s">
         <v>292</v>
       </c>
       <c r="J1265" s="63" t="s">
-        <v>3669</v>
+        <v>3668</v>
       </c>
       <c r="K1265">
         <v>1266</v>
@@ -65999,7 +66040,7 @@
         <v>857</v>
       </c>
       <c r="N1265" t="s">
-        <v>3675</v>
+        <v>3674</v>
       </c>
     </row>
     <row r="1266" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66031,7 +66072,7 @@
         <v>292</v>
       </c>
       <c r="J1266" s="63" t="s">
-        <v>3670</v>
+        <v>3669</v>
       </c>
       <c r="K1266">
         <v>1267</v>
@@ -66040,7 +66081,7 @@
         <v>857</v>
       </c>
       <c r="N1266" t="s">
-        <v>3676</v>
+        <v>3675</v>
       </c>
     </row>
     <row r="1267" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66072,7 +66113,7 @@
         <v>292</v>
       </c>
       <c r="J1267" s="63" t="s">
-        <v>3671</v>
+        <v>3670</v>
       </c>
       <c r="K1267">
         <v>1268</v>
@@ -66081,7 +66122,7 @@
         <v>857</v>
       </c>
       <c r="N1267" t="s">
-        <v>3677</v>
+        <v>3676</v>
       </c>
     </row>
     <row r="1268" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66095,7 +66136,7 @@
         <v>25</v>
       </c>
       <c r="D1268" t="s">
-        <v>3674</v>
+        <v>3673</v>
       </c>
       <c r="E1268" t="s">
         <v>3433</v>
@@ -66113,7 +66154,7 @@
         <v>292</v>
       </c>
       <c r="J1268" s="63" t="s">
-        <v>3672</v>
+        <v>3671</v>
       </c>
       <c r="K1268">
         <v>1269</v>
@@ -66122,7 +66163,7 @@
         <v>857</v>
       </c>
       <c r="N1268" t="s">
-        <v>3678</v>
+        <v>3677</v>
       </c>
     </row>
     <row r="1269" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66154,7 +66195,7 @@
         <v>292</v>
       </c>
       <c r="J1269" s="63" t="s">
-        <v>3679</v>
+        <v>3678</v>
       </c>
       <c r="K1269">
         <v>1270</v>
@@ -66163,7 +66204,7 @@
         <v>857</v>
       </c>
       <c r="N1269" t="s">
-        <v>3685</v>
+        <v>3684</v>
       </c>
     </row>
     <row r="1270" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66174,13 +66215,13 @@
         <v>12357428</v>
       </c>
       <c r="C1270" t="s">
-        <v>3680</v>
+        <v>3679</v>
       </c>
       <c r="D1270" t="s">
         <v>285</v>
       </c>
       <c r="E1270" t="s">
-        <v>3680</v>
+        <v>3679</v>
       </c>
       <c r="F1270" s="29">
         <v>46098</v>
@@ -66195,7 +66236,7 @@
         <v>292</v>
       </c>
       <c r="J1270" s="63" t="s">
-        <v>3681</v>
+        <v>3680</v>
       </c>
       <c r="K1270">
         <v>1271</v>
@@ -66204,7 +66245,7 @@
         <v>857</v>
       </c>
       <c r="N1270" t="s">
-        <v>3686</v>
+        <v>3685</v>
       </c>
     </row>
     <row r="1271" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66236,7 +66277,7 @@
         <v>292</v>
       </c>
       <c r="J1271" s="63" t="s">
-        <v>3682</v>
+        <v>3681</v>
       </c>
       <c r="K1271">
         <v>1272</v>
@@ -66245,7 +66286,7 @@
         <v>857</v>
       </c>
       <c r="N1271" t="s">
-        <v>3687</v>
+        <v>3686</v>
       </c>
     </row>
     <row r="1272" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66271,13 +66312,13 @@
         <v>0.11376157407407407</v>
       </c>
       <c r="H1272" t="s">
-        <v>3684</v>
+        <v>3683</v>
       </c>
       <c r="I1272" t="s">
         <v>809</v>
       </c>
       <c r="J1272" s="63" t="s">
-        <v>3683</v>
+        <v>3682</v>
       </c>
       <c r="K1272">
         <v>1273</v>
@@ -66286,7 +66327,7 @@
         <v>857</v>
       </c>
       <c r="N1272" t="s">
-        <v>3688</v>
+        <v>3687</v>
       </c>
     </row>
     <row r="1273" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66297,7 +66338,7 @@
         <v>15637601</v>
       </c>
       <c r="C1273" t="s">
-        <v>3689</v>
+        <v>3688</v>
       </c>
       <c r="D1273" t="s">
         <v>366</v>
@@ -66318,7 +66359,7 @@
         <v>809</v>
       </c>
       <c r="J1273" s="63" t="s">
-        <v>3690</v>
+        <v>3689</v>
       </c>
       <c r="K1273">
         <v>1274</v>
@@ -66327,7 +66368,7 @@
         <v>857</v>
       </c>
       <c r="N1273" t="s">
-        <v>3698</v>
+        <v>3697</v>
       </c>
     </row>
     <row r="1274" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66359,7 +66400,7 @@
         <v>816</v>
       </c>
       <c r="J1274" s="63" t="s">
-        <v>3691</v>
+        <v>3690</v>
       </c>
       <c r="K1274">
         <v>1275</v>
@@ -66368,7 +66409,7 @@
         <v>857</v>
       </c>
       <c r="N1274" t="s">
-        <v>3699</v>
+        <v>3698</v>
       </c>
     </row>
     <row r="1275" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66400,7 +66441,7 @@
         <v>809</v>
       </c>
       <c r="J1275" s="63" t="s">
-        <v>3692</v>
+        <v>3691</v>
       </c>
       <c r="K1275">
         <v>1276</v>
@@ -66409,7 +66450,7 @@
         <v>857</v>
       </c>
       <c r="N1275" t="s">
-        <v>3700</v>
+        <v>3699</v>
       </c>
     </row>
     <row r="1276" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66441,7 +66482,7 @@
         <v>809</v>
       </c>
       <c r="J1276" s="63" t="s">
-        <v>3693</v>
+        <v>3692</v>
       </c>
       <c r="K1276">
         <v>1277</v>
@@ -66450,7 +66491,7 @@
         <v>857</v>
       </c>
       <c r="N1276" t="s">
-        <v>3701</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="1277" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66482,7 +66523,7 @@
         <v>809</v>
       </c>
       <c r="J1277" s="63" t="s">
-        <v>3694</v>
+        <v>3693</v>
       </c>
       <c r="K1277">
         <v>1278</v>
@@ -66491,7 +66532,7 @@
         <v>857</v>
       </c>
       <c r="N1277" t="s">
-        <v>3702</v>
+        <v>3701</v>
       </c>
     </row>
     <row r="1278" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66523,7 +66564,7 @@
         <v>809</v>
       </c>
       <c r="J1278" s="63" t="s">
-        <v>3695</v>
+        <v>3694</v>
       </c>
       <c r="K1278">
         <v>1279</v>
@@ -66532,7 +66573,7 @@
         <v>857</v>
       </c>
       <c r="N1278" t="s">
-        <v>3703</v>
+        <v>3702</v>
       </c>
     </row>
     <row r="1279" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66558,13 +66599,13 @@
         <v>8.5636574074074087E-2</v>
       </c>
       <c r="H1279" t="s">
-        <v>3697</v>
+        <v>3696</v>
       </c>
       <c r="I1279" t="s">
         <v>809</v>
       </c>
       <c r="J1279" s="63" t="s">
-        <v>3696</v>
+        <v>3695</v>
       </c>
       <c r="K1279">
         <v>1280</v>
@@ -66573,7 +66614,7 @@
         <v>857</v>
       </c>
       <c r="N1279" t="s">
-        <v>3704</v>
+        <v>3703</v>
       </c>
     </row>
     <row r="1280" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66584,13 +66625,13 @@
         <v>2459104</v>
       </c>
       <c r="C1280" t="s">
-        <v>3711</v>
+        <v>3710</v>
       </c>
       <c r="D1280" t="s">
-        <v>3710</v>
+        <v>3709</v>
       </c>
       <c r="E1280" t="s">
-        <v>3746</v>
+        <v>3745</v>
       </c>
       <c r="F1280" s="29">
         <v>46102</v>
@@ -66605,7 +66646,7 @@
         <v>809</v>
       </c>
       <c r="J1280" s="63" t="s">
-        <v>3705</v>
+        <v>3704</v>
       </c>
       <c r="K1280">
         <v>1281</v>
@@ -66614,7 +66655,7 @@
         <v>857</v>
       </c>
       <c r="N1280" t="s">
-        <v>3732</v>
+        <v>3731</v>
       </c>
     </row>
     <row r="1281" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66628,7 +66669,7 @@
         <v>17</v>
       </c>
       <c r="D1281" t="s">
-        <v>3710</v>
+        <v>3709</v>
       </c>
       <c r="E1281" t="s">
         <v>18</v>
@@ -66640,13 +66681,13 @@
         <v>4.6192129629629632E-2</v>
       </c>
       <c r="H1281" t="s">
-        <v>3684</v>
+        <v>3683</v>
       </c>
       <c r="I1281" t="s">
         <v>809</v>
       </c>
       <c r="J1281" s="63" t="s">
-        <v>3706</v>
+        <v>3705</v>
       </c>
       <c r="K1281">
         <v>1282</v>
@@ -66655,7 +66696,7 @@
         <v>857</v>
       </c>
       <c r="N1281" t="s">
-        <v>3733</v>
+        <v>3732</v>
       </c>
     </row>
     <row r="1282" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66666,7 +66707,7 @@
         <v>38584884</v>
       </c>
       <c r="C1282" t="s">
-        <v>3712</v>
+        <v>3711</v>
       </c>
       <c r="D1282" t="s">
         <v>9</v>
@@ -66687,7 +66728,7 @@
         <v>809</v>
       </c>
       <c r="J1282" s="63" t="s">
-        <v>3707</v>
+        <v>3706</v>
       </c>
       <c r="K1282">
         <v>1283</v>
@@ -66696,7 +66737,7 @@
         <v>857</v>
       </c>
       <c r="N1282" t="s">
-        <v>3734</v>
+        <v>3733</v>
       </c>
     </row>
     <row r="1283" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66707,7 +66748,7 @@
         <v>20008060</v>
       </c>
       <c r="C1283" t="s">
-        <v>3713</v>
+        <v>3712</v>
       </c>
       <c r="D1283" t="s">
         <v>15</v>
@@ -66728,7 +66769,7 @@
         <v>809</v>
       </c>
       <c r="J1283" s="63" t="s">
-        <v>3708</v>
+        <v>3707</v>
       </c>
       <c r="K1283">
         <v>1284</v>
@@ -66737,7 +66778,7 @@
         <v>857</v>
       </c>
       <c r="N1283" t="s">
-        <v>3735</v>
+        <v>3734</v>
       </c>
     </row>
     <row r="1284" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66748,7 +66789,7 @@
         <v>6665326</v>
       </c>
       <c r="C1284" t="s">
-        <v>3714</v>
+        <v>3713</v>
       </c>
       <c r="D1284" t="s">
         <v>340</v>
@@ -66769,7 +66810,7 @@
         <v>809</v>
       </c>
       <c r="J1284" s="63" t="s">
-        <v>3709</v>
+        <v>3708</v>
       </c>
       <c r="K1284">
         <v>1285</v>
@@ -66778,7 +66819,7 @@
         <v>857</v>
       </c>
       <c r="N1284" t="s">
-        <v>3736</v>
+        <v>3735</v>
       </c>
     </row>
     <row r="1285" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66789,7 +66830,7 @@
         <v>14678575</v>
       </c>
       <c r="C1285" t="s">
-        <v>3715</v>
+        <v>3714</v>
       </c>
       <c r="D1285" t="s">
         <v>15</v>
@@ -66810,7 +66851,7 @@
         <v>809</v>
       </c>
       <c r="J1285" s="63" t="s">
-        <v>3716</v>
+        <v>3715</v>
       </c>
       <c r="K1285">
         <v>1286</v>
@@ -66819,7 +66860,7 @@
         <v>857</v>
       </c>
       <c r="N1285" t="s">
-        <v>3737</v>
+        <v>3736</v>
       </c>
     </row>
     <row r="1286" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66851,7 +66892,7 @@
         <v>809</v>
       </c>
       <c r="J1286" s="63" t="s">
-        <v>3717</v>
+        <v>3716</v>
       </c>
       <c r="K1286">
         <v>1287</v>
@@ -66860,7 +66901,7 @@
         <v>857</v>
       </c>
       <c r="N1286" t="s">
-        <v>3738</v>
+        <v>3737</v>
       </c>
     </row>
     <row r="1287" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66871,7 +66912,7 @@
         <v>15035249</v>
       </c>
       <c r="C1287" t="s">
-        <v>3719</v>
+        <v>3718</v>
       </c>
       <c r="D1287" t="s">
         <v>447</v>
@@ -66892,7 +66933,7 @@
         <v>809</v>
       </c>
       <c r="J1287" s="63" t="s">
-        <v>3718</v>
+        <v>3717</v>
       </c>
       <c r="K1287">
         <v>1288</v>
@@ -66901,7 +66942,7 @@
         <v>857</v>
       </c>
       <c r="N1287" t="s">
-        <v>3739</v>
+        <v>3738</v>
       </c>
     </row>
     <row r="1288" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66927,13 +66968,13 @@
         <v>0.1292939814814815</v>
       </c>
       <c r="H1288" t="s">
+        <v>3719</v>
+      </c>
+      <c r="I1288" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1288" s="63" t="s">
         <v>3720</v>
-      </c>
-      <c r="I1288" t="s">
-        <v>809</v>
-      </c>
-      <c r="J1288" s="63" t="s">
-        <v>3721</v>
       </c>
       <c r="K1288">
         <v>1289</v>
@@ -66942,7 +66983,7 @@
         <v>857</v>
       </c>
       <c r="N1288" t="s">
-        <v>3740</v>
+        <v>3739</v>
       </c>
     </row>
     <row r="1289" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66956,7 +66997,7 @@
         <v>214</v>
       </c>
       <c r="D1289" t="s">
-        <v>3723</v>
+        <v>3722</v>
       </c>
       <c r="E1289" t="s">
         <v>51</v>
@@ -66974,7 +67015,7 @@
         <v>809</v>
       </c>
       <c r="J1289" s="63" t="s">
-        <v>3722</v>
+        <v>3721</v>
       </c>
       <c r="K1289">
         <v>1290</v>
@@ -66983,7 +67024,7 @@
         <v>857</v>
       </c>
       <c r="N1289" t="s">
-        <v>3741</v>
+        <v>3740</v>
       </c>
     </row>
     <row r="1290" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66997,7 +67038,7 @@
         <v>17</v>
       </c>
       <c r="D1290" t="s">
-        <v>3727</v>
+        <v>3726</v>
       </c>
       <c r="E1290" t="s">
         <v>18</v>
@@ -67015,7 +67056,7 @@
         <v>809</v>
       </c>
       <c r="J1290" s="63" t="s">
-        <v>3724</v>
+        <v>3723</v>
       </c>
       <c r="K1290">
         <v>1291</v>
@@ -67024,7 +67065,7 @@
         <v>857</v>
       </c>
       <c r="N1290" t="s">
-        <v>3742</v>
+        <v>3741</v>
       </c>
     </row>
     <row r="1291" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67056,7 +67097,7 @@
         <v>809</v>
       </c>
       <c r="J1291" s="63" t="s">
-        <v>3725</v>
+        <v>3724</v>
       </c>
       <c r="K1291">
         <v>1292</v>
@@ -67065,7 +67106,7 @@
         <v>857</v>
       </c>
       <c r="N1291" t="s">
-        <v>3743</v>
+        <v>3742</v>
       </c>
     </row>
     <row r="1292" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67091,13 +67132,13 @@
         <v>504</v>
       </c>
       <c r="H1292" t="s">
-        <v>3728</v>
+        <v>3727</v>
       </c>
       <c r="I1292" t="s">
         <v>809</v>
       </c>
       <c r="J1292" s="63" t="s">
-        <v>3726</v>
+        <v>3725</v>
       </c>
       <c r="K1292">
         <v>1293</v>
@@ -67106,7 +67147,7 @@
         <v>857</v>
       </c>
       <c r="N1292" t="s">
-        <v>3744</v>
+        <v>3743</v>
       </c>
     </row>
     <row r="1293" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67117,10 +67158,10 @@
         <v>6886047</v>
       </c>
       <c r="C1293" t="s">
-        <v>3729</v>
+        <v>3728</v>
       </c>
       <c r="D1293" t="s">
-        <v>3723</v>
+        <v>3722</v>
       </c>
       <c r="E1293" t="s">
         <v>51</v>
@@ -67132,13 +67173,13 @@
         <v>4.3784722222222218E-2</v>
       </c>
       <c r="H1293" t="s">
+        <v>3729</v>
+      </c>
+      <c r="I1293" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1293" s="63" t="s">
         <v>3730</v>
-      </c>
-      <c r="I1293" t="s">
-        <v>809</v>
-      </c>
-      <c r="J1293" s="63" t="s">
-        <v>3731</v>
       </c>
       <c r="K1293">
         <v>1294</v>
@@ -67147,7 +67188,7 @@
         <v>857</v>
       </c>
       <c r="N1293" t="s">
-        <v>3745</v>
+        <v>3744</v>
       </c>
     </row>
     <row r="1294" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67158,10 +67199,10 @@
         <v>1778128</v>
       </c>
       <c r="C1294" t="s">
+        <v>3747</v>
+      </c>
+      <c r="D1294" t="s">
         <v>3748</v>
-      </c>
-      <c r="D1294" t="s">
-        <v>3749</v>
       </c>
       <c r="E1294" t="s">
         <v>218</v>
@@ -67173,13 +67214,13 @@
         <v>6.6203703703703709E-2</v>
       </c>
       <c r="H1294" t="s">
-        <v>3750</v>
+        <v>3749</v>
       </c>
       <c r="I1294" t="s">
         <v>809</v>
       </c>
       <c r="J1294" s="63" t="s">
-        <v>3747</v>
+        <v>3746</v>
       </c>
       <c r="K1294">
         <v>1295</v>
@@ -67188,7 +67229,7 @@
         <v>857</v>
       </c>
       <c r="N1294" t="s">
-        <v>3751</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="1295" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67202,7 +67243,7 @@
         <v>32</v>
       </c>
       <c r="D1295" t="s">
-        <v>3753</v>
+        <v>3752</v>
       </c>
       <c r="E1295" t="s">
         <v>29</v>
@@ -67220,7 +67261,7 @@
         <v>809</v>
       </c>
       <c r="J1295" s="63" t="s">
-        <v>3752</v>
+        <v>3751</v>
       </c>
       <c r="K1295">
         <v>1296</v>
@@ -67229,7 +67270,7 @@
         <v>857</v>
       </c>
       <c r="N1295" t="s">
-        <v>3754</v>
+        <v>3753</v>
       </c>
     </row>
     <row r="1296" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67243,7 +67284,7 @@
         <v>32</v>
       </c>
       <c r="D1296" t="s">
-        <v>3755</v>
+        <v>3754</v>
       </c>
       <c r="E1296" t="s">
         <v>29</v>
@@ -67261,7 +67302,7 @@
         <v>809</v>
       </c>
       <c r="J1296" s="63" t="s">
-        <v>3756</v>
+        <v>3755</v>
       </c>
       <c r="K1296">
         <v>1297</v>
@@ -67270,7 +67311,7 @@
         <v>857</v>
       </c>
       <c r="N1296" t="s">
-        <v>3762</v>
+        <v>3761</v>
       </c>
     </row>
     <row r="1297" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67296,13 +67337,13 @@
         <v>3.6064814814814813E-2</v>
       </c>
       <c r="H1297" t="s">
-        <v>3758</v>
+        <v>3757</v>
       </c>
       <c r="I1297" t="s">
         <v>809</v>
       </c>
       <c r="J1297" s="63" t="s">
-        <v>3757</v>
+        <v>3756</v>
       </c>
       <c r="K1297">
         <v>1298</v>
@@ -67311,7 +67352,7 @@
         <v>857</v>
       </c>
       <c r="N1297" t="s">
-        <v>3763</v>
+        <v>3762</v>
       </c>
     </row>
     <row r="1298" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67337,13 +67378,13 @@
         <v>9.1122685185185182E-2</v>
       </c>
       <c r="H1298" t="s">
+        <v>3758</v>
+      </c>
+      <c r="I1298" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1298" s="63" t="s">
         <v>3759</v>
-      </c>
-      <c r="I1298" t="s">
-        <v>809</v>
-      </c>
-      <c r="J1298" s="63" t="s">
-        <v>3760</v>
       </c>
       <c r="K1298">
         <v>1299</v>
@@ -67352,7 +67393,7 @@
         <v>857</v>
       </c>
       <c r="N1298" t="s">
-        <v>3764</v>
+        <v>3763</v>
       </c>
     </row>
     <row r="1299" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67384,7 +67425,7 @@
         <v>809</v>
       </c>
       <c r="J1299" s="63" t="s">
-        <v>3761</v>
+        <v>3760</v>
       </c>
       <c r="K1299">
         <v>1300</v>
@@ -67393,7 +67434,7 @@
         <v>857</v>
       </c>
       <c r="N1299" t="s">
-        <v>3765</v>
+        <v>3764</v>
       </c>
     </row>
     <row r="1300" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67407,7 +67448,7 @@
         <v>442</v>
       </c>
       <c r="D1300" t="s">
-        <v>3770</v>
+        <v>3769</v>
       </c>
       <c r="E1300" t="s">
         <v>435</v>
@@ -67419,13 +67460,13 @@
         <v>6.4432870370370363E-2</v>
       </c>
       <c r="H1300" t="s">
-        <v>3766</v>
+        <v>3765</v>
       </c>
       <c r="I1300" t="s">
         <v>292</v>
       </c>
       <c r="J1300" s="63" t="s">
-        <v>3767</v>
+        <v>3766</v>
       </c>
       <c r="K1300">
         <v>1301</v>
@@ -67434,7 +67475,7 @@
         <v>857</v>
       </c>
       <c r="N1300" t="s">
-        <v>3774</v>
+        <v>3773</v>
       </c>
     </row>
     <row r="1301" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67448,7 +67489,7 @@
         <v>442</v>
       </c>
       <c r="D1301" t="s">
-        <v>3771</v>
+        <v>3770</v>
       </c>
       <c r="E1301" t="s">
         <v>435</v>
@@ -67466,7 +67507,7 @@
         <v>292</v>
       </c>
       <c r="J1301" s="63" t="s">
-        <v>3768</v>
+        <v>3767</v>
       </c>
       <c r="K1301">
         <v>1302</v>
@@ -67475,7 +67516,7 @@
         <v>857</v>
       </c>
       <c r="N1301" t="s">
-        <v>3775</v>
+        <v>3774</v>
       </c>
     </row>
     <row r="1302" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67489,7 +67530,7 @@
         <v>442</v>
       </c>
       <c r="D1302" t="s">
-        <v>3772</v>
+        <v>3771</v>
       </c>
       <c r="E1302" t="s">
         <v>435</v>
@@ -67501,13 +67542,13 @@
         <v>5.5960648148148141E-2</v>
       </c>
       <c r="H1302" t="s">
-        <v>3773</v>
+        <v>3772</v>
       </c>
       <c r="I1302" t="s">
         <v>292</v>
       </c>
       <c r="J1302" s="63" t="s">
-        <v>3769</v>
+        <v>3768</v>
       </c>
       <c r="K1302">
         <v>1303</v>
@@ -67516,7 +67557,7 @@
         <v>857</v>
       </c>
       <c r="N1302" t="s">
-        <v>3776</v>
+        <v>3775</v>
       </c>
     </row>
     <row r="1303" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67530,7 +67571,7 @@
         <v>25</v>
       </c>
       <c r="D1303" t="s">
-        <v>3782</v>
+        <v>3781</v>
       </c>
       <c r="E1303">
         <v>44100</v>
@@ -67548,7 +67589,7 @@
         <v>292</v>
       </c>
       <c r="J1303" s="63" t="s">
-        <v>3777</v>
+        <v>3776</v>
       </c>
       <c r="K1303">
         <v>1304</v>
@@ -67557,7 +67598,7 @@
         <v>857</v>
       </c>
       <c r="N1303" t="s">
-        <v>3791</v>
+        <v>3790</v>
       </c>
     </row>
     <row r="1304" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67571,7 +67612,7 @@
         <v>442</v>
       </c>
       <c r="D1304" t="s">
-        <v>3783</v>
+        <v>3782</v>
       </c>
       <c r="E1304" t="s">
         <v>435</v>
@@ -67589,7 +67630,7 @@
         <v>292</v>
       </c>
       <c r="J1304" s="63" t="s">
-        <v>3778</v>
+        <v>3777</v>
       </c>
       <c r="K1304">
         <v>1305</v>
@@ -67598,7 +67639,7 @@
         <v>857</v>
       </c>
       <c r="N1304" t="s">
-        <v>3792</v>
+        <v>3791</v>
       </c>
     </row>
     <row r="1305" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67612,7 +67653,7 @@
         <v>442</v>
       </c>
       <c r="D1305" t="s">
-        <v>3784</v>
+        <v>3783</v>
       </c>
       <c r="E1305" t="s">
         <v>435</v>
@@ -67630,7 +67671,7 @@
         <v>292</v>
       </c>
       <c r="J1305" s="63" t="s">
-        <v>3779</v>
+        <v>3778</v>
       </c>
       <c r="K1305">
         <v>1306</v>
@@ -67639,7 +67680,7 @@
         <v>857</v>
       </c>
       <c r="N1305" t="s">
-        <v>3793</v>
+        <v>3792</v>
       </c>
     </row>
     <row r="1306" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67650,7 +67691,7 @@
         <v>9033862</v>
       </c>
       <c r="C1306" t="s">
-        <v>3785</v>
+        <v>3784</v>
       </c>
       <c r="D1306" t="s">
         <v>408</v>
@@ -67671,7 +67712,7 @@
         <v>292</v>
       </c>
       <c r="J1306" s="63" t="s">
-        <v>3780</v>
+        <v>3779</v>
       </c>
       <c r="K1306">
         <v>1307</v>
@@ -67680,7 +67721,7 @@
         <v>857</v>
       </c>
       <c r="N1306" t="s">
-        <v>3794</v>
+        <v>3793</v>
       </c>
     </row>
     <row r="1307" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67712,7 +67753,7 @@
         <v>292</v>
       </c>
       <c r="J1307" s="63" t="s">
-        <v>3781</v>
+        <v>3780</v>
       </c>
       <c r="K1307">
         <v>1308</v>
@@ -67721,7 +67762,7 @@
         <v>857</v>
       </c>
       <c r="N1307" t="s">
-        <v>3795</v>
+        <v>3794</v>
       </c>
     </row>
     <row r="1308" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67735,7 +67776,7 @@
         <v>442</v>
       </c>
       <c r="D1308" t="s">
-        <v>3921</v>
+        <v>3920</v>
       </c>
       <c r="E1308" t="s">
         <v>435</v>
@@ -67753,7 +67794,7 @@
         <v>292</v>
       </c>
       <c r="J1308" s="63" t="s">
-        <v>3786</v>
+        <v>3785</v>
       </c>
       <c r="K1308">
         <v>1309</v>
@@ -67762,7 +67803,7 @@
         <v>857</v>
       </c>
       <c r="N1308" t="s">
-        <v>3796</v>
+        <v>3795</v>
       </c>
     </row>
     <row r="1309" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67776,7 +67817,7 @@
         <v>442</v>
       </c>
       <c r="D1309" t="s">
-        <v>3788</v>
+        <v>3787</v>
       </c>
       <c r="E1309" t="s">
         <v>435</v>
@@ -67788,13 +67829,13 @@
         <v>4.2546296296296297E-2</v>
       </c>
       <c r="H1309" t="s">
-        <v>3789</v>
+        <v>3788</v>
       </c>
       <c r="I1309" t="s">
         <v>292</v>
       </c>
       <c r="J1309" s="63" t="s">
-        <v>3787</v>
+        <v>3786</v>
       </c>
       <c r="K1309">
         <v>1310</v>
@@ -67803,7 +67844,7 @@
         <v>857</v>
       </c>
       <c r="N1309" t="s">
-        <v>3797</v>
+        <v>3796</v>
       </c>
     </row>
     <row r="1310" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67835,7 +67876,7 @@
         <v>809</v>
       </c>
       <c r="J1310" s="63" t="s">
-        <v>3790</v>
+        <v>3789</v>
       </c>
       <c r="K1310">
         <v>1311</v>
@@ -67844,7 +67885,7 @@
         <v>857</v>
       </c>
       <c r="N1310" t="s">
-        <v>3798</v>
+        <v>3797</v>
       </c>
     </row>
     <row r="1311" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67876,7 +67917,7 @@
         <v>809</v>
       </c>
       <c r="J1311" s="63" t="s">
-        <v>3799</v>
+        <v>3798</v>
       </c>
       <c r="K1311">
         <v>1312</v>
@@ -67885,7 +67926,7 @@
         <v>857</v>
       </c>
       <c r="N1311" t="s">
-        <v>3804</v>
+        <v>3803</v>
       </c>
     </row>
     <row r="1312" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67917,7 +67958,7 @@
         <v>809</v>
       </c>
       <c r="J1312" s="63" t="s">
-        <v>3800</v>
+        <v>3799</v>
       </c>
       <c r="K1312">
         <v>1313</v>
@@ -67926,7 +67967,7 @@
         <v>857</v>
       </c>
       <c r="N1312" t="s">
-        <v>3805</v>
+        <v>3804</v>
       </c>
     </row>
     <row r="1313" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67937,7 +67978,7 @@
         <v>15142034</v>
       </c>
       <c r="C1313" t="s">
-        <v>3802</v>
+        <v>3801</v>
       </c>
       <c r="D1313" t="s">
         <v>60</v>
@@ -67958,7 +67999,7 @@
         <v>809</v>
       </c>
       <c r="J1313" s="63" t="s">
-        <v>3801</v>
+        <v>3800</v>
       </c>
       <c r="K1313">
         <v>1314</v>
@@ -67967,7 +68008,7 @@
         <v>857</v>
       </c>
       <c r="N1313" t="s">
-        <v>3806</v>
+        <v>3805</v>
       </c>
     </row>
     <row r="1314" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67999,7 +68040,7 @@
         <v>809</v>
       </c>
       <c r="J1314" s="63" t="s">
-        <v>3803</v>
+        <v>3802</v>
       </c>
       <c r="K1314">
         <v>1315</v>
@@ -68008,7 +68049,7 @@
         <v>857</v>
       </c>
       <c r="N1314" t="s">
-        <v>3807</v>
+        <v>3806</v>
       </c>
     </row>
     <row r="1315" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68040,7 +68081,7 @@
         <v>809</v>
       </c>
       <c r="J1315" s="63" t="s">
-        <v>3808</v>
+        <v>3807</v>
       </c>
       <c r="K1315">
         <v>1316</v>
@@ -68049,7 +68090,7 @@
         <v>857</v>
       </c>
       <c r="N1315" t="s">
-        <v>3834</v>
+        <v>3833</v>
       </c>
     </row>
     <row r="1316" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68081,7 +68122,7 @@
         <v>809</v>
       </c>
       <c r="J1316" s="63" t="s">
-        <v>3809</v>
+        <v>3808</v>
       </c>
       <c r="K1316">
         <v>1317</v>
@@ -68090,7 +68131,7 @@
         <v>857</v>
       </c>
       <c r="N1316" t="s">
-        <v>3835</v>
+        <v>3834</v>
       </c>
     </row>
     <row r="1317" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68101,7 +68142,7 @@
         <v>61493897</v>
       </c>
       <c r="C1317" t="s">
-        <v>3810</v>
+        <v>3809</v>
       </c>
       <c r="D1317" t="s">
         <v>15</v>
@@ -68122,7 +68163,7 @@
         <v>809</v>
       </c>
       <c r="J1317" s="63" t="s">
-        <v>3811</v>
+        <v>3810</v>
       </c>
       <c r="K1317">
         <v>1318</v>
@@ -68131,7 +68172,7 @@
         <v>857</v>
       </c>
       <c r="N1317" t="s">
-        <v>3836</v>
+        <v>3835</v>
       </c>
     </row>
     <row r="1318" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68145,7 +68186,7 @@
         <v>25</v>
       </c>
       <c r="D1318" t="s">
-        <v>3813</v>
+        <v>3812</v>
       </c>
       <c r="E1318" t="s">
         <v>3433</v>
@@ -68163,7 +68204,7 @@
         <v>809</v>
       </c>
       <c r="J1318" s="63" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="K1318">
         <v>1319</v>
@@ -68172,7 +68213,7 @@
         <v>857</v>
       </c>
       <c r="N1318" t="s">
-        <v>3837</v>
+        <v>3836</v>
       </c>
     </row>
     <row r="1319" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68204,7 +68245,7 @@
         <v>809</v>
       </c>
       <c r="J1319" s="63" t="s">
-        <v>3814</v>
+        <v>3813</v>
       </c>
       <c r="K1319">
         <v>1320</v>
@@ -68213,7 +68254,7 @@
         <v>857</v>
       </c>
       <c r="N1319" t="s">
-        <v>3838</v>
+        <v>3837</v>
       </c>
     </row>
     <row r="1320" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68245,7 +68286,7 @@
         <v>809</v>
       </c>
       <c r="J1320" s="63" t="s">
-        <v>3815</v>
+        <v>3814</v>
       </c>
       <c r="K1320">
         <v>1321</v>
@@ -68254,7 +68295,7 @@
         <v>857</v>
       </c>
       <c r="N1320" t="s">
-        <v>3839</v>
+        <v>3838</v>
       </c>
     </row>
     <row r="1321" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68286,7 +68327,7 @@
         <v>809</v>
       </c>
       <c r="J1321" s="63" t="s">
-        <v>3816</v>
+        <v>3815</v>
       </c>
       <c r="K1321">
         <v>1322</v>
@@ -68295,7 +68336,7 @@
         <v>857</v>
       </c>
       <c r="N1321" t="s">
-        <v>3840</v>
+        <v>3839</v>
       </c>
     </row>
     <row r="1322" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68327,7 +68368,7 @@
         <v>809</v>
       </c>
       <c r="J1322" s="63" t="s">
-        <v>3817</v>
+        <v>3816</v>
       </c>
       <c r="K1322">
         <v>1323</v>
@@ -68336,7 +68377,7 @@
         <v>857</v>
       </c>
       <c r="N1322" t="s">
-        <v>3841</v>
+        <v>3840</v>
       </c>
     </row>
     <row r="1323" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68368,7 +68409,7 @@
         <v>809</v>
       </c>
       <c r="J1323" s="63" t="s">
-        <v>3818</v>
+        <v>3817</v>
       </c>
       <c r="K1323">
         <v>1324</v>
@@ -68377,7 +68418,7 @@
         <v>857</v>
       </c>
       <c r="N1323" t="s">
-        <v>3842</v>
+        <v>3841</v>
       </c>
     </row>
     <row r="1324" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68391,7 +68432,7 @@
         <v>4</v>
       </c>
       <c r="D1324" t="s">
-        <v>3821</v>
+        <v>3820</v>
       </c>
       <c r="E1324" t="s">
         <v>697</v>
@@ -68409,7 +68450,7 @@
         <v>809</v>
       </c>
       <c r="J1324" s="63" t="s">
-        <v>3819</v>
+        <v>3818</v>
       </c>
       <c r="K1324">
         <v>1325</v>
@@ -68418,7 +68459,7 @@
         <v>857</v>
       </c>
       <c r="N1324" t="s">
-        <v>3843</v>
+        <v>3842</v>
       </c>
     </row>
     <row r="1325" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68429,7 +68470,7 @@
         <v>8540141</v>
       </c>
       <c r="C1325" t="s">
-        <v>3785</v>
+        <v>3784</v>
       </c>
       <c r="D1325" t="s">
         <v>40</v>
@@ -68450,7 +68491,7 @@
         <v>809</v>
       </c>
       <c r="J1325" s="63" t="s">
-        <v>3820</v>
+        <v>3819</v>
       </c>
       <c r="K1325">
         <v>1326</v>
@@ -68459,7 +68500,7 @@
         <v>857</v>
       </c>
       <c r="N1325" t="s">
-        <v>3844</v>
+        <v>3843</v>
       </c>
     </row>
     <row r="1326" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68491,7 +68532,7 @@
         <v>809</v>
       </c>
       <c r="J1326" s="63" t="s">
-        <v>3822</v>
+        <v>3821</v>
       </c>
       <c r="K1326">
         <v>1327</v>
@@ -68500,7 +68541,7 @@
         <v>857</v>
       </c>
       <c r="N1326" t="s">
-        <v>3845</v>
+        <v>3844</v>
       </c>
     </row>
     <row r="1327" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68526,13 +68567,13 @@
         <v>0.14083333333333334</v>
       </c>
       <c r="H1327" t="s">
-        <v>3827</v>
+        <v>3826</v>
       </c>
       <c r="I1327" t="s">
         <v>809</v>
       </c>
       <c r="J1327" s="63" t="s">
-        <v>3823</v>
+        <v>3822</v>
       </c>
       <c r="K1327">
         <v>1328</v>
@@ -68541,7 +68582,7 @@
         <v>857</v>
       </c>
       <c r="N1327" t="s">
-        <v>3846</v>
+        <v>3845</v>
       </c>
     </row>
     <row r="1328" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68573,7 +68614,7 @@
         <v>809</v>
       </c>
       <c r="J1328" s="63" t="s">
-        <v>3824</v>
+        <v>3823</v>
       </c>
       <c r="K1328">
         <v>1329</v>
@@ -68582,7 +68623,7 @@
         <v>857</v>
       </c>
       <c r="N1328" t="s">
-        <v>3847</v>
+        <v>3846</v>
       </c>
     </row>
     <row r="1329" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68614,7 +68655,7 @@
         <v>809</v>
       </c>
       <c r="J1329" s="63" t="s">
-        <v>3825</v>
+        <v>3824</v>
       </c>
       <c r="K1329">
         <v>1330</v>
@@ -68623,7 +68664,7 @@
         <v>857</v>
       </c>
       <c r="N1329" t="s">
-        <v>3848</v>
+        <v>3847</v>
       </c>
     </row>
     <row r="1330" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68655,7 +68696,7 @@
         <v>809</v>
       </c>
       <c r="J1330" s="63" t="s">
-        <v>3826</v>
+        <v>3825</v>
       </c>
       <c r="K1330">
         <v>1331</v>
@@ -68664,7 +68705,7 @@
         <v>857</v>
       </c>
       <c r="N1330" t="s">
-        <v>3849</v>
+        <v>3848</v>
       </c>
     </row>
     <row r="1331" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68678,7 +68719,7 @@
         <v>504</v>
       </c>
       <c r="D1331" t="s">
-        <v>3753</v>
+        <v>3752</v>
       </c>
       <c r="E1331" t="s">
         <v>209</v>
@@ -68696,7 +68737,7 @@
         <v>809</v>
       </c>
       <c r="J1331" s="63" t="s">
-        <v>3828</v>
+        <v>3827</v>
       </c>
       <c r="K1331">
         <v>1332</v>
@@ -68705,7 +68746,7 @@
         <v>857</v>
       </c>
       <c r="N1331" t="s">
-        <v>3850</v>
+        <v>3849</v>
       </c>
     </row>
     <row r="1332" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68737,7 +68778,7 @@
         <v>809</v>
       </c>
       <c r="J1332" s="63" t="s">
-        <v>3829</v>
+        <v>3828</v>
       </c>
       <c r="K1332">
         <v>1333</v>
@@ -68746,7 +68787,7 @@
         <v>857</v>
       </c>
       <c r="N1332" t="s">
-        <v>3851</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="1333" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68757,13 +68798,13 @@
         <v>13298242</v>
       </c>
       <c r="C1333" t="s">
-        <v>3830</v>
+        <v>3829</v>
       </c>
       <c r="D1333" s="133" t="s">
         <v>1998</v>
       </c>
       <c r="E1333" s="137" t="s">
-        <v>3854</v>
+        <v>3853</v>
       </c>
       <c r="F1333" s="29">
         <v>46110</v>
@@ -68778,7 +68819,7 @@
         <v>809</v>
       </c>
       <c r="J1333" s="134" t="s">
-        <v>3831</v>
+        <v>3830</v>
       </c>
       <c r="K1333">
         <v>1334</v>
@@ -68787,7 +68828,7 @@
         <v>857</v>
       </c>
       <c r="N1333" t="s">
-        <v>3852</v>
+        <v>3851</v>
       </c>
     </row>
     <row r="1334" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68801,7 +68842,7 @@
         <v>17</v>
       </c>
       <c r="D1334" s="135" t="s">
-        <v>3833</v>
+        <v>3832</v>
       </c>
       <c r="E1334" s="135" t="s">
         <v>18</v>
@@ -68819,7 +68860,7 @@
         <v>809</v>
       </c>
       <c r="J1334" s="136" t="s">
-        <v>3832</v>
+        <v>3831</v>
       </c>
       <c r="K1334">
         <v>1335</v>
@@ -68828,7 +68869,7 @@
         <v>857</v>
       </c>
       <c r="N1334" t="s">
-        <v>3853</v>
+        <v>3852</v>
       </c>
     </row>
     <row r="1335" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68839,7 +68880,7 @@
         <v>14527446</v>
       </c>
       <c r="C1335" t="s">
-        <v>3858</v>
+        <v>3857</v>
       </c>
       <c r="D1335" s="137" t="s">
         <v>15</v>
@@ -68854,25 +68895,25 @@
         <v>8.4050925925925932E-2</v>
       </c>
       <c r="H1335" s="137" t="s">
-        <v>3857</v>
+        <v>3856</v>
       </c>
       <c r="I1335" s="137" t="s">
         <v>809</v>
       </c>
       <c r="J1335" s="63" t="s">
-        <v>3856</v>
+        <v>3855</v>
       </c>
       <c r="K1335">
         <v>1336</v>
       </c>
       <c r="L1335" t="s">
-        <v>3855</v>
+        <v>3854</v>
       </c>
       <c r="M1335" s="57" t="s">
         <v>857</v>
       </c>
       <c r="N1335" t="s">
-        <v>3859</v>
+        <v>3858</v>
       </c>
     </row>
     <row r="1336" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68883,10 +68924,10 @@
         <v>5081926</v>
       </c>
       <c r="C1336" t="s">
+        <v>3859</v>
+      </c>
+      <c r="D1336" s="138" t="s">
         <v>3860</v>
-      </c>
-      <c r="D1336" s="138" t="s">
-        <v>3861</v>
       </c>
       <c r="E1336" t="s">
         <v>29</v>
@@ -68904,7 +68945,7 @@
         <v>809</v>
       </c>
       <c r="J1336" s="63" t="s">
-        <v>3862</v>
+        <v>3861</v>
       </c>
       <c r="K1336">
         <v>1337</v>
@@ -68913,7 +68954,7 @@
         <v>857</v>
       </c>
       <c r="N1336" t="s">
-        <v>3873</v>
+        <v>3872</v>
       </c>
     </row>
     <row r="1337" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68927,7 +68968,7 @@
         <v>25</v>
       </c>
       <c r="D1337" s="138" t="s">
-        <v>3863</v>
+        <v>3862</v>
       </c>
       <c r="E1337" t="s">
         <v>3433</v>
@@ -68945,7 +68986,7 @@
         <v>809</v>
       </c>
       <c r="J1337" s="63" t="s">
-        <v>3864</v>
+        <v>3863</v>
       </c>
       <c r="K1337">
         <v>1338</v>
@@ -68954,7 +68995,7 @@
         <v>857</v>
       </c>
       <c r="N1337" t="s">
-        <v>3874</v>
+        <v>3873</v>
       </c>
     </row>
     <row r="1338" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68965,7 +69006,7 @@
         <v>30358417</v>
       </c>
       <c r="C1338" t="s">
-        <v>3866</v>
+        <v>3865</v>
       </c>
       <c r="D1338" s="138" t="s">
         <v>426</v>
@@ -68986,7 +69027,7 @@
         <v>809</v>
       </c>
       <c r="J1338" s="63" t="s">
-        <v>3865</v>
+        <v>3864</v>
       </c>
       <c r="K1338">
         <v>1339</v>
@@ -68995,7 +69036,7 @@
         <v>857</v>
       </c>
       <c r="N1338" t="s">
-        <v>3875</v>
+        <v>3874</v>
       </c>
     </row>
     <row r="1339" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69027,7 +69068,7 @@
         <v>809</v>
       </c>
       <c r="J1339" s="63" t="s">
-        <v>3867</v>
+        <v>3866</v>
       </c>
       <c r="K1339">
         <v>1340</v>
@@ -69036,7 +69077,7 @@
         <v>857</v>
       </c>
       <c r="N1339" t="s">
-        <v>3876</v>
+        <v>3875</v>
       </c>
     </row>
     <row r="1340" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69050,7 +69091,7 @@
         <v>25</v>
       </c>
       <c r="D1340" s="138" t="s">
-        <v>3868</v>
+        <v>3867</v>
       </c>
       <c r="E1340" t="s">
         <v>650</v>
@@ -69068,7 +69109,7 @@
         <v>809</v>
       </c>
       <c r="J1340" s="63" t="s">
-        <v>3869</v>
+        <v>3868</v>
       </c>
       <c r="K1340">
         <v>1341</v>
@@ -69077,7 +69118,7 @@
         <v>857</v>
       </c>
       <c r="N1340" t="s">
-        <v>3877</v>
+        <v>3876</v>
       </c>
     </row>
     <row r="1341" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69109,7 +69150,7 @@
         <v>809</v>
       </c>
       <c r="J1341" s="63" t="s">
-        <v>3870</v>
+        <v>3869</v>
       </c>
       <c r="K1341">
         <v>1342</v>
@@ -69118,7 +69159,7 @@
         <v>857</v>
       </c>
       <c r="N1341" t="s">
-        <v>3878</v>
+        <v>3877</v>
       </c>
     </row>
     <row r="1342" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69150,7 +69191,7 @@
         <v>809</v>
       </c>
       <c r="J1342" s="63" t="s">
-        <v>3871</v>
+        <v>3870</v>
       </c>
       <c r="K1342">
         <v>1343</v>
@@ -69159,7 +69200,7 @@
         <v>857</v>
       </c>
       <c r="N1342" t="s">
-        <v>3879</v>
+        <v>3878</v>
       </c>
     </row>
     <row r="1343" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69191,7 +69232,7 @@
         <v>809</v>
       </c>
       <c r="J1343" s="63" t="s">
-        <v>3872</v>
+        <v>3871</v>
       </c>
       <c r="K1343">
         <v>1344</v>
@@ -69200,7 +69241,7 @@
         <v>857</v>
       </c>
       <c r="N1343" t="s">
-        <v>3880</v>
+        <v>3879</v>
       </c>
     </row>
     <row r="1344" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69232,7 +69273,7 @@
         <v>292</v>
       </c>
       <c r="J1344" s="63" t="s">
-        <v>3882</v>
+        <v>3881</v>
       </c>
       <c r="K1344">
         <v>1345</v>
@@ -69241,7 +69282,7 @@
         <v>857</v>
       </c>
       <c r="N1344" t="s">
-        <v>3892</v>
+        <v>3891</v>
       </c>
     </row>
     <row r="1345" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69273,7 +69314,7 @@
         <v>292</v>
       </c>
       <c r="J1345" s="63" t="s">
-        <v>3883</v>
+        <v>3882</v>
       </c>
       <c r="K1345">
         <v>1346</v>
@@ -69282,7 +69323,7 @@
         <v>857</v>
       </c>
       <c r="N1345" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
     </row>
     <row r="1346" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69293,7 +69334,7 @@
         <v>4196788</v>
       </c>
       <c r="C1346" t="s">
-        <v>3885</v>
+        <v>3884</v>
       </c>
       <c r="D1346" s="140" t="s">
         <v>443</v>
@@ -69314,7 +69355,7 @@
         <v>292</v>
       </c>
       <c r="J1346" s="63" t="s">
-        <v>3884</v>
+        <v>3883</v>
       </c>
       <c r="K1346">
         <v>1347</v>
@@ -69323,7 +69364,7 @@
         <v>857</v>
       </c>
       <c r="N1346" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="1347" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69334,7 +69375,7 @@
         <v>11596975</v>
       </c>
       <c r="C1347" t="s">
-        <v>3886</v>
+        <v>3885</v>
       </c>
       <c r="D1347" s="140" t="s">
         <v>374</v>
@@ -69355,7 +69396,7 @@
         <v>292</v>
       </c>
       <c r="J1347" s="63" t="s">
-        <v>3887</v>
+        <v>3886</v>
       </c>
       <c r="K1347">
         <v>1348</v>
@@ -69364,7 +69405,7 @@
         <v>857</v>
       </c>
       <c r="N1347" t="s">
-        <v>3895</v>
+        <v>3894</v>
       </c>
     </row>
     <row r="1348" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69396,7 +69437,7 @@
         <v>809</v>
       </c>
       <c r="J1348" s="63" t="s">
-        <v>3888</v>
+        <v>3887</v>
       </c>
       <c r="K1348">
         <v>1349</v>
@@ -69405,7 +69446,7 @@
         <v>857</v>
       </c>
       <c r="N1348" t="s">
-        <v>3896</v>
+        <v>3895</v>
       </c>
     </row>
     <row r="1349" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69437,7 +69478,7 @@
         <v>809</v>
       </c>
       <c r="J1349" s="63" t="s">
-        <v>3889</v>
+        <v>3888</v>
       </c>
       <c r="K1349">
         <v>1350</v>
@@ -69446,7 +69487,7 @@
         <v>857</v>
       </c>
       <c r="N1349" t="s">
-        <v>3897</v>
+        <v>3896</v>
       </c>
     </row>
     <row r="1350" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69460,7 +69501,7 @@
         <v>17</v>
       </c>
       <c r="D1350" s="140" t="s">
-        <v>3782</v>
+        <v>3781</v>
       </c>
       <c r="E1350" t="s">
         <v>18</v>
@@ -69478,7 +69519,7 @@
         <v>292</v>
       </c>
       <c r="J1350" s="63" t="s">
-        <v>3890</v>
+        <v>3889</v>
       </c>
       <c r="K1350">
         <v>1351</v>
@@ -69487,7 +69528,7 @@
         <v>857</v>
       </c>
       <c r="N1350" t="s">
-        <v>3898</v>
+        <v>3897</v>
       </c>
     </row>
     <row r="1351" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69501,7 +69542,7 @@
         <v>17</v>
       </c>
       <c r="D1351" s="140" t="s">
-        <v>3782</v>
+        <v>3781</v>
       </c>
       <c r="E1351" t="s">
         <v>18</v>
@@ -69519,7 +69560,7 @@
         <v>292</v>
       </c>
       <c r="J1351" s="63" t="s">
-        <v>3891</v>
+        <v>3890</v>
       </c>
       <c r="K1351">
         <v>1352</v>
@@ -69528,7 +69569,7 @@
         <v>857</v>
       </c>
       <c r="N1351" t="s">
-        <v>3899</v>
+        <v>3898</v>
       </c>
     </row>
     <row r="1352" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69539,10 +69580,10 @@
         <v>6980000</v>
       </c>
       <c r="C1352" t="s">
-        <v>3902</v>
+        <v>3901</v>
       </c>
       <c r="D1352" s="141" t="s">
-        <v>3906</v>
+        <v>3905</v>
       </c>
       <c r="E1352" t="s">
         <v>368</v>
@@ -69560,7 +69601,7 @@
         <v>292</v>
       </c>
       <c r="J1352" s="63" t="s">
-        <v>3903</v>
+        <v>3902</v>
       </c>
       <c r="K1352">
         <v>1353</v>
@@ -69569,7 +69610,7 @@
         <v>857</v>
       </c>
       <c r="N1352" t="s">
-        <v>3915</v>
+        <v>3914</v>
       </c>
     </row>
     <row r="1353" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69580,7 +69621,7 @@
         <v>4892080</v>
       </c>
       <c r="C1353" t="s">
-        <v>3907</v>
+        <v>3906</v>
       </c>
       <c r="D1353" s="141" t="s">
         <v>648</v>
@@ -69595,13 +69636,13 @@
         <v>4.6365740740740742E-2</v>
       </c>
       <c r="H1353" s="141" t="s">
-        <v>3908</v>
+        <v>3907</v>
       </c>
       <c r="I1353" s="141" t="s">
         <v>292</v>
       </c>
       <c r="J1353" s="63" t="s">
-        <v>3904</v>
+        <v>3903</v>
       </c>
       <c r="K1353">
         <v>1354</v>
@@ -69610,7 +69651,7 @@
         <v>857</v>
       </c>
       <c r="N1353" t="s">
-        <v>3916</v>
+        <v>3915</v>
       </c>
     </row>
     <row r="1354" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69624,7 +69665,7 @@
         <v>442</v>
       </c>
       <c r="D1354" t="s">
-        <v>3909</v>
+        <v>3908</v>
       </c>
       <c r="E1354" t="s">
         <v>435</v>
@@ -69642,7 +69683,7 @@
         <v>292</v>
       </c>
       <c r="J1354" s="63" t="s">
-        <v>3905</v>
+        <v>3904</v>
       </c>
       <c r="K1354">
         <v>1355</v>
@@ -69651,7 +69692,7 @@
         <v>857</v>
       </c>
       <c r="N1354" t="s">
-        <v>3917</v>
+        <v>3916</v>
       </c>
     </row>
     <row r="1355" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69662,7 +69703,7 @@
         <v>4255101</v>
       </c>
       <c r="C1355" t="s">
-        <v>3910</v>
+        <v>3909</v>
       </c>
       <c r="D1355" t="s">
         <v>374</v>
@@ -69683,7 +69724,7 @@
         <v>292</v>
       </c>
       <c r="J1355" s="63" t="s">
-        <v>3911</v>
+        <v>3910</v>
       </c>
       <c r="K1355">
         <v>1356</v>
@@ -69692,7 +69733,7 @@
         <v>857</v>
       </c>
       <c r="N1355" t="s">
-        <v>3918</v>
+        <v>3917</v>
       </c>
     </row>
     <row r="1356" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69706,7 +69747,7 @@
         <v>209</v>
       </c>
       <c r="D1356" t="s">
-        <v>3914</v>
+        <v>3913</v>
       </c>
       <c r="E1356" t="s">
         <v>209</v>
@@ -69724,7 +69765,7 @@
         <v>292</v>
       </c>
       <c r="J1356" s="63" t="s">
-        <v>3912</v>
+        <v>3911</v>
       </c>
       <c r="K1356">
         <v>1357</v>
@@ -69733,7 +69774,7 @@
         <v>857</v>
       </c>
       <c r="N1356" t="s">
-        <v>3919</v>
+        <v>3918</v>
       </c>
     </row>
     <row r="1357" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69765,7 +69806,7 @@
         <v>292</v>
       </c>
       <c r="J1357" s="63" t="s">
-        <v>3913</v>
+        <v>3912</v>
       </c>
       <c r="K1357">
         <v>1358</v>
@@ -69774,7 +69815,7 @@
         <v>857</v>
       </c>
       <c r="N1357" t="s">
-        <v>3920</v>
+        <v>3919</v>
       </c>
     </row>
     <row r="1358" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69806,7 +69847,7 @@
         <v>809</v>
       </c>
       <c r="J1358" s="63" t="s">
-        <v>3925</v>
+        <v>3924</v>
       </c>
       <c r="K1358">
         <v>1359</v>
@@ -69815,7 +69856,7 @@
         <v>857</v>
       </c>
       <c r="N1358" t="s">
-        <v>3938</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="1359" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69847,7 +69888,7 @@
         <v>292</v>
       </c>
       <c r="J1359" s="63" t="s">
-        <v>3926</v>
+        <v>3925</v>
       </c>
       <c r="K1359">
         <v>1360</v>
@@ -69856,7 +69897,7 @@
         <v>857</v>
       </c>
       <c r="N1359" t="s">
-        <v>3939</v>
+        <v>3938</v>
       </c>
     </row>
     <row r="1360" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69867,7 +69908,7 @@
         <v>16543175</v>
       </c>
       <c r="C1360" t="s">
-        <v>3927</v>
+        <v>3926</v>
       </c>
       <c r="D1360" t="s">
         <v>426</v>
@@ -69888,7 +69929,7 @@
         <v>809</v>
       </c>
       <c r="J1360" s="63" t="s">
-        <v>3928</v>
+        <v>3927</v>
       </c>
       <c r="K1360">
         <v>1361</v>
@@ -69897,7 +69938,7 @@
         <v>857</v>
       </c>
       <c r="N1360" t="s">
-        <v>3940</v>
+        <v>3939</v>
       </c>
     </row>
     <row r="1361" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69908,7 +69949,7 @@
         <v>8112313</v>
       </c>
       <c r="C1361" t="s">
-        <v>3930</v>
+        <v>3929</v>
       </c>
       <c r="D1361" t="s">
         <v>592</v>
@@ -69929,7 +69970,7 @@
         <v>809</v>
       </c>
       <c r="J1361" s="63" t="s">
-        <v>3929</v>
+        <v>3928</v>
       </c>
       <c r="K1361">
         <v>1362</v>
@@ -69938,7 +69979,7 @@
         <v>857</v>
       </c>
       <c r="N1361" t="s">
-        <v>3941</v>
+        <v>3940</v>
       </c>
     </row>
     <row r="1362" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69952,7 +69993,7 @@
         <v>17</v>
       </c>
       <c r="D1362" t="s">
-        <v>3833</v>
+        <v>3832</v>
       </c>
       <c r="E1362" t="s">
         <v>18</v>
@@ -69970,7 +70011,7 @@
         <v>809</v>
       </c>
       <c r="J1362" s="63" t="s">
-        <v>3931</v>
+        <v>3930</v>
       </c>
       <c r="K1362">
         <v>1363</v>
@@ -69979,7 +70020,7 @@
         <v>857</v>
       </c>
       <c r="N1362" t="s">
-        <v>3942</v>
+        <v>3941</v>
       </c>
     </row>
     <row r="1363" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69990,7 +70031,7 @@
         <v>19167309</v>
       </c>
       <c r="C1363" t="s">
-        <v>3934</v>
+        <v>3933</v>
       </c>
       <c r="D1363" t="s">
         <v>161</v>
@@ -70005,13 +70046,13 @@
         <v>0.14107638888888888</v>
       </c>
       <c r="H1363" s="143" t="s">
-        <v>3933</v>
+        <v>3932</v>
       </c>
       <c r="I1363" s="143" t="s">
         <v>809</v>
       </c>
       <c r="J1363" s="63" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
       <c r="K1363">
         <v>1364</v>
@@ -70020,7 +70061,7 @@
         <v>857</v>
       </c>
       <c r="N1363" t="s">
-        <v>3943</v>
+        <v>3942</v>
       </c>
     </row>
     <row r="1364" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70031,7 +70072,7 @@
         <v>15541720</v>
       </c>
       <c r="C1364" t="s">
-        <v>3886</v>
+        <v>3885</v>
       </c>
       <c r="D1364" t="s">
         <v>374</v>
@@ -70052,7 +70093,7 @@
         <v>292</v>
       </c>
       <c r="J1364" s="63" t="s">
-        <v>3935</v>
+        <v>3934</v>
       </c>
       <c r="K1364">
         <v>1365</v>
@@ -70061,7 +70102,7 @@
         <v>857</v>
       </c>
       <c r="N1364" t="s">
-        <v>3944</v>
+        <v>3943</v>
       </c>
     </row>
     <row r="1365" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70075,7 +70116,7 @@
         <v>3538</v>
       </c>
       <c r="D1365" t="s">
-        <v>3937</v>
+        <v>3936</v>
       </c>
       <c r="E1365" t="s">
         <v>18</v>
@@ -70093,7 +70134,7 @@
         <v>809</v>
       </c>
       <c r="J1365" s="63" t="s">
-        <v>3936</v>
+        <v>3935</v>
       </c>
       <c r="K1365">
         <v>1366</v>
@@ -70102,7 +70143,7 @@
         <v>857</v>
       </c>
       <c r="N1365" t="s">
-        <v>3945</v>
+        <v>3944</v>
       </c>
     </row>
     <row r="1366" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70134,7 +70175,7 @@
         <v>809</v>
       </c>
       <c r="J1366" s="63" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
       <c r="K1366">
         <v>1367</v>
@@ -70143,7 +70184,7 @@
         <v>857</v>
       </c>
       <c r="N1366" t="s">
-        <v>3947</v>
+        <v>3946</v>
       </c>
     </row>
     <row r="1367" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70154,7 +70195,7 @@
         <v>25352781</v>
       </c>
       <c r="C1367" t="s">
-        <v>3948</v>
+        <v>3947</v>
       </c>
       <c r="D1367" t="s">
         <v>60</v>
@@ -70169,13 +70210,13 @@
         <v>504</v>
       </c>
       <c r="H1367" s="145" t="s">
+        <v>3948</v>
+      </c>
+      <c r="I1367" s="145" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1367" s="63" t="s">
         <v>3949</v>
-      </c>
-      <c r="I1367" s="145" t="s">
-        <v>809</v>
-      </c>
-      <c r="J1367" s="63" t="s">
-        <v>3950</v>
       </c>
       <c r="K1367">
         <v>1368</v>
@@ -70184,7 +70225,7 @@
         <v>857</v>
       </c>
       <c r="N1367" t="s">
-        <v>3954</v>
+        <v>3953</v>
       </c>
     </row>
     <row r="1368" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70216,7 +70257,7 @@
         <v>809</v>
       </c>
       <c r="J1368" s="63" t="s">
-        <v>3951</v>
+        <v>3950</v>
       </c>
       <c r="K1368">
         <v>1369</v>
@@ -70225,7 +70266,7 @@
         <v>857</v>
       </c>
       <c r="N1368" t="s">
-        <v>3955</v>
+        <v>3954</v>
       </c>
     </row>
     <row r="1369" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70236,10 +70277,10 @@
         <v>10476636</v>
       </c>
       <c r="C1369" t="s">
-        <v>3934</v>
+        <v>3933</v>
       </c>
       <c r="D1369" t="s">
-        <v>3723</v>
+        <v>3722</v>
       </c>
       <c r="E1369" t="s">
         <v>51</v>
@@ -70257,7 +70298,7 @@
         <v>809</v>
       </c>
       <c r="J1369" s="63" t="s">
-        <v>3952</v>
+        <v>3951</v>
       </c>
       <c r="K1369">
         <v>1370</v>
@@ -70266,7 +70307,7 @@
         <v>857</v>
       </c>
       <c r="N1369" t="s">
-        <v>3956</v>
+        <v>3955</v>
       </c>
     </row>
     <row r="1370" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70298,7 +70339,7 @@
         <v>809</v>
       </c>
       <c r="J1370" s="63" t="s">
-        <v>3953</v>
+        <v>3952</v>
       </c>
       <c r="K1370">
         <v>1371</v>
@@ -70307,7 +70348,7 @@
         <v>857</v>
       </c>
       <c r="N1370" t="s">
-        <v>3957</v>
+        <v>3956</v>
       </c>
     </row>
     <row r="1371" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70318,7 +70359,7 @@
         <v>43719222</v>
       </c>
       <c r="C1371" t="s">
-        <v>3959</v>
+        <v>3958</v>
       </c>
       <c r="D1371" t="s">
         <v>60</v>
@@ -70339,7 +70380,7 @@
         <v>809</v>
       </c>
       <c r="J1371" s="63" t="s">
-        <v>3958</v>
+        <v>3957</v>
       </c>
       <c r="K1371">
         <v>1372</v>
@@ -70348,7 +70389,7 @@
         <v>857</v>
       </c>
       <c r="N1371" t="s">
-        <v>3984</v>
+        <v>3983</v>
       </c>
     </row>
     <row r="1372" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70374,13 +70415,13 @@
         <v>504</v>
       </c>
       <c r="H1372" s="146" t="s">
-        <v>3961</v>
+        <v>3960</v>
       </c>
       <c r="I1372" s="146" t="s">
         <v>816</v>
       </c>
       <c r="J1372" s="63" t="s">
-        <v>3960</v>
+        <v>3959</v>
       </c>
       <c r="K1372">
         <v>1373</v>
@@ -70389,7 +70430,7 @@
         <v>857</v>
       </c>
       <c r="N1372" t="s">
-        <v>3985</v>
+        <v>3984</v>
       </c>
     </row>
     <row r="1373" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70400,7 +70441,7 @@
         <v>4790253</v>
       </c>
       <c r="C1373" t="s">
-        <v>3963</v>
+        <v>3962</v>
       </c>
       <c r="D1373" t="s">
         <v>285</v>
@@ -70421,7 +70462,7 @@
         <v>292</v>
       </c>
       <c r="J1373" s="63" t="s">
-        <v>3962</v>
+        <v>3961</v>
       </c>
       <c r="K1373">
         <v>1374</v>
@@ -70430,7 +70471,7 @@
         <v>857</v>
       </c>
       <c r="N1373" t="s">
-        <v>3986</v>
+        <v>3985</v>
       </c>
     </row>
     <row r="1374" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70441,7 +70482,7 @@
         <v>7656870</v>
       </c>
       <c r="C1374" t="s">
-        <v>3965</v>
+        <v>3964</v>
       </c>
       <c r="D1374" t="s">
         <v>128</v>
@@ -70462,7 +70503,7 @@
         <v>809</v>
       </c>
       <c r="J1374" s="63" t="s">
-        <v>3964</v>
+        <v>3963</v>
       </c>
       <c r="K1374">
         <v>1375</v>
@@ -70471,7 +70512,7 @@
         <v>857</v>
       </c>
       <c r="N1374" t="s">
-        <v>3987</v>
+        <v>3986</v>
       </c>
     </row>
     <row r="1375" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70482,7 +70523,7 @@
         <v>8733988</v>
       </c>
       <c r="C1375" t="s">
-        <v>3965</v>
+        <v>3964</v>
       </c>
       <c r="D1375" t="s">
         <v>68</v>
@@ -70503,7 +70544,7 @@
         <v>809</v>
       </c>
       <c r="J1375" s="63" t="s">
-        <v>3966</v>
+        <v>3965</v>
       </c>
       <c r="K1375">
         <v>1376</v>
@@ -70512,7 +70553,7 @@
         <v>857</v>
       </c>
       <c r="N1375" t="s">
-        <v>3988</v>
+        <v>3987</v>
       </c>
     </row>
     <row r="1376" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70538,13 +70579,13 @@
         <v>9.2604166666666668E-2</v>
       </c>
       <c r="H1376" s="146" t="s">
+        <v>3966</v>
+      </c>
+      <c r="I1376" s="146" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1376" s="63" t="s">
         <v>3967</v>
-      </c>
-      <c r="I1376" s="146" t="s">
-        <v>809</v>
-      </c>
-      <c r="J1376" s="63" t="s">
-        <v>3968</v>
       </c>
       <c r="K1376">
         <v>1377</v>
@@ -70553,7 +70594,7 @@
         <v>857</v>
       </c>
       <c r="N1376" t="s">
-        <v>3989</v>
+        <v>3988</v>
       </c>
     </row>
     <row r="1377" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70564,7 +70605,7 @@
         <v>14343403</v>
       </c>
       <c r="C1377" t="s">
-        <v>3970</v>
+        <v>3969</v>
       </c>
       <c r="D1377" t="s">
         <v>96</v>
@@ -70579,13 +70620,13 @@
         <v>0.10716435185185186</v>
       </c>
       <c r="H1377" s="146" t="s">
-        <v>3969</v>
+        <v>3968</v>
       </c>
       <c r="I1377" s="146" t="s">
         <v>809</v>
       </c>
       <c r="J1377" s="63" t="s">
-        <v>3972</v>
+        <v>3971</v>
       </c>
       <c r="K1377">
         <v>1378</v>
@@ -70594,7 +70635,7 @@
         <v>857</v>
       </c>
       <c r="N1377" t="s">
-        <v>3990</v>
+        <v>3989</v>
       </c>
     </row>
     <row r="1378" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70605,7 +70646,7 @@
         <v>12410166</v>
       </c>
       <c r="C1378" t="s">
-        <v>3971</v>
+        <v>3970</v>
       </c>
       <c r="D1378" t="s">
         <v>448</v>
@@ -70626,7 +70667,7 @@
         <v>809</v>
       </c>
       <c r="J1378" s="63" t="s">
-        <v>3973</v>
+        <v>3972</v>
       </c>
       <c r="K1378">
         <v>1379</v>
@@ -70635,7 +70676,7 @@
         <v>857</v>
       </c>
       <c r="N1378" t="s">
-        <v>3991</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="1379" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70667,7 +70708,7 @@
         <v>809</v>
       </c>
       <c r="J1379" s="63" t="s">
-        <v>3974</v>
+        <v>3973</v>
       </c>
       <c r="K1379">
         <v>1380</v>
@@ -70676,7 +70717,7 @@
         <v>857</v>
       </c>
       <c r="N1379" t="s">
-        <v>3992</v>
+        <v>3991</v>
       </c>
     </row>
     <row r="1380" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70702,13 +70743,13 @@
         <v>504</v>
       </c>
       <c r="H1380" s="146" t="s">
-        <v>3728</v>
+        <v>3727</v>
       </c>
       <c r="I1380" s="146" t="s">
         <v>809</v>
       </c>
       <c r="J1380" s="63" t="s">
-        <v>3975</v>
+        <v>3974</v>
       </c>
       <c r="K1380">
         <v>1381</v>
@@ -70717,7 +70758,7 @@
         <v>857</v>
       </c>
       <c r="N1380" t="s">
-        <v>3993</v>
+        <v>3992</v>
       </c>
     </row>
     <row r="1381" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70728,13 +70769,13 @@
         <v>9380000</v>
       </c>
       <c r="C1381" t="s">
-        <v>3976</v>
+        <v>3975</v>
       </c>
       <c r="D1381" t="s">
         <v>621</v>
       </c>
       <c r="E1381" t="s">
-        <v>3976</v>
+        <v>3975</v>
       </c>
       <c r="F1381" s="29">
         <v>46120</v>
@@ -70749,7 +70790,7 @@
         <v>809</v>
       </c>
       <c r="J1381" s="63" t="s">
-        <v>3977</v>
+        <v>3976</v>
       </c>
       <c r="K1381">
         <v>1382</v>
@@ -70758,7 +70799,7 @@
         <v>857</v>
       </c>
       <c r="N1381" t="s">
-        <v>3994</v>
+        <v>3993</v>
       </c>
     </row>
     <row r="1382" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70769,7 +70810,7 @@
         <v>18187409</v>
       </c>
       <c r="C1382" t="s">
-        <v>3981</v>
+        <v>3980</v>
       </c>
       <c r="D1382" t="s">
         <v>79</v>
@@ -70784,13 +70825,13 @@
         <v>0.11269675925925926</v>
       </c>
       <c r="H1382" s="146" t="s">
+        <v>3977</v>
+      </c>
+      <c r="I1382" s="146" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1382" s="63" t="s">
         <v>3978</v>
-      </c>
-      <c r="I1382" s="146" t="s">
-        <v>809</v>
-      </c>
-      <c r="J1382" s="63" t="s">
-        <v>3979</v>
       </c>
       <c r="K1382">
         <v>1383</v>
@@ -70799,7 +70840,7 @@
         <v>857</v>
       </c>
       <c r="N1382" t="s">
-        <v>3995</v>
+        <v>3994</v>
       </c>
     </row>
     <row r="1383" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70810,10 +70851,10 @@
         <v>9353760</v>
       </c>
       <c r="C1383" t="s">
-        <v>3982</v>
+        <v>3981</v>
       </c>
       <c r="D1383" t="s">
-        <v>3868</v>
+        <v>3867</v>
       </c>
       <c r="E1383" t="s">
         <v>650</v>
@@ -70825,13 +70866,13 @@
         <v>4.7731481481481486E-2</v>
       </c>
       <c r="H1383" s="146" t="s">
-        <v>3983</v>
+        <v>3982</v>
       </c>
       <c r="I1383" s="146" t="s">
         <v>809</v>
       </c>
       <c r="J1383" s="63" t="s">
-        <v>3980</v>
+        <v>3979</v>
       </c>
       <c r="K1383">
         <v>1384</v>
@@ -70840,7 +70881,7 @@
         <v>857</v>
       </c>
       <c r="N1383" t="s">
-        <v>3996</v>
+        <v>3995</v>
       </c>
     </row>
     <row r="1384" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70857,7 +70898,7 @@
         <v>426</v>
       </c>
       <c r="E1384" t="s">
-        <v>3997</v>
+        <v>3996</v>
       </c>
       <c r="F1384" s="29">
         <v>46123</v>
@@ -70872,7 +70913,7 @@
         <v>809</v>
       </c>
       <c r="J1384" s="63" t="s">
-        <v>3998</v>
+        <v>3997</v>
       </c>
       <c r="K1384">
         <v>1385</v>
@@ -70881,7 +70922,7 @@
         <v>857</v>
       </c>
       <c r="N1384" t="s">
-        <v>4006</v>
+        <v>4005</v>
       </c>
     </row>
     <row r="1385" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70907,13 +70948,13 @@
         <v>0.11065972222222221</v>
       </c>
       <c r="H1385" s="147" t="s">
+        <v>3998</v>
+      </c>
+      <c r="I1385" s="147" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1385" s="63" t="s">
         <v>3999</v>
-      </c>
-      <c r="I1385" s="147" t="s">
-        <v>809</v>
-      </c>
-      <c r="J1385" s="63" t="s">
-        <v>4000</v>
       </c>
       <c r="K1385">
         <v>1386</v>
@@ -70922,7 +70963,7 @@
         <v>857</v>
       </c>
       <c r="N1385" t="s">
-        <v>4007</v>
+        <v>4006</v>
       </c>
     </row>
     <row r="1386" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70954,7 +70995,7 @@
         <v>809</v>
       </c>
       <c r="J1386" s="63" t="s">
-        <v>4001</v>
+        <v>4000</v>
       </c>
       <c r="K1386">
         <v>1387</v>
@@ -70963,7 +71004,7 @@
         <v>857</v>
       </c>
       <c r="N1386" t="s">
-        <v>4008</v>
+        <v>4007</v>
       </c>
     </row>
     <row r="1387" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70974,7 +71015,7 @@
         <v>10483435</v>
       </c>
       <c r="C1387" t="s">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="D1387" t="s">
         <v>401</v>
@@ -70995,7 +71036,7 @@
         <v>809</v>
       </c>
       <c r="J1387" s="63" t="s">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="K1387">
         <v>1388</v>
@@ -71004,7 +71045,7 @@
         <v>857</v>
       </c>
       <c r="N1387" t="s">
-        <v>4009</v>
+        <v>4008</v>
       </c>
     </row>
     <row r="1388" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71030,13 +71071,13 @@
         <v>6.3472222222222222E-2</v>
       </c>
       <c r="H1388" s="147" t="s">
+        <v>4003</v>
+      </c>
+      <c r="I1388" s="147" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1388" s="63" t="s">
         <v>4004</v>
-      </c>
-      <c r="I1388" s="147" t="s">
-        <v>809</v>
-      </c>
-      <c r="J1388" s="63" t="s">
-        <v>4005</v>
       </c>
       <c r="K1388">
         <v>1389</v>
@@ -71045,7 +71086,7 @@
         <v>857</v>
       </c>
       <c r="N1388" t="s">
-        <v>4010</v>
+        <v>4009</v>
       </c>
     </row>
     <row r="1389" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71056,7 +71097,7 @@
         <v>3935653</v>
       </c>
       <c r="C1389" t="s">
-        <v>4011</v>
+        <v>4010</v>
       </c>
       <c r="D1389" t="s">
         <v>615</v>
@@ -71077,7 +71118,7 @@
         <v>809</v>
       </c>
       <c r="J1389" s="63" t="s">
-        <v>4012</v>
+        <v>4011</v>
       </c>
       <c r="K1389">
         <v>1390</v>
@@ -71086,7 +71127,7 @@
         <v>857</v>
       </c>
       <c r="N1389" t="s">
-        <v>4014</v>
+        <v>4013</v>
       </c>
     </row>
     <row r="1390" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71118,7 +71159,7 @@
         <v>809</v>
       </c>
       <c r="J1390" s="63" t="s">
-        <v>4013</v>
+        <v>4012</v>
       </c>
       <c r="K1390">
         <v>1391</v>
@@ -71127,7 +71168,7 @@
         <v>857</v>
       </c>
       <c r="N1390" t="s">
-        <v>4015</v>
+        <v>4014</v>
       </c>
     </row>
     <row r="1391" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71141,7 +71182,7 @@
         <v>32</v>
       </c>
       <c r="D1391" t="s">
-        <v>4016</v>
+        <v>4015</v>
       </c>
       <c r="E1391" t="s">
         <v>29</v>
@@ -71153,13 +71194,13 @@
         <v>6.9641203703703705E-2</v>
       </c>
       <c r="H1391" s="149" t="s">
+        <v>4016</v>
+      </c>
+      <c r="I1391" s="149" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1391" s="63" t="s">
         <v>4017</v>
-      </c>
-      <c r="I1391" s="149" t="s">
-        <v>809</v>
-      </c>
-      <c r="J1391" s="63" t="s">
-        <v>4018</v>
       </c>
       <c r="K1391">
         <v>1392</v>
@@ -71168,7 +71209,7 @@
         <v>857</v>
       </c>
       <c r="N1391" t="s">
-        <v>4022</v>
+        <v>4021</v>
       </c>
     </row>
     <row r="1392" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71200,7 +71241,7 @@
         <v>809</v>
       </c>
       <c r="J1392" s="63" t="s">
-        <v>4019</v>
+        <v>4018</v>
       </c>
       <c r="K1392">
         <v>1393</v>
@@ -71209,7 +71250,7 @@
         <v>857</v>
       </c>
       <c r="N1392" t="s">
-        <v>4049</v>
+        <v>4048</v>
       </c>
     </row>
     <row r="1393" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71241,7 +71282,7 @@
         <v>809</v>
       </c>
       <c r="J1393" s="63" t="s">
-        <v>4020</v>
+        <v>4019</v>
       </c>
       <c r="K1393">
         <v>1394</v>
@@ -71250,7 +71291,7 @@
         <v>857</v>
       </c>
       <c r="N1393" t="s">
-        <v>4023</v>
+        <v>4022</v>
       </c>
     </row>
     <row r="1394" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71261,7 +71302,7 @@
         <v>8459179</v>
       </c>
       <c r="C1394" t="s">
-        <v>3715</v>
+        <v>3714</v>
       </c>
       <c r="D1394" t="s">
         <v>395</v>
@@ -71282,7 +71323,7 @@
         <v>809</v>
       </c>
       <c r="J1394" s="63" t="s">
-        <v>4021</v>
+        <v>4020</v>
       </c>
       <c r="K1394">
         <v>1395</v>
@@ -71291,7 +71332,7 @@
         <v>857</v>
       </c>
       <c r="N1394" t="s">
-        <v>4024</v>
+        <v>4023</v>
       </c>
     </row>
     <row r="1395" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71302,7 +71343,7 @@
         <v>21177695</v>
       </c>
       <c r="C1395" t="s">
-        <v>3689</v>
+        <v>3688</v>
       </c>
       <c r="D1395" t="s">
         <v>366</v>
@@ -71323,7 +71364,7 @@
         <v>809</v>
       </c>
       <c r="J1395" s="63" t="s">
-        <v>4026</v>
+        <v>4025</v>
       </c>
       <c r="K1395">
         <v>1396</v>
@@ -71332,7 +71373,7 @@
         <v>857</v>
       </c>
       <c r="N1395" t="s">
-        <v>4050</v>
+        <v>4049</v>
       </c>
     </row>
     <row r="1396" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71343,13 +71384,13 @@
         <v>9514769</v>
       </c>
       <c r="C1396" t="s">
-        <v>4028</v>
+        <v>4027</v>
       </c>
       <c r="D1396" t="s">
         <v>76</v>
       </c>
       <c r="E1396" t="s">
-        <v>4027</v>
+        <v>4026</v>
       </c>
       <c r="F1396" s="29">
         <v>44675</v>
@@ -71364,7 +71405,7 @@
         <v>816</v>
       </c>
       <c r="J1396" s="63" t="s">
-        <v>4025</v>
+        <v>4024</v>
       </c>
       <c r="K1396">
         <v>1397</v>
@@ -71373,7 +71414,7 @@
         <v>857</v>
       </c>
       <c r="N1396" t="s">
-        <v>4051</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="1397" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71390,7 +71431,7 @@
         <v>76</v>
       </c>
       <c r="E1397" t="s">
-        <v>4027</v>
+        <v>4026</v>
       </c>
       <c r="F1397" s="29">
         <v>44677</v>
@@ -71405,7 +71446,7 @@
         <v>816</v>
       </c>
       <c r="J1397" s="63" t="s">
-        <v>4029</v>
+        <v>4028</v>
       </c>
       <c r="K1397">
         <v>1398</v>
@@ -71414,7 +71455,7 @@
         <v>857</v>
       </c>
       <c r="N1397" t="s">
-        <v>4052</v>
+        <v>4051</v>
       </c>
     </row>
     <row r="1398" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71431,7 +71472,7 @@
         <v>438</v>
       </c>
       <c r="E1398" t="s">
-        <v>4027</v>
+        <v>4026</v>
       </c>
       <c r="F1398" s="29">
         <v>44679</v>
@@ -71446,7 +71487,7 @@
         <v>816</v>
       </c>
       <c r="J1398" s="63" t="s">
-        <v>4030</v>
+        <v>4029</v>
       </c>
       <c r="K1398">
         <v>1399</v>
@@ -71455,7 +71496,7 @@
         <v>857</v>
       </c>
       <c r="N1398" t="s">
-        <v>4053</v>
+        <v>4052</v>
       </c>
     </row>
     <row r="1399" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71466,13 +71507,13 @@
         <v>3397005</v>
       </c>
       <c r="C1399" t="s">
-        <v>4034</v>
+        <v>4033</v>
       </c>
       <c r="D1399" t="s">
         <v>76</v>
       </c>
       <c r="E1399" t="s">
-        <v>4027</v>
+        <v>4026</v>
       </c>
       <c r="F1399" s="29">
         <v>44556</v>
@@ -71481,13 +71522,13 @@
         <v>2.7152777777777779E-2</v>
       </c>
       <c r="H1399" s="150" t="s">
-        <v>4033</v>
+        <v>4032</v>
       </c>
       <c r="I1399" s="150" t="s">
         <v>816</v>
       </c>
       <c r="J1399" s="63" t="s">
-        <v>4031</v>
+        <v>4030</v>
       </c>
       <c r="K1399">
         <v>1400</v>
@@ -71496,7 +71537,7 @@
         <v>857</v>
       </c>
       <c r="N1399" t="s">
-        <v>4054</v>
+        <v>4053</v>
       </c>
     </row>
     <row r="1400" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71507,13 +71548,13 @@
         <v>3817177</v>
       </c>
       <c r="C1400" t="s">
-        <v>4036</v>
+        <v>4035</v>
       </c>
       <c r="D1400" t="s">
-        <v>3914</v>
+        <v>3913</v>
       </c>
       <c r="E1400" t="s">
-        <v>4035</v>
+        <v>4034</v>
       </c>
       <c r="F1400" s="29">
         <v>44579</v>
@@ -71528,7 +71569,7 @@
         <v>816</v>
       </c>
       <c r="J1400" s="63" t="s">
-        <v>4032</v>
+        <v>4031</v>
       </c>
       <c r="K1400">
         <v>1401</v>
@@ -71537,7 +71578,7 @@
         <v>857</v>
       </c>
       <c r="N1400" t="s">
-        <v>4055</v>
+        <v>4054</v>
       </c>
     </row>
     <row r="1401" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71548,13 +71589,13 @@
         <v>4527031</v>
       </c>
       <c r="C1401" t="s">
-        <v>4037</v>
+        <v>4036</v>
       </c>
       <c r="D1401" t="s">
         <v>76</v>
       </c>
       <c r="E1401" t="s">
-        <v>4035</v>
+        <v>4034</v>
       </c>
       <c r="F1401" s="29">
         <v>44549</v>
@@ -71569,7 +71610,7 @@
         <v>816</v>
       </c>
       <c r="J1401" s="63" t="s">
-        <v>4038</v>
+        <v>4037</v>
       </c>
       <c r="K1401">
         <v>1402</v>
@@ -71578,7 +71619,7 @@
         <v>857</v>
       </c>
       <c r="N1401" t="s">
-        <v>4056</v>
+        <v>4055</v>
       </c>
     </row>
     <row r="1402" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71589,13 +71630,13 @@
         <v>3055127</v>
       </c>
       <c r="C1402" t="s">
-        <v>4040</v>
+        <v>4039</v>
       </c>
       <c r="D1402" t="s">
         <v>203</v>
       </c>
       <c r="E1402" t="s">
-        <v>4027</v>
+        <v>4026</v>
       </c>
       <c r="F1402" s="29">
         <v>44563</v>
@@ -71604,13 +71645,13 @@
         <v>4.2222222222222223E-2</v>
       </c>
       <c r="H1402" s="150" t="s">
-        <v>4041</v>
+        <v>4040</v>
       </c>
       <c r="I1402" s="150" t="s">
         <v>292</v>
       </c>
       <c r="J1402" s="63" t="s">
-        <v>4039</v>
+        <v>4038</v>
       </c>
       <c r="K1402">
         <v>1403</v>
@@ -71619,7 +71660,7 @@
         <v>857</v>
       </c>
       <c r="N1402" t="s">
-        <v>4057</v>
+        <v>4056</v>
       </c>
     </row>
     <row r="1403" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71630,13 +71671,13 @@
         <v>2745915</v>
       </c>
       <c r="C1403" t="s">
-        <v>4044</v>
+        <v>4043</v>
       </c>
       <c r="D1403" t="s">
         <v>489</v>
       </c>
       <c r="E1403" t="s">
-        <v>4027</v>
+        <v>4026</v>
       </c>
       <c r="F1403" s="29">
         <v>44582</v>
@@ -71651,7 +71692,7 @@
         <v>816</v>
       </c>
       <c r="J1403" s="63" t="s">
-        <v>4042</v>
+        <v>4041</v>
       </c>
       <c r="K1403">
         <v>1404</v>
@@ -71660,7 +71701,7 @@
         <v>857</v>
       </c>
       <c r="N1403" t="s">
-        <v>4058</v>
+        <v>4057</v>
       </c>
     </row>
     <row r="1404" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71677,7 +71718,7 @@
         <v>76</v>
       </c>
       <c r="E1404" t="s">
-        <v>4027</v>
+        <v>4026</v>
       </c>
       <c r="F1404" s="29">
         <v>46142</v>
@@ -71692,7 +71733,7 @@
         <v>816</v>
       </c>
       <c r="J1404" s="63" t="s">
-        <v>4043</v>
+        <v>4042</v>
       </c>
       <c r="K1404">
         <v>1405</v>
@@ -71701,7 +71742,7 @@
         <v>857</v>
       </c>
       <c r="N1404" t="s">
-        <v>4059</v>
+        <v>4058</v>
       </c>
     </row>
     <row r="1405" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71712,13 +71753,13 @@
         <v>3379190</v>
       </c>
       <c r="C1405" t="s">
-        <v>4045</v>
+        <v>4044</v>
       </c>
       <c r="D1405" t="s">
         <v>489</v>
       </c>
       <c r="E1405" t="s">
-        <v>4027</v>
+        <v>4026</v>
       </c>
       <c r="F1405" s="29">
         <v>44590</v>
@@ -71733,7 +71774,7 @@
         <v>816</v>
       </c>
       <c r="J1405" s="63" t="s">
-        <v>4046</v>
+        <v>4045</v>
       </c>
       <c r="K1405">
         <v>1406</v>
@@ -71742,7 +71783,7 @@
         <v>857</v>
       </c>
       <c r="N1405" t="s">
-        <v>4060</v>
+        <v>4059</v>
       </c>
     </row>
     <row r="1406" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71774,7 +71815,7 @@
         <v>816</v>
       </c>
       <c r="J1406" s="63" t="s">
-        <v>4047</v>
+        <v>4046</v>
       </c>
       <c r="K1406">
         <v>1407</v>
@@ -71783,7 +71824,7 @@
         <v>857</v>
       </c>
       <c r="N1406" t="s">
-        <v>4061</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="1407" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71800,7 +71841,7 @@
         <v>489</v>
       </c>
       <c r="E1407" t="s">
-        <v>4027</v>
+        <v>4026</v>
       </c>
       <c r="F1407" s="29">
         <v>44680</v>
@@ -71815,7 +71856,7 @@
         <v>816</v>
       </c>
       <c r="J1407" s="63" t="s">
-        <v>4048</v>
+        <v>4047</v>
       </c>
       <c r="K1407">
         <v>1408</v>
@@ -71824,7 +71865,171 @@
         <v>857</v>
       </c>
       <c r="N1407" t="s">
+        <v>4061</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1408">
+        <v>66</v>
+      </c>
+      <c r="B1408" s="7">
+        <v>54137910</v>
+      </c>
+      <c r="C1408" t="s">
+        <v>4063</v>
+      </c>
+      <c r="D1408" t="s">
+        <v>426</v>
+      </c>
+      <c r="E1408" t="s">
+        <v>722</v>
+      </c>
+      <c r="F1408" s="29">
+        <v>46110</v>
+      </c>
+      <c r="G1408" s="56">
+        <v>0.24459490740740741</v>
+      </c>
+      <c r="H1408" s="151" t="s">
+        <v>818</v>
+      </c>
+      <c r="I1408" s="151" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1408" s="63" t="s">
         <v>4062</v>
+      </c>
+      <c r="K1408">
+        <v>1409</v>
+      </c>
+      <c r="M1408" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1408" t="s">
+        <v>4068</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1409">
+        <v>66</v>
+      </c>
+      <c r="B1409" s="7">
+        <v>4901310</v>
+      </c>
+      <c r="C1409" t="s">
+        <v>236</v>
+      </c>
+      <c r="D1409" t="s">
+        <v>374</v>
+      </c>
+      <c r="E1409" t="s">
+        <v>236</v>
+      </c>
+      <c r="F1409" s="29">
+        <v>46128</v>
+      </c>
+      <c r="G1409" s="56">
+        <v>6.7835648148148145E-2</v>
+      </c>
+      <c r="H1409" s="151" t="s">
+        <v>1391</v>
+      </c>
+      <c r="I1409" s="151" t="s">
+        <v>292</v>
+      </c>
+      <c r="J1409" s="63" t="s">
+        <v>4065</v>
+      </c>
+      <c r="K1409">
+        <v>1410</v>
+      </c>
+      <c r="M1409" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1409" t="s">
+        <v>4069</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1410">
+        <v>66</v>
+      </c>
+      <c r="B1410" s="7">
+        <v>11211012</v>
+      </c>
+      <c r="C1410" t="s">
+        <v>490</v>
+      </c>
+      <c r="D1410" t="s">
+        <v>279</v>
+      </c>
+      <c r="E1410" t="s">
+        <v>490</v>
+      </c>
+      <c r="F1410" s="29">
+        <v>45685</v>
+      </c>
+      <c r="G1410" s="56">
+        <v>0.10422453703703705</v>
+      </c>
+      <c r="H1410" s="151" t="s">
+        <v>4066</v>
+      </c>
+      <c r="I1410" s="151" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1410" s="63" t="s">
+        <v>4067</v>
+      </c>
+      <c r="K1410">
+        <v>1411</v>
+      </c>
+      <c r="M1410" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1410" t="s">
+        <v>4070</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1411">
+        <v>66</v>
+      </c>
+      <c r="B1411" s="7">
+        <v>11246243</v>
+      </c>
+      <c r="C1411" t="s">
+        <v>490</v>
+      </c>
+      <c r="D1411" t="s">
+        <v>426</v>
+      </c>
+      <c r="E1411" t="s">
+        <v>490</v>
+      </c>
+      <c r="F1411" s="29">
+        <v>45649</v>
+      </c>
+      <c r="G1411" s="56">
+        <v>9.4386574074074081E-2</v>
+      </c>
+      <c r="H1411" s="151" t="s">
+        <v>4072</v>
+      </c>
+      <c r="I1411" s="151" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1411" s="63" t="s">
+        <v>4071</v>
+      </c>
+      <c r="K1411">
+        <v>1412</v>
+      </c>
+      <c r="M1411" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1411" t="s">
+        <v>4073</v>
       </c>
     </row>
   </sheetData>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11696" uniqueCount="4074">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11704" uniqueCount="4076">
   <si>
     <t>Ņ</t>
   </si>
@@ -12249,6 +12249,12 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1494594362443698286/id_WE.png?ex=69e32cf8&amp;is=69e1db78&amp;hm=8f2623622210c6789379d3dced64784b05736a8ebbade9bdd077a9a70e2c5fa5</t>
+  </si>
+  <si>
+    <t>WF</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1494671590963806289/id_WF.png?ex=69e374e4&amp;is=69e22364&amp;hm=68c4f015b0605bb3fd026d0be5d6b01d8e1dd5047d8b854b8bc865e5a28a3ff4</t>
   </si>
 </sst>
 </file>
@@ -12260,11 +12266,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="101" x14ac:knownFonts="1">
+  <fonts count="102" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -13000,118 +13013,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="152">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="98" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="82" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="97" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="81" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="96" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="88" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="82" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="89" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="83" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="66" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="66" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="66" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="66" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="62" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="62" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="65" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="66" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="59" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="59" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13120,18 +13134,18 @@
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="35" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="36" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13145,15 +13159,15 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13385,7 +13399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1411"/>
+  <dimension ref="A1:O1412"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -71721,7 +71735,7 @@
         <v>4026</v>
       </c>
       <c r="F1404" s="29">
-        <v>46142</v>
+        <v>44681</v>
       </c>
       <c r="G1404" s="56">
         <v>7.2013888888888891E-2</v>
@@ -72030,6 +72044,47 @@
       </c>
       <c r="N1411" t="s">
         <v>4073</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1412">
+        <v>66</v>
+      </c>
+      <c r="B1412" s="7">
+        <v>5735961</v>
+      </c>
+      <c r="C1412" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1412" t="s">
+        <v>278</v>
+      </c>
+      <c r="E1412" t="s">
+        <v>650</v>
+      </c>
+      <c r="F1412" s="29">
+        <v>46126</v>
+      </c>
+      <c r="G1412" s="56">
+        <v>7.0405092592592589E-2</v>
+      </c>
+      <c r="H1412" s="152" t="s">
+        <v>818</v>
+      </c>
+      <c r="I1412" s="152" t="s">
+        <v>292</v>
+      </c>
+      <c r="J1412" s="63" t="s">
+        <v>4074</v>
+      </c>
+      <c r="K1412">
+        <v>1413</v>
+      </c>
+      <c r="M1412" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1412" t="s">
+        <v>4075</v>
       </c>
     </row>
   </sheetData>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11704" uniqueCount="4076">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11728" uniqueCount="4085">
   <si>
     <t>Ņ</t>
   </si>
@@ -12255,6 +12255,33 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1494671590963806289/id_WF.png?ex=69e374e4&amp;is=69e22364&amp;hm=68c4f015b0605bb3fd026d0be5d6b01d8e1dd5047d8b854b8bc865e5a28a3ff4</t>
+  </si>
+  <si>
+    <t>Försöker, försöker&lt;3</t>
+  </si>
+  <si>
+    <t>Armsman</t>
+  </si>
+  <si>
+    <t>WG</t>
+  </si>
+  <si>
+    <t>WH</t>
+  </si>
+  <si>
+    <t>WI</t>
+  </si>
+  <si>
+    <t>[] Directional Strike</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1494939288846995557/id_WG.png?ex=69e46e35&amp;is=69e31cb5&amp;hm=a769acc2ad1ff52700c13e87bd5570886153f2e591925897419af5a2bac288a1</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1494939337031155772/id_WH.jpg?ex=69e46e40&amp;is=69e31cc0&amp;hm=f405f028b86282b585a315f887f24842df1cdeb3bd0cfb677adde06fb54346f5</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1494939400247705622/id_WI.png?ex=69e46e4f&amp;is=69e31ccf&amp;hm=d5cf6383e760e08b62722055c81d249694da31a1590cac4d7c66e9323081ee67</t>
   </si>
 </sst>
 </file>
@@ -12266,11 +12293,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="102" x14ac:knownFonts="1">
+  <fonts count="103" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -13013,118 +13047,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="99" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="83" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="98" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="82" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="97" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="89" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="83" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="90" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="84" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="67" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="67" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="66" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="66" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="67" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="66" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="67" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="66" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="66" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="62" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="59" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="59" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13133,18 +13168,18 @@
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="36" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="37" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13158,15 +13193,15 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13399,7 +13434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1412"/>
+  <dimension ref="A1:O1415"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -31685,8 +31720,8 @@
       <c r="H432" t="s">
         <v>838</v>
       </c>
-      <c r="I432" s="104" t="s">
-        <v>292</v>
+      <c r="I432" s="153" t="s">
+        <v>809</v>
       </c>
       <c r="J432" s="63" t="s">
         <v>1800</v>
@@ -34879,8 +34914,8 @@
       <c r="H509" t="s">
         <v>833</v>
       </c>
-      <c r="I509" s="104" t="s">
-        <v>292</v>
+      <c r="I509" s="153" t="s">
+        <v>809</v>
       </c>
       <c r="J509" s="63" t="s">
         <v>1977</v>
@@ -72085,6 +72120,129 @@
       </c>
       <c r="N1412" t="s">
         <v>4075</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1413">
+        <v>67</v>
+      </c>
+      <c r="B1413" s="7">
+        <v>7693476</v>
+      </c>
+      <c r="C1413" t="s">
+        <v>4076</v>
+      </c>
+      <c r="D1413" t="s">
+        <v>4077</v>
+      </c>
+      <c r="E1413" t="s">
+        <v>650</v>
+      </c>
+      <c r="F1413" s="29">
+        <v>46129</v>
+      </c>
+      <c r="G1413" s="56">
+        <v>0.10199074074074073</v>
+      </c>
+      <c r="H1413" s="153" t="s">
+        <v>817</v>
+      </c>
+      <c r="I1413" s="153" t="s">
+        <v>292</v>
+      </c>
+      <c r="J1413" s="63" t="s">
+        <v>4078</v>
+      </c>
+      <c r="K1413">
+        <v>1414</v>
+      </c>
+      <c r="M1413" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1413" t="s">
+        <v>4082</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1414">
+        <v>67</v>
+      </c>
+      <c r="B1414" s="7">
+        <v>30007279</v>
+      </c>
+      <c r="C1414" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1414" t="s">
+        <v>1723</v>
+      </c>
+      <c r="E1414" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1414" s="29">
+        <v>46129</v>
+      </c>
+      <c r="G1414" s="56">
+        <v>0.25377314814814816</v>
+      </c>
+      <c r="H1414" s="153" t="s">
+        <v>1357</v>
+      </c>
+      <c r="I1414" s="153" t="s">
+        <v>292</v>
+      </c>
+      <c r="J1414" s="63" t="s">
+        <v>4079</v>
+      </c>
+      <c r="K1414">
+        <v>1415</v>
+      </c>
+      <c r="M1414" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1414" t="s">
+        <v>4083</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1415">
+        <v>67</v>
+      </c>
+      <c r="B1415" s="7">
+        <v>13091775</v>
+      </c>
+      <c r="C1415" t="s">
+        <v>4081</v>
+      </c>
+      <c r="D1415" t="s">
+        <v>3913</v>
+      </c>
+      <c r="E1415" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1415" s="29">
+        <v>46129</v>
+      </c>
+      <c r="G1415" s="56">
+        <v>0.14434027777777778</v>
+      </c>
+      <c r="H1415" s="153" t="s">
+        <v>808</v>
+      </c>
+      <c r="I1415" s="153" t="s">
+        <v>292</v>
+      </c>
+      <c r="J1415" s="63" t="s">
+        <v>4080</v>
+      </c>
+      <c r="K1415">
+        <v>1416</v>
+      </c>
+      <c r="M1415" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1415" t="s">
+        <v>4084</v>
       </c>
     </row>
   </sheetData>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11728" uniqueCount="4085">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11788" uniqueCount="4105">
   <si>
     <t>Ņ</t>
   </si>
@@ -12282,6 +12282,66 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1494939400247705622/id_WI.png?ex=69e46e4f&amp;is=69e31ccf&amp;hm=d5cf6383e760e08b62722055c81d249694da31a1590cac4d7c66e9323081ee67</t>
+  </si>
+  <si>
+    <t>WJ</t>
+  </si>
+  <si>
+    <t>WK</t>
+  </si>
+  <si>
+    <t>ια</t>
+  </si>
+  <si>
+    <t>from basic</t>
+  </si>
+  <si>
+    <t>,</t>
+  </si>
+  <si>
+    <t>ia</t>
+  </si>
+  <si>
+    <t>WL</t>
+  </si>
+  <si>
+    <t>RAmPER</t>
+  </si>
+  <si>
+    <t>Ramper</t>
+  </si>
+  <si>
+    <t>WM</t>
+  </si>
+  <si>
+    <t>WN</t>
+  </si>
+  <si>
+    <t>WO</t>
+  </si>
+  <si>
+    <t>WP</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1496044272070295592/id_WJ.png?ex=69e8734d&amp;is=69e721cd&amp;hm=f51e3da401d95e75c5ef0067cc4ca7970476c75e5d8f268dff394ac1fe7826ac</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1496044325774299246/id_WK.png?ex=69e8735a&amp;is=69e721da&amp;hm=b3532be41a44c3e80e8350250923991a2654f30f1223c46960d66e3dbdc37486</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1496044372322554019/id_WL.png?ex=69e87365&amp;is=69e721e5&amp;hm=cdbff7aa0ce800b3eedb837ae6dbb8df703cc7e50565a27eda1d1dd334ac13ab</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1496044420045471805/id_WM.png?ex=69e87370&amp;is=69e721f0&amp;hm=1a4c7843c81b0e95ac92bdf66389b37da98468c9ba3102ae5cc81ed6162f821b</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1496044462391037973/id_WN.jpg?ex=69e8737a&amp;is=69e721fa&amp;hm=f4dbb605f5ceb1f194f06f3df5c38d484e9eeaa5f29fff9ec9c8485477b6e6cb</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1496044502954151976/id_WO.png?ex=69e87384&amp;is=69e72204&amp;hm=294a02076d5497ca965b5cd0f1d1cfc5420c0601d9f104c1f964c3632b017cb9</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1496044546713325598/id_WP.jpg?ex=69e8738f&amp;is=69e7220f&amp;hm=84ad0018fe279f035265ab77669f61de5001d9e9bfcaac7498ced150e6ff71a2</t>
   </si>
 </sst>
 </file>
@@ -12293,11 +12353,25 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="103" x14ac:knownFonts="1">
+  <fonts count="105" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -13047,118 +13121,120 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="156">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="101" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="85" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="100" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="92" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="86" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="99" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="83" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="98" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="90" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="84" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="82" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="69" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="69" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="69" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="67" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="67" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="69" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="67" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="67" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="66" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="66" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="69" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="62" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="62" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13166,19 +13242,19 @@
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="37" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="39" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13191,16 +13267,16 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13434,7 +13510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1415"/>
+  <dimension ref="A1:O1422"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -72238,11 +72314,307 @@
       <c r="K1415">
         <v>1416</v>
       </c>
+      <c r="L1415" t="s">
+        <v>4088</v>
+      </c>
       <c r="M1415" s="57" t="s">
         <v>857</v>
       </c>
       <c r="N1415" t="s">
         <v>4084</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1416">
+        <v>68</v>
+      </c>
+      <c r="B1416" s="7">
+        <v>5054515</v>
+      </c>
+      <c r="C1416" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1416" t="s">
+        <v>3908</v>
+      </c>
+      <c r="E1416" t="s">
+        <v>650</v>
+      </c>
+      <c r="F1416" s="29">
+        <v>46131</v>
+      </c>
+      <c r="G1416" s="56">
+        <v>8.8391203703703694E-2</v>
+      </c>
+      <c r="H1416" s="154" t="s">
+        <v>818</v>
+      </c>
+      <c r="I1416" s="154" t="s">
+        <v>292</v>
+      </c>
+      <c r="J1416" s="63" t="s">
+        <v>4085</v>
+      </c>
+      <c r="K1416">
+        <v>1417</v>
+      </c>
+      <c r="M1416" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1416" t="s">
+        <v>4098</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1417">
+        <v>68</v>
+      </c>
+      <c r="B1417" s="7">
+        <v>11466215</v>
+      </c>
+      <c r="C1417" t="s">
+        <v>4089</v>
+      </c>
+      <c r="D1417" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1417" t="s">
+        <v>4090</v>
+      </c>
+      <c r="F1417" s="29">
+        <v>44658</v>
+      </c>
+      <c r="G1417" s="56">
+        <v>5.486111111111111E-2</v>
+      </c>
+      <c r="H1417" s="155" t="s">
+        <v>820</v>
+      </c>
+      <c r="I1417" s="155" t="s">
+        <v>816</v>
+      </c>
+      <c r="J1417" s="63" t="s">
+        <v>4086</v>
+      </c>
+      <c r="K1417">
+        <v>1418</v>
+      </c>
+      <c r="L1417" t="s">
+        <v>4087</v>
+      </c>
+      <c r="M1417" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1417" t="s">
+        <v>4099</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1418">
+        <v>68</v>
+      </c>
+      <c r="B1418" s="7">
+        <v>3883470</v>
+      </c>
+      <c r="C1418" t="s">
+        <v>4089</v>
+      </c>
+      <c r="D1418" t="s">
+        <v>203</v>
+      </c>
+      <c r="E1418" t="s">
+        <v>4090</v>
+      </c>
+      <c r="F1418" s="29">
+        <v>44665</v>
+      </c>
+      <c r="G1418" s="56">
+        <v>3.8124999999999999E-2</v>
+      </c>
+      <c r="H1418" s="155" t="s">
+        <v>808</v>
+      </c>
+      <c r="I1418" s="155" t="s">
+        <v>292</v>
+      </c>
+      <c r="J1418" s="63" t="s">
+        <v>4091</v>
+      </c>
+      <c r="K1418">
+        <v>1419</v>
+      </c>
+      <c r="L1418" t="s">
+        <v>4087</v>
+      </c>
+      <c r="M1418" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1418" t="s">
+        <v>4100</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1419">
+        <v>69</v>
+      </c>
+      <c r="B1419" s="7">
+        <v>9895396</v>
+      </c>
+      <c r="C1419" t="s">
+        <v>4092</v>
+      </c>
+      <c r="D1419" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1419" t="s">
+        <v>4093</v>
+      </c>
+      <c r="F1419" s="29">
+        <v>44675</v>
+      </c>
+      <c r="G1419" s="56" t="s">
+        <v>504</v>
+      </c>
+      <c r="H1419" s="155" t="s">
+        <v>504</v>
+      </c>
+      <c r="I1419" s="155" t="s">
+        <v>816</v>
+      </c>
+      <c r="J1419" s="63" t="s">
+        <v>4094</v>
+      </c>
+      <c r="K1419">
+        <v>1420</v>
+      </c>
+      <c r="M1419" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1419" t="s">
+        <v>4101</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1420">
+        <v>69</v>
+      </c>
+      <c r="B1420" s="7">
+        <v>3177318</v>
+      </c>
+      <c r="C1420" t="s">
+        <v>490</v>
+      </c>
+      <c r="D1420" t="s">
+        <v>3913</v>
+      </c>
+      <c r="E1420" t="s">
+        <v>490</v>
+      </c>
+      <c r="F1420" s="29">
+        <v>45015</v>
+      </c>
+      <c r="G1420" s="56">
+        <v>9.673611111111112E-2</v>
+      </c>
+      <c r="H1420" s="155" t="s">
+        <v>945</v>
+      </c>
+      <c r="I1420" s="155" t="s">
+        <v>816</v>
+      </c>
+      <c r="J1420" s="63" t="s">
+        <v>4095</v>
+      </c>
+      <c r="K1420">
+        <v>1421</v>
+      </c>
+      <c r="M1420" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1420" t="s">
+        <v>4102</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1421">
+        <v>69</v>
+      </c>
+      <c r="B1421" s="7">
+        <v>3430484</v>
+      </c>
+      <c r="C1421" t="s">
+        <v>490</v>
+      </c>
+      <c r="D1421" t="s">
+        <v>374</v>
+      </c>
+      <c r="E1421" t="s">
+        <v>490</v>
+      </c>
+      <c r="F1421" s="29">
+        <v>45516</v>
+      </c>
+      <c r="G1421" s="56">
+        <v>6.4826388888888892E-2</v>
+      </c>
+      <c r="H1421" s="155" t="s">
+        <v>838</v>
+      </c>
+      <c r="I1421" s="155" t="s">
+        <v>292</v>
+      </c>
+      <c r="J1421" s="63" t="s">
+        <v>4096</v>
+      </c>
+      <c r="K1421">
+        <v>1422</v>
+      </c>
+      <c r="M1421" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1421" t="s">
+        <v>4103</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1422">
+        <v>69</v>
+      </c>
+      <c r="B1422" s="7">
+        <v>12407653</v>
+      </c>
+      <c r="C1422" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1422" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1422" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1422" s="29">
+        <v>45875</v>
+      </c>
+      <c r="G1422" s="56">
+        <v>5.8136574074074077E-2</v>
+      </c>
+      <c r="H1422" s="155" t="s">
+        <v>808</v>
+      </c>
+      <c r="I1422" s="155" t="s">
+        <v>809</v>
+      </c>
+      <c r="J1422" s="63" t="s">
+        <v>4097</v>
+      </c>
+      <c r="K1422">
+        <v>1423</v>
+      </c>
+      <c r="M1422" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1422" t="s">
+        <v>4104</v>
       </c>
     </row>
   </sheetData>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11788" uniqueCount="4105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11801" uniqueCount="4109">
   <si>
     <t>Ņ</t>
   </si>
@@ -12342,6 +12342,18 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1496044546713325598/id_WP.jpg?ex=69e8738f&amp;is=69e7220f&amp;hm=84ad0018fe279f035265ab77669f61de5001d9e9bfcaac7498ced150e6ff71a2</t>
+  </si>
+  <si>
+    <t>Disconect</t>
+  </si>
+  <si>
+    <t>WQ</t>
+  </si>
+  <si>
+    <t>WR</t>
+  </si>
+  <si>
+    <t>Ragnarok/Nest Keeper/Kronos</t>
   </si>
 </sst>
 </file>
@@ -12353,11 +12365,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="105" x14ac:knownFonts="1">
+  <fonts count="106" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -13121,118 +13140,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="156">
+  <cellXfs count="157">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="102" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="86" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="101" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="85" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="100" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="92" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="86" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="93" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="87" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="83" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="82" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="70" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="70" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="69" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="69" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="70" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="69" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="70" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="69" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="66" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="66" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="67" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="67" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="69" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="62" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="62" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13241,18 +13261,18 @@
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="39" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="40" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13266,15 +13286,15 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13510,7 +13530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1422"/>
+  <dimension ref="A1:O1424"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -72617,6 +72637,76 @@
         <v>4104</v>
       </c>
     </row>
+    <row r="1423" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1423">
+        <v>70</v>
+      </c>
+      <c r="B1423" s="7">
+        <v>24906950</v>
+      </c>
+      <c r="C1423" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1423" t="s">
+        <v>315</v>
+      </c>
+      <c r="E1423" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1423" s="29">
+        <v>46135</v>
+      </c>
+      <c r="G1423" s="56" t="s">
+        <v>504</v>
+      </c>
+      <c r="H1423" s="156" t="s">
+        <v>4105</v>
+      </c>
+      <c r="I1423" s="156" t="s">
+        <v>809</v>
+      </c>
+      <c r="K1423">
+        <v>1424</v>
+      </c>
+      <c r="L1423" s="63" t="s">
+        <v>4106</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1424">
+        <v>70</v>
+      </c>
+      <c r="B1424" s="7">
+        <v>13265551</v>
+      </c>
+      <c r="C1424" t="s">
+        <v>1107</v>
+      </c>
+      <c r="D1424" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1424" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1424" s="29">
+        <v>46135</v>
+      </c>
+      <c r="G1424" s="56">
+        <v>9.1712962962962954E-2</v>
+      </c>
+      <c r="H1424" s="156" t="s">
+        <v>4108</v>
+      </c>
+      <c r="I1424" s="156" t="s">
+        <v>809</v>
+      </c>
+      <c r="K1424">
+        <v>1425</v>
+      </c>
+      <c r="L1424" s="63" t="s">
+        <v>4107</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N1">
     <sortState ref="A2:N1357">

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11801" uniqueCount="4109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11821" uniqueCount="4115">
   <si>
     <t>Ņ</t>
   </si>
@@ -12354,6 +12354,24 @@
   </si>
   <si>
     <t>Ragnarok/Nest Keeper/Kronos</t>
+  </si>
+  <si>
+    <t>WS</t>
+  </si>
+  <si>
+    <t>WT</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1497496961790771251/id_WQ.jpg?ex=69edbc39&amp;is=69ec6ab9&amp;hm=d60ebcf7489603e47ef549b4e9c4c3b142004c6130f513353be18dcda8f30720</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1497497045903343777/id_WR.png?ex=69edbc4d&amp;is=69ec6acd&amp;hm=8084d5e2511264da8530ea084928c5735a0684353820dc7c244f99a06a7ecd9d</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1497497104233267260/id_WS.png?ex=69edbc5b&amp;is=69ec6adb&amp;hm=749c286aa9debec4848e4208aa68d5c2570053034cd5c33ed775a425301cf687</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1497497152803311646/id_WT.png?ex=69edbc67&amp;is=69ec6ae7&amp;hm=517cb721ab80af60c08d8f5dc0d89fbaec62e46060ae6b968b2cee05b1251ee4</t>
   </si>
 </sst>
 </file>
@@ -12365,11 +12383,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="106" x14ac:knownFonts="1">
+  <fonts count="107" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -13140,118 +13165,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="157">
+  <cellXfs count="158">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="103" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="87" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="102" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="86" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="101" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="93" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="87" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="94" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="88" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="84" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="83" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="71" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="71" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="70" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="70" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="71" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="70" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="71" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="70" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="67" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="67" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="68" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="68" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="71" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="66" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13260,18 +13286,18 @@
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="40" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="41" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13285,15 +13311,15 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13530,7 +13556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1424"/>
+  <dimension ref="A1:O1426"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -72671,6 +72697,12 @@
       <c r="L1423" s="63" t="s">
         <v>4106</v>
       </c>
+      <c r="M1423" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1423" t="s">
+        <v>4111</v>
+      </c>
     </row>
     <row r="1424" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1424">
@@ -72705,6 +72737,94 @@
       </c>
       <c r="L1424" s="63" t="s">
         <v>4107</v>
+      </c>
+      <c r="M1424" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1424" t="s">
+        <v>4112</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1425">
+        <v>71</v>
+      </c>
+      <c r="B1425" s="7">
+        <v>10146360</v>
+      </c>
+      <c r="C1425" t="s">
+        <v>3714</v>
+      </c>
+      <c r="D1425" t="s">
+        <v>395</v>
+      </c>
+      <c r="E1425" t="s">
+        <v>236</v>
+      </c>
+      <c r="F1425" s="29">
+        <v>46135</v>
+      </c>
+      <c r="G1425" s="56">
+        <v>0.13195601851851851</v>
+      </c>
+      <c r="H1425" s="157" t="s">
+        <v>814</v>
+      </c>
+      <c r="I1425" s="157" t="s">
+        <v>809</v>
+      </c>
+      <c r="K1425">
+        <v>1426</v>
+      </c>
+      <c r="L1425" t="s">
+        <v>4109</v>
+      </c>
+      <c r="M1425" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1425" t="s">
+        <v>4113</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1426">
+        <v>71</v>
+      </c>
+      <c r="B1426" s="7">
+        <v>6340676</v>
+      </c>
+      <c r="C1426" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1426" t="s">
+        <v>172</v>
+      </c>
+      <c r="E1426" t="s">
+        <v>236</v>
+      </c>
+      <c r="F1426" s="29">
+        <v>46136</v>
+      </c>
+      <c r="G1426" s="56">
+        <v>6.9930555555555551E-2</v>
+      </c>
+      <c r="H1426" s="157" t="s">
+        <v>838</v>
+      </c>
+      <c r="I1426" s="157" t="s">
+        <v>809</v>
+      </c>
+      <c r="K1426">
+        <v>1427</v>
+      </c>
+      <c r="L1426" t="s">
+        <v>4110</v>
+      </c>
+      <c r="M1426" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1426" t="s">
+        <v>4114</v>
       </c>
     </row>
   </sheetData>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11821" uniqueCount="4115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11846" uniqueCount="4121">
   <si>
     <t>Ņ</t>
   </si>
@@ -12372,6 +12372,24 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1497497152803311646/id_WT.png?ex=69edbc67&amp;is=69ec6ae7&amp;hm=517cb721ab80af60c08d8f5dc0d89fbaec62e46060ae6b968b2cee05b1251ee4</t>
+  </si>
+  <si>
+    <t>WU</t>
+  </si>
+  <si>
+    <t>WV</t>
+  </si>
+  <si>
+    <t>WW</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1497542505619783870/id_WU.jpg?ex=69ede6a4&amp;is=69ec9524&amp;hm=04cc0572f4c6559993afd51e2f3466d48c4dcd65b15c9e732196a6701c115e87</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1497542567829569618/id_WV.png?ex=69ede6b3&amp;is=69ec9533&amp;hm=8a6137d638011a88924c9440c8d25c29b443195cf4298d5fdce056f89c070991</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1497542610347229276/id_WW.png?ex=69ede6bd&amp;is=69ec953d&amp;hm=05a193a38e5390ce82274ff705044ae45984fda30c2521575a22a283555b149d</t>
   </si>
 </sst>
 </file>
@@ -12383,11 +12401,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="107" x14ac:knownFonts="1">
+  <fonts count="108" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -13165,118 +13190,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="158">
+  <cellXfs count="159">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="104" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="88" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="103" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="87" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="102" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="94" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="88" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="95" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="89" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="85" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="84" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="72" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="72" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="71" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="71" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="72" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="71" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="72" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="71" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="68" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="68" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="69" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="69" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="71" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="72" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="67" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="66" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13285,18 +13311,18 @@
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="41" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="42" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13310,15 +13336,15 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13556,7 +13582,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1426"/>
+  <dimension ref="A1:O1429"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -72691,11 +72717,11 @@
       <c r="I1423" s="156" t="s">
         <v>809</v>
       </c>
+      <c r="J1423" s="63" t="s">
+        <v>4106</v>
+      </c>
       <c r="K1423">
         <v>1424</v>
-      </c>
-      <c r="L1423" s="63" t="s">
-        <v>4106</v>
       </c>
       <c r="M1423" s="57" t="s">
         <v>857</v>
@@ -72732,11 +72758,11 @@
       <c r="I1424" s="156" t="s">
         <v>809</v>
       </c>
+      <c r="J1424" s="63" t="s">
+        <v>4107</v>
+      </c>
       <c r="K1424">
         <v>1425</v>
-      </c>
-      <c r="L1424" s="63" t="s">
-        <v>4107</v>
       </c>
       <c r="M1424" s="57" t="s">
         <v>857</v>
@@ -72773,11 +72799,11 @@
       <c r="I1425" s="157" t="s">
         <v>809</v>
       </c>
+      <c r="J1425" t="s">
+        <v>4109</v>
+      </c>
       <c r="K1425">
         <v>1426</v>
-      </c>
-      <c r="L1425" t="s">
-        <v>4109</v>
       </c>
       <c r="M1425" s="57" t="s">
         <v>857</v>
@@ -72814,17 +72840,140 @@
       <c r="I1426" s="157" t="s">
         <v>809</v>
       </c>
+      <c r="J1426" t="s">
+        <v>4110</v>
+      </c>
       <c r="K1426">
         <v>1427</v>
       </c>
-      <c r="L1426" t="s">
-        <v>4110</v>
-      </c>
       <c r="M1426" s="57" t="s">
         <v>857</v>
       </c>
       <c r="N1426" t="s">
         <v>4114</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1427">
+        <v>71</v>
+      </c>
+      <c r="B1427" s="7">
+        <v>7756507</v>
+      </c>
+      <c r="C1427" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1427" t="s">
+        <v>458</v>
+      </c>
+      <c r="E1427" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1427" s="29">
+        <v>46137</v>
+      </c>
+      <c r="G1427" s="56">
+        <v>5.9282407407407402E-2</v>
+      </c>
+      <c r="H1427" s="158" t="s">
+        <v>1111</v>
+      </c>
+      <c r="I1427" s="158" t="s">
+        <v>292</v>
+      </c>
+      <c r="J1427" s="63" t="s">
+        <v>4115</v>
+      </c>
+      <c r="K1427">
+        <v>1428</v>
+      </c>
+      <c r="M1427" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1427" t="s">
+        <v>4118</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1428">
+        <v>71</v>
+      </c>
+      <c r="B1428" s="7">
+        <v>10009000</v>
+      </c>
+      <c r="C1428" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D1428" t="s">
+        <v>3921</v>
+      </c>
+      <c r="E1428" t="s">
+        <v>1477</v>
+      </c>
+      <c r="F1428" s="29">
+        <v>46137</v>
+      </c>
+      <c r="G1428" s="56" t="s">
+        <v>504</v>
+      </c>
+      <c r="H1428" s="158" t="s">
+        <v>504</v>
+      </c>
+      <c r="I1428" s="158" t="s">
+        <v>292</v>
+      </c>
+      <c r="J1428" s="63" t="s">
+        <v>4116</v>
+      </c>
+      <c r="K1428">
+        <v>1429</v>
+      </c>
+      <c r="M1428" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1428" t="s">
+        <v>4119</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1429">
+        <v>71</v>
+      </c>
+      <c r="B1429" s="7">
+        <v>11082827</v>
+      </c>
+      <c r="C1429" t="s">
+        <v>3714</v>
+      </c>
+      <c r="D1429" t="s">
+        <v>172</v>
+      </c>
+      <c r="E1429" t="s">
+        <v>236</v>
+      </c>
+      <c r="F1429" s="29">
+        <v>46137</v>
+      </c>
+      <c r="G1429" s="56">
+        <v>0.11660879629629629</v>
+      </c>
+      <c r="H1429" s="158" t="s">
+        <v>941</v>
+      </c>
+      <c r="I1429" s="158" t="s">
+        <v>292</v>
+      </c>
+      <c r="J1429" s="63" t="s">
+        <v>4117</v>
+      </c>
+      <c r="K1429">
+        <v>1430</v>
+      </c>
+      <c r="M1429" s="57" t="s">
+        <v>857</v>
+      </c>
+      <c r="N1429" t="s">
+        <v>4120</v>
       </c>
     </row>
   </sheetData>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -25005,7 +25005,7 @@
         <v>426</v>
       </c>
       <c r="E267" t="s">
-        <v>266</v>
+        <v>722</v>
       </c>
       <c r="F267" s="29">
         <v>45568</v>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11962" uniqueCount="4161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12045" uniqueCount="4184">
   <si>
     <t>Ņ</t>
   </si>
@@ -12491,9 +12491,6 @@
     <t>Wk</t>
   </si>
   <si>
-    <t>[o]</t>
-  </si>
-  <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1499685388426412092/id_Wg.png?ex=69f5b25b&amp;is=69f460db&amp;hm=8964f8f6a7a328767cba7113a29ac9a67b189839740cad36fe0076259dd569e0</t>
   </si>
   <si>
@@ -12510,6 +12507,78 @@
   </si>
   <si>
     <t>Find</t>
+  </si>
+  <si>
+    <t>;</t>
+  </si>
+  <si>
+    <t>Wl</t>
+  </si>
+  <si>
+    <t>Wm</t>
+  </si>
+  <si>
+    <t>Wn</t>
+  </si>
+  <si>
+    <t>Wo</t>
+  </si>
+  <si>
+    <t>Wp</t>
+  </si>
+  <si>
+    <t>Wq</t>
+  </si>
+  <si>
+    <t>Eternal . Permafrost</t>
+  </si>
+  <si>
+    <t>Wr</t>
+  </si>
+  <si>
+    <t>Ws</t>
+  </si>
+  <si>
+    <t>Delayer</t>
+  </si>
+  <si>
+    <t>Wt</t>
+  </si>
+  <si>
+    <t>タカ -v-</t>
+  </si>
+  <si>
+    <t>Wu</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1500111082436431932/id_Wl.png?ex=69f73ed0&amp;is=69f5ed50&amp;hm=e82e4138a828755e5ff89e3a03b13dbb7308fbc2ac85caa3abda758738143b76</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1500111140628336765/id_Wm.png?ex=69f73ede&amp;is=69f5ed5e&amp;hm=fd8b2285d20c872a4ba9b9a9e789da437c0e30c2216af3f99f00a2a586ac64f1</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1500111209008201758/id_Wn.png?ex=69f73eee&amp;is=69f5ed6e&amp;hm=3119b65e31ace6b15a73ad60f7dd79d62236750a1757abaeaf8839e5814c45ee</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1500111326964486175/id_Wo.png?ex=69f73f0b&amp;is=69f5ed8b&amp;hm=fcc4005fad67d4c47da624b970535304a25418d75fb09f0f45512160cbb9fccd</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1500111394702491658/id_Wp.jpg?ex=69f73f1b&amp;is=69f5ed9b&amp;hm=30bc9653a44994ca8372b56b77daa0aeac2a4359aedf26ae4f8b8a6c16b86370</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1500111472628338769/id_Wq.png?ex=69f73f2d&amp;is=69f5edad&amp;hm=0e4a40a68b3c29715ad21ec570c82fde9fd9a7669a8e35cc875589fca0aa7823</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1500111534762885181/id_Wr.png?ex=69f73f3c&amp;is=69f5edbc&amp;hm=e603dd109eb1b1e7c5a783a2d168df9aa92e77ff88ee9ae58e1258d1f0fe8a45</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1500111586247970958/id_Ws.jpg?ex=69f73f48&amp;is=69f5edc8&amp;hm=f97bb8409bab7fdfda74bcc1819a7ce6c20a02c0540e9250ab7aa015bcd3a1cf</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1500111628123902002/id_Wt.jpg?ex=69f73f52&amp;is=69f5edd2&amp;hm=54d7c52b864b1c9311f517ae0c6c171fb92763bf37f3fdfc5e01c943880a378e</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1500111686156423228/id_Wu.png?ex=69f73f60&amp;is=69f5ede0&amp;hm=d0b23df228f1fb17d4e3e7ece143eb847c4573e170ffda9909298192c0361083</t>
   </si>
 </sst>
 </file>
@@ -12521,11 +12590,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="110" x14ac:knownFonts="1">
+  <fonts count="111" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -13324,118 +13400,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="161">
+  <cellXfs count="162">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="107" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="91" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="106" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="90" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="105" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="97" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="91" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="98" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="92" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="88" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="87" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="75" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="75" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="74" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="74" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="75" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="74" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="75" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="74" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="71" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="71" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="72" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="72" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="74" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="75" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="70" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="69" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="68" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="68" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="67" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="67" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13444,18 +13521,18 @@
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="44" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="45" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13469,15 +13546,15 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13718,7 +13795,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1443"/>
+  <dimension ref="A1:O1453"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -28717,7 +28794,7 @@
         <v>15</v>
       </c>
       <c r="E353" t="s">
-        <v>4160</v>
+        <v>4159</v>
       </c>
       <c r="F353" s="29">
         <v>45647</v>
@@ -48622,7 +48699,7 @@
         <v>259</v>
       </c>
       <c r="E834" t="s">
-        <v>4160</v>
+        <v>4159</v>
       </c>
       <c r="F834" s="29">
         <v>46016</v>
@@ -73515,11 +73592,11 @@
       <c r="K1439">
         <v>1440</v>
       </c>
-      <c r="M1439" s="160" t="s">
+      <c r="M1439" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1439" t="s">
         <v>4154</v>
-      </c>
-      <c r="N1439" t="s">
-        <v>4155</v>
       </c>
     </row>
     <row r="1440" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73556,11 +73633,11 @@
       <c r="K1440">
         <v>1441</v>
       </c>
-      <c r="M1440" s="160" t="s">
-        <v>4154</v>
+      <c r="M1440" s="57" t="s">
+        <v>854</v>
       </c>
       <c r="N1440" t="s">
-        <v>4156</v>
+        <v>4155</v>
       </c>
     </row>
     <row r="1441" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73597,11 +73674,11 @@
       <c r="K1441">
         <v>1442</v>
       </c>
-      <c r="M1441" s="160" t="s">
-        <v>4154</v>
+      <c r="M1441" s="57" t="s">
+        <v>854</v>
       </c>
       <c r="N1441" t="s">
-        <v>4157</v>
+        <v>4156</v>
       </c>
     </row>
     <row r="1442" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73618,7 +73695,7 @@
         <v>40</v>
       </c>
       <c r="E1442" t="s">
-        <v>4160</v>
+        <v>4159</v>
       </c>
       <c r="F1442" s="29">
         <v>45875</v>
@@ -73638,11 +73715,11 @@
       <c r="K1442">
         <v>1443</v>
       </c>
-      <c r="M1442" s="160" t="s">
-        <v>4154</v>
+      <c r="M1442" s="57" t="s">
+        <v>854</v>
       </c>
       <c r="N1442" t="s">
-        <v>4158</v>
+        <v>4157</v>
       </c>
     </row>
     <row r="1443" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73679,11 +73756,418 @@
       <c r="K1443">
         <v>1444</v>
       </c>
-      <c r="M1443" s="160" t="s">
-        <v>4154</v>
+      <c r="M1443" s="57" t="s">
+        <v>854</v>
       </c>
       <c r="N1443" t="s">
-        <v>4159</v>
+        <v>4158</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1444">
+        <v>74</v>
+      </c>
+      <c r="B1444" s="7">
+        <v>22630000</v>
+      </c>
+      <c r="C1444" t="s">
+        <v>4160</v>
+      </c>
+      <c r="D1444" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1444" t="s">
+        <v>4160</v>
+      </c>
+      <c r="F1444" s="29">
+        <v>46144</v>
+      </c>
+      <c r="G1444" s="56" t="s">
+        <v>502</v>
+      </c>
+      <c r="H1444" s="161" t="s">
+        <v>2031</v>
+      </c>
+      <c r="I1444" s="161" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1444" s="63" t="s">
+        <v>4161</v>
+      </c>
+      <c r="K1444">
+        <v>1445</v>
+      </c>
+      <c r="M1444" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1444" t="s">
+        <v>4174</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1445">
+        <v>74</v>
+      </c>
+      <c r="B1445" s="7">
+        <v>13895681</v>
+      </c>
+      <c r="C1445" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1445" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1445" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1445" s="29">
+        <v>46144</v>
+      </c>
+      <c r="H1445" s="161" t="s">
+        <v>2031</v>
+      </c>
+      <c r="I1445" s="161" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1445" s="63" t="s">
+        <v>4162</v>
+      </c>
+      <c r="K1445">
+        <v>1446</v>
+      </c>
+      <c r="M1445" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1445" t="s">
+        <v>4175</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1446">
+        <v>74</v>
+      </c>
+      <c r="B1446" s="7">
+        <v>7170844</v>
+      </c>
+      <c r="C1446" t="s">
+        <v>236</v>
+      </c>
+      <c r="D1446" t="s">
+        <v>171</v>
+      </c>
+      <c r="E1446" t="s">
+        <v>236</v>
+      </c>
+      <c r="F1446" s="29">
+        <v>46144</v>
+      </c>
+      <c r="G1446" s="56">
+        <v>7.3657407407407408E-2</v>
+      </c>
+      <c r="H1446" s="161" t="s">
+        <v>817</v>
+      </c>
+      <c r="I1446" s="161" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1446" s="63" t="s">
+        <v>4163</v>
+      </c>
+      <c r="K1446">
+        <v>1447</v>
+      </c>
+      <c r="M1446" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1446" t="s">
+        <v>4176</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1447">
+        <v>74</v>
+      </c>
+      <c r="B1447" s="7">
+        <v>13197466</v>
+      </c>
+      <c r="C1447" t="s">
+        <v>4167</v>
+      </c>
+      <c r="D1447" t="s">
+        <v>3718</v>
+      </c>
+      <c r="E1447" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1447" s="29">
+        <v>46144</v>
+      </c>
+      <c r="G1447" s="56">
+        <v>0.12055555555555557</v>
+      </c>
+      <c r="H1447" s="161" t="s">
+        <v>825</v>
+      </c>
+      <c r="I1447" s="161" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1447" s="63" t="s">
+        <v>4164</v>
+      </c>
+      <c r="K1447">
+        <v>1448</v>
+      </c>
+      <c r="M1447" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1447" t="s">
+        <v>4177</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1448">
+        <v>74</v>
+      </c>
+      <c r="B1448" s="7">
+        <v>7650000</v>
+      </c>
+      <c r="C1448" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1448" t="s">
+        <v>3828</v>
+      </c>
+      <c r="E1448" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1448" s="29">
+        <v>46144</v>
+      </c>
+      <c r="G1448" s="56">
+        <v>8.0532407407407414E-2</v>
+      </c>
+      <c r="H1448" s="161" t="s">
+        <v>833</v>
+      </c>
+      <c r="I1448" s="161" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1448" s="63" t="s">
+        <v>4165</v>
+      </c>
+      <c r="K1448">
+        <v>1449</v>
+      </c>
+      <c r="M1448" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1448" t="s">
+        <v>4178</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1449">
+        <v>74</v>
+      </c>
+      <c r="B1449" s="7">
+        <v>9164274</v>
+      </c>
+      <c r="C1449" t="s">
+        <v>4167</v>
+      </c>
+      <c r="D1449" t="s">
+        <v>3718</v>
+      </c>
+      <c r="E1449" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1449" s="29">
+        <v>46144</v>
+      </c>
+      <c r="G1449" s="56">
+        <v>8.1504629629629635E-2</v>
+      </c>
+      <c r="H1449" s="161" t="s">
+        <v>1239</v>
+      </c>
+      <c r="I1449" s="161" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1449" s="63" t="s">
+        <v>4166</v>
+      </c>
+      <c r="K1449">
+        <v>1450</v>
+      </c>
+      <c r="M1449" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1449" t="s">
+        <v>4179</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1450">
+        <v>74</v>
+      </c>
+      <c r="B1450" s="7">
+        <v>7516720</v>
+      </c>
+      <c r="C1450" t="s">
+        <v>4167</v>
+      </c>
+      <c r="D1450" t="s">
+        <v>3718</v>
+      </c>
+      <c r="E1450" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1450" s="29">
+        <v>46144</v>
+      </c>
+      <c r="G1450" s="56">
+        <v>4.4236111111111115E-2</v>
+      </c>
+      <c r="H1450" s="161" t="s">
+        <v>825</v>
+      </c>
+      <c r="I1450" s="161" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1450" s="63" t="s">
+        <v>4168</v>
+      </c>
+      <c r="K1450">
+        <v>1451</v>
+      </c>
+      <c r="M1450" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1450" t="s">
+        <v>4180</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1451">
+        <v>74</v>
+      </c>
+      <c r="B1451" s="7">
+        <v>9007528</v>
+      </c>
+      <c r="C1451" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1451" t="s">
+        <v>4170</v>
+      </c>
+      <c r="E1451" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1451" s="29">
+        <v>46144</v>
+      </c>
+      <c r="G1451" s="56" t="s">
+        <v>502</v>
+      </c>
+      <c r="H1451" s="161" t="s">
+        <v>2031</v>
+      </c>
+      <c r="I1451" s="161" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1451" s="63" t="s">
+        <v>4169</v>
+      </c>
+      <c r="K1451">
+        <v>1452</v>
+      </c>
+      <c r="M1451" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1451" t="s">
+        <v>4181</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1452">
+        <v>74</v>
+      </c>
+      <c r="B1452" s="7">
+        <v>5748956</v>
+      </c>
+      <c r="C1452" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1452" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1452" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1452" s="29">
+        <v>46144</v>
+      </c>
+      <c r="G1452" s="56">
+        <v>2.0474537037037038E-2</v>
+      </c>
+      <c r="H1452" s="161" t="s">
+        <v>835</v>
+      </c>
+      <c r="I1452" s="161" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1452" s="63" t="s">
+        <v>4171</v>
+      </c>
+      <c r="K1452">
+        <v>1453</v>
+      </c>
+      <c r="M1452" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1452" t="s">
+        <v>4182</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1453">
+        <v>74</v>
+      </c>
+      <c r="B1453" s="7">
+        <v>8740000</v>
+      </c>
+      <c r="C1453" t="s">
+        <v>4172</v>
+      </c>
+      <c r="D1453" t="s">
+        <v>330</v>
+      </c>
+      <c r="E1453" t="s">
+        <v>4172</v>
+      </c>
+      <c r="F1453" s="29">
+        <v>46144</v>
+      </c>
+      <c r="G1453" s="56" t="s">
+        <v>502</v>
+      </c>
+      <c r="H1453" s="161" t="s">
+        <v>502</v>
+      </c>
+      <c r="I1453" s="161" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1453" s="63" t="s">
+        <v>4173</v>
+      </c>
+      <c r="K1453">
+        <v>1454</v>
+      </c>
+      <c r="M1453" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1453" t="s">
+        <v>4183</v>
       </c>
     </row>
   </sheetData>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12045" uniqueCount="4184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12100" uniqueCount="4204">
   <si>
     <t>Ņ</t>
   </si>
@@ -10349,9 +10349,6 @@
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1477258987496931449/id_Sd.png?ex=69a41c24&amp;is=69a2caa4&amp;hm=f7d3d6c817ae202625ff5f03c91159ad1f2e0574a6f10be17a19a0c148fb5867</t>
   </si>
   <si>
-    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1477259062138896434/id_Se.png?ex=69a41c36&amp;is=69a2cab6&amp;hm=d1c79d4d760997781c9f471548a154729cfd964bfeb9900fa0fbfeff24aea512</t>
-  </si>
-  <si>
     <t>♥⎛⎠ Mitsuko&lt;3Synie</t>
   </si>
   <si>
@@ -12579,6 +12576,69 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1500111686156423228/id_Wu.png?ex=69f73f60&amp;is=69f5ede0&amp;hm=d0b23df228f1fb17d4e3e7ece143eb847c4573e170ffda9909298192c0361083</t>
+  </si>
+  <si>
+    <t>Wv</t>
+  </si>
+  <si>
+    <t>Ww</t>
+  </si>
+  <si>
+    <t>[AB-a]IPBM Inheritrix</t>
+  </si>
+  <si>
+    <t>Wx</t>
+  </si>
+  <si>
+    <t>Wy</t>
+  </si>
+  <si>
+    <t>Wz</t>
+  </si>
+  <si>
+    <t>Auto-Crossbow</t>
+  </si>
+  <si>
+    <t>[LAN]Bloon</t>
+  </si>
+  <si>
+    <t>Bloon</t>
+  </si>
+  <si>
+    <t>W0</t>
+  </si>
+  <si>
+    <t>W1</t>
+  </si>
+  <si>
+    <t>[o]</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1500398868628635658/id_Wv.png?ex=69f84ad6&amp;is=69f6f956&amp;hm=993b9cd57845eac5b3144be2d5bca870686f2f050e847f1f6c35f97f771117e9</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1500398973561602140/id_Ww.png?ex=69f84aef&amp;is=69f6f96f&amp;hm=9469ae0ff91f747ab5095a59b90791c9a4008d7ec776ac2f41600cbe9a9bc926</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1500399038778834974/id_Wx.png?ex=69f84afe&amp;is=69f6f97e&amp;hm=9b6b6a74d29a477712f92a03ee067b405ecdcc6554996bfb417697125691c753</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1500399084563988480/id_Wy.png?ex=69f84b09&amp;is=69f6f989&amp;hm=6c11e0da69b79d090bd8986ebba525a22045f068bdbce5b06eda119a404b8303</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1500399131481604207/id_Wz.png?ex=69f84b15&amp;is=69f6f995&amp;hm=609a9f6d5c50137301ea3e4f69a258f441feac9aee0e1b70bf322a722ddf3087</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1500399204814819328/id_W0.png?ex=69f84b26&amp;is=69f6f9a6&amp;hm=66f17086c0709c400dab0b884a532dc32afb5d01d45397f8388435cfb09b6216</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1500399255347527852/id_W1.jpg?ex=69f84b32&amp;is=69f6f9b2&amp;hm=1b6e7115b5012d9bb4c4f514f8b4f7352fcdf91e5438b840450e93ddce32c8f2</t>
+  </si>
+  <si>
+    <t>Missclick/Redwall</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1471844339931021342/1500407515505098913/id_Se.jpg?ex=69f852e3&amp;is=69f70163&amp;hm=4c4367f728acd972513e2851d41e96dc514991e6f6b7f68f33bfb12143695d86</t>
   </si>
 </sst>
 </file>
@@ -12590,11 +12650,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="111" x14ac:knownFonts="1">
+  <fonts count="112" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -13400,118 +13467,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="162">
+  <cellXfs count="163">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="108" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="92" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="107" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="91" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="106" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="98" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="92" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="99" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="93" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="89" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="88" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="76" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="76" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="75" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="75" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="76" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="75" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="76" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="75" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="72" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="72" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="73" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="73" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="75" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="76" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="71" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="70" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="69" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="69" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="68" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="68" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13520,18 +13588,18 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="52" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="52" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="45" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="46" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13545,15 +13613,15 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13795,7 +13863,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1453"/>
+  <dimension ref="A1:O1461"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -13945,7 +14013,7 @@
         <v>854</v>
       </c>
       <c r="N3" t="s">
-        <v>3640</v>
+        <v>3639</v>
       </c>
       <c r="O3" s="1"/>
     </row>
@@ -17250,7 +17318,7 @@
         <v>854</v>
       </c>
       <c r="N80" s="159" t="s">
-        <v>4135</v>
+        <v>4134</v>
       </c>
       <c r="O80" s="1"/>
     </row>
@@ -17392,7 +17460,7 @@
         <v>30380000</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>3895</v>
+        <v>3894</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>5</v>
@@ -18167,13 +18235,13 @@
         <v>28770000</v>
       </c>
       <c r="C102" t="s">
-        <v>4125</v>
+        <v>4124</v>
       </c>
       <c r="D102" t="s">
         <v>424</v>
       </c>
       <c r="E102" t="s">
-        <v>4125</v>
+        <v>4124</v>
       </c>
       <c r="F102" s="29">
         <v>45767</v>
@@ -19068,7 +19136,7 @@
         <v>26686674</v>
       </c>
       <c r="C123" t="s">
-        <v>3896</v>
+        <v>3895</v>
       </c>
       <c r="D123" t="s">
         <v>7</v>
@@ -25212,7 +25280,7 @@
         <v>20000000</v>
       </c>
       <c r="C267" t="s">
-        <v>4118</v>
+        <v>4117</v>
       </c>
       <c r="D267" s="12" t="s">
         <v>424</v>
@@ -27580,7 +27648,7 @@
         <v>17859596</v>
       </c>
       <c r="C324" t="s">
-        <v>3606</v>
+        <v>3605</v>
       </c>
       <c r="D324" t="s">
         <v>15</v>
@@ -28794,7 +28862,7 @@
         <v>15</v>
       </c>
       <c r="E353" t="s">
-        <v>4159</v>
+        <v>4158</v>
       </c>
       <c r="F353" s="29">
         <v>45647</v>
@@ -36541,7 +36609,7 @@
         <v>9</v>
       </c>
       <c r="D540" s="142" t="s">
-        <v>3919</v>
+        <v>3918</v>
       </c>
       <c r="E540" t="s">
         <v>3430</v>
@@ -42882,7 +42950,7 @@
         <v>76</v>
       </c>
       <c r="E693" t="s">
-        <v>4022</v>
+        <v>4021</v>
       </c>
       <c r="F693" s="29">
         <v>44676</v>
@@ -43495,7 +43563,7 @@
         <v>407</v>
       </c>
       <c r="D708" t="s">
-        <v>3917</v>
+        <v>3916</v>
       </c>
       <c r="E708" t="s">
         <v>408</v>
@@ -43870,7 +43938,7 @@
         <v>76</v>
       </c>
       <c r="E717" t="s">
-        <v>4022</v>
+        <v>4021</v>
       </c>
       <c r="F717" s="29">
         <v>44676</v>
@@ -45275,7 +45343,7 @@
         <v>785</v>
       </c>
       <c r="D751" t="s">
-        <v>3919</v>
+        <v>3918</v>
       </c>
       <c r="E751" s="52" t="s">
         <v>439</v>
@@ -46429,7 +46497,7 @@
         <v>414</v>
       </c>
       <c r="D779" t="s">
-        <v>3918</v>
+        <v>3917</v>
       </c>
       <c r="E779" t="s">
         <v>8</v>
@@ -48699,7 +48767,7 @@
         <v>259</v>
       </c>
       <c r="E834" t="s">
-        <v>4159</v>
+        <v>4158</v>
       </c>
       <c r="F834" s="29">
         <v>46016</v>
@@ -57851,7 +57919,7 @@
         <v>679</v>
       </c>
       <c r="E1056" s="131" t="s">
-        <v>3675</v>
+        <v>3674</v>
       </c>
       <c r="F1056" s="29">
         <v>46020</v>
@@ -60323,7 +60391,7 @@
         <v>0.55555555555555558</v>
       </c>
       <c r="H1116" s="159" t="s">
-        <v>4101</v>
+        <v>4100</v>
       </c>
       <c r="I1116" s="101" t="s">
         <v>806</v>
@@ -60882,7 +60950,7 @@
         <v>3683365</v>
       </c>
       <c r="C1130" s="139" t="s">
-        <v>3876</v>
+        <v>3875</v>
       </c>
       <c r="D1130" s="103" t="s">
         <v>372</v>
@@ -60923,7 +60991,7 @@
         <v>16246656</v>
       </c>
       <c r="C1131" s="139" t="s">
-        <v>3876</v>
+        <v>3875</v>
       </c>
       <c r="D1131" s="103" t="s">
         <v>66</v>
@@ -60964,7 +61032,7 @@
         <v>7945684</v>
       </c>
       <c r="C1132" s="139" t="s">
-        <v>3876</v>
+        <v>3875</v>
       </c>
       <c r="D1132" s="103" t="s">
         <v>24</v>
@@ -61497,7 +61565,7 @@
         <v>31682775</v>
       </c>
       <c r="C1145" s="139" t="s">
-        <v>3876</v>
+        <v>3875</v>
       </c>
       <c r="D1145" s="105" t="s">
         <v>15</v>
@@ -61784,7 +61852,7 @@
         <v>39229228</v>
       </c>
       <c r="C1152" s="139" t="s">
-        <v>3876</v>
+        <v>3875</v>
       </c>
       <c r="D1152" s="109" t="s">
         <v>13</v>
@@ -62768,7 +62836,7 @@
         <v>39654728</v>
       </c>
       <c r="C1176" t="s">
-        <v>3441</v>
+        <v>3440</v>
       </c>
       <c r="D1176" s="121" t="s">
         <v>13</v>
@@ -62970,7 +63038,7 @@
         <v>752</v>
       </c>
       <c r="B1181" s="7">
-        <v>10140000</v>
+        <v>10144385</v>
       </c>
       <c r="C1181" t="s">
         <v>720</v>
@@ -62984,11 +63052,11 @@
       <c r="F1181" s="29">
         <v>46081</v>
       </c>
-      <c r="G1181" s="56" t="s">
-        <v>502</v>
-      </c>
-      <c r="H1181" s="123" t="s">
-        <v>502</v>
+      <c r="G1181" s="56">
+        <v>0.10390046296296296</v>
+      </c>
+      <c r="H1181" s="162" t="s">
+        <v>4202</v>
       </c>
       <c r="I1181" s="123" t="s">
         <v>806</v>
@@ -63006,7 +63074,7 @@
         <v>854</v>
       </c>
       <c r="N1181" t="s">
-        <v>3440</v>
+        <v>4203</v>
       </c>
     </row>
     <row r="1182" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -63017,7 +63085,7 @@
         <v>4326028</v>
       </c>
       <c r="C1182" t="s">
-        <v>3442</v>
+        <v>3441</v>
       </c>
       <c r="D1182" s="124" t="s">
         <v>709</v>
@@ -63038,7 +63106,7 @@
         <v>806</v>
       </c>
       <c r="J1182" s="63" t="s">
-        <v>3443</v>
+        <v>3442</v>
       </c>
       <c r="K1182">
         <v>1183</v>
@@ -63047,7 +63115,7 @@
         <v>854</v>
       </c>
       <c r="N1182" t="s">
-        <v>3450</v>
+        <v>3449</v>
       </c>
     </row>
     <row r="1183" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -63058,7 +63126,7 @@
         <v>21801892</v>
       </c>
       <c r="C1183" t="s">
-        <v>3444</v>
+        <v>3443</v>
       </c>
       <c r="D1183" s="124" t="s">
         <v>15</v>
@@ -63073,13 +63141,13 @@
         <v>0.10748842592592593</v>
       </c>
       <c r="H1183" s="124" t="s">
+        <v>3444</v>
+      </c>
+      <c r="I1183" s="124" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1183" s="63" t="s">
         <v>3445</v>
-      </c>
-      <c r="I1183" s="124" t="s">
-        <v>806</v>
-      </c>
-      <c r="J1183" s="63" t="s">
-        <v>3446</v>
       </c>
       <c r="K1183">
         <v>1184</v>
@@ -63088,7 +63156,7 @@
         <v>854</v>
       </c>
       <c r="N1183" t="s">
-        <v>3451</v>
+        <v>3450</v>
       </c>
     </row>
     <row r="1184" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -63120,7 +63188,7 @@
         <v>806</v>
       </c>
       <c r="J1184" s="63" t="s">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="K1184">
         <v>1185</v>
@@ -63129,7 +63197,7 @@
         <v>854</v>
       </c>
       <c r="N1184" t="s">
-        <v>3452</v>
+        <v>3451</v>
       </c>
     </row>
     <row r="1185" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -63155,13 +63223,13 @@
         <v>7.7858796296296287E-2</v>
       </c>
       <c r="H1185" s="124" t="s">
+        <v>3447</v>
+      </c>
+      <c r="I1185" s="124" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1185" s="63" t="s">
         <v>3448</v>
-      </c>
-      <c r="I1185" s="124" t="s">
-        <v>806</v>
-      </c>
-      <c r="J1185" s="63" t="s">
-        <v>3449</v>
       </c>
       <c r="K1185">
         <v>1186</v>
@@ -63170,7 +63238,7 @@
         <v>854</v>
       </c>
       <c r="N1185" t="s">
-        <v>3453</v>
+        <v>3452</v>
       </c>
     </row>
     <row r="1186" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -63184,7 +63252,7 @@
         <v>4</v>
       </c>
       <c r="D1186" s="125" t="s">
-        <v>3458</v>
+        <v>3457</v>
       </c>
       <c r="E1186" s="125" t="s">
         <v>695</v>
@@ -63202,7 +63270,7 @@
         <v>806</v>
       </c>
       <c r="J1186" s="63" t="s">
-        <v>3454</v>
+        <v>3453</v>
       </c>
       <c r="K1186">
         <v>1187</v>
@@ -63211,7 +63279,7 @@
         <v>854</v>
       </c>
       <c r="N1186" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
     </row>
     <row r="1187" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -63222,10 +63290,10 @@
         <v>1230601</v>
       </c>
       <c r="C1187" t="s">
+        <v>3458</v>
+      </c>
+      <c r="D1187" s="125" t="s">
         <v>3459</v>
-      </c>
-      <c r="D1187" s="125" t="s">
-        <v>3460</v>
       </c>
       <c r="E1187" s="125" t="s">
         <v>798</v>
@@ -63243,7 +63311,7 @@
         <v>806</v>
       </c>
       <c r="J1187" s="63" t="s">
-        <v>3455</v>
+        <v>3454</v>
       </c>
       <c r="K1187">
         <v>1188</v>
@@ -63252,7 +63320,7 @@
         <v>854</v>
       </c>
       <c r="N1187" t="s">
-        <v>3476</v>
+        <v>3475</v>
       </c>
     </row>
     <row r="1188" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -63263,10 +63331,10 @@
         <v>2674915</v>
       </c>
       <c r="C1188" t="s">
-        <v>3462</v>
+        <v>3461</v>
       </c>
       <c r="D1188" s="125" t="s">
-        <v>3461</v>
+        <v>3460</v>
       </c>
       <c r="E1188" s="125" t="s">
         <v>798</v>
@@ -63284,7 +63352,7 @@
         <v>806</v>
       </c>
       <c r="J1188" s="63" t="s">
-        <v>3456</v>
+        <v>3455</v>
       </c>
       <c r="K1188">
         <v>1189</v>
@@ -63293,7 +63361,7 @@
         <v>854</v>
       </c>
       <c r="N1188" t="s">
-        <v>3477</v>
+        <v>3476</v>
       </c>
     </row>
     <row r="1189" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -63304,7 +63372,7 @@
         <v>12969835</v>
       </c>
       <c r="C1189" t="s">
-        <v>3463</v>
+        <v>3462</v>
       </c>
       <c r="D1189" s="125" t="s">
         <v>15</v>
@@ -63325,7 +63393,7 @@
         <v>806</v>
       </c>
       <c r="J1189" s="63" t="s">
-        <v>3457</v>
+        <v>3456</v>
       </c>
       <c r="K1189">
         <v>1190</v>
@@ -63334,7 +63402,7 @@
         <v>854</v>
       </c>
       <c r="N1189" t="s">
-        <v>3478</v>
+        <v>3477</v>
       </c>
     </row>
     <row r="1190" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -63360,13 +63428,13 @@
         <v>7.9895833333333333E-2</v>
       </c>
       <c r="H1190" s="125" t="s">
+        <v>3463</v>
+      </c>
+      <c r="I1190" s="125" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1190" s="63" t="s">
         <v>3464</v>
-      </c>
-      <c r="I1190" s="125" t="s">
-        <v>806</v>
-      </c>
-      <c r="J1190" s="63" t="s">
-        <v>3465</v>
       </c>
       <c r="K1190">
         <v>1191</v>
@@ -63375,7 +63443,7 @@
         <v>854</v>
       </c>
       <c r="N1190" t="s">
-        <v>3479</v>
+        <v>3478</v>
       </c>
     </row>
     <row r="1191" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -63386,7 +63454,7 @@
         <v>4417949</v>
       </c>
       <c r="C1191" t="s">
-        <v>3466</v>
+        <v>3465</v>
       </c>
       <c r="D1191" s="125" t="s">
         <v>361</v>
@@ -63407,7 +63475,7 @@
         <v>806</v>
       </c>
       <c r="J1191" s="63" t="s">
-        <v>3467</v>
+        <v>3466</v>
       </c>
       <c r="K1191">
         <v>1192</v>
@@ -63416,7 +63484,7 @@
         <v>854</v>
       </c>
       <c r="N1191" t="s">
-        <v>3480</v>
+        <v>3479</v>
       </c>
     </row>
     <row r="1192" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -63448,7 +63516,7 @@
         <v>806</v>
       </c>
       <c r="J1192" s="63" t="s">
-        <v>3468</v>
+        <v>3467</v>
       </c>
       <c r="K1192">
         <v>1193</v>
@@ -63457,7 +63525,7 @@
         <v>854</v>
       </c>
       <c r="N1192" t="s">
-        <v>3481</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="1193" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -63489,7 +63557,7 @@
         <v>806</v>
       </c>
       <c r="J1193" s="63" t="s">
-        <v>3469</v>
+        <v>3468</v>
       </c>
       <c r="K1193">
         <v>1194</v>
@@ -63498,7 +63566,7 @@
         <v>854</v>
       </c>
       <c r="N1193" t="s">
-        <v>3482</v>
+        <v>3481</v>
       </c>
     </row>
     <row r="1194" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -63524,13 +63592,13 @@
         <v>7.0254629629629625E-2</v>
       </c>
       <c r="H1194" s="125" t="s">
+        <v>3469</v>
+      </c>
+      <c r="I1194" s="125" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1194" s="63" t="s">
         <v>3470</v>
-      </c>
-      <c r="I1194" s="125" t="s">
-        <v>806</v>
-      </c>
-      <c r="J1194" s="63" t="s">
-        <v>3471</v>
       </c>
       <c r="K1194">
         <v>1195</v>
@@ -63539,7 +63607,7 @@
         <v>854</v>
       </c>
       <c r="N1194" t="s">
-        <v>3483</v>
+        <v>3482</v>
       </c>
     </row>
     <row r="1195" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -63550,7 +63618,7 @@
         <v>27873133</v>
       </c>
       <c r="C1195" t="s">
-        <v>3485</v>
+        <v>3484</v>
       </c>
       <c r="D1195" s="126" t="s">
         <v>55</v>
@@ -63571,7 +63639,7 @@
         <v>806</v>
       </c>
       <c r="J1195" s="63" t="s">
-        <v>3486</v>
+        <v>3485</v>
       </c>
       <c r="K1195">
         <v>1196</v>
@@ -63580,7 +63648,7 @@
         <v>854</v>
       </c>
       <c r="N1195" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
     </row>
     <row r="1196" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -63591,13 +63659,13 @@
         <v>14420055</v>
       </c>
       <c r="C1196" t="s">
-        <v>3490</v>
+        <v>3489</v>
       </c>
       <c r="D1196" s="126" t="s">
         <v>13</v>
       </c>
       <c r="E1196" s="126" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="F1196" s="29">
         <v>46083</v>
@@ -63612,7 +63680,7 @@
         <v>806</v>
       </c>
       <c r="J1196" s="63" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
       <c r="K1196">
         <v>1197</v>
@@ -63621,7 +63689,7 @@
         <v>854</v>
       </c>
       <c r="N1196" t="s">
-        <v>3496</v>
+        <v>3495</v>
       </c>
     </row>
     <row r="1197" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -63653,7 +63721,7 @@
         <v>806</v>
       </c>
       <c r="J1197" s="63" t="s">
-        <v>3489</v>
+        <v>3488</v>
       </c>
       <c r="K1197">
         <v>1198</v>
@@ -63662,7 +63730,7 @@
         <v>854</v>
       </c>
       <c r="N1197" t="s">
-        <v>3498</v>
+        <v>3497</v>
       </c>
     </row>
     <row r="1198" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -63673,10 +63741,10 @@
         <v>3347554</v>
       </c>
       <c r="C1198" t="s">
+        <v>3491</v>
+      </c>
+      <c r="D1198" s="126" t="s">
         <v>3492</v>
-      </c>
-      <c r="D1198" s="126" t="s">
-        <v>3493</v>
       </c>
       <c r="E1198" s="126" t="s">
         <v>798</v>
@@ -63694,7 +63762,7 @@
         <v>806</v>
       </c>
       <c r="J1198" s="63" t="s">
-        <v>3488</v>
+        <v>3487</v>
       </c>
       <c r="K1198">
         <v>1199</v>
@@ -63703,7 +63771,7 @@
         <v>854</v>
       </c>
       <c r="N1198" t="s">
-        <v>3497</v>
+        <v>3496</v>
       </c>
     </row>
     <row r="1199" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -63714,10 +63782,10 @@
         <v>1259579</v>
       </c>
       <c r="C1199" t="s">
+        <v>3472</v>
+      </c>
+      <c r="D1199" s="125" t="s">
         <v>3473</v>
-      </c>
-      <c r="D1199" s="125" t="s">
-        <v>3474</v>
       </c>
       <c r="E1199" s="125" t="s">
         <v>439</v>
@@ -63735,7 +63803,7 @@
         <v>806</v>
       </c>
       <c r="J1199" s="63" t="s">
-        <v>3472</v>
+        <v>3471</v>
       </c>
       <c r="K1199">
         <v>1200</v>
@@ -63744,7 +63812,7 @@
         <v>854</v>
       </c>
       <c r="N1199" t="s">
-        <v>3484</v>
+        <v>3483</v>
       </c>
     </row>
     <row r="1200" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -63776,7 +63844,7 @@
         <v>806</v>
       </c>
       <c r="J1200" s="63" t="s">
-        <v>3494</v>
+        <v>3493</v>
       </c>
       <c r="K1200">
         <v>1201</v>
@@ -63785,7 +63853,7 @@
         <v>854</v>
       </c>
       <c r="N1200" t="s">
-        <v>3499</v>
+        <v>3498</v>
       </c>
     </row>
     <row r="1201" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -63796,13 +63864,13 @@
         <v>12860000</v>
       </c>
       <c r="C1201" t="s">
-        <v>3502</v>
+        <v>3501</v>
       </c>
       <c r="D1201" s="127" t="s">
         <v>24</v>
       </c>
       <c r="E1201" t="s">
-        <v>3502</v>
+        <v>3501</v>
       </c>
       <c r="F1201" s="29">
         <v>46081</v>
@@ -63817,7 +63885,7 @@
         <v>806</v>
       </c>
       <c r="J1201" s="63" t="s">
-        <v>3500</v>
+        <v>3499</v>
       </c>
       <c r="K1201">
         <v>1202</v>
@@ -63826,7 +63894,7 @@
         <v>854</v>
       </c>
       <c r="N1201" t="s">
-        <v>3513</v>
+        <v>3512</v>
       </c>
     </row>
     <row r="1202" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -63858,7 +63926,7 @@
         <v>821</v>
       </c>
       <c r="J1202" s="63" t="s">
-        <v>3501</v>
+        <v>3500</v>
       </c>
       <c r="K1202">
         <v>1203</v>
@@ -63867,7 +63935,7 @@
         <v>854</v>
       </c>
       <c r="N1202" t="s">
-        <v>3514</v>
+        <v>3513</v>
       </c>
     </row>
     <row r="1203" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -63899,7 +63967,7 @@
         <v>821</v>
       </c>
       <c r="J1203" s="63" t="s">
-        <v>3503</v>
+        <v>3502</v>
       </c>
       <c r="K1203">
         <v>1204</v>
@@ -63908,7 +63976,7 @@
         <v>854</v>
       </c>
       <c r="N1203" t="s">
-        <v>3515</v>
+        <v>3514</v>
       </c>
     </row>
     <row r="1204" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -63940,7 +64008,7 @@
         <v>806</v>
       </c>
       <c r="J1204" s="63" t="s">
-        <v>3504</v>
+        <v>3503</v>
       </c>
       <c r="K1204">
         <v>1205</v>
@@ -63949,7 +64017,7 @@
         <v>854</v>
       </c>
       <c r="N1204" t="s">
-        <v>3516</v>
+        <v>3515</v>
       </c>
     </row>
     <row r="1205" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -63960,7 +64028,7 @@
         <v>15026322</v>
       </c>
       <c r="C1205" t="s">
-        <v>3507</v>
+        <v>3506</v>
       </c>
       <c r="D1205" s="127" t="s">
         <v>259</v>
@@ -63981,7 +64049,7 @@
         <v>806</v>
       </c>
       <c r="J1205" s="63" t="s">
-        <v>3505</v>
+        <v>3504</v>
       </c>
       <c r="K1205">
         <v>1206</v>
@@ -63990,7 +64058,7 @@
         <v>854</v>
       </c>
       <c r="N1205" t="s">
-        <v>3517</v>
+        <v>3516</v>
       </c>
     </row>
     <row r="1206" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64001,10 +64069,10 @@
         <v>7688466</v>
       </c>
       <c r="C1206" t="s">
+        <v>3506</v>
+      </c>
+      <c r="D1206" s="127" t="s">
         <v>3507</v>
-      </c>
-      <c r="D1206" s="127" t="s">
-        <v>3508</v>
       </c>
       <c r="E1206" t="s">
         <v>29</v>
@@ -64022,7 +64090,7 @@
         <v>806</v>
       </c>
       <c r="J1206" s="63" t="s">
-        <v>3506</v>
+        <v>3505</v>
       </c>
       <c r="K1206">
         <v>1207</v>
@@ -64031,7 +64099,7 @@
         <v>854</v>
       </c>
       <c r="N1206" t="s">
-        <v>3518</v>
+        <v>3517</v>
       </c>
     </row>
     <row r="1207" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64045,7 +64113,7 @@
         <v>25</v>
       </c>
       <c r="D1207" s="127" t="s">
-        <v>3509</v>
+        <v>3508</v>
       </c>
       <c r="E1207" t="s">
         <v>25</v>
@@ -64063,7 +64131,7 @@
         <v>806</v>
       </c>
       <c r="J1207" s="63" t="s">
-        <v>3510</v>
+        <v>3509</v>
       </c>
       <c r="K1207">
         <v>1208</v>
@@ -64072,7 +64140,7 @@
         <v>854</v>
       </c>
       <c r="N1207" t="s">
-        <v>3519</v>
+        <v>3518</v>
       </c>
     </row>
     <row r="1208" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64104,7 +64172,7 @@
         <v>806</v>
       </c>
       <c r="J1208" s="63" t="s">
-        <v>3511</v>
+        <v>3510</v>
       </c>
       <c r="K1208">
         <v>1209</v>
@@ -64113,7 +64181,7 @@
         <v>854</v>
       </c>
       <c r="N1208" t="s">
-        <v>3520</v>
+        <v>3519</v>
       </c>
     </row>
     <row r="1209" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64145,7 +64213,7 @@
         <v>806</v>
       </c>
       <c r="J1209" s="63" t="s">
-        <v>3512</v>
+        <v>3511</v>
       </c>
       <c r="K1209">
         <v>1210</v>
@@ -64154,7 +64222,7 @@
         <v>854</v>
       </c>
       <c r="N1209" t="s">
-        <v>3521</v>
+        <v>3520</v>
       </c>
     </row>
     <row r="1210" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64186,7 +64254,7 @@
         <v>806</v>
       </c>
       <c r="J1210" s="63" t="s">
-        <v>3522</v>
+        <v>3521</v>
       </c>
       <c r="K1210">
         <v>1211</v>
@@ -64195,7 +64263,7 @@
         <v>854</v>
       </c>
       <c r="N1210" t="s">
-        <v>3542</v>
+        <v>3541</v>
       </c>
     </row>
     <row r="1211" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64227,7 +64295,7 @@
         <v>806</v>
       </c>
       <c r="J1211" s="63" t="s">
-        <v>3523</v>
+        <v>3522</v>
       </c>
       <c r="K1211">
         <v>1212</v>
@@ -64236,7 +64304,7 @@
         <v>854</v>
       </c>
       <c r="N1211" t="s">
-        <v>3543</v>
+        <v>3542</v>
       </c>
     </row>
     <row r="1212" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64268,7 +64336,7 @@
         <v>806</v>
       </c>
       <c r="J1212" s="63" t="s">
-        <v>3524</v>
+        <v>3523</v>
       </c>
       <c r="K1212">
         <v>1213</v>
@@ -64277,7 +64345,7 @@
         <v>854</v>
       </c>
       <c r="N1212" t="s">
-        <v>3544</v>
+        <v>3543</v>
       </c>
     </row>
     <row r="1213" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64309,7 +64377,7 @@
         <v>806</v>
       </c>
       <c r="J1213" s="63" t="s">
-        <v>3526</v>
+        <v>3525</v>
       </c>
       <c r="K1213">
         <v>1214</v>
@@ -64318,7 +64386,7 @@
         <v>854</v>
       </c>
       <c r="N1213" t="s">
-        <v>3545</v>
+        <v>3544</v>
       </c>
     </row>
     <row r="1214" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64350,7 +64418,7 @@
         <v>806</v>
       </c>
       <c r="J1214" s="63" t="s">
-        <v>3527</v>
+        <v>3526</v>
       </c>
       <c r="K1214">
         <v>1215</v>
@@ -64359,7 +64427,7 @@
         <v>854</v>
       </c>
       <c r="N1214" t="s">
-        <v>3546</v>
+        <v>3545</v>
       </c>
     </row>
     <row r="1215" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64391,7 +64459,7 @@
         <v>806</v>
       </c>
       <c r="J1215" s="63" t="s">
-        <v>3525</v>
+        <v>3524</v>
       </c>
       <c r="K1215">
         <v>1216</v>
@@ -64400,7 +64468,7 @@
         <v>854</v>
       </c>
       <c r="N1215" t="s">
-        <v>3547</v>
+        <v>3546</v>
       </c>
     </row>
     <row r="1216" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64432,7 +64500,7 @@
         <v>806</v>
       </c>
       <c r="J1216" s="63" t="s">
-        <v>3528</v>
+        <v>3527</v>
       </c>
       <c r="K1216">
         <v>1217</v>
@@ -64441,7 +64509,7 @@
         <v>854</v>
       </c>
       <c r="N1216" t="s">
-        <v>3548</v>
+        <v>3547</v>
       </c>
     </row>
     <row r="1217" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64452,13 +64520,13 @@
         <v>34098075</v>
       </c>
       <c r="C1217" t="s">
-        <v>3490</v>
+        <v>3489</v>
       </c>
       <c r="D1217" t="s">
         <v>424</v>
       </c>
       <c r="E1217" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="F1217" s="29">
         <v>46086</v>
@@ -64473,7 +64541,7 @@
         <v>806</v>
       </c>
       <c r="J1217" s="63" t="s">
-        <v>3529</v>
+        <v>3528</v>
       </c>
       <c r="K1217">
         <v>1218</v>
@@ -64482,7 +64550,7 @@
         <v>854</v>
       </c>
       <c r="N1217" t="s">
-        <v>3549</v>
+        <v>3548</v>
       </c>
     </row>
     <row r="1218" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64493,7 +64561,7 @@
         <v>3681697</v>
       </c>
       <c r="C1218" t="s">
-        <v>3532</v>
+        <v>3531</v>
       </c>
       <c r="D1218" t="s">
         <v>460</v>
@@ -64514,7 +64582,7 @@
         <v>290</v>
       </c>
       <c r="J1218" s="63" t="s">
-        <v>3530</v>
+        <v>3529</v>
       </c>
       <c r="K1218">
         <v>1219</v>
@@ -64523,7 +64591,7 @@
         <v>854</v>
       </c>
       <c r="N1218" t="s">
-        <v>3550</v>
+        <v>3549</v>
       </c>
     </row>
     <row r="1219" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64555,7 +64623,7 @@
         <v>806</v>
       </c>
       <c r="J1219" s="63" t="s">
-        <v>3531</v>
+        <v>3530</v>
       </c>
       <c r="K1219">
         <v>1220</v>
@@ -64564,7 +64632,7 @@
         <v>854</v>
       </c>
       <c r="N1219" t="s">
-        <v>3551</v>
+        <v>3550</v>
       </c>
     </row>
     <row r="1220" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64575,7 +64643,7 @@
         <v>6070960</v>
       </c>
       <c r="C1220" t="s">
-        <v>3534</v>
+        <v>3533</v>
       </c>
       <c r="D1220" t="s">
         <v>634</v>
@@ -64596,7 +64664,7 @@
         <v>806</v>
       </c>
       <c r="J1220" s="63" t="s">
-        <v>3533</v>
+        <v>3532</v>
       </c>
       <c r="K1220">
         <v>1221</v>
@@ -64605,7 +64673,7 @@
         <v>854</v>
       </c>
       <c r="N1220" t="s">
-        <v>3552</v>
+        <v>3551</v>
       </c>
     </row>
     <row r="1221" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64637,7 +64705,7 @@
         <v>806</v>
       </c>
       <c r="J1221" s="63" t="s">
-        <v>3535</v>
+        <v>3534</v>
       </c>
       <c r="K1221">
         <v>1222</v>
@@ -64646,7 +64714,7 @@
         <v>854</v>
       </c>
       <c r="N1221" t="s">
-        <v>3553</v>
+        <v>3552</v>
       </c>
     </row>
     <row r="1222" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64657,7 +64725,7 @@
         <v>23677087</v>
       </c>
       <c r="C1222" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D1222" t="s">
         <v>60</v>
@@ -64678,7 +64746,7 @@
         <v>806</v>
       </c>
       <c r="J1222" s="63" t="s">
-        <v>3537</v>
+        <v>3536</v>
       </c>
       <c r="K1222">
         <v>1223</v>
@@ -64687,7 +64755,7 @@
         <v>854</v>
       </c>
       <c r="N1222" t="s">
-        <v>3554</v>
+        <v>3553</v>
       </c>
     </row>
     <row r="1223" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64698,7 +64766,7 @@
         <v>28277226</v>
       </c>
       <c r="C1223" t="s">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="D1223" t="s">
         <v>15</v>
@@ -64719,7 +64787,7 @@
         <v>806</v>
       </c>
       <c r="J1223" s="63" t="s">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="K1223">
         <v>1224</v>
@@ -64728,7 +64796,7 @@
         <v>854</v>
       </c>
       <c r="N1223" t="s">
-        <v>3555</v>
+        <v>3554</v>
       </c>
     </row>
     <row r="1224" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64760,7 +64828,7 @@
         <v>806</v>
       </c>
       <c r="J1224" s="63" t="s">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="K1224">
         <v>1225</v>
@@ -64769,7 +64837,7 @@
         <v>854</v>
       </c>
       <c r="N1224" t="s">
-        <v>3556</v>
+        <v>3555</v>
       </c>
     </row>
     <row r="1225" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64801,7 +64869,7 @@
         <v>806</v>
       </c>
       <c r="J1225" s="63" t="s">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="K1225">
         <v>1226</v>
@@ -64810,7 +64878,7 @@
         <v>854</v>
       </c>
       <c r="N1225" t="s">
-        <v>3557</v>
+        <v>3556</v>
       </c>
     </row>
     <row r="1226" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64821,10 +64889,10 @@
         <v>5203370</v>
       </c>
       <c r="C1226" t="s">
-        <v>3559</v>
+        <v>3558</v>
       </c>
       <c r="D1226" t="s">
-        <v>3558</v>
+        <v>3557</v>
       </c>
       <c r="E1226" t="s">
         <v>1762</v>
@@ -64842,7 +64910,7 @@
         <v>806</v>
       </c>
       <c r="J1226" s="63" t="s">
-        <v>3560</v>
+        <v>3559</v>
       </c>
       <c r="K1226">
         <v>1227</v>
@@ -64851,7 +64919,7 @@
         <v>854</v>
       </c>
       <c r="N1226" t="s">
-        <v>3569</v>
+        <v>3568</v>
       </c>
     </row>
     <row r="1227" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64883,7 +64951,7 @@
         <v>806</v>
       </c>
       <c r="J1227" s="63" t="s">
-        <v>3561</v>
+        <v>3560</v>
       </c>
       <c r="K1227">
         <v>1228</v>
@@ -64892,7 +64960,7 @@
         <v>854</v>
       </c>
       <c r="N1227" t="s">
-        <v>3570</v>
+        <v>3569</v>
       </c>
     </row>
     <row r="1228" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64918,13 +64986,13 @@
         <v>0.12835648148148149</v>
       </c>
       <c r="H1228" t="s">
-        <v>3563</v>
+        <v>3562</v>
       </c>
       <c r="I1228" t="s">
         <v>806</v>
       </c>
       <c r="J1228" s="63" t="s">
-        <v>3562</v>
+        <v>3561</v>
       </c>
       <c r="K1228">
         <v>1229</v>
@@ -64933,7 +65001,7 @@
         <v>854</v>
       </c>
       <c r="N1228" t="s">
-        <v>3571</v>
+        <v>3570</v>
       </c>
     </row>
     <row r="1229" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64965,7 +65033,7 @@
         <v>813</v>
       </c>
       <c r="J1229" s="63" t="s">
-        <v>3564</v>
+        <v>3563</v>
       </c>
       <c r="K1229">
         <v>1230</v>
@@ -64974,7 +65042,7 @@
         <v>854</v>
       </c>
       <c r="N1229" t="s">
-        <v>3572</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="1230" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -64985,7 +65053,7 @@
         <v>9587418</v>
       </c>
       <c r="C1230" t="s">
-        <v>3565</v>
+        <v>3564</v>
       </c>
       <c r="D1230" t="s">
         <v>603</v>
@@ -65006,7 +65074,7 @@
         <v>806</v>
       </c>
       <c r="J1230" s="63" t="s">
-        <v>3566</v>
+        <v>3565</v>
       </c>
       <c r="K1230">
         <v>1231</v>
@@ -65015,7 +65083,7 @@
         <v>854</v>
       </c>
       <c r="N1230" t="s">
-        <v>3573</v>
+        <v>3572</v>
       </c>
     </row>
     <row r="1231" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65026,7 +65094,7 @@
         <v>20000646</v>
       </c>
       <c r="C1231" t="s">
-        <v>3567</v>
+        <v>3566</v>
       </c>
       <c r="D1231" t="s">
         <v>60</v>
@@ -65047,7 +65115,7 @@
         <v>806</v>
       </c>
       <c r="J1231" s="63" t="s">
-        <v>3568</v>
+        <v>3567</v>
       </c>
       <c r="K1231">
         <v>1232</v>
@@ -65056,7 +65124,7 @@
         <v>854</v>
       </c>
       <c r="N1231" t="s">
-        <v>3574</v>
+        <v>3573</v>
       </c>
     </row>
     <row r="1232" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65067,10 +65135,10 @@
         <v>3986203</v>
       </c>
       <c r="C1232" t="s">
+        <v>3574</v>
+      </c>
+      <c r="D1232" t="s">
         <v>3575</v>
-      </c>
-      <c r="D1232" t="s">
-        <v>3576</v>
       </c>
       <c r="E1232" t="s">
         <v>439</v>
@@ -65088,7 +65156,7 @@
         <v>806</v>
       </c>
       <c r="J1232" s="63" t="s">
-        <v>3577</v>
+        <v>3576</v>
       </c>
       <c r="K1232">
         <v>1233</v>
@@ -65097,7 +65165,7 @@
         <v>854</v>
       </c>
       <c r="N1232" t="s">
-        <v>3586</v>
+        <v>3585</v>
       </c>
     </row>
     <row r="1233" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65108,7 +65176,7 @@
         <v>14629441</v>
       </c>
       <c r="C1233" t="s">
-        <v>3579</v>
+        <v>3578</v>
       </c>
       <c r="D1233" t="s">
         <v>60</v>
@@ -65129,7 +65197,7 @@
         <v>806</v>
       </c>
       <c r="J1233" s="63" t="s">
-        <v>3578</v>
+        <v>3577</v>
       </c>
       <c r="K1233">
         <v>1234</v>
@@ -65138,7 +65206,7 @@
         <v>854</v>
       </c>
       <c r="N1233" t="s">
-        <v>3587</v>
+        <v>3586</v>
       </c>
     </row>
     <row r="1234" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65170,7 +65238,7 @@
         <v>806</v>
       </c>
       <c r="J1234" s="63" t="s">
-        <v>3596</v>
+        <v>3595</v>
       </c>
       <c r="K1234">
         <v>1235</v>
@@ -65179,7 +65247,7 @@
         <v>854</v>
       </c>
       <c r="N1234" t="s">
-        <v>3588</v>
+        <v>3587</v>
       </c>
     </row>
     <row r="1235" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65190,7 +65258,7 @@
         <v>41657675</v>
       </c>
       <c r="C1235" t="s">
-        <v>3582</v>
+        <v>3581</v>
       </c>
       <c r="D1235" t="s">
         <v>424</v>
@@ -65211,7 +65279,7 @@
         <v>806</v>
       </c>
       <c r="J1235" s="63" t="s">
-        <v>3580</v>
+        <v>3579</v>
       </c>
       <c r="K1235">
         <v>1236</v>
@@ -65220,7 +65288,7 @@
         <v>854</v>
       </c>
       <c r="N1235" t="s">
-        <v>4060</v>
+        <v>4059</v>
       </c>
     </row>
     <row r="1236" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65252,7 +65320,7 @@
         <v>806</v>
       </c>
       <c r="J1236" s="63" t="s">
-        <v>3581</v>
+        <v>3580</v>
       </c>
       <c r="K1236">
         <v>1237</v>
@@ -65261,7 +65329,7 @@
         <v>854</v>
       </c>
       <c r="N1236" t="s">
-        <v>3589</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="1237" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65293,7 +65361,7 @@
         <v>806</v>
       </c>
       <c r="J1237" s="63" t="s">
-        <v>3583</v>
+        <v>3582</v>
       </c>
       <c r="K1237">
         <v>1238</v>
@@ -65302,7 +65370,7 @@
         <v>854</v>
       </c>
       <c r="N1237" t="s">
-        <v>3590</v>
+        <v>3589</v>
       </c>
     </row>
     <row r="1238" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65313,7 +65381,7 @@
         <v>53438793</v>
       </c>
       <c r="C1238" t="s">
-        <v>3579</v>
+        <v>3578</v>
       </c>
       <c r="D1238" t="s">
         <v>60</v>
@@ -65334,7 +65402,7 @@
         <v>806</v>
       </c>
       <c r="J1238" s="63" t="s">
-        <v>3584</v>
+        <v>3583</v>
       </c>
       <c r="K1238">
         <v>1239</v>
@@ -65343,7 +65411,7 @@
         <v>854</v>
       </c>
       <c r="N1238" t="s">
-        <v>3591</v>
+        <v>3590</v>
       </c>
     </row>
     <row r="1239" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65354,7 +65422,7 @@
         <v>27655583</v>
       </c>
       <c r="C1239" t="s">
-        <v>3565</v>
+        <v>3564</v>
       </c>
       <c r="D1239" t="s">
         <v>603</v>
@@ -65375,7 +65443,7 @@
         <v>806</v>
       </c>
       <c r="J1239" s="63" t="s">
-        <v>3585</v>
+        <v>3584</v>
       </c>
       <c r="K1239">
         <v>1240</v>
@@ -65384,7 +65452,7 @@
         <v>854</v>
       </c>
       <c r="N1239" t="s">
-        <v>3601</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="1240" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65395,7 +65463,7 @@
         <v>13795880</v>
       </c>
       <c r="C1240" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
       <c r="D1240" t="s">
         <v>66</v>
@@ -65410,13 +65478,13 @@
         <v>9.8101851851851843E-2</v>
       </c>
       <c r="H1240" t="s">
-        <v>3594</v>
+        <v>3593</v>
       </c>
       <c r="I1240" t="s">
         <v>806</v>
       </c>
       <c r="J1240" s="63" t="s">
-        <v>3592</v>
+        <v>3591</v>
       </c>
       <c r="K1240">
         <v>1241</v>
@@ -65425,7 +65493,7 @@
         <v>854</v>
       </c>
       <c r="N1240" t="s">
-        <v>3602</v>
+        <v>3601</v>
       </c>
     </row>
     <row r="1241" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65436,7 +65504,7 @@
         <v>34231677</v>
       </c>
       <c r="C1241" t="s">
-        <v>3597</v>
+        <v>3596</v>
       </c>
       <c r="D1241" t="s">
         <v>9</v>
@@ -65457,7 +65525,7 @@
         <v>806</v>
       </c>
       <c r="J1241" s="63" t="s">
-        <v>3593</v>
+        <v>3592</v>
       </c>
       <c r="K1241">
         <v>1242</v>
@@ -65466,7 +65534,7 @@
         <v>854</v>
       </c>
       <c r="N1241" t="s">
-        <v>3603</v>
+        <v>3602</v>
       </c>
     </row>
     <row r="1242" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65498,7 +65566,7 @@
         <v>806</v>
       </c>
       <c r="J1242" s="63" t="s">
-        <v>3598</v>
+        <v>3597</v>
       </c>
       <c r="K1242">
         <v>1243</v>
@@ -65507,7 +65575,7 @@
         <v>854</v>
       </c>
       <c r="N1242" t="s">
-        <v>3604</v>
+        <v>3603</v>
       </c>
     </row>
     <row r="1243" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65518,7 +65586,7 @@
         <v>11840108</v>
       </c>
       <c r="C1243" t="s">
-        <v>3599</v>
+        <v>3598</v>
       </c>
       <c r="D1243" t="s">
         <v>15</v>
@@ -65539,7 +65607,7 @@
         <v>806</v>
       </c>
       <c r="J1243" s="63" t="s">
-        <v>3600</v>
+        <v>3599</v>
       </c>
       <c r="K1243">
         <v>1244</v>
@@ -65548,7 +65616,7 @@
         <v>854</v>
       </c>
       <c r="N1243" t="s">
-        <v>3605</v>
+        <v>3604</v>
       </c>
     </row>
     <row r="1244" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65562,7 +65630,7 @@
         <v>25</v>
       </c>
       <c r="D1244" t="s">
-        <v>3607</v>
+        <v>3606</v>
       </c>
       <c r="E1244" t="s">
         <v>25</v>
@@ -65580,7 +65648,7 @@
         <v>806</v>
       </c>
       <c r="J1244" s="63" t="s">
-        <v>3608</v>
+        <v>3607</v>
       </c>
       <c r="K1244">
         <v>1245</v>
@@ -65589,7 +65657,7 @@
         <v>854</v>
       </c>
       <c r="N1244" t="s">
-        <v>3628</v>
+        <v>3627</v>
       </c>
     </row>
     <row r="1245" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65621,7 +65689,7 @@
         <v>806</v>
       </c>
       <c r="J1245" s="63" t="s">
-        <v>3609</v>
+        <v>3608</v>
       </c>
       <c r="K1245">
         <v>1246</v>
@@ -65630,7 +65698,7 @@
         <v>854</v>
       </c>
       <c r="N1245" t="s">
-        <v>3629</v>
+        <v>3628</v>
       </c>
     </row>
     <row r="1246" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65662,7 +65730,7 @@
         <v>806</v>
       </c>
       <c r="J1246" s="63" t="s">
-        <v>3610</v>
+        <v>3609</v>
       </c>
       <c r="K1246">
         <v>1247</v>
@@ -65671,7 +65739,7 @@
         <v>854</v>
       </c>
       <c r="N1246" t="s">
-        <v>3630</v>
+        <v>3629</v>
       </c>
     </row>
     <row r="1247" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65682,7 +65750,7 @@
         <v>11950000</v>
       </c>
       <c r="C1247" t="s">
-        <v>3612</v>
+        <v>3611</v>
       </c>
       <c r="D1247" t="s">
         <v>13</v>
@@ -65703,7 +65771,7 @@
         <v>806</v>
       </c>
       <c r="J1247" s="63" t="s">
-        <v>3611</v>
+        <v>3610</v>
       </c>
       <c r="K1247">
         <v>1248</v>
@@ -65712,7 +65780,7 @@
         <v>854</v>
       </c>
       <c r="N1247" t="s">
-        <v>3631</v>
+        <v>3630</v>
       </c>
     </row>
     <row r="1248" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65723,7 +65791,7 @@
         <v>12259407</v>
       </c>
       <c r="C1248" t="s">
-        <v>3534</v>
+        <v>3533</v>
       </c>
       <c r="D1248" t="s">
         <v>60</v>
@@ -65744,7 +65812,7 @@
         <v>806</v>
       </c>
       <c r="J1248" s="63" t="s">
-        <v>3613</v>
+        <v>3612</v>
       </c>
       <c r="K1248">
         <v>1249</v>
@@ -65753,7 +65821,7 @@
         <v>854</v>
       </c>
       <c r="N1248" t="s">
-        <v>3632</v>
+        <v>3631</v>
       </c>
     </row>
     <row r="1249" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65764,7 +65832,7 @@
         <v>14403585</v>
       </c>
       <c r="C1249" t="s">
-        <v>3615</v>
+        <v>3614</v>
       </c>
       <c r="D1249" t="s">
         <v>424</v>
@@ -65785,7 +65853,7 @@
         <v>806</v>
       </c>
       <c r="J1249" s="63" t="s">
-        <v>3614</v>
+        <v>3613</v>
       </c>
       <c r="K1249">
         <v>1250</v>
@@ -65794,7 +65862,7 @@
         <v>854</v>
       </c>
       <c r="N1249" t="s">
-        <v>3633</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="1250" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65805,7 +65873,7 @@
         <v>11846355</v>
       </c>
       <c r="C1250" t="s">
-        <v>3616</v>
+        <v>3615</v>
       </c>
       <c r="D1250" t="s">
         <v>35</v>
@@ -65820,13 +65888,13 @@
         <v>8.4108796296296293E-2</v>
       </c>
       <c r="H1250" t="s">
+        <v>3616</v>
+      </c>
+      <c r="I1250" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1250" s="63" t="s">
         <v>3617</v>
-      </c>
-      <c r="I1250" t="s">
-        <v>806</v>
-      </c>
-      <c r="J1250" s="63" t="s">
-        <v>3618</v>
       </c>
       <c r="K1250">
         <v>1251</v>
@@ -65835,7 +65903,7 @@
         <v>854</v>
       </c>
       <c r="N1250" t="s">
-        <v>3634</v>
+        <v>3633</v>
       </c>
     </row>
     <row r="1251" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65846,7 +65914,7 @@
         <v>26285296</v>
       </c>
       <c r="C1251" t="s">
-        <v>3620</v>
+        <v>3619</v>
       </c>
       <c r="D1251" t="s">
         <v>60</v>
@@ -65867,7 +65935,7 @@
         <v>806</v>
       </c>
       <c r="J1251" s="63" t="s">
-        <v>3619</v>
+        <v>3618</v>
       </c>
       <c r="K1251">
         <v>1252</v>
@@ -65876,7 +65944,7 @@
         <v>854</v>
       </c>
       <c r="N1251" t="s">
-        <v>3635</v>
+        <v>3634</v>
       </c>
     </row>
     <row r="1252" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65908,7 +65976,7 @@
         <v>806</v>
       </c>
       <c r="J1252" s="63" t="s">
-        <v>3621</v>
+        <v>3620</v>
       </c>
       <c r="K1252">
         <v>1253</v>
@@ -65917,7 +65985,7 @@
         <v>854</v>
       </c>
       <c r="N1252" t="s">
-        <v>3636</v>
+        <v>3635</v>
       </c>
     </row>
     <row r="1253" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65943,13 +66011,13 @@
         <v>502</v>
       </c>
       <c r="H1253" t="s">
+        <v>3621</v>
+      </c>
+      <c r="I1253" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1253" s="63" t="s">
         <v>3622</v>
-      </c>
-      <c r="I1253" t="s">
-        <v>806</v>
-      </c>
-      <c r="J1253" s="63" t="s">
-        <v>3623</v>
       </c>
       <c r="K1253">
         <v>1254</v>
@@ -65958,7 +66026,7 @@
         <v>854</v>
       </c>
       <c r="N1253" t="s">
-        <v>3637</v>
+        <v>3636</v>
       </c>
     </row>
     <row r="1254" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65969,7 +66037,7 @@
         <v>10868943</v>
       </c>
       <c r="C1254" t="s">
-        <v>3625</v>
+        <v>3624</v>
       </c>
       <c r="D1254" t="s">
         <v>15</v>
@@ -65990,7 +66058,7 @@
         <v>806</v>
       </c>
       <c r="J1254" s="63" t="s">
-        <v>3624</v>
+        <v>3623</v>
       </c>
       <c r="K1254">
         <v>1255</v>
@@ -65999,7 +66067,7 @@
         <v>854</v>
       </c>
       <c r="N1254" t="s">
-        <v>3638</v>
+        <v>3637</v>
       </c>
     </row>
     <row r="1255" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66010,7 +66078,7 @@
         <v>11939361</v>
       </c>
       <c r="C1255" t="s">
-        <v>3627</v>
+        <v>3626</v>
       </c>
       <c r="D1255" t="s">
         <v>15</v>
@@ -66025,13 +66093,13 @@
         <v>0.11023148148148149</v>
       </c>
       <c r="H1255" t="s">
-        <v>3622</v>
+        <v>3621</v>
       </c>
       <c r="I1255" t="s">
         <v>806</v>
       </c>
       <c r="J1255" s="63" t="s">
-        <v>3626</v>
+        <v>3625</v>
       </c>
       <c r="K1255">
         <v>1256</v>
@@ -66040,7 +66108,7 @@
         <v>854</v>
       </c>
       <c r="N1255" t="s">
-        <v>3639</v>
+        <v>3638</v>
       </c>
     </row>
     <row r="1256" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66051,7 +66119,7 @@
         <v>11773223</v>
       </c>
       <c r="C1256" t="s">
-        <v>3534</v>
+        <v>3533</v>
       </c>
       <c r="D1256" t="s">
         <v>463</v>
@@ -66072,7 +66140,7 @@
         <v>806</v>
       </c>
       <c r="J1256" s="63" t="s">
-        <v>3641</v>
+        <v>3640</v>
       </c>
       <c r="K1256">
         <v>1257</v>
@@ -66081,7 +66149,7 @@
         <v>854</v>
       </c>
       <c r="N1256" t="s">
-        <v>3642</v>
+        <v>3641</v>
       </c>
     </row>
     <row r="1257" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66092,10 +66160,10 @@
         <v>3039493</v>
       </c>
       <c r="C1257" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
       <c r="D1257" t="s">
-        <v>3643</v>
+        <v>3642</v>
       </c>
       <c r="E1257" t="s">
         <v>433</v>
@@ -66113,7 +66181,7 @@
         <v>290</v>
       </c>
       <c r="J1257" s="63" t="s">
-        <v>3644</v>
+        <v>3643</v>
       </c>
       <c r="K1257">
         <v>1258</v>
@@ -66122,7 +66190,7 @@
         <v>854</v>
       </c>
       <c r="N1257" t="s">
-        <v>3656</v>
+        <v>3655</v>
       </c>
     </row>
     <row r="1258" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66154,7 +66222,7 @@
         <v>290</v>
       </c>
       <c r="J1258" s="63" t="s">
-        <v>3645</v>
+        <v>3644</v>
       </c>
       <c r="K1258">
         <v>1259</v>
@@ -66163,7 +66231,7 @@
         <v>854</v>
       </c>
       <c r="N1258" t="s">
-        <v>3657</v>
+        <v>3656</v>
       </c>
     </row>
     <row r="1259" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66174,10 +66242,10 @@
         <v>2009695</v>
       </c>
       <c r="C1259" t="s">
-        <v>3595</v>
+        <v>3594</v>
       </c>
       <c r="D1259" t="s">
-        <v>3647</v>
+        <v>3646</v>
       </c>
       <c r="E1259" t="s">
         <v>433</v>
@@ -66195,7 +66263,7 @@
         <v>290</v>
       </c>
       <c r="J1259" s="63" t="s">
-        <v>3646</v>
+        <v>3645</v>
       </c>
       <c r="K1259">
         <v>1260</v>
@@ -66204,7 +66272,7 @@
         <v>854</v>
       </c>
       <c r="N1259" t="s">
-        <v>3658</v>
+        <v>3657</v>
       </c>
     </row>
     <row r="1260" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66215,7 +66283,7 @@
         <v>5275387</v>
       </c>
       <c r="C1260" t="s">
-        <v>3648</v>
+        <v>3647</v>
       </c>
       <c r="D1260" t="s">
         <v>1719</v>
@@ -66230,13 +66298,13 @@
         <v>5.4467592592592595E-2</v>
       </c>
       <c r="H1260" t="s">
-        <v>3649</v>
+        <v>3648</v>
       </c>
       <c r="I1260" t="s">
         <v>290</v>
       </c>
       <c r="J1260" s="63" t="s">
-        <v>3650</v>
+        <v>3649</v>
       </c>
       <c r="K1260">
         <v>1261</v>
@@ -66245,7 +66313,7 @@
         <v>854</v>
       </c>
       <c r="N1260" t="s">
-        <v>3659</v>
+        <v>3658</v>
       </c>
     </row>
     <row r="1261" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66256,13 +66324,13 @@
         <v>17490000</v>
       </c>
       <c r="C1261" t="s">
-        <v>3652</v>
+        <v>3651</v>
       </c>
       <c r="D1261" t="s">
         <v>54</v>
       </c>
       <c r="E1261" t="s">
-        <v>3652</v>
+        <v>3651</v>
       </c>
       <c r="F1261" s="29">
         <v>46090</v>
@@ -66277,7 +66345,7 @@
         <v>806</v>
       </c>
       <c r="J1261" s="63" t="s">
-        <v>3651</v>
+        <v>3650</v>
       </c>
       <c r="K1261">
         <v>1262</v>
@@ -66286,7 +66354,7 @@
         <v>854</v>
       </c>
       <c r="N1261" t="s">
-        <v>3660</v>
+        <v>3659</v>
       </c>
     </row>
     <row r="1262" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66318,7 +66386,7 @@
         <v>813</v>
       </c>
       <c r="J1262" s="63" t="s">
-        <v>3653</v>
+        <v>3652</v>
       </c>
       <c r="K1262">
         <v>1263</v>
@@ -66327,7 +66395,7 @@
         <v>854</v>
       </c>
       <c r="N1262" t="s">
-        <v>3661</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="1263" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66359,7 +66427,7 @@
         <v>813</v>
       </c>
       <c r="J1263" s="63" t="s">
-        <v>3654</v>
+        <v>3653</v>
       </c>
       <c r="K1263">
         <v>1264</v>
@@ -66368,7 +66436,7 @@
         <v>854</v>
       </c>
       <c r="N1263" t="s">
-        <v>3662</v>
+        <v>3661</v>
       </c>
     </row>
     <row r="1264" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66400,7 +66468,7 @@
         <v>290</v>
       </c>
       <c r="J1264" s="63" t="s">
-        <v>3655</v>
+        <v>3654</v>
       </c>
       <c r="K1264">
         <v>1265</v>
@@ -66409,7 +66477,7 @@
         <v>854</v>
       </c>
       <c r="N1264" t="s">
-        <v>3663</v>
+        <v>3662</v>
       </c>
     </row>
     <row r="1265" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66435,13 +66503,13 @@
         <v>0.11001157407407407</v>
       </c>
       <c r="H1265" t="s">
-        <v>3668</v>
+        <v>3667</v>
       </c>
       <c r="I1265" t="s">
         <v>290</v>
       </c>
       <c r="J1265" s="63" t="s">
-        <v>3664</v>
+        <v>3663</v>
       </c>
       <c r="K1265">
         <v>1266</v>
@@ -66450,7 +66518,7 @@
         <v>854</v>
       </c>
       <c r="N1265" t="s">
-        <v>3670</v>
+        <v>3669</v>
       </c>
     </row>
     <row r="1266" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66482,7 +66550,7 @@
         <v>290</v>
       </c>
       <c r="J1266" s="63" t="s">
-        <v>3665</v>
+        <v>3664</v>
       </c>
       <c r="K1266">
         <v>1267</v>
@@ -66491,7 +66559,7 @@
         <v>854</v>
       </c>
       <c r="N1266" t="s">
-        <v>3671</v>
+        <v>3670</v>
       </c>
     </row>
     <row r="1267" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66523,7 +66591,7 @@
         <v>290</v>
       </c>
       <c r="J1267" s="63" t="s">
-        <v>3666</v>
+        <v>3665</v>
       </c>
       <c r="K1267">
         <v>1268</v>
@@ -66532,7 +66600,7 @@
         <v>854</v>
       </c>
       <c r="N1267" t="s">
-        <v>3672</v>
+        <v>3671</v>
       </c>
     </row>
     <row r="1268" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66546,7 +66614,7 @@
         <v>25</v>
       </c>
       <c r="D1268" t="s">
-        <v>3669</v>
+        <v>3668</v>
       </c>
       <c r="E1268" t="s">
         <v>3429</v>
@@ -66564,7 +66632,7 @@
         <v>290</v>
       </c>
       <c r="J1268" s="63" t="s">
-        <v>3667</v>
+        <v>3666</v>
       </c>
       <c r="K1268">
         <v>1269</v>
@@ -66573,7 +66641,7 @@
         <v>854</v>
       </c>
       <c r="N1268" t="s">
-        <v>3673</v>
+        <v>3672</v>
       </c>
     </row>
     <row r="1269" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66605,7 +66673,7 @@
         <v>290</v>
       </c>
       <c r="J1269" s="63" t="s">
-        <v>3674</v>
+        <v>3673</v>
       </c>
       <c r="K1269">
         <v>1270</v>
@@ -66614,7 +66682,7 @@
         <v>854</v>
       </c>
       <c r="N1269" t="s">
-        <v>3680</v>
+        <v>3679</v>
       </c>
     </row>
     <row r="1270" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66625,13 +66693,13 @@
         <v>12357428</v>
       </c>
       <c r="C1270" t="s">
-        <v>3675</v>
+        <v>3674</v>
       </c>
       <c r="D1270" t="s">
         <v>283</v>
       </c>
       <c r="E1270" t="s">
-        <v>3675</v>
+        <v>3674</v>
       </c>
       <c r="F1270" s="29">
         <v>46098</v>
@@ -66646,7 +66714,7 @@
         <v>290</v>
       </c>
       <c r="J1270" s="63" t="s">
-        <v>3676</v>
+        <v>3675</v>
       </c>
       <c r="K1270">
         <v>1271</v>
@@ -66655,7 +66723,7 @@
         <v>854</v>
       </c>
       <c r="N1270" t="s">
-        <v>3681</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="1271" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66687,7 +66755,7 @@
         <v>290</v>
       </c>
       <c r="J1271" s="63" t="s">
-        <v>3677</v>
+        <v>3676</v>
       </c>
       <c r="K1271">
         <v>1272</v>
@@ -66696,7 +66764,7 @@
         <v>854</v>
       </c>
       <c r="N1271" t="s">
-        <v>3682</v>
+        <v>3681</v>
       </c>
     </row>
     <row r="1272" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66707,7 +66775,7 @@
         <v>20655781</v>
       </c>
       <c r="C1272" t="s">
-        <v>3534</v>
+        <v>3533</v>
       </c>
       <c r="D1272" t="s">
         <v>13</v>
@@ -66722,13 +66790,13 @@
         <v>0.11376157407407407</v>
       </c>
       <c r="H1272" t="s">
-        <v>3679</v>
+        <v>3678</v>
       </c>
       <c r="I1272" t="s">
         <v>806</v>
       </c>
       <c r="J1272" s="63" t="s">
-        <v>3678</v>
+        <v>3677</v>
       </c>
       <c r="K1272">
         <v>1273</v>
@@ -66737,7 +66805,7 @@
         <v>854</v>
       </c>
       <c r="N1272" t="s">
-        <v>3683</v>
+        <v>3682</v>
       </c>
     </row>
     <row r="1273" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66748,7 +66816,7 @@
         <v>15637601</v>
       </c>
       <c r="C1273" t="s">
-        <v>3684</v>
+        <v>3683</v>
       </c>
       <c r="D1273" t="s">
         <v>364</v>
@@ -66769,7 +66837,7 @@
         <v>806</v>
       </c>
       <c r="J1273" s="63" t="s">
-        <v>3685</v>
+        <v>3684</v>
       </c>
       <c r="K1273">
         <v>1274</v>
@@ -66778,7 +66846,7 @@
         <v>854</v>
       </c>
       <c r="N1273" t="s">
-        <v>3693</v>
+        <v>3692</v>
       </c>
     </row>
     <row r="1274" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66810,7 +66878,7 @@
         <v>813</v>
       </c>
       <c r="J1274" s="63" t="s">
-        <v>3686</v>
+        <v>3685</v>
       </c>
       <c r="K1274">
         <v>1275</v>
@@ -66819,7 +66887,7 @@
         <v>854</v>
       </c>
       <c r="N1274" t="s">
-        <v>3694</v>
+        <v>3693</v>
       </c>
     </row>
     <row r="1275" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66830,7 +66898,7 @@
         <v>10019685</v>
       </c>
       <c r="C1275" t="s">
-        <v>3534</v>
+        <v>3533</v>
       </c>
       <c r="D1275" t="s">
         <v>463</v>
@@ -66851,7 +66919,7 @@
         <v>806</v>
       </c>
       <c r="J1275" s="63" t="s">
-        <v>3687</v>
+        <v>3686</v>
       </c>
       <c r="K1275">
         <v>1276</v>
@@ -66860,7 +66928,7 @@
         <v>854</v>
       </c>
       <c r="N1275" t="s">
-        <v>3695</v>
+        <v>3694</v>
       </c>
     </row>
     <row r="1276" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66871,7 +66939,7 @@
         <v>24416863</v>
       </c>
       <c r="C1276" t="s">
-        <v>3534</v>
+        <v>3533</v>
       </c>
       <c r="D1276" t="s">
         <v>74</v>
@@ -66892,7 +66960,7 @@
         <v>806</v>
       </c>
       <c r="J1276" s="63" t="s">
-        <v>3688</v>
+        <v>3687</v>
       </c>
       <c r="K1276">
         <v>1277</v>
@@ -66901,7 +66969,7 @@
         <v>854</v>
       </c>
       <c r="N1276" t="s">
-        <v>3696</v>
+        <v>3695</v>
       </c>
     </row>
     <row r="1277" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66912,7 +66980,7 @@
         <v>20390911</v>
       </c>
       <c r="C1277" t="s">
-        <v>3534</v>
+        <v>3533</v>
       </c>
       <c r="D1277" t="s">
         <v>40</v>
@@ -66933,7 +67001,7 @@
         <v>806</v>
       </c>
       <c r="J1277" s="63" t="s">
-        <v>3689</v>
+        <v>3688</v>
       </c>
       <c r="K1277">
         <v>1278</v>
@@ -66942,7 +67010,7 @@
         <v>854</v>
       </c>
       <c r="N1277" t="s">
-        <v>3697</v>
+        <v>3696</v>
       </c>
     </row>
     <row r="1278" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -66953,7 +67021,7 @@
         <v>36572979</v>
       </c>
       <c r="C1278" t="s">
-        <v>3534</v>
+        <v>3533</v>
       </c>
       <c r="D1278" t="s">
         <v>9</v>
@@ -66974,7 +67042,7 @@
         <v>806</v>
       </c>
       <c r="J1278" s="63" t="s">
-        <v>3690</v>
+        <v>3689</v>
       </c>
       <c r="K1278">
         <v>1279</v>
@@ -66983,7 +67051,7 @@
         <v>854</v>
       </c>
       <c r="N1278" t="s">
-        <v>3698</v>
+        <v>3697</v>
       </c>
     </row>
     <row r="1279" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67009,13 +67077,13 @@
         <v>8.5636574074074087E-2</v>
       </c>
       <c r="H1279" t="s">
-        <v>3692</v>
+        <v>3691</v>
       </c>
       <c r="I1279" t="s">
         <v>806</v>
       </c>
       <c r="J1279" s="63" t="s">
-        <v>3691</v>
+        <v>3690</v>
       </c>
       <c r="K1279">
         <v>1280</v>
@@ -67024,7 +67092,7 @@
         <v>854</v>
       </c>
       <c r="N1279" t="s">
-        <v>3699</v>
+        <v>3698</v>
       </c>
     </row>
     <row r="1280" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67035,13 +67103,13 @@
         <v>2459104</v>
       </c>
       <c r="C1280" t="s">
-        <v>3706</v>
+        <v>3705</v>
       </c>
       <c r="D1280" t="s">
-        <v>3705</v>
+        <v>3704</v>
       </c>
       <c r="E1280" t="s">
-        <v>3741</v>
+        <v>3740</v>
       </c>
       <c r="F1280" s="29">
         <v>46102</v>
@@ -67056,7 +67124,7 @@
         <v>806</v>
       </c>
       <c r="J1280" s="63" t="s">
-        <v>3700</v>
+        <v>3699</v>
       </c>
       <c r="K1280">
         <v>1281</v>
@@ -67065,7 +67133,7 @@
         <v>854</v>
       </c>
       <c r="N1280" t="s">
-        <v>3727</v>
+        <v>3726</v>
       </c>
     </row>
     <row r="1281" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67079,7 +67147,7 @@
         <v>17</v>
       </c>
       <c r="D1281" t="s">
-        <v>3705</v>
+        <v>3704</v>
       </c>
       <c r="E1281" t="s">
         <v>18</v>
@@ -67091,13 +67159,13 @@
         <v>4.6192129629629632E-2</v>
       </c>
       <c r="H1281" t="s">
-        <v>3679</v>
+        <v>3678</v>
       </c>
       <c r="I1281" t="s">
         <v>806</v>
       </c>
       <c r="J1281" s="63" t="s">
-        <v>3701</v>
+        <v>3700</v>
       </c>
       <c r="K1281">
         <v>1282</v>
@@ -67106,7 +67174,7 @@
         <v>854</v>
       </c>
       <c r="N1281" t="s">
-        <v>3728</v>
+        <v>3727</v>
       </c>
     </row>
     <row r="1282" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67117,7 +67185,7 @@
         <v>38584884</v>
       </c>
       <c r="C1282" t="s">
-        <v>3707</v>
+        <v>3706</v>
       </c>
       <c r="D1282" t="s">
         <v>9</v>
@@ -67138,7 +67206,7 @@
         <v>806</v>
       </c>
       <c r="J1282" s="63" t="s">
-        <v>3702</v>
+        <v>3701</v>
       </c>
       <c r="K1282">
         <v>1283</v>
@@ -67147,7 +67215,7 @@
         <v>854</v>
       </c>
       <c r="N1282" t="s">
-        <v>3729</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="1283" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67158,7 +67226,7 @@
         <v>20008060</v>
       </c>
       <c r="C1283" t="s">
-        <v>3708</v>
+        <v>3707</v>
       </c>
       <c r="D1283" t="s">
         <v>15</v>
@@ -67179,7 +67247,7 @@
         <v>806</v>
       </c>
       <c r="J1283" s="63" t="s">
-        <v>3703</v>
+        <v>3702</v>
       </c>
       <c r="K1283">
         <v>1284</v>
@@ -67188,7 +67256,7 @@
         <v>854</v>
       </c>
       <c r="N1283" t="s">
-        <v>3730</v>
+        <v>3729</v>
       </c>
     </row>
     <row r="1284" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67199,7 +67267,7 @@
         <v>6665326</v>
       </c>
       <c r="C1284" t="s">
-        <v>3709</v>
+        <v>3708</v>
       </c>
       <c r="D1284" t="s">
         <v>338</v>
@@ -67220,7 +67288,7 @@
         <v>806</v>
       </c>
       <c r="J1284" s="63" t="s">
-        <v>3704</v>
+        <v>3703</v>
       </c>
       <c r="K1284">
         <v>1285</v>
@@ -67229,7 +67297,7 @@
         <v>854</v>
       </c>
       <c r="N1284" t="s">
-        <v>3731</v>
+        <v>3730</v>
       </c>
     </row>
     <row r="1285" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67240,7 +67308,7 @@
         <v>14678575</v>
       </c>
       <c r="C1285" t="s">
-        <v>3710</v>
+        <v>3709</v>
       </c>
       <c r="D1285" t="s">
         <v>15</v>
@@ -67261,7 +67329,7 @@
         <v>806</v>
       </c>
       <c r="J1285" s="63" t="s">
-        <v>3711</v>
+        <v>3710</v>
       </c>
       <c r="K1285">
         <v>1286</v>
@@ -67270,7 +67338,7 @@
         <v>854</v>
       </c>
       <c r="N1285" t="s">
-        <v>3732</v>
+        <v>3731</v>
       </c>
     </row>
     <row r="1286" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67302,7 +67370,7 @@
         <v>806</v>
       </c>
       <c r="J1286" s="63" t="s">
-        <v>3712</v>
+        <v>3711</v>
       </c>
       <c r="K1286">
         <v>1287</v>
@@ -67311,7 +67379,7 @@
         <v>854</v>
       </c>
       <c r="N1286" t="s">
-        <v>3733</v>
+        <v>3732</v>
       </c>
     </row>
     <row r="1287" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67322,7 +67390,7 @@
         <v>15035249</v>
       </c>
       <c r="C1287" t="s">
-        <v>3714</v>
+        <v>3713</v>
       </c>
       <c r="D1287" t="s">
         <v>445</v>
@@ -67343,7 +67411,7 @@
         <v>806</v>
       </c>
       <c r="J1287" s="63" t="s">
-        <v>3713</v>
+        <v>3712</v>
       </c>
       <c r="K1287">
         <v>1288</v>
@@ -67352,7 +67420,7 @@
         <v>854</v>
       </c>
       <c r="N1287" t="s">
-        <v>3734</v>
+        <v>3733</v>
       </c>
     </row>
     <row r="1288" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67378,13 +67446,13 @@
         <v>0.1292939814814815</v>
       </c>
       <c r="H1288" t="s">
+        <v>3714</v>
+      </c>
+      <c r="I1288" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1288" s="63" t="s">
         <v>3715</v>
-      </c>
-      <c r="I1288" t="s">
-        <v>806</v>
-      </c>
-      <c r="J1288" s="63" t="s">
-        <v>3716</v>
       </c>
       <c r="K1288">
         <v>1289</v>
@@ -67393,7 +67461,7 @@
         <v>854</v>
       </c>
       <c r="N1288" t="s">
-        <v>3735</v>
+        <v>3734</v>
       </c>
     </row>
     <row r="1289" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67407,7 +67475,7 @@
         <v>214</v>
       </c>
       <c r="D1289" t="s">
-        <v>3718</v>
+        <v>3717</v>
       </c>
       <c r="E1289" t="s">
         <v>51</v>
@@ -67425,7 +67493,7 @@
         <v>806</v>
       </c>
       <c r="J1289" s="63" t="s">
-        <v>3717</v>
+        <v>3716</v>
       </c>
       <c r="K1289">
         <v>1290</v>
@@ -67434,7 +67502,7 @@
         <v>854</v>
       </c>
       <c r="N1289" t="s">
-        <v>3736</v>
+        <v>3735</v>
       </c>
     </row>
     <row r="1290" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67448,7 +67516,7 @@
         <v>17</v>
       </c>
       <c r="D1290" t="s">
-        <v>3722</v>
+        <v>3721</v>
       </c>
       <c r="E1290" t="s">
         <v>18</v>
@@ -67466,7 +67534,7 @@
         <v>806</v>
       </c>
       <c r="J1290" s="63" t="s">
-        <v>3719</v>
+        <v>3718</v>
       </c>
       <c r="K1290">
         <v>1291</v>
@@ -67475,7 +67543,7 @@
         <v>854</v>
       </c>
       <c r="N1290" t="s">
-        <v>3737</v>
+        <v>3736</v>
       </c>
     </row>
     <row r="1291" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67507,7 +67575,7 @@
         <v>806</v>
       </c>
       <c r="J1291" s="63" t="s">
-        <v>3720</v>
+        <v>3719</v>
       </c>
       <c r="K1291">
         <v>1292</v>
@@ -67516,7 +67584,7 @@
         <v>854</v>
       </c>
       <c r="N1291" t="s">
-        <v>3738</v>
+        <v>3737</v>
       </c>
     </row>
     <row r="1292" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67542,13 +67610,13 @@
         <v>502</v>
       </c>
       <c r="H1292" t="s">
-        <v>3723</v>
+        <v>3722</v>
       </c>
       <c r="I1292" t="s">
         <v>806</v>
       </c>
       <c r="J1292" s="63" t="s">
-        <v>3721</v>
+        <v>3720</v>
       </c>
       <c r="K1292">
         <v>1293</v>
@@ -67557,7 +67625,7 @@
         <v>854</v>
       </c>
       <c r="N1292" t="s">
-        <v>3739</v>
+        <v>3738</v>
       </c>
     </row>
     <row r="1293" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67568,10 +67636,10 @@
         <v>6886047</v>
       </c>
       <c r="C1293" t="s">
-        <v>3724</v>
+        <v>3723</v>
       </c>
       <c r="D1293" t="s">
-        <v>3718</v>
+        <v>3717</v>
       </c>
       <c r="E1293" t="s">
         <v>51</v>
@@ -67583,13 +67651,13 @@
         <v>4.3784722222222218E-2</v>
       </c>
       <c r="H1293" t="s">
+        <v>3724</v>
+      </c>
+      <c r="I1293" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1293" s="63" t="s">
         <v>3725</v>
-      </c>
-      <c r="I1293" t="s">
-        <v>806</v>
-      </c>
-      <c r="J1293" s="63" t="s">
-        <v>3726</v>
       </c>
       <c r="K1293">
         <v>1294</v>
@@ -67598,7 +67666,7 @@
         <v>854</v>
       </c>
       <c r="N1293" t="s">
-        <v>3740</v>
+        <v>3739</v>
       </c>
     </row>
     <row r="1294" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67609,10 +67677,10 @@
         <v>1778128</v>
       </c>
       <c r="C1294" t="s">
+        <v>3742</v>
+      </c>
+      <c r="D1294" t="s">
         <v>3743</v>
-      </c>
-      <c r="D1294" t="s">
-        <v>3744</v>
       </c>
       <c r="E1294" t="s">
         <v>218</v>
@@ -67624,13 +67692,13 @@
         <v>6.6203703703703709E-2</v>
       </c>
       <c r="H1294" t="s">
-        <v>3745</v>
+        <v>3744</v>
       </c>
       <c r="I1294" t="s">
         <v>806</v>
       </c>
       <c r="J1294" s="63" t="s">
-        <v>3742</v>
+        <v>3741</v>
       </c>
       <c r="K1294">
         <v>1295</v>
@@ -67639,7 +67707,7 @@
         <v>854</v>
       </c>
       <c r="N1294" t="s">
-        <v>3746</v>
+        <v>3745</v>
       </c>
     </row>
     <row r="1295" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67653,7 +67721,7 @@
         <v>32</v>
       </c>
       <c r="D1295" t="s">
-        <v>3748</v>
+        <v>3747</v>
       </c>
       <c r="E1295" t="s">
         <v>29</v>
@@ -67671,7 +67739,7 @@
         <v>806</v>
       </c>
       <c r="J1295" s="63" t="s">
-        <v>3747</v>
+        <v>3746</v>
       </c>
       <c r="K1295">
         <v>1296</v>
@@ -67680,7 +67748,7 @@
         <v>854</v>
       </c>
       <c r="N1295" t="s">
-        <v>3749</v>
+        <v>3748</v>
       </c>
     </row>
     <row r="1296" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67694,7 +67762,7 @@
         <v>32</v>
       </c>
       <c r="D1296" t="s">
-        <v>3750</v>
+        <v>3749</v>
       </c>
       <c r="E1296" t="s">
         <v>29</v>
@@ -67712,7 +67780,7 @@
         <v>806</v>
       </c>
       <c r="J1296" s="63" t="s">
-        <v>3751</v>
+        <v>3750</v>
       </c>
       <c r="K1296">
         <v>1297</v>
@@ -67721,7 +67789,7 @@
         <v>854</v>
       </c>
       <c r="N1296" t="s">
-        <v>3757</v>
+        <v>3756</v>
       </c>
     </row>
     <row r="1297" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67747,13 +67815,13 @@
         <v>3.6064814814814813E-2</v>
       </c>
       <c r="H1297" t="s">
-        <v>3753</v>
+        <v>3752</v>
       </c>
       <c r="I1297" t="s">
         <v>806</v>
       </c>
       <c r="J1297" s="63" t="s">
-        <v>3752</v>
+        <v>3751</v>
       </c>
       <c r="K1297">
         <v>1298</v>
@@ -67762,7 +67830,7 @@
         <v>854</v>
       </c>
       <c r="N1297" t="s">
-        <v>3758</v>
+        <v>3757</v>
       </c>
     </row>
     <row r="1298" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67788,13 +67856,13 @@
         <v>9.1122685185185182E-2</v>
       </c>
       <c r="H1298" t="s">
+        <v>3753</v>
+      </c>
+      <c r="I1298" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1298" s="63" t="s">
         <v>3754</v>
-      </c>
-      <c r="I1298" t="s">
-        <v>806</v>
-      </c>
-      <c r="J1298" s="63" t="s">
-        <v>3755</v>
       </c>
       <c r="K1298">
         <v>1299</v>
@@ -67803,7 +67871,7 @@
         <v>854</v>
       </c>
       <c r="N1298" t="s">
-        <v>3759</v>
+        <v>3758</v>
       </c>
     </row>
     <row r="1299" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67814,7 +67882,7 @@
         <v>25358803</v>
       </c>
       <c r="C1299" t="s">
-        <v>3534</v>
+        <v>3533</v>
       </c>
       <c r="D1299" t="s">
         <v>424</v>
@@ -67835,7 +67903,7 @@
         <v>806</v>
       </c>
       <c r="J1299" s="63" t="s">
-        <v>3756</v>
+        <v>3755</v>
       </c>
       <c r="K1299">
         <v>1300</v>
@@ -67844,7 +67912,7 @@
         <v>854</v>
       </c>
       <c r="N1299" t="s">
-        <v>3760</v>
+        <v>3759</v>
       </c>
     </row>
     <row r="1300" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67858,7 +67926,7 @@
         <v>440</v>
       </c>
       <c r="D1300" t="s">
-        <v>3765</v>
+        <v>3764</v>
       </c>
       <c r="E1300" t="s">
         <v>433</v>
@@ -67870,13 +67938,13 @@
         <v>6.4432870370370363E-2</v>
       </c>
       <c r="H1300" t="s">
-        <v>3761</v>
+        <v>3760</v>
       </c>
       <c r="I1300" t="s">
         <v>290</v>
       </c>
       <c r="J1300" s="63" t="s">
-        <v>3762</v>
+        <v>3761</v>
       </c>
       <c r="K1300">
         <v>1301</v>
@@ -67885,7 +67953,7 @@
         <v>854</v>
       </c>
       <c r="N1300" t="s">
-        <v>3769</v>
+        <v>3768</v>
       </c>
     </row>
     <row r="1301" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67899,7 +67967,7 @@
         <v>440</v>
       </c>
       <c r="D1301" t="s">
-        <v>3766</v>
+        <v>3765</v>
       </c>
       <c r="E1301" t="s">
         <v>433</v>
@@ -67917,7 +67985,7 @@
         <v>290</v>
       </c>
       <c r="J1301" s="63" t="s">
-        <v>3763</v>
+        <v>3762</v>
       </c>
       <c r="K1301">
         <v>1302</v>
@@ -67926,7 +67994,7 @@
         <v>854</v>
       </c>
       <c r="N1301" t="s">
-        <v>3770</v>
+        <v>3769</v>
       </c>
     </row>
     <row r="1302" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67940,7 +68008,7 @@
         <v>440</v>
       </c>
       <c r="D1302" t="s">
-        <v>3767</v>
+        <v>3766</v>
       </c>
       <c r="E1302" t="s">
         <v>433</v>
@@ -67952,13 +68020,13 @@
         <v>5.5960648148148141E-2</v>
       </c>
       <c r="H1302" t="s">
-        <v>3768</v>
+        <v>3767</v>
       </c>
       <c r="I1302" t="s">
         <v>290</v>
       </c>
       <c r="J1302" s="63" t="s">
-        <v>3764</v>
+        <v>3763</v>
       </c>
       <c r="K1302">
         <v>1303</v>
@@ -67967,7 +68035,7 @@
         <v>854</v>
       </c>
       <c r="N1302" t="s">
-        <v>3771</v>
+        <v>3770</v>
       </c>
     </row>
     <row r="1303" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -67981,7 +68049,7 @@
         <v>25</v>
       </c>
       <c r="D1303" t="s">
-        <v>3777</v>
+        <v>3776</v>
       </c>
       <c r="E1303">
         <v>44100</v>
@@ -67999,7 +68067,7 @@
         <v>290</v>
       </c>
       <c r="J1303" s="63" t="s">
-        <v>3772</v>
+        <v>3771</v>
       </c>
       <c r="K1303">
         <v>1304</v>
@@ -68008,7 +68076,7 @@
         <v>854</v>
       </c>
       <c r="N1303" t="s">
-        <v>3786</v>
+        <v>3785</v>
       </c>
     </row>
     <row r="1304" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68022,7 +68090,7 @@
         <v>440</v>
       </c>
       <c r="D1304" t="s">
-        <v>3778</v>
+        <v>3777</v>
       </c>
       <c r="E1304" t="s">
         <v>433</v>
@@ -68040,7 +68108,7 @@
         <v>290</v>
       </c>
       <c r="J1304" s="63" t="s">
-        <v>3773</v>
+        <v>3772</v>
       </c>
       <c r="K1304">
         <v>1305</v>
@@ -68049,7 +68117,7 @@
         <v>854</v>
       </c>
       <c r="N1304" t="s">
-        <v>3787</v>
+        <v>3786</v>
       </c>
     </row>
     <row r="1305" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68063,7 +68131,7 @@
         <v>440</v>
       </c>
       <c r="D1305" t="s">
-        <v>3779</v>
+        <v>3778</v>
       </c>
       <c r="E1305" t="s">
         <v>433</v>
@@ -68081,7 +68149,7 @@
         <v>290</v>
       </c>
       <c r="J1305" s="63" t="s">
-        <v>3774</v>
+        <v>3773</v>
       </c>
       <c r="K1305">
         <v>1306</v>
@@ -68090,7 +68158,7 @@
         <v>854</v>
       </c>
       <c r="N1305" t="s">
-        <v>3788</v>
+        <v>3787</v>
       </c>
     </row>
     <row r="1306" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68101,7 +68169,7 @@
         <v>9033862</v>
       </c>
       <c r="C1306" t="s">
-        <v>3780</v>
+        <v>3779</v>
       </c>
       <c r="D1306" t="s">
         <v>406</v>
@@ -68122,7 +68190,7 @@
         <v>290</v>
       </c>
       <c r="J1306" s="63" t="s">
-        <v>3775</v>
+        <v>3774</v>
       </c>
       <c r="K1306">
         <v>1307</v>
@@ -68131,7 +68199,7 @@
         <v>854</v>
       </c>
       <c r="N1306" t="s">
-        <v>3789</v>
+        <v>3788</v>
       </c>
     </row>
     <row r="1307" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68163,7 +68231,7 @@
         <v>290</v>
       </c>
       <c r="J1307" s="63" t="s">
-        <v>3776</v>
+        <v>3775</v>
       </c>
       <c r="K1307">
         <v>1308</v>
@@ -68172,7 +68240,7 @@
         <v>854</v>
       </c>
       <c r="N1307" t="s">
-        <v>3790</v>
+        <v>3789</v>
       </c>
     </row>
     <row r="1308" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68186,7 +68254,7 @@
         <v>440</v>
       </c>
       <c r="D1308" t="s">
-        <v>3916</v>
+        <v>3915</v>
       </c>
       <c r="E1308" t="s">
         <v>433</v>
@@ -68204,7 +68272,7 @@
         <v>290</v>
       </c>
       <c r="J1308" s="63" t="s">
-        <v>3781</v>
+        <v>3780</v>
       </c>
       <c r="K1308">
         <v>1309</v>
@@ -68213,7 +68281,7 @@
         <v>854</v>
       </c>
       <c r="N1308" t="s">
-        <v>3791</v>
+        <v>3790</v>
       </c>
     </row>
     <row r="1309" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68227,7 +68295,7 @@
         <v>440</v>
       </c>
       <c r="D1309" t="s">
-        <v>3783</v>
+        <v>3782</v>
       </c>
       <c r="E1309" t="s">
         <v>433</v>
@@ -68239,13 +68307,13 @@
         <v>4.2546296296296297E-2</v>
       </c>
       <c r="H1309" t="s">
-        <v>3784</v>
+        <v>3783</v>
       </c>
       <c r="I1309" t="s">
         <v>290</v>
       </c>
       <c r="J1309" s="63" t="s">
-        <v>3782</v>
+        <v>3781</v>
       </c>
       <c r="K1309">
         <v>1310</v>
@@ -68254,7 +68322,7 @@
         <v>854</v>
       </c>
       <c r="N1309" t="s">
-        <v>3792</v>
+        <v>3791</v>
       </c>
     </row>
     <row r="1310" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68286,7 +68354,7 @@
         <v>806</v>
       </c>
       <c r="J1310" s="63" t="s">
-        <v>3785</v>
+        <v>3784</v>
       </c>
       <c r="K1310">
         <v>1311</v>
@@ -68295,7 +68363,7 @@
         <v>854</v>
       </c>
       <c r="N1310" t="s">
-        <v>3793</v>
+        <v>3792</v>
       </c>
     </row>
     <row r="1311" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68327,7 +68395,7 @@
         <v>806</v>
       </c>
       <c r="J1311" s="63" t="s">
-        <v>3794</v>
+        <v>3793</v>
       </c>
       <c r="K1311">
         <v>1312</v>
@@ -68336,7 +68404,7 @@
         <v>854</v>
       </c>
       <c r="N1311" t="s">
-        <v>3799</v>
+        <v>3798</v>
       </c>
     </row>
     <row r="1312" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68368,7 +68436,7 @@
         <v>806</v>
       </c>
       <c r="J1312" s="63" t="s">
-        <v>3795</v>
+        <v>3794</v>
       </c>
       <c r="K1312">
         <v>1313</v>
@@ -68377,7 +68445,7 @@
         <v>854</v>
       </c>
       <c r="N1312" t="s">
-        <v>3800</v>
+        <v>3799</v>
       </c>
     </row>
     <row r="1313" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68388,7 +68456,7 @@
         <v>15142034</v>
       </c>
       <c r="C1313" t="s">
-        <v>3797</v>
+        <v>3796</v>
       </c>
       <c r="D1313" t="s">
         <v>60</v>
@@ -68409,7 +68477,7 @@
         <v>806</v>
       </c>
       <c r="J1313" s="63" t="s">
-        <v>3796</v>
+        <v>3795</v>
       </c>
       <c r="K1313">
         <v>1314</v>
@@ -68418,7 +68486,7 @@
         <v>854</v>
       </c>
       <c r="N1313" t="s">
-        <v>3801</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="1314" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68450,7 +68518,7 @@
         <v>806</v>
       </c>
       <c r="J1314" s="63" t="s">
-        <v>3798</v>
+        <v>3797</v>
       </c>
       <c r="K1314">
         <v>1315</v>
@@ -68459,7 +68527,7 @@
         <v>854</v>
       </c>
       <c r="N1314" t="s">
-        <v>3802</v>
+        <v>3801</v>
       </c>
     </row>
     <row r="1315" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68491,7 +68559,7 @@
         <v>806</v>
       </c>
       <c r="J1315" s="63" t="s">
-        <v>3803</v>
+        <v>3802</v>
       </c>
       <c r="K1315">
         <v>1316</v>
@@ -68500,7 +68568,7 @@
         <v>854</v>
       </c>
       <c r="N1315" t="s">
-        <v>3829</v>
+        <v>3828</v>
       </c>
     </row>
     <row r="1316" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68532,7 +68600,7 @@
         <v>806</v>
       </c>
       <c r="J1316" s="63" t="s">
-        <v>3804</v>
+        <v>3803</v>
       </c>
       <c r="K1316">
         <v>1317</v>
@@ -68541,7 +68609,7 @@
         <v>854</v>
       </c>
       <c r="N1316" t="s">
-        <v>3830</v>
+        <v>3829</v>
       </c>
     </row>
     <row r="1317" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68552,7 +68620,7 @@
         <v>61493897</v>
       </c>
       <c r="C1317" t="s">
-        <v>3805</v>
+        <v>3804</v>
       </c>
       <c r="D1317" t="s">
         <v>15</v>
@@ -68573,7 +68641,7 @@
         <v>806</v>
       </c>
       <c r="J1317" s="63" t="s">
-        <v>3806</v>
+        <v>3805</v>
       </c>
       <c r="K1317">
         <v>1318</v>
@@ -68582,7 +68650,7 @@
         <v>854</v>
       </c>
       <c r="N1317" t="s">
-        <v>3831</v>
+        <v>3830</v>
       </c>
     </row>
     <row r="1318" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68596,7 +68664,7 @@
         <v>25</v>
       </c>
       <c r="D1318" t="s">
-        <v>3808</v>
+        <v>3807</v>
       </c>
       <c r="E1318" t="s">
         <v>3429</v>
@@ -68614,7 +68682,7 @@
         <v>806</v>
       </c>
       <c r="J1318" s="63" t="s">
-        <v>3807</v>
+        <v>3806</v>
       </c>
       <c r="K1318">
         <v>1319</v>
@@ -68623,7 +68691,7 @@
         <v>854</v>
       </c>
       <c r="N1318" t="s">
-        <v>3832</v>
+        <v>3831</v>
       </c>
     </row>
     <row r="1319" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68655,7 +68723,7 @@
         <v>806</v>
       </c>
       <c r="J1319" s="63" t="s">
-        <v>3809</v>
+        <v>3808</v>
       </c>
       <c r="K1319">
         <v>1320</v>
@@ -68664,7 +68732,7 @@
         <v>854</v>
       </c>
       <c r="N1319" t="s">
-        <v>3833</v>
+        <v>3832</v>
       </c>
     </row>
     <row r="1320" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68696,7 +68764,7 @@
         <v>806</v>
       </c>
       <c r="J1320" s="63" t="s">
-        <v>3810</v>
+        <v>3809</v>
       </c>
       <c r="K1320">
         <v>1321</v>
@@ -68705,7 +68773,7 @@
         <v>854</v>
       </c>
       <c r="N1320" t="s">
-        <v>3834</v>
+        <v>3833</v>
       </c>
     </row>
     <row r="1321" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68737,7 +68805,7 @@
         <v>806</v>
       </c>
       <c r="J1321" s="63" t="s">
-        <v>3811</v>
+        <v>3810</v>
       </c>
       <c r="K1321">
         <v>1322</v>
@@ -68746,7 +68814,7 @@
         <v>854</v>
       </c>
       <c r="N1321" t="s">
-        <v>3835</v>
+        <v>3834</v>
       </c>
     </row>
     <row r="1322" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68778,7 +68846,7 @@
         <v>806</v>
       </c>
       <c r="J1322" s="63" t="s">
-        <v>3812</v>
+        <v>3811</v>
       </c>
       <c r="K1322">
         <v>1323</v>
@@ -68787,7 +68855,7 @@
         <v>854</v>
       </c>
       <c r="N1322" t="s">
-        <v>3836</v>
+        <v>3835</v>
       </c>
     </row>
     <row r="1323" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68819,7 +68887,7 @@
         <v>806</v>
       </c>
       <c r="J1323" s="63" t="s">
-        <v>3813</v>
+        <v>3812</v>
       </c>
       <c r="K1323">
         <v>1324</v>
@@ -68828,7 +68896,7 @@
         <v>854</v>
       </c>
       <c r="N1323" t="s">
-        <v>3837</v>
+        <v>3836</v>
       </c>
     </row>
     <row r="1324" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68842,7 +68910,7 @@
         <v>4</v>
       </c>
       <c r="D1324" t="s">
-        <v>3816</v>
+        <v>3815</v>
       </c>
       <c r="E1324" t="s">
         <v>695</v>
@@ -68860,7 +68928,7 @@
         <v>806</v>
       </c>
       <c r="J1324" s="63" t="s">
-        <v>3814</v>
+        <v>3813</v>
       </c>
       <c r="K1324">
         <v>1325</v>
@@ -68869,7 +68937,7 @@
         <v>854</v>
       </c>
       <c r="N1324" t="s">
-        <v>3838</v>
+        <v>3837</v>
       </c>
     </row>
     <row r="1325" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68880,7 +68948,7 @@
         <v>8540141</v>
       </c>
       <c r="C1325" t="s">
-        <v>3780</v>
+        <v>3779</v>
       </c>
       <c r="D1325" t="s">
         <v>40</v>
@@ -68901,7 +68969,7 @@
         <v>806</v>
       </c>
       <c r="J1325" s="63" t="s">
-        <v>3815</v>
+        <v>3814</v>
       </c>
       <c r="K1325">
         <v>1326</v>
@@ -68910,7 +68978,7 @@
         <v>854</v>
       </c>
       <c r="N1325" t="s">
-        <v>3839</v>
+        <v>3838</v>
       </c>
     </row>
     <row r="1326" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68942,7 +69010,7 @@
         <v>806</v>
       </c>
       <c r="J1326" s="63" t="s">
-        <v>3817</v>
+        <v>3816</v>
       </c>
       <c r="K1326">
         <v>1327</v>
@@ -68951,7 +69019,7 @@
         <v>854</v>
       </c>
       <c r="N1326" t="s">
-        <v>3840</v>
+        <v>3839</v>
       </c>
     </row>
     <row r="1327" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -68977,13 +69045,13 @@
         <v>0.14083333333333334</v>
       </c>
       <c r="H1327" t="s">
-        <v>3822</v>
+        <v>3821</v>
       </c>
       <c r="I1327" t="s">
         <v>806</v>
       </c>
       <c r="J1327" s="63" t="s">
-        <v>3818</v>
+        <v>3817</v>
       </c>
       <c r="K1327">
         <v>1328</v>
@@ -68992,7 +69060,7 @@
         <v>854</v>
       </c>
       <c r="N1327" t="s">
-        <v>3841</v>
+        <v>3840</v>
       </c>
     </row>
     <row r="1328" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69024,7 +69092,7 @@
         <v>806</v>
       </c>
       <c r="J1328" s="63" t="s">
-        <v>3819</v>
+        <v>3818</v>
       </c>
       <c r="K1328">
         <v>1329</v>
@@ -69033,7 +69101,7 @@
         <v>854</v>
       </c>
       <c r="N1328" t="s">
-        <v>3842</v>
+        <v>3841</v>
       </c>
     </row>
     <row r="1329" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69065,7 +69133,7 @@
         <v>806</v>
       </c>
       <c r="J1329" s="63" t="s">
-        <v>3820</v>
+        <v>3819</v>
       </c>
       <c r="K1329">
         <v>1330</v>
@@ -69074,7 +69142,7 @@
         <v>854</v>
       </c>
       <c r="N1329" t="s">
-        <v>3843</v>
+        <v>3842</v>
       </c>
     </row>
     <row r="1330" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69106,7 +69174,7 @@
         <v>806</v>
       </c>
       <c r="J1330" s="63" t="s">
-        <v>3821</v>
+        <v>3820</v>
       </c>
       <c r="K1330">
         <v>1331</v>
@@ -69115,7 +69183,7 @@
         <v>854</v>
       </c>
       <c r="N1330" t="s">
-        <v>3844</v>
+        <v>3843</v>
       </c>
     </row>
     <row r="1331" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69129,7 +69197,7 @@
         <v>502</v>
       </c>
       <c r="D1331" t="s">
-        <v>3748</v>
+        <v>3747</v>
       </c>
       <c r="E1331" t="s">
         <v>209</v>
@@ -69147,7 +69215,7 @@
         <v>806</v>
       </c>
       <c r="J1331" s="63" t="s">
-        <v>3823</v>
+        <v>3822</v>
       </c>
       <c r="K1331">
         <v>1332</v>
@@ -69156,7 +69224,7 @@
         <v>854</v>
       </c>
       <c r="N1331" t="s">
-        <v>3845</v>
+        <v>3844</v>
       </c>
     </row>
     <row r="1332" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69188,7 +69256,7 @@
         <v>806</v>
       </c>
       <c r="J1332" s="63" t="s">
-        <v>3824</v>
+        <v>3823</v>
       </c>
       <c r="K1332">
         <v>1333</v>
@@ -69197,7 +69265,7 @@
         <v>854</v>
       </c>
       <c r="N1332" t="s">
-        <v>3846</v>
+        <v>3845</v>
       </c>
     </row>
     <row r="1333" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69208,13 +69276,13 @@
         <v>13298242</v>
       </c>
       <c r="C1333" t="s">
-        <v>3825</v>
+        <v>3824</v>
       </c>
       <c r="D1333" s="133" t="s">
         <v>1994</v>
       </c>
       <c r="E1333" s="137" t="s">
-        <v>3849</v>
+        <v>3848</v>
       </c>
       <c r="F1333" s="29">
         <v>46110</v>
@@ -69229,7 +69297,7 @@
         <v>806</v>
       </c>
       <c r="J1333" s="134" t="s">
-        <v>3826</v>
+        <v>3825</v>
       </c>
       <c r="K1333">
         <v>1334</v>
@@ -69238,7 +69306,7 @@
         <v>854</v>
       </c>
       <c r="N1333" t="s">
-        <v>3847</v>
+        <v>3846</v>
       </c>
     </row>
     <row r="1334" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69252,7 +69320,7 @@
         <v>17</v>
       </c>
       <c r="D1334" s="135" t="s">
-        <v>3828</v>
+        <v>3827</v>
       </c>
       <c r="E1334" s="135" t="s">
         <v>18</v>
@@ -69270,7 +69338,7 @@
         <v>806</v>
       </c>
       <c r="J1334" s="136" t="s">
-        <v>3827</v>
+        <v>3826</v>
       </c>
       <c r="K1334">
         <v>1335</v>
@@ -69279,7 +69347,7 @@
         <v>854</v>
       </c>
       <c r="N1334" t="s">
-        <v>3848</v>
+        <v>3847</v>
       </c>
     </row>
     <row r="1335" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69290,7 +69358,7 @@
         <v>14527446</v>
       </c>
       <c r="C1335" t="s">
-        <v>3853</v>
+        <v>3852</v>
       </c>
       <c r="D1335" s="137" t="s">
         <v>15</v>
@@ -69305,25 +69373,25 @@
         <v>8.4050925925925932E-2</v>
       </c>
       <c r="H1335" s="137" t="s">
-        <v>3852</v>
+        <v>3851</v>
       </c>
       <c r="I1335" s="137" t="s">
         <v>806</v>
       </c>
       <c r="J1335" s="63" t="s">
-        <v>3851</v>
+        <v>3850</v>
       </c>
       <c r="K1335">
         <v>1336</v>
       </c>
       <c r="L1335" t="s">
-        <v>3850</v>
+        <v>3849</v>
       </c>
       <c r="M1335" s="57" t="s">
         <v>854</v>
       </c>
       <c r="N1335" t="s">
-        <v>3854</v>
+        <v>3853</v>
       </c>
     </row>
     <row r="1336" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69334,10 +69402,10 @@
         <v>5081926</v>
       </c>
       <c r="C1336" t="s">
+        <v>3854</v>
+      </c>
+      <c r="D1336" s="138" t="s">
         <v>3855</v>
-      </c>
-      <c r="D1336" s="138" t="s">
-        <v>3856</v>
       </c>
       <c r="E1336" t="s">
         <v>29</v>
@@ -69355,7 +69423,7 @@
         <v>806</v>
       </c>
       <c r="J1336" s="63" t="s">
-        <v>3857</v>
+        <v>3856</v>
       </c>
       <c r="K1336">
         <v>1337</v>
@@ -69364,7 +69432,7 @@
         <v>854</v>
       </c>
       <c r="N1336" t="s">
-        <v>3868</v>
+        <v>3867</v>
       </c>
     </row>
     <row r="1337" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69378,7 +69446,7 @@
         <v>25</v>
       </c>
       <c r="D1337" s="138" t="s">
-        <v>3858</v>
+        <v>3857</v>
       </c>
       <c r="E1337" t="s">
         <v>3429</v>
@@ -69396,7 +69464,7 @@
         <v>806</v>
       </c>
       <c r="J1337" s="63" t="s">
-        <v>3859</v>
+        <v>3858</v>
       </c>
       <c r="K1337">
         <v>1338</v>
@@ -69405,7 +69473,7 @@
         <v>854</v>
       </c>
       <c r="N1337" t="s">
-        <v>3869</v>
+        <v>3868</v>
       </c>
     </row>
     <row r="1338" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69416,7 +69484,7 @@
         <v>30358417</v>
       </c>
       <c r="C1338" t="s">
-        <v>3861</v>
+        <v>3860</v>
       </c>
       <c r="D1338" s="138" t="s">
         <v>424</v>
@@ -69437,7 +69505,7 @@
         <v>806</v>
       </c>
       <c r="J1338" s="63" t="s">
-        <v>3860</v>
+        <v>3859</v>
       </c>
       <c r="K1338">
         <v>1339</v>
@@ -69446,7 +69514,7 @@
         <v>854</v>
       </c>
       <c r="N1338" t="s">
-        <v>3870</v>
+        <v>3869</v>
       </c>
     </row>
     <row r="1339" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69478,7 +69546,7 @@
         <v>806</v>
       </c>
       <c r="J1339" s="63" t="s">
-        <v>3862</v>
+        <v>3861</v>
       </c>
       <c r="K1339">
         <v>1340</v>
@@ -69487,7 +69555,7 @@
         <v>854</v>
       </c>
       <c r="N1339" t="s">
-        <v>3871</v>
+        <v>3870</v>
       </c>
     </row>
     <row r="1340" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69501,7 +69569,7 @@
         <v>25</v>
       </c>
       <c r="D1340" s="138" t="s">
-        <v>3863</v>
+        <v>3862</v>
       </c>
       <c r="E1340" t="s">
         <v>648</v>
@@ -69519,7 +69587,7 @@
         <v>806</v>
       </c>
       <c r="J1340" s="63" t="s">
-        <v>3864</v>
+        <v>3863</v>
       </c>
       <c r="K1340">
         <v>1341</v>
@@ -69528,7 +69596,7 @@
         <v>854</v>
       </c>
       <c r="N1340" t="s">
-        <v>3872</v>
+        <v>3871</v>
       </c>
     </row>
     <row r="1341" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69560,7 +69628,7 @@
         <v>806</v>
       </c>
       <c r="J1341" s="63" t="s">
-        <v>3865</v>
+        <v>3864</v>
       </c>
       <c r="K1341">
         <v>1342</v>
@@ -69569,7 +69637,7 @@
         <v>854</v>
       </c>
       <c r="N1341" t="s">
-        <v>3873</v>
+        <v>3872</v>
       </c>
     </row>
     <row r="1342" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69601,7 +69669,7 @@
         <v>806</v>
       </c>
       <c r="J1342" s="63" t="s">
-        <v>3866</v>
+        <v>3865</v>
       </c>
       <c r="K1342">
         <v>1343</v>
@@ -69610,7 +69678,7 @@
         <v>854</v>
       </c>
       <c r="N1342" t="s">
-        <v>3874</v>
+        <v>3873</v>
       </c>
     </row>
     <row r="1343" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69642,7 +69710,7 @@
         <v>806</v>
       </c>
       <c r="J1343" s="63" t="s">
-        <v>3867</v>
+        <v>3866</v>
       </c>
       <c r="K1343">
         <v>1344</v>
@@ -69651,7 +69719,7 @@
         <v>854</v>
       </c>
       <c r="N1343" t="s">
-        <v>3875</v>
+        <v>3874</v>
       </c>
     </row>
     <row r="1344" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69683,7 +69751,7 @@
         <v>290</v>
       </c>
       <c r="J1344" s="63" t="s">
-        <v>3877</v>
+        <v>3876</v>
       </c>
       <c r="K1344">
         <v>1345</v>
@@ -69692,7 +69760,7 @@
         <v>854</v>
       </c>
       <c r="N1344" t="s">
-        <v>3887</v>
+        <v>3886</v>
       </c>
     </row>
     <row r="1345" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69724,7 +69792,7 @@
         <v>290</v>
       </c>
       <c r="J1345" s="63" t="s">
-        <v>3878</v>
+        <v>3877</v>
       </c>
       <c r="K1345">
         <v>1346</v>
@@ -69733,7 +69801,7 @@
         <v>854</v>
       </c>
       <c r="N1345" t="s">
-        <v>3888</v>
+        <v>3887</v>
       </c>
     </row>
     <row r="1346" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69744,7 +69812,7 @@
         <v>4196788</v>
       </c>
       <c r="C1346" t="s">
-        <v>3880</v>
+        <v>3879</v>
       </c>
       <c r="D1346" s="140" t="s">
         <v>441</v>
@@ -69765,7 +69833,7 @@
         <v>290</v>
       </c>
       <c r="J1346" s="63" t="s">
-        <v>3879</v>
+        <v>3878</v>
       </c>
       <c r="K1346">
         <v>1347</v>
@@ -69774,7 +69842,7 @@
         <v>854</v>
       </c>
       <c r="N1346" t="s">
-        <v>3889</v>
+        <v>3888</v>
       </c>
     </row>
     <row r="1347" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69785,7 +69853,7 @@
         <v>11596975</v>
       </c>
       <c r="C1347" t="s">
-        <v>3881</v>
+        <v>3880</v>
       </c>
       <c r="D1347" s="140" t="s">
         <v>372</v>
@@ -69806,7 +69874,7 @@
         <v>290</v>
       </c>
       <c r="J1347" s="63" t="s">
-        <v>3882</v>
+        <v>3881</v>
       </c>
       <c r="K1347">
         <v>1348</v>
@@ -69815,7 +69883,7 @@
         <v>854</v>
       </c>
       <c r="N1347" t="s">
-        <v>3890</v>
+        <v>3889</v>
       </c>
     </row>
     <row r="1348" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69847,7 +69915,7 @@
         <v>806</v>
       </c>
       <c r="J1348" s="63" t="s">
-        <v>3883</v>
+        <v>3882</v>
       </c>
       <c r="K1348">
         <v>1349</v>
@@ -69856,7 +69924,7 @@
         <v>854</v>
       </c>
       <c r="N1348" t="s">
-        <v>3891</v>
+        <v>3890</v>
       </c>
     </row>
     <row r="1349" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69867,7 +69935,7 @@
         <v>13525265</v>
       </c>
       <c r="C1349" t="s">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D1349" s="140" t="s">
         <v>60</v>
@@ -69888,7 +69956,7 @@
         <v>806</v>
       </c>
       <c r="J1349" s="63" t="s">
-        <v>3884</v>
+        <v>3883</v>
       </c>
       <c r="K1349">
         <v>1350</v>
@@ -69897,7 +69965,7 @@
         <v>854</v>
       </c>
       <c r="N1349" t="s">
-        <v>3892</v>
+        <v>3891</v>
       </c>
     </row>
     <row r="1350" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69911,7 +69979,7 @@
         <v>17</v>
       </c>
       <c r="D1350" s="140" t="s">
-        <v>3777</v>
+        <v>3776</v>
       </c>
       <c r="E1350" t="s">
         <v>18</v>
@@ -69929,7 +69997,7 @@
         <v>290</v>
       </c>
       <c r="J1350" s="63" t="s">
-        <v>3885</v>
+        <v>3884</v>
       </c>
       <c r="K1350">
         <v>1351</v>
@@ -69938,7 +70006,7 @@
         <v>854</v>
       </c>
       <c r="N1350" t="s">
-        <v>3893</v>
+        <v>3892</v>
       </c>
     </row>
     <row r="1351" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69952,7 +70020,7 @@
         <v>17</v>
       </c>
       <c r="D1351" s="140" t="s">
-        <v>3777</v>
+        <v>3776</v>
       </c>
       <c r="E1351" t="s">
         <v>18</v>
@@ -69970,7 +70038,7 @@
         <v>290</v>
       </c>
       <c r="J1351" s="63" t="s">
-        <v>3886</v>
+        <v>3885</v>
       </c>
       <c r="K1351">
         <v>1352</v>
@@ -69979,7 +70047,7 @@
         <v>854</v>
       </c>
       <c r="N1351" t="s">
-        <v>3894</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="1352" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69990,10 +70058,10 @@
         <v>6980000</v>
       </c>
       <c r="C1352" t="s">
-        <v>3897</v>
+        <v>3896</v>
       </c>
       <c r="D1352" s="141" t="s">
-        <v>3901</v>
+        <v>3900</v>
       </c>
       <c r="E1352" t="s">
         <v>366</v>
@@ -70011,7 +70079,7 @@
         <v>290</v>
       </c>
       <c r="J1352" s="63" t="s">
-        <v>3898</v>
+        <v>3897</v>
       </c>
       <c r="K1352">
         <v>1353</v>
@@ -70020,7 +70088,7 @@
         <v>854</v>
       </c>
       <c r="N1352" t="s">
-        <v>3910</v>
+        <v>3909</v>
       </c>
     </row>
     <row r="1353" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70031,7 +70099,7 @@
         <v>4892080</v>
       </c>
       <c r="C1353" t="s">
-        <v>3902</v>
+        <v>3901</v>
       </c>
       <c r="D1353" s="141" t="s">
         <v>646</v>
@@ -70046,13 +70114,13 @@
         <v>4.6365740740740742E-2</v>
       </c>
       <c r="H1353" s="141" t="s">
-        <v>3903</v>
+        <v>3902</v>
       </c>
       <c r="I1353" s="141" t="s">
         <v>290</v>
       </c>
       <c r="J1353" s="63" t="s">
-        <v>3899</v>
+        <v>3898</v>
       </c>
       <c r="K1353">
         <v>1354</v>
@@ -70061,7 +70129,7 @@
         <v>854</v>
       </c>
       <c r="N1353" t="s">
-        <v>3911</v>
+        <v>3910</v>
       </c>
     </row>
     <row r="1354" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70075,7 +70143,7 @@
         <v>440</v>
       </c>
       <c r="D1354" t="s">
-        <v>3904</v>
+        <v>3903</v>
       </c>
       <c r="E1354" t="s">
         <v>433</v>
@@ -70093,7 +70161,7 @@
         <v>290</v>
       </c>
       <c r="J1354" s="63" t="s">
-        <v>3900</v>
+        <v>3899</v>
       </c>
       <c r="K1354">
         <v>1355</v>
@@ -70102,7 +70170,7 @@
         <v>854</v>
       </c>
       <c r="N1354" t="s">
-        <v>3912</v>
+        <v>3911</v>
       </c>
     </row>
     <row r="1355" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70113,7 +70181,7 @@
         <v>4255101</v>
       </c>
       <c r="C1355" t="s">
-        <v>3905</v>
+        <v>3904</v>
       </c>
       <c r="D1355" t="s">
         <v>372</v>
@@ -70134,7 +70202,7 @@
         <v>290</v>
       </c>
       <c r="J1355" s="63" t="s">
-        <v>3906</v>
+        <v>3905</v>
       </c>
       <c r="K1355">
         <v>1356</v>
@@ -70143,7 +70211,7 @@
         <v>854</v>
       </c>
       <c r="N1355" t="s">
-        <v>3913</v>
+        <v>3912</v>
       </c>
     </row>
     <row r="1356" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70157,7 +70225,7 @@
         <v>209</v>
       </c>
       <c r="D1356" t="s">
-        <v>3909</v>
+        <v>3908</v>
       </c>
       <c r="E1356" t="s">
         <v>209</v>
@@ -70175,7 +70243,7 @@
         <v>290</v>
       </c>
       <c r="J1356" s="63" t="s">
-        <v>3907</v>
+        <v>3906</v>
       </c>
       <c r="K1356">
         <v>1357</v>
@@ -70184,7 +70252,7 @@
         <v>854</v>
       </c>
       <c r="N1356" t="s">
-        <v>3914</v>
+        <v>3913</v>
       </c>
     </row>
     <row r="1357" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70216,7 +70284,7 @@
         <v>290</v>
       </c>
       <c r="J1357" s="63" t="s">
-        <v>3908</v>
+        <v>3907</v>
       </c>
       <c r="K1357">
         <v>1358</v>
@@ -70225,7 +70293,7 @@
         <v>854</v>
       </c>
       <c r="N1357" t="s">
-        <v>3915</v>
+        <v>3914</v>
       </c>
     </row>
     <row r="1358" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70257,7 +70325,7 @@
         <v>806</v>
       </c>
       <c r="J1358" s="63" t="s">
-        <v>3920</v>
+        <v>3919</v>
       </c>
       <c r="K1358">
         <v>1359</v>
@@ -70266,7 +70334,7 @@
         <v>854</v>
       </c>
       <c r="N1358" t="s">
-        <v>3933</v>
+        <v>3932</v>
       </c>
     </row>
     <row r="1359" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70298,7 +70366,7 @@
         <v>290</v>
       </c>
       <c r="J1359" s="63" t="s">
-        <v>3921</v>
+        <v>3920</v>
       </c>
       <c r="K1359">
         <v>1360</v>
@@ -70307,7 +70375,7 @@
         <v>854</v>
       </c>
       <c r="N1359" t="s">
-        <v>3934</v>
+        <v>3933</v>
       </c>
     </row>
     <row r="1360" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70318,7 +70386,7 @@
         <v>16543175</v>
       </c>
       <c r="C1360" t="s">
-        <v>3922</v>
+        <v>3921</v>
       </c>
       <c r="D1360" t="s">
         <v>424</v>
@@ -70339,7 +70407,7 @@
         <v>806</v>
       </c>
       <c r="J1360" s="63" t="s">
-        <v>3923</v>
+        <v>3922</v>
       </c>
       <c r="K1360">
         <v>1361</v>
@@ -70348,7 +70416,7 @@
         <v>854</v>
       </c>
       <c r="N1360" t="s">
-        <v>3935</v>
+        <v>3934</v>
       </c>
     </row>
     <row r="1361" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70359,7 +70427,7 @@
         <v>8112313</v>
       </c>
       <c r="C1361" t="s">
-        <v>3925</v>
+        <v>3924</v>
       </c>
       <c r="D1361" t="s">
         <v>590</v>
@@ -70380,7 +70448,7 @@
         <v>806</v>
       </c>
       <c r="J1361" s="63" t="s">
-        <v>3924</v>
+        <v>3923</v>
       </c>
       <c r="K1361">
         <v>1362</v>
@@ -70389,7 +70457,7 @@
         <v>854</v>
       </c>
       <c r="N1361" t="s">
-        <v>3936</v>
+        <v>3935</v>
       </c>
     </row>
     <row r="1362" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70403,7 +70471,7 @@
         <v>17</v>
       </c>
       <c r="D1362" t="s">
-        <v>3828</v>
+        <v>3827</v>
       </c>
       <c r="E1362" t="s">
         <v>18</v>
@@ -70421,7 +70489,7 @@
         <v>806</v>
       </c>
       <c r="J1362" s="63" t="s">
-        <v>3926</v>
+        <v>3925</v>
       </c>
       <c r="K1362">
         <v>1363</v>
@@ -70430,7 +70498,7 @@
         <v>854</v>
       </c>
       <c r="N1362" t="s">
-        <v>3937</v>
+        <v>3936</v>
       </c>
     </row>
     <row r="1363" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70441,7 +70509,7 @@
         <v>19167309</v>
       </c>
       <c r="C1363" t="s">
-        <v>3929</v>
+        <v>3928</v>
       </c>
       <c r="D1363" t="s">
         <v>161</v>
@@ -70456,13 +70524,13 @@
         <v>0.14107638888888888</v>
       </c>
       <c r="H1363" s="143" t="s">
-        <v>3928</v>
+        <v>3927</v>
       </c>
       <c r="I1363" s="143" t="s">
         <v>806</v>
       </c>
       <c r="J1363" s="63" t="s">
-        <v>3927</v>
+        <v>3926</v>
       </c>
       <c r="K1363">
         <v>1364</v>
@@ -70471,7 +70539,7 @@
         <v>854</v>
       </c>
       <c r="N1363" t="s">
-        <v>3938</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="1364" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70482,7 +70550,7 @@
         <v>15541720</v>
       </c>
       <c r="C1364" t="s">
-        <v>3881</v>
+        <v>3880</v>
       </c>
       <c r="D1364" t="s">
         <v>372</v>
@@ -70503,7 +70571,7 @@
         <v>290</v>
       </c>
       <c r="J1364" s="63" t="s">
-        <v>3930</v>
+        <v>3929</v>
       </c>
       <c r="K1364">
         <v>1365</v>
@@ -70512,7 +70580,7 @@
         <v>854</v>
       </c>
       <c r="N1364" t="s">
-        <v>3939</v>
+        <v>3938</v>
       </c>
     </row>
     <row r="1365" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70523,10 +70591,10 @@
         <v>4033637</v>
       </c>
       <c r="C1365" t="s">
-        <v>3534</v>
+        <v>3533</v>
       </c>
       <c r="D1365" t="s">
-        <v>3932</v>
+        <v>3931</v>
       </c>
       <c r="E1365" t="s">
         <v>18</v>
@@ -70544,7 +70612,7 @@
         <v>806</v>
       </c>
       <c r="J1365" s="63" t="s">
-        <v>3931</v>
+        <v>3930</v>
       </c>
       <c r="K1365">
         <v>1366</v>
@@ -70553,7 +70621,7 @@
         <v>854</v>
       </c>
       <c r="N1365" t="s">
-        <v>3940</v>
+        <v>3939</v>
       </c>
     </row>
     <row r="1366" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70585,7 +70653,7 @@
         <v>806</v>
       </c>
       <c r="J1366" s="63" t="s">
-        <v>3941</v>
+        <v>3940</v>
       </c>
       <c r="K1366">
         <v>1367</v>
@@ -70594,7 +70662,7 @@
         <v>854</v>
       </c>
       <c r="N1366" t="s">
-        <v>3942</v>
+        <v>3941</v>
       </c>
     </row>
     <row r="1367" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70605,7 +70673,7 @@
         <v>25352781</v>
       </c>
       <c r="C1367" t="s">
-        <v>3943</v>
+        <v>3942</v>
       </c>
       <c r="D1367" t="s">
         <v>60</v>
@@ -70620,13 +70688,13 @@
         <v>502</v>
       </c>
       <c r="H1367" s="145" t="s">
+        <v>3943</v>
+      </c>
+      <c r="I1367" s="145" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1367" s="63" t="s">
         <v>3944</v>
-      </c>
-      <c r="I1367" s="145" t="s">
-        <v>806</v>
-      </c>
-      <c r="J1367" s="63" t="s">
-        <v>3945</v>
       </c>
       <c r="K1367">
         <v>1368</v>
@@ -70635,7 +70703,7 @@
         <v>854</v>
       </c>
       <c r="N1367" t="s">
-        <v>3949</v>
+        <v>3948</v>
       </c>
     </row>
     <row r="1368" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70667,7 +70735,7 @@
         <v>806</v>
       </c>
       <c r="J1368" s="63" t="s">
-        <v>3946</v>
+        <v>3945</v>
       </c>
       <c r="K1368">
         <v>1369</v>
@@ -70676,7 +70744,7 @@
         <v>854</v>
       </c>
       <c r="N1368" t="s">
-        <v>3950</v>
+        <v>3949</v>
       </c>
     </row>
     <row r="1369" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70687,10 +70755,10 @@
         <v>10476636</v>
       </c>
       <c r="C1369" t="s">
-        <v>3929</v>
+        <v>3928</v>
       </c>
       <c r="D1369" t="s">
-        <v>3718</v>
+        <v>3717</v>
       </c>
       <c r="E1369" t="s">
         <v>51</v>
@@ -70708,7 +70776,7 @@
         <v>806</v>
       </c>
       <c r="J1369" s="63" t="s">
-        <v>3947</v>
+        <v>3946</v>
       </c>
       <c r="K1369">
         <v>1370</v>
@@ -70717,7 +70785,7 @@
         <v>854</v>
       </c>
       <c r="N1369" t="s">
-        <v>3951</v>
+        <v>3950</v>
       </c>
     </row>
     <row r="1370" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70749,7 +70817,7 @@
         <v>806</v>
       </c>
       <c r="J1370" s="63" t="s">
-        <v>3948</v>
+        <v>3947</v>
       </c>
       <c r="K1370">
         <v>1371</v>
@@ -70758,7 +70826,7 @@
         <v>854</v>
       </c>
       <c r="N1370" t="s">
-        <v>3952</v>
+        <v>3951</v>
       </c>
     </row>
     <row r="1371" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70769,7 +70837,7 @@
         <v>43719222</v>
       </c>
       <c r="C1371" t="s">
-        <v>3954</v>
+        <v>3953</v>
       </c>
       <c r="D1371" t="s">
         <v>60</v>
@@ -70790,7 +70858,7 @@
         <v>806</v>
       </c>
       <c r="J1371" s="63" t="s">
-        <v>3953</v>
+        <v>3952</v>
       </c>
       <c r="K1371">
         <v>1372</v>
@@ -70799,7 +70867,7 @@
         <v>854</v>
       </c>
       <c r="N1371" t="s">
-        <v>3979</v>
+        <v>3978</v>
       </c>
     </row>
     <row r="1372" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70825,13 +70893,13 @@
         <v>502</v>
       </c>
       <c r="H1372" s="146" t="s">
-        <v>3956</v>
+        <v>3955</v>
       </c>
       <c r="I1372" s="146" t="s">
         <v>813</v>
       </c>
       <c r="J1372" s="63" t="s">
-        <v>3955</v>
+        <v>3954</v>
       </c>
       <c r="K1372">
         <v>1373</v>
@@ -70840,7 +70908,7 @@
         <v>854</v>
       </c>
       <c r="N1372" t="s">
-        <v>3980</v>
+        <v>3979</v>
       </c>
     </row>
     <row r="1373" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70851,7 +70919,7 @@
         <v>4790253</v>
       </c>
       <c r="C1373" t="s">
-        <v>3958</v>
+        <v>3957</v>
       </c>
       <c r="D1373" t="s">
         <v>283</v>
@@ -70872,7 +70940,7 @@
         <v>290</v>
       </c>
       <c r="J1373" s="63" t="s">
-        <v>3957</v>
+        <v>3956</v>
       </c>
       <c r="K1373">
         <v>1374</v>
@@ -70881,7 +70949,7 @@
         <v>854</v>
       </c>
       <c r="N1373" t="s">
-        <v>3981</v>
+        <v>3980</v>
       </c>
     </row>
     <row r="1374" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70892,7 +70960,7 @@
         <v>7656870</v>
       </c>
       <c r="C1374" t="s">
-        <v>3960</v>
+        <v>3959</v>
       </c>
       <c r="D1374" t="s">
         <v>128</v>
@@ -70913,7 +70981,7 @@
         <v>806</v>
       </c>
       <c r="J1374" s="63" t="s">
-        <v>3959</v>
+        <v>3958</v>
       </c>
       <c r="K1374">
         <v>1375</v>
@@ -70922,7 +70990,7 @@
         <v>854</v>
       </c>
       <c r="N1374" t="s">
-        <v>3982</v>
+        <v>3981</v>
       </c>
     </row>
     <row r="1375" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70933,7 +71001,7 @@
         <v>8733988</v>
       </c>
       <c r="C1375" t="s">
-        <v>3960</v>
+        <v>3959</v>
       </c>
       <c r="D1375" t="s">
         <v>68</v>
@@ -70954,7 +71022,7 @@
         <v>806</v>
       </c>
       <c r="J1375" s="63" t="s">
-        <v>3961</v>
+        <v>3960</v>
       </c>
       <c r="K1375">
         <v>1376</v>
@@ -70963,7 +71031,7 @@
         <v>854</v>
       </c>
       <c r="N1375" t="s">
-        <v>3983</v>
+        <v>3982</v>
       </c>
     </row>
     <row r="1376" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -70989,13 +71057,13 @@
         <v>9.2604166666666668E-2</v>
       </c>
       <c r="H1376" s="146" t="s">
+        <v>3961</v>
+      </c>
+      <c r="I1376" s="146" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1376" s="63" t="s">
         <v>3962</v>
-      </c>
-      <c r="I1376" s="146" t="s">
-        <v>806</v>
-      </c>
-      <c r="J1376" s="63" t="s">
-        <v>3963</v>
       </c>
       <c r="K1376">
         <v>1377</v>
@@ -71004,7 +71072,7 @@
         <v>854</v>
       </c>
       <c r="N1376" t="s">
-        <v>3984</v>
+        <v>3983</v>
       </c>
     </row>
     <row r="1377" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71015,7 +71083,7 @@
         <v>14343403</v>
       </c>
       <c r="C1377" t="s">
-        <v>3965</v>
+        <v>3964</v>
       </c>
       <c r="D1377" t="s">
         <v>96</v>
@@ -71030,13 +71098,13 @@
         <v>0.10716435185185186</v>
       </c>
       <c r="H1377" s="146" t="s">
-        <v>3964</v>
+        <v>3963</v>
       </c>
       <c r="I1377" s="146" t="s">
         <v>806</v>
       </c>
       <c r="J1377" s="63" t="s">
-        <v>3967</v>
+        <v>3966</v>
       </c>
       <c r="K1377">
         <v>1378</v>
@@ -71045,7 +71113,7 @@
         <v>854</v>
       </c>
       <c r="N1377" t="s">
-        <v>3985</v>
+        <v>3984</v>
       </c>
     </row>
     <row r="1378" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71056,7 +71124,7 @@
         <v>12410166</v>
       </c>
       <c r="C1378" t="s">
-        <v>3966</v>
+        <v>3965</v>
       </c>
       <c r="D1378" t="s">
         <v>446</v>
@@ -71077,7 +71145,7 @@
         <v>806</v>
       </c>
       <c r="J1378" s="63" t="s">
-        <v>3968</v>
+        <v>3967</v>
       </c>
       <c r="K1378">
         <v>1379</v>
@@ -71086,7 +71154,7 @@
         <v>854</v>
       </c>
       <c r="N1378" t="s">
-        <v>3986</v>
+        <v>3985</v>
       </c>
     </row>
     <row r="1379" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71118,7 +71186,7 @@
         <v>806</v>
       </c>
       <c r="J1379" s="63" t="s">
-        <v>3969</v>
+        <v>3968</v>
       </c>
       <c r="K1379">
         <v>1380</v>
@@ -71127,7 +71195,7 @@
         <v>854</v>
       </c>
       <c r="N1379" t="s">
-        <v>3987</v>
+        <v>3986</v>
       </c>
     </row>
     <row r="1380" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71153,13 +71221,13 @@
         <v>502</v>
       </c>
       <c r="H1380" s="146" t="s">
-        <v>3723</v>
+        <v>3722</v>
       </c>
       <c r="I1380" s="146" t="s">
         <v>806</v>
       </c>
       <c r="J1380" s="63" t="s">
-        <v>3970</v>
+        <v>3969</v>
       </c>
       <c r="K1380">
         <v>1381</v>
@@ -71168,7 +71236,7 @@
         <v>854</v>
       </c>
       <c r="N1380" t="s">
-        <v>3988</v>
+        <v>3987</v>
       </c>
     </row>
     <row r="1381" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71179,13 +71247,13 @@
         <v>9380000</v>
       </c>
       <c r="C1381" t="s">
-        <v>3971</v>
+        <v>3970</v>
       </c>
       <c r="D1381" t="s">
         <v>619</v>
       </c>
       <c r="E1381" t="s">
-        <v>3971</v>
+        <v>3970</v>
       </c>
       <c r="F1381" s="29">
         <v>46120</v>
@@ -71200,7 +71268,7 @@
         <v>806</v>
       </c>
       <c r="J1381" s="63" t="s">
-        <v>3972</v>
+        <v>3971</v>
       </c>
       <c r="K1381">
         <v>1382</v>
@@ -71209,7 +71277,7 @@
         <v>854</v>
       </c>
       <c r="N1381" t="s">
-        <v>3989</v>
+        <v>3988</v>
       </c>
     </row>
     <row r="1382" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71220,7 +71288,7 @@
         <v>18187409</v>
       </c>
       <c r="C1382" t="s">
-        <v>3976</v>
+        <v>3975</v>
       </c>
       <c r="D1382" t="s">
         <v>79</v>
@@ -71235,13 +71303,13 @@
         <v>0.11269675925925926</v>
       </c>
       <c r="H1382" s="146" t="s">
+        <v>3972</v>
+      </c>
+      <c r="I1382" s="146" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1382" s="63" t="s">
         <v>3973</v>
-      </c>
-      <c r="I1382" s="146" t="s">
-        <v>806</v>
-      </c>
-      <c r="J1382" s="63" t="s">
-        <v>3974</v>
       </c>
       <c r="K1382">
         <v>1383</v>
@@ -71250,7 +71318,7 @@
         <v>854</v>
       </c>
       <c r="N1382" t="s">
-        <v>3990</v>
+        <v>3989</v>
       </c>
     </row>
     <row r="1383" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71261,10 +71329,10 @@
         <v>9353760</v>
       </c>
       <c r="C1383" t="s">
-        <v>3977</v>
+        <v>3976</v>
       </c>
       <c r="D1383" t="s">
-        <v>3863</v>
+        <v>3862</v>
       </c>
       <c r="E1383" t="s">
         <v>648</v>
@@ -71276,13 +71344,13 @@
         <v>4.7731481481481486E-2</v>
       </c>
       <c r="H1383" s="146" t="s">
-        <v>3978</v>
+        <v>3977</v>
       </c>
       <c r="I1383" s="146" t="s">
         <v>806</v>
       </c>
       <c r="J1383" s="63" t="s">
-        <v>3975</v>
+        <v>3974</v>
       </c>
       <c r="K1383">
         <v>1384</v>
@@ -71291,7 +71359,7 @@
         <v>854</v>
       </c>
       <c r="N1383" t="s">
-        <v>3991</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="1384" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71308,7 +71376,7 @@
         <v>424</v>
       </c>
       <c r="E1384" t="s">
-        <v>3992</v>
+        <v>3991</v>
       </c>
       <c r="F1384" s="29">
         <v>46123</v>
@@ -71323,7 +71391,7 @@
         <v>806</v>
       </c>
       <c r="J1384" s="63" t="s">
-        <v>3993</v>
+        <v>3992</v>
       </c>
       <c r="K1384">
         <v>1385</v>
@@ -71332,7 +71400,7 @@
         <v>854</v>
       </c>
       <c r="N1384" t="s">
-        <v>4001</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="1385" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71358,13 +71426,13 @@
         <v>0.11065972222222221</v>
       </c>
       <c r="H1385" s="147" t="s">
+        <v>3993</v>
+      </c>
+      <c r="I1385" s="147" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1385" s="63" t="s">
         <v>3994</v>
-      </c>
-      <c r="I1385" s="147" t="s">
-        <v>806</v>
-      </c>
-      <c r="J1385" s="63" t="s">
-        <v>3995</v>
       </c>
       <c r="K1385">
         <v>1386</v>
@@ -71373,7 +71441,7 @@
         <v>854</v>
       </c>
       <c r="N1385" t="s">
-        <v>4002</v>
+        <v>4001</v>
       </c>
     </row>
     <row r="1386" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71405,7 +71473,7 @@
         <v>806</v>
       </c>
       <c r="J1386" s="63" t="s">
-        <v>3996</v>
+        <v>3995</v>
       </c>
       <c r="K1386">
         <v>1387</v>
@@ -71414,7 +71482,7 @@
         <v>854</v>
       </c>
       <c r="N1386" t="s">
-        <v>4003</v>
+        <v>4002</v>
       </c>
     </row>
     <row r="1387" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71425,7 +71493,7 @@
         <v>10483435</v>
       </c>
       <c r="C1387" t="s">
-        <v>3997</v>
+        <v>3996</v>
       </c>
       <c r="D1387" t="s">
         <v>399</v>
@@ -71446,7 +71514,7 @@
         <v>806</v>
       </c>
       <c r="J1387" s="63" t="s">
-        <v>3998</v>
+        <v>3997</v>
       </c>
       <c r="K1387">
         <v>1388</v>
@@ -71455,7 +71523,7 @@
         <v>854</v>
       </c>
       <c r="N1387" t="s">
-        <v>4004</v>
+        <v>4003</v>
       </c>
     </row>
     <row r="1388" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71481,13 +71549,13 @@
         <v>6.3472222222222222E-2</v>
       </c>
       <c r="H1388" s="147" t="s">
+        <v>3998</v>
+      </c>
+      <c r="I1388" s="147" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1388" s="63" t="s">
         <v>3999</v>
-      </c>
-      <c r="I1388" s="147" t="s">
-        <v>806</v>
-      </c>
-      <c r="J1388" s="63" t="s">
-        <v>4000</v>
       </c>
       <c r="K1388">
         <v>1389</v>
@@ -71496,7 +71564,7 @@
         <v>854</v>
       </c>
       <c r="N1388" t="s">
-        <v>4005</v>
+        <v>4004</v>
       </c>
     </row>
     <row r="1389" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71507,7 +71575,7 @@
         <v>3935653</v>
       </c>
       <c r="C1389" t="s">
-        <v>4006</v>
+        <v>4005</v>
       </c>
       <c r="D1389" t="s">
         <v>613</v>
@@ -71528,7 +71596,7 @@
         <v>806</v>
       </c>
       <c r="J1389" s="63" t="s">
-        <v>4007</v>
+        <v>4006</v>
       </c>
       <c r="K1389">
         <v>1390</v>
@@ -71537,7 +71605,7 @@
         <v>854</v>
       </c>
       <c r="N1389" t="s">
-        <v>4009</v>
+        <v>4008</v>
       </c>
     </row>
     <row r="1390" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71569,7 +71637,7 @@
         <v>806</v>
       </c>
       <c r="J1390" s="63" t="s">
-        <v>4008</v>
+        <v>4007</v>
       </c>
       <c r="K1390">
         <v>1391</v>
@@ -71578,7 +71646,7 @@
         <v>854</v>
       </c>
       <c r="N1390" t="s">
-        <v>4010</v>
+        <v>4009</v>
       </c>
     </row>
     <row r="1391" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71592,7 +71660,7 @@
         <v>32</v>
       </c>
       <c r="D1391" t="s">
-        <v>4011</v>
+        <v>4010</v>
       </c>
       <c r="E1391" t="s">
         <v>29</v>
@@ -71604,13 +71672,13 @@
         <v>6.9641203703703705E-2</v>
       </c>
       <c r="H1391" s="149" t="s">
+        <v>4011</v>
+      </c>
+      <c r="I1391" s="149" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1391" s="63" t="s">
         <v>4012</v>
-      </c>
-      <c r="I1391" s="149" t="s">
-        <v>806</v>
-      </c>
-      <c r="J1391" s="63" t="s">
-        <v>4013</v>
       </c>
       <c r="K1391">
         <v>1392</v>
@@ -71619,7 +71687,7 @@
         <v>854</v>
       </c>
       <c r="N1391" t="s">
-        <v>4017</v>
+        <v>4016</v>
       </c>
     </row>
     <row r="1392" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71651,7 +71719,7 @@
         <v>806</v>
       </c>
       <c r="J1392" s="63" t="s">
-        <v>4014</v>
+        <v>4013</v>
       </c>
       <c r="K1392">
         <v>1393</v>
@@ -71660,7 +71728,7 @@
         <v>854</v>
       </c>
       <c r="N1392" t="s">
-        <v>4044</v>
+        <v>4043</v>
       </c>
     </row>
     <row r="1393" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71692,7 +71760,7 @@
         <v>806</v>
       </c>
       <c r="J1393" s="63" t="s">
-        <v>4015</v>
+        <v>4014</v>
       </c>
       <c r="K1393">
         <v>1394</v>
@@ -71701,7 +71769,7 @@
         <v>854</v>
       </c>
       <c r="N1393" t="s">
-        <v>4018</v>
+        <v>4017</v>
       </c>
     </row>
     <row r="1394" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71712,7 +71780,7 @@
         <v>8459179</v>
       </c>
       <c r="C1394" t="s">
-        <v>3710</v>
+        <v>3709</v>
       </c>
       <c r="D1394" t="s">
         <v>393</v>
@@ -71733,7 +71801,7 @@
         <v>806</v>
       </c>
       <c r="J1394" s="63" t="s">
-        <v>4016</v>
+        <v>4015</v>
       </c>
       <c r="K1394">
         <v>1395</v>
@@ -71742,7 +71810,7 @@
         <v>854</v>
       </c>
       <c r="N1394" t="s">
-        <v>4019</v>
+        <v>4018</v>
       </c>
     </row>
     <row r="1395" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71753,7 +71821,7 @@
         <v>21177695</v>
       </c>
       <c r="C1395" t="s">
-        <v>3684</v>
+        <v>3683</v>
       </c>
       <c r="D1395" t="s">
         <v>364</v>
@@ -71774,7 +71842,7 @@
         <v>806</v>
       </c>
       <c r="J1395" s="63" t="s">
-        <v>4021</v>
+        <v>4020</v>
       </c>
       <c r="K1395">
         <v>1396</v>
@@ -71783,7 +71851,7 @@
         <v>854</v>
       </c>
       <c r="N1395" t="s">
-        <v>4045</v>
+        <v>4044</v>
       </c>
     </row>
     <row r="1396" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71794,13 +71862,13 @@
         <v>9514769</v>
       </c>
       <c r="C1396" t="s">
-        <v>4023</v>
+        <v>4022</v>
       </c>
       <c r="D1396" t="s">
         <v>76</v>
       </c>
       <c r="E1396" t="s">
-        <v>4022</v>
+        <v>4021</v>
       </c>
       <c r="F1396" s="29">
         <v>44675</v>
@@ -71815,7 +71883,7 @@
         <v>813</v>
       </c>
       <c r="J1396" s="63" t="s">
-        <v>4020</v>
+        <v>4019</v>
       </c>
       <c r="K1396">
         <v>1397</v>
@@ -71824,7 +71892,7 @@
         <v>854</v>
       </c>
       <c r="N1396" t="s">
-        <v>4046</v>
+        <v>4045</v>
       </c>
     </row>
     <row r="1397" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71841,7 +71909,7 @@
         <v>76</v>
       </c>
       <c r="E1397" t="s">
-        <v>4022</v>
+        <v>4021</v>
       </c>
       <c r="F1397" s="29">
         <v>44677</v>
@@ -71856,7 +71924,7 @@
         <v>813</v>
       </c>
       <c r="J1397" s="63" t="s">
-        <v>4024</v>
+        <v>4023</v>
       </c>
       <c r="K1397">
         <v>1398</v>
@@ -71865,7 +71933,7 @@
         <v>854</v>
       </c>
       <c r="N1397" t="s">
-        <v>4047</v>
+        <v>4046</v>
       </c>
     </row>
     <row r="1398" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71882,7 +71950,7 @@
         <v>436</v>
       </c>
       <c r="E1398" t="s">
-        <v>4022</v>
+        <v>4021</v>
       </c>
       <c r="F1398" s="29">
         <v>44679</v>
@@ -71897,7 +71965,7 @@
         <v>813</v>
       </c>
       <c r="J1398" s="63" t="s">
-        <v>4025</v>
+        <v>4024</v>
       </c>
       <c r="K1398">
         <v>1399</v>
@@ -71906,7 +71974,7 @@
         <v>854</v>
       </c>
       <c r="N1398" t="s">
-        <v>4048</v>
+        <v>4047</v>
       </c>
     </row>
     <row r="1399" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71917,13 +71985,13 @@
         <v>3397005</v>
       </c>
       <c r="C1399" t="s">
-        <v>4029</v>
+        <v>4028</v>
       </c>
       <c r="D1399" t="s">
         <v>76</v>
       </c>
       <c r="E1399" t="s">
-        <v>4022</v>
+        <v>4021</v>
       </c>
       <c r="F1399" s="29">
         <v>44556</v>
@@ -71932,13 +72000,13 @@
         <v>2.7152777777777779E-2</v>
       </c>
       <c r="H1399" s="150" t="s">
-        <v>4028</v>
+        <v>4027</v>
       </c>
       <c r="I1399" s="150" t="s">
         <v>813</v>
       </c>
       <c r="J1399" s="63" t="s">
-        <v>4026</v>
+        <v>4025</v>
       </c>
       <c r="K1399">
         <v>1400</v>
@@ -71947,7 +72015,7 @@
         <v>854</v>
       </c>
       <c r="N1399" t="s">
-        <v>4049</v>
+        <v>4048</v>
       </c>
     </row>
     <row r="1400" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71958,13 +72026,13 @@
         <v>3817177</v>
       </c>
       <c r="C1400" t="s">
-        <v>4031</v>
+        <v>4030</v>
       </c>
       <c r="D1400" t="s">
-        <v>3909</v>
+        <v>3908</v>
       </c>
       <c r="E1400" t="s">
-        <v>4030</v>
+        <v>4029</v>
       </c>
       <c r="F1400" s="29">
         <v>44579</v>
@@ -71979,7 +72047,7 @@
         <v>813</v>
       </c>
       <c r="J1400" s="63" t="s">
-        <v>4027</v>
+        <v>4026</v>
       </c>
       <c r="K1400">
         <v>1401</v>
@@ -71988,7 +72056,7 @@
         <v>854</v>
       </c>
       <c r="N1400" t="s">
-        <v>4050</v>
+        <v>4049</v>
       </c>
     </row>
     <row r="1401" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -71999,13 +72067,13 @@
         <v>4527031</v>
       </c>
       <c r="C1401" t="s">
-        <v>4032</v>
+        <v>4031</v>
       </c>
       <c r="D1401" t="s">
         <v>76</v>
       </c>
       <c r="E1401" t="s">
-        <v>4030</v>
+        <v>4029</v>
       </c>
       <c r="F1401" s="29">
         <v>44549</v>
@@ -72020,7 +72088,7 @@
         <v>813</v>
       </c>
       <c r="J1401" s="63" t="s">
-        <v>4033</v>
+        <v>4032</v>
       </c>
       <c r="K1401">
         <v>1402</v>
@@ -72029,7 +72097,7 @@
         <v>854</v>
       </c>
       <c r="N1401" t="s">
-        <v>4051</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="1402" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -72040,13 +72108,13 @@
         <v>3055127</v>
       </c>
       <c r="C1402" t="s">
-        <v>4035</v>
+        <v>4034</v>
       </c>
       <c r="D1402" t="s">
         <v>203</v>
       </c>
       <c r="E1402" t="s">
-        <v>4022</v>
+        <v>4021</v>
       </c>
       <c r="F1402" s="29">
         <v>44563</v>
@@ -72055,13 +72123,13 @@
         <v>4.2222222222222223E-2</v>
       </c>
       <c r="H1402" s="150" t="s">
-        <v>4036</v>
+        <v>4035</v>
       </c>
       <c r="I1402" s="150" t="s">
         <v>290</v>
       </c>
       <c r="J1402" s="63" t="s">
-        <v>4034</v>
+        <v>4033</v>
       </c>
       <c r="K1402">
         <v>1403</v>
@@ -72070,7 +72138,7 @@
         <v>854</v>
       </c>
       <c r="N1402" t="s">
-        <v>4052</v>
+        <v>4051</v>
       </c>
     </row>
     <row r="1403" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -72081,13 +72149,13 @@
         <v>2745915</v>
       </c>
       <c r="C1403" t="s">
-        <v>4039</v>
+        <v>4038</v>
       </c>
       <c r="D1403" t="s">
         <v>487</v>
       </c>
       <c r="E1403" t="s">
-        <v>4022</v>
+        <v>4021</v>
       </c>
       <c r="F1403" s="29">
         <v>44582</v>
@@ -72102,7 +72170,7 @@
         <v>813</v>
       </c>
       <c r="J1403" s="63" t="s">
-        <v>4037</v>
+        <v>4036</v>
       </c>
       <c r="K1403">
         <v>1404</v>
@@ -72111,7 +72179,7 @@
         <v>854</v>
       </c>
       <c r="N1403" t="s">
-        <v>4053</v>
+        <v>4052</v>
       </c>
     </row>
     <row r="1404" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -72128,7 +72196,7 @@
         <v>76</v>
       </c>
       <c r="E1404" t="s">
-        <v>4022</v>
+        <v>4021</v>
       </c>
       <c r="F1404" s="29">
         <v>44681</v>
@@ -72143,7 +72211,7 @@
         <v>813</v>
       </c>
       <c r="J1404" s="63" t="s">
-        <v>4038</v>
+        <v>4037</v>
       </c>
       <c r="K1404">
         <v>1405</v>
@@ -72152,7 +72220,7 @@
         <v>854</v>
       </c>
       <c r="N1404" t="s">
-        <v>4054</v>
+        <v>4053</v>
       </c>
     </row>
     <row r="1405" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -72163,13 +72231,13 @@
         <v>3379190</v>
       </c>
       <c r="C1405" t="s">
-        <v>4040</v>
+        <v>4039</v>
       </c>
       <c r="D1405" t="s">
         <v>487</v>
       </c>
       <c r="E1405" t="s">
-        <v>4022</v>
+        <v>4021</v>
       </c>
       <c r="F1405" s="29">
         <v>44590</v>
@@ -72184,7 +72252,7 @@
         <v>813</v>
       </c>
       <c r="J1405" s="63" t="s">
-        <v>4041</v>
+        <v>4040</v>
       </c>
       <c r="K1405">
         <v>1406</v>
@@ -72193,7 +72261,7 @@
         <v>854</v>
       </c>
       <c r="N1405" t="s">
-        <v>4055</v>
+        <v>4054</v>
       </c>
     </row>
     <row r="1406" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -72225,7 +72293,7 @@
         <v>813</v>
       </c>
       <c r="J1406" s="63" t="s">
-        <v>4042</v>
+        <v>4041</v>
       </c>
       <c r="K1406">
         <v>1407</v>
@@ -72234,7 +72302,7 @@
         <v>854</v>
       </c>
       <c r="N1406" t="s">
-        <v>4056</v>
+        <v>4055</v>
       </c>
     </row>
     <row r="1407" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -72251,7 +72319,7 @@
         <v>487</v>
       </c>
       <c r="E1407" t="s">
-        <v>4022</v>
+        <v>4021</v>
       </c>
       <c r="F1407" s="29">
         <v>44680</v>
@@ -72266,7 +72334,7 @@
         <v>813</v>
       </c>
       <c r="J1407" s="63" t="s">
-        <v>4043</v>
+        <v>4042</v>
       </c>
       <c r="K1407">
         <v>1408</v>
@@ -72275,7 +72343,7 @@
         <v>854</v>
       </c>
       <c r="N1407" t="s">
-        <v>4057</v>
+        <v>4056</v>
       </c>
     </row>
     <row r="1408" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -72286,7 +72354,7 @@
         <v>54137910</v>
       </c>
       <c r="C1408" t="s">
-        <v>4059</v>
+        <v>4058</v>
       </c>
       <c r="D1408" t="s">
         <v>424</v>
@@ -72307,7 +72375,7 @@
         <v>806</v>
       </c>
       <c r="J1408" s="63" t="s">
-        <v>4058</v>
+        <v>4057</v>
       </c>
       <c r="K1408">
         <v>1409</v>
@@ -72316,7 +72384,7 @@
         <v>854</v>
       </c>
       <c r="N1408" t="s">
-        <v>4064</v>
+        <v>4063</v>
       </c>
     </row>
     <row r="1409" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -72348,7 +72416,7 @@
         <v>290</v>
       </c>
       <c r="J1409" s="63" t="s">
-        <v>4061</v>
+        <v>4060</v>
       </c>
       <c r="K1409">
         <v>1410</v>
@@ -72357,7 +72425,7 @@
         <v>854</v>
       </c>
       <c r="N1409" t="s">
-        <v>4065</v>
+        <v>4064</v>
       </c>
     </row>
     <row r="1410" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -72383,13 +72451,13 @@
         <v>0.10422453703703705</v>
       </c>
       <c r="H1410" s="151" t="s">
+        <v>4061</v>
+      </c>
+      <c r="I1410" s="151" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1410" s="63" t="s">
         <v>4062</v>
-      </c>
-      <c r="I1410" s="151" t="s">
-        <v>806</v>
-      </c>
-      <c r="J1410" s="63" t="s">
-        <v>4063</v>
       </c>
       <c r="K1410">
         <v>1411</v>
@@ -72398,7 +72466,7 @@
         <v>854</v>
       </c>
       <c r="N1410" t="s">
-        <v>4066</v>
+        <v>4065</v>
       </c>
     </row>
     <row r="1411" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -72424,13 +72492,13 @@
         <v>9.4386574074074081E-2</v>
       </c>
       <c r="H1411" s="151" t="s">
-        <v>4068</v>
+        <v>4067</v>
       </c>
       <c r="I1411" s="151" t="s">
         <v>806</v>
       </c>
       <c r="J1411" s="63" t="s">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="K1411">
         <v>1412</v>
@@ -72439,7 +72507,7 @@
         <v>854</v>
       </c>
       <c r="N1411" t="s">
-        <v>4069</v>
+        <v>4068</v>
       </c>
     </row>
     <row r="1412" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -72471,7 +72539,7 @@
         <v>290</v>
       </c>
       <c r="J1412" s="63" t="s">
-        <v>4070</v>
+        <v>4069</v>
       </c>
       <c r="K1412">
         <v>1413</v>
@@ -72480,7 +72548,7 @@
         <v>854</v>
       </c>
       <c r="N1412" t="s">
-        <v>4071</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="1413" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -72491,10 +72559,10 @@
         <v>7693476</v>
       </c>
       <c r="C1413" t="s">
+        <v>4071</v>
+      </c>
+      <c r="D1413" t="s">
         <v>4072</v>
-      </c>
-      <c r="D1413" t="s">
-        <v>4073</v>
       </c>
       <c r="E1413" t="s">
         <v>648</v>
@@ -72512,7 +72580,7 @@
         <v>290</v>
       </c>
       <c r="J1413" s="63" t="s">
-        <v>4074</v>
+        <v>4073</v>
       </c>
       <c r="K1413">
         <v>1414</v>
@@ -72521,7 +72589,7 @@
         <v>854</v>
       </c>
       <c r="N1413" t="s">
-        <v>4078</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1414" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -72553,7 +72621,7 @@
         <v>290</v>
       </c>
       <c r="J1414" s="63" t="s">
-        <v>4075</v>
+        <v>4074</v>
       </c>
       <c r="K1414">
         <v>1415</v>
@@ -72562,7 +72630,7 @@
         <v>854</v>
       </c>
       <c r="N1414" t="s">
-        <v>4079</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="1415" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -72573,10 +72641,10 @@
         <v>13091775</v>
       </c>
       <c r="C1415" t="s">
-        <v>4077</v>
+        <v>4076</v>
       </c>
       <c r="D1415" t="s">
-        <v>3909</v>
+        <v>3908</v>
       </c>
       <c r="E1415" t="s">
         <v>88</v>
@@ -72594,19 +72662,19 @@
         <v>290</v>
       </c>
       <c r="J1415" s="63" t="s">
-        <v>4076</v>
+        <v>4075</v>
       </c>
       <c r="K1415">
         <v>1416</v>
       </c>
       <c r="L1415" t="s">
-        <v>4084</v>
+        <v>4083</v>
       </c>
       <c r="M1415" s="57" t="s">
         <v>854</v>
       </c>
       <c r="N1415" t="s">
-        <v>4080</v>
+        <v>4079</v>
       </c>
     </row>
     <row r="1416" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -72620,7 +72688,7 @@
         <v>25</v>
       </c>
       <c r="D1416" t="s">
-        <v>3904</v>
+        <v>3903</v>
       </c>
       <c r="E1416" t="s">
         <v>648</v>
@@ -72638,7 +72706,7 @@
         <v>290</v>
       </c>
       <c r="J1416" s="63" t="s">
-        <v>4081</v>
+        <v>4080</v>
       </c>
       <c r="K1416">
         <v>1417</v>
@@ -72647,7 +72715,7 @@
         <v>854</v>
       </c>
       <c r="N1416" t="s">
-        <v>4094</v>
+        <v>4093</v>
       </c>
     </row>
     <row r="1417" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -72658,13 +72726,13 @@
         <v>11466215</v>
       </c>
       <c r="C1417" t="s">
-        <v>4085</v>
+        <v>4084</v>
       </c>
       <c r="D1417" t="s">
         <v>76</v>
       </c>
       <c r="E1417" t="s">
-        <v>4086</v>
+        <v>4085</v>
       </c>
       <c r="F1417" s="29">
         <v>44658</v>
@@ -72679,19 +72747,19 @@
         <v>813</v>
       </c>
       <c r="J1417" s="63" t="s">
-        <v>4082</v>
+        <v>4081</v>
       </c>
       <c r="K1417">
         <v>1418</v>
       </c>
       <c r="L1417" t="s">
-        <v>4083</v>
+        <v>4082</v>
       </c>
       <c r="M1417" s="57" t="s">
         <v>854</v>
       </c>
       <c r="N1417" t="s">
-        <v>4095</v>
+        <v>4094</v>
       </c>
     </row>
     <row r="1418" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -72702,13 +72770,13 @@
         <v>3883470</v>
       </c>
       <c r="C1418" t="s">
-        <v>4085</v>
+        <v>4084</v>
       </c>
       <c r="D1418" t="s">
         <v>203</v>
       </c>
       <c r="E1418" t="s">
-        <v>4086</v>
+        <v>4085</v>
       </c>
       <c r="F1418" s="29">
         <v>44665</v>
@@ -72723,19 +72791,19 @@
         <v>290</v>
       </c>
       <c r="J1418" s="63" t="s">
-        <v>4087</v>
+        <v>4086</v>
       </c>
       <c r="K1418">
         <v>1419</v>
       </c>
       <c r="L1418" t="s">
-        <v>4083</v>
+        <v>4082</v>
       </c>
       <c r="M1418" s="57" t="s">
         <v>854</v>
       </c>
       <c r="N1418" t="s">
-        <v>4096</v>
+        <v>4095</v>
       </c>
     </row>
     <row r="1419" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -72746,13 +72814,13 @@
         <v>9895396</v>
       </c>
       <c r="C1419" t="s">
-        <v>4088</v>
+        <v>4087</v>
       </c>
       <c r="D1419" t="s">
         <v>76</v>
       </c>
       <c r="E1419" t="s">
-        <v>4089</v>
+        <v>4088</v>
       </c>
       <c r="F1419" s="29">
         <v>44675</v>
@@ -72767,7 +72835,7 @@
         <v>813</v>
       </c>
       <c r="J1419" s="63" t="s">
-        <v>4090</v>
+        <v>4089</v>
       </c>
       <c r="K1419">
         <v>1420</v>
@@ -72776,7 +72844,7 @@
         <v>854</v>
       </c>
       <c r="N1419" t="s">
-        <v>4097</v>
+        <v>4096</v>
       </c>
     </row>
     <row r="1420" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -72790,7 +72858,7 @@
         <v>488</v>
       </c>
       <c r="D1420" t="s">
-        <v>3909</v>
+        <v>3908</v>
       </c>
       <c r="E1420" t="s">
         <v>488</v>
@@ -72808,7 +72876,7 @@
         <v>813</v>
       </c>
       <c r="J1420" s="63" t="s">
-        <v>4091</v>
+        <v>4090</v>
       </c>
       <c r="K1420">
         <v>1421</v>
@@ -72817,7 +72885,7 @@
         <v>854</v>
       </c>
       <c r="N1420" t="s">
-        <v>4098</v>
+        <v>4097</v>
       </c>
     </row>
     <row r="1421" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -72849,7 +72917,7 @@
         <v>290</v>
       </c>
       <c r="J1421" s="63" t="s">
-        <v>4092</v>
+        <v>4091</v>
       </c>
       <c r="K1421">
         <v>1422</v>
@@ -72858,7 +72926,7 @@
         <v>854</v>
       </c>
       <c r="N1421" t="s">
-        <v>4099</v>
+        <v>4098</v>
       </c>
     </row>
     <row r="1422" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -72890,7 +72958,7 @@
         <v>806</v>
       </c>
       <c r="J1422" s="63" t="s">
-        <v>4093</v>
+        <v>4092</v>
       </c>
       <c r="K1422">
         <v>1423</v>
@@ -72899,7 +72967,7 @@
         <v>854</v>
       </c>
       <c r="N1422" t="s">
-        <v>4100</v>
+        <v>4099</v>
       </c>
     </row>
     <row r="1423" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -72925,13 +72993,13 @@
         <v>502</v>
       </c>
       <c r="H1423" s="156" t="s">
+        <v>4100</v>
+      </c>
+      <c r="I1423" s="156" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1423" s="63" t="s">
         <v>4101</v>
-      </c>
-      <c r="I1423" s="156" t="s">
-        <v>806</v>
-      </c>
-      <c r="J1423" s="63" t="s">
-        <v>4102</v>
       </c>
       <c r="K1423">
         <v>1424</v>
@@ -72940,7 +73008,7 @@
         <v>854</v>
       </c>
       <c r="N1423" t="s">
-        <v>4107</v>
+        <v>4106</v>
       </c>
     </row>
     <row r="1424" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -72966,13 +73034,13 @@
         <v>9.1712962962962954E-2</v>
       </c>
       <c r="H1424" s="156" t="s">
-        <v>4104</v>
+        <v>4103</v>
       </c>
       <c r="I1424" s="156" t="s">
         <v>806</v>
       </c>
       <c r="J1424" s="63" t="s">
-        <v>4103</v>
+        <v>4102</v>
       </c>
       <c r="K1424">
         <v>1425</v>
@@ -72981,7 +73049,7 @@
         <v>854</v>
       </c>
       <c r="N1424" t="s">
-        <v>4108</v>
+        <v>4107</v>
       </c>
     </row>
     <row r="1425" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -72992,7 +73060,7 @@
         <v>10146360</v>
       </c>
       <c r="C1425" t="s">
-        <v>3710</v>
+        <v>3709</v>
       </c>
       <c r="D1425" t="s">
         <v>393</v>
@@ -73013,7 +73081,7 @@
         <v>806</v>
       </c>
       <c r="J1425" t="s">
-        <v>4105</v>
+        <v>4104</v>
       </c>
       <c r="K1425">
         <v>1426</v>
@@ -73022,7 +73090,7 @@
         <v>854</v>
       </c>
       <c r="N1425" t="s">
-        <v>4109</v>
+        <v>4108</v>
       </c>
     </row>
     <row r="1426" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73054,7 +73122,7 @@
         <v>806</v>
       </c>
       <c r="J1426" t="s">
-        <v>4106</v>
+        <v>4105</v>
       </c>
       <c r="K1426">
         <v>1427</v>
@@ -73063,7 +73131,7 @@
         <v>854</v>
       </c>
       <c r="N1426" t="s">
-        <v>4110</v>
+        <v>4109</v>
       </c>
     </row>
     <row r="1427" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73095,7 +73163,7 @@
         <v>290</v>
       </c>
       <c r="J1427" s="63" t="s">
-        <v>4111</v>
+        <v>4110</v>
       </c>
       <c r="K1427">
         <v>1428</v>
@@ -73104,7 +73172,7 @@
         <v>854</v>
       </c>
       <c r="N1427" t="s">
-        <v>4114</v>
+        <v>4113</v>
       </c>
     </row>
     <row r="1428" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73118,7 +73186,7 @@
         <v>1473</v>
       </c>
       <c r="D1428" t="s">
-        <v>3917</v>
+        <v>3916</v>
       </c>
       <c r="E1428" t="s">
         <v>1473</v>
@@ -73136,7 +73204,7 @@
         <v>290</v>
       </c>
       <c r="J1428" s="63" t="s">
-        <v>4112</v>
+        <v>4111</v>
       </c>
       <c r="K1428">
         <v>1429</v>
@@ -73145,7 +73213,7 @@
         <v>854</v>
       </c>
       <c r="N1428" t="s">
-        <v>4115</v>
+        <v>4114</v>
       </c>
     </row>
     <row r="1429" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73156,7 +73224,7 @@
         <v>11082827</v>
       </c>
       <c r="C1429" t="s">
-        <v>3710</v>
+        <v>3709</v>
       </c>
       <c r="D1429" t="s">
         <v>172</v>
@@ -73177,7 +73245,7 @@
         <v>290</v>
       </c>
       <c r="J1429" s="63" t="s">
-        <v>4113</v>
+        <v>4112</v>
       </c>
       <c r="K1429">
         <v>1430</v>
@@ -73186,7 +73254,7 @@
         <v>854</v>
       </c>
       <c r="N1429" t="s">
-        <v>4116</v>
+        <v>4115</v>
       </c>
     </row>
     <row r="1430" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73197,7 +73265,7 @@
         <v>17360872</v>
       </c>
       <c r="C1430" t="s">
-        <v>4117</v>
+        <v>4116</v>
       </c>
       <c r="D1430" t="s">
         <v>424</v>
@@ -73218,7 +73286,7 @@
         <v>806</v>
       </c>
       <c r="J1430" s="63" t="s">
-        <v>4119</v>
+        <v>4118</v>
       </c>
       <c r="K1430">
         <v>1431</v>
@@ -73227,7 +73295,7 @@
         <v>854</v>
       </c>
       <c r="N1430" t="s">
-        <v>4136</v>
+        <v>4135</v>
       </c>
     </row>
     <row r="1431" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73238,7 +73306,7 @@
         <v>12424839</v>
       </c>
       <c r="C1431" t="s">
-        <v>4121</v>
+        <v>4120</v>
       </c>
       <c r="D1431" t="s">
         <v>424</v>
@@ -73259,7 +73327,7 @@
         <v>806</v>
       </c>
       <c r="J1431" s="63" t="s">
-        <v>4120</v>
+        <v>4119</v>
       </c>
       <c r="K1431">
         <v>1432</v>
@@ -73268,7 +73336,7 @@
         <v>854</v>
       </c>
       <c r="N1431" t="s">
-        <v>4137</v>
+        <v>4136</v>
       </c>
     </row>
     <row r="1432" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73300,7 +73368,7 @@
         <v>290</v>
       </c>
       <c r="J1432" s="63" t="s">
-        <v>4122</v>
+        <v>4121</v>
       </c>
       <c r="K1432">
         <v>1433</v>
@@ -73309,7 +73377,7 @@
         <v>854</v>
       </c>
       <c r="N1432" t="s">
-        <v>4138</v>
+        <v>4137</v>
       </c>
     </row>
     <row r="1433" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73341,7 +73409,7 @@
         <v>290</v>
       </c>
       <c r="J1433" s="63" t="s">
-        <v>4123</v>
+        <v>4122</v>
       </c>
       <c r="K1433">
         <v>1434</v>
@@ -73350,7 +73418,7 @@
         <v>854</v>
       </c>
       <c r="N1433" t="s">
-        <v>4139</v>
+        <v>4138</v>
       </c>
     </row>
     <row r="1434" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73361,7 +73429,7 @@
         <v>7706544</v>
       </c>
       <c r="C1434" t="s">
-        <v>4126</v>
+        <v>4125</v>
       </c>
       <c r="D1434" t="s">
         <v>276</v>
@@ -73376,13 +73444,13 @@
         <v>8.6296296296296301E-2</v>
       </c>
       <c r="H1434" s="159" t="s">
-        <v>4127</v>
+        <v>4126</v>
       </c>
       <c r="I1434" s="159" t="s">
         <v>290</v>
       </c>
       <c r="J1434" s="63" t="s">
-        <v>4124</v>
+        <v>4123</v>
       </c>
       <c r="K1434">
         <v>1435</v>
@@ -73391,7 +73459,7 @@
         <v>854</v>
       </c>
       <c r="N1434" t="s">
-        <v>4140</v>
+        <v>4139</v>
       </c>
     </row>
     <row r="1435" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73423,7 +73491,7 @@
         <v>806</v>
       </c>
       <c r="J1435" s="63" t="s">
-        <v>4128</v>
+        <v>4127</v>
       </c>
       <c r="K1435">
         <v>1436</v>
@@ -73432,7 +73500,7 @@
         <v>854</v>
       </c>
       <c r="N1435" t="s">
-        <v>4141</v>
+        <v>4140</v>
       </c>
     </row>
     <row r="1436" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73443,7 +73511,7 @@
         <v>4687810</v>
       </c>
       <c r="C1436" t="s">
-        <v>4130</v>
+        <v>4129</v>
       </c>
       <c r="D1436" t="s">
         <v>117</v>
@@ -73458,13 +73526,13 @@
         <v>3.7893518518518521E-2</v>
       </c>
       <c r="H1436" s="159" t="s">
-        <v>4131</v>
+        <v>4130</v>
       </c>
       <c r="I1436" s="159" t="s">
         <v>806</v>
       </c>
       <c r="J1436" s="63" t="s">
-        <v>4129</v>
+        <v>4128</v>
       </c>
       <c r="K1436">
         <v>1437</v>
@@ -73473,7 +73541,7 @@
         <v>854</v>
       </c>
       <c r="N1436" t="s">
-        <v>4142</v>
+        <v>4141</v>
       </c>
     </row>
     <row r="1437" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73505,7 +73573,7 @@
         <v>290</v>
       </c>
       <c r="J1437" s="63" t="s">
-        <v>4132</v>
+        <v>4131</v>
       </c>
       <c r="K1437">
         <v>1438</v>
@@ -73514,7 +73582,7 @@
         <v>854</v>
       </c>
       <c r="N1437" t="s">
-        <v>4143</v>
+        <v>4142</v>
       </c>
     </row>
     <row r="1438" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73525,7 +73593,7 @@
         <v>11879917</v>
       </c>
       <c r="C1438" t="s">
-        <v>4133</v>
+        <v>4132</v>
       </c>
       <c r="D1438" t="s">
         <v>9</v>
@@ -73546,7 +73614,7 @@
         <v>806</v>
       </c>
       <c r="J1438" s="63" t="s">
-        <v>4134</v>
+        <v>4133</v>
       </c>
       <c r="K1438">
         <v>1439</v>
@@ -73555,7 +73623,7 @@
         <v>854</v>
       </c>
       <c r="N1438" t="s">
-        <v>4144</v>
+        <v>4143</v>
       </c>
     </row>
     <row r="1439" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73566,7 +73634,7 @@
         <v>9493583</v>
       </c>
       <c r="C1439" t="s">
-        <v>4145</v>
+        <v>4144</v>
       </c>
       <c r="D1439" t="s">
         <v>33</v>
@@ -73587,7 +73655,7 @@
         <v>806</v>
       </c>
       <c r="J1439" s="63" t="s">
-        <v>4146</v>
+        <v>4145</v>
       </c>
       <c r="K1439">
         <v>1440</v>
@@ -73596,7 +73664,7 @@
         <v>854</v>
       </c>
       <c r="N1439" t="s">
-        <v>4154</v>
+        <v>4153</v>
       </c>
     </row>
     <row r="1440" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73628,7 +73696,7 @@
         <v>806</v>
       </c>
       <c r="J1440" s="63" t="s">
-        <v>4147</v>
+        <v>4146</v>
       </c>
       <c r="K1440">
         <v>1441</v>
@@ -73637,7 +73705,7 @@
         <v>854</v>
       </c>
       <c r="N1440" t="s">
-        <v>4155</v>
+        <v>4154</v>
       </c>
     </row>
     <row r="1441" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73648,13 +73716,13 @@
         <v>4930000</v>
       </c>
       <c r="C1441" t="s">
-        <v>4149</v>
+        <v>4148</v>
       </c>
       <c r="D1441" t="s">
         <v>305</v>
       </c>
       <c r="E1441" t="s">
-        <v>4149</v>
+        <v>4148</v>
       </c>
       <c r="F1441" s="29">
         <v>45766</v>
@@ -73669,7 +73737,7 @@
         <v>806</v>
       </c>
       <c r="J1441" s="63" t="s">
-        <v>4148</v>
+        <v>4147</v>
       </c>
       <c r="K1441">
         <v>1442</v>
@@ -73678,7 +73746,7 @@
         <v>854</v>
       </c>
       <c r="N1441" t="s">
-        <v>4156</v>
+        <v>4155</v>
       </c>
     </row>
     <row r="1442" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73689,13 +73757,13 @@
         <v>12540000</v>
       </c>
       <c r="C1442" t="s">
-        <v>4150</v>
+        <v>4149</v>
       </c>
       <c r="D1442" t="s">
         <v>40</v>
       </c>
       <c r="E1442" t="s">
-        <v>4159</v>
+        <v>4158</v>
       </c>
       <c r="F1442" s="29">
         <v>45875</v>
@@ -73710,7 +73778,7 @@
         <v>806</v>
       </c>
       <c r="J1442" s="63" t="s">
-        <v>4152</v>
+        <v>4151</v>
       </c>
       <c r="K1442">
         <v>1443</v>
@@ -73719,7 +73787,7 @@
         <v>854</v>
       </c>
       <c r="N1442" t="s">
-        <v>4157</v>
+        <v>4156</v>
       </c>
     </row>
     <row r="1443" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73730,13 +73798,13 @@
         <v>12210000</v>
       </c>
       <c r="C1443" t="s">
-        <v>4151</v>
+        <v>4150</v>
       </c>
       <c r="D1443" t="s">
         <v>65</v>
       </c>
       <c r="E1443" t="s">
-        <v>4151</v>
+        <v>4150</v>
       </c>
       <c r="F1443" s="29">
         <v>45875</v>
@@ -73751,7 +73819,7 @@
         <v>806</v>
       </c>
       <c r="J1443" s="63" t="s">
-        <v>4153</v>
+        <v>4152</v>
       </c>
       <c r="K1443">
         <v>1444</v>
@@ -73760,7 +73828,7 @@
         <v>854</v>
       </c>
       <c r="N1443" t="s">
-        <v>4158</v>
+        <v>4157</v>
       </c>
     </row>
     <row r="1444" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73771,13 +73839,13 @@
         <v>22630000</v>
       </c>
       <c r="C1444" t="s">
-        <v>4160</v>
+        <v>4159</v>
       </c>
       <c r="D1444" t="s">
         <v>60</v>
       </c>
       <c r="E1444" t="s">
-        <v>4160</v>
+        <v>4159</v>
       </c>
       <c r="F1444" s="29">
         <v>46144</v>
@@ -73792,7 +73860,7 @@
         <v>806</v>
       </c>
       <c r="J1444" s="63" t="s">
-        <v>4161</v>
+        <v>4160</v>
       </c>
       <c r="K1444">
         <v>1445</v>
@@ -73801,7 +73869,7 @@
         <v>854</v>
       </c>
       <c r="N1444" t="s">
-        <v>4174</v>
+        <v>4173</v>
       </c>
     </row>
     <row r="1445" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73830,7 +73898,7 @@
         <v>806</v>
       </c>
       <c r="J1445" s="63" t="s">
-        <v>4162</v>
+        <v>4161</v>
       </c>
       <c r="K1445">
         <v>1446</v>
@@ -73839,7 +73907,7 @@
         <v>854</v>
       </c>
       <c r="N1445" t="s">
-        <v>4175</v>
+        <v>4174</v>
       </c>
     </row>
     <row r="1446" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73871,7 +73939,7 @@
         <v>806</v>
       </c>
       <c r="J1446" s="63" t="s">
-        <v>4163</v>
+        <v>4162</v>
       </c>
       <c r="K1446">
         <v>1447</v>
@@ -73880,7 +73948,7 @@
         <v>854</v>
       </c>
       <c r="N1446" t="s">
-        <v>4176</v>
+        <v>4175</v>
       </c>
     </row>
     <row r="1447" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73891,10 +73959,10 @@
         <v>13197466</v>
       </c>
       <c r="C1447" t="s">
-        <v>4167</v>
+        <v>4166</v>
       </c>
       <c r="D1447" t="s">
-        <v>3718</v>
+        <v>3717</v>
       </c>
       <c r="E1447" t="s">
         <v>51</v>
@@ -73912,7 +73980,7 @@
         <v>806</v>
       </c>
       <c r="J1447" s="63" t="s">
-        <v>4164</v>
+        <v>4163</v>
       </c>
       <c r="K1447">
         <v>1448</v>
@@ -73921,7 +73989,7 @@
         <v>854</v>
       </c>
       <c r="N1447" t="s">
-        <v>4177</v>
+        <v>4176</v>
       </c>
     </row>
     <row r="1448" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73935,7 +74003,7 @@
         <v>17</v>
       </c>
       <c r="D1448" t="s">
-        <v>3828</v>
+        <v>3827</v>
       </c>
       <c r="E1448" t="s">
         <v>18</v>
@@ -73953,7 +74021,7 @@
         <v>806</v>
       </c>
       <c r="J1448" s="63" t="s">
-        <v>4165</v>
+        <v>4164</v>
       </c>
       <c r="K1448">
         <v>1449</v>
@@ -73962,7 +74030,7 @@
         <v>854</v>
       </c>
       <c r="N1448" t="s">
-        <v>4178</v>
+        <v>4177</v>
       </c>
     </row>
     <row r="1449" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73973,10 +74041,10 @@
         <v>9164274</v>
       </c>
       <c r="C1449" t="s">
-        <v>4167</v>
+        <v>4166</v>
       </c>
       <c r="D1449" t="s">
-        <v>3718</v>
+        <v>3717</v>
       </c>
       <c r="E1449" t="s">
         <v>51</v>
@@ -73994,7 +74062,7 @@
         <v>806</v>
       </c>
       <c r="J1449" s="63" t="s">
-        <v>4166</v>
+        <v>4165</v>
       </c>
       <c r="K1449">
         <v>1450</v>
@@ -74003,7 +74071,7 @@
         <v>854</v>
       </c>
       <c r="N1449" t="s">
-        <v>4179</v>
+        <v>4178</v>
       </c>
     </row>
     <row r="1450" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74014,10 +74082,10 @@
         <v>7516720</v>
       </c>
       <c r="C1450" t="s">
-        <v>4167</v>
+        <v>4166</v>
       </c>
       <c r="D1450" t="s">
-        <v>3718</v>
+        <v>3717</v>
       </c>
       <c r="E1450" t="s">
         <v>51</v>
@@ -74035,7 +74103,7 @@
         <v>806</v>
       </c>
       <c r="J1450" s="63" t="s">
-        <v>4168</v>
+        <v>4167</v>
       </c>
       <c r="K1450">
         <v>1451</v>
@@ -74044,7 +74112,7 @@
         <v>854</v>
       </c>
       <c r="N1450" t="s">
-        <v>4180</v>
+        <v>4179</v>
       </c>
     </row>
     <row r="1451" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74058,7 +74126,7 @@
         <v>17</v>
       </c>
       <c r="D1451" t="s">
-        <v>4170</v>
+        <v>4169</v>
       </c>
       <c r="E1451" t="s">
         <v>18</v>
@@ -74076,7 +74144,7 @@
         <v>806</v>
       </c>
       <c r="J1451" s="63" t="s">
-        <v>4169</v>
+        <v>4168</v>
       </c>
       <c r="K1451">
         <v>1452</v>
@@ -74085,7 +74153,7 @@
         <v>854</v>
       </c>
       <c r="N1451" t="s">
-        <v>4181</v>
+        <v>4180</v>
       </c>
     </row>
     <row r="1452" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74117,7 +74185,7 @@
         <v>806</v>
       </c>
       <c r="J1452" s="63" t="s">
-        <v>4171</v>
+        <v>4170</v>
       </c>
       <c r="K1452">
         <v>1453</v>
@@ -74126,7 +74194,7 @@
         <v>854</v>
       </c>
       <c r="N1452" t="s">
-        <v>4182</v>
+        <v>4181</v>
       </c>
     </row>
     <row r="1453" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74137,13 +74205,13 @@
         <v>8740000</v>
       </c>
       <c r="C1453" t="s">
-        <v>4172</v>
+        <v>4171</v>
       </c>
       <c r="D1453" t="s">
         <v>330</v>
       </c>
       <c r="E1453" t="s">
-        <v>4172</v>
+        <v>4171</v>
       </c>
       <c r="F1453" s="29">
         <v>46144</v>
@@ -74158,7 +74226,7 @@
         <v>806</v>
       </c>
       <c r="J1453" s="63" t="s">
-        <v>4173</v>
+        <v>4172</v>
       </c>
       <c r="K1453">
         <v>1454</v>
@@ -74167,7 +74235,299 @@
         <v>854</v>
       </c>
       <c r="N1453" t="s">
+        <v>4182</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1454">
+        <v>75</v>
+      </c>
+      <c r="B1454" s="7">
+        <v>12338944</v>
+      </c>
+      <c r="C1454" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1454" t="s">
+        <v>691</v>
+      </c>
+      <c r="E1454" t="s">
+        <v>3429</v>
+      </c>
+      <c r="F1454" s="29">
+        <v>46144</v>
+      </c>
+      <c r="G1454" s="56">
+        <v>0.10556712962962962</v>
+      </c>
+      <c r="H1454" s="162" t="s">
+        <v>2753</v>
+      </c>
+      <c r="I1454" s="162" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1454" s="63" t="s">
         <v>4183</v>
+      </c>
+      <c r="K1454">
+        <v>1455</v>
+      </c>
+      <c r="M1454" s="162" t="s">
+        <v>4194</v>
+      </c>
+      <c r="N1454" t="s">
+        <v>4195</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1455">
+        <v>75</v>
+      </c>
+      <c r="B1455" s="7">
+        <v>8421047</v>
+      </c>
+      <c r="C1455" t="s">
+        <v>4185</v>
+      </c>
+      <c r="D1455" t="s">
+        <v>395</v>
+      </c>
+      <c r="E1455" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1455" s="29">
+        <v>46144</v>
+      </c>
+      <c r="G1455" s="56">
+        <v>7.03125E-2</v>
+      </c>
+      <c r="H1455" s="162" t="s">
+        <v>1106</v>
+      </c>
+      <c r="I1455" s="162" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1455" s="63" t="s">
+        <v>4184</v>
+      </c>
+      <c r="K1455">
+        <v>1456</v>
+      </c>
+      <c r="M1455" s="162" t="s">
+        <v>4194</v>
+      </c>
+      <c r="N1455" t="s">
+        <v>4196</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1456">
+        <v>75</v>
+      </c>
+      <c r="B1456" s="7">
+        <v>8509859</v>
+      </c>
+      <c r="C1456" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1456" t="s">
+        <v>4189</v>
+      </c>
+      <c r="E1456" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1456" s="29">
+        <v>46145</v>
+      </c>
+      <c r="G1456" s="56">
+        <v>6.4398148148148149E-2</v>
+      </c>
+      <c r="H1456" s="162" t="s">
+        <v>817</v>
+      </c>
+      <c r="I1456" s="162" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1456" s="63" t="s">
+        <v>4186</v>
+      </c>
+      <c r="K1456">
+        <v>1457</v>
+      </c>
+      <c r="M1456" s="162" t="s">
+        <v>4194</v>
+      </c>
+      <c r="N1456" t="s">
+        <v>4197</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1457">
+        <v>75</v>
+      </c>
+      <c r="B1457" s="7">
+        <v>1003218</v>
+      </c>
+      <c r="C1457" t="s">
+        <v>4190</v>
+      </c>
+      <c r="D1457" t="s">
+        <v>604</v>
+      </c>
+      <c r="E1457" t="s">
+        <v>4191</v>
+      </c>
+      <c r="F1457" s="29">
+        <v>46145</v>
+      </c>
+      <c r="G1457" s="56">
+        <v>2.9976851851851852E-2</v>
+      </c>
+      <c r="H1457" s="162" t="s">
+        <v>805</v>
+      </c>
+      <c r="I1457" s="162" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1457" s="63" t="s">
+        <v>4187</v>
+      </c>
+      <c r="K1457">
+        <v>1458</v>
+      </c>
+      <c r="M1457" s="162" t="s">
+        <v>4194</v>
+      </c>
+      <c r="N1457" t="s">
+        <v>4198</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1458">
+        <v>75</v>
+      </c>
+      <c r="B1458" s="7">
+        <v>17200702</v>
+      </c>
+      <c r="C1458" t="s">
+        <v>3709</v>
+      </c>
+      <c r="D1458" t="s">
+        <v>564</v>
+      </c>
+      <c r="E1458" t="s">
+        <v>236</v>
+      </c>
+      <c r="F1458" s="29">
+        <v>46145</v>
+      </c>
+      <c r="G1458" s="56">
+        <v>0.17938657407407407</v>
+      </c>
+      <c r="H1458" s="162" t="s">
+        <v>817</v>
+      </c>
+      <c r="I1458" s="162" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1458" s="63" t="s">
+        <v>4188</v>
+      </c>
+      <c r="K1458">
+        <v>1459</v>
+      </c>
+      <c r="M1458" s="162" t="s">
+        <v>4194</v>
+      </c>
+      <c r="N1458" t="s">
+        <v>4199</v>
+      </c>
+    </row>
+    <row r="1459" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1459">
+        <v>75</v>
+      </c>
+      <c r="B1459" s="7">
+        <v>10745119</v>
+      </c>
+      <c r="C1459" t="s">
+        <v>4166</v>
+      </c>
+      <c r="D1459" t="s">
+        <v>3717</v>
+      </c>
+      <c r="E1459" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1459" s="29">
+        <v>46145</v>
+      </c>
+      <c r="G1459" s="56">
+        <v>5.2731481481481483E-2</v>
+      </c>
+      <c r="H1459" s="162" t="s">
+        <v>2352</v>
+      </c>
+      <c r="I1459" s="162" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1459" s="63" t="s">
+        <v>4192</v>
+      </c>
+      <c r="K1459">
+        <v>1460</v>
+      </c>
+      <c r="M1459" s="162" t="s">
+        <v>4194</v>
+      </c>
+      <c r="N1459" t="s">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="1460" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1460">
+        <v>75</v>
+      </c>
+      <c r="B1460" s="7">
+        <v>38086184</v>
+      </c>
+      <c r="C1460" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1460" t="s">
+        <v>463</v>
+      </c>
+      <c r="E1460" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1460" s="29">
+        <v>46145</v>
+      </c>
+      <c r="G1460" s="56">
+        <v>0.23512731481481483</v>
+      </c>
+      <c r="H1460" s="162" t="s">
+        <v>825</v>
+      </c>
+      <c r="I1460" s="162" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1460" s="63" t="s">
+        <v>4193</v>
+      </c>
+      <c r="K1460">
+        <v>1461</v>
+      </c>
+      <c r="M1460" s="162" t="s">
+        <v>4194</v>
+      </c>
+      <c r="N1460" t="s">
+        <v>4201</v>
+      </c>
+    </row>
+    <row r="1461" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1461">
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12100" uniqueCount="4204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12197" uniqueCount="4233">
   <si>
     <t>Ņ</t>
   </si>
@@ -12611,9 +12611,6 @@
     <t>W1</t>
   </si>
   <si>
-    <t>[o]</t>
-  </si>
-  <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1500398868628635658/id_Wv.png?ex=69f84ad6&amp;is=69f6f956&amp;hm=993b9cd57845eac5b3144be2d5bca870686f2f050e847f1f6c35f97f771117e9</t>
   </si>
   <si>
@@ -12639,6 +12636,96 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1471844339931021342/1500407515505098913/id_Se.jpg?ex=69f852e3&amp;is=69f70163&amp;hm=4c4367f728acd972513e2851d41e96dc514991e6f6b7f68f33bfb12143695d86</t>
+  </si>
+  <si>
+    <t>W2</t>
+  </si>
+  <si>
+    <t>W3</t>
+  </si>
+  <si>
+    <t>Zaphkiel/Nest Guardian/Elite Crasher</t>
+  </si>
+  <si>
+    <t>FS💫</t>
+  </si>
+  <si>
+    <t>W4</t>
+  </si>
+  <si>
+    <t>W5</t>
+  </si>
+  <si>
+    <t>W6</t>
+  </si>
+  <si>
+    <t>Elite Crasher/LC</t>
+  </si>
+  <si>
+    <t>Cant wait to be crashed!</t>
+  </si>
+  <si>
+    <t>Cant wait</t>
+  </si>
+  <si>
+    <t>W7</t>
+  </si>
+  <si>
+    <t>W8</t>
+  </si>
+  <si>
+    <t>W9</t>
+  </si>
+  <si>
+    <t>Ragnarok/Exorcistor</t>
+  </si>
+  <si>
+    <t>W(</t>
+  </si>
+  <si>
+    <t>W)</t>
+  </si>
+  <si>
+    <t>XA</t>
+  </si>
+  <si>
+    <t>XB</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1501172707050524753/id_W2.png?ex=69fb1b87&amp;is=69f9ca07&amp;hm=48403b8fdbe49800fe9ce52a8bb95af3a5e5f6806829c8ed44861a076b818672</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1501172771927883786/id_W3.png?ex=69fb1b97&amp;is=69f9ca17&amp;hm=c5175a6ffdb1f3194f5387a3e9c4af1d78fa4557833bec4699552a08b8508e14</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1501172832397430794/id_W4.png?ex=69fb1ba5&amp;is=69f9ca25&amp;hm=702be0a489c72e25614946838994527616cc49313960a5ca10416d618ab98019</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1501172928862228530/id_W5.png?ex=69fb1bbc&amp;is=69f9ca3c&amp;hm=98f806afda4e19fe4162a8f41d4da7c86c0e4b4645f5b5b7adf5bae06c13d607</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1501173015818539028/id_W6.png?ex=69fb1bd1&amp;is=69f9ca51&amp;hm=26f996a83d876485efd8f356cae2c9c70dcc9003583f5e76ddb630d22a2f0657</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1501173175550083093/id_W7.png?ex=69fb1bf7&amp;is=69f9ca77&amp;hm=f9758e6a43f5a99f66bfe3ef824979292518adaf4cfe2a8828d9582559e7c3ce</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1501173266860216370/id_W8.png?ex=69fb1c0d&amp;is=69f9ca8d&amp;hm=db0bfff38a4c0cbaa9ddabf722db23fe29bebb72a2e65d328bbf296cf6b0c813</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1501173320362496010/id_W9.jpg?ex=69fb1c1a&amp;is=69f9ca9a&amp;hm=4bd93e1d0c9ba09a9f72274de84a25e5f03be2f63ea6fae320d8c884d4c64586</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1501173404038860840/id_W.png?ex=69fb1c2d&amp;is=69f9caad&amp;hm=ccacb5f9ac3c6104f3bbaea5283fad26b1055e6df9d89c9766588e46811d2b79</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1501173461127790613/id_W.jpg?ex=69fb1c3b&amp;is=69f9cabb&amp;hm=8ceed48ea98b454535e3cf17c9e239ee2a3a199ab3d6bb88d5b13afbfd08fac0</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1501173521911644201/id_XA.jpg?ex=69fb1c4a&amp;is=69f9caca&amp;hm=03ebf48306387d65fa635626f7e3a74c51753af8a2e7dc12a72c1611b5952dd0</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1501173581525287023/id_XB.png?ex=69fb1c58&amp;is=69f9cad8&amp;hm=522edbd94604304201c5515662101d31a98d9a2e5afb97e8a02ac3fdba625772</t>
   </si>
 </sst>
 </file>
@@ -12650,11 +12737,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="112" x14ac:knownFonts="1">
+  <fonts count="113" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -13467,118 +13561,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="163">
+  <cellXfs count="164">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="109" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="93" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="108" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="92" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="107" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="99" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="93" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="100" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="94" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="90" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="89" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="77" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="77" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="76" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="76" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="77" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="76" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="77" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="76" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="73" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="73" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="74" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="74" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="76" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="77" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="72" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="71" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="70" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="70" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="69" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="69" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13587,18 +13682,18 @@
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="53" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="53" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="52" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="52" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="46" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13612,15 +13707,15 @@
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13863,7 +13958,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1461"/>
+  <dimension ref="A1:O1472"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -63056,7 +63151,7 @@
         <v>0.10390046296296296</v>
       </c>
       <c r="H1181" s="162" t="s">
-        <v>4202</v>
+        <v>4201</v>
       </c>
       <c r="I1181" s="123" t="s">
         <v>806</v>
@@ -63074,7 +63169,7 @@
         <v>854</v>
       </c>
       <c r="N1181" t="s">
-        <v>4203</v>
+        <v>4202</v>
       </c>
     </row>
     <row r="1182" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74272,11 +74367,11 @@
       <c r="K1454">
         <v>1455</v>
       </c>
-      <c r="M1454" s="162" t="s">
+      <c r="M1454" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1454" t="s">
         <v>4194</v>
-      </c>
-      <c r="N1454" t="s">
-        <v>4195</v>
       </c>
     </row>
     <row r="1455" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74313,11 +74408,11 @@
       <c r="K1455">
         <v>1456</v>
       </c>
-      <c r="M1455" s="162" t="s">
-        <v>4194</v>
+      <c r="M1455" s="57" t="s">
+        <v>854</v>
       </c>
       <c r="N1455" t="s">
-        <v>4196</v>
+        <v>4195</v>
       </c>
     </row>
     <row r="1456" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74354,11 +74449,11 @@
       <c r="K1456">
         <v>1457</v>
       </c>
-      <c r="M1456" s="162" t="s">
-        <v>4194</v>
+      <c r="M1456" s="57" t="s">
+        <v>854</v>
       </c>
       <c r="N1456" t="s">
-        <v>4197</v>
+        <v>4196</v>
       </c>
     </row>
     <row r="1457" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74395,11 +74490,11 @@
       <c r="K1457">
         <v>1458</v>
       </c>
-      <c r="M1457" s="162" t="s">
-        <v>4194</v>
+      <c r="M1457" s="57" t="s">
+        <v>854</v>
       </c>
       <c r="N1457" t="s">
-        <v>4198</v>
+        <v>4197</v>
       </c>
     </row>
     <row r="1458" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74436,11 +74531,11 @@
       <c r="K1458">
         <v>1459</v>
       </c>
-      <c r="M1458" s="162" t="s">
-        <v>4194</v>
+      <c r="M1458" s="57" t="s">
+        <v>854</v>
       </c>
       <c r="N1458" t="s">
-        <v>4199</v>
+        <v>4198</v>
       </c>
     </row>
     <row r="1459" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74477,11 +74572,11 @@
       <c r="K1459">
         <v>1460</v>
       </c>
-      <c r="M1459" s="162" t="s">
-        <v>4194</v>
+      <c r="M1459" s="57" t="s">
+        <v>854</v>
       </c>
       <c r="N1459" t="s">
-        <v>4200</v>
+        <v>4199</v>
       </c>
     </row>
     <row r="1460" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74518,16 +74613,503 @@
       <c r="K1460">
         <v>1461</v>
       </c>
-      <c r="M1460" s="162" t="s">
-        <v>4194</v>
+      <c r="M1460" s="57" t="s">
+        <v>854</v>
       </c>
       <c r="N1460" t="s">
-        <v>4201</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="1461" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1461">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="B1461" s="7">
+        <v>24656052</v>
+      </c>
+      <c r="C1461" t="s">
+        <v>325</v>
+      </c>
+      <c r="D1461" t="s">
+        <v>313</v>
+      </c>
+      <c r="E1461" t="s">
+        <v>433</v>
+      </c>
+      <c r="F1461" s="29">
+        <v>46145</v>
+      </c>
+      <c r="G1461" s="56">
+        <v>0.22863425925925926</v>
+      </c>
+      <c r="H1461" s="163" t="s">
+        <v>885</v>
+      </c>
+      <c r="I1461" s="163" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1461" s="63" t="s">
+        <v>4203</v>
+      </c>
+      <c r="K1461">
+        <v>1462</v>
+      </c>
+      <c r="M1461" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1461" t="s">
+        <v>4221</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1462">
+        <v>76</v>
+      </c>
+      <c r="B1462" s="7">
+        <v>8318208</v>
+      </c>
+      <c r="C1462" t="s">
+        <v>4190</v>
+      </c>
+      <c r="D1462" t="s">
+        <v>424</v>
+      </c>
+      <c r="E1462" t="s">
+        <v>4191</v>
+      </c>
+      <c r="F1462" s="29">
+        <v>46146</v>
+      </c>
+      <c r="G1462" s="56">
+        <v>9.2615740740740748E-2</v>
+      </c>
+      <c r="H1462" s="163" t="s">
+        <v>4205</v>
+      </c>
+      <c r="I1462" s="163" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1462" s="63" t="s">
+        <v>4204</v>
+      </c>
+      <c r="K1462">
+        <v>1463</v>
+      </c>
+      <c r="M1462" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1462" t="s">
+        <v>4222</v>
+      </c>
+    </row>
+    <row r="1463" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1463">
+        <v>76</v>
+      </c>
+      <c r="B1463" s="7">
+        <v>14457611</v>
+      </c>
+      <c r="C1463" t="s">
+        <v>4206</v>
+      </c>
+      <c r="D1463" t="s">
+        <v>424</v>
+      </c>
+      <c r="E1463" t="s">
+        <v>720</v>
+      </c>
+      <c r="F1463" s="29">
+        <v>46145</v>
+      </c>
+      <c r="G1463" s="56">
+        <v>7.8599537037037037E-2</v>
+      </c>
+      <c r="H1463" s="163" t="s">
+        <v>815</v>
+      </c>
+      <c r="I1463" s="163" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1463" s="63" t="s">
+        <v>4207</v>
+      </c>
+      <c r="K1463">
+        <v>1464</v>
+      </c>
+      <c r="M1463" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1463" t="s">
+        <v>4223</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1464">
+        <v>76</v>
+      </c>
+      <c r="B1464" s="7">
+        <v>19385852</v>
+      </c>
+      <c r="C1464" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D1464" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1464" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1464" s="29">
+        <v>46145</v>
+      </c>
+      <c r="G1464" s="56">
+        <v>0.14760416666666668</v>
+      </c>
+      <c r="H1464" s="163" t="s">
+        <v>4100</v>
+      </c>
+      <c r="I1464" s="163" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1464" s="63" t="s">
+        <v>4208</v>
+      </c>
+      <c r="K1464">
+        <v>1465</v>
+      </c>
+      <c r="M1464" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1464" t="s">
+        <v>4224</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1465">
+        <v>76</v>
+      </c>
+      <c r="B1465" s="7">
+        <v>8040655</v>
+      </c>
+      <c r="C1465" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1465" t="s">
+        <v>3862</v>
+      </c>
+      <c r="E1465" t="s">
+        <v>648</v>
+      </c>
+      <c r="F1465" s="29">
+        <v>46145</v>
+      </c>
+      <c r="G1465" s="56">
+        <v>6.3842592592592604E-2</v>
+      </c>
+      <c r="H1465" s="163" t="s">
+        <v>4210</v>
+      </c>
+      <c r="I1465" s="163" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1465" s="63" t="s">
+        <v>4209</v>
+      </c>
+      <c r="K1465">
+        <v>1466</v>
+      </c>
+      <c r="M1465" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1465" t="s">
+        <v>4225</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1466">
+        <v>76</v>
+      </c>
+      <c r="B1466" s="7">
+        <v>24870000</v>
+      </c>
+      <c r="C1466" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D1466" t="s">
+        <v>424</v>
+      </c>
+      <c r="E1466" t="s">
+        <v>4212</v>
+      </c>
+      <c r="F1466" s="29">
+        <v>46145</v>
+      </c>
+      <c r="G1466" s="56" t="s">
+        <v>502</v>
+      </c>
+      <c r="H1466" s="163" t="s">
+        <v>502</v>
+      </c>
+      <c r="I1466" s="163" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1466" s="63" t="s">
+        <v>4213</v>
+      </c>
+      <c r="K1466">
+        <v>1467</v>
+      </c>
+      <c r="M1466" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1466" t="s">
+        <v>4226</v>
+      </c>
+    </row>
+    <row r="1467" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1467">
+        <v>76</v>
+      </c>
+      <c r="B1467" s="7">
+        <v>14722092</v>
+      </c>
+      <c r="C1467" t="s">
+        <v>4166</v>
+      </c>
+      <c r="D1467" t="s">
+        <v>3717</v>
+      </c>
+      <c r="E1467" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1467" s="29">
+        <v>46145</v>
+      </c>
+      <c r="G1467" s="56">
+        <v>9.780092592592593E-2</v>
+      </c>
+      <c r="H1467" s="163" t="s">
+        <v>885</v>
+      </c>
+      <c r="I1467" s="163" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1467" s="63" t="s">
+        <v>4214</v>
+      </c>
+      <c r="K1467">
+        <v>1468</v>
+      </c>
+      <c r="M1467" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1467" t="s">
+        <v>4227</v>
+      </c>
+    </row>
+    <row r="1468" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1468">
+        <v>76</v>
+      </c>
+      <c r="B1468" s="7">
+        <v>20236171</v>
+      </c>
+      <c r="C1468" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1468" t="s">
+        <v>463</v>
+      </c>
+      <c r="E1468" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1468" s="29">
+        <v>46145</v>
+      </c>
+      <c r="G1468" s="56">
+        <v>0.15199074074074073</v>
+      </c>
+      <c r="H1468" s="163" t="s">
+        <v>4216</v>
+      </c>
+      <c r="I1468" s="163" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1468" s="63" t="s">
+        <v>4215</v>
+      </c>
+      <c r="K1468">
+        <v>1469</v>
+      </c>
+      <c r="M1468" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1468" t="s">
+        <v>4228</v>
+      </c>
+    </row>
+    <row r="1469" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1469">
+        <v>76</v>
+      </c>
+      <c r="B1469" s="7">
+        <v>24456625</v>
+      </c>
+      <c r="C1469" t="s">
+        <v>4166</v>
+      </c>
+      <c r="D1469" t="s">
+        <v>3717</v>
+      </c>
+      <c r="E1469" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1469" s="29">
+        <v>46146</v>
+      </c>
+      <c r="G1469" s="56">
+        <v>0.19692129629629629</v>
+      </c>
+      <c r="H1469" s="163" t="s">
+        <v>942</v>
+      </c>
+      <c r="I1469" s="163" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1469" s="63" t="s">
+        <v>4217</v>
+      </c>
+      <c r="K1469">
+        <v>1470</v>
+      </c>
+      <c r="M1469" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1469" t="s">
+        <v>4229</v>
+      </c>
+    </row>
+    <row r="1470" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1470">
+        <v>76</v>
+      </c>
+      <c r="B1470" s="7">
+        <v>32348267</v>
+      </c>
+      <c r="C1470" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1470" t="s">
+        <v>619</v>
+      </c>
+      <c r="E1470" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1470" s="29">
+        <v>46146</v>
+      </c>
+      <c r="G1470" s="56">
+        <v>0.22931712962962961</v>
+      </c>
+      <c r="H1470" s="163" t="s">
+        <v>885</v>
+      </c>
+      <c r="I1470" s="163" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1470" s="63" t="s">
+        <v>4218</v>
+      </c>
+      <c r="K1470">
+        <v>1471</v>
+      </c>
+      <c r="M1470" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1470" t="s">
+        <v>4230</v>
+      </c>
+    </row>
+    <row r="1471" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1471">
+        <v>76</v>
+      </c>
+      <c r="B1471" s="7">
+        <v>15121012</v>
+      </c>
+      <c r="C1471" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1471" t="s">
+        <v>382</v>
+      </c>
+      <c r="E1471" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1471" s="29">
+        <v>46145</v>
+      </c>
+      <c r="G1471" s="56">
+        <v>7.5613425925925917E-2</v>
+      </c>
+      <c r="H1471" s="163" t="s">
+        <v>811</v>
+      </c>
+      <c r="I1471" s="163" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1471" s="63" t="s">
+        <v>4219</v>
+      </c>
+      <c r="K1471">
+        <v>1472</v>
+      </c>
+      <c r="M1471" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1471" t="s">
+        <v>4231</v>
+      </c>
+    </row>
+    <row r="1472" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1472">
+        <v>76</v>
+      </c>
+      <c r="B1472" s="7">
+        <v>41366389</v>
+      </c>
+      <c r="C1472" t="s">
+        <v>325</v>
+      </c>
+      <c r="D1472" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1472" t="s">
+        <v>433</v>
+      </c>
+      <c r="F1472" s="29">
+        <v>46146</v>
+      </c>
+      <c r="G1472" s="56">
+        <v>0.23133101851851853</v>
+      </c>
+      <c r="H1472" s="163" t="s">
+        <v>2415</v>
+      </c>
+      <c r="I1472" s="163" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1472" s="63" t="s">
+        <v>4220</v>
+      </c>
+      <c r="K1472">
+        <v>1473</v>
+      </c>
+      <c r="M1472" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1472" t="s">
+        <v>4232</v>
       </c>
     </row>
   </sheetData>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -74918,7 +74918,7 @@
         <v>17</v>
       </c>
       <c r="D1468" t="s">
-        <v>463</v>
+        <v>4169</v>
       </c>
       <c r="E1468" t="s">
         <v>18</v>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12197" uniqueCount="4233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12310" uniqueCount="4273">
   <si>
     <t>Ņ</t>
   </si>
@@ -12726,6 +12726,126 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1501173581525287023/id_XB.png?ex=69fb1c58&amp;is=69f9cad8&amp;hm=522edbd94604304201c5515662101d31a98d9a2e5afb97e8a02ac3fdba625772</t>
+  </si>
+  <si>
+    <t>Revolver</t>
+  </si>
+  <si>
+    <t>Nest Keeper/Nest Warden</t>
+  </si>
+  <si>
+    <t>XC</t>
+  </si>
+  <si>
+    <t>Desmos</t>
+  </si>
+  <si>
+    <t>Vanished</t>
+  </si>
+  <si>
+    <t>XD</t>
+  </si>
+  <si>
+    <t>XE</t>
+  </si>
+  <si>
+    <t>XF</t>
+  </si>
+  <si>
+    <t>XG</t>
+  </si>
+  <si>
+    <t>XH</t>
+  </si>
+  <si>
+    <t>XI</t>
+  </si>
+  <si>
+    <t>XJ</t>
+  </si>
+  <si>
+    <t>fragment of memories</t>
+  </si>
+  <si>
+    <t>XK</t>
+  </si>
+  <si>
+    <t>XL</t>
+  </si>
+  <si>
+    <t>Ragnarok/Kronos</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1502710974409609386/id_XC.png?ex=6a00b427&amp;is=69ff62a7&amp;hm=4a324ddb0b9b9f19aa14fb4548868d676ac7d387f9e76ff3d71107fdd1964064</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1502711093728903209/id_XD.png?ex=6a00b443&amp;is=69ff62c3&amp;hm=3db2afab5e6cea930b4b2a0e306d2ce4a2e4cd77243cf8d381b50d0a039a91f1</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1502711150352011488/id_XE.png?ex=6a00b451&amp;is=69ff62d1&amp;hm=8698f93356c7925cf0e7eb67ebe1cd172b0f0f2437a790ad14e14a1998515f67</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1502711200708956384/id_XF.png?ex=6a00b45d&amp;is=69ff62dd&amp;hm=b4fe6763225378a59fa2c562c0ce2b221e534b9f3df7b79a23a45c50c34af893</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1502711264307314890/id_XG.png?ex=6a00b46c&amp;is=69ff62ec&amp;hm=e677e5b41346cdd0f3d3f19a64a35d371e867e743398368ac2d9be46f8def986</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1502711326387208373/id_XH.png?ex=6a00b47b&amp;is=69ff62fb&amp;hm=42cae081831e8a7934d17b289887805671b77dfbaa8c8f4d776203f210a2f512</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1502711382183772313/id_XI.jpg?ex=6a00b488&amp;is=69ff6308&amp;hm=4559089fd5c1f7bed5c3807c0bd089cc91c4e71079ff72eb2e46d214ac7458f9</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1502711445731934208/id_XJ.jpg?ex=6a00b497&amp;is=69ff6317&amp;hm=980a66f8f2fa1a9129f7b5ae539c339458147500a93883233039acc03d4b7773</t>
+  </si>
+  <si>
+    <t>Vulture (re)</t>
+  </si>
+  <si>
+    <t>Enchantress/Summoner/Exorcistor</t>
+  </si>
+  <si>
+    <t>Single</t>
+  </si>
+  <si>
+    <t>XM</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1502713337472090173/id_XK.png?ex=6a00b65a&amp;is=69ff64da&amp;hm=ca67fed74068ce25550e8e4d0d511ac1e05c4f7d91ad7fd706ee973f0348eb92</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1502713413447712869/id_XL.png?ex=6a00b66c&amp;is=69ff64ec&amp;hm=ada3522143f38a3b2c9bac5db8ac889fe65de50aea70a21acc5a4b68213393f6</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1502713457651482687/id_XM.png?ex=6a00b677&amp;is=69ff64f7&amp;hm=8a209b156568021c638dec9d41295db76b02fb8be061048982e26d17a022966b</t>
+  </si>
+  <si>
+    <t>[] Deformed cat I am sorry</t>
+  </si>
+  <si>
+    <t>Auto-Tri-Angle</t>
+  </si>
+  <si>
+    <t>XN</t>
+  </si>
+  <si>
+    <t>XO</t>
+  </si>
+  <si>
+    <t>XP</t>
+  </si>
+  <si>
+    <t>Trap Guard</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1502715102586208507/id_XN.jpg?ex=6a00b7ff&amp;is=69ff667f&amp;hm=2536f96e8db165accfde781c06dedee99277a63470f5504ed1ea9d658800ad3b</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1502715174669521077/id_XO.jpg?ex=6a00b810&amp;is=69ff6690&amp;hm=879fc3da26659279807bf41832b08cfacf1a20be4b937bf657eac1b4b8de7594</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1502715223184773394/id_XP.png?ex=6a00b81c&amp;is=69ff669c&amp;hm=ec145eaaefb5d8a64bd389d86c0e44e0033d11fc4ffb01c595565418ca05d0c0</t>
   </si>
 </sst>
 </file>
@@ -12737,11 +12857,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="113" x14ac:knownFonts="1">
+  <fonts count="114" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -13561,118 +13688,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="164">
+  <cellXfs count="165">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="110" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="94" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="109" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="93" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="108" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="100" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="94" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="101" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="95" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="91" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="90" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="77" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="77" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="77" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="77" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="74" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="74" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="75" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="75" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="77" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="78" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="73" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="72" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="71" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="71" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="70" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="70" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13681,18 +13809,18 @@
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="53" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="53" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="48" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13706,15 +13834,15 @@
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13958,7 +14086,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1472"/>
+  <dimension ref="A1:O1486"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -75112,6 +75240,580 @@
         <v>4232</v>
       </c>
     </row>
+    <row r="1473" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1473">
+        <v>77</v>
+      </c>
+      <c r="B1473" s="7">
+        <v>11468036</v>
+      </c>
+      <c r="C1473" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1473" t="s">
+        <v>4233</v>
+      </c>
+      <c r="E1473" t="s">
+        <v>433</v>
+      </c>
+      <c r="F1473" s="29">
+        <v>46150</v>
+      </c>
+      <c r="G1473" s="56">
+        <v>0.17630787037037035</v>
+      </c>
+      <c r="H1473" s="164" t="s">
+        <v>4234</v>
+      </c>
+      <c r="I1473" s="164" t="s">
+        <v>290</v>
+      </c>
+      <c r="J1473" s="63" t="s">
+        <v>4235</v>
+      </c>
+      <c r="K1473">
+        <v>1474</v>
+      </c>
+      <c r="M1473" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1473" t="s">
+        <v>4249</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1474">
+        <v>77</v>
+      </c>
+      <c r="B1474" s="7">
+        <v>4841277</v>
+      </c>
+      <c r="C1474" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1474" t="s">
+        <v>4236</v>
+      </c>
+      <c r="E1474" t="s">
+        <v>157</v>
+      </c>
+      <c r="F1474" s="29">
+        <v>46150</v>
+      </c>
+      <c r="G1474" s="56">
+        <v>6.5173611111111113E-2</v>
+      </c>
+      <c r="H1474" s="164" t="s">
+        <v>4237</v>
+      </c>
+      <c r="I1474" s="164" t="s">
+        <v>290</v>
+      </c>
+      <c r="J1474" s="63" t="s">
+        <v>4238</v>
+      </c>
+      <c r="K1474">
+        <v>1475</v>
+      </c>
+      <c r="M1474" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1474" t="s">
+        <v>4250</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1475">
+        <v>77</v>
+      </c>
+      <c r="B1475" s="7">
+        <v>11244318</v>
+      </c>
+      <c r="C1475" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1475" t="s">
+        <v>276</v>
+      </c>
+      <c r="E1475" t="s">
+        <v>157</v>
+      </c>
+      <c r="F1475" s="29">
+        <v>46151</v>
+      </c>
+      <c r="G1475" s="56">
+        <v>8.324074074074074E-2</v>
+      </c>
+      <c r="H1475" s="164" t="s">
+        <v>885</v>
+      </c>
+      <c r="I1475" s="164" t="s">
+        <v>290</v>
+      </c>
+      <c r="J1475" s="63" t="s">
+        <v>4239</v>
+      </c>
+      <c r="K1475">
+        <v>1476</v>
+      </c>
+      <c r="M1475" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1475" t="s">
+        <v>4251</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1476">
+        <v>77</v>
+      </c>
+      <c r="B1476" s="7">
+        <v>8288200</v>
+      </c>
+      <c r="C1476" t="s">
+        <v>3709</v>
+      </c>
+      <c r="D1476" t="s">
+        <v>451</v>
+      </c>
+      <c r="E1476" t="s">
+        <v>236</v>
+      </c>
+      <c r="F1476" s="29">
+        <v>46150</v>
+      </c>
+      <c r="G1476" s="56">
+        <v>0.10398148148148149</v>
+      </c>
+      <c r="H1476" s="164" t="s">
+        <v>825</v>
+      </c>
+      <c r="I1476" s="164" t="s">
+        <v>290</v>
+      </c>
+      <c r="J1476" s="63" t="s">
+        <v>4240</v>
+      </c>
+      <c r="K1476">
+        <v>1477</v>
+      </c>
+      <c r="M1476" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1476" t="s">
+        <v>4252</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1477">
+        <v>77</v>
+      </c>
+      <c r="B1477" s="7">
+        <v>4313046</v>
+      </c>
+      <c r="C1477" t="s">
+        <v>3709</v>
+      </c>
+      <c r="D1477" t="s">
+        <v>451</v>
+      </c>
+      <c r="E1477" t="s">
+        <v>236</v>
+      </c>
+      <c r="F1477" s="29">
+        <v>46151</v>
+      </c>
+      <c r="G1477" s="56">
+        <v>5.4988425925925927E-2</v>
+      </c>
+      <c r="H1477" s="164" t="s">
+        <v>2459</v>
+      </c>
+      <c r="I1477" s="164" t="s">
+        <v>290</v>
+      </c>
+      <c r="J1477" s="63" t="s">
+        <v>4241</v>
+      </c>
+      <c r="K1477">
+        <v>1478</v>
+      </c>
+      <c r="M1477" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1477" t="s">
+        <v>4253</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1478">
+        <v>77</v>
+      </c>
+      <c r="B1478" s="7">
+        <v>10105389</v>
+      </c>
+      <c r="C1478" t="s">
+        <v>3709</v>
+      </c>
+      <c r="D1478" t="s">
+        <v>319</v>
+      </c>
+      <c r="E1478" t="s">
+        <v>236</v>
+      </c>
+      <c r="F1478" s="29">
+        <v>46151</v>
+      </c>
+      <c r="G1478" s="56">
+        <v>7.0983796296296295E-2</v>
+      </c>
+      <c r="H1478" s="164" t="s">
+        <v>885</v>
+      </c>
+      <c r="I1478" s="164" t="s">
+        <v>290</v>
+      </c>
+      <c r="J1478" s="63" t="s">
+        <v>4242</v>
+      </c>
+      <c r="K1478">
+        <v>1479</v>
+      </c>
+      <c r="M1478" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1478" t="s">
+        <v>4254</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1479">
+        <v>77</v>
+      </c>
+      <c r="B1479" s="7">
+        <v>11030705</v>
+      </c>
+      <c r="C1479" t="s">
+        <v>4245</v>
+      </c>
+      <c r="D1479" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1479" t="s">
+        <v>525</v>
+      </c>
+      <c r="F1479" s="29">
+        <v>46057</v>
+      </c>
+      <c r="G1479" s="56">
+        <v>7.9837962962962958E-2</v>
+      </c>
+      <c r="H1479" s="164" t="s">
+        <v>825</v>
+      </c>
+      <c r="I1479" s="164" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1479" s="63" t="s">
+        <v>4243</v>
+      </c>
+      <c r="K1479">
+        <v>1480</v>
+      </c>
+      <c r="M1479" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1479" t="s">
+        <v>4255</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1480">
+        <v>77</v>
+      </c>
+      <c r="B1480" s="7">
+        <v>5114100</v>
+      </c>
+      <c r="C1480" t="s">
+        <v>720</v>
+      </c>
+      <c r="D1480" t="s">
+        <v>372</v>
+      </c>
+      <c r="E1480" t="s">
+        <v>720</v>
+      </c>
+      <c r="F1480" s="29">
+        <v>46151</v>
+      </c>
+      <c r="G1480" s="56">
+        <v>5.0868055555555548E-2</v>
+      </c>
+      <c r="H1480" s="164" t="s">
+        <v>4248</v>
+      </c>
+      <c r="I1480" s="164" t="s">
+        <v>290</v>
+      </c>
+      <c r="J1480" s="63" t="s">
+        <v>4244</v>
+      </c>
+      <c r="K1480">
+        <v>1481</v>
+      </c>
+      <c r="M1480" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1480" t="s">
+        <v>4256</v>
+      </c>
+    </row>
+    <row r="1481" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1481">
+        <v>77</v>
+      </c>
+      <c r="B1481" s="7">
+        <v>3478697</v>
+      </c>
+      <c r="C1481" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1481" t="s">
+        <v>4257</v>
+      </c>
+      <c r="E1481" t="s">
+        <v>433</v>
+      </c>
+      <c r="F1481" s="29">
+        <v>46151</v>
+      </c>
+      <c r="G1481" s="56">
+        <v>5.2627314814814814E-2</v>
+      </c>
+      <c r="H1481" s="164" t="s">
+        <v>4258</v>
+      </c>
+      <c r="I1481" s="164" t="s">
+        <v>290</v>
+      </c>
+      <c r="J1481" s="63" t="s">
+        <v>4246</v>
+      </c>
+      <c r="K1481">
+        <v>1482</v>
+      </c>
+      <c r="M1481" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1481" t="s">
+        <v>4261</v>
+      </c>
+    </row>
+    <row r="1482" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1482">
+        <v>77</v>
+      </c>
+      <c r="B1482" s="7">
+        <v>2286366</v>
+      </c>
+      <c r="C1482" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1482" t="s">
+        <v>4259</v>
+      </c>
+      <c r="E1482" t="s">
+        <v>433</v>
+      </c>
+      <c r="F1482" s="29">
+        <v>46151</v>
+      </c>
+      <c r="G1482" s="56">
+        <v>9.0185185185185188E-2</v>
+      </c>
+      <c r="H1482" s="164" t="s">
+        <v>805</v>
+      </c>
+      <c r="I1482" s="164" t="s">
+        <v>290</v>
+      </c>
+      <c r="J1482" s="63" t="s">
+        <v>4247</v>
+      </c>
+      <c r="K1482">
+        <v>1483</v>
+      </c>
+      <c r="M1482" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1482" t="s">
+        <v>4262</v>
+      </c>
+    </row>
+    <row r="1483" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1483">
+        <v>77</v>
+      </c>
+      <c r="B1483" s="7">
+        <v>10099082</v>
+      </c>
+      <c r="C1483" t="s">
+        <v>4190</v>
+      </c>
+      <c r="D1483" t="s">
+        <v>333</v>
+      </c>
+      <c r="E1483" t="s">
+        <v>4191</v>
+      </c>
+      <c r="F1483" s="29">
+        <v>46151</v>
+      </c>
+      <c r="G1483" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1483" s="164" t="s">
+        <v>837</v>
+      </c>
+      <c r="I1483" s="164" t="s">
+        <v>290</v>
+      </c>
+      <c r="J1483" s="63" t="s">
+        <v>4260</v>
+      </c>
+      <c r="K1483">
+        <v>1484</v>
+      </c>
+      <c r="M1483" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1483" t="s">
+        <v>4263</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1484">
+        <v>77</v>
+      </c>
+      <c r="B1484" s="7">
+        <v>4039390</v>
+      </c>
+      <c r="C1484" t="s">
+        <v>4264</v>
+      </c>
+      <c r="D1484" t="s">
+        <v>4265</v>
+      </c>
+      <c r="E1484" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1484" s="29">
+        <v>46151</v>
+      </c>
+      <c r="G1484" s="56">
+        <v>4.0844907407407406E-2</v>
+      </c>
+      <c r="H1484" s="164" t="s">
+        <v>885</v>
+      </c>
+      <c r="I1484" s="164" t="s">
+        <v>290</v>
+      </c>
+      <c r="J1484" s="63" t="s">
+        <v>4266</v>
+      </c>
+      <c r="K1484">
+        <v>1485</v>
+      </c>
+      <c r="M1484" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1484" t="s">
+        <v>4270</v>
+      </c>
+    </row>
+    <row r="1485" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1485">
+        <v>77</v>
+      </c>
+      <c r="B1485" s="7">
+        <v>13739338</v>
+      </c>
+      <c r="C1485" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1485" t="s">
+        <v>456</v>
+      </c>
+      <c r="E1485" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1485" s="29">
+        <v>46151</v>
+      </c>
+      <c r="G1485" s="56">
+        <v>0.10276620370370371</v>
+      </c>
+      <c r="H1485" s="164" t="s">
+        <v>1106</v>
+      </c>
+      <c r="I1485" s="164" t="s">
+        <v>290</v>
+      </c>
+      <c r="J1485" s="63" t="s">
+        <v>4267</v>
+      </c>
+      <c r="K1485">
+        <v>1486</v>
+      </c>
+      <c r="M1485" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1485" t="s">
+        <v>4271</v>
+      </c>
+    </row>
+    <row r="1486" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1486">
+        <v>77</v>
+      </c>
+      <c r="B1486" s="7">
+        <v>15608673</v>
+      </c>
+      <c r="C1486" t="s">
+        <v>4264</v>
+      </c>
+      <c r="D1486" t="s">
+        <v>4269</v>
+      </c>
+      <c r="E1486" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1486" s="29">
+        <v>46151</v>
+      </c>
+      <c r="G1486" s="56">
+        <v>0.15770833333333334</v>
+      </c>
+      <c r="H1486" s="164" t="s">
+        <v>885</v>
+      </c>
+      <c r="I1486" s="164" t="s">
+        <v>290</v>
+      </c>
+      <c r="J1486" s="63" t="s">
+        <v>4268</v>
+      </c>
+      <c r="K1486">
+        <v>1487</v>
+      </c>
+      <c r="M1486" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1486" t="s">
+        <v>4272</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N1">
     <sortState ref="A2:N1443">

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12310" uniqueCount="4273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12375" uniqueCount="4292">
   <si>
     <t>Ņ</t>
   </si>
@@ -12846,6 +12846,63 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1502715223184773394/id_XP.png?ex=6a00b81c&amp;is=69ff669c&amp;hm=ec145eaaefb5d8a64bd389d86c0e44e0033d11fc4ffb01c595565418ca05d0c0</t>
+  </si>
+  <si>
+    <t>Artillery</t>
+  </si>
+  <si>
+    <t>XQ</t>
+  </si>
+  <si>
+    <t>XR</t>
+  </si>
+  <si>
+    <t>XS</t>
+  </si>
+  <si>
+    <t>XT</t>
+  </si>
+  <si>
+    <t>XU</t>
+  </si>
+  <si>
+    <t>(un)rd</t>
+  </si>
+  <si>
+    <t>XV</t>
+  </si>
+  <si>
+    <t>XW</t>
+  </si>
+  <si>
+    <t>XX</t>
+  </si>
+  <si>
+    <t>Sprayer</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1503020281852203139/id_XQ.png?ex=6a01d437&amp;is=6a0082b7&amp;hm=6e7f8239697cbfa6b8c11e49cc379390be97bdfb00ffcfa331471282530531aa</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1503020334163693739/id_XR.png?ex=6a01d444&amp;is=6a0082c4&amp;hm=c1e25276286a6bee5140b8a5009dde6ec11158e36e98da20394e6a13ab57be22</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1503020388639047821/id_XS.png?ex=6a01d451&amp;is=6a0082d1&amp;hm=7ee62ee707dd407fbeb9c93ab5c7c0b6e9cbc2dba026c0ead57e4b941b7dc7a8</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1503020440623255647/id_XT.png?ex=6a01d45d&amp;is=6a0082dd&amp;hm=06318053e80534c4181a748cc132473ce568687c111790bacd0f45c9400ee7ce</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1503020499763200090/id_XU.png?ex=6a01d46b&amp;is=6a0082eb&amp;hm=941b9c1c705924c85374617bcf18446f5b5cd6855b9ae58b5a5ccd6b007eacf8</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1503020551168590075/id_XV.png?ex=6a01d478&amp;is=6a0082f8&amp;hm=5343edf3cee3c589938c601a5d61f5bb72b56fdbf1e79747f1e38f2fd3b78501</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1503020598639591547/id_XW.jpg?ex=6a01d483&amp;is=6a008303&amp;hm=baf3fbaa0d5b1e8142253265292087d62184691aa36818c61c06459a06a965f7</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1503020664871845908/id_XX.png?ex=6a01d493&amp;is=6a008313&amp;hm=ba7f1c469e921bade3b77d82df8501bdaa4be410f02a1824cf8115d560097756</t>
   </si>
 </sst>
 </file>
@@ -12857,11 +12914,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="114" x14ac:knownFonts="1">
+  <fonts count="115" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -13688,118 +13752,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="165">
+  <cellXfs count="166">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="111" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="95" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="110" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="94" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="109" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="101" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="95" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="102" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="96" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="92" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="91" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="75" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="75" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="76" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="76" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="78" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="79" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="74" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="73" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="72" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="72" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="71" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="71" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13808,18 +13873,18 @@
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="48" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="49" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13833,15 +13898,15 @@
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14086,7 +14151,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1486"/>
+  <dimension ref="A1:O1494"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -75814,6 +75879,334 @@
         <v>4272</v>
       </c>
     </row>
+    <row r="1487" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1487">
+        <v>78</v>
+      </c>
+      <c r="B1487" s="7">
+        <v>3536598</v>
+      </c>
+      <c r="C1487" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1487" t="s">
+        <v>4273</v>
+      </c>
+      <c r="E1487" t="s">
+        <v>433</v>
+      </c>
+      <c r="F1487" s="29">
+        <v>46152</v>
+      </c>
+      <c r="G1487" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1487" s="165" t="s">
+        <v>1313</v>
+      </c>
+      <c r="I1487" s="165" t="s">
+        <v>290</v>
+      </c>
+      <c r="J1487" s="63" t="s">
+        <v>4274</v>
+      </c>
+      <c r="K1487">
+        <v>1488</v>
+      </c>
+      <c r="M1487" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1487" t="s">
+        <v>4284</v>
+      </c>
+    </row>
+    <row r="1488" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1488">
+        <v>78</v>
+      </c>
+      <c r="B1488" s="7">
+        <v>3328031</v>
+      </c>
+      <c r="C1488" t="s">
+        <v>4035</v>
+      </c>
+      <c r="D1488" t="s">
+        <v>699</v>
+      </c>
+      <c r="E1488" t="s">
+        <v>4035</v>
+      </c>
+      <c r="F1488" s="29">
+        <v>46152</v>
+      </c>
+      <c r="G1488" s="56">
+        <v>3.3692129629629627E-2</v>
+      </c>
+      <c r="H1488" s="165" t="s">
+        <v>1107</v>
+      </c>
+      <c r="I1488" s="165" t="s">
+        <v>290</v>
+      </c>
+      <c r="J1488" s="63" t="s">
+        <v>4275</v>
+      </c>
+      <c r="K1488">
+        <v>1489</v>
+      </c>
+      <c r="M1488" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1488" t="s">
+        <v>4285</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1489">
+        <v>78</v>
+      </c>
+      <c r="B1489" s="7">
+        <v>9948808</v>
+      </c>
+      <c r="C1489" t="s">
+        <v>265</v>
+      </c>
+      <c r="D1489" t="s">
+        <v>172</v>
+      </c>
+      <c r="E1489" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1489" s="29">
+        <v>46152</v>
+      </c>
+      <c r="G1489" s="56">
+        <v>0.1155324074074074</v>
+      </c>
+      <c r="H1489" s="165" t="s">
+        <v>832</v>
+      </c>
+      <c r="I1489" s="165" t="s">
+        <v>290</v>
+      </c>
+      <c r="J1489" s="63" t="s">
+        <v>4276</v>
+      </c>
+      <c r="K1489">
+        <v>1490</v>
+      </c>
+      <c r="M1489" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1489" t="s">
+        <v>4286</v>
+      </c>
+    </row>
+    <row r="1490" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1490">
+        <v>78</v>
+      </c>
+      <c r="B1490" s="7">
+        <v>14599551</v>
+      </c>
+      <c r="C1490" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1490" t="s">
+        <v>590</v>
+      </c>
+      <c r="E1490" t="s">
+        <v>157</v>
+      </c>
+      <c r="F1490" s="29">
+        <v>46152</v>
+      </c>
+      <c r="G1490" s="56">
+        <v>0.16002314814814814</v>
+      </c>
+      <c r="H1490" s="165" t="s">
+        <v>815</v>
+      </c>
+      <c r="I1490" s="165" t="s">
+        <v>290</v>
+      </c>
+      <c r="J1490" s="63" t="s">
+        <v>4277</v>
+      </c>
+      <c r="K1490">
+        <v>1491</v>
+      </c>
+      <c r="M1490" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1490" t="s">
+        <v>4287</v>
+      </c>
+    </row>
+    <row r="1491" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1491">
+        <v>78</v>
+      </c>
+      <c r="B1491" s="7">
+        <v>11177616</v>
+      </c>
+      <c r="C1491" t="s">
+        <v>720</v>
+      </c>
+      <c r="D1491" t="s">
+        <v>703</v>
+      </c>
+      <c r="E1491" t="s">
+        <v>720</v>
+      </c>
+      <c r="F1491" s="29">
+        <v>46152</v>
+      </c>
+      <c r="G1491" s="56">
+        <v>0.10849537037037038</v>
+      </c>
+      <c r="H1491" s="165" t="s">
+        <v>815</v>
+      </c>
+      <c r="I1491" s="165" t="s">
+        <v>290</v>
+      </c>
+      <c r="J1491" s="63" t="s">
+        <v>4278</v>
+      </c>
+      <c r="K1491">
+        <v>1492</v>
+      </c>
+      <c r="M1491" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1491" t="s">
+        <v>4288</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1492">
+        <v>78</v>
+      </c>
+      <c r="B1492" s="7">
+        <v>33109588</v>
+      </c>
+      <c r="C1492" t="s">
+        <v>4279</v>
+      </c>
+      <c r="D1492" t="s">
+        <v>319</v>
+      </c>
+      <c r="E1492" t="s">
+        <v>236</v>
+      </c>
+      <c r="F1492" s="29">
+        <v>46152</v>
+      </c>
+      <c r="G1492" s="56">
+        <v>0.29434027777777777</v>
+      </c>
+      <c r="H1492" s="165" t="s">
+        <v>1107</v>
+      </c>
+      <c r="I1492" s="165" t="s">
+        <v>290</v>
+      </c>
+      <c r="J1492" s="63" t="s">
+        <v>4280</v>
+      </c>
+      <c r="K1492">
+        <v>1493</v>
+      </c>
+      <c r="M1492" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1492" t="s">
+        <v>4289</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1493">
+        <v>78</v>
+      </c>
+      <c r="B1493" s="7">
+        <v>12013785</v>
+      </c>
+      <c r="C1493" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1493" t="s">
+        <v>701</v>
+      </c>
+      <c r="E1493" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1493" s="29">
+        <v>46152</v>
+      </c>
+      <c r="G1493" s="56">
+        <v>8.2199074074074077E-2</v>
+      </c>
+      <c r="H1493" s="165" t="s">
+        <v>2415</v>
+      </c>
+      <c r="I1493" s="165" t="s">
+        <v>290</v>
+      </c>
+      <c r="J1493" s="63" t="s">
+        <v>4281</v>
+      </c>
+      <c r="K1493">
+        <v>1494</v>
+      </c>
+      <c r="M1493" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1493" t="s">
+        <v>4290</v>
+      </c>
+    </row>
+    <row r="1494" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1494">
+        <v>78</v>
+      </c>
+      <c r="B1494" s="7">
+        <v>13003479</v>
+      </c>
+      <c r="C1494" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1494" t="s">
+        <v>4283</v>
+      </c>
+      <c r="E1494" t="s">
+        <v>433</v>
+      </c>
+      <c r="F1494" s="29">
+        <v>46152</v>
+      </c>
+      <c r="G1494" s="56">
+        <v>0.14137731481481483</v>
+      </c>
+      <c r="H1494" s="165" t="s">
+        <v>885</v>
+      </c>
+      <c r="I1494" s="165" t="s">
+        <v>290</v>
+      </c>
+      <c r="J1494" s="63" t="s">
+        <v>4282</v>
+      </c>
+      <c r="K1494">
+        <v>1495</v>
+      </c>
+      <c r="M1494" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1494" t="s">
+        <v>4291</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N1">
     <sortState ref="A2:N1443">

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12375" uniqueCount="4292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12419" uniqueCount="4308">
   <si>
     <t>Ņ</t>
   </si>
@@ -12903,6 +12903,54 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1503020664871845908/id_XX.png?ex=6a01d493&amp;is=6a008313&amp;hm=ba7f1c469e921bade3b77d82df8501bdaa4be410f02a1824cf8115d560097756</t>
+  </si>
+  <si>
+    <t>Internetwork Collapse</t>
+  </si>
+  <si>
+    <t>XY</t>
+  </si>
+  <si>
+    <t>XZ</t>
+  </si>
+  <si>
+    <t>Caster</t>
+  </si>
+  <si>
+    <t>Xa</t>
+  </si>
+  <si>
+    <t>Freyja/Exorcistor/Summoner</t>
+  </si>
+  <si>
+    <t>Xb</t>
+  </si>
+  <si>
+    <t>Xc</t>
+  </si>
+  <si>
+    <t>PLEASE GO SOUTH SANK Aaaaaaaaaaaaaaa</t>
+  </si>
+  <si>
+    <t>was more but I lost the screenshot somehow</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1503807471788097577/id_XY.png?ex=6a04b158&amp;is=6a035fd8&amp;hm=71016db3689f5b9c6a63324624a439535ac668d74b3ddcc3162646a46cfe1998</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1503807569536487494/id_XZ.png?ex=6a04b16f&amp;is=6a035fef&amp;hm=23974af7ef9d7174216105d6ba8285e079fc3bc7647a384d64c9c97475f66875</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1503807642332823602/id_Xa.png?ex=6a04b181&amp;is=6a036001&amp;hm=3f4b793a3398c5f248ce5c5cbcbdd465eee55d9e4df56d6818c68f3068649183</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1503807699211649194/id_Xb.jpg?ex=6a04b18e&amp;is=6a03600e&amp;hm=fa4e9e4f89886ac8b0280ab1f34dcd8819b44904f913018d6a415ca084ad55b4</t>
+  </si>
+  <si>
+    <t>yes it was ziziks</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1503807761035563221/id_Xc.png?ex=6a04b19d&amp;is=6a03601d&amp;hm=df359581780fe4ab6267942c6cec70f87cfd3d2a6c94adb74f2a5a14cff59802</t>
   </si>
 </sst>
 </file>
@@ -12914,11 +12962,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="115" x14ac:knownFonts="1">
+  <fonts count="116" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -13752,118 +13807,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="166">
+  <cellXfs count="167">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="112" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="96" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="111" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="95" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="110" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="102" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="96" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="103" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="97" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="93" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="92" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="76" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="76" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="77" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="77" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="79" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="80" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="75" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="74" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="73" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="73" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="72" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="72" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13872,18 +13928,18 @@
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="49" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="50" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13897,15 +13953,15 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14151,7 +14207,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1494"/>
+  <dimension ref="A1:O1499"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -76118,6 +76174,9 @@
       <c r="K1492">
         <v>1493</v>
       </c>
+      <c r="L1492" t="s">
+        <v>4300</v>
+      </c>
       <c r="M1492" s="57" t="s">
         <v>854</v>
       </c>
@@ -76205,6 +76264,217 @@
       </c>
       <c r="N1494" t="s">
         <v>4291</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1495">
+        <v>79</v>
+      </c>
+      <c r="B1495" s="7">
+        <v>14100000</v>
+      </c>
+      <c r="C1495" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1495" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1495" t="s">
+        <v>695</v>
+      </c>
+      <c r="F1495" s="29">
+        <v>46154</v>
+      </c>
+      <c r="G1495" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1495" s="166" t="s">
+        <v>4292</v>
+      </c>
+      <c r="I1495" s="166" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1495" s="63" t="s">
+        <v>4293</v>
+      </c>
+      <c r="K1495">
+        <v>1496</v>
+      </c>
+      <c r="L1495" t="s">
+        <v>4301</v>
+      </c>
+      <c r="M1495" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1495" t="s">
+        <v>4302</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1496">
+        <v>79</v>
+      </c>
+      <c r="B1496" s="7">
+        <v>5621462</v>
+      </c>
+      <c r="C1496" t="s">
+        <v>2452</v>
+      </c>
+      <c r="D1496" t="s">
+        <v>4295</v>
+      </c>
+      <c r="E1496" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1496" s="29">
+        <v>46154</v>
+      </c>
+      <c r="G1496" s="56">
+        <v>6.6805555555555562E-2</v>
+      </c>
+      <c r="H1496" s="166" t="s">
+        <v>1522</v>
+      </c>
+      <c r="I1496" s="166" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1496" s="63" t="s">
+        <v>4294</v>
+      </c>
+      <c r="K1496">
+        <v>1497</v>
+      </c>
+      <c r="M1496" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1496" t="s">
+        <v>4303</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1497">
+        <v>79</v>
+      </c>
+      <c r="B1497" s="7">
+        <v>14803590</v>
+      </c>
+      <c r="C1497" t="s">
+        <v>4190</v>
+      </c>
+      <c r="D1497" t="s">
+        <v>424</v>
+      </c>
+      <c r="E1497" t="s">
+        <v>4191</v>
+      </c>
+      <c r="F1497" s="29">
+        <v>46154</v>
+      </c>
+      <c r="G1497" s="56">
+        <v>9.9641203703703704E-2</v>
+      </c>
+      <c r="H1497" s="166" t="s">
+        <v>1239</v>
+      </c>
+      <c r="I1497" s="166" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1497" s="63" t="s">
+        <v>4296</v>
+      </c>
+      <c r="K1497">
+        <v>1498</v>
+      </c>
+      <c r="M1497" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1497" t="s">
+        <v>4304</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1498">
+        <v>79</v>
+      </c>
+      <c r="B1498" s="7">
+        <v>12048587</v>
+      </c>
+      <c r="C1498" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1498" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1498" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1498" s="29">
+        <v>46154</v>
+      </c>
+      <c r="G1498" s="56">
+        <v>7.8333333333333324E-2</v>
+      </c>
+      <c r="H1498" s="166" t="s">
+        <v>4297</v>
+      </c>
+      <c r="I1498" s="166" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1498" s="63" t="s">
+        <v>4298</v>
+      </c>
+      <c r="K1498">
+        <v>1499</v>
+      </c>
+      <c r="M1498" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1498" t="s">
+        <v>4305</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1499">
+        <v>79</v>
+      </c>
+      <c r="B1499" s="7">
+        <v>12429388</v>
+      </c>
+      <c r="C1499" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1499" t="s">
+        <v>96</v>
+      </c>
+      <c r="E1499" t="s">
+        <v>157</v>
+      </c>
+      <c r="F1499" s="29">
+        <v>46154</v>
+      </c>
+      <c r="G1499" s="56">
+        <v>7.615740740740741E-2</v>
+      </c>
+      <c r="H1499" s="166" t="s">
+        <v>830</v>
+      </c>
+      <c r="I1499" s="166" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1499" s="63" t="s">
+        <v>4299</v>
+      </c>
+      <c r="K1499">
+        <v>1500</v>
+      </c>
+      <c r="L1499" t="s">
+        <v>4306</v>
+      </c>
+      <c r="M1499" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1499" t="s">
+        <v>4307</v>
       </c>
     </row>
   </sheetData>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12419" uniqueCount="4308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12445" uniqueCount="4314">
   <si>
     <t>Ņ</t>
   </si>
@@ -12951,6 +12951,24 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1503807761035563221/id_Xc.png?ex=6a04b19d&amp;is=6a03601d&amp;hm=df359581780fe4ab6267942c6cec70f87cfd3d2a6c94adb74f2a5a14cff59802</t>
+  </si>
+  <si>
+    <t>Xd</t>
+  </si>
+  <si>
+    <t>Xe</t>
+  </si>
+  <si>
+    <t>Xf</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1504526343059017909/id_Xd.jpg?ex=6a074ed8&amp;is=6a05fd58&amp;hm=6f7d3266455a07b7d8035da38d9f35f99bdc9879e6d015945deb0feb10b22788</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1504526411543875634/id_Xe.png?ex=6a074ee9&amp;is=6a05fd69&amp;hm=d1ff4eef9743ef931a1607d50d6b52d8c3469057f6b1ce681bf65f2d124c24cc</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1504526495928946728/id_Xf.png?ex=6a074efd&amp;is=6a05fd7d&amp;hm=169743fcc226b49610446fda2a36ff90f571adff9da415a3086a2aec2f097e60</t>
   </si>
 </sst>
 </file>
@@ -12962,11 +12980,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="116" x14ac:knownFonts="1">
+  <fonts count="117" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -13807,118 +13832,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="167">
+  <cellXfs count="168">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="113" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="97" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="112" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="96" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="111" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="103" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="97" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="104" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="98" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="94" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="93" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="81" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="81" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="81" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="81" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="77" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="77" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="80" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="81" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="76" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="75" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="74" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="74" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="73" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="73" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13927,18 +13953,18 @@
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="57" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="57" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="50" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="51" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -13952,15 +13978,15 @@
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14207,7 +14233,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1499"/>
+  <dimension ref="A1:O1504"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -76477,6 +76503,139 @@
         <v>4307</v>
       </c>
     </row>
+    <row r="1500" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1500">
+        <v>80</v>
+      </c>
+      <c r="B1500" s="7">
+        <v>12522594</v>
+      </c>
+      <c r="C1500" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1500" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1500" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1500" s="29">
+        <v>46156</v>
+      </c>
+      <c r="G1500" s="56">
+        <v>5.5740740740740737E-2</v>
+      </c>
+      <c r="H1500" s="167" t="s">
+        <v>885</v>
+      </c>
+      <c r="I1500" s="167" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1500" s="63" t="s">
+        <v>4308</v>
+      </c>
+      <c r="K1500">
+        <v>1501</v>
+      </c>
+      <c r="M1500" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1500" t="s">
+        <v>4311</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1501">
+        <v>80</v>
+      </c>
+      <c r="B1501" s="7">
+        <v>20214841</v>
+      </c>
+      <c r="C1501" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1501" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1501" t="s">
+        <v>695</v>
+      </c>
+      <c r="F1501" s="29">
+        <v>46156</v>
+      </c>
+      <c r="G1501" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1501" s="167" t="s">
+        <v>1313</v>
+      </c>
+      <c r="I1501" s="167" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1501" s="63" t="s">
+        <v>4309</v>
+      </c>
+      <c r="K1501">
+        <v>1502</v>
+      </c>
+      <c r="M1501" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1501" t="s">
+        <v>4312</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1502">
+        <v>80</v>
+      </c>
+      <c r="B1502" s="7">
+        <v>7267509</v>
+      </c>
+      <c r="C1502" t="s">
+        <v>3709</v>
+      </c>
+      <c r="D1502" t="s">
+        <v>393</v>
+      </c>
+      <c r="E1502" t="s">
+        <v>236</v>
+      </c>
+      <c r="F1502" s="29">
+        <v>46156</v>
+      </c>
+      <c r="G1502" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1502" s="167" t="s">
+        <v>1313</v>
+      </c>
+      <c r="I1502" s="167" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1502" s="63" t="s">
+        <v>4310</v>
+      </c>
+      <c r="K1502">
+        <v>1503</v>
+      </c>
+      <c r="M1502" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1502" t="s">
+        <v>4313</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1503">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1504">
+        <v>80</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N1">
     <sortState ref="A2:N1443">

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12445" uniqueCount="4314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12497" uniqueCount="4332">
   <si>
     <t>Ņ</t>
   </si>
@@ -12206,9 +12206,6 @@
     <t>FS⬆️</t>
   </si>
   <si>
-    <t>https://cdn.discordapp.com/attachments/1471844339931021342/1494590697292959846/id_TV.jpg?ex=69e3298e&amp;is=69e1d80e&amp;hm=37430cf5f0ca3c820fb1a7b4d27572ece8117d6c6702abc1e639beda41071bf9</t>
-  </si>
-  <si>
     <t>WC</t>
   </si>
   <si>
@@ -12218,9 +12215,6 @@
     <t>WD</t>
   </si>
   <si>
-    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1494593655049289810/id_WB.jpg?ex=69e32c4f&amp;is=69e1dacf&amp;hm=345c058011c4ce06ad76ee8dc1f6c9e87e3702e9494762054b4de7ace4289d33</t>
-  </si>
-  <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1494593703958941786/id_WC.png?ex=69e32c5b&amp;is=69e1dadb&amp;hm=af2e0973c664c7b4fe6a3018aee898209a1bf3c1164888462b148d55b52fb911</t>
   </si>
   <si>
@@ -12969,6 +12963,66 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1504526495928946728/id_Xf.png?ex=6a074efd&amp;is=6a05fd7d&amp;hm=169743fcc226b49610446fda2a36ff90f571adff9da415a3086a2aec2f097e60</t>
+  </si>
+  <si>
+    <t>Theia/Lag</t>
+  </si>
+  <si>
+    <t>Xg</t>
+  </si>
+  <si>
+    <t>Xh</t>
+  </si>
+  <si>
+    <t>Elite Crasher/Paladin/Sorcerer</t>
+  </si>
+  <si>
+    <t>Xi</t>
+  </si>
+  <si>
+    <t>Xj</t>
+  </si>
+  <si>
+    <t>Xk</t>
+  </si>
+  <si>
+    <t>or 16th</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lag i pressume </t>
+  </si>
+  <si>
+    <t>Nyx/Freyja</t>
+  </si>
+  <si>
+    <t>Xl</t>
+  </si>
+  <si>
+    <t>[o]</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1505541001261879468/id_Xg.png?ex=6a0affd2&amp;is=6a09ae52&amp;hm=2ceb2cfbf799ee9af638dc4473c40df6684e495363067c7902399b8119a71ce2</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1505541047412064306/id_Xh.png?ex=6a0affdd&amp;is=6a09ae5d&amp;hm=5331f5276ec2e163a210bf12e8f673f6c14a4e18d913f7270697024666484808</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1505541099912171783/id_Xi.png?ex=6a0affe9&amp;is=6a09ae69&amp;hm=ebec1658203d7c27be4ce37097f94964f6d61ddfcca94bf419e63b01a13bd3e6</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1505541152294699150/id_Xj.png?ex=6a0afff6&amp;is=6a09ae76&amp;hm=f897c984cbeafd6ddd3828cdf4fa8dc4e0216c0c233df6fd1b0e050aaf17fab8</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1505541200982052966/id_Xk.jpg?ex=6a0b0001&amp;is=6a09ae81&amp;hm=f309a0cdd6459451e26b7dc35fba2ca6bd2f75575ec2eed4118b3f7dd435c043</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1505541247899537408/id_Xl.png?ex=6a0b000d&amp;is=6a09ae8d&amp;hm=80c67d17bb9eb1857b007200ccc6071d62d2d51bd02d424a8f5de4cb01d1367d</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1471844339931021342/1505541757750743170/id_WB.png?ex=6a0b0086&amp;is=6a09af06&amp;hm=2f22ad5e8fc3107289a2b3f0c86b9c086760474ee6ab0fda0d091ae240a25666</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1471844339931021342/1505542228599111770/id_TU.png?ex=6a0b00f6&amp;is=6a09af76&amp;hm=b0074b701036d4ee99b045aae269549aee54e1dbf61e1bb6ab7d772d4f9aa545</t>
   </si>
 </sst>
 </file>
@@ -13982,10 +14036,10 @@
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14233,7 +14287,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1504"/>
+  <dimension ref="A1:O1509"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -17663,8 +17717,8 @@
       <c r="D80" s="12" t="s">
         <v>424</v>
       </c>
-      <c r="E80" s="123" t="s">
-        <v>720</v>
+      <c r="E80" t="s">
+        <v>1583</v>
       </c>
       <c r="F80" s="29">
         <v>45647</v>
@@ -17687,8 +17741,8 @@
       <c r="M80" s="57" t="s">
         <v>854</v>
       </c>
-      <c r="N80" s="159" t="s">
-        <v>4134</v>
+      <c r="N80" s="158" t="s">
+        <v>4132</v>
       </c>
       <c r="O80" s="1"/>
     </row>
@@ -18605,13 +18659,13 @@
         <v>28770000</v>
       </c>
       <c r="C102" t="s">
-        <v>4124</v>
+        <v>4122</v>
       </c>
       <c r="D102" t="s">
         <v>424</v>
       </c>
       <c r="E102" t="s">
-        <v>4124</v>
+        <v>4122</v>
       </c>
       <c r="F102" s="29">
         <v>45767</v>
@@ -22554,7 +22608,7 @@
         <v>424</v>
       </c>
       <c r="E194" t="s">
-        <v>720</v>
+        <v>1583</v>
       </c>
       <c r="F194" s="29">
         <v>45648</v>
@@ -23847,7 +23901,7 @@
       <c r="H224" t="s">
         <v>815</v>
       </c>
-      <c r="I224" s="131" t="s">
+      <c r="I224" s="130" t="s">
         <v>813</v>
       </c>
       <c r="J224" s="63" t="s">
@@ -25650,13 +25704,13 @@
         <v>20000000</v>
       </c>
       <c r="C267" t="s">
-        <v>4117</v>
+        <v>4115</v>
       </c>
       <c r="D267" s="12" t="s">
         <v>424</v>
       </c>
       <c r="E267" t="s">
-        <v>720</v>
+        <v>1583</v>
       </c>
       <c r="F267" s="29">
         <v>45568</v>
@@ -25793,7 +25847,7 @@
       <c r="H270" t="s">
         <v>1422</v>
       </c>
-      <c r="I270" s="131" t="s">
+      <c r="I270" s="130" t="s">
         <v>813</v>
       </c>
       <c r="J270" s="63" t="s">
@@ -27227,7 +27281,7 @@
       <c r="B305" s="7">
         <v>18377129</v>
       </c>
-      <c r="C305" s="132" t="s">
+      <c r="C305" s="131" t="s">
         <v>440</v>
       </c>
       <c r="D305" s="16" t="s">
@@ -28815,7 +28869,7 @@
         <v>424</v>
       </c>
       <c r="E343" t="s">
-        <v>720</v>
+        <v>1583</v>
       </c>
       <c r="F343" s="29">
         <v>45792</v>
@@ -29232,7 +29286,7 @@
         <v>15</v>
       </c>
       <c r="E353" t="s">
-        <v>4158</v>
+        <v>4156</v>
       </c>
       <c r="F353" s="29">
         <v>45647</v>
@@ -32519,7 +32573,7 @@
       <c r="H432" t="s">
         <v>835</v>
       </c>
-      <c r="I432" s="153" t="s">
+      <c r="I432" s="152" t="s">
         <v>806</v>
       </c>
       <c r="J432" s="63" t="s">
@@ -35713,7 +35767,7 @@
       <c r="H509" t="s">
         <v>830</v>
       </c>
-      <c r="I509" s="153" t="s">
+      <c r="I509" s="152" t="s">
         <v>806</v>
       </c>
       <c r="J509" s="63" t="s">
@@ -36405,7 +36459,7 @@
         <v>223</v>
       </c>
       <c r="E526" t="s">
-        <v>720</v>
+        <v>1583</v>
       </c>
       <c r="F526" s="29">
         <v>45850</v>
@@ -36978,7 +37032,7 @@
       <c r="C540">
         <v>9</v>
       </c>
-      <c r="D540" s="142" t="s">
+      <c r="D540" s="141" t="s">
         <v>3918</v>
       </c>
       <c r="E540" t="s">
@@ -49137,7 +49191,7 @@
         <v>259</v>
       </c>
       <c r="E834" t="s">
-        <v>4158</v>
+        <v>4156</v>
       </c>
       <c r="F834" s="29">
         <v>46016</v>
@@ -58288,7 +58342,7 @@
       <c r="D1056" s="37" t="s">
         <v>679</v>
       </c>
-      <c r="E1056" s="131" t="s">
+      <c r="E1056" s="130" t="s">
         <v>3674</v>
       </c>
       <c r="F1056" s="29">
@@ -60760,8 +60814,8 @@
       <c r="G1116" s="56">
         <v>0.55555555555555558</v>
       </c>
-      <c r="H1116" s="159" t="s">
-        <v>4100</v>
+      <c r="H1116" s="158" t="s">
+        <v>4098</v>
       </c>
       <c r="I1116" s="101" t="s">
         <v>806</v>
@@ -61319,7 +61373,7 @@
       <c r="B1130" s="7">
         <v>3683365</v>
       </c>
-      <c r="C1130" s="139" t="s">
+      <c r="C1130" s="138" t="s">
         <v>3875</v>
       </c>
       <c r="D1130" s="103" t="s">
@@ -61360,7 +61414,7 @@
       <c r="B1131" s="7">
         <v>16246656</v>
       </c>
-      <c r="C1131" s="139" t="s">
+      <c r="C1131" s="138" t="s">
         <v>3875</v>
       </c>
       <c r="D1131" s="103" t="s">
@@ -61401,7 +61455,7 @@
       <c r="B1132" s="7">
         <v>7945684</v>
       </c>
-      <c r="C1132" s="139" t="s">
+      <c r="C1132" s="138" t="s">
         <v>3875</v>
       </c>
       <c r="D1132" s="103" t="s">
@@ -61934,7 +61988,7 @@
       <c r="B1145" s="7">
         <v>31682775</v>
       </c>
-      <c r="C1145" s="139" t="s">
+      <c r="C1145" s="138" t="s">
         <v>3875</v>
       </c>
       <c r="D1145" s="105" t="s">
@@ -62221,7 +62275,7 @@
       <c r="B1152" s="7">
         <v>39229228</v>
       </c>
-      <c r="C1152" s="139" t="s">
+      <c r="C1152" s="138" t="s">
         <v>3875</v>
       </c>
       <c r="D1152" s="109" t="s">
@@ -62962,7 +63016,7 @@
       <c r="C1170" s="121" t="s">
         <v>25</v>
       </c>
-      <c r="D1170" s="140" t="s">
+      <c r="D1170" s="139" t="s">
         <v>283</v>
       </c>
       <c r="E1170" t="s">
@@ -63416,8 +63470,8 @@
       <c r="D1181" s="123" t="s">
         <v>703</v>
       </c>
-      <c r="E1181" s="130" t="s">
-        <v>720</v>
+      <c r="E1181" t="s">
+        <v>1583</v>
       </c>
       <c r="F1181" s="29">
         <v>46081</v>
@@ -63425,8 +63479,8 @@
       <c r="G1181" s="56">
         <v>0.10390046296296296</v>
       </c>
-      <c r="H1181" s="162" t="s">
-        <v>4201</v>
+      <c r="H1181" s="161" t="s">
+        <v>4199</v>
       </c>
       <c r="I1181" s="123" t="s">
         <v>806</v>
@@ -63444,7 +63498,7 @@
         <v>854</v>
       </c>
       <c r="N1181" t="s">
-        <v>4202</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="1182" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -65634,7 +65688,7 @@
         <v>424</v>
       </c>
       <c r="E1235" t="s">
-        <v>720</v>
+        <v>1583</v>
       </c>
       <c r="F1235" s="29">
         <v>46089</v>
@@ -65658,7 +65712,7 @@
         <v>854</v>
       </c>
       <c r="N1235" t="s">
-        <v>4059</v>
+        <v>4331</v>
       </c>
     </row>
     <row r="1236" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -69648,10 +69702,10 @@
       <c r="C1333" t="s">
         <v>3824</v>
       </c>
-      <c r="D1333" s="133" t="s">
+      <c r="D1333" s="132" t="s">
         <v>1994</v>
       </c>
-      <c r="E1333" s="137" t="s">
+      <c r="E1333" s="136" t="s">
         <v>3848</v>
       </c>
       <c r="F1333" s="29">
@@ -69660,13 +69714,13 @@
       <c r="G1333" s="56">
         <v>0.13412037037037036</v>
       </c>
-      <c r="H1333" s="133" t="s">
+      <c r="H1333" s="132" t="s">
         <v>805</v>
       </c>
-      <c r="I1333" s="133" t="s">
-        <v>806</v>
-      </c>
-      <c r="J1333" s="134" t="s">
+      <c r="I1333" s="132" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1333" s="133" t="s">
         <v>3825</v>
       </c>
       <c r="K1333">
@@ -69689,10 +69743,10 @@
       <c r="C1334" t="s">
         <v>17</v>
       </c>
-      <c r="D1334" s="135" t="s">
+      <c r="D1334" s="134" t="s">
         <v>3827</v>
       </c>
-      <c r="E1334" s="135" t="s">
+      <c r="E1334" s="134" t="s">
         <v>18</v>
       </c>
       <c r="F1334" s="29">
@@ -69701,13 +69755,13 @@
       <c r="G1334" s="56">
         <v>4.0648148148148149E-2</v>
       </c>
-      <c r="H1334" s="135" t="s">
+      <c r="H1334" s="134" t="s">
         <v>1321</v>
       </c>
-      <c r="I1334" s="135" t="s">
-        <v>806</v>
-      </c>
-      <c r="J1334" s="136" t="s">
+      <c r="I1334" s="134" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1334" s="135" t="s">
         <v>3826</v>
       </c>
       <c r="K1334">
@@ -69730,7 +69784,7 @@
       <c r="C1335" t="s">
         <v>3852</v>
       </c>
-      <c r="D1335" s="137" t="s">
+      <c r="D1335" s="136" t="s">
         <v>15</v>
       </c>
       <c r="E1335" t="s">
@@ -69742,10 +69796,10 @@
       <c r="G1335" s="56">
         <v>8.4050925925925932E-2</v>
       </c>
-      <c r="H1335" s="137" t="s">
+      <c r="H1335" s="136" t="s">
         <v>3851</v>
       </c>
-      <c r="I1335" s="137" t="s">
+      <c r="I1335" s="136" t="s">
         <v>806</v>
       </c>
       <c r="J1335" s="63" t="s">
@@ -69774,7 +69828,7 @@
       <c r="C1336" t="s">
         <v>3854</v>
       </c>
-      <c r="D1336" s="138" t="s">
+      <c r="D1336" s="137" t="s">
         <v>3855</v>
       </c>
       <c r="E1336" t="s">
@@ -69786,10 +69840,10 @@
       <c r="G1336" s="56">
         <v>0.11712962962962963</v>
       </c>
-      <c r="H1336" s="138" t="s">
+      <c r="H1336" s="137" t="s">
         <v>815</v>
       </c>
-      <c r="I1336" s="138" t="s">
+      <c r="I1336" s="137" t="s">
         <v>806</v>
       </c>
       <c r="J1336" s="63" t="s">
@@ -69815,7 +69869,7 @@
       <c r="C1337" t="s">
         <v>25</v>
       </c>
-      <c r="D1337" s="138" t="s">
+      <c r="D1337" s="137" t="s">
         <v>3857</v>
       </c>
       <c r="E1337" t="s">
@@ -69827,10 +69881,10 @@
       <c r="G1337" s="56">
         <v>0.12475694444444445</v>
       </c>
-      <c r="H1337" s="138" t="s">
+      <c r="H1337" s="137" t="s">
         <v>2457</v>
       </c>
-      <c r="I1337" s="138" t="s">
+      <c r="I1337" s="137" t="s">
         <v>806</v>
       </c>
       <c r="J1337" s="63" t="s">
@@ -69856,7 +69910,7 @@
       <c r="C1338" t="s">
         <v>3860</v>
       </c>
-      <c r="D1338" s="138" t="s">
+      <c r="D1338" s="137" t="s">
         <v>424</v>
       </c>
       <c r="E1338" t="s">
@@ -69868,10 +69922,10 @@
       <c r="G1338" s="56">
         <v>0.1675925925925926</v>
       </c>
-      <c r="H1338" s="138" t="s">
+      <c r="H1338" s="137" t="s">
         <v>835</v>
       </c>
-      <c r="I1338" s="138" t="s">
+      <c r="I1338" s="137" t="s">
         <v>806</v>
       </c>
       <c r="J1338" s="63" t="s">
@@ -69897,7 +69951,7 @@
       <c r="C1339" t="s">
         <v>25</v>
       </c>
-      <c r="D1339" s="138" t="s">
+      <c r="D1339" s="137" t="s">
         <v>128</v>
       </c>
       <c r="E1339" t="s">
@@ -69909,10 +69963,10 @@
       <c r="G1339" s="56">
         <v>2.8784722222222225E-2</v>
       </c>
-      <c r="H1339" s="138" t="s">
+      <c r="H1339" s="137" t="s">
         <v>835</v>
       </c>
-      <c r="I1339" s="138" t="s">
+      <c r="I1339" s="137" t="s">
         <v>806</v>
       </c>
       <c r="J1339" s="63" t="s">
@@ -69938,7 +69992,7 @@
       <c r="C1340" t="s">
         <v>25</v>
       </c>
-      <c r="D1340" s="138" t="s">
+      <c r="D1340" s="137" t="s">
         <v>3862</v>
       </c>
       <c r="E1340" t="s">
@@ -69950,10 +70004,10 @@
       <c r="G1340" s="56">
         <v>5.4652777777777772E-2</v>
       </c>
-      <c r="H1340" s="138" t="s">
+      <c r="H1340" s="137" t="s">
         <v>825</v>
       </c>
-      <c r="I1340" s="138" t="s">
+      <c r="I1340" s="137" t="s">
         <v>806</v>
       </c>
       <c r="J1340" s="63" t="s">
@@ -69979,7 +70033,7 @@
       <c r="C1341" t="s">
         <v>654</v>
       </c>
-      <c r="D1341" s="138" t="s">
+      <c r="D1341" s="137" t="s">
         <v>540</v>
       </c>
       <c r="E1341" t="s">
@@ -69991,10 +70045,10 @@
       <c r="G1341" s="56">
         <v>6.385416666666667E-2</v>
       </c>
-      <c r="H1341" s="138" t="s">
+      <c r="H1341" s="137" t="s">
         <v>805</v>
       </c>
-      <c r="I1341" s="138" t="s">
+      <c r="I1341" s="137" t="s">
         <v>806</v>
       </c>
       <c r="J1341" s="63" t="s">
@@ -70020,7 +70074,7 @@
       <c r="C1342" t="s">
         <v>654</v>
       </c>
-      <c r="D1342" s="138" t="s">
+      <c r="D1342" s="137" t="s">
         <v>338</v>
       </c>
       <c r="E1342" t="s">
@@ -70032,10 +70086,10 @@
       <c r="G1342" s="56">
         <v>0.11258101851851852</v>
       </c>
-      <c r="H1342" s="138" t="s">
+      <c r="H1342" s="137" t="s">
         <v>938</v>
       </c>
-      <c r="I1342" s="138" t="s">
+      <c r="I1342" s="137" t="s">
         <v>806</v>
       </c>
       <c r="J1342" s="63" t="s">
@@ -70061,7 +70115,7 @@
       <c r="C1343" t="s">
         <v>8</v>
       </c>
-      <c r="D1343" s="138" t="s">
+      <c r="D1343" s="137" t="s">
         <v>89</v>
       </c>
       <c r="E1343" t="s">
@@ -70073,10 +70127,10 @@
       <c r="G1343" s="56">
         <v>6.9201388888888882E-2</v>
       </c>
-      <c r="H1343" s="138" t="s">
+      <c r="H1343" s="137" t="s">
         <v>1107</v>
       </c>
-      <c r="I1343" s="138" t="s">
+      <c r="I1343" s="137" t="s">
         <v>806</v>
       </c>
       <c r="J1343" s="63" t="s">
@@ -70102,7 +70156,7 @@
       <c r="C1344" t="s">
         <v>236</v>
       </c>
-      <c r="D1344" s="140" t="s">
+      <c r="D1344" s="139" t="s">
         <v>172</v>
       </c>
       <c r="E1344" t="s">
@@ -70114,10 +70168,10 @@
       <c r="G1344" s="56">
         <v>0.17105324074074071</v>
       </c>
-      <c r="H1344" s="140" t="s">
+      <c r="H1344" s="139" t="s">
         <v>1107</v>
       </c>
-      <c r="I1344" s="140" t="s">
+      <c r="I1344" s="139" t="s">
         <v>290</v>
       </c>
       <c r="J1344" s="63" t="s">
@@ -70143,7 +70197,7 @@
       <c r="C1345" t="s">
         <v>236</v>
       </c>
-      <c r="D1345" s="140" t="s">
+      <c r="D1345" s="139" t="s">
         <v>436</v>
       </c>
       <c r="E1345" t="s">
@@ -70155,10 +70209,10 @@
       <c r="G1345" s="56" t="s">
         <v>502</v>
       </c>
-      <c r="H1345" s="140" t="s">
+      <c r="H1345" s="139" t="s">
         <v>885</v>
       </c>
-      <c r="I1345" s="140" t="s">
+      <c r="I1345" s="139" t="s">
         <v>290</v>
       </c>
       <c r="J1345" s="63" t="s">
@@ -70184,7 +70238,7 @@
       <c r="C1346" t="s">
         <v>3879</v>
       </c>
-      <c r="D1346" s="140" t="s">
+      <c r="D1346" s="139" t="s">
         <v>441</v>
       </c>
       <c r="E1346" t="s">
@@ -70196,10 +70250,10 @@
       <c r="G1346" s="56">
         <v>3.9212962962962963E-2</v>
       </c>
-      <c r="H1346" s="140" t="s">
+      <c r="H1346" s="139" t="s">
         <v>1560</v>
       </c>
-      <c r="I1346" s="140" t="s">
+      <c r="I1346" s="139" t="s">
         <v>290</v>
       </c>
       <c r="J1346" s="63" t="s">
@@ -70225,7 +70279,7 @@
       <c r="C1347" t="s">
         <v>3880</v>
       </c>
-      <c r="D1347" s="140" t="s">
+      <c r="D1347" s="139" t="s">
         <v>372</v>
       </c>
       <c r="E1347" t="s">
@@ -70237,10 +70291,10 @@
       <c r="G1347" s="56" t="s">
         <v>502</v>
       </c>
-      <c r="H1347" s="140" t="s">
+      <c r="H1347" s="139" t="s">
         <v>502</v>
       </c>
-      <c r="I1347" s="140" t="s">
+      <c r="I1347" s="139" t="s">
         <v>290</v>
       </c>
       <c r="J1347" s="63" t="s">
@@ -70266,7 +70320,7 @@
       <c r="C1348" t="s">
         <v>17</v>
       </c>
-      <c r="D1348" s="140" t="s">
+      <c r="D1348" s="139" t="s">
         <v>227</v>
       </c>
       <c r="E1348" t="s">
@@ -70278,10 +70332,10 @@
       <c r="G1348" s="56">
         <v>6.986111111111111E-2</v>
       </c>
-      <c r="H1348" s="140" t="s">
+      <c r="H1348" s="139" t="s">
         <v>963</v>
       </c>
-      <c r="I1348" s="140" t="s">
+      <c r="I1348" s="139" t="s">
         <v>806</v>
       </c>
       <c r="J1348" s="63" t="s">
@@ -70307,7 +70361,7 @@
       <c r="C1349" t="s">
         <v>3535</v>
       </c>
-      <c r="D1349" s="140" t="s">
+      <c r="D1349" s="139" t="s">
         <v>60</v>
       </c>
       <c r="E1349" t="s">
@@ -70319,10 +70373,10 @@
       <c r="G1349" s="56">
         <v>7.4930555555555556E-2</v>
       </c>
-      <c r="H1349" s="140" t="s">
+      <c r="H1349" s="139" t="s">
         <v>1239</v>
       </c>
-      <c r="I1349" s="140" t="s">
+      <c r="I1349" s="139" t="s">
         <v>806</v>
       </c>
       <c r="J1349" s="63" t="s">
@@ -70348,7 +70402,7 @@
       <c r="C1350" t="s">
         <v>17</v>
       </c>
-      <c r="D1350" s="140" t="s">
+      <c r="D1350" s="139" t="s">
         <v>3776</v>
       </c>
       <c r="E1350" t="s">
@@ -70360,10 +70414,10 @@
       <c r="G1350" s="56">
         <v>4.0185185185185185E-2</v>
       </c>
-      <c r="H1350" s="140" t="s">
+      <c r="H1350" s="139" t="s">
         <v>1107</v>
       </c>
-      <c r="I1350" s="140" t="s">
+      <c r="I1350" s="139" t="s">
         <v>290</v>
       </c>
       <c r="J1350" s="63" t="s">
@@ -70389,7 +70443,7 @@
       <c r="C1351" t="s">
         <v>17</v>
       </c>
-      <c r="D1351" s="140" t="s">
+      <c r="D1351" s="139" t="s">
         <v>3776</v>
       </c>
       <c r="E1351" t="s">
@@ -70401,10 +70455,10 @@
       <c r="G1351" s="56">
         <v>0.22577546296296294</v>
       </c>
-      <c r="H1351" s="140" t="s">
+      <c r="H1351" s="139" t="s">
         <v>885</v>
       </c>
-      <c r="I1351" s="140" t="s">
+      <c r="I1351" s="139" t="s">
         <v>290</v>
       </c>
       <c r="J1351" s="63" t="s">
@@ -70430,7 +70484,7 @@
       <c r="C1352" t="s">
         <v>3896</v>
       </c>
-      <c r="D1352" s="141" t="s">
+      <c r="D1352" s="140" t="s">
         <v>3900</v>
       </c>
       <c r="E1352" t="s">
@@ -70442,10 +70496,10 @@
       <c r="G1352" s="56" t="s">
         <v>502</v>
       </c>
-      <c r="H1352" s="141" t="s">
+      <c r="H1352" s="140" t="s">
         <v>502</v>
       </c>
-      <c r="I1352" s="141" t="s">
+      <c r="I1352" s="140" t="s">
         <v>290</v>
       </c>
       <c r="J1352" s="63" t="s">
@@ -70471,7 +70525,7 @@
       <c r="C1353" t="s">
         <v>3901</v>
       </c>
-      <c r="D1353" s="141" t="s">
+      <c r="D1353" s="140" t="s">
         <v>646</v>
       </c>
       <c r="E1353" t="s">
@@ -70483,10 +70537,10 @@
       <c r="G1353" s="56">
         <v>4.6365740740740742E-2</v>
       </c>
-      <c r="H1353" s="141" t="s">
+      <c r="H1353" s="140" t="s">
         <v>3902</v>
       </c>
-      <c r="I1353" s="141" t="s">
+      <c r="I1353" s="140" t="s">
         <v>290</v>
       </c>
       <c r="J1353" s="63" t="s">
@@ -70524,10 +70578,10 @@
       <c r="G1354" s="56">
         <v>2.7893518518518515E-2</v>
       </c>
-      <c r="H1354" s="141" t="s">
+      <c r="H1354" s="140" t="s">
         <v>815</v>
       </c>
-      <c r="I1354" s="141" t="s">
+      <c r="I1354" s="140" t="s">
         <v>290</v>
       </c>
       <c r="J1354" s="63" t="s">
@@ -70565,10 +70619,10 @@
       <c r="G1355" s="56">
         <v>3.7256944444444447E-2</v>
       </c>
-      <c r="H1355" s="141" t="s">
+      <c r="H1355" s="140" t="s">
         <v>1387</v>
       </c>
-      <c r="I1355" s="141" t="s">
+      <c r="I1355" s="140" t="s">
         <v>290</v>
       </c>
       <c r="J1355" s="63" t="s">
@@ -70606,10 +70660,10 @@
       <c r="G1356" s="56">
         <v>4.2696759259259261E-2</v>
       </c>
-      <c r="H1356" s="141" t="s">
+      <c r="H1356" s="140" t="s">
         <v>830</v>
       </c>
-      <c r="I1356" s="141" t="s">
+      <c r="I1356" s="140" t="s">
         <v>290</v>
       </c>
       <c r="J1356" s="63" t="s">
@@ -70647,10 +70701,10 @@
       <c r="G1357" s="56">
         <v>0.10803240740740742</v>
       </c>
-      <c r="H1357" s="141" t="s">
+      <c r="H1357" s="140" t="s">
         <v>885</v>
       </c>
-      <c r="I1357" s="141" t="s">
+      <c r="I1357" s="140" t="s">
         <v>290</v>
       </c>
       <c r="J1357" s="63" t="s">
@@ -70688,10 +70742,10 @@
       <c r="G1358" s="56">
         <v>0.12408564814814815</v>
       </c>
-      <c r="H1358" s="143" t="s">
+      <c r="H1358" s="142" t="s">
         <v>1276</v>
       </c>
-      <c r="I1358" s="143" t="s">
+      <c r="I1358" s="142" t="s">
         <v>806</v>
       </c>
       <c r="J1358" s="63" t="s">
@@ -70729,10 +70783,10 @@
       <c r="G1359" s="56">
         <v>7.6006944444444446E-2</v>
       </c>
-      <c r="H1359" s="143" t="s">
+      <c r="H1359" s="142" t="s">
         <v>1321</v>
       </c>
-      <c r="I1359" s="143" t="s">
+      <c r="I1359" s="142" t="s">
         <v>290</v>
       </c>
       <c r="J1359" s="63" t="s">
@@ -70770,10 +70824,10 @@
       <c r="G1360" s="56">
         <v>8.6956018518518516E-2</v>
       </c>
-      <c r="H1360" s="143" t="s">
+      <c r="H1360" s="142" t="s">
         <v>1766</v>
       </c>
-      <c r="I1360" s="143" t="s">
+      <c r="I1360" s="142" t="s">
         <v>806</v>
       </c>
       <c r="J1360" s="63" t="s">
@@ -70811,10 +70865,10 @@
       <c r="G1361" s="56" t="s">
         <v>502</v>
       </c>
-      <c r="H1361" s="143" t="s">
+      <c r="H1361" s="142" t="s">
         <v>1171</v>
       </c>
-      <c r="I1361" s="143" t="s">
+      <c r="I1361" s="142" t="s">
         <v>806</v>
       </c>
       <c r="J1361" s="63" t="s">
@@ -70852,10 +70906,10 @@
       <c r="G1362" s="56">
         <v>9.4328703703703706E-2</v>
       </c>
-      <c r="H1362" s="143" t="s">
+      <c r="H1362" s="142" t="s">
         <v>965</v>
       </c>
-      <c r="I1362" s="143" t="s">
+      <c r="I1362" s="142" t="s">
         <v>806</v>
       </c>
       <c r="J1362" s="63" t="s">
@@ -70893,10 +70947,10 @@
       <c r="G1363" s="56">
         <v>0.14107638888888888</v>
       </c>
-      <c r="H1363" s="143" t="s">
+      <c r="H1363" s="142" t="s">
         <v>3927</v>
       </c>
-      <c r="I1363" s="143" t="s">
+      <c r="I1363" s="142" t="s">
         <v>806</v>
       </c>
       <c r="J1363" s="63" t="s">
@@ -70934,10 +70988,10 @@
       <c r="G1364" s="56">
         <v>0.20168981481481482</v>
       </c>
-      <c r="H1364" s="143" t="s">
+      <c r="H1364" s="142" t="s">
         <v>815</v>
       </c>
-      <c r="I1364" s="143" t="s">
+      <c r="I1364" s="142" t="s">
         <v>290</v>
       </c>
       <c r="J1364" s="63" t="s">
@@ -70975,10 +71029,10 @@
       <c r="G1365" s="56">
         <v>3.3680555555555554E-2</v>
       </c>
-      <c r="H1365" s="143" t="s">
+      <c r="H1365" s="142" t="s">
         <v>1732</v>
       </c>
-      <c r="I1365" s="143" t="s">
+      <c r="I1365" s="142" t="s">
         <v>806</v>
       </c>
       <c r="J1365" s="63" t="s">
@@ -71016,10 +71070,10 @@
       <c r="G1366" s="56">
         <v>4.6307870370370374E-2</v>
       </c>
-      <c r="H1366" s="144" t="s">
+      <c r="H1366" s="143" t="s">
         <v>1106</v>
       </c>
-      <c r="I1366" s="144" t="s">
+      <c r="I1366" s="143" t="s">
         <v>806</v>
       </c>
       <c r="J1366" s="63" t="s">
@@ -71057,10 +71111,10 @@
       <c r="G1367" s="56" t="s">
         <v>502</v>
       </c>
-      <c r="H1367" s="145" t="s">
+      <c r="H1367" s="144" t="s">
         <v>3943</v>
       </c>
-      <c r="I1367" s="145" t="s">
+      <c r="I1367" s="144" t="s">
         <v>806</v>
       </c>
       <c r="J1367" s="63" t="s">
@@ -71098,10 +71152,10 @@
       <c r="G1368" s="56">
         <v>3.1041666666666665E-2</v>
       </c>
-      <c r="H1368" s="145" t="s">
+      <c r="H1368" s="144" t="s">
         <v>837</v>
       </c>
-      <c r="I1368" s="145" t="s">
+      <c r="I1368" s="144" t="s">
         <v>806</v>
       </c>
       <c r="J1368" s="63" t="s">
@@ -71139,10 +71193,10 @@
       <c r="G1369" s="56">
         <v>5.9467592592592593E-2</v>
       </c>
-      <c r="H1369" s="145" t="s">
+      <c r="H1369" s="144" t="s">
         <v>805</v>
       </c>
-      <c r="I1369" s="145" t="s">
+      <c r="I1369" s="144" t="s">
         <v>806</v>
       </c>
       <c r="J1369" s="63" t="s">
@@ -71180,10 +71234,10 @@
       <c r="G1370" s="56">
         <v>0.10738425925925926</v>
       </c>
-      <c r="H1370" s="145" t="s">
+      <c r="H1370" s="144" t="s">
         <v>805</v>
       </c>
-      <c r="I1370" s="145" t="s">
+      <c r="I1370" s="144" t="s">
         <v>806</v>
       </c>
       <c r="J1370" s="63" t="s">
@@ -71221,10 +71275,10 @@
       <c r="G1371" s="56">
         <v>0.20519675925925926</v>
       </c>
-      <c r="H1371" s="146" t="s">
+      <c r="H1371" s="145" t="s">
         <v>835</v>
       </c>
-      <c r="I1371" s="146" t="s">
+      <c r="I1371" s="145" t="s">
         <v>806</v>
       </c>
       <c r="J1371" s="63" t="s">
@@ -71262,10 +71316,10 @@
       <c r="G1372" s="56" t="s">
         <v>502</v>
       </c>
-      <c r="H1372" s="146" t="s">
+      <c r="H1372" s="145" t="s">
         <v>3955</v>
       </c>
-      <c r="I1372" s="146" t="s">
+      <c r="I1372" s="145" t="s">
         <v>813</v>
       </c>
       <c r="J1372" s="63" t="s">
@@ -71303,10 +71357,10 @@
       <c r="G1373" s="56">
         <v>5.8692129629629629E-2</v>
       </c>
-      <c r="H1373" s="146" t="s">
+      <c r="H1373" s="145" t="s">
         <v>835</v>
       </c>
-      <c r="I1373" s="146" t="s">
+      <c r="I1373" s="145" t="s">
         <v>290</v>
       </c>
       <c r="J1373" s="63" t="s">
@@ -71344,10 +71398,10 @@
       <c r="G1374" s="56">
         <v>6.2395833333333338E-2</v>
       </c>
-      <c r="H1374" s="146" t="s">
+      <c r="H1374" s="145" t="s">
         <v>1321</v>
       </c>
-      <c r="I1374" s="146" t="s">
+      <c r="I1374" s="145" t="s">
         <v>806</v>
       </c>
       <c r="J1374" s="63" t="s">
@@ -71385,10 +71439,10 @@
       <c r="G1375" s="56">
         <v>7.604166666666666E-2</v>
       </c>
-      <c r="H1375" s="146" t="s">
+      <c r="H1375" s="145" t="s">
         <v>1107</v>
       </c>
-      <c r="I1375" s="146" t="s">
+      <c r="I1375" s="145" t="s">
         <v>806</v>
       </c>
       <c r="J1375" s="63" t="s">
@@ -71426,10 +71480,10 @@
       <c r="G1376" s="56">
         <v>9.2604166666666668E-2</v>
       </c>
-      <c r="H1376" s="146" t="s">
+      <c r="H1376" s="145" t="s">
         <v>3961</v>
       </c>
-      <c r="I1376" s="146" t="s">
+      <c r="I1376" s="145" t="s">
         <v>806</v>
       </c>
       <c r="J1376" s="63" t="s">
@@ -71467,10 +71521,10 @@
       <c r="G1377" s="56">
         <v>0.10716435185185186</v>
       </c>
-      <c r="H1377" s="146" t="s">
+      <c r="H1377" s="145" t="s">
         <v>3963</v>
       </c>
-      <c r="I1377" s="146" t="s">
+      <c r="I1377" s="145" t="s">
         <v>806</v>
       </c>
       <c r="J1377" s="63" t="s">
@@ -71508,10 +71562,10 @@
       <c r="G1378" s="56">
         <v>7.3055555555555554E-2</v>
       </c>
-      <c r="H1378" s="146" t="s">
+      <c r="H1378" s="145" t="s">
         <v>1276</v>
       </c>
-      <c r="I1378" s="146" t="s">
+      <c r="I1378" s="145" t="s">
         <v>806</v>
       </c>
       <c r="J1378" s="63" t="s">
@@ -71549,10 +71603,10 @@
       <c r="G1379" s="56">
         <v>0.15314814814814814</v>
       </c>
-      <c r="H1379" s="146" t="s">
+      <c r="H1379" s="145" t="s">
         <v>815</v>
       </c>
-      <c r="I1379" s="146" t="s">
+      <c r="I1379" s="145" t="s">
         <v>806</v>
       </c>
       <c r="J1379" s="63" t="s">
@@ -71590,10 +71644,10 @@
       <c r="G1380" s="56" t="s">
         <v>502</v>
       </c>
-      <c r="H1380" s="146" t="s">
+      <c r="H1380" s="145" t="s">
         <v>3722</v>
       </c>
-      <c r="I1380" s="146" t="s">
+      <c r="I1380" s="145" t="s">
         <v>806</v>
       </c>
       <c r="J1380" s="63" t="s">
@@ -71631,10 +71685,10 @@
       <c r="G1381" s="56" t="s">
         <v>502</v>
       </c>
-      <c r="H1381" s="146" t="s">
+      <c r="H1381" s="145" t="s">
         <v>840</v>
       </c>
-      <c r="I1381" s="146" t="s">
+      <c r="I1381" s="145" t="s">
         <v>806</v>
       </c>
       <c r="J1381" s="63" t="s">
@@ -71672,10 +71726,10 @@
       <c r="G1382" s="56">
         <v>0.11269675925925926</v>
       </c>
-      <c r="H1382" s="146" t="s">
+      <c r="H1382" s="145" t="s">
         <v>3972</v>
       </c>
-      <c r="I1382" s="146" t="s">
+      <c r="I1382" s="145" t="s">
         <v>806</v>
       </c>
       <c r="J1382" s="63" t="s">
@@ -71713,10 +71767,10 @@
       <c r="G1383" s="56">
         <v>4.7731481481481486E-2</v>
       </c>
-      <c r="H1383" s="146" t="s">
+      <c r="H1383" s="145" t="s">
         <v>3977</v>
       </c>
-      <c r="I1383" s="146" t="s">
+      <c r="I1383" s="145" t="s">
         <v>806</v>
       </c>
       <c r="J1383" s="63" t="s">
@@ -71754,10 +71808,10 @@
       <c r="G1384" s="56" t="s">
         <v>502</v>
       </c>
-      <c r="H1384" s="147" t="s">
+      <c r="H1384" s="146" t="s">
         <v>502</v>
       </c>
-      <c r="I1384" s="147" t="s">
+      <c r="I1384" s="146" t="s">
         <v>806</v>
       </c>
       <c r="J1384" s="63" t="s">
@@ -71795,10 +71849,10 @@
       <c r="G1385" s="56">
         <v>0.11065972222222221</v>
       </c>
-      <c r="H1385" s="147" t="s">
+      <c r="H1385" s="146" t="s">
         <v>3993</v>
       </c>
-      <c r="I1385" s="147" t="s">
+      <c r="I1385" s="146" t="s">
         <v>806</v>
       </c>
       <c r="J1385" s="63" t="s">
@@ -71836,10 +71890,10 @@
       <c r="G1386" s="56">
         <v>0.13692129629629629</v>
       </c>
-      <c r="H1386" s="147" t="s">
+      <c r="H1386" s="146" t="s">
         <v>34</v>
       </c>
-      <c r="I1386" s="147" t="s">
+      <c r="I1386" s="146" t="s">
         <v>806</v>
       </c>
       <c r="J1386" s="63" t="s">
@@ -71877,10 +71931,10 @@
       <c r="G1387" s="56">
         <v>5.7592592592592591E-2</v>
       </c>
-      <c r="H1387" s="147" t="s">
+      <c r="H1387" s="146" t="s">
         <v>1975</v>
       </c>
-      <c r="I1387" s="147" t="s">
+      <c r="I1387" s="146" t="s">
         <v>806</v>
       </c>
       <c r="J1387" s="63" t="s">
@@ -71918,10 +71972,10 @@
       <c r="G1388" s="56">
         <v>6.3472222222222222E-2</v>
       </c>
-      <c r="H1388" s="147" t="s">
+      <c r="H1388" s="146" t="s">
         <v>3998</v>
       </c>
-      <c r="I1388" s="147" t="s">
+      <c r="I1388" s="146" t="s">
         <v>806</v>
       </c>
       <c r="J1388" s="63" t="s">
@@ -71959,10 +72013,10 @@
       <c r="G1389" s="56">
         <v>3.9745370370370368E-2</v>
       </c>
-      <c r="H1389" s="148" t="s">
+      <c r="H1389" s="147" t="s">
         <v>885</v>
       </c>
-      <c r="I1389" s="148" t="s">
+      <c r="I1389" s="147" t="s">
         <v>806</v>
       </c>
       <c r="J1389" s="63" t="s">
@@ -72000,10 +72054,10 @@
       <c r="G1390" s="56" t="s">
         <v>502</v>
       </c>
-      <c r="H1390" s="149" t="s">
+      <c r="H1390" s="148" t="s">
         <v>840</v>
       </c>
-      <c r="I1390" s="148" t="s">
+      <c r="I1390" s="147" t="s">
         <v>806</v>
       </c>
       <c r="J1390" s="63" t="s">
@@ -72041,10 +72095,10 @@
       <c r="G1391" s="56">
         <v>6.9641203703703705E-2</v>
       </c>
-      <c r="H1391" s="149" t="s">
+      <c r="H1391" s="148" t="s">
         <v>4011</v>
       </c>
-      <c r="I1391" s="149" t="s">
+      <c r="I1391" s="148" t="s">
         <v>806</v>
       </c>
       <c r="J1391" s="63" t="s">
@@ -72082,10 +72136,10 @@
       <c r="G1392" s="56" t="s">
         <v>502</v>
       </c>
-      <c r="H1392" s="149" t="s">
+      <c r="H1392" s="148" t="s">
         <v>2031</v>
       </c>
-      <c r="I1392" s="149" t="s">
+      <c r="I1392" s="148" t="s">
         <v>806</v>
       </c>
       <c r="J1392" s="63" t="s">
@@ -72123,10 +72177,10 @@
       <c r="G1393" s="56">
         <v>2.8472222222222222E-2</v>
       </c>
-      <c r="H1393" s="149" t="s">
+      <c r="H1393" s="148" t="s">
         <v>835</v>
       </c>
-      <c r="I1393" s="149" t="s">
+      <c r="I1393" s="148" t="s">
         <v>806</v>
       </c>
       <c r="J1393" s="63" t="s">
@@ -72164,10 +72218,10 @@
       <c r="G1394" s="56" t="s">
         <v>502</v>
       </c>
-      <c r="H1394" s="149" t="s">
+      <c r="H1394" s="148" t="s">
         <v>817</v>
       </c>
-      <c r="I1394" s="149" t="s">
+      <c r="I1394" s="148" t="s">
         <v>806</v>
       </c>
       <c r="J1394" s="63" t="s">
@@ -72205,10 +72259,10 @@
       <c r="G1395" s="56">
         <v>0.1496990740740741</v>
       </c>
-      <c r="H1395" s="150" t="s">
+      <c r="H1395" s="149" t="s">
         <v>1626</v>
       </c>
-      <c r="I1395" s="150" t="s">
+      <c r="I1395" s="149" t="s">
         <v>806</v>
       </c>
       <c r="J1395" s="63" t="s">
@@ -72246,10 +72300,10 @@
       <c r="G1396" s="56">
         <v>4.612268518518519E-2</v>
       </c>
-      <c r="H1396" s="150" t="s">
+      <c r="H1396" s="149" t="s">
         <v>1106</v>
       </c>
-      <c r="I1396" s="150" t="s">
+      <c r="I1396" s="149" t="s">
         <v>813</v>
       </c>
       <c r="J1396" s="63" t="s">
@@ -72287,10 +72341,10 @@
       <c r="G1397" s="56">
         <v>6.8703703703703697E-2</v>
       </c>
-      <c r="H1397" s="150" t="s">
+      <c r="H1397" s="149" t="s">
         <v>837</v>
       </c>
-      <c r="I1397" s="150" t="s">
+      <c r="I1397" s="149" t="s">
         <v>813</v>
       </c>
       <c r="J1397" s="63" t="s">
@@ -72328,10 +72382,10 @@
       <c r="G1398" s="56">
         <v>3.107638888888889E-2</v>
       </c>
-      <c r="H1398" s="150" t="s">
+      <c r="H1398" s="149" t="s">
         <v>965</v>
       </c>
-      <c r="I1398" s="150" t="s">
+      <c r="I1398" s="149" t="s">
         <v>813</v>
       </c>
       <c r="J1398" s="63" t="s">
@@ -72369,10 +72423,10 @@
       <c r="G1399" s="56">
         <v>2.7152777777777779E-2</v>
       </c>
-      <c r="H1399" s="150" t="s">
+      <c r="H1399" s="149" t="s">
         <v>4027</v>
       </c>
-      <c r="I1399" s="150" t="s">
+      <c r="I1399" s="149" t="s">
         <v>813</v>
       </c>
       <c r="J1399" s="63" t="s">
@@ -72410,10 +72464,10 @@
       <c r="G1400" s="56">
         <v>5.2650462962962961E-2</v>
       </c>
-      <c r="H1400" s="150" t="s">
+      <c r="H1400" s="149" t="s">
         <v>817</v>
       </c>
-      <c r="I1400" s="150" t="s">
+      <c r="I1400" s="149" t="s">
         <v>813</v>
       </c>
       <c r="J1400" s="63" t="s">
@@ -72451,10 +72505,10 @@
       <c r="G1401" s="56">
         <v>6.3622685185185185E-2</v>
       </c>
-      <c r="H1401" s="150" t="s">
+      <c r="H1401" s="149" t="s">
         <v>817</v>
       </c>
-      <c r="I1401" s="150" t="s">
+      <c r="I1401" s="149" t="s">
         <v>813</v>
       </c>
       <c r="J1401" s="63" t="s">
@@ -72492,10 +72546,10 @@
       <c r="G1402" s="56">
         <v>4.2222222222222223E-2</v>
       </c>
-      <c r="H1402" s="150" t="s">
+      <c r="H1402" s="149" t="s">
         <v>4035</v>
       </c>
-      <c r="I1402" s="150" t="s">
+      <c r="I1402" s="149" t="s">
         <v>290</v>
       </c>
       <c r="J1402" s="63" t="s">
@@ -72533,10 +72587,10 @@
       <c r="G1403" s="56">
         <v>4.0543981481481479E-2</v>
       </c>
-      <c r="H1403" s="150" t="s">
+      <c r="H1403" s="149" t="s">
         <v>1277</v>
       </c>
-      <c r="I1403" s="150" t="s">
+      <c r="I1403" s="149" t="s">
         <v>813</v>
       </c>
       <c r="J1403" s="63" t="s">
@@ -72574,10 +72628,10 @@
       <c r="G1404" s="56">
         <v>7.2013888888888891E-2</v>
       </c>
-      <c r="H1404" s="150" t="s">
+      <c r="H1404" s="149" t="s">
         <v>817</v>
       </c>
-      <c r="I1404" s="150" t="s">
+      <c r="I1404" s="149" t="s">
         <v>813</v>
       </c>
       <c r="J1404" s="63" t="s">
@@ -72615,10 +72669,10 @@
       <c r="G1405" s="56">
         <v>4.4826388888888895E-2</v>
       </c>
-      <c r="H1405" s="150" t="s">
+      <c r="H1405" s="149" t="s">
         <v>817</v>
       </c>
-      <c r="I1405" s="150" t="s">
+      <c r="I1405" s="149" t="s">
         <v>813</v>
       </c>
       <c r="J1405" s="63" t="s">
@@ -72656,10 +72710,10 @@
       <c r="G1406" s="56">
         <v>5.6840277777777781E-2</v>
       </c>
-      <c r="H1406" s="150" t="s">
+      <c r="H1406" s="149" t="s">
         <v>34</v>
       </c>
-      <c r="I1406" s="150" t="s">
+      <c r="I1406" s="149" t="s">
         <v>813</v>
       </c>
       <c r="J1406" s="63" t="s">
@@ -72697,10 +72751,10 @@
       <c r="G1407" s="56">
         <v>5.0219907407407414E-2</v>
       </c>
-      <c r="H1407" s="150" t="s">
+      <c r="H1407" s="149" t="s">
         <v>817</v>
       </c>
-      <c r="I1407" s="150" t="s">
+      <c r="I1407" s="149" t="s">
         <v>813</v>
       </c>
       <c r="J1407" s="63" t="s">
@@ -72730,7 +72784,7 @@
         <v>424</v>
       </c>
       <c r="E1408" t="s">
-        <v>720</v>
+        <v>1583</v>
       </c>
       <c r="F1408" s="29">
         <v>46110</v>
@@ -72738,10 +72792,10 @@
       <c r="G1408" s="56">
         <v>0.24459490740740741</v>
       </c>
-      <c r="H1408" s="151" t="s">
+      <c r="H1408" s="150" t="s">
         <v>815</v>
       </c>
-      <c r="I1408" s="151" t="s">
+      <c r="I1408" s="150" t="s">
         <v>806</v>
       </c>
       <c r="J1408" s="63" t="s">
@@ -72754,7 +72808,7 @@
         <v>854</v>
       </c>
       <c r="N1408" t="s">
-        <v>4063</v>
+        <v>4330</v>
       </c>
     </row>
     <row r="1409" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -72779,14 +72833,14 @@
       <c r="G1409" s="56">
         <v>6.7835648148148145E-2</v>
       </c>
-      <c r="H1409" s="151" t="s">
+      <c r="H1409" s="150" t="s">
         <v>1387</v>
       </c>
-      <c r="I1409" s="151" t="s">
+      <c r="I1409" s="150" t="s">
         <v>290</v>
       </c>
       <c r="J1409" s="63" t="s">
-        <v>4060</v>
+        <v>4059</v>
       </c>
       <c r="K1409">
         <v>1410</v>
@@ -72795,7 +72849,7 @@
         <v>854</v>
       </c>
       <c r="N1409" t="s">
-        <v>4064</v>
+        <v>4062</v>
       </c>
     </row>
     <row r="1410" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -72820,14 +72874,14 @@
       <c r="G1410" s="56">
         <v>0.10422453703703705</v>
       </c>
-      <c r="H1410" s="151" t="s">
+      <c r="H1410" s="150" t="s">
+        <v>4060</v>
+      </c>
+      <c r="I1410" s="150" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1410" s="63" t="s">
         <v>4061</v>
-      </c>
-      <c r="I1410" s="151" t="s">
-        <v>806</v>
-      </c>
-      <c r="J1410" s="63" t="s">
-        <v>4062</v>
       </c>
       <c r="K1410">
         <v>1411</v>
@@ -72836,7 +72890,7 @@
         <v>854</v>
       </c>
       <c r="N1410" t="s">
-        <v>4065</v>
+        <v>4063</v>
       </c>
     </row>
     <row r="1411" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -72861,14 +72915,14 @@
       <c r="G1411" s="56">
         <v>9.4386574074074081E-2</v>
       </c>
-      <c r="H1411" s="151" t="s">
-        <v>4067</v>
-      </c>
-      <c r="I1411" s="151" t="s">
+      <c r="H1411" s="150" t="s">
+        <v>4065</v>
+      </c>
+      <c r="I1411" s="150" t="s">
         <v>806</v>
       </c>
       <c r="J1411" s="63" t="s">
-        <v>4066</v>
+        <v>4064</v>
       </c>
       <c r="K1411">
         <v>1412</v>
@@ -72877,7 +72931,7 @@
         <v>854</v>
       </c>
       <c r="N1411" t="s">
-        <v>4068</v>
+        <v>4066</v>
       </c>
     </row>
     <row r="1412" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -72902,14 +72956,14 @@
       <c r="G1412" s="56">
         <v>7.0405092592592589E-2</v>
       </c>
-      <c r="H1412" s="152" t="s">
+      <c r="H1412" s="151" t="s">
         <v>815</v>
       </c>
-      <c r="I1412" s="152" t="s">
+      <c r="I1412" s="151" t="s">
         <v>290</v>
       </c>
       <c r="J1412" s="63" t="s">
-        <v>4069</v>
+        <v>4067</v>
       </c>
       <c r="K1412">
         <v>1413</v>
@@ -72918,7 +72972,7 @@
         <v>854</v>
       </c>
       <c r="N1412" t="s">
-        <v>4070</v>
+        <v>4068</v>
       </c>
     </row>
     <row r="1413" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -72929,10 +72983,10 @@
         <v>7693476</v>
       </c>
       <c r="C1413" t="s">
-        <v>4071</v>
+        <v>4069</v>
       </c>
       <c r="D1413" t="s">
-        <v>4072</v>
+        <v>4070</v>
       </c>
       <c r="E1413" t="s">
         <v>648</v>
@@ -72943,14 +72997,14 @@
       <c r="G1413" s="56">
         <v>0.10199074074074073</v>
       </c>
-      <c r="H1413" s="153" t="s">
+      <c r="H1413" s="152" t="s">
         <v>814</v>
       </c>
-      <c r="I1413" s="153" t="s">
+      <c r="I1413" s="152" t="s">
         <v>290</v>
       </c>
       <c r="J1413" s="63" t="s">
-        <v>4073</v>
+        <v>4071</v>
       </c>
       <c r="K1413">
         <v>1414</v>
@@ -72959,7 +73013,7 @@
         <v>854</v>
       </c>
       <c r="N1413" t="s">
-        <v>4077</v>
+        <v>4075</v>
       </c>
     </row>
     <row r="1414" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -72984,14 +73038,14 @@
       <c r="G1414" s="56">
         <v>0.25377314814814816</v>
       </c>
-      <c r="H1414" s="153" t="s">
+      <c r="H1414" s="152" t="s">
         <v>1353</v>
       </c>
-      <c r="I1414" s="153" t="s">
+      <c r="I1414" s="152" t="s">
         <v>290</v>
       </c>
       <c r="J1414" s="63" t="s">
-        <v>4074</v>
+        <v>4072</v>
       </c>
       <c r="K1414">
         <v>1415</v>
@@ -73000,7 +73054,7 @@
         <v>854</v>
       </c>
       <c r="N1414" t="s">
-        <v>4078</v>
+        <v>4076</v>
       </c>
     </row>
     <row r="1415" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73011,7 +73065,7 @@
         <v>13091775</v>
       </c>
       <c r="C1415" t="s">
-        <v>4076</v>
+        <v>4074</v>
       </c>
       <c r="D1415" t="s">
         <v>3908</v>
@@ -73025,26 +73079,26 @@
       <c r="G1415" s="56">
         <v>0.14434027777777778</v>
       </c>
-      <c r="H1415" s="153" t="s">
+      <c r="H1415" s="152" t="s">
         <v>805</v>
       </c>
-      <c r="I1415" s="153" t="s">
+      <c r="I1415" s="152" t="s">
         <v>290</v>
       </c>
       <c r="J1415" s="63" t="s">
-        <v>4075</v>
+        <v>4073</v>
       </c>
       <c r="K1415">
         <v>1416</v>
       </c>
       <c r="L1415" t="s">
-        <v>4083</v>
+        <v>4081</v>
       </c>
       <c r="M1415" s="57" t="s">
         <v>854</v>
       </c>
       <c r="N1415" t="s">
-        <v>4079</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="1416" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73069,14 +73123,14 @@
       <c r="G1416" s="56">
         <v>8.8391203703703694E-2</v>
       </c>
-      <c r="H1416" s="154" t="s">
+      <c r="H1416" s="153" t="s">
         <v>815</v>
       </c>
-      <c r="I1416" s="154" t="s">
+      <c r="I1416" s="153" t="s">
         <v>290</v>
       </c>
       <c r="J1416" s="63" t="s">
-        <v>4080</v>
+        <v>4078</v>
       </c>
       <c r="K1416">
         <v>1417</v>
@@ -73085,7 +73139,7 @@
         <v>854</v>
       </c>
       <c r="N1416" t="s">
-        <v>4093</v>
+        <v>4091</v>
       </c>
     </row>
     <row r="1417" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73096,13 +73150,13 @@
         <v>11466215</v>
       </c>
       <c r="C1417" t="s">
-        <v>4084</v>
+        <v>4082</v>
       </c>
       <c r="D1417" t="s">
         <v>76</v>
       </c>
       <c r="E1417" t="s">
-        <v>4085</v>
+        <v>4083</v>
       </c>
       <c r="F1417" s="29">
         <v>44658</v>
@@ -73110,26 +73164,26 @@
       <c r="G1417" s="56">
         <v>5.486111111111111E-2</v>
       </c>
-      <c r="H1417" s="155" t="s">
+      <c r="H1417" s="154" t="s">
         <v>817</v>
       </c>
-      <c r="I1417" s="155" t="s">
+      <c r="I1417" s="154" t="s">
         <v>813</v>
       </c>
       <c r="J1417" s="63" t="s">
-        <v>4081</v>
+        <v>4079</v>
       </c>
       <c r="K1417">
         <v>1418</v>
       </c>
       <c r="L1417" t="s">
-        <v>4082</v>
+        <v>4080</v>
       </c>
       <c r="M1417" s="57" t="s">
         <v>854</v>
       </c>
       <c r="N1417" t="s">
-        <v>4094</v>
+        <v>4092</v>
       </c>
     </row>
     <row r="1418" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73140,13 +73194,13 @@
         <v>3883470</v>
       </c>
       <c r="C1418" t="s">
-        <v>4084</v>
+        <v>4082</v>
       </c>
       <c r="D1418" t="s">
         <v>203</v>
       </c>
       <c r="E1418" t="s">
-        <v>4085</v>
+        <v>4083</v>
       </c>
       <c r="F1418" s="29">
         <v>44665</v>
@@ -73154,26 +73208,26 @@
       <c r="G1418" s="56">
         <v>3.8124999999999999E-2</v>
       </c>
-      <c r="H1418" s="155" t="s">
+      <c r="H1418" s="154" t="s">
         <v>805</v>
       </c>
-      <c r="I1418" s="155" t="s">
+      <c r="I1418" s="154" t="s">
         <v>290</v>
       </c>
       <c r="J1418" s="63" t="s">
-        <v>4086</v>
+        <v>4084</v>
       </c>
       <c r="K1418">
         <v>1419</v>
       </c>
       <c r="L1418" t="s">
-        <v>4082</v>
+        <v>4080</v>
       </c>
       <c r="M1418" s="57" t="s">
         <v>854</v>
       </c>
       <c r="N1418" t="s">
-        <v>4095</v>
+        <v>4093</v>
       </c>
     </row>
     <row r="1419" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73184,13 +73238,13 @@
         <v>9895396</v>
       </c>
       <c r="C1419" t="s">
-        <v>4087</v>
+        <v>4085</v>
       </c>
       <c r="D1419" t="s">
         <v>76</v>
       </c>
       <c r="E1419" t="s">
-        <v>4088</v>
+        <v>4086</v>
       </c>
       <c r="F1419" s="29">
         <v>44675</v>
@@ -73198,14 +73252,14 @@
       <c r="G1419" s="56" t="s">
         <v>502</v>
       </c>
-      <c r="H1419" s="155" t="s">
+      <c r="H1419" s="154" t="s">
         <v>502</v>
       </c>
-      <c r="I1419" s="155" t="s">
+      <c r="I1419" s="154" t="s">
         <v>813</v>
       </c>
       <c r="J1419" s="63" t="s">
-        <v>4089</v>
+        <v>4087</v>
       </c>
       <c r="K1419">
         <v>1420</v>
@@ -73214,7 +73268,7 @@
         <v>854</v>
       </c>
       <c r="N1419" t="s">
-        <v>4096</v>
+        <v>4094</v>
       </c>
     </row>
     <row r="1420" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73239,14 +73293,14 @@
       <c r="G1420" s="56">
         <v>9.673611111111112E-2</v>
       </c>
-      <c r="H1420" s="155" t="s">
+      <c r="H1420" s="154" t="s">
         <v>942</v>
       </c>
-      <c r="I1420" s="155" t="s">
+      <c r="I1420" s="154" t="s">
         <v>813</v>
       </c>
       <c r="J1420" s="63" t="s">
-        <v>4090</v>
+        <v>4088</v>
       </c>
       <c r="K1420">
         <v>1421</v>
@@ -73255,7 +73309,7 @@
         <v>854</v>
       </c>
       <c r="N1420" t="s">
-        <v>4097</v>
+        <v>4095</v>
       </c>
     </row>
     <row r="1421" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73280,14 +73334,14 @@
       <c r="G1421" s="56">
         <v>6.4826388888888892E-2</v>
       </c>
-      <c r="H1421" s="155" t="s">
+      <c r="H1421" s="154" t="s">
         <v>835</v>
       </c>
-      <c r="I1421" s="155" t="s">
+      <c r="I1421" s="154" t="s">
         <v>290</v>
       </c>
       <c r="J1421" s="63" t="s">
-        <v>4091</v>
+        <v>4089</v>
       </c>
       <c r="K1421">
         <v>1422</v>
@@ -73296,7 +73350,7 @@
         <v>854</v>
       </c>
       <c r="N1421" t="s">
-        <v>4098</v>
+        <v>4096</v>
       </c>
     </row>
     <row r="1422" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73321,14 +73375,14 @@
       <c r="G1422" s="56">
         <v>5.8136574074074077E-2</v>
       </c>
-      <c r="H1422" s="155" t="s">
+      <c r="H1422" s="154" t="s">
         <v>805</v>
       </c>
-      <c r="I1422" s="155" t="s">
+      <c r="I1422" s="154" t="s">
         <v>806</v>
       </c>
       <c r="J1422" s="63" t="s">
-        <v>4092</v>
+        <v>4090</v>
       </c>
       <c r="K1422">
         <v>1423</v>
@@ -73337,7 +73391,7 @@
         <v>854</v>
       </c>
       <c r="N1422" t="s">
-        <v>4099</v>
+        <v>4097</v>
       </c>
     </row>
     <row r="1423" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73362,14 +73416,14 @@
       <c r="G1423" s="56" t="s">
         <v>502</v>
       </c>
-      <c r="H1423" s="156" t="s">
-        <v>4100</v>
-      </c>
-      <c r="I1423" s="156" t="s">
+      <c r="H1423" s="155" t="s">
+        <v>4098</v>
+      </c>
+      <c r="I1423" s="155" t="s">
         <v>806</v>
       </c>
       <c r="J1423" s="63" t="s">
-        <v>4101</v>
+        <v>4099</v>
       </c>
       <c r="K1423">
         <v>1424</v>
@@ -73378,7 +73432,7 @@
         <v>854</v>
       </c>
       <c r="N1423" t="s">
-        <v>4106</v>
+        <v>4104</v>
       </c>
     </row>
     <row r="1424" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73403,14 +73457,14 @@
       <c r="G1424" s="56">
         <v>9.1712962962962954E-2</v>
       </c>
-      <c r="H1424" s="156" t="s">
-        <v>4103</v>
-      </c>
-      <c r="I1424" s="156" t="s">
+      <c r="H1424" s="155" t="s">
+        <v>4101</v>
+      </c>
+      <c r="I1424" s="155" t="s">
         <v>806</v>
       </c>
       <c r="J1424" s="63" t="s">
-        <v>4102</v>
+        <v>4100</v>
       </c>
       <c r="K1424">
         <v>1425</v>
@@ -73419,7 +73473,7 @@
         <v>854</v>
       </c>
       <c r="N1424" t="s">
-        <v>4107</v>
+        <v>4105</v>
       </c>
     </row>
     <row r="1425" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73444,14 +73498,14 @@
       <c r="G1425" s="56">
         <v>0.13195601851851851</v>
       </c>
-      <c r="H1425" s="157" t="s">
+      <c r="H1425" s="156" t="s">
         <v>811</v>
       </c>
-      <c r="I1425" s="157" t="s">
+      <c r="I1425" s="156" t="s">
         <v>806</v>
       </c>
       <c r="J1425" t="s">
-        <v>4104</v>
+        <v>4102</v>
       </c>
       <c r="K1425">
         <v>1426</v>
@@ -73460,7 +73514,7 @@
         <v>854</v>
       </c>
       <c r="N1425" t="s">
-        <v>4108</v>
+        <v>4106</v>
       </c>
     </row>
     <row r="1426" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73485,14 +73539,14 @@
       <c r="G1426" s="56">
         <v>6.9930555555555551E-2</v>
       </c>
-      <c r="H1426" s="157" t="s">
+      <c r="H1426" s="156" t="s">
         <v>835</v>
       </c>
-      <c r="I1426" s="157" t="s">
+      <c r="I1426" s="156" t="s">
         <v>806</v>
       </c>
       <c r="J1426" t="s">
-        <v>4105</v>
+        <v>4103</v>
       </c>
       <c r="K1426">
         <v>1427</v>
@@ -73501,7 +73555,7 @@
         <v>854</v>
       </c>
       <c r="N1426" t="s">
-        <v>4109</v>
+        <v>4107</v>
       </c>
     </row>
     <row r="1427" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73526,14 +73580,14 @@
       <c r="G1427" s="56">
         <v>5.9282407407407402E-2</v>
       </c>
-      <c r="H1427" s="158" t="s">
+      <c r="H1427" s="157" t="s">
         <v>1107</v>
       </c>
-      <c r="I1427" s="158" t="s">
+      <c r="I1427" s="157" t="s">
         <v>290</v>
       </c>
       <c r="J1427" s="63" t="s">
-        <v>4110</v>
+        <v>4108</v>
       </c>
       <c r="K1427">
         <v>1428</v>
@@ -73542,7 +73596,7 @@
         <v>854</v>
       </c>
       <c r="N1427" t="s">
-        <v>4113</v>
+        <v>4111</v>
       </c>
     </row>
     <row r="1428" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73567,14 +73621,14 @@
       <c r="G1428" s="56" t="s">
         <v>502</v>
       </c>
-      <c r="H1428" s="158" t="s">
+      <c r="H1428" s="157" t="s">
         <v>502</v>
       </c>
-      <c r="I1428" s="158" t="s">
+      <c r="I1428" s="157" t="s">
         <v>290</v>
       </c>
       <c r="J1428" s="63" t="s">
-        <v>4111</v>
+        <v>4109</v>
       </c>
       <c r="K1428">
         <v>1429</v>
@@ -73583,7 +73637,7 @@
         <v>854</v>
       </c>
       <c r="N1428" t="s">
-        <v>4114</v>
+        <v>4112</v>
       </c>
     </row>
     <row r="1429" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73608,14 +73662,14 @@
       <c r="G1429" s="56">
         <v>0.11660879629629629</v>
       </c>
-      <c r="H1429" s="158" t="s">
+      <c r="H1429" s="157" t="s">
         <v>938</v>
       </c>
-      <c r="I1429" s="158" t="s">
+      <c r="I1429" s="157" t="s">
         <v>290</v>
       </c>
       <c r="J1429" s="63" t="s">
-        <v>4112</v>
+        <v>4110</v>
       </c>
       <c r="K1429">
         <v>1430</v>
@@ -73624,7 +73678,7 @@
         <v>854</v>
       </c>
       <c r="N1429" t="s">
-        <v>4115</v>
+        <v>4113</v>
       </c>
     </row>
     <row r="1430" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73635,13 +73689,13 @@
         <v>17360872</v>
       </c>
       <c r="C1430" t="s">
-        <v>4116</v>
+        <v>4114</v>
       </c>
       <c r="D1430" t="s">
         <v>424</v>
       </c>
       <c r="E1430" t="s">
-        <v>720</v>
+        <v>1583</v>
       </c>
       <c r="F1430" s="29">
         <v>46074</v>
@@ -73649,14 +73703,14 @@
       <c r="G1430" s="56">
         <v>7.9027777777777766E-2</v>
       </c>
-      <c r="H1430" s="159" t="s">
+      <c r="H1430" s="158" t="s">
         <v>825</v>
       </c>
-      <c r="I1430" s="159" t="s">
+      <c r="I1430" s="158" t="s">
         <v>806</v>
       </c>
       <c r="J1430" s="63" t="s">
-        <v>4118</v>
+        <v>4116</v>
       </c>
       <c r="K1430">
         <v>1431</v>
@@ -73665,7 +73719,7 @@
         <v>854</v>
       </c>
       <c r="N1430" t="s">
-        <v>4135</v>
+        <v>4133</v>
       </c>
     </row>
     <row r="1431" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73676,13 +73730,13 @@
         <v>12424839</v>
       </c>
       <c r="C1431" t="s">
-        <v>4120</v>
+        <v>4118</v>
       </c>
       <c r="D1431" t="s">
         <v>424</v>
       </c>
       <c r="E1431" t="s">
-        <v>720</v>
+        <v>1583</v>
       </c>
       <c r="F1431" s="29">
         <v>46058</v>
@@ -73690,14 +73744,14 @@
       <c r="G1431" s="56">
         <v>5.903935185185185E-2</v>
       </c>
-      <c r="H1431" s="159" t="s">
+      <c r="H1431" s="158" t="s">
         <v>815</v>
       </c>
-      <c r="I1431" s="159" t="s">
+      <c r="I1431" s="158" t="s">
         <v>806</v>
       </c>
       <c r="J1431" s="63" t="s">
-        <v>4119</v>
+        <v>4117</v>
       </c>
       <c r="K1431">
         <v>1432</v>
@@ -73706,7 +73760,7 @@
         <v>854</v>
       </c>
       <c r="N1431" t="s">
-        <v>4136</v>
+        <v>4134</v>
       </c>
     </row>
     <row r="1432" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73731,14 +73785,14 @@
       <c r="G1432" s="56">
         <v>8.1250000000000003E-2</v>
       </c>
-      <c r="H1432" s="159" t="s">
+      <c r="H1432" s="158" t="s">
         <v>1387</v>
       </c>
-      <c r="I1432" s="159" t="s">
+      <c r="I1432" s="158" t="s">
         <v>290</v>
       </c>
       <c r="J1432" s="63" t="s">
-        <v>4121</v>
+        <v>4119</v>
       </c>
       <c r="K1432">
         <v>1433</v>
@@ -73747,7 +73801,7 @@
         <v>854</v>
       </c>
       <c r="N1432" t="s">
-        <v>4137</v>
+        <v>4135</v>
       </c>
     </row>
     <row r="1433" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73772,14 +73826,14 @@
       <c r="G1433" s="56" t="s">
         <v>502</v>
       </c>
-      <c r="H1433" s="159" t="s">
+      <c r="H1433" s="158" t="s">
         <v>502</v>
       </c>
-      <c r="I1433" s="159" t="s">
+      <c r="I1433" s="158" t="s">
         <v>290</v>
       </c>
       <c r="J1433" s="63" t="s">
-        <v>4122</v>
+        <v>4120</v>
       </c>
       <c r="K1433">
         <v>1434</v>
@@ -73788,7 +73842,7 @@
         <v>854</v>
       </c>
       <c r="N1433" t="s">
-        <v>4138</v>
+        <v>4136</v>
       </c>
     </row>
     <row r="1434" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73799,7 +73853,7 @@
         <v>7706544</v>
       </c>
       <c r="C1434" t="s">
-        <v>4125</v>
+        <v>4123</v>
       </c>
       <c r="D1434" t="s">
         <v>276</v>
@@ -73813,14 +73867,14 @@
       <c r="G1434" s="56">
         <v>8.6296296296296301E-2</v>
       </c>
-      <c r="H1434" s="159" t="s">
-        <v>4126</v>
-      </c>
-      <c r="I1434" s="159" t="s">
+      <c r="H1434" s="158" t="s">
+        <v>4124</v>
+      </c>
+      <c r="I1434" s="158" t="s">
         <v>290</v>
       </c>
       <c r="J1434" s="63" t="s">
-        <v>4123</v>
+        <v>4121</v>
       </c>
       <c r="K1434">
         <v>1435</v>
@@ -73829,7 +73883,7 @@
         <v>854</v>
       </c>
       <c r="N1434" t="s">
-        <v>4139</v>
+        <v>4137</v>
       </c>
     </row>
     <row r="1435" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73854,14 +73908,14 @@
       <c r="G1435" s="56">
         <v>6.5648148148148136E-2</v>
       </c>
-      <c r="H1435" s="159" t="s">
+      <c r="H1435" s="158" t="s">
         <v>825</v>
       </c>
-      <c r="I1435" s="159" t="s">
+      <c r="I1435" s="158" t="s">
         <v>806</v>
       </c>
       <c r="J1435" s="63" t="s">
-        <v>4127</v>
+        <v>4125</v>
       </c>
       <c r="K1435">
         <v>1436</v>
@@ -73870,7 +73924,7 @@
         <v>854</v>
       </c>
       <c r="N1435" t="s">
-        <v>4140</v>
+        <v>4138</v>
       </c>
     </row>
     <row r="1436" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73881,7 +73935,7 @@
         <v>4687810</v>
       </c>
       <c r="C1436" t="s">
-        <v>4129</v>
+        <v>4127</v>
       </c>
       <c r="D1436" t="s">
         <v>117</v>
@@ -73895,14 +73949,14 @@
       <c r="G1436" s="56">
         <v>3.7893518518518521E-2</v>
       </c>
-      <c r="H1436" s="159" t="s">
-        <v>4130</v>
-      </c>
-      <c r="I1436" s="159" t="s">
+      <c r="H1436" s="158" t="s">
+        <v>4128</v>
+      </c>
+      <c r="I1436" s="158" t="s">
         <v>806</v>
       </c>
       <c r="J1436" s="63" t="s">
-        <v>4128</v>
+        <v>4126</v>
       </c>
       <c r="K1436">
         <v>1437</v>
@@ -73911,7 +73965,7 @@
         <v>854</v>
       </c>
       <c r="N1436" t="s">
-        <v>4141</v>
+        <v>4139</v>
       </c>
     </row>
     <row r="1437" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73936,14 +73990,14 @@
       <c r="G1437" s="56">
         <v>5.3807870370370374E-2</v>
       </c>
-      <c r="H1437" s="159" t="s">
+      <c r="H1437" s="158" t="s">
         <v>1107</v>
       </c>
-      <c r="I1437" s="159" t="s">
+      <c r="I1437" s="158" t="s">
         <v>290</v>
       </c>
       <c r="J1437" s="63" t="s">
-        <v>4131</v>
+        <v>4129</v>
       </c>
       <c r="K1437">
         <v>1438</v>
@@ -73952,7 +74006,7 @@
         <v>854</v>
       </c>
       <c r="N1437" t="s">
-        <v>4142</v>
+        <v>4140</v>
       </c>
     </row>
     <row r="1438" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -73963,7 +74017,7 @@
         <v>11879917</v>
       </c>
       <c r="C1438" t="s">
-        <v>4132</v>
+        <v>4130</v>
       </c>
       <c r="D1438" t="s">
         <v>9</v>
@@ -73977,14 +74031,14 @@
       <c r="G1438" s="56">
         <v>6.3912037037037031E-2</v>
       </c>
-      <c r="H1438" s="159" t="s">
+      <c r="H1438" s="158" t="s">
         <v>817</v>
       </c>
-      <c r="I1438" s="159" t="s">
+      <c r="I1438" s="158" t="s">
         <v>806</v>
       </c>
       <c r="J1438" s="63" t="s">
-        <v>4133</v>
+        <v>4131</v>
       </c>
       <c r="K1438">
         <v>1439</v>
@@ -73993,7 +74047,7 @@
         <v>854</v>
       </c>
       <c r="N1438" t="s">
-        <v>4143</v>
+        <v>4141</v>
       </c>
     </row>
     <row r="1439" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74004,7 +74058,7 @@
         <v>9493583</v>
       </c>
       <c r="C1439" t="s">
-        <v>4144</v>
+        <v>4142</v>
       </c>
       <c r="D1439" t="s">
         <v>33</v>
@@ -74018,14 +74072,14 @@
       <c r="G1439" s="56">
         <v>9.9444444444444446E-2</v>
       </c>
-      <c r="H1439" s="160" t="s">
+      <c r="H1439" s="159" t="s">
         <v>830</v>
       </c>
-      <c r="I1439" s="160" t="s">
+      <c r="I1439" s="159" t="s">
         <v>806</v>
       </c>
       <c r="J1439" s="63" t="s">
-        <v>4145</v>
+        <v>4143</v>
       </c>
       <c r="K1439">
         <v>1440</v>
@@ -74034,7 +74088,7 @@
         <v>854</v>
       </c>
       <c r="N1439" t="s">
-        <v>4153</v>
+        <v>4151</v>
       </c>
     </row>
     <row r="1440" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74051,7 +74105,7 @@
         <v>277</v>
       </c>
       <c r="E1440" t="s">
-        <v>720</v>
+        <v>1583</v>
       </c>
       <c r="F1440" s="29">
         <v>45766</v>
@@ -74059,14 +74113,14 @@
       <c r="G1440" s="56" t="s">
         <v>502</v>
       </c>
-      <c r="H1440" s="160" t="s">
+      <c r="H1440" s="159" t="s">
         <v>502</v>
       </c>
-      <c r="I1440" s="160" t="s">
+      <c r="I1440" s="159" t="s">
         <v>806</v>
       </c>
       <c r="J1440" s="63" t="s">
-        <v>4146</v>
+        <v>4144</v>
       </c>
       <c r="K1440">
         <v>1441</v>
@@ -74075,7 +74129,7 @@
         <v>854</v>
       </c>
       <c r="N1440" t="s">
-        <v>4154</v>
+        <v>4152</v>
       </c>
     </row>
     <row r="1441" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74086,13 +74140,13 @@
         <v>4930000</v>
       </c>
       <c r="C1441" t="s">
-        <v>4148</v>
+        <v>4146</v>
       </c>
       <c r="D1441" t="s">
         <v>305</v>
       </c>
       <c r="E1441" t="s">
-        <v>4148</v>
+        <v>4146</v>
       </c>
       <c r="F1441" s="29">
         <v>45766</v>
@@ -74100,14 +74154,14 @@
       <c r="G1441" s="56" t="s">
         <v>502</v>
       </c>
-      <c r="H1441" s="160" t="s">
+      <c r="H1441" s="159" t="s">
         <v>502</v>
       </c>
-      <c r="I1441" s="160" t="s">
+      <c r="I1441" s="159" t="s">
         <v>806</v>
       </c>
       <c r="J1441" s="63" t="s">
-        <v>4147</v>
+        <v>4145</v>
       </c>
       <c r="K1441">
         <v>1442</v>
@@ -74116,7 +74170,7 @@
         <v>854</v>
       </c>
       <c r="N1441" t="s">
-        <v>4155</v>
+        <v>4153</v>
       </c>
     </row>
     <row r="1442" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74127,13 +74181,13 @@
         <v>12540000</v>
       </c>
       <c r="C1442" t="s">
-        <v>4149</v>
+        <v>4147</v>
       </c>
       <c r="D1442" t="s">
         <v>40</v>
       </c>
       <c r="E1442" t="s">
-        <v>4158</v>
+        <v>4156</v>
       </c>
       <c r="F1442" s="29">
         <v>45875</v>
@@ -74141,14 +74195,14 @@
       <c r="G1442" s="56" t="s">
         <v>502</v>
       </c>
-      <c r="H1442" s="160" t="s">
+      <c r="H1442" s="159" t="s">
         <v>502</v>
       </c>
-      <c r="I1442" s="160" t="s">
+      <c r="I1442" s="159" t="s">
         <v>806</v>
       </c>
       <c r="J1442" s="63" t="s">
-        <v>4151</v>
+        <v>4149</v>
       </c>
       <c r="K1442">
         <v>1443</v>
@@ -74157,7 +74211,7 @@
         <v>854</v>
       </c>
       <c r="N1442" t="s">
-        <v>4156</v>
+        <v>4154</v>
       </c>
     </row>
     <row r="1443" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74168,13 +74222,13 @@
         <v>12210000</v>
       </c>
       <c r="C1443" t="s">
-        <v>4150</v>
+        <v>4148</v>
       </c>
       <c r="D1443" t="s">
         <v>65</v>
       </c>
       <c r="E1443" t="s">
-        <v>4150</v>
+        <v>4148</v>
       </c>
       <c r="F1443" s="29">
         <v>45875</v>
@@ -74182,14 +74236,14 @@
       <c r="G1443" s="56" t="s">
         <v>502</v>
       </c>
-      <c r="H1443" s="160" t="s">
+      <c r="H1443" s="159" t="s">
         <v>502</v>
       </c>
-      <c r="I1443" s="160" t="s">
+      <c r="I1443" s="159" t="s">
         <v>806</v>
       </c>
       <c r="J1443" s="63" t="s">
-        <v>4152</v>
+        <v>4150</v>
       </c>
       <c r="K1443">
         <v>1444</v>
@@ -74198,7 +74252,7 @@
         <v>854</v>
       </c>
       <c r="N1443" t="s">
-        <v>4157</v>
+        <v>4155</v>
       </c>
     </row>
     <row r="1444" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74209,13 +74263,13 @@
         <v>22630000</v>
       </c>
       <c r="C1444" t="s">
-        <v>4159</v>
+        <v>4157</v>
       </c>
       <c r="D1444" t="s">
         <v>60</v>
       </c>
       <c r="E1444" t="s">
-        <v>4159</v>
+        <v>4157</v>
       </c>
       <c r="F1444" s="29">
         <v>46144</v>
@@ -74223,14 +74277,14 @@
       <c r="G1444" s="56" t="s">
         <v>502</v>
       </c>
-      <c r="H1444" s="161" t="s">
+      <c r="H1444" s="160" t="s">
         <v>2031</v>
       </c>
-      <c r="I1444" s="161" t="s">
+      <c r="I1444" s="160" t="s">
         <v>806</v>
       </c>
       <c r="J1444" s="63" t="s">
-        <v>4160</v>
+        <v>4158</v>
       </c>
       <c r="K1444">
         <v>1445</v>
@@ -74239,7 +74293,7 @@
         <v>854</v>
       </c>
       <c r="N1444" t="s">
-        <v>4173</v>
+        <v>4171</v>
       </c>
     </row>
     <row r="1445" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74261,14 +74315,14 @@
       <c r="F1445" s="29">
         <v>46144</v>
       </c>
-      <c r="H1445" s="161" t="s">
+      <c r="H1445" s="160" t="s">
         <v>2031</v>
       </c>
-      <c r="I1445" s="161" t="s">
+      <c r="I1445" s="160" t="s">
         <v>806</v>
       </c>
       <c r="J1445" s="63" t="s">
-        <v>4161</v>
+        <v>4159</v>
       </c>
       <c r="K1445">
         <v>1446</v>
@@ -74277,7 +74331,7 @@
         <v>854</v>
       </c>
       <c r="N1445" t="s">
-        <v>4174</v>
+        <v>4172</v>
       </c>
     </row>
     <row r="1446" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74302,14 +74356,14 @@
       <c r="G1446" s="56">
         <v>7.3657407407407408E-2</v>
       </c>
-      <c r="H1446" s="161" t="s">
+      <c r="H1446" s="160" t="s">
         <v>817</v>
       </c>
-      <c r="I1446" s="161" t="s">
+      <c r="I1446" s="160" t="s">
         <v>806</v>
       </c>
       <c r="J1446" s="63" t="s">
-        <v>4162</v>
+        <v>4160</v>
       </c>
       <c r="K1446">
         <v>1447</v>
@@ -74318,7 +74372,7 @@
         <v>854</v>
       </c>
       <c r="N1446" t="s">
-        <v>4175</v>
+        <v>4173</v>
       </c>
     </row>
     <row r="1447" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74329,7 +74383,7 @@
         <v>13197466</v>
       </c>
       <c r="C1447" t="s">
-        <v>4166</v>
+        <v>4164</v>
       </c>
       <c r="D1447" t="s">
         <v>3717</v>
@@ -74343,14 +74397,14 @@
       <c r="G1447" s="56">
         <v>0.12055555555555557</v>
       </c>
-      <c r="H1447" s="161" t="s">
+      <c r="H1447" s="160" t="s">
         <v>825</v>
       </c>
-      <c r="I1447" s="161" t="s">
+      <c r="I1447" s="160" t="s">
         <v>806</v>
       </c>
       <c r="J1447" s="63" t="s">
-        <v>4163</v>
+        <v>4161</v>
       </c>
       <c r="K1447">
         <v>1448</v>
@@ -74359,7 +74413,7 @@
         <v>854</v>
       </c>
       <c r="N1447" t="s">
-        <v>4176</v>
+        <v>4174</v>
       </c>
     </row>
     <row r="1448" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74384,14 +74438,14 @@
       <c r="G1448" s="56">
         <v>8.0532407407407414E-2</v>
       </c>
-      <c r="H1448" s="161" t="s">
+      <c r="H1448" s="160" t="s">
         <v>833</v>
       </c>
-      <c r="I1448" s="161" t="s">
+      <c r="I1448" s="160" t="s">
         <v>806</v>
       </c>
       <c r="J1448" s="63" t="s">
-        <v>4164</v>
+        <v>4162</v>
       </c>
       <c r="K1448">
         <v>1449</v>
@@ -74400,7 +74454,7 @@
         <v>854</v>
       </c>
       <c r="N1448" t="s">
-        <v>4177</v>
+        <v>4175</v>
       </c>
     </row>
     <row r="1449" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74411,7 +74465,7 @@
         <v>9164274</v>
       </c>
       <c r="C1449" t="s">
-        <v>4166</v>
+        <v>4164</v>
       </c>
       <c r="D1449" t="s">
         <v>3717</v>
@@ -74425,14 +74479,14 @@
       <c r="G1449" s="56">
         <v>8.1504629629629635E-2</v>
       </c>
-      <c r="H1449" s="161" t="s">
+      <c r="H1449" s="160" t="s">
         <v>1239</v>
       </c>
-      <c r="I1449" s="161" t="s">
+      <c r="I1449" s="160" t="s">
         <v>806</v>
       </c>
       <c r="J1449" s="63" t="s">
-        <v>4165</v>
+        <v>4163</v>
       </c>
       <c r="K1449">
         <v>1450</v>
@@ -74441,7 +74495,7 @@
         <v>854</v>
       </c>
       <c r="N1449" t="s">
-        <v>4178</v>
+        <v>4176</v>
       </c>
     </row>
     <row r="1450" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74452,7 +74506,7 @@
         <v>7516720</v>
       </c>
       <c r="C1450" t="s">
-        <v>4166</v>
+        <v>4164</v>
       </c>
       <c r="D1450" t="s">
         <v>3717</v>
@@ -74466,14 +74520,14 @@
       <c r="G1450" s="56">
         <v>4.4236111111111115E-2</v>
       </c>
-      <c r="H1450" s="161" t="s">
+      <c r="H1450" s="160" t="s">
         <v>825</v>
       </c>
-      <c r="I1450" s="161" t="s">
+      <c r="I1450" s="160" t="s">
         <v>806</v>
       </c>
       <c r="J1450" s="63" t="s">
-        <v>4167</v>
+        <v>4165</v>
       </c>
       <c r="K1450">
         <v>1451</v>
@@ -74482,7 +74536,7 @@
         <v>854</v>
       </c>
       <c r="N1450" t="s">
-        <v>4179</v>
+        <v>4177</v>
       </c>
     </row>
     <row r="1451" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74496,7 +74550,7 @@
         <v>17</v>
       </c>
       <c r="D1451" t="s">
-        <v>4169</v>
+        <v>4167</v>
       </c>
       <c r="E1451" t="s">
         <v>18</v>
@@ -74507,14 +74561,14 @@
       <c r="G1451" s="56" t="s">
         <v>502</v>
       </c>
-      <c r="H1451" s="161" t="s">
+      <c r="H1451" s="160" t="s">
         <v>2031</v>
       </c>
-      <c r="I1451" s="161" t="s">
+      <c r="I1451" s="160" t="s">
         <v>806</v>
       </c>
       <c r="J1451" s="63" t="s">
-        <v>4168</v>
+        <v>4166</v>
       </c>
       <c r="K1451">
         <v>1452</v>
@@ -74523,7 +74577,7 @@
         <v>854</v>
       </c>
       <c r="N1451" t="s">
-        <v>4180</v>
+        <v>4178</v>
       </c>
     </row>
     <row r="1452" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74548,14 +74602,14 @@
       <c r="G1452" s="56">
         <v>2.0474537037037038E-2</v>
       </c>
-      <c r="H1452" s="161" t="s">
+      <c r="H1452" s="160" t="s">
         <v>835</v>
       </c>
-      <c r="I1452" s="161" t="s">
+      <c r="I1452" s="160" t="s">
         <v>806</v>
       </c>
       <c r="J1452" s="63" t="s">
-        <v>4170</v>
+        <v>4168</v>
       </c>
       <c r="K1452">
         <v>1453</v>
@@ -74564,7 +74618,7 @@
         <v>854</v>
       </c>
       <c r="N1452" t="s">
-        <v>4181</v>
+        <v>4179</v>
       </c>
     </row>
     <row r="1453" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74575,13 +74629,13 @@
         <v>8740000</v>
       </c>
       <c r="C1453" t="s">
-        <v>4171</v>
+        <v>4169</v>
       </c>
       <c r="D1453" t="s">
         <v>330</v>
       </c>
       <c r="E1453" t="s">
-        <v>4171</v>
+        <v>4169</v>
       </c>
       <c r="F1453" s="29">
         <v>46144</v>
@@ -74589,14 +74643,14 @@
       <c r="G1453" s="56" t="s">
         <v>502</v>
       </c>
-      <c r="H1453" s="161" t="s">
+      <c r="H1453" s="160" t="s">
         <v>502</v>
       </c>
-      <c r="I1453" s="161" t="s">
+      <c r="I1453" s="160" t="s">
         <v>806</v>
       </c>
       <c r="J1453" s="63" t="s">
-        <v>4172</v>
+        <v>4170</v>
       </c>
       <c r="K1453">
         <v>1454</v>
@@ -74605,7 +74659,7 @@
         <v>854</v>
       </c>
       <c r="N1453" t="s">
-        <v>4182</v>
+        <v>4180</v>
       </c>
     </row>
     <row r="1454" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74630,14 +74684,14 @@
       <c r="G1454" s="56">
         <v>0.10556712962962962</v>
       </c>
-      <c r="H1454" s="162" t="s">
+      <c r="H1454" s="161" t="s">
         <v>2753</v>
       </c>
-      <c r="I1454" s="162" t="s">
+      <c r="I1454" s="161" t="s">
         <v>806</v>
       </c>
       <c r="J1454" s="63" t="s">
-        <v>4183</v>
+        <v>4181</v>
       </c>
       <c r="K1454">
         <v>1455</v>
@@ -74646,7 +74700,7 @@
         <v>854</v>
       </c>
       <c r="N1454" t="s">
-        <v>4194</v>
+        <v>4192</v>
       </c>
     </row>
     <row r="1455" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74657,7 +74711,7 @@
         <v>8421047</v>
       </c>
       <c r="C1455" t="s">
-        <v>4185</v>
+        <v>4183</v>
       </c>
       <c r="D1455" t="s">
         <v>395</v>
@@ -74671,14 +74725,14 @@
       <c r="G1455" s="56">
         <v>7.03125E-2</v>
       </c>
-      <c r="H1455" s="162" t="s">
+      <c r="H1455" s="161" t="s">
         <v>1106</v>
       </c>
-      <c r="I1455" s="162" t="s">
+      <c r="I1455" s="161" t="s">
         <v>806</v>
       </c>
       <c r="J1455" s="63" t="s">
-        <v>4184</v>
+        <v>4182</v>
       </c>
       <c r="K1455">
         <v>1456</v>
@@ -74687,7 +74741,7 @@
         <v>854</v>
       </c>
       <c r="N1455" t="s">
-        <v>4195</v>
+        <v>4193</v>
       </c>
     </row>
     <row r="1456" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74701,7 +74755,7 @@
         <v>32</v>
       </c>
       <c r="D1456" t="s">
-        <v>4189</v>
+        <v>4187</v>
       </c>
       <c r="E1456" t="s">
         <v>29</v>
@@ -74712,14 +74766,14 @@
       <c r="G1456" s="56">
         <v>6.4398148148148149E-2</v>
       </c>
-      <c r="H1456" s="162" t="s">
+      <c r="H1456" s="161" t="s">
         <v>817</v>
       </c>
-      <c r="I1456" s="162" t="s">
+      <c r="I1456" s="161" t="s">
         <v>806</v>
       </c>
       <c r="J1456" s="63" t="s">
-        <v>4186</v>
+        <v>4184</v>
       </c>
       <c r="K1456">
         <v>1457</v>
@@ -74728,7 +74782,7 @@
         <v>854</v>
       </c>
       <c r="N1456" t="s">
-        <v>4196</v>
+        <v>4194</v>
       </c>
     </row>
     <row r="1457" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74739,13 +74793,13 @@
         <v>1003218</v>
       </c>
       <c r="C1457" t="s">
-        <v>4190</v>
+        <v>4188</v>
       </c>
       <c r="D1457" t="s">
         <v>604</v>
       </c>
       <c r="E1457" t="s">
-        <v>4191</v>
+        <v>4189</v>
       </c>
       <c r="F1457" s="29">
         <v>46145</v>
@@ -74753,14 +74807,14 @@
       <c r="G1457" s="56">
         <v>2.9976851851851852E-2</v>
       </c>
-      <c r="H1457" s="162" t="s">
+      <c r="H1457" s="161" t="s">
         <v>805</v>
       </c>
-      <c r="I1457" s="162" t="s">
+      <c r="I1457" s="161" t="s">
         <v>806</v>
       </c>
       <c r="J1457" s="63" t="s">
-        <v>4187</v>
+        <v>4185</v>
       </c>
       <c r="K1457">
         <v>1458</v>
@@ -74769,7 +74823,7 @@
         <v>854</v>
       </c>
       <c r="N1457" t="s">
-        <v>4197</v>
+        <v>4195</v>
       </c>
     </row>
     <row r="1458" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74794,14 +74848,14 @@
       <c r="G1458" s="56">
         <v>0.17938657407407407</v>
       </c>
-      <c r="H1458" s="162" t="s">
+      <c r="H1458" s="161" t="s">
         <v>817</v>
       </c>
-      <c r="I1458" s="162" t="s">
+      <c r="I1458" s="161" t="s">
         <v>806</v>
       </c>
       <c r="J1458" s="63" t="s">
-        <v>4188</v>
+        <v>4186</v>
       </c>
       <c r="K1458">
         <v>1459</v>
@@ -74810,7 +74864,7 @@
         <v>854</v>
       </c>
       <c r="N1458" t="s">
-        <v>4198</v>
+        <v>4196</v>
       </c>
     </row>
     <row r="1459" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74821,7 +74875,7 @@
         <v>10745119</v>
       </c>
       <c r="C1459" t="s">
-        <v>4166</v>
+        <v>4164</v>
       </c>
       <c r="D1459" t="s">
         <v>3717</v>
@@ -74835,14 +74889,14 @@
       <c r="G1459" s="56">
         <v>5.2731481481481483E-2</v>
       </c>
-      <c r="H1459" s="162" t="s">
+      <c r="H1459" s="161" t="s">
         <v>2352</v>
       </c>
-      <c r="I1459" s="162" t="s">
+      <c r="I1459" s="161" t="s">
         <v>806</v>
       </c>
       <c r="J1459" s="63" t="s">
-        <v>4192</v>
+        <v>4190</v>
       </c>
       <c r="K1459">
         <v>1460</v>
@@ -74851,7 +74905,7 @@
         <v>854</v>
       </c>
       <c r="N1459" t="s">
-        <v>4199</v>
+        <v>4197</v>
       </c>
     </row>
     <row r="1460" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74876,14 +74930,14 @@
       <c r="G1460" s="56">
         <v>0.23512731481481483</v>
       </c>
-      <c r="H1460" s="162" t="s">
+      <c r="H1460" s="161" t="s">
         <v>825</v>
       </c>
-      <c r="I1460" s="162" t="s">
+      <c r="I1460" s="161" t="s">
         <v>806</v>
       </c>
       <c r="J1460" s="63" t="s">
-        <v>4193</v>
+        <v>4191</v>
       </c>
       <c r="K1460">
         <v>1461</v>
@@ -74892,7 +74946,7 @@
         <v>854</v>
       </c>
       <c r="N1460" t="s">
-        <v>4200</v>
+        <v>4198</v>
       </c>
     </row>
     <row r="1461" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74917,14 +74971,14 @@
       <c r="G1461" s="56">
         <v>0.22863425925925926</v>
       </c>
-      <c r="H1461" s="163" t="s">
+      <c r="H1461" s="162" t="s">
         <v>885</v>
       </c>
-      <c r="I1461" s="163" t="s">
+      <c r="I1461" s="162" t="s">
         <v>806</v>
       </c>
       <c r="J1461" s="63" t="s">
-        <v>4203</v>
+        <v>4201</v>
       </c>
       <c r="K1461">
         <v>1462</v>
@@ -74933,7 +74987,7 @@
         <v>854</v>
       </c>
       <c r="N1461" t="s">
-        <v>4221</v>
+        <v>4219</v>
       </c>
     </row>
     <row r="1462" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74944,13 +74998,13 @@
         <v>8318208</v>
       </c>
       <c r="C1462" t="s">
-        <v>4190</v>
+        <v>4188</v>
       </c>
       <c r="D1462" t="s">
         <v>424</v>
       </c>
       <c r="E1462" t="s">
-        <v>4191</v>
+        <v>4189</v>
       </c>
       <c r="F1462" s="29">
         <v>46146</v>
@@ -74958,14 +75012,14 @@
       <c r="G1462" s="56">
         <v>9.2615740740740748E-2</v>
       </c>
-      <c r="H1462" s="163" t="s">
-        <v>4205</v>
-      </c>
-      <c r="I1462" s="163" t="s">
+      <c r="H1462" s="162" t="s">
+        <v>4203</v>
+      </c>
+      <c r="I1462" s="162" t="s">
         <v>806</v>
       </c>
       <c r="J1462" s="63" t="s">
-        <v>4204</v>
+        <v>4202</v>
       </c>
       <c r="K1462">
         <v>1463</v>
@@ -74974,7 +75028,7 @@
         <v>854</v>
       </c>
       <c r="N1462" t="s">
-        <v>4222</v>
+        <v>4220</v>
       </c>
     </row>
     <row r="1463" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -74985,13 +75039,13 @@
         <v>14457611</v>
       </c>
       <c r="C1463" t="s">
-        <v>4206</v>
+        <v>4204</v>
       </c>
       <c r="D1463" t="s">
         <v>424</v>
       </c>
       <c r="E1463" t="s">
-        <v>720</v>
+        <v>1583</v>
       </c>
       <c r="F1463" s="29">
         <v>46145</v>
@@ -74999,14 +75053,14 @@
       <c r="G1463" s="56">
         <v>7.8599537037037037E-2</v>
       </c>
-      <c r="H1463" s="163" t="s">
+      <c r="H1463" s="162" t="s">
         <v>815</v>
       </c>
-      <c r="I1463" s="163" t="s">
+      <c r="I1463" s="162" t="s">
         <v>806</v>
       </c>
       <c r="J1463" s="63" t="s">
-        <v>4207</v>
+        <v>4205</v>
       </c>
       <c r="K1463">
         <v>1464</v>
@@ -75015,7 +75069,7 @@
         <v>854</v>
       </c>
       <c r="N1463" t="s">
-        <v>4223</v>
+        <v>4221</v>
       </c>
     </row>
     <row r="1464" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -75040,14 +75094,14 @@
       <c r="G1464" s="56">
         <v>0.14760416666666668</v>
       </c>
-      <c r="H1464" s="163" t="s">
-        <v>4100</v>
-      </c>
-      <c r="I1464" s="163" t="s">
+      <c r="H1464" s="162" t="s">
+        <v>4098</v>
+      </c>
+      <c r="I1464" s="162" t="s">
         <v>806</v>
       </c>
       <c r="J1464" s="63" t="s">
-        <v>4208</v>
+        <v>4206</v>
       </c>
       <c r="K1464">
         <v>1465</v>
@@ -75056,7 +75110,7 @@
         <v>854</v>
       </c>
       <c r="N1464" t="s">
-        <v>4224</v>
+        <v>4222</v>
       </c>
     </row>
     <row r="1465" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -75081,14 +75135,14 @@
       <c r="G1465" s="56">
         <v>6.3842592592592604E-2</v>
       </c>
-      <c r="H1465" s="163" t="s">
-        <v>4210</v>
-      </c>
-      <c r="I1465" s="163" t="s">
+      <c r="H1465" s="162" t="s">
+        <v>4208</v>
+      </c>
+      <c r="I1465" s="162" t="s">
         <v>806</v>
       </c>
       <c r="J1465" s="63" t="s">
-        <v>4209</v>
+        <v>4207</v>
       </c>
       <c r="K1465">
         <v>1466</v>
@@ -75097,7 +75151,7 @@
         <v>854</v>
       </c>
       <c r="N1465" t="s">
-        <v>4225</v>
+        <v>4223</v>
       </c>
     </row>
     <row r="1466" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -75108,13 +75162,13 @@
         <v>24870000</v>
       </c>
       <c r="C1466" t="s">
-        <v>4211</v>
+        <v>4209</v>
       </c>
       <c r="D1466" t="s">
         <v>424</v>
       </c>
       <c r="E1466" t="s">
-        <v>4212</v>
+        <v>4210</v>
       </c>
       <c r="F1466" s="29">
         <v>46145</v>
@@ -75122,14 +75176,14 @@
       <c r="G1466" s="56" t="s">
         <v>502</v>
       </c>
-      <c r="H1466" s="163" t="s">
+      <c r="H1466" s="162" t="s">
         <v>502</v>
       </c>
-      <c r="I1466" s="163" t="s">
+      <c r="I1466" s="162" t="s">
         <v>806</v>
       </c>
       <c r="J1466" s="63" t="s">
-        <v>4213</v>
+        <v>4211</v>
       </c>
       <c r="K1466">
         <v>1467</v>
@@ -75138,7 +75192,7 @@
         <v>854</v>
       </c>
       <c r="N1466" t="s">
-        <v>4226</v>
+        <v>4224</v>
       </c>
     </row>
     <row r="1467" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -75149,7 +75203,7 @@
         <v>14722092</v>
       </c>
       <c r="C1467" t="s">
-        <v>4166</v>
+        <v>4164</v>
       </c>
       <c r="D1467" t="s">
         <v>3717</v>
@@ -75163,14 +75217,14 @@
       <c r="G1467" s="56">
         <v>9.780092592592593E-2</v>
       </c>
-      <c r="H1467" s="163" t="s">
+      <c r="H1467" s="162" t="s">
         <v>885</v>
       </c>
-      <c r="I1467" s="163" t="s">
+      <c r="I1467" s="162" t="s">
         <v>806</v>
       </c>
       <c r="J1467" s="63" t="s">
-        <v>4214</v>
+        <v>4212</v>
       </c>
       <c r="K1467">
         <v>1468</v>
@@ -75179,7 +75233,7 @@
         <v>854</v>
       </c>
       <c r="N1467" t="s">
-        <v>4227</v>
+        <v>4225</v>
       </c>
     </row>
     <row r="1468" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -75193,7 +75247,7 @@
         <v>17</v>
       </c>
       <c r="D1468" t="s">
-        <v>4169</v>
+        <v>4167</v>
       </c>
       <c r="E1468" t="s">
         <v>18</v>
@@ -75204,14 +75258,14 @@
       <c r="G1468" s="56">
         <v>0.15199074074074073</v>
       </c>
-      <c r="H1468" s="163" t="s">
-        <v>4216</v>
-      </c>
-      <c r="I1468" s="163" t="s">
+      <c r="H1468" s="162" t="s">
+        <v>4214</v>
+      </c>
+      <c r="I1468" s="162" t="s">
         <v>806</v>
       </c>
       <c r="J1468" s="63" t="s">
-        <v>4215</v>
+        <v>4213</v>
       </c>
       <c r="K1468">
         <v>1469</v>
@@ -75220,7 +75274,7 @@
         <v>854</v>
       </c>
       <c r="N1468" t="s">
-        <v>4228</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="1469" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -75231,7 +75285,7 @@
         <v>24456625</v>
       </c>
       <c r="C1469" t="s">
-        <v>4166</v>
+        <v>4164</v>
       </c>
       <c r="D1469" t="s">
         <v>3717</v>
@@ -75245,14 +75299,14 @@
       <c r="G1469" s="56">
         <v>0.19692129629629629</v>
       </c>
-      <c r="H1469" s="163" t="s">
+      <c r="H1469" s="162" t="s">
         <v>942</v>
       </c>
-      <c r="I1469" s="163" t="s">
+      <c r="I1469" s="162" t="s">
         <v>806</v>
       </c>
       <c r="J1469" s="63" t="s">
-        <v>4217</v>
+        <v>4215</v>
       </c>
       <c r="K1469">
         <v>1470</v>
@@ -75261,7 +75315,7 @@
         <v>854</v>
       </c>
       <c r="N1469" t="s">
-        <v>4229</v>
+        <v>4227</v>
       </c>
     </row>
     <row r="1470" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -75286,14 +75340,14 @@
       <c r="G1470" s="56">
         <v>0.22931712962962961</v>
       </c>
-      <c r="H1470" s="163" t="s">
+      <c r="H1470" s="162" t="s">
         <v>885</v>
       </c>
-      <c r="I1470" s="163" t="s">
+      <c r="I1470" s="162" t="s">
         <v>806</v>
       </c>
       <c r="J1470" s="63" t="s">
-        <v>4218</v>
+        <v>4216</v>
       </c>
       <c r="K1470">
         <v>1471</v>
@@ -75302,7 +75356,7 @@
         <v>854</v>
       </c>
       <c r="N1470" t="s">
-        <v>4230</v>
+        <v>4228</v>
       </c>
     </row>
     <row r="1471" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -75327,14 +75381,14 @@
       <c r="G1471" s="56">
         <v>7.5613425925925917E-2</v>
       </c>
-      <c r="H1471" s="163" t="s">
+      <c r="H1471" s="162" t="s">
         <v>811</v>
       </c>
-      <c r="I1471" s="163" t="s">
+      <c r="I1471" s="162" t="s">
         <v>806</v>
       </c>
       <c r="J1471" s="63" t="s">
-        <v>4219</v>
+        <v>4217</v>
       </c>
       <c r="K1471">
         <v>1472</v>
@@ -75343,7 +75397,7 @@
         <v>854</v>
       </c>
       <c r="N1471" t="s">
-        <v>4231</v>
+        <v>4229</v>
       </c>
     </row>
     <row r="1472" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -75368,14 +75422,14 @@
       <c r="G1472" s="56">
         <v>0.23133101851851853</v>
       </c>
-      <c r="H1472" s="163" t="s">
+      <c r="H1472" s="162" t="s">
         <v>2415</v>
       </c>
-      <c r="I1472" s="163" t="s">
+      <c r="I1472" s="162" t="s">
         <v>806</v>
       </c>
       <c r="J1472" s="63" t="s">
-        <v>4220</v>
+        <v>4218</v>
       </c>
       <c r="K1472">
         <v>1473</v>
@@ -75384,7 +75438,7 @@
         <v>854</v>
       </c>
       <c r="N1472" t="s">
-        <v>4232</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="1473" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -75398,7 +75452,7 @@
         <v>440</v>
       </c>
       <c r="D1473" t="s">
-        <v>4233</v>
+        <v>4231</v>
       </c>
       <c r="E1473" t="s">
         <v>433</v>
@@ -75409,14 +75463,14 @@
       <c r="G1473" s="56">
         <v>0.17630787037037035</v>
       </c>
-      <c r="H1473" s="164" t="s">
-        <v>4234</v>
-      </c>
-      <c r="I1473" s="164" t="s">
+      <c r="H1473" s="163" t="s">
+        <v>4232</v>
+      </c>
+      <c r="I1473" s="163" t="s">
         <v>290</v>
       </c>
       <c r="J1473" s="63" t="s">
-        <v>4235</v>
+        <v>4233</v>
       </c>
       <c r="K1473">
         <v>1474</v>
@@ -75425,7 +75479,7 @@
         <v>854</v>
       </c>
       <c r="N1473" t="s">
-        <v>4249</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="1474" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -75439,7 +75493,7 @@
         <v>25</v>
       </c>
       <c r="D1474" t="s">
-        <v>4236</v>
+        <v>4234</v>
       </c>
       <c r="E1474" t="s">
         <v>157</v>
@@ -75450,14 +75504,14 @@
       <c r="G1474" s="56">
         <v>6.5173611111111113E-2</v>
       </c>
-      <c r="H1474" s="164" t="s">
-        <v>4237</v>
-      </c>
-      <c r="I1474" s="164" t="s">
+      <c r="H1474" s="163" t="s">
+        <v>4235</v>
+      </c>
+      <c r="I1474" s="163" t="s">
         <v>290</v>
       </c>
       <c r="J1474" s="63" t="s">
-        <v>4238</v>
+        <v>4236</v>
       </c>
       <c r="K1474">
         <v>1475</v>
@@ -75466,7 +75520,7 @@
         <v>854</v>
       </c>
       <c r="N1474" t="s">
-        <v>4250</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="1475" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -75491,14 +75545,14 @@
       <c r="G1475" s="56">
         <v>8.324074074074074E-2</v>
       </c>
-      <c r="H1475" s="164" t="s">
+      <c r="H1475" s="163" t="s">
         <v>885</v>
       </c>
-      <c r="I1475" s="164" t="s">
+      <c r="I1475" s="163" t="s">
         <v>290</v>
       </c>
       <c r="J1475" s="63" t="s">
-        <v>4239</v>
+        <v>4237</v>
       </c>
       <c r="K1475">
         <v>1476</v>
@@ -75507,7 +75561,7 @@
         <v>854</v>
       </c>
       <c r="N1475" t="s">
-        <v>4251</v>
+        <v>4249</v>
       </c>
     </row>
     <row r="1476" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -75532,14 +75586,14 @@
       <c r="G1476" s="56">
         <v>0.10398148148148149</v>
       </c>
-      <c r="H1476" s="164" t="s">
+      <c r="H1476" s="163" t="s">
         <v>825</v>
       </c>
-      <c r="I1476" s="164" t="s">
+      <c r="I1476" s="163" t="s">
         <v>290</v>
       </c>
       <c r="J1476" s="63" t="s">
-        <v>4240</v>
+        <v>4238</v>
       </c>
       <c r="K1476">
         <v>1477</v>
@@ -75548,7 +75602,7 @@
         <v>854</v>
       </c>
       <c r="N1476" t="s">
-        <v>4252</v>
+        <v>4250</v>
       </c>
     </row>
     <row r="1477" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -75573,14 +75627,14 @@
       <c r="G1477" s="56">
         <v>5.4988425925925927E-2</v>
       </c>
-      <c r="H1477" s="164" t="s">
+      <c r="H1477" s="163" t="s">
         <v>2459</v>
       </c>
-      <c r="I1477" s="164" t="s">
+      <c r="I1477" s="163" t="s">
         <v>290</v>
       </c>
       <c r="J1477" s="63" t="s">
-        <v>4241</v>
+        <v>4239</v>
       </c>
       <c r="K1477">
         <v>1478</v>
@@ -75589,7 +75643,7 @@
         <v>854</v>
       </c>
       <c r="N1477" t="s">
-        <v>4253</v>
+        <v>4251</v>
       </c>
     </row>
     <row r="1478" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -75614,14 +75668,14 @@
       <c r="G1478" s="56">
         <v>7.0983796296296295E-2</v>
       </c>
-      <c r="H1478" s="164" t="s">
+      <c r="H1478" s="163" t="s">
         <v>885</v>
       </c>
-      <c r="I1478" s="164" t="s">
+      <c r="I1478" s="163" t="s">
         <v>290</v>
       </c>
       <c r="J1478" s="63" t="s">
-        <v>4242</v>
+        <v>4240</v>
       </c>
       <c r="K1478">
         <v>1479</v>
@@ -75630,7 +75684,7 @@
         <v>854</v>
       </c>
       <c r="N1478" t="s">
-        <v>4254</v>
+        <v>4252</v>
       </c>
     </row>
     <row r="1479" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -75641,7 +75695,7 @@
         <v>11030705</v>
       </c>
       <c r="C1479" t="s">
-        <v>4245</v>
+        <v>4243</v>
       </c>
       <c r="D1479" t="s">
         <v>54</v>
@@ -75655,14 +75709,14 @@
       <c r="G1479" s="56">
         <v>7.9837962962962958E-2</v>
       </c>
-      <c r="H1479" s="164" t="s">
+      <c r="H1479" s="163" t="s">
         <v>825</v>
       </c>
-      <c r="I1479" s="164" t="s">
+      <c r="I1479" s="163" t="s">
         <v>806</v>
       </c>
       <c r="J1479" s="63" t="s">
-        <v>4243</v>
+        <v>4241</v>
       </c>
       <c r="K1479">
         <v>1480</v>
@@ -75671,7 +75725,7 @@
         <v>854</v>
       </c>
       <c r="N1479" t="s">
-        <v>4255</v>
+        <v>4253</v>
       </c>
     </row>
     <row r="1480" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -75688,7 +75742,7 @@
         <v>372</v>
       </c>
       <c r="E1480" t="s">
-        <v>720</v>
+        <v>1583</v>
       </c>
       <c r="F1480" s="29">
         <v>46151</v>
@@ -75696,14 +75750,14 @@
       <c r="G1480" s="56">
         <v>5.0868055555555548E-2</v>
       </c>
-      <c r="H1480" s="164" t="s">
-        <v>4248</v>
-      </c>
-      <c r="I1480" s="164" t="s">
+      <c r="H1480" s="163" t="s">
+        <v>4246</v>
+      </c>
+      <c r="I1480" s="163" t="s">
         <v>290</v>
       </c>
       <c r="J1480" s="63" t="s">
-        <v>4244</v>
+        <v>4242</v>
       </c>
       <c r="K1480">
         <v>1481</v>
@@ -75712,7 +75766,7 @@
         <v>854</v>
       </c>
       <c r="N1480" t="s">
-        <v>4256</v>
+        <v>4254</v>
       </c>
     </row>
     <row r="1481" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -75726,7 +75780,7 @@
         <v>440</v>
       </c>
       <c r="D1481" t="s">
-        <v>4257</v>
+        <v>4255</v>
       </c>
       <c r="E1481" t="s">
         <v>433</v>
@@ -75737,14 +75791,14 @@
       <c r="G1481" s="56">
         <v>5.2627314814814814E-2</v>
       </c>
-      <c r="H1481" s="164" t="s">
-        <v>4258</v>
-      </c>
-      <c r="I1481" s="164" t="s">
+      <c r="H1481" s="163" t="s">
+        <v>4256</v>
+      </c>
+      <c r="I1481" s="163" t="s">
         <v>290</v>
       </c>
       <c r="J1481" s="63" t="s">
-        <v>4246</v>
+        <v>4244</v>
       </c>
       <c r="K1481">
         <v>1482</v>
@@ -75753,7 +75807,7 @@
         <v>854</v>
       </c>
       <c r="N1481" t="s">
-        <v>4261</v>
+        <v>4259</v>
       </c>
     </row>
     <row r="1482" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -75767,7 +75821,7 @@
         <v>440</v>
       </c>
       <c r="D1482" t="s">
-        <v>4259</v>
+        <v>4257</v>
       </c>
       <c r="E1482" t="s">
         <v>433</v>
@@ -75778,14 +75832,14 @@
       <c r="G1482" s="56">
         <v>9.0185185185185188E-2</v>
       </c>
-      <c r="H1482" s="164" t="s">
+      <c r="H1482" s="163" t="s">
         <v>805</v>
       </c>
-      <c r="I1482" s="164" t="s">
+      <c r="I1482" s="163" t="s">
         <v>290</v>
       </c>
       <c r="J1482" s="63" t="s">
-        <v>4247</v>
+        <v>4245</v>
       </c>
       <c r="K1482">
         <v>1483</v>
@@ -75794,7 +75848,7 @@
         <v>854</v>
       </c>
       <c r="N1482" t="s">
-        <v>4262</v>
+        <v>4260</v>
       </c>
     </row>
     <row r="1483" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -75805,13 +75859,13 @@
         <v>10099082</v>
       </c>
       <c r="C1483" t="s">
-        <v>4190</v>
+        <v>4188</v>
       </c>
       <c r="D1483" t="s">
         <v>333</v>
       </c>
       <c r="E1483" t="s">
-        <v>4191</v>
+        <v>4189</v>
       </c>
       <c r="F1483" s="29">
         <v>46151</v>
@@ -75819,14 +75873,14 @@
       <c r="G1483" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="H1483" s="164" t="s">
+      <c r="H1483" s="163" t="s">
         <v>837</v>
       </c>
-      <c r="I1483" s="164" t="s">
+      <c r="I1483" s="163" t="s">
         <v>290</v>
       </c>
       <c r="J1483" s="63" t="s">
-        <v>4260</v>
+        <v>4258</v>
       </c>
       <c r="K1483">
         <v>1484</v>
@@ -75835,7 +75889,7 @@
         <v>854</v>
       </c>
       <c r="N1483" t="s">
-        <v>4263</v>
+        <v>4261</v>
       </c>
     </row>
     <row r="1484" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -75846,10 +75900,10 @@
         <v>4039390</v>
       </c>
       <c r="C1484" t="s">
-        <v>4264</v>
+        <v>4262</v>
       </c>
       <c r="D1484" t="s">
-        <v>4265</v>
+        <v>4263</v>
       </c>
       <c r="E1484" t="s">
         <v>51</v>
@@ -75860,14 +75914,14 @@
       <c r="G1484" s="56">
         <v>4.0844907407407406E-2</v>
       </c>
-      <c r="H1484" s="164" t="s">
+      <c r="H1484" s="163" t="s">
         <v>885</v>
       </c>
-      <c r="I1484" s="164" t="s">
+      <c r="I1484" s="163" t="s">
         <v>290</v>
       </c>
       <c r="J1484" s="63" t="s">
-        <v>4266</v>
+        <v>4264</v>
       </c>
       <c r="K1484">
         <v>1485</v>
@@ -75876,7 +75930,7 @@
         <v>854</v>
       </c>
       <c r="N1484" t="s">
-        <v>4270</v>
+        <v>4268</v>
       </c>
     </row>
     <row r="1485" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -75901,14 +75955,14 @@
       <c r="G1485" s="56">
         <v>0.10276620370370371</v>
       </c>
-      <c r="H1485" s="164" t="s">
+      <c r="H1485" s="163" t="s">
         <v>1106</v>
       </c>
-      <c r="I1485" s="164" t="s">
+      <c r="I1485" s="163" t="s">
         <v>290</v>
       </c>
       <c r="J1485" s="63" t="s">
-        <v>4267</v>
+        <v>4265</v>
       </c>
       <c r="K1485">
         <v>1486</v>
@@ -75917,7 +75971,7 @@
         <v>854</v>
       </c>
       <c r="N1485" t="s">
-        <v>4271</v>
+        <v>4269</v>
       </c>
     </row>
     <row r="1486" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -75928,10 +75982,10 @@
         <v>15608673</v>
       </c>
       <c r="C1486" t="s">
-        <v>4264</v>
+        <v>4262</v>
       </c>
       <c r="D1486" t="s">
-        <v>4269</v>
+        <v>4267</v>
       </c>
       <c r="E1486" t="s">
         <v>51</v>
@@ -75942,14 +75996,14 @@
       <c r="G1486" s="56">
         <v>0.15770833333333334</v>
       </c>
-      <c r="H1486" s="164" t="s">
+      <c r="H1486" s="163" t="s">
         <v>885</v>
       </c>
-      <c r="I1486" s="164" t="s">
+      <c r="I1486" s="163" t="s">
         <v>290</v>
       </c>
       <c r="J1486" s="63" t="s">
-        <v>4268</v>
+        <v>4266</v>
       </c>
       <c r="K1486">
         <v>1487</v>
@@ -75958,7 +76012,7 @@
         <v>854</v>
       </c>
       <c r="N1486" t="s">
-        <v>4272</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="1487" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -75972,7 +76026,7 @@
         <v>440</v>
       </c>
       <c r="D1487" t="s">
-        <v>4273</v>
+        <v>4271</v>
       </c>
       <c r="E1487" t="s">
         <v>433</v>
@@ -75983,14 +76037,14 @@
       <c r="G1487" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="H1487" s="165" t="s">
+      <c r="H1487" s="164" t="s">
         <v>1313</v>
       </c>
-      <c r="I1487" s="165" t="s">
+      <c r="I1487" s="164" t="s">
         <v>290</v>
       </c>
       <c r="J1487" s="63" t="s">
-        <v>4274</v>
+        <v>4272</v>
       </c>
       <c r="K1487">
         <v>1488</v>
@@ -75999,7 +76053,7 @@
         <v>854</v>
       </c>
       <c r="N1487" t="s">
-        <v>4284</v>
+        <v>4282</v>
       </c>
     </row>
     <row r="1488" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -76024,14 +76078,14 @@
       <c r="G1488" s="56">
         <v>3.3692129629629627E-2</v>
       </c>
-      <c r="H1488" s="165" t="s">
+      <c r="H1488" s="164" t="s">
         <v>1107</v>
       </c>
-      <c r="I1488" s="165" t="s">
+      <c r="I1488" s="164" t="s">
         <v>290</v>
       </c>
       <c r="J1488" s="63" t="s">
-        <v>4275</v>
+        <v>4273</v>
       </c>
       <c r="K1488">
         <v>1489</v>
@@ -76040,7 +76094,7 @@
         <v>854</v>
       </c>
       <c r="N1488" t="s">
-        <v>4285</v>
+        <v>4283</v>
       </c>
     </row>
     <row r="1489" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -76065,14 +76119,14 @@
       <c r="G1489" s="56">
         <v>0.1155324074074074</v>
       </c>
-      <c r="H1489" s="165" t="s">
+      <c r="H1489" s="164" t="s">
         <v>832</v>
       </c>
-      <c r="I1489" s="165" t="s">
+      <c r="I1489" s="164" t="s">
         <v>290</v>
       </c>
       <c r="J1489" s="63" t="s">
-        <v>4276</v>
+        <v>4274</v>
       </c>
       <c r="K1489">
         <v>1490</v>
@@ -76081,7 +76135,7 @@
         <v>854</v>
       </c>
       <c r="N1489" t="s">
-        <v>4286</v>
+        <v>4284</v>
       </c>
     </row>
     <row r="1490" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -76106,14 +76160,14 @@
       <c r="G1490" s="56">
         <v>0.16002314814814814</v>
       </c>
-      <c r="H1490" s="165" t="s">
+      <c r="H1490" s="164" t="s">
         <v>815</v>
       </c>
-      <c r="I1490" s="165" t="s">
+      <c r="I1490" s="164" t="s">
         <v>290</v>
       </c>
       <c r="J1490" s="63" t="s">
-        <v>4277</v>
+        <v>4275</v>
       </c>
       <c r="K1490">
         <v>1491</v>
@@ -76122,7 +76176,7 @@
         <v>854</v>
       </c>
       <c r="N1490" t="s">
-        <v>4287</v>
+        <v>4285</v>
       </c>
     </row>
     <row r="1491" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -76139,7 +76193,7 @@
         <v>703</v>
       </c>
       <c r="E1491" t="s">
-        <v>720</v>
+        <v>1583</v>
       </c>
       <c r="F1491" s="29">
         <v>46152</v>
@@ -76147,14 +76201,14 @@
       <c r="G1491" s="56">
         <v>0.10849537037037038</v>
       </c>
-      <c r="H1491" s="165" t="s">
+      <c r="H1491" s="164" t="s">
         <v>815</v>
       </c>
-      <c r="I1491" s="165" t="s">
+      <c r="I1491" s="164" t="s">
         <v>290</v>
       </c>
       <c r="J1491" s="63" t="s">
-        <v>4278</v>
+        <v>4276</v>
       </c>
       <c r="K1491">
         <v>1492</v>
@@ -76163,7 +76217,7 @@
         <v>854</v>
       </c>
       <c r="N1491" t="s">
-        <v>4288</v>
+        <v>4286</v>
       </c>
     </row>
     <row r="1492" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -76174,7 +76228,7 @@
         <v>33109588</v>
       </c>
       <c r="C1492" t="s">
-        <v>4279</v>
+        <v>4277</v>
       </c>
       <c r="D1492" t="s">
         <v>319</v>
@@ -76188,26 +76242,26 @@
       <c r="G1492" s="56">
         <v>0.29434027777777777</v>
       </c>
-      <c r="H1492" s="165" t="s">
+      <c r="H1492" s="164" t="s">
         <v>1107</v>
       </c>
-      <c r="I1492" s="165" t="s">
+      <c r="I1492" s="164" t="s">
         <v>290</v>
       </c>
       <c r="J1492" s="63" t="s">
-        <v>4280</v>
+        <v>4278</v>
       </c>
       <c r="K1492">
         <v>1493</v>
       </c>
       <c r="L1492" t="s">
-        <v>4300</v>
+        <v>4298</v>
       </c>
       <c r="M1492" s="57" t="s">
         <v>854</v>
       </c>
       <c r="N1492" t="s">
-        <v>4289</v>
+        <v>4287</v>
       </c>
     </row>
     <row r="1493" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -76232,14 +76286,14 @@
       <c r="G1493" s="56">
         <v>8.2199074074074077E-2</v>
       </c>
-      <c r="H1493" s="165" t="s">
+      <c r="H1493" s="164" t="s">
         <v>2415</v>
       </c>
-      <c r="I1493" s="165" t="s">
+      <c r="I1493" s="164" t="s">
         <v>290</v>
       </c>
       <c r="J1493" s="63" t="s">
-        <v>4281</v>
+        <v>4279</v>
       </c>
       <c r="K1493">
         <v>1494</v>
@@ -76248,7 +76302,7 @@
         <v>854</v>
       </c>
       <c r="N1493" t="s">
-        <v>4290</v>
+        <v>4288</v>
       </c>
     </row>
     <row r="1494" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -76262,7 +76316,7 @@
         <v>440</v>
       </c>
       <c r="D1494" t="s">
-        <v>4283</v>
+        <v>4281</v>
       </c>
       <c r="E1494" t="s">
         <v>433</v>
@@ -76273,14 +76327,14 @@
       <c r="G1494" s="56">
         <v>0.14137731481481483</v>
       </c>
-      <c r="H1494" s="165" t="s">
+      <c r="H1494" s="164" t="s">
         <v>885</v>
       </c>
-      <c r="I1494" s="165" t="s">
+      <c r="I1494" s="164" t="s">
         <v>290</v>
       </c>
       <c r="J1494" s="63" t="s">
-        <v>4282</v>
+        <v>4280</v>
       </c>
       <c r="K1494">
         <v>1495</v>
@@ -76289,7 +76343,7 @@
         <v>854</v>
       </c>
       <c r="N1494" t="s">
-        <v>4291</v>
+        <v>4289</v>
       </c>
     </row>
     <row r="1495" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -76314,26 +76368,26 @@
       <c r="G1495" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="H1495" s="166" t="s">
-        <v>4292</v>
-      </c>
-      <c r="I1495" s="166" t="s">
+      <c r="H1495" s="165" t="s">
+        <v>4290</v>
+      </c>
+      <c r="I1495" s="165" t="s">
         <v>806</v>
       </c>
       <c r="J1495" s="63" t="s">
-        <v>4293</v>
+        <v>4291</v>
       </c>
       <c r="K1495">
         <v>1496</v>
       </c>
       <c r="L1495" t="s">
-        <v>4301</v>
+        <v>4299</v>
       </c>
       <c r="M1495" s="57" t="s">
         <v>854</v>
       </c>
       <c r="N1495" t="s">
-        <v>4302</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="1496" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -76347,7 +76401,7 @@
         <v>2452</v>
       </c>
       <c r="D1496" t="s">
-        <v>4295</v>
+        <v>4293</v>
       </c>
       <c r="E1496" t="s">
         <v>29</v>
@@ -76358,14 +76412,14 @@
       <c r="G1496" s="56">
         <v>6.6805555555555562E-2</v>
       </c>
-      <c r="H1496" s="166" t="s">
+      <c r="H1496" s="165" t="s">
         <v>1522</v>
       </c>
-      <c r="I1496" s="166" t="s">
+      <c r="I1496" s="165" t="s">
         <v>806</v>
       </c>
       <c r="J1496" s="63" t="s">
-        <v>4294</v>
+        <v>4292</v>
       </c>
       <c r="K1496">
         <v>1497</v>
@@ -76374,7 +76428,7 @@
         <v>854</v>
       </c>
       <c r="N1496" t="s">
-        <v>4303</v>
+        <v>4301</v>
       </c>
     </row>
     <row r="1497" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -76385,13 +76439,13 @@
         <v>14803590</v>
       </c>
       <c r="C1497" t="s">
-        <v>4190</v>
+        <v>4188</v>
       </c>
       <c r="D1497" t="s">
         <v>424</v>
       </c>
       <c r="E1497" t="s">
-        <v>4191</v>
+        <v>4189</v>
       </c>
       <c r="F1497" s="29">
         <v>46154</v>
@@ -76399,14 +76453,14 @@
       <c r="G1497" s="56">
         <v>9.9641203703703704E-2</v>
       </c>
-      <c r="H1497" s="166" t="s">
+      <c r="H1497" s="165" t="s">
         <v>1239</v>
       </c>
-      <c r="I1497" s="166" t="s">
+      <c r="I1497" s="165" t="s">
         <v>806</v>
       </c>
       <c r="J1497" s="63" t="s">
-        <v>4296</v>
+        <v>4294</v>
       </c>
       <c r="K1497">
         <v>1498</v>
@@ -76415,7 +76469,7 @@
         <v>854</v>
       </c>
       <c r="N1497" t="s">
-        <v>4304</v>
+        <v>4302</v>
       </c>
     </row>
     <row r="1498" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -76440,14 +76494,14 @@
       <c r="G1498" s="56">
         <v>7.8333333333333324E-2</v>
       </c>
-      <c r="H1498" s="166" t="s">
-        <v>4297</v>
-      </c>
-      <c r="I1498" s="166" t="s">
+      <c r="H1498" s="165" t="s">
+        <v>4295</v>
+      </c>
+      <c r="I1498" s="165" t="s">
         <v>806</v>
       </c>
       <c r="J1498" s="63" t="s">
-        <v>4298</v>
+        <v>4296</v>
       </c>
       <c r="K1498">
         <v>1499</v>
@@ -76456,7 +76510,7 @@
         <v>854</v>
       </c>
       <c r="N1498" t="s">
-        <v>4305</v>
+        <v>4303</v>
       </c>
     </row>
     <row r="1499" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -76481,26 +76535,26 @@
       <c r="G1499" s="56">
         <v>7.615740740740741E-2</v>
       </c>
-      <c r="H1499" s="166" t="s">
+      <c r="H1499" s="165" t="s">
         <v>830</v>
       </c>
-      <c r="I1499" s="166" t="s">
+      <c r="I1499" s="165" t="s">
         <v>806</v>
       </c>
       <c r="J1499" s="63" t="s">
-        <v>4299</v>
+        <v>4297</v>
       </c>
       <c r="K1499">
         <v>1500</v>
       </c>
       <c r="L1499" t="s">
-        <v>4306</v>
+        <v>4304</v>
       </c>
       <c r="M1499" s="57" t="s">
         <v>854</v>
       </c>
       <c r="N1499" t="s">
-        <v>4307</v>
+        <v>4305</v>
       </c>
     </row>
     <row r="1500" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -76525,14 +76579,14 @@
       <c r="G1500" s="56">
         <v>5.5740740740740737E-2</v>
       </c>
-      <c r="H1500" s="167" t="s">
+      <c r="H1500" s="166" t="s">
         <v>885</v>
       </c>
-      <c r="I1500" s="167" t="s">
+      <c r="I1500" s="166" t="s">
         <v>806</v>
       </c>
       <c r="J1500" s="63" t="s">
-        <v>4308</v>
+        <v>4306</v>
       </c>
       <c r="K1500">
         <v>1501</v>
@@ -76541,7 +76595,7 @@
         <v>854</v>
       </c>
       <c r="N1500" t="s">
-        <v>4311</v>
+        <v>4309</v>
       </c>
     </row>
     <row r="1501" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -76566,14 +76620,14 @@
       <c r="G1501" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="H1501" s="167" t="s">
+      <c r="H1501" s="166" t="s">
         <v>1313</v>
       </c>
-      <c r="I1501" s="167" t="s">
+      <c r="I1501" s="166" t="s">
         <v>806</v>
       </c>
       <c r="J1501" s="63" t="s">
-        <v>4309</v>
+        <v>4307</v>
       </c>
       <c r="K1501">
         <v>1502</v>
@@ -76582,7 +76636,7 @@
         <v>854</v>
       </c>
       <c r="N1501" t="s">
-        <v>4312</v>
+        <v>4310</v>
       </c>
     </row>
     <row r="1502" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -76607,14 +76661,14 @@
       <c r="G1502" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="H1502" s="167" t="s">
+      <c r="H1502" s="166" t="s">
         <v>1313</v>
       </c>
-      <c r="I1502" s="167" t="s">
+      <c r="I1502" s="166" t="s">
         <v>806</v>
       </c>
       <c r="J1502" s="63" t="s">
-        <v>4310</v>
+        <v>4308</v>
       </c>
       <c r="K1502">
         <v>1503</v>
@@ -76623,22 +76677,266 @@
         <v>854</v>
       </c>
       <c r="N1502" t="s">
-        <v>4313</v>
+        <v>4311</v>
       </c>
     </row>
     <row r="1503" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1503">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="B1503" s="7">
+        <v>4860394</v>
+      </c>
+      <c r="C1503" t="s">
+        <v>720</v>
+      </c>
+      <c r="D1503" t="s">
+        <v>372</v>
+      </c>
+      <c r="E1503" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F1503" s="29">
+        <v>46156</v>
+      </c>
+      <c r="G1503" s="56">
+        <v>4.8194444444444449E-2</v>
+      </c>
+      <c r="H1503" s="167" t="s">
+        <v>4312</v>
+      </c>
+      <c r="I1503" s="167" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1503" s="63" t="s">
+        <v>4313</v>
+      </c>
+      <c r="K1503">
+        <v>1504</v>
+      </c>
+      <c r="M1503" s="167" t="s">
+        <v>4323</v>
+      </c>
+      <c r="N1503" t="s">
+        <v>4324</v>
       </c>
     </row>
     <row r="1504" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1504">
-        <v>80</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="B1504" s="7">
+        <v>5738121</v>
+      </c>
+      <c r="C1504" t="s">
+        <v>720</v>
+      </c>
+      <c r="D1504" t="s">
+        <v>372</v>
+      </c>
+      <c r="E1504" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F1504" s="29">
+        <v>46157</v>
+      </c>
+      <c r="G1504" s="56">
+        <v>6.1261574074074072E-2</v>
+      </c>
+      <c r="H1504" s="167" t="s">
+        <v>4315</v>
+      </c>
+      <c r="I1504" s="167" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1504" s="63" t="s">
+        <v>4314</v>
+      </c>
+      <c r="K1504">
+        <v>1505</v>
+      </c>
+      <c r="M1504" s="167" t="s">
+        <v>4323</v>
+      </c>
+      <c r="N1504" t="s">
+        <v>4325</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1505">
+        <v>81</v>
+      </c>
+      <c r="B1505" s="7">
+        <v>6044359</v>
+      </c>
+      <c r="C1505" t="s">
+        <v>720</v>
+      </c>
+      <c r="D1505" t="s">
+        <v>372</v>
+      </c>
+      <c r="E1505" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F1505" s="29">
+        <v>46157</v>
+      </c>
+      <c r="G1505" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1505" s="167" t="s">
+        <v>817</v>
+      </c>
+      <c r="I1505" s="167" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1505" s="63" t="s">
+        <v>4316</v>
+      </c>
+      <c r="K1505">
+        <v>1506</v>
+      </c>
+      <c r="M1505" s="167" t="s">
+        <v>4323</v>
+      </c>
+      <c r="N1505" t="s">
+        <v>4326</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1506">
+        <v>81</v>
+      </c>
+      <c r="B1506" s="7">
+        <v>6251496</v>
+      </c>
+      <c r="C1506" t="s">
+        <v>720</v>
+      </c>
+      <c r="D1506" t="s">
+        <v>372</v>
+      </c>
+      <c r="E1506" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F1506" s="29">
+        <v>46159</v>
+      </c>
+      <c r="G1506" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1506" s="167" t="s">
+        <v>840</v>
+      </c>
+      <c r="I1506" s="167" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1506" s="63" t="s">
+        <v>4317</v>
+      </c>
+      <c r="K1506">
+        <v>1507</v>
+      </c>
+      <c r="L1506" t="s">
+        <v>4319</v>
+      </c>
+      <c r="M1506" s="167" t="s">
+        <v>4323</v>
+      </c>
+      <c r="N1506" t="s">
+        <v>4327</v>
+      </c>
+    </row>
+    <row r="1507" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1507">
+        <v>81</v>
+      </c>
+      <c r="B1507" s="7">
+        <v>12779605</v>
+      </c>
+      <c r="C1507" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1507" t="s">
+        <v>752</v>
+      </c>
+      <c r="E1507" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1507" s="29">
+        <v>46159</v>
+      </c>
+      <c r="G1507" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1507" s="167" t="s">
+        <v>4320</v>
+      </c>
+      <c r="I1507" s="167" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1507" s="63" t="s">
+        <v>4318</v>
+      </c>
+      <c r="K1507">
+        <v>1508</v>
+      </c>
+      <c r="M1507" s="167" t="s">
+        <v>4323</v>
+      </c>
+      <c r="N1507" t="s">
+        <v>4328</v>
+      </c>
+    </row>
+    <row r="1508" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1508">
+        <v>81</v>
+      </c>
+      <c r="B1508" s="7">
+        <v>11255886</v>
+      </c>
+      <c r="C1508" t="s">
+        <v>720</v>
+      </c>
+      <c r="D1508" t="s">
+        <v>424</v>
+      </c>
+      <c r="E1508" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F1508" s="29">
+        <v>46156</v>
+      </c>
+      <c r="G1508" s="56">
+        <v>6.5104166666666671E-2</v>
+      </c>
+      <c r="H1508" s="167" t="s">
+        <v>4321</v>
+      </c>
+      <c r="I1508" s="167" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1508" s="63" t="s">
+        <v>4322</v>
+      </c>
+      <c r="K1508">
+        <v>1509</v>
+      </c>
+      <c r="M1508" s="167" t="s">
+        <v>4323</v>
+      </c>
+      <c r="N1508" t="s">
+        <v>4329</v>
+      </c>
+    </row>
+    <row r="1509" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1509" s="7"/>
+      <c r="H1509" s="167"/>
+      <c r="I1509" s="167"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N1">
-    <sortState ref="A2:N1443">
+    <sortState ref="A2:N1508">
       <sortCondition ref="K1"/>
     </sortState>
   </autoFilter>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12497" uniqueCount="4332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12505" uniqueCount="4334">
   <si>
     <t>Ņ</t>
   </si>
@@ -12998,9 +12998,6 @@
     <t>Xl</t>
   </si>
   <si>
-    <t>[o]</t>
-  </si>
-  <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1505541001261879468/id_Xg.png?ex=6a0affd2&amp;is=6a09ae52&amp;hm=2ceb2cfbf799ee9af638dc4473c40df6684e495363067c7902399b8119a71ce2</t>
   </si>
   <si>
@@ -13023,6 +13020,15 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1471844339931021342/1505542228599111770/id_TU.png?ex=6a0b00f6&amp;is=6a09af76&amp;hm=b0074b701036d4ee99b045aae269549aee54e1dbf61e1bb6ab7d772d4f9aa545</t>
+  </si>
+  <si>
+    <t>Sty</t>
+  </si>
+  <si>
+    <t>Xm</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1506190698427322399/id_Xm.png?ex=6a0d5ce6&amp;is=6a0c0b66&amp;hm=de9b79cbeb6e0cc12596b8af4e0bf668f7fee85865f4a95c3b4d167d32983500</t>
   </si>
 </sst>
 </file>
@@ -13034,11 +13040,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="117" x14ac:knownFonts="1">
+  <fonts count="118" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -13886,118 +13899,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="168">
+  <cellXfs count="169">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="114" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="98" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="113" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="97" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="112" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="104" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="98" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="105" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="99" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="95" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="94" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="82" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="82" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="81" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="81" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="82" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="81" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="82" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="81" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="81" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="82" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="77" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="76" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="75" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="75" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="74" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="74" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14006,18 +14020,18 @@
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="57" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="57" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="51" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="52" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14031,14 +14045,14 @@
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -65712,7 +65726,7 @@
         <v>854</v>
       </c>
       <c r="N1235" t="s">
-        <v>4331</v>
+        <v>4330</v>
       </c>
     </row>
     <row r="1236" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -72808,7 +72822,7 @@
         <v>854</v>
       </c>
       <c r="N1408" t="s">
-        <v>4330</v>
+        <v>4329</v>
       </c>
     </row>
     <row r="1409" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -76714,11 +76728,11 @@
       <c r="K1503">
         <v>1504</v>
       </c>
-      <c r="M1503" s="167" t="s">
+      <c r="M1503" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1503" t="s">
         <v>4323</v>
-      </c>
-      <c r="N1503" t="s">
-        <v>4324</v>
       </c>
     </row>
     <row r="1504" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -76755,11 +76769,11 @@
       <c r="K1504">
         <v>1505</v>
       </c>
-      <c r="M1504" s="167" t="s">
-        <v>4323</v>
+      <c r="M1504" s="57" t="s">
+        <v>854</v>
       </c>
       <c r="N1504" t="s">
-        <v>4325</v>
+        <v>4324</v>
       </c>
     </row>
     <row r="1505" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -76796,11 +76810,11 @@
       <c r="K1505">
         <v>1506</v>
       </c>
-      <c r="M1505" s="167" t="s">
-        <v>4323</v>
+      <c r="M1505" s="57" t="s">
+        <v>854</v>
       </c>
       <c r="N1505" t="s">
-        <v>4326</v>
+        <v>4325</v>
       </c>
     </row>
     <row r="1506" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -76840,11 +76854,11 @@
       <c r="L1506" t="s">
         <v>4319</v>
       </c>
-      <c r="M1506" s="167" t="s">
-        <v>4323</v>
+      <c r="M1506" s="57" t="s">
+        <v>854</v>
       </c>
       <c r="N1506" t="s">
-        <v>4327</v>
+        <v>4326</v>
       </c>
     </row>
     <row r="1507" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -76881,11 +76895,11 @@
       <c r="K1507">
         <v>1508</v>
       </c>
-      <c r="M1507" s="167" t="s">
-        <v>4323</v>
+      <c r="M1507" s="57" t="s">
+        <v>854</v>
       </c>
       <c r="N1507" t="s">
-        <v>4328</v>
+        <v>4327</v>
       </c>
     </row>
     <row r="1508" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -76922,17 +76936,53 @@
       <c r="K1508">
         <v>1509</v>
       </c>
-      <c r="M1508" s="167" t="s">
-        <v>4323</v>
+      <c r="M1508" s="57" t="s">
+        <v>854</v>
       </c>
       <c r="N1508" t="s">
-        <v>4329</v>
+        <v>4328</v>
       </c>
     </row>
     <row r="1509" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1509" s="7"/>
-      <c r="H1509" s="167"/>
-      <c r="I1509" s="167"/>
+      <c r="A1509">
+        <v>82</v>
+      </c>
+      <c r="B1509" s="7">
+        <v>2244541</v>
+      </c>
+      <c r="C1509" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1509" t="s">
+        <v>4331</v>
+      </c>
+      <c r="E1509" t="s">
+        <v>433</v>
+      </c>
+      <c r="F1509" s="29">
+        <v>46158</v>
+      </c>
+      <c r="G1509" s="56">
+        <v>1.9282407407407408E-2</v>
+      </c>
+      <c r="H1509" s="168" t="s">
+        <v>805</v>
+      </c>
+      <c r="I1509" s="168" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1509" s="63" t="s">
+        <v>4332</v>
+      </c>
+      <c r="K1509">
+        <v>1510</v>
+      </c>
+      <c r="M1509" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1509" t="s">
+        <v>4333</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N1">

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12505" uniqueCount="4334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12510" uniqueCount="4336">
   <si>
     <t>Ņ</t>
   </si>
@@ -13029,6 +13029,12 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1506190698427322399/id_Xm.png?ex=6a0d5ce6&amp;is=6a0c0b66&amp;hm=de9b79cbeb6e0cc12596b8af4e0bf668f7fee85865f4a95c3b4d167d32983500</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>Jon</t>
   </si>
 </sst>
 </file>
@@ -13040,11 +13046,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="118" x14ac:knownFonts="1">
+  <fonts count="119" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -13899,118 +13912,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="116" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="169">
+  <cellXfs count="170">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="115" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="99" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="114" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="98" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="113" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="105" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="99" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="106" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="100" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="96" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="95" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="83" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="83" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="82" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="82" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="83" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="82" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="83" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="82" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="82" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="83" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="77" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="76" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="76" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="75" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="75" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14019,18 +14033,18 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="59" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="59" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="52" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="53" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14044,14 +14058,14 @@
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14301,7 +14315,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1509"/>
+  <dimension ref="A1:O1510"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -76984,6 +76998,35 @@
         <v>4333</v>
       </c>
     </row>
+    <row r="1510" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1510">
+        <v>83</v>
+      </c>
+      <c r="B1510" s="7">
+        <v>1000000</v>
+      </c>
+      <c r="C1510" t="s">
+        <v>4334</v>
+      </c>
+      <c r="D1510" t="s">
+        <v>4334</v>
+      </c>
+      <c r="E1510" t="s">
+        <v>4334</v>
+      </c>
+      <c r="F1510" s="29">
+        <v>38027</v>
+      </c>
+      <c r="G1510" s="56">
+        <v>0.38135416666666666</v>
+      </c>
+      <c r="H1510" s="169" t="s">
+        <v>4335</v>
+      </c>
+      <c r="I1510" s="169" t="s">
+        <v>806</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N1">
     <sortState ref="A2:N1508">

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12510" uniqueCount="4336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12507" uniqueCount="4336">
   <si>
     <t>Ņ</t>
   </si>
@@ -15860,8 +15860,8 @@
       <c r="F36" s="30">
         <v>45905</v>
       </c>
-      <c r="G36" s="55" t="s">
-        <v>502</v>
+      <c r="G36" s="55">
+        <v>0.32569444444444445</v>
       </c>
       <c r="H36" s="60" t="s">
         <v>840</v>
@@ -72161,8 +72161,8 @@
       <c r="F1392" s="29">
         <v>46124</v>
       </c>
-      <c r="G1392" s="56" t="s">
-        <v>502</v>
+      <c r="G1392" s="56">
+        <v>9.375E-2</v>
       </c>
       <c r="H1392" s="148" t="s">
         <v>2031</v>
@@ -73441,8 +73441,8 @@
       <c r="F1423" s="29">
         <v>46135</v>
       </c>
-      <c r="G1423" s="56" t="s">
-        <v>502</v>
+      <c r="G1423" s="56">
+        <v>0.18402777777777779</v>
       </c>
       <c r="H1423" s="155" t="s">
         <v>4098</v>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12507" uniqueCount="4336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12526" uniqueCount="4343">
   <si>
     <t>Ņ</t>
   </si>
@@ -13031,10 +13031,31 @@
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1506190698427322399/id_Xm.png?ex=6a0d5ce6&amp;is=6a0c0b66&amp;hm=de9b79cbeb6e0cc12596b8af4e0bf668f7fee85865f4a95c3b4d167d32983500</t>
   </si>
   <si>
-    <t>Test</t>
-  </si>
-  <si>
-    <t>Jon</t>
+    <t>Frisdihh</t>
+  </si>
+  <si>
+    <t>Xn</t>
+  </si>
+  <si>
+    <t>Summoner/Nyx</t>
+  </si>
+  <si>
+    <t>Xo</t>
+  </si>
+  <si>
+    <t>un(racist)</t>
+  </si>
+  <si>
+    <t>Xp</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1507269625602379776/id_Xn.png?ex=6a1149ba&amp;is=6a0ff83a&amp;hm=4b14df318487e1f5611e18dd00b85337eb4d61a83cb962d2ef53c0e5a5b9ab3a</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1507269679557902446/id_Xo.png?ex=6a1149c7&amp;is=6a0ff847&amp;hm=0e512105d4ab33998cfffa0464defd30266fd4d0ccdabb53859f20f707990a34</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1507269733471358976/id_Xp.png?ex=6a1149d4&amp;is=6a0ff854&amp;hm=e6063e98f2685a86fe802491a0ad7d57ac7b1e68d2e53bdc3f57a2952dcfbf45</t>
   </si>
 </sst>
 </file>
@@ -14315,7 +14336,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1510"/>
+  <dimension ref="A1:O1512"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -77003,28 +77024,122 @@
         <v>83</v>
       </c>
       <c r="B1510" s="7">
-        <v>1000000</v>
+        <v>12970205</v>
       </c>
       <c r="C1510" t="s">
         <v>4334</v>
       </c>
       <c r="D1510" t="s">
-        <v>4334</v>
+        <v>3668</v>
       </c>
       <c r="E1510" t="s">
-        <v>4334</v>
+        <v>433</v>
       </c>
       <c r="F1510" s="29">
-        <v>38027</v>
+        <v>46164</v>
       </c>
       <c r="G1510" s="56">
-        <v>0.38135416666666666</v>
+        <v>0.16290509259259259</v>
       </c>
       <c r="H1510" s="169" t="s">
+        <v>832</v>
+      </c>
+      <c r="I1510" s="169" t="s">
+        <v>290</v>
+      </c>
+      <c r="J1510" s="63" t="s">
         <v>4335</v>
       </c>
-      <c r="I1510" s="169" t="s">
-        <v>806</v>
+      <c r="K1510">
+        <v>1511</v>
+      </c>
+      <c r="M1510" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1510" t="s">
+        <v>4340</v>
+      </c>
+    </row>
+    <row r="1511" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1511">
+        <v>83</v>
+      </c>
+      <c r="B1511" s="7">
+        <v>8983998</v>
+      </c>
+      <c r="C1511" t="s">
+        <v>4338</v>
+      </c>
+      <c r="D1511" t="s">
+        <v>319</v>
+      </c>
+      <c r="E1511" t="s">
+        <v>236</v>
+      </c>
+      <c r="F1511" s="29">
+        <v>46163</v>
+      </c>
+      <c r="G1511" s="56">
+        <v>7.7800925925925926E-2</v>
+      </c>
+      <c r="H1511" s="169" t="s">
+        <v>4336</v>
+      </c>
+      <c r="I1511" s="169" t="s">
+        <v>290</v>
+      </c>
+      <c r="J1511" s="63" t="s">
+        <v>4337</v>
+      </c>
+      <c r="K1511">
+        <v>1512</v>
+      </c>
+      <c r="M1511" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1511" t="s">
+        <v>4341</v>
+      </c>
+    </row>
+    <row r="1512" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1512">
+        <v>83</v>
+      </c>
+      <c r="B1512" s="7">
+        <v>7395250</v>
+      </c>
+      <c r="C1512" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1512" t="s">
+        <v>646</v>
+      </c>
+      <c r="E1512" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1512" s="29">
+        <v>46163</v>
+      </c>
+      <c r="G1512" s="56">
+        <v>0.16445601851851852</v>
+      </c>
+      <c r="H1512" s="169" t="s">
+        <v>840</v>
+      </c>
+      <c r="I1512" s="169" t="s">
+        <v>290</v>
+      </c>
+      <c r="J1512" s="63" t="s">
+        <v>4339</v>
+      </c>
+      <c r="K1512">
+        <v>1513</v>
+      </c>
+      <c r="M1512" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1512" t="s">
+        <v>4342</v>
       </c>
     </row>
   </sheetData>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12526" uniqueCount="4343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12543" uniqueCount="4349">
   <si>
     <t>Ņ</t>
   </si>
@@ -13056,6 +13056,24 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1507269733471358976/id_Xp.png?ex=6a1149d4&amp;is=6a0ff854&amp;hm=e6063e98f2685a86fe802491a0ad7d57ac7b1e68d2e53bdc3f57a2952dcfbf45</t>
+  </si>
+  <si>
+    <t>Xq</t>
+  </si>
+  <si>
+    <t>Xr</t>
+  </si>
+  <si>
+    <t>FS☄</t>
+  </si>
+  <si>
+    <t>/.-`&gt;`-&gt;</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1507624159000399923/id_Xq.jpg?ex=6a1293e9&amp;is=6a114269&amp;hm=42e3cde067ec5b4793e52a4218659a1f4adb2d8c185e244e2fb8d2cc91a94485</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1507624228436971540/id_Xr.png?ex=6a1293fa&amp;is=6a11427a&amp;hm=ec43bb90e102dca93776d91fe4f8f81202cc7c5401df9a110a69f6ae720442c1</t>
   </si>
 </sst>
 </file>
@@ -13067,11 +13085,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="119" x14ac:knownFonts="1">
+  <fonts count="120" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -13933,118 +13958,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="170">
+  <cellXfs count="171">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="116" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="100" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="115" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="99" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="114" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="106" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="100" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="107" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="101" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="97" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="96" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="84" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="84" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="83" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="83" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="84" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="83" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="84" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="83" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="81" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="81" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="83" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="84" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="77" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="77" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="76" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="76" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14053,18 +14079,18 @@
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="59" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="59" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="53" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="54" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14078,14 +14104,14 @@
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14336,7 +14362,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1512"/>
+  <dimension ref="A1:O1514"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -77142,6 +77168,88 @@
         <v>4342</v>
       </c>
     </row>
+    <row r="1513" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1513">
+        <v>84</v>
+      </c>
+      <c r="B1513" s="7">
+        <v>10490000</v>
+      </c>
+      <c r="C1513" t="s">
+        <v>4345</v>
+      </c>
+      <c r="D1513" t="s">
+        <v>424</v>
+      </c>
+      <c r="E1513" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F1513" s="29">
+        <v>46124</v>
+      </c>
+      <c r="G1513" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1513" s="170" t="s">
+        <v>2031</v>
+      </c>
+      <c r="I1513" s="170" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1513" s="63" t="s">
+        <v>4343</v>
+      </c>
+      <c r="K1513">
+        <v>1514</v>
+      </c>
+      <c r="M1513" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1513" t="s">
+        <v>4347</v>
+      </c>
+    </row>
+    <row r="1514" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1514">
+        <v>84</v>
+      </c>
+      <c r="B1514" s="7">
+        <v>5612341</v>
+      </c>
+      <c r="C1514" t="s">
+        <v>4346</v>
+      </c>
+      <c r="D1514" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1514" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1514" s="29">
+        <v>46092</v>
+      </c>
+      <c r="G1514" s="56">
+        <v>2.2442129629629631E-2</v>
+      </c>
+      <c r="H1514" s="170" t="s">
+        <v>805</v>
+      </c>
+      <c r="I1514" s="170" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1514" s="63" t="s">
+        <v>4344</v>
+      </c>
+      <c r="K1514">
+        <v>1515</v>
+      </c>
+      <c r="M1514" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1514" t="s">
+        <v>4348</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N1">
     <sortState ref="A2:N1508">

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12543" uniqueCount="4349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12551" uniqueCount="4352">
   <si>
     <t>Ņ</t>
   </si>
@@ -13074,6 +13074,15 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1507624228436971540/id_Xr.png?ex=6a1293fa&amp;is=6a11427a&amp;hm=ec43bb90e102dca93776d91fe4f8f81202cc7c5401df9a110a69f6ae720442c1</t>
+  </si>
+  <si>
+    <t>Raiko Horikawa</t>
+  </si>
+  <si>
+    <t>Xs</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1509468146237706240/id_Xs.jpg?ex=6a194942&amp;is=6a17f7c2&amp;hm=9d5a6db5edeaf312679d9ed678e91bece26ab6181037a296532112d88c328a80</t>
   </si>
 </sst>
 </file>
@@ -13085,11 +13094,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="120" x14ac:knownFonts="1">
+  <fonts count="121" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -13958,118 +13974,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="171">
+  <cellXfs count="172">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="117" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="101" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="116" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="100" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="115" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="107" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="101" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="108" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="102" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="98" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="97" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="85" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="85" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="84" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="84" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="85" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="84" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="85" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="84" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="81" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="81" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="82" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="82" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="84" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="85" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="120" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="119" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="77" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="77" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14078,18 +14095,18 @@
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="54" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="55" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14103,14 +14120,14 @@
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14362,7 +14379,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1514"/>
+  <dimension ref="A1:O1515"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -77250,6 +77267,47 @@
         <v>4348</v>
       </c>
     </row>
+    <row r="1515" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1515">
+        <v>85</v>
+      </c>
+      <c r="B1515" s="7">
+        <v>2008884</v>
+      </c>
+      <c r="C1515" t="s">
+        <v>4349</v>
+      </c>
+      <c r="D1515" t="s">
+        <v>478</v>
+      </c>
+      <c r="E1515" t="s">
+        <v>798</v>
+      </c>
+      <c r="F1515" s="29">
+        <v>46105</v>
+      </c>
+      <c r="G1515" s="56">
+        <v>5.7650462962962966E-2</v>
+      </c>
+      <c r="H1515" s="171" t="s">
+        <v>832</v>
+      </c>
+      <c r="I1515" s="171" t="s">
+        <v>290</v>
+      </c>
+      <c r="J1515" s="63" t="s">
+        <v>4350</v>
+      </c>
+      <c r="K1515">
+        <v>1516</v>
+      </c>
+      <c r="M1515" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1515" t="s">
+        <v>4351</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N1">
     <sortState ref="A2:N1508">

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12551" uniqueCount="4352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12551" uniqueCount="4353">
   <si>
     <t>Ņ</t>
   </si>
@@ -13083,6 +13083,9 @@
   </si>
   <si>
     <t>by Ogres orders</t>
+  </si>
+  <si>
+    <t>465 Solar</t>
   </si>
 </sst>
 </file>
@@ -16872,8 +16875,8 @@
       <c r="D58" s="12" t="s">
         <v>424</v>
       </c>
-      <c r="E58" s="1" t="s">
-        <v>51</v>
+      <c r="E58" t="s">
+        <v>4352</v>
       </c>
       <c r="F58" s="30">
         <v>45767</v>
@@ -16917,8 +16920,8 @@
       <c r="D59" t="s">
         <v>424</v>
       </c>
-      <c r="E59" s="1" t="s">
-        <v>51</v>
+      <c r="E59" t="s">
+        <v>4352</v>
       </c>
       <c r="F59" s="29">
         <v>46000</v>
@@ -21380,8 +21383,8 @@
       <c r="D163" t="s">
         <v>399</v>
       </c>
-      <c r="E163" s="37" t="s">
-        <v>51</v>
+      <c r="E163" t="s">
+        <v>4352</v>
       </c>
       <c r="F163" s="29">
         <v>46047</v>
@@ -22540,7 +22543,7 @@
         <v>417</v>
       </c>
       <c r="E190" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F190" s="29">
         <v>46012</v>
@@ -24379,8 +24382,8 @@
       <c r="D233" s="12" t="s">
         <v>424</v>
       </c>
-      <c r="E233" s="1" t="s">
-        <v>51</v>
+      <c r="E233" t="s">
+        <v>4352</v>
       </c>
       <c r="F233" s="29">
         <v>45946</v>
@@ -28634,8 +28637,8 @@
       <c r="D335" t="s">
         <v>380</v>
       </c>
-      <c r="E335" s="1" t="s">
-        <v>51</v>
+      <c r="E335" t="s">
+        <v>4352</v>
       </c>
       <c r="F335" s="29">
         <v>45991</v>
@@ -29304,8 +29307,8 @@
       <c r="D351" s="12" t="s">
         <v>424</v>
       </c>
-      <c r="E351" s="1" t="s">
-        <v>51</v>
+      <c r="E351" t="s">
+        <v>4352</v>
       </c>
       <c r="F351" s="30">
         <v>45963</v>
@@ -30709,7 +30712,7 @@
         <v>495</v>
       </c>
       <c r="E385" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F385" s="29">
         <v>46015</v>
@@ -31706,7 +31709,7 @@
         <v>54</v>
       </c>
       <c r="E409" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F409" s="29">
         <v>46002</v>
@@ -31959,7 +31962,7 @@
         <v>463</v>
       </c>
       <c r="E415" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F415" s="29">
         <v>46001</v>
@@ -34037,8 +34040,8 @@
       <c r="D465" t="s">
         <v>5</v>
       </c>
-      <c r="E465" s="1" t="s">
-        <v>51</v>
+      <c r="E465" t="s">
+        <v>4352</v>
       </c>
       <c r="F465" s="29">
         <v>45791</v>
@@ -36437,8 +36440,8 @@
       <c r="D523" t="s">
         <v>172</v>
       </c>
-      <c r="E523" s="1" t="s">
-        <v>51</v>
+      <c r="E523" t="s">
+        <v>4352</v>
       </c>
       <c r="F523" s="29">
         <v>45808</v>
@@ -36891,7 +36894,7 @@
         <v>662</v>
       </c>
       <c r="E534" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F534" s="29">
         <v>46018</v>
@@ -39677,8 +39680,8 @@
       <c r="D601" t="s">
         <v>417</v>
       </c>
-      <c r="E601" s="1" t="s">
-        <v>51</v>
+      <c r="E601" t="s">
+        <v>4352</v>
       </c>
       <c r="F601" s="29">
         <v>46009</v>
@@ -41369,7 +41372,7 @@
         <v>402</v>
       </c>
       <c r="E642" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F642" s="29">
         <v>46018</v>
@@ -43516,8 +43519,8 @@
       <c r="D694" t="s">
         <v>159</v>
       </c>
-      <c r="E694" s="1" t="s">
-        <v>51</v>
+      <c r="E694" t="s">
+        <v>4352</v>
       </c>
       <c r="F694" s="29">
         <v>45937</v>
@@ -43886,8 +43889,8 @@
       <c r="D703" t="s">
         <v>613</v>
       </c>
-      <c r="E703" s="1" t="s">
-        <v>51</v>
+      <c r="E703" t="s">
+        <v>4352</v>
       </c>
       <c r="F703" s="29">
         <v>46010</v>
@@ -44050,8 +44053,8 @@
       <c r="D707" t="s">
         <v>364</v>
       </c>
-      <c r="E707" s="1" t="s">
-        <v>51</v>
+      <c r="E707" t="s">
+        <v>4352</v>
       </c>
       <c r="F707" s="29">
         <v>45900</v>
@@ -44258,8 +44261,8 @@
       <c r="D712" t="s">
         <v>224</v>
       </c>
-      <c r="E712" s="1" t="s">
-        <v>51</v>
+      <c r="E712" t="s">
+        <v>4352</v>
       </c>
       <c r="F712" s="29">
         <v>45956</v>
@@ -44671,8 +44674,8 @@
       <c r="D722" t="s">
         <v>159</v>
       </c>
-      <c r="E722" s="1" t="s">
-        <v>51</v>
+      <c r="E722" t="s">
+        <v>4352</v>
       </c>
       <c r="F722" s="29">
         <v>45941</v>
@@ -45458,8 +45461,8 @@
       <c r="D741" t="s">
         <v>372</v>
       </c>
-      <c r="E741" s="1" t="s">
-        <v>51</v>
+      <c r="E741" t="s">
+        <v>4352</v>
       </c>
       <c r="F741" s="29">
         <v>45865</v>
@@ -46328,8 +46331,8 @@
       <c r="D762" t="s">
         <v>404</v>
       </c>
-      <c r="E762" s="1" t="s">
-        <v>51</v>
+      <c r="E762" t="s">
+        <v>4352</v>
       </c>
       <c r="F762" s="29">
         <v>46003</v>
@@ -46984,8 +46987,8 @@
       <c r="D778" t="s">
         <v>398</v>
       </c>
-      <c r="E778" s="37" t="s">
-        <v>51</v>
+      <c r="E778" t="s">
+        <v>4352</v>
       </c>
       <c r="F778" s="29">
         <v>46048</v>
@@ -47108,7 +47111,7 @@
         <v>364</v>
       </c>
       <c r="E781" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F781" s="29">
         <v>46019</v>
@@ -47148,8 +47151,8 @@
       <c r="D782" t="s">
         <v>372</v>
       </c>
-      <c r="E782" s="1" t="s">
-        <v>51</v>
+      <c r="E782" t="s">
+        <v>4352</v>
       </c>
       <c r="F782" s="29">
         <v>45808</v>
@@ -47230,8 +47233,8 @@
       <c r="D784" t="s">
         <v>370</v>
       </c>
-      <c r="E784" s="1" t="s">
-        <v>51</v>
+      <c r="E784" t="s">
+        <v>4352</v>
       </c>
       <c r="F784" s="29">
         <v>45982</v>
@@ -47681,8 +47684,8 @@
       <c r="D795" t="s">
         <v>417</v>
       </c>
-      <c r="E795" s="1" t="s">
-        <v>51</v>
+      <c r="E795" t="s">
+        <v>4352</v>
       </c>
       <c r="F795" s="29">
         <v>45992</v>
@@ -48221,7 +48224,7 @@
         <v>655</v>
       </c>
       <c r="E808" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F808" s="29">
         <v>46017</v>
@@ -48262,7 +48265,7 @@
         <v>674</v>
       </c>
       <c r="E809" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F809" s="29">
         <v>46019</v>
@@ -48507,8 +48510,8 @@
       <c r="D815" t="s">
         <v>340</v>
       </c>
-      <c r="E815" s="37" t="s">
-        <v>51</v>
+      <c r="E815" t="s">
+        <v>4352</v>
       </c>
       <c r="F815" s="29">
         <v>46028</v>
@@ -48548,8 +48551,8 @@
       <c r="D816" s="21" t="s">
         <v>531</v>
       </c>
-      <c r="E816" s="1" t="s">
-        <v>51</v>
+      <c r="E816" t="s">
+        <v>4352</v>
       </c>
       <c r="F816" s="29">
         <v>46000</v>
@@ -49251,8 +49254,8 @@
       <c r="D833" t="s">
         <v>693</v>
       </c>
-      <c r="E833" s="37" t="s">
-        <v>51</v>
+      <c r="E833" t="s">
+        <v>4352</v>
       </c>
       <c r="F833" s="29">
         <v>46040</v>
@@ -49662,7 +49665,7 @@
         <v>537</v>
       </c>
       <c r="E843" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F843" s="29">
         <v>46004</v>
@@ -49744,7 +49747,7 @@
         <v>662</v>
       </c>
       <c r="E845" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F845" s="29">
         <v>46018</v>
@@ -49825,8 +49828,8 @@
       <c r="D847" t="s">
         <v>372</v>
       </c>
-      <c r="E847" s="1" t="s">
-        <v>51</v>
+      <c r="E847" t="s">
+        <v>4352</v>
       </c>
       <c r="F847" s="29">
         <v>45808</v>
@@ -50154,7 +50157,7 @@
         <v>495</v>
       </c>
       <c r="E855" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F855" s="29">
         <v>46015</v>
@@ -51474,8 +51477,8 @@
       <c r="D887" t="s">
         <v>463</v>
       </c>
-      <c r="E887" s="1" t="s">
-        <v>51</v>
+      <c r="E887" t="s">
+        <v>4352</v>
       </c>
       <c r="F887" s="29">
         <v>46000</v>
@@ -53663,7 +53666,7 @@
         <v>662</v>
       </c>
       <c r="E940" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F940" s="29">
         <v>46018</v>
@@ -55839,8 +55842,8 @@
       <c r="D993" t="s">
         <v>503</v>
       </c>
-      <c r="E993" s="1" t="s">
-        <v>51</v>
+      <c r="E993" t="s">
+        <v>4352</v>
       </c>
       <c r="F993" s="29">
         <v>46002</v>
@@ -56249,8 +56252,8 @@
       <c r="D1003" t="s">
         <v>369</v>
       </c>
-      <c r="E1003" s="1" t="s">
-        <v>51</v>
+      <c r="E1003" t="s">
+        <v>4352</v>
       </c>
       <c r="F1003" s="29">
         <v>45942</v>
@@ -56414,7 +56417,7 @@
         <v>374</v>
       </c>
       <c r="E1007" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F1007" s="29">
         <v>46015</v>
@@ -56454,8 +56457,8 @@
       <c r="D1008" t="s">
         <v>703</v>
       </c>
-      <c r="E1008" s="37" t="s">
-        <v>51</v>
+      <c r="E1008" t="s">
+        <v>4352</v>
       </c>
       <c r="F1008" s="29">
         <v>46025</v>
@@ -56536,8 +56539,8 @@
       <c r="D1010" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="E1010" s="1" t="s">
-        <v>51</v>
+      <c r="E1010" t="s">
+        <v>4352</v>
       </c>
       <c r="F1010" s="30">
         <v>45769</v>
@@ -57365,8 +57368,8 @@
       <c r="D1030" t="s">
         <v>374</v>
       </c>
-      <c r="E1030" s="1" t="s">
-        <v>51</v>
+      <c r="E1030" t="s">
+        <v>4352</v>
       </c>
       <c r="F1030" s="29">
         <v>45962</v>
@@ -57866,8 +57869,8 @@
       <c r="D1042" t="s">
         <v>693</v>
       </c>
-      <c r="E1042" s="37" t="s">
-        <v>51</v>
+      <c r="E1042" t="s">
+        <v>4352</v>
       </c>
       <c r="F1042" s="38">
         <v>46021</v>
@@ -58154,7 +58157,7 @@
         <v>419</v>
       </c>
       <c r="E1049" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F1049" s="32">
         <v>46014</v>
@@ -58568,7 +58571,7 @@
         <v>305</v>
       </c>
       <c r="E1059" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F1059" s="29">
         <v>46050</v>
@@ -63040,7 +63043,7 @@
         <v>2457</v>
       </c>
       <c r="E1168" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F1168" s="29">
         <v>46075</v>
@@ -65257,7 +65260,7 @@
         <v>60</v>
       </c>
       <c r="E1222" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F1222" s="29">
         <v>46088</v>
@@ -65708,7 +65711,7 @@
         <v>60</v>
       </c>
       <c r="E1233" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F1233" s="29">
         <v>46089</v>
@@ -65913,7 +65916,7 @@
         <v>60</v>
       </c>
       <c r="E1238" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F1238" s="29">
         <v>46089</v>
@@ -66364,7 +66367,7 @@
         <v>424</v>
       </c>
       <c r="E1249" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F1249" s="29">
         <v>46090</v>
@@ -66405,7 +66408,7 @@
         <v>35</v>
       </c>
       <c r="E1250" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F1250" s="29">
         <v>46090</v>
@@ -67963,7 +67966,7 @@
         <v>247</v>
       </c>
       <c r="E1288" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F1288" s="29">
         <v>46059</v>
@@ -68004,7 +68007,7 @@
         <v>3716</v>
       </c>
       <c r="E1289" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F1289" s="29">
         <v>46102</v>
@@ -68168,7 +68171,7 @@
         <v>3716</v>
       </c>
       <c r="E1293" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F1293" s="29">
         <v>46102</v>
@@ -68701,7 +68704,7 @@
         <v>406</v>
       </c>
       <c r="E1306" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F1306" s="29">
         <v>46106</v>
@@ -69480,7 +69483,7 @@
         <v>40</v>
       </c>
       <c r="E1325" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F1325" s="29">
         <v>46109</v>
@@ -69521,7 +69524,7 @@
         <v>364</v>
       </c>
       <c r="E1326" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F1326" s="29">
         <v>46109</v>
@@ -69603,7 +69606,7 @@
         <v>473</v>
       </c>
       <c r="E1328" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F1328" s="29">
         <v>46109</v>
@@ -69644,7 +69647,7 @@
         <v>447</v>
       </c>
       <c r="E1329" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F1329" s="29">
         <v>46110</v>
@@ -69890,7 +69893,7 @@
         <v>15</v>
       </c>
       <c r="E1335" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F1335" s="29">
         <v>46111</v>
@@ -70139,7 +70142,7 @@
         <v>540</v>
       </c>
       <c r="E1341" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F1341" s="29">
         <v>46112</v>
@@ -70180,7 +70183,7 @@
         <v>338</v>
       </c>
       <c r="E1342" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F1342" s="29">
         <v>46112</v>
@@ -70467,7 +70470,7 @@
         <v>60</v>
       </c>
       <c r="E1349" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F1349" s="29">
         <v>46088</v>
@@ -70918,7 +70921,7 @@
         <v>424</v>
       </c>
       <c r="E1360" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F1360" s="29">
         <v>46120</v>
@@ -71041,7 +71044,7 @@
         <v>161</v>
       </c>
       <c r="E1363" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F1363" s="29">
         <v>46120</v>
@@ -71287,7 +71290,7 @@
         <v>3716</v>
       </c>
       <c r="E1369" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F1369" s="29">
         <v>46121</v>
@@ -72025,7 +72028,7 @@
         <v>399</v>
       </c>
       <c r="E1387" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F1387" s="29">
         <v>46123</v>
@@ -74491,7 +74494,7 @@
         <v>3716</v>
       </c>
       <c r="E1447" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F1447" s="29">
         <v>46144</v>
@@ -74573,7 +74576,7 @@
         <v>3716</v>
       </c>
       <c r="E1449" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F1449" s="29">
         <v>46144</v>
@@ -74614,7 +74617,7 @@
         <v>3716</v>
       </c>
       <c r="E1450" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F1450" s="29">
         <v>46144</v>
@@ -74983,7 +74986,7 @@
         <v>3716</v>
       </c>
       <c r="E1459" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F1459" s="29">
         <v>46145</v>
@@ -75311,7 +75314,7 @@
         <v>3716</v>
       </c>
       <c r="E1467" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F1467" s="29">
         <v>46145</v>
@@ -75393,7 +75396,7 @@
         <v>3716</v>
       </c>
       <c r="E1469" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F1469" s="29">
         <v>46146</v>
@@ -76008,7 +76011,7 @@
         <v>4262</v>
       </c>
       <c r="E1484" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F1484" s="29">
         <v>46151</v>
@@ -76090,7 +76093,7 @@
         <v>4266</v>
       </c>
       <c r="E1486" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F1486" s="29">
         <v>46151</v>
@@ -77250,7 +77253,7 @@
         <v>62</v>
       </c>
       <c r="E1514" t="s">
-        <v>51</v>
+        <v>4352</v>
       </c>
       <c r="F1514" s="29">
         <v>46092</v>
@@ -77320,7 +77323,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:N1">
-    <sortState ref="A2:N1508">
+    <sortState ref="A2:N1515">
       <sortCondition ref="K1"/>
     </sortState>
   </autoFilter>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12551" uniqueCount="4353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12623" uniqueCount="4374">
   <si>
     <t>Ņ</t>
   </si>
@@ -13086,6 +13086,69 @@
   </si>
   <si>
     <t>465 Solar</t>
+  </si>
+  <si>
+    <t>Xt</t>
+  </si>
+  <si>
+    <t>Pounder</t>
+  </si>
+  <si>
+    <t>Xu</t>
+  </si>
+  <si>
+    <t>Xv</t>
+  </si>
+  <si>
+    <t>Xw</t>
+  </si>
+  <si>
+    <t>Xx</t>
+  </si>
+  <si>
+    <t>Xy</t>
+  </si>
+  <si>
+    <t>Xz</t>
+  </si>
+  <si>
+    <t>Auto-Battery</t>
+  </si>
+  <si>
+    <t>X0</t>
+  </si>
+  <si>
+    <t>Paladin/Elite Crasher/Ezekiel</t>
+  </si>
+  <si>
+    <t>X1</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1511789415977062500/id_Xt.png?ex=6a21bb1c&amp;is=6a20699c&amp;hm=5c26be79271a3c5bf63920977ce3be9e35544d0d8a2118c8964441c9f333b0fe</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1511789490035753010/id_Xu.png?ex=6a21bb2e&amp;is=6a2069ae&amp;hm=80c53ea33acc98cac34ff7f6f3aa2060c4a4d9e60f0ec41a2e7b68b1df24a120</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1511789550211563793/id_Xv.png?ex=6a21bb3c&amp;is=6a2069bc&amp;hm=d27e9578afd0700cf77a79ca788c097068dcf18aafe12a3e749d14461b71a96c</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1511789651344752691/id_Xw.png?ex=6a21bb54&amp;is=6a2069d4&amp;hm=3230e40f531ccf9734fb0f9e3a985899f8680644cbdb84f1c9f71853deffd330</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1511790294746534008/id_Xx.png?ex=6a21bbed&amp;is=6a206a6d&amp;hm=c2180808efd41afb941b7ee0c333c9a96893abe8434900eeb248cfd06f5754ca</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1511790365475340338/id_Xy.jpg?ex=6a21bbfe&amp;is=6a206a7e&amp;hm=6d19b07aafcc63c78b094a7c9d4c5ed069b6b0e0d3248b92a7fcb6b5fbcea666</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1511790446601568288/id_Xz.jpg?ex=6a21bc12&amp;is=6a206a92&amp;hm=fa79713c5727d50f4196c8afd60e9d7ad0bb0e4f2284f394e8a6620bbea1a841</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1511790526079307966/id_X0.png?ex=6a21bc25&amp;is=6a206aa5&amp;hm=ca4af0309b232c61685534a7d8db38055ac19b46dd4be44043be3af5aedac5f7</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1511790596040429741/id_X1.png?ex=6a21bc35&amp;is=6a206ab5&amp;hm=9b8cdf051d9130d61c83ef1ff051c0e53981f2afb4208241eaa4977570f4eec9</t>
   </si>
 </sst>
 </file>
@@ -13097,11 +13160,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="122" x14ac:knownFonts="1">
+  <fonts count="123" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -13984,118 +14054,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="173">
+  <cellXfs count="174">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="120" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="119" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="119" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="103" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="118" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="102" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="117" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="109" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="103" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="110" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="104" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="100" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="99" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="87" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="87" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="86" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="86" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="87" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="86" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="87" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="86" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="83" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="83" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="84" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="84" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="86" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="87" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="82" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="81" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14104,18 +14175,18 @@
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="62" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="62" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="57" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14129,14 +14200,14 @@
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14390,7 +14461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1515"/>
+  <dimension ref="A1:O1524"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -61478,7 +61549,7 @@
       <c r="B1130" s="7">
         <v>3683365</v>
       </c>
-      <c r="C1130" s="138" t="s">
+      <c r="C1130" s="173" t="s">
         <v>3874</v>
       </c>
       <c r="D1130" s="103" t="s">
@@ -77319,6 +77390,375 @@
       </c>
       <c r="N1515" t="s">
         <v>4350</v>
+      </c>
+    </row>
+    <row r="1516" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1516">
+        <v>86</v>
+      </c>
+      <c r="B1516" s="7">
+        <v>11122464</v>
+      </c>
+      <c r="C1516" t="s">
+        <v>236</v>
+      </c>
+      <c r="D1516" t="s">
+        <v>564</v>
+      </c>
+      <c r="E1516" t="s">
+        <v>236</v>
+      </c>
+      <c r="F1516" s="29">
+        <v>46176</v>
+      </c>
+      <c r="G1516" s="56">
+        <v>9.9467592592592594E-2</v>
+      </c>
+      <c r="H1516" s="173" t="s">
+        <v>835</v>
+      </c>
+      <c r="I1516" s="173" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1516" s="63" t="s">
+        <v>4353</v>
+      </c>
+      <c r="K1516">
+        <v>1517</v>
+      </c>
+      <c r="M1516" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1516" t="s">
+        <v>4365</v>
+      </c>
+    </row>
+    <row r="1517" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1517">
+        <v>86</v>
+      </c>
+      <c r="B1517" s="7">
+        <v>5218919</v>
+      </c>
+      <c r="C1517" t="s">
+        <v>720</v>
+      </c>
+      <c r="D1517" t="s">
+        <v>4354</v>
+      </c>
+      <c r="E1517" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F1517" s="29">
+        <v>46174</v>
+      </c>
+      <c r="G1517" s="56">
+        <v>7.2627314814814811E-2</v>
+      </c>
+      <c r="H1517" s="173" t="s">
+        <v>1106</v>
+      </c>
+      <c r="I1517" s="173" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1517" s="63" t="s">
+        <v>4355</v>
+      </c>
+      <c r="K1517">
+        <v>1518</v>
+      </c>
+      <c r="M1517" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1517" t="s">
+        <v>4366</v>
+      </c>
+    </row>
+    <row r="1518" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1518">
+        <v>86</v>
+      </c>
+      <c r="B1518" s="7">
+        <v>21274025</v>
+      </c>
+      <c r="C1518" t="s">
+        <v>720</v>
+      </c>
+      <c r="D1518" t="s">
+        <v>385</v>
+      </c>
+      <c r="E1518" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F1518" s="29">
+        <v>46175</v>
+      </c>
+      <c r="G1518" s="56">
+        <v>0.1885300925925926</v>
+      </c>
+      <c r="H1518" s="173" t="s">
+        <v>815</v>
+      </c>
+      <c r="I1518" s="173" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1518" s="63" t="s">
+        <v>4356</v>
+      </c>
+      <c r="K1518">
+        <v>1519</v>
+      </c>
+      <c r="M1518" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1518" t="s">
+        <v>4367</v>
+      </c>
+    </row>
+    <row r="1519" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1519">
+        <v>86</v>
+      </c>
+      <c r="B1519" s="7">
+        <v>17120051</v>
+      </c>
+      <c r="C1519" t="s">
+        <v>4182</v>
+      </c>
+      <c r="D1519" t="s">
+        <v>395</v>
+      </c>
+      <c r="E1519" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1519" s="29">
+        <v>46175</v>
+      </c>
+      <c r="G1519" s="56">
+        <v>0.1113425925925926</v>
+      </c>
+      <c r="H1519" s="173" t="s">
+        <v>887</v>
+      </c>
+      <c r="I1519" s="173" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1519" s="63" t="s">
+        <v>4357</v>
+      </c>
+      <c r="K1519">
+        <v>1520</v>
+      </c>
+      <c r="M1519" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1519" t="s">
+        <v>4368</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1520">
+        <v>86</v>
+      </c>
+      <c r="B1520" s="7">
+        <v>8862301</v>
+      </c>
+      <c r="C1520" t="s">
+        <v>4187</v>
+      </c>
+      <c r="D1520" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1520" t="s">
+        <v>4188</v>
+      </c>
+      <c r="F1520" s="29">
+        <v>46176</v>
+      </c>
+      <c r="G1520" s="56">
+        <v>4.4236111111111115E-2</v>
+      </c>
+      <c r="H1520" s="173" t="s">
+        <v>825</v>
+      </c>
+      <c r="I1520" s="173" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1520" s="63" t="s">
+        <v>4358</v>
+      </c>
+      <c r="K1520">
+        <v>1521</v>
+      </c>
+      <c r="M1520" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1520" t="s">
+        <v>4369</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1521">
+        <v>86</v>
+      </c>
+      <c r="B1521" s="7">
+        <v>5000016</v>
+      </c>
+      <c r="C1521" t="s">
+        <v>502</v>
+      </c>
+      <c r="D1521" t="s">
+        <v>632</v>
+      </c>
+      <c r="E1521" t="s">
+        <v>1761</v>
+      </c>
+      <c r="F1521" s="29">
+        <v>46175</v>
+      </c>
+      <c r="G1521" s="56">
+        <v>8.6180555555555552E-2</v>
+      </c>
+      <c r="H1521" s="173" t="s">
+        <v>835</v>
+      </c>
+      <c r="I1521" s="173" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1521" s="63" t="s">
+        <v>4359</v>
+      </c>
+      <c r="K1521">
+        <v>1522</v>
+      </c>
+      <c r="M1521" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1521" t="s">
+        <v>4370</v>
+      </c>
+    </row>
+    <row r="1522" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1522">
+        <v>86</v>
+      </c>
+      <c r="B1522" s="7">
+        <v>2500020</v>
+      </c>
+      <c r="C1522" t="s">
+        <v>3874</v>
+      </c>
+      <c r="D1522" t="s">
+        <v>478</v>
+      </c>
+      <c r="E1522" t="s">
+        <v>1761</v>
+      </c>
+      <c r="F1522" s="29">
+        <v>46176</v>
+      </c>
+      <c r="G1522" s="56">
+        <v>5.2256944444444446E-2</v>
+      </c>
+      <c r="H1522" s="173" t="s">
+        <v>815</v>
+      </c>
+      <c r="I1522" s="173" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1522" s="63" t="s">
+        <v>4360</v>
+      </c>
+      <c r="K1522">
+        <v>1523</v>
+      </c>
+      <c r="M1522" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1522" t="s">
+        <v>4371</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1523">
+        <v>86</v>
+      </c>
+      <c r="B1523" s="7">
+        <v>12154872</v>
+      </c>
+      <c r="C1523" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1523" t="s">
+        <v>4361</v>
+      </c>
+      <c r="E1523" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1523" s="29">
+        <v>46175</v>
+      </c>
+      <c r="G1523" s="56">
+        <v>0.15039351851851854</v>
+      </c>
+      <c r="H1523" s="173" t="s">
+        <v>815</v>
+      </c>
+      <c r="I1523" s="173" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1523" s="63" t="s">
+        <v>4362</v>
+      </c>
+      <c r="K1523">
+        <v>1524</v>
+      </c>
+      <c r="M1523" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1523" t="s">
+        <v>4372</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1524">
+        <v>86</v>
+      </c>
+      <c r="B1524" s="7">
+        <v>13149146</v>
+      </c>
+      <c r="C1524" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1524" t="s">
+        <v>79</v>
+      </c>
+      <c r="E1524" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1524" s="29">
+        <v>46176</v>
+      </c>
+      <c r="G1524" s="56">
+        <v>0.12686342592592592</v>
+      </c>
+      <c r="H1524" s="173" t="s">
+        <v>4363</v>
+      </c>
+      <c r="I1524" s="173" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1524" s="63" t="s">
+        <v>4364</v>
+      </c>
+      <c r="K1524">
+        <v>1525</v>
+      </c>
+      <c r="M1524" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1524" t="s">
+        <v>4373</v>
       </c>
     </row>
   </sheetData>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12623" uniqueCount="4374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12663" uniqueCount="4387">
   <si>
     <t>Ņ</t>
   </si>
@@ -13149,6 +13149,45 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1511790596040429741/id_X1.png?ex=6a21bc35&amp;is=6a206ab5&amp;hm=9b8cdf051d9130d61c83ef1ff051c0e53981f2afb4208241eaa4977570f4eec9</t>
+  </si>
+  <si>
+    <t>X2</t>
+  </si>
+  <si>
+    <t>(un_paralyzed doctor</t>
+  </si>
+  <si>
+    <t>X3</t>
+  </si>
+  <si>
+    <t>Ezekiel/Paladin/Theia</t>
+  </si>
+  <si>
+    <t>X4</t>
+  </si>
+  <si>
+    <t>Elite Skimmer/Theia</t>
+  </si>
+  <si>
+    <t>X5</t>
+  </si>
+  <si>
+    <t>X6</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1517143677292511373/id_X2.png?ex=6a3535a7&amp;is=6a33e427&amp;hm=7554b67cda389ec106e4083846adf2b406b4514ae8f6e5403b30126b17d65800</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1517143749317099622/id_X3.png?ex=6a3535b9&amp;is=6a33e439&amp;hm=027915c1e21592099831ebbb0a584befc4126a8d38cdc6d7621ddb5c87f07a55</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1517143812210950246/id_X4.png?ex=6a3535c8&amp;is=6a33e448&amp;hm=6ec8e504ac14e1f4bedfa4863093c7db7501ec39e0047a278b0a114709b3af74</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1517143858452893856/id_X5.png?ex=6a3535d3&amp;is=6a33e453&amp;hm=c3fe004f18980ac5b070b7c79b23fb8c6734d1e9eebecce56d3e5b7ea29dccc3</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1517143933686382783/id_X6.png?ex=6a3535e4&amp;is=6a33e464&amp;hm=b75102877861446da5cd1db57f2792ecbbaf5de0dfa6b1b8aa24dd91a1f9233a</t>
   </si>
 </sst>
 </file>
@@ -13160,11 +13199,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="123" x14ac:knownFonts="1">
+  <fonts count="124" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -14054,118 +14100,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="174">
+  <cellXfs count="175">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="120" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="120" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="119" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="119" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="120" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="104" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="119" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="103" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="118" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="110" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="104" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="111" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="105" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="101" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="100" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="88" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="88" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="87" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="87" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="88" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="87" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="88" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="87" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="84" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="84" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="85" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="85" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="87" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="88" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="83" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="82" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="81" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="81" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14174,18 +14221,18 @@
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="57" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="58" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14199,14 +14246,14 @@
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14461,7 +14508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1524"/>
+  <dimension ref="A1:O1529"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -17887,7 +17934,7 @@
       <c r="B80" s="7">
         <v>30980000</v>
       </c>
-      <c r="C80" s="123" t="s">
+      <c r="C80" s="174" t="s">
         <v>723</v>
       </c>
       <c r="D80" s="12" t="s">
@@ -77759,6 +77806,211 @@
       </c>
       <c r="N1524" t="s">
         <v>4373</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1525">
+        <v>87</v>
+      </c>
+      <c r="B1525" s="7">
+        <v>8967523</v>
+      </c>
+      <c r="C1525" t="s">
+        <v>236</v>
+      </c>
+      <c r="D1525" t="s">
+        <v>119</v>
+      </c>
+      <c r="E1525" t="s">
+        <v>236</v>
+      </c>
+      <c r="F1525" s="29">
+        <v>46176</v>
+      </c>
+      <c r="G1525" s="56">
+        <v>6.8263888888888888E-2</v>
+      </c>
+      <c r="H1525" s="174" t="s">
+        <v>835</v>
+      </c>
+      <c r="I1525" s="174" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1525" s="63" t="s">
+        <v>4374</v>
+      </c>
+      <c r="K1525">
+        <v>1526</v>
+      </c>
+      <c r="M1525" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1525" t="s">
+        <v>4382</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1526">
+        <v>87</v>
+      </c>
+      <c r="B1526" s="7">
+        <v>4098248</v>
+      </c>
+      <c r="C1526" t="s">
+        <v>4375</v>
+      </c>
+      <c r="D1526" t="s">
+        <v>203</v>
+      </c>
+      <c r="E1526" t="s">
+        <v>236</v>
+      </c>
+      <c r="F1526" s="29">
+        <v>46181</v>
+      </c>
+      <c r="G1526" s="56">
+        <v>5.2326388888888888E-2</v>
+      </c>
+      <c r="H1526" s="174" t="s">
+        <v>815</v>
+      </c>
+      <c r="I1526" s="174" t="s">
+        <v>290</v>
+      </c>
+      <c r="J1526" s="63" t="s">
+        <v>4376</v>
+      </c>
+      <c r="K1526">
+        <v>1527</v>
+      </c>
+      <c r="M1526" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1526" t="s">
+        <v>4383</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1527">
+        <v>87</v>
+      </c>
+      <c r="B1527" s="7">
+        <v>3436073</v>
+      </c>
+      <c r="C1527" t="s">
+        <v>720</v>
+      </c>
+      <c r="D1527" t="s">
+        <v>451</v>
+      </c>
+      <c r="E1527" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F1527" s="29">
+        <v>46180</v>
+      </c>
+      <c r="G1527" s="56">
+        <v>5.226851851851852E-2</v>
+      </c>
+      <c r="H1527" s="174" t="s">
+        <v>4377</v>
+      </c>
+      <c r="I1527" s="174" t="s">
+        <v>290</v>
+      </c>
+      <c r="J1527" s="63" t="s">
+        <v>4378</v>
+      </c>
+      <c r="K1527">
+        <v>1528</v>
+      </c>
+      <c r="M1527" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1527" t="s">
+        <v>4384</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1528">
+        <v>87</v>
+      </c>
+      <c r="B1528" s="7">
+        <v>8994754</v>
+      </c>
+      <c r="C1528" t="s">
+        <v>3964</v>
+      </c>
+      <c r="D1528" t="s">
+        <v>460</v>
+      </c>
+      <c r="E1528" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1528" s="29">
+        <v>46181</v>
+      </c>
+      <c r="G1528" s="56">
+        <v>9.9340277777777777E-2</v>
+      </c>
+      <c r="H1528" s="174" t="s">
+        <v>4379</v>
+      </c>
+      <c r="I1528" s="174" t="s">
+        <v>290</v>
+      </c>
+      <c r="J1528" s="63" t="s">
+        <v>4380</v>
+      </c>
+      <c r="K1528">
+        <v>1529</v>
+      </c>
+      <c r="M1528" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1528" t="s">
+        <v>4385</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1529">
+        <v>87</v>
+      </c>
+      <c r="B1529" s="7">
+        <v>5216712</v>
+      </c>
+      <c r="C1529" t="s">
+        <v>720</v>
+      </c>
+      <c r="D1529" t="s">
+        <v>223</v>
+      </c>
+      <c r="E1529" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F1529" s="29">
+        <v>46182</v>
+      </c>
+      <c r="G1529" s="56">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="H1529" s="174" t="s">
+        <v>805</v>
+      </c>
+      <c r="I1529" s="174" t="s">
+        <v>290</v>
+      </c>
+      <c r="J1529" s="63" t="s">
+        <v>4381</v>
+      </c>
+      <c r="K1529">
+        <v>1530</v>
+      </c>
+      <c r="M1529" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1529" t="s">
+        <v>4386</v>
       </c>
     </row>
   </sheetData>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12663" uniqueCount="4387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12721" uniqueCount="4406">
   <si>
     <t>Ņ</t>
   </si>
@@ -13188,6 +13188,63 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1517143933686382783/id_X6.png?ex=6a3535e4&amp;is=6a33e464&amp;hm=b75102877861446da5cd1db57f2792ecbbaf5de0dfa6b1b8aa24dd91a1f9233a</t>
+  </si>
+  <si>
+    <t>X7</t>
+  </si>
+  <si>
+    <t>Integratordrive</t>
+  </si>
+  <si>
+    <t>X8</t>
+  </si>
+  <si>
+    <t>Field Gun</t>
+  </si>
+  <si>
+    <t>X9</t>
+  </si>
+  <si>
+    <t>X(</t>
+  </si>
+  <si>
+    <t>X)</t>
+  </si>
+  <si>
+    <t>YA</t>
+  </si>
+  <si>
+    <t>Kettle</t>
+  </si>
+  <si>
+    <t>Nest Guardian/Eliye Crasher</t>
+  </si>
+  <si>
+    <t>YB</t>
+  </si>
+  <si>
+    <t>Summoner/Exorcistor/Elite Crasher</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1520708766734090261/id_X7.png?ex=6a422de7&amp;is=6a40dc67&amp;hm=76c2b0fe52e1aa84ade5785aaa362c644bda18774621622bf26e74d4d3232bf6</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1520708858614513684/id_X8.png?ex=6a422dfd&amp;is=6a40dc7d&amp;hm=db5fac3ccf9cd284b8fed1907e7a5e7e3e04178216a0a4948688ce4a6fe928bd</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1520708915606847498/id_X9.png?ex=6a422e0a&amp;is=6a40dc8a&amp;hm=50efdde51a922bad3d37e0ad772aa9172e6cfdd4117446a86e572a750eaedb73</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1520709045818884147/id_X.png?ex=6a422e29&amp;is=6a40dca9&amp;hm=f6958dd1203214947c2c73245105bc44ebec5e1e04220f9a620e83ff1a9d8d0d</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1520709093143351316/id_X.png?ex=6a422e35&amp;is=6a40dcb5&amp;hm=0d666c31306bf3146813c0f9feba2ce8508073fe89dbe4ffcef7755ceaf52e69</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1520709350748979310/id_YA.png?ex=6a422e72&amp;is=6a40dcf2&amp;hm=6405bbbd476ba346fc7b87c9dfa0f4ea6afe2e02dc9723e5b38ab5f489aa5d54</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1520709400447422504/id_YB.png?ex=6a422e7e&amp;is=6a40dcfe&amp;hm=1d0d00eb91f28f5e38f745d2a0f055c4770ec43a9bbbaabbfd511f31f3d585dd</t>
   </si>
 </sst>
 </file>
@@ -13199,11 +13256,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="124" x14ac:knownFonts="1">
+  <fonts count="125" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -14100,118 +14164,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="175">
+  <cellXfs count="176">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="120" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="120" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="119" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="119" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="121" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="105" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="120" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="104" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="119" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="111" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="105" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="112" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="106" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="102" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="101" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="89" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="89" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="88" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="88" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="89" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="88" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="89" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="88" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="85" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="85" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="86" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="86" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="88" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="89" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="84" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="83" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="82" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="82" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="81" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="81" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14220,18 +14285,18 @@
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="58" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="59" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14245,14 +14310,14 @@
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14508,7 +14573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1529"/>
+  <dimension ref="A1:O1536"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -78013,6 +78078,290 @@
         <v>4386</v>
       </c>
     </row>
+    <row r="1530" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1530">
+        <v>88</v>
+      </c>
+      <c r="B1530" s="7">
+        <v>15356210</v>
+      </c>
+      <c r="C1530" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1530" t="s">
+        <v>691</v>
+      </c>
+      <c r="E1530" t="s">
+        <v>3428</v>
+      </c>
+      <c r="F1530" s="29">
+        <v>46145</v>
+      </c>
+      <c r="G1530" s="56">
+        <v>8.8784722222222223E-2</v>
+      </c>
+      <c r="H1530" s="175" t="s">
+        <v>811</v>
+      </c>
+      <c r="I1530" s="175" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1530" s="63" t="s">
+        <v>4387</v>
+      </c>
+      <c r="K1530">
+        <v>1531</v>
+      </c>
+      <c r="M1530" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1530" t="s">
+        <v>4399</v>
+      </c>
+    </row>
+    <row r="1531" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1531">
+        <v>88</v>
+      </c>
+      <c r="B1531" s="7">
+        <v>2932941</v>
+      </c>
+      <c r="C1531" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1531" t="s">
+        <v>4388</v>
+      </c>
+      <c r="E1531" t="s">
+        <v>3428</v>
+      </c>
+      <c r="F1531" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1531" s="56">
+        <v>3.3993055555555561E-2</v>
+      </c>
+      <c r="H1531" s="175" t="s">
+        <v>835</v>
+      </c>
+      <c r="I1531" s="175" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1531" s="63" t="s">
+        <v>4389</v>
+      </c>
+      <c r="K1531">
+        <v>1532</v>
+      </c>
+      <c r="M1531" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1531" t="s">
+        <v>4400</v>
+      </c>
+    </row>
+    <row r="1532" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1532">
+        <v>88</v>
+      </c>
+      <c r="B1532" s="7">
+        <v>3365510</v>
+      </c>
+      <c r="C1532" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1532" t="s">
+        <v>4390</v>
+      </c>
+      <c r="E1532" t="s">
+        <v>3428</v>
+      </c>
+      <c r="F1532" s="29">
+        <v>46122</v>
+      </c>
+      <c r="G1532" s="56">
+        <v>3.1458333333333331E-2</v>
+      </c>
+      <c r="H1532" s="175" t="s">
+        <v>830</v>
+      </c>
+      <c r="I1532" s="175" t="s">
+        <v>290</v>
+      </c>
+      <c r="J1532" s="63" t="s">
+        <v>4391</v>
+      </c>
+      <c r="K1532">
+        <v>1533</v>
+      </c>
+      <c r="M1532" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1532" t="s">
+        <v>4401</v>
+      </c>
+    </row>
+    <row r="1533" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1533">
+        <v>88</v>
+      </c>
+      <c r="B1533" s="7">
+        <v>7501979</v>
+      </c>
+      <c r="C1533" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1533" t="s">
+        <v>4395</v>
+      </c>
+      <c r="E1533" t="s">
+        <v>3428</v>
+      </c>
+      <c r="F1533" s="29">
+        <v>46090</v>
+      </c>
+      <c r="G1533" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1533" s="175" t="s">
+        <v>811</v>
+      </c>
+      <c r="I1533" s="175" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1533" s="63" t="s">
+        <v>4392</v>
+      </c>
+      <c r="K1533">
+        <v>1534</v>
+      </c>
+      <c r="M1533" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1533" t="s">
+        <v>4402</v>
+      </c>
+    </row>
+    <row r="1534" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1534">
+        <v>88</v>
+      </c>
+      <c r="B1534" s="7">
+        <v>4106987</v>
+      </c>
+      <c r="C1534" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1534" t="s">
+        <v>627</v>
+      </c>
+      <c r="E1534" t="s">
+        <v>3428</v>
+      </c>
+      <c r="F1534" s="29">
+        <v>46069</v>
+      </c>
+      <c r="G1534" s="56">
+        <v>3.8865740740740742E-2</v>
+      </c>
+      <c r="H1534" s="175" t="s">
+        <v>1139</v>
+      </c>
+      <c r="I1534" s="175" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1534" s="63" t="s">
+        <v>4393</v>
+      </c>
+      <c r="K1534">
+        <v>1535</v>
+      </c>
+      <c r="M1534" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1534" t="s">
+        <v>4403</v>
+      </c>
+    </row>
+    <row r="1535" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1535">
+        <v>88</v>
+      </c>
+      <c r="B1535" s="7">
+        <v>4096660</v>
+      </c>
+      <c r="C1535" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1535" t="s">
+        <v>585</v>
+      </c>
+      <c r="E1535" t="s">
+        <v>3428</v>
+      </c>
+      <c r="F1535" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1535" s="56">
+        <v>3.4189814814814819E-2</v>
+      </c>
+      <c r="H1535" s="175" t="s">
+        <v>4396</v>
+      </c>
+      <c r="I1535" s="175" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1535" s="63" t="s">
+        <v>4394</v>
+      </c>
+      <c r="K1535">
+        <v>1536</v>
+      </c>
+      <c r="M1535" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1535" t="s">
+        <v>4404</v>
+      </c>
+    </row>
+    <row r="1536" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1536">
+        <v>88</v>
+      </c>
+      <c r="B1536" s="7">
+        <v>4018708</v>
+      </c>
+      <c r="C1536" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1536" t="s">
+        <v>627</v>
+      </c>
+      <c r="E1536" t="s">
+        <v>3428</v>
+      </c>
+      <c r="F1536" s="29">
+        <v>46069</v>
+      </c>
+      <c r="G1536" s="56">
+        <v>3.6145833333333328E-2</v>
+      </c>
+      <c r="H1536" s="175" t="s">
+        <v>4398</v>
+      </c>
+      <c r="J1536" s="63" t="s">
+        <v>4397</v>
+      </c>
+      <c r="K1536">
+        <v>1537</v>
+      </c>
+      <c r="M1536" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1536" t="s">
+        <v>4405</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N1">
     <sortState ref="A2:N1515">

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12721" uniqueCount="4406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12754" uniqueCount="4414">
   <si>
     <t>Ņ</t>
   </si>
@@ -13245,6 +13245,30 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1520709400447422504/id_YB.png?ex=6a422e7e&amp;is=6a40dcfe&amp;hm=1d0d00eb91f28f5e38f745d2a0f055c4770ec43a9bbbaabbfd511f31f3d585dd</t>
+  </si>
+  <si>
+    <t>YC</t>
+  </si>
+  <si>
+    <t>YD</t>
+  </si>
+  <si>
+    <t>YE</t>
+  </si>
+  <si>
+    <t>YF</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1522979270547476560/id_YC.png?ex=6a4a7079&amp;is=6a491ef9&amp;hm=4aff1ab1626e149ae013894612b5f56491e9272ac07574d096208eb969558605</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1522979362666840416/id_YD.jpg?ex=6a4a708f&amp;is=6a491f0f&amp;hm=3d044ab06d50e092f3afaa48be3df212bfa5c348dacf9bd03d7cd85b71844863</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1522979436805488802/id_YE.png?ex=6a4a70a1&amp;is=6a491f21&amp;hm=626aeb8008320ee695bf9e6796cc013185a1231c8070c83f836a613a0e689adb</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1522979512197841008/id_YF.png?ex=6a4a70b3&amp;is=6a491f33&amp;hm=c7a3a7205e45e8adc8717163e68a74a10b0442dfa729b0877762202b2bc120a3</t>
   </si>
 </sst>
 </file>
@@ -13256,11 +13280,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="125" x14ac:knownFonts="1">
+  <fonts count="126" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -14164,118 +14195,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="176">
+  <cellXfs count="177">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="122" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="120" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="119" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="122" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="106" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="121" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="105" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="120" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="112" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="106" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="113" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="107" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="103" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="102" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="90" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="90" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="89" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="89" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="90" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="89" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="90" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="89" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="86" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="86" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="87" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="87" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="89" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="90" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="85" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="84" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="83" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="83" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="82" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="82" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14284,18 +14316,18 @@
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="66" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="66" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="59" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="60" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14309,14 +14341,14 @@
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14573,7 +14605,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1536"/>
+  <dimension ref="A1:O1542"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -78349,6 +78381,9 @@
       <c r="H1536" s="175" t="s">
         <v>4398</v>
       </c>
+      <c r="I1536" s="176" t="s">
+        <v>806</v>
+      </c>
       <c r="J1536" s="63" t="s">
         <v>4397</v>
       </c>
@@ -78360,6 +78395,180 @@
       </c>
       <c r="N1536" t="s">
         <v>4405</v>
+      </c>
+    </row>
+    <row r="1537" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1537">
+        <v>89</v>
+      </c>
+      <c r="B1537" s="7">
+        <v>8456693</v>
+      </c>
+      <c r="C1537" t="s">
+        <v>236</v>
+      </c>
+      <c r="D1537" t="s">
+        <v>119</v>
+      </c>
+      <c r="E1537" t="s">
+        <v>236</v>
+      </c>
+      <c r="F1537" s="29">
+        <v>46207</v>
+      </c>
+      <c r="G1537" s="56">
+        <v>6.5578703703703708E-2</v>
+      </c>
+      <c r="H1537" s="176" t="s">
+        <v>885</v>
+      </c>
+      <c r="I1537" s="176" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1537" s="63" t="s">
+        <v>4406</v>
+      </c>
+      <c r="K1537">
+        <v>1538</v>
+      </c>
+      <c r="M1537" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1537" t="s">
+        <v>4410</v>
+      </c>
+    </row>
+    <row r="1538" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1538">
+        <v>89</v>
+      </c>
+      <c r="B1538" s="7">
+        <v>17414236</v>
+      </c>
+      <c r="C1538" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1538" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1538" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1538" s="29">
+        <v>46207</v>
+      </c>
+      <c r="G1538" s="56">
+        <v>0.10415509259259259</v>
+      </c>
+      <c r="H1538" s="176" t="s">
+        <v>1239</v>
+      </c>
+      <c r="I1538" s="176" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1538" s="63" t="s">
+        <v>4407</v>
+      </c>
+      <c r="K1538">
+        <v>1539</v>
+      </c>
+      <c r="M1538" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1538" t="s">
+        <v>4411</v>
+      </c>
+    </row>
+    <row r="1539" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1539">
+        <v>89</v>
+      </c>
+      <c r="B1539" s="7">
+        <v>16168740</v>
+      </c>
+      <c r="C1539" t="s">
+        <v>720</v>
+      </c>
+      <c r="D1539" t="s">
+        <v>372</v>
+      </c>
+      <c r="E1539" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F1539" s="29">
+        <v>46207</v>
+      </c>
+      <c r="G1539" s="56">
+        <v>0.16452546296296297</v>
+      </c>
+      <c r="H1539" s="176" t="s">
+        <v>815</v>
+      </c>
+      <c r="I1539" s="176" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1539" s="63" t="s">
+        <v>4408</v>
+      </c>
+      <c r="K1539">
+        <v>1540</v>
+      </c>
+      <c r="M1539" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1539" t="s">
+        <v>4412</v>
+      </c>
+    </row>
+    <row r="1540" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1540">
+        <v>89</v>
+      </c>
+      <c r="B1540" s="7">
+        <v>33158458</v>
+      </c>
+      <c r="C1540" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1540" t="s">
+        <v>79</v>
+      </c>
+      <c r="E1540" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1540" s="29">
+        <v>46207</v>
+      </c>
+      <c r="G1540" s="56">
+        <v>0.34974537037037035</v>
+      </c>
+      <c r="H1540" s="176" t="s">
+        <v>1860</v>
+      </c>
+      <c r="I1540" s="176" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1540" s="63" t="s">
+        <v>4409</v>
+      </c>
+      <c r="K1540">
+        <v>1541</v>
+      </c>
+      <c r="M1540" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1540" t="s">
+        <v>4413</v>
+      </c>
+    </row>
+    <row r="1541" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1541">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="1542" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1542">
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12754" uniqueCount="4414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12787" uniqueCount="4424">
   <si>
     <t>Ņ</t>
   </si>
@@ -13269,6 +13269,36 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1522979512197841008/id_YF.png?ex=6a4a70b3&amp;is=6a491f33&amp;hm=c7a3a7205e45e8adc8717163e68a74a10b0442dfa729b0877762202b2bc120a3</t>
+  </si>
+  <si>
+    <t>YG</t>
+  </si>
+  <si>
+    <t>YH</t>
+  </si>
+  <si>
+    <t>YI</t>
+  </si>
+  <si>
+    <t>kotya .:</t>
+  </si>
+  <si>
+    <t>mogi</t>
+  </si>
+  <si>
+    <t>YJ</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1523024194814742568/id_YG.png?ex=6a4a9a50&amp;is=6a4948d0&amp;hm=2b2ae6e7a36df2c52b9b4128936804f781216d8285aaa17184aedd41f8b2deb1</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1523024374171701389/id_YH.png?ex=6a4a9a7b&amp;is=6a4948fb&amp;hm=2699d56195380cf6d788cf86d47bebf1cbf415a6253c12286e7a87c19523988c</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1523024521571860520/id_YI.png?ex=6a4a9a9e&amp;is=6a49491e&amp;hm=fde4da0aa8e485ac08c8b0b22ad7b7336f4820cde7b0ddb60413449715a873be</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1523024722072174812/id_YJ.png?ex=6a4a9ace&amp;is=6a49494e&amp;hm=bb5c3df686831f271e58b2143a422084b1c88c2e295d8f484522c888f0e59855</t>
   </si>
 </sst>
 </file>
@@ -13280,11 +13310,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="126" x14ac:knownFonts="1">
+  <fonts count="127" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -14195,118 +14232,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="177">
+  <cellXfs count="178">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="123" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="122" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="122" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="120" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="119" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="123" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="107" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="122" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="106" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="121" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="113" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="107" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="114" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="108" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="104" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="103" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="91" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="91" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="90" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="90" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="91" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="90" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="91" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="90" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="87" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="87" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="88" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="88" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="90" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="91" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="86" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="126" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="85" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="84" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="84" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="83" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="83" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14315,18 +14353,18 @@
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="67" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="67" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="66" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="66" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="60" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="61" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14340,14 +14378,14 @@
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14605,7 +14643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1542"/>
+  <dimension ref="A1:O1544"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -78565,10 +78603,164 @@
       <c r="A1541">
         <v>89</v>
       </c>
+      <c r="B1541" s="7">
+        <v>10306682</v>
+      </c>
+      <c r="C1541" t="s">
+        <v>236</v>
+      </c>
+      <c r="D1541" t="s">
+        <v>119</v>
+      </c>
+      <c r="E1541" t="s">
+        <v>236</v>
+      </c>
+      <c r="F1541" s="29">
+        <v>46207</v>
+      </c>
+      <c r="G1541" s="56">
+        <v>0.32843749999999999</v>
+      </c>
+      <c r="H1541" s="177" t="s">
+        <v>815</v>
+      </c>
+      <c r="I1541" s="177" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1541" s="63" t="s">
+        <v>4414</v>
+      </c>
+      <c r="K1541">
+        <v>1542</v>
+      </c>
+      <c r="M1541" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1541" t="s">
+        <v>4420</v>
+      </c>
     </row>
     <row r="1542" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1542">
         <v>89</v>
+      </c>
+      <c r="B1542" s="7">
+        <v>19344631</v>
+      </c>
+      <c r="C1542" t="s">
+        <v>3795</v>
+      </c>
+      <c r="D1542" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1542" t="s">
+        <v>731</v>
+      </c>
+      <c r="F1542" s="29">
+        <v>46176</v>
+      </c>
+      <c r="G1542" s="56">
+        <v>9.7905092592592599E-2</v>
+      </c>
+      <c r="H1542" s="177" t="s">
+        <v>1239</v>
+      </c>
+      <c r="I1542" s="177" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1542" s="63" t="s">
+        <v>4415</v>
+      </c>
+      <c r="K1542">
+        <v>1543</v>
+      </c>
+      <c r="M1542" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1542" t="s">
+        <v>4421</v>
+      </c>
+    </row>
+    <row r="1543" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1543">
+        <v>89</v>
+      </c>
+      <c r="B1543" s="7">
+        <v>25680447</v>
+      </c>
+      <c r="C1543" t="s">
+        <v>4417</v>
+      </c>
+      <c r="D1543" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1543" t="s">
+        <v>731</v>
+      </c>
+      <c r="F1543" s="29">
+        <v>46207</v>
+      </c>
+      <c r="G1543" s="56">
+        <v>0.18515046296296298</v>
+      </c>
+      <c r="H1543" s="177" t="s">
+        <v>817</v>
+      </c>
+      <c r="I1543" s="177" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1543" s="63" t="s">
+        <v>4416</v>
+      </c>
+      <c r="K1543">
+        <v>1544</v>
+      </c>
+      <c r="M1543" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1543" t="s">
+        <v>4422</v>
+      </c>
+    </row>
+    <row r="1544" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1544">
+        <v>89</v>
+      </c>
+      <c r="B1544" s="7">
+        <v>42130000</v>
+      </c>
+      <c r="C1544" t="s">
+        <v>4418</v>
+      </c>
+      <c r="D1544" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1544" t="s">
+        <v>4418</v>
+      </c>
+      <c r="F1544" s="29">
+        <v>46207</v>
+      </c>
+      <c r="G1544" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1544" s="177" t="s">
+        <v>817</v>
+      </c>
+      <c r="I1544" s="177" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1544" s="63" t="s">
+        <v>4419</v>
+      </c>
+      <c r="K1544">
+        <v>1545</v>
+      </c>
+      <c r="M1544" s="57" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1544" t="s">
+        <v>4423</v>
       </c>
     </row>
   </sheetData>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12787" uniqueCount="4424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12843" uniqueCount="4446">
   <si>
     <t>Ņ</t>
   </si>
@@ -13299,6 +13299,72 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1523024722072174812/id_YJ.png?ex=6a4a9ace&amp;is=6a49494e&amp;hm=bb5c3df686831f271e58b2143a422084b1c88c2e295d8f484522c888f0e59855</t>
+  </si>
+  <si>
+    <t>legendary florida</t>
+  </si>
+  <si>
+    <t>Freyja/Nest Guardian</t>
+  </si>
+  <si>
+    <t>YK</t>
+  </si>
+  <si>
+    <t>YL</t>
+  </si>
+  <si>
+    <t>Kronos/Freyja/Nest Guardian/Ragnarok</t>
+  </si>
+  <si>
+    <t>Offstentarrium &lt;3</t>
+  </si>
+  <si>
+    <t>Auto-Zipper</t>
+  </si>
+  <si>
+    <t>YM</t>
+  </si>
+  <si>
+    <t>YN</t>
+  </si>
+  <si>
+    <t>YO</t>
+  </si>
+  <si>
+    <t>Theia/Summoner</t>
+  </si>
+  <si>
+    <t>456 Solar</t>
+  </si>
+  <si>
+    <t>YP</t>
+  </si>
+  <si>
+    <t>YQ</t>
+  </si>
+  <si>
+    <t>[o]</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1523259465996959764/id_YK.png?ex=6a4b756d&amp;is=6a4a23ed&amp;hm=e7fde05fa1bd11eb7e5321e5bb62f56aa5977d8b565fa205ad613e3d1e025e8d</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1523259536373190669/id_YL.png?ex=6a4b757e&amp;is=6a4a23fe&amp;hm=5e464215481b51d7d49be68385dc9a5855cc0b7409d9072198469e41268c186c</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1523259609119457420/id_YM.png?ex=6a4b758f&amp;is=6a4a240f&amp;hm=0b488fa69a10c4c1b3802670fa6de2d49b980d31531880c29974e95934c26803</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1523259734134882374/id_YN.jpg?ex=6a4b75ad&amp;is=6a4a242d&amp;hm=071f81a88634d8ae8247a10f05434d9704ac7d4ad013574e956c9bba8765dc84</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1523259839915098162/id_YO.png?ex=6a4b75c6&amp;is=6a4a2446&amp;hm=a38d18a92b3ea0827d3eee8d482e1692b8f0f022604230f7ed45c841bae25d59</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1523259910572216371/id_YP.png?ex=6a4b75d7&amp;is=6a4a2457&amp;hm=f8b83bd65be94a13e73e9c1a000da848f0636b77b75476fd4da10d3e3ed399a6</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1523259975714078771/id_YQ.png?ex=6a4b75e7&amp;is=6a4a2467&amp;hm=c406483c83fe301867a9dbc37d1a9a07fe2b7c241b74b234812c7ea2b9db4a56</t>
   </si>
 </sst>
 </file>
@@ -13310,11 +13376,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="127" x14ac:knownFonts="1">
+  <fonts count="128" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -14232,118 +14305,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="126" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="178">
+  <cellXfs count="179">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="124" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="123" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="123" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="122" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="120" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="120" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="119" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="119" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="124" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="108" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="123" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="107" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="122" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="114" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="108" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="115" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="109" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="105" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="104" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="92" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="92" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="91" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="91" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="92" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="91" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="92" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="91" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="88" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="88" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="89" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="89" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="91" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="92" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="87" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="127" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="86" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="126" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="85" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="85" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="84" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="84" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14352,18 +14426,18 @@
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="68" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="68" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="67" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="67" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="61" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="62" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14377,14 +14451,14 @@
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14643,7 +14717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1544"/>
+  <dimension ref="A1:O1552"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -78763,6 +78837,298 @@
         <v>4423</v>
       </c>
     </row>
+    <row r="1545" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1545">
+        <v>90</v>
+      </c>
+      <c r="B1545" s="7">
+        <v>18110061</v>
+      </c>
+      <c r="C1545" t="s">
+        <v>4424</v>
+      </c>
+      <c r="D1545" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1545" t="s">
+        <v>218</v>
+      </c>
+      <c r="F1545" s="29">
+        <v>46207</v>
+      </c>
+      <c r="G1545" s="56">
+        <v>0.15687500000000001</v>
+      </c>
+      <c r="H1545" s="178" t="s">
+        <v>4425</v>
+      </c>
+      <c r="I1545" s="178" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1545" s="63" t="s">
+        <v>4426</v>
+      </c>
+      <c r="K1545">
+        <v>1546</v>
+      </c>
+      <c r="M1545" s="178" t="s">
+        <v>4438</v>
+      </c>
+      <c r="N1545" t="s">
+        <v>4439</v>
+      </c>
+    </row>
+    <row r="1546" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1546">
+        <v>90</v>
+      </c>
+      <c r="B1546" s="7">
+        <v>13434712</v>
+      </c>
+      <c r="C1546" t="s">
+        <v>720</v>
+      </c>
+      <c r="D1546" t="s">
+        <v>424</v>
+      </c>
+      <c r="E1546" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F1546" s="29">
+        <v>46207</v>
+      </c>
+      <c r="G1546" s="56">
+        <v>7.211805555555556E-2</v>
+      </c>
+      <c r="H1546" s="178" t="s">
+        <v>4428</v>
+      </c>
+      <c r="I1546" s="178" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1546" s="63" t="s">
+        <v>4427</v>
+      </c>
+      <c r="K1546">
+        <v>1547</v>
+      </c>
+      <c r="M1546" s="178" t="s">
+        <v>4438</v>
+      </c>
+      <c r="N1546" t="s">
+        <v>4440</v>
+      </c>
+    </row>
+    <row r="1547" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1547">
+        <v>90</v>
+      </c>
+      <c r="B1547" s="7">
+        <v>4392116</v>
+      </c>
+      <c r="C1547" t="s">
+        <v>4429</v>
+      </c>
+      <c r="D1547" t="s">
+        <v>4430</v>
+      </c>
+      <c r="E1547" t="s">
+        <v>648</v>
+      </c>
+      <c r="F1547" s="29">
+        <v>46207</v>
+      </c>
+      <c r="G1547" s="56">
+        <v>4.0428240740740744E-2</v>
+      </c>
+      <c r="H1547" s="178" t="s">
+        <v>832</v>
+      </c>
+      <c r="I1547" s="178" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1547" s="63" t="s">
+        <v>4431</v>
+      </c>
+      <c r="K1547">
+        <v>1548</v>
+      </c>
+      <c r="M1547" s="178" t="s">
+        <v>4438</v>
+      </c>
+      <c r="N1547" t="s">
+        <v>4441</v>
+      </c>
+    </row>
+    <row r="1548" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1548">
+        <v>90</v>
+      </c>
+      <c r="B1548" s="7">
+        <v>6376347</v>
+      </c>
+      <c r="C1548" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1548" t="s">
+        <v>468</v>
+      </c>
+      <c r="E1548" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1548" s="29">
+        <v>46208</v>
+      </c>
+      <c r="G1548" s="56">
+        <v>5.1886574074074071E-2</v>
+      </c>
+      <c r="H1548" s="178" t="s">
+        <v>4434</v>
+      </c>
+      <c r="I1548" s="178" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1548" s="63" t="s">
+        <v>4432</v>
+      </c>
+      <c r="K1548">
+        <v>1549</v>
+      </c>
+      <c r="M1548" s="178" t="s">
+        <v>4438</v>
+      </c>
+      <c r="N1548" t="s">
+        <v>4442</v>
+      </c>
+    </row>
+    <row r="1549" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1549">
+        <v>90</v>
+      </c>
+      <c r="B1549" s="7">
+        <v>20826460</v>
+      </c>
+      <c r="C1549" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1549" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1549" t="s">
+        <v>4435</v>
+      </c>
+      <c r="F1549" s="29">
+        <v>46208</v>
+      </c>
+      <c r="G1549" s="56">
+        <v>0.14120370370370369</v>
+      </c>
+      <c r="H1549" s="178" t="s">
+        <v>811</v>
+      </c>
+      <c r="I1549" s="178" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1549" s="63" t="s">
+        <v>4433</v>
+      </c>
+      <c r="K1549">
+        <v>1550</v>
+      </c>
+      <c r="M1549" s="178" t="s">
+        <v>4438</v>
+      </c>
+      <c r="N1549" t="s">
+        <v>4443</v>
+      </c>
+    </row>
+    <row r="1550" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1550">
+        <v>90</v>
+      </c>
+      <c r="B1550" s="7">
+        <v>2588583</v>
+      </c>
+      <c r="C1550" t="s">
+        <v>325</v>
+      </c>
+      <c r="D1550" t="s">
+        <v>637</v>
+      </c>
+      <c r="E1550" t="s">
+        <v>433</v>
+      </c>
+      <c r="F1550" s="29">
+        <v>46208</v>
+      </c>
+      <c r="G1550" s="56">
+        <v>2.0578703703703703E-2</v>
+      </c>
+      <c r="H1550" s="178" t="s">
+        <v>965</v>
+      </c>
+      <c r="I1550" s="178" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1550" s="63" t="s">
+        <v>4436</v>
+      </c>
+      <c r="K1550">
+        <v>1551</v>
+      </c>
+      <c r="M1550" s="178" t="s">
+        <v>4438</v>
+      </c>
+      <c r="N1550" t="s">
+        <v>4444</v>
+      </c>
+    </row>
+    <row r="1551" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1551">
+        <v>90</v>
+      </c>
+      <c r="B1551" s="7">
+        <v>13329209</v>
+      </c>
+      <c r="C1551" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1551" t="s">
+        <v>1993</v>
+      </c>
+      <c r="E1551" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1551" s="29">
+        <v>46208</v>
+      </c>
+      <c r="G1551" s="56">
+        <v>0.10957175925925926</v>
+      </c>
+      <c r="H1551" s="178" t="s">
+        <v>1241</v>
+      </c>
+      <c r="I1551" s="178" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1551" s="63" t="s">
+        <v>4437</v>
+      </c>
+      <c r="K1551">
+        <v>1552</v>
+      </c>
+      <c r="M1551" s="178" t="s">
+        <v>4438</v>
+      </c>
+      <c r="N1551" t="s">
+        <v>4445</v>
+      </c>
+    </row>
+    <row r="1552" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1552">
+        <v>90</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N1">
     <sortState ref="A2:N1515">

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12843" uniqueCount="4446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12894" uniqueCount="4457">
   <si>
     <t>Ņ</t>
   </si>
@@ -13365,6 +13365,39 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1523259975714078771/id_YQ.png?ex=6a4b75e7&amp;is=6a4a2467&amp;hm=c406483c83fe301867a9dbc37d1a9a07fe2b7c241b74b234812c7ea2b9db4a56</t>
+  </si>
+  <si>
+    <t>Nyx/Eris</t>
+  </si>
+  <si>
+    <t>YT</t>
+  </si>
+  <si>
+    <t>YR</t>
+  </si>
+  <si>
+    <t>YS</t>
+  </si>
+  <si>
+    <t>YU</t>
+  </si>
+  <si>
+    <t>un(racist) doctor</t>
+  </si>
+  <si>
+    <t>YV</t>
+  </si>
+  <si>
+    <t>YW</t>
+  </si>
+  <si>
+    <t>LC/Lmao</t>
+  </si>
+  <si>
+    <t>YX</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1523391148494688266/id_YR.png?ex=6a4bf011&amp;is=6a4a9e91&amp;hm=83789a14262d883853971cebc650684188b4928b67aa4958880b2328be3b11ff</t>
   </si>
 </sst>
 </file>
@@ -13376,11 +13409,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="128" x14ac:knownFonts="1">
+  <fonts count="129" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -14305,118 +14345,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="126" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="127" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="179">
+  <cellXfs count="180">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="126" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="125" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="124" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="124" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="123" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="122" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="120" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="119" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="125" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="109" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="124" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="108" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="123" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="115" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="109" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="116" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="110" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="106" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="105" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="93" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="93" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="92" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="92" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="93" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="92" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="93" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="92" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="89" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="89" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="90" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="90" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="92" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="93" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="126" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="88" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="128" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="87" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="127" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="86" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="86" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="85" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="85" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14425,18 +14466,18 @@
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="69" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="69" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="68" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="68" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="62" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="63" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14450,14 +14491,14 @@
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14717,7 +14758,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1552"/>
+  <dimension ref="A1:O1558"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -61272,7 +61313,7 @@
       <c r="B1117" s="7">
         <v>51447973</v>
       </c>
-      <c r="C1117" s="101" t="s">
+      <c r="C1117" s="179" t="s">
         <v>1752</v>
       </c>
       <c r="D1117" s="101" t="s">
@@ -79127,6 +79168,270 @@
     <row r="1552" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1552">
         <v>90</v>
+      </c>
+      <c r="B1552" s="7">
+        <v>23825548</v>
+      </c>
+      <c r="C1552" t="s">
+        <v>720</v>
+      </c>
+      <c r="D1552" t="s">
+        <v>424</v>
+      </c>
+      <c r="E1552" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F1552" s="29">
+        <v>46208</v>
+      </c>
+      <c r="G1552" s="56">
+        <v>0.12238425925925926</v>
+      </c>
+      <c r="H1552" s="179" t="s">
+        <v>4446</v>
+      </c>
+      <c r="I1552" s="179" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1552" s="63" t="s">
+        <v>4448</v>
+      </c>
+      <c r="K1552">
+        <v>1553</v>
+      </c>
+      <c r="M1552" s="179" t="s">
+        <v>4438</v>
+      </c>
+      <c r="N1552" t="s">
+        <v>4456</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1553">
+        <v>90</v>
+      </c>
+      <c r="B1553" s="7">
+        <v>18566195</v>
+      </c>
+      <c r="C1553" t="s">
+        <v>720</v>
+      </c>
+      <c r="D1553" t="s">
+        <v>277</v>
+      </c>
+      <c r="E1553" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F1553" s="29">
+        <v>46208</v>
+      </c>
+      <c r="G1553" s="56">
+        <v>0.10565972222222221</v>
+      </c>
+      <c r="H1553" s="179" t="s">
+        <v>2286</v>
+      </c>
+      <c r="I1553" s="179" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1553" s="63" t="s">
+        <v>4449</v>
+      </c>
+      <c r="K1553">
+        <v>1554</v>
+      </c>
+      <c r="M1553" s="179" t="s">
+        <v>4438</v>
+      </c>
+    </row>
+    <row r="1554" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1554">
+        <v>90</v>
+      </c>
+      <c r="B1554" s="7">
+        <v>7037358</v>
+      </c>
+      <c r="C1554" t="s">
+        <v>1752</v>
+      </c>
+      <c r="D1554" t="s">
+        <v>372</v>
+      </c>
+      <c r="E1554" t="s">
+        <v>1761</v>
+      </c>
+      <c r="F1554" s="29">
+        <v>46208</v>
+      </c>
+      <c r="G1554" s="56">
+        <v>6.6377314814814806E-2</v>
+      </c>
+      <c r="H1554" s="179" t="s">
+        <v>885</v>
+      </c>
+      <c r="I1554" s="179" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1554" s="63" t="s">
+        <v>4447</v>
+      </c>
+      <c r="K1554">
+        <v>1555</v>
+      </c>
+      <c r="M1554" s="179" t="s">
+        <v>4438</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1555">
+        <v>90</v>
+      </c>
+      <c r="B1555" s="7">
+        <v>34340000</v>
+      </c>
+      <c r="C1555" t="s">
+        <v>4418</v>
+      </c>
+      <c r="D1555" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1555" t="s">
+        <v>4418</v>
+      </c>
+      <c r="F1555" s="29">
+        <v>46208</v>
+      </c>
+      <c r="G1555" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1555" s="179" t="s">
+        <v>815</v>
+      </c>
+      <c r="I1555" s="179" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1555" s="63" t="s">
+        <v>4450</v>
+      </c>
+      <c r="K1555">
+        <v>1556</v>
+      </c>
+      <c r="M1555" s="179" t="s">
+        <v>4438</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1556">
+        <v>90</v>
+      </c>
+      <c r="B1556" s="7">
+        <v>15001077</v>
+      </c>
+      <c r="C1556" t="s">
+        <v>4451</v>
+      </c>
+      <c r="D1556" t="s">
+        <v>119</v>
+      </c>
+      <c r="E1556" t="s">
+        <v>236</v>
+      </c>
+      <c r="F1556" s="29">
+        <v>46208</v>
+      </c>
+      <c r="G1556" s="56">
+        <v>0.11548611111111111</v>
+      </c>
+      <c r="H1556" s="179" t="s">
+        <v>1560</v>
+      </c>
+      <c r="I1556" s="179" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1556" s="63" t="s">
+        <v>4452</v>
+      </c>
+      <c r="K1556">
+        <v>1557</v>
+      </c>
+      <c r="M1556" s="179" t="s">
+        <v>4438</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1557">
+        <v>90</v>
+      </c>
+      <c r="B1557" s="7">
+        <v>11018920</v>
+      </c>
+      <c r="C1557" t="s">
+        <v>4451</v>
+      </c>
+      <c r="D1557" t="s">
+        <v>628</v>
+      </c>
+      <c r="E1557" t="s">
+        <v>236</v>
+      </c>
+      <c r="F1557" s="29">
+        <v>46208</v>
+      </c>
+      <c r="G1557" s="56">
+        <v>4.7233796296296295E-2</v>
+      </c>
+      <c r="H1557" s="179" t="s">
+        <v>815</v>
+      </c>
+      <c r="I1557" s="179" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1557" s="63" t="s">
+        <v>4453</v>
+      </c>
+      <c r="K1557">
+        <v>1558</v>
+      </c>
+      <c r="M1557" s="179" t="s">
+        <v>4438</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1558">
+        <v>90</v>
+      </c>
+      <c r="B1558" s="7">
+        <v>10727262</v>
+      </c>
+      <c r="C1558" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1558" t="s">
+        <v>3861</v>
+      </c>
+      <c r="E1558" t="s">
+        <v>648</v>
+      </c>
+      <c r="F1558" s="29">
+        <v>46208</v>
+      </c>
+      <c r="G1558" s="56">
+        <v>6.1712962962962963E-2</v>
+      </c>
+      <c r="H1558" s="179" t="s">
+        <v>4454</v>
+      </c>
+      <c r="I1558" s="179" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1558" s="63" t="s">
+        <v>4455</v>
+      </c>
+      <c r="K1558">
+        <v>1559</v>
+      </c>
+      <c r="M1558" s="179" t="s">
+        <v>4438</v>
       </c>
     </row>
   </sheetData>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12894" uniqueCount="4457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12908" uniqueCount="4466">
   <si>
     <t>Ņ</t>
   </si>
@@ -13398,6 +13398,33 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1523391148494688266/id_YR.png?ex=6a4bf011&amp;is=6a4a9e91&amp;hm=83789a14262d883853971cebc650684188b4928b67aa4958880b2328be3b11ff</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1523391463952748645/id_YS.png?ex=6a4bf05c&amp;is=6a4a9edc&amp;hm=8ceaf5055aa336322be1f2d27cd0dc354e2e4e367606dc81097c03e2e9487e96</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1523391626880221214/id_YT.png?ex=6a4bf083&amp;is=6a4a9f03&amp;hm=eb308d347bd3b6988a3bacdeb8a4907e3502e35658f1f7911813d92ddd0c9386</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1523391734728626297/id_YU.png?ex=6a4bf09c&amp;is=6a4a9f1c&amp;hm=adfccbcce6af11d66aa36ac9926b5c5f957073023870816f00bf764acce93f7e</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1523391792739909707/id_YV.png?ex=6a4bf0aa&amp;is=6a4a9f2a&amp;hm=55dbe108fd01be8dad4d04617997f636e35efbf1d420bc8b24650ef50f7d2c72</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1523391891331088595/id_YW.png?ex=6a4bf0c2&amp;is=6a4a9f42&amp;hm=8948a714cb8aabd7c39fd7e6dd437c9ff031f7d5418520388f1c72ccb568ccb5</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1523391974177116280/id_YX.png?ex=6a4bf0d5&amp;is=6a4a9f55&amp;hm=6e264b8a17cc22ace25c67f1399443df31e3aefe27ef3ab7a11d686714252cee</t>
+  </si>
+  <si>
+    <t>nliaxtiba</t>
+  </si>
+  <si>
+    <t>YY</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1523393265636868186/id_YY.png?ex=6a4bf209&amp;is=6a4aa089&amp;hm=3343fdb7622e0fd83a6cb4806c13fd9974832d4264a4f99c5b129e5d7f921199</t>
   </si>
 </sst>
 </file>
@@ -14758,7 +14785,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1558"/>
+  <dimension ref="A1:O1559"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -79206,7 +79233,7 @@
         <v>4456</v>
       </c>
     </row>
-    <row r="1553" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1553" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1553">
         <v>90</v>
       </c>
@@ -79243,8 +79270,11 @@
       <c r="M1553" s="179" t="s">
         <v>4438</v>
       </c>
-    </row>
-    <row r="1554" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N1553" t="s">
+        <v>4457</v>
+      </c>
+    </row>
+    <row r="1554" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1554">
         <v>90</v>
       </c>
@@ -79281,8 +79311,11 @@
       <c r="M1554" s="179" t="s">
         <v>4438</v>
       </c>
-    </row>
-    <row r="1555" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N1554" t="s">
+        <v>4458</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1555">
         <v>90</v>
       </c>
@@ -79319,8 +79352,11 @@
       <c r="M1555" s="179" t="s">
         <v>4438</v>
       </c>
-    </row>
-    <row r="1556" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N1555" t="s">
+        <v>4459</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1556">
         <v>90</v>
       </c>
@@ -79357,8 +79393,11 @@
       <c r="M1556" s="179" t="s">
         <v>4438</v>
       </c>
-    </row>
-    <row r="1557" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N1556" t="s">
+        <v>4460</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1557">
         <v>90</v>
       </c>
@@ -79395,8 +79434,11 @@
       <c r="M1557" s="179" t="s">
         <v>4438</v>
       </c>
-    </row>
-    <row r="1558" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N1557" t="s">
+        <v>4461</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1558">
         <v>90</v>
       </c>
@@ -79432,6 +79474,50 @@
       </c>
       <c r="M1558" s="179" t="s">
         <v>4438</v>
+      </c>
+      <c r="N1558" t="s">
+        <v>4462</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1559">
+        <v>90</v>
+      </c>
+      <c r="B1559" s="7">
+        <v>8021713</v>
+      </c>
+      <c r="C1559" t="s">
+        <v>4463</v>
+      </c>
+      <c r="D1559" t="s">
+        <v>501</v>
+      </c>
+      <c r="E1559" t="s">
+        <v>648</v>
+      </c>
+      <c r="F1559" s="29">
+        <v>46208</v>
+      </c>
+      <c r="G1559" s="56">
+        <v>5.2071759259259255E-2</v>
+      </c>
+      <c r="H1559" s="179" t="s">
+        <v>825</v>
+      </c>
+      <c r="I1559" s="179" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1559" s="63" t="s">
+        <v>4464</v>
+      </c>
+      <c r="K1559">
+        <v>1560</v>
+      </c>
+      <c r="M1559" s="179" t="s">
+        <v>4438</v>
+      </c>
+      <c r="N1559" t="s">
+        <v>4465</v>
       </c>
     </row>
   </sheetData>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12908" uniqueCount="4466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12940" uniqueCount="4476">
   <si>
     <t>Ņ</t>
   </si>
@@ -13418,13 +13418,43 @@
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1523391974177116280/id_YX.png?ex=6a4bf0d5&amp;is=6a4a9f55&amp;hm=6e264b8a17cc22ace25c67f1399443df31e3aefe27ef3ab7a11d686714252cee</t>
   </si>
   <si>
-    <t>nliaxtiba</t>
-  </si>
-  <si>
     <t>YY</t>
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1523393265636868186/id_YY.png?ex=6a4bf209&amp;is=6a4aa089&amp;hm=3343fdb7622e0fd83a6cb4806c13fd9974832d4264a4f99c5b129e5d7f921199</t>
+  </si>
+  <si>
+    <t>projectbulletstorm[base]</t>
+  </si>
+  <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t>ηλιαχτίδα &lt;3</t>
+  </si>
+  <si>
+    <t>YZ</t>
+  </si>
+  <si>
+    <t>Ya</t>
+  </si>
+  <si>
+    <t>Yb</t>
+  </si>
+  <si>
+    <t>Yc</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1523622656035913850/id_YZ.png?ex=6a4cc7ac&amp;is=6a4b762c&amp;hm=2be7bc0ec2f0d5284babacdc06b4ecc91312ce3605dface37e657757afb4e573</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1523622860785188884/id_Ya.png?ex=6a4cc7dd&amp;is=6a4b765d&amp;hm=3317bd8beb139a03fa21107de354d9b09ee6872de7ac3e28713615386503dad0</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1523622912802684968/id_Yb.png?ex=6a4cc7e9&amp;is=6a4b7669&amp;hm=8c8937adca4a22fe2a70c05ba1e617f273c7c0943c301ceacfe3fcf86f5c6c3f</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1523622955647500358/id_Yc.png?ex=6a4cc7f4&amp;is=6a4b7674&amp;hm=8b458e2bc3f4116be1336498719d7de97a9d10dcbd573b076061b1cb7bdf3f4d</t>
   </si>
 </sst>
 </file>
@@ -13436,11 +13466,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="129" x14ac:knownFonts="1">
+  <fonts count="130" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -14372,118 +14409,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="127" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="128" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="180">
+  <cellXfs count="182">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="127" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="126" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="126" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="125" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="125" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="124" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="123" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="122" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="120" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="119" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="126" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="110" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="125" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="109" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="124" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="116" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="110" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="117" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="111" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="107" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="106" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="94" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="94" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="93" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="93" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="94" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="93" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="94" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="93" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="90" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="90" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="91" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="91" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="93" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="94" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="127" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="89" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="88" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="128" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="87" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="87" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="86" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="86" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14492,18 +14530,18 @@
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="70" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="70" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="69" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="69" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="63" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14517,14 +14555,14 @@
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14569,6 +14607,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -14785,7 +14824,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1559"/>
+  <dimension ref="A1:O1563"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -78953,7 +78992,7 @@
       <c r="B1546" s="7">
         <v>13434712</v>
       </c>
-      <c r="C1546" t="s">
+      <c r="C1546" s="180" t="s">
         <v>720</v>
       </c>
       <c r="D1546" t="s">
@@ -79486,8 +79525,8 @@
       <c r="B1559" s="7">
         <v>8021713</v>
       </c>
-      <c r="C1559" t="s">
-        <v>4463</v>
+      <c r="C1559" s="180" t="s">
+        <v>4467</v>
       </c>
       <c r="D1559" t="s">
         <v>501</v>
@@ -79508,7 +79547,7 @@
         <v>806</v>
       </c>
       <c r="J1559" s="63" t="s">
-        <v>4464</v>
+        <v>4463</v>
       </c>
       <c r="K1559">
         <v>1560</v>
@@ -79517,7 +79556,171 @@
         <v>4438</v>
       </c>
       <c r="N1559" t="s">
+        <v>4464</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1560">
+        <v>91</v>
+      </c>
+      <c r="B1560" s="7">
+        <v>30281656</v>
+      </c>
+      <c r="C1560" t="s">
         <v>4465</v>
+      </c>
+      <c r="D1560" s="180" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1560" t="s">
+        <v>4466</v>
+      </c>
+      <c r="F1560" s="29">
+        <v>46208</v>
+      </c>
+      <c r="G1560" s="56">
+        <v>0.32047453703703704</v>
+      </c>
+      <c r="H1560" s="180" t="s">
+        <v>815</v>
+      </c>
+      <c r="I1560" s="180" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1560" s="181" t="s">
+        <v>4468</v>
+      </c>
+      <c r="K1560">
+        <v>1561</v>
+      </c>
+      <c r="M1560" s="179" t="s">
+        <v>4438</v>
+      </c>
+      <c r="N1560" t="s">
+        <v>4472</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1561">
+        <v>91</v>
+      </c>
+      <c r="B1561" s="7">
+        <v>13631084</v>
+      </c>
+      <c r="C1561" t="s">
+        <v>720</v>
+      </c>
+      <c r="D1561" s="180" t="s">
+        <v>424</v>
+      </c>
+      <c r="E1561" s="180" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F1561" s="29">
+        <v>46208</v>
+      </c>
+      <c r="G1561" s="56">
+        <v>6.039351851851852E-2</v>
+      </c>
+      <c r="H1561" s="180" t="s">
+        <v>832</v>
+      </c>
+      <c r="I1561" s="180" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1561" s="181" t="s">
+        <v>4469</v>
+      </c>
+      <c r="K1561">
+        <v>1562</v>
+      </c>
+      <c r="M1561" s="179" t="s">
+        <v>4438</v>
+      </c>
+      <c r="N1561" t="s">
+        <v>4473</v>
+      </c>
+    </row>
+    <row r="1562" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1562">
+        <v>91</v>
+      </c>
+      <c r="B1562" s="7">
+        <v>5396151</v>
+      </c>
+      <c r="C1562" s="180" t="s">
+        <v>236</v>
+      </c>
+      <c r="D1562" s="180" t="s">
+        <v>309</v>
+      </c>
+      <c r="E1562" s="180" t="s">
+        <v>236</v>
+      </c>
+      <c r="F1562" s="29">
+        <v>46158</v>
+      </c>
+      <c r="G1562" s="56">
+        <v>6.0798611111111116E-2</v>
+      </c>
+      <c r="H1562" s="180" t="s">
+        <v>835</v>
+      </c>
+      <c r="I1562" s="180" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1562" s="181" t="s">
+        <v>4470</v>
+      </c>
+      <c r="K1562">
+        <v>1563</v>
+      </c>
+      <c r="M1562" s="179" t="s">
+        <v>4438</v>
+      </c>
+      <c r="N1562" t="s">
+        <v>4474</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1563">
+        <v>91</v>
+      </c>
+      <c r="B1563" s="7">
+        <v>6714971</v>
+      </c>
+      <c r="C1563" s="180" t="s">
+        <v>236</v>
+      </c>
+      <c r="D1563" s="180" t="s">
+        <v>119</v>
+      </c>
+      <c r="E1563" s="180" t="s">
+        <v>236</v>
+      </c>
+      <c r="F1563" s="29">
+        <v>46176</v>
+      </c>
+      <c r="G1563" s="56">
+        <v>8.8680555555555554E-2</v>
+      </c>
+      <c r="H1563" s="180" t="s">
+        <v>830</v>
+      </c>
+      <c r="I1563" s="180" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1563" s="181" t="s">
+        <v>4471</v>
+      </c>
+      <c r="K1563">
+        <v>1564</v>
+      </c>
+      <c r="M1563" s="179" t="s">
+        <v>4438</v>
+      </c>
+      <c r="N1563" t="s">
+        <v>4475</v>
       </c>
     </row>
   </sheetData>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12940" uniqueCount="4476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12973" uniqueCount="4487">
   <si>
     <t>Ņ</t>
   </si>
@@ -13427,9 +13427,6 @@
     <t>projectbulletstorm[base]</t>
   </si>
   <si>
-    <t>Project</t>
-  </si>
-  <si>
     <t>ηλιαχτίδα &lt;3</t>
   </si>
   <si>
@@ -13455,6 +13452,42 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1523622955647500358/id_Yc.png?ex=6a4cc7f4&amp;is=6a4b7674&amp;hm=8b458e2bc3f4116be1336498719d7de97a9d10dcbd573b076061b1cb7bdf3f4d</t>
+  </si>
+  <si>
+    <t>Enchantress/LC</t>
+  </si>
+  <si>
+    <t>Yd</t>
+  </si>
+  <si>
+    <t>PBS</t>
+  </si>
+  <si>
+    <t>Kronos/Nest Warden/Shiny Sentry</t>
+  </si>
+  <si>
+    <t>Ye</t>
+  </si>
+  <si>
+    <t>[QV✅]FS™</t>
+  </si>
+  <si>
+    <t>Yf</t>
+  </si>
+  <si>
+    <t>Yg</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1471844339931021342/1523741620858785853/id_Yd.png?ex=6a4d3678&amp;is=6a4be4f8&amp;hm=b7c990e696c1ab0e75ecc4dfdaf6ab43307295971a5a02858df9d731da91a0f7</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1471844339931021342/1523741682380570815/id_Ye.png?ex=6a4d3686&amp;is=6a4be506&amp;hm=f2280681b8f2e60639718dd67fbc8a2328e7fac2ab1f3865341007e0f7eba770</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1471844339931021342/1523742100477448264/id_Yf.png?ex=6a4d36ea&amp;is=6a4be56a&amp;hm=acda6ea50294f1466e80745283b3df90386cc22fdf978f8754ca83ba2e04c637</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1471844339931021342/1523742164155367525/id_Yg.png?ex=6a4d36f9&amp;is=6a4be579&amp;hm=5217bfe58bc85bae2135bd3a4733c4e074752904adadfecf143eeb5162e183f1</t>
   </si>
 </sst>
 </file>
@@ -13466,11 +13499,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="130" x14ac:knownFonts="1">
+  <fonts count="131" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -14409,118 +14449,119 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="128" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="182">
+  <cellXfs count="183">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="128" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="127" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="127" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="126" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="126" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="125" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="124" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="123" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="122" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="120" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="119" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="127" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="111" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="126" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="110" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="125" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="117" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="111" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="118" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="112" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="108" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="107" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="95" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="95" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="94" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="94" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="95" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="94" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="95" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="94" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="91" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="91" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="92" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="92" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="94" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="95" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="128" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="90" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="130" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="89" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="129" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="88" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="88" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="87" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="87" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14529,18 +14570,18 @@
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="71" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="71" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="70" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="70" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="65" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14554,14 +14595,14 @@
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14606,8 +14647,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -14824,7 +14865,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1563"/>
+  <dimension ref="A1:O1568"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -79526,7 +79567,7 @@
         <v>8021713</v>
       </c>
       <c r="C1559" s="180" t="s">
-        <v>4467</v>
+        <v>4466</v>
       </c>
       <c r="D1559" t="s">
         <v>501</v>
@@ -79573,7 +79614,7 @@
         <v>13</v>
       </c>
       <c r="E1560" t="s">
-        <v>4466</v>
+        <v>4477</v>
       </c>
       <c r="F1560" s="29">
         <v>46208</v>
@@ -79588,7 +79629,7 @@
         <v>806</v>
       </c>
       <c r="J1560" s="181" t="s">
-        <v>4468</v>
+        <v>4467</v>
       </c>
       <c r="K1560">
         <v>1561</v>
@@ -79597,7 +79638,7 @@
         <v>4438</v>
       </c>
       <c r="N1560" t="s">
-        <v>4472</v>
+        <v>4471</v>
       </c>
     </row>
     <row r="1561" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -79629,7 +79670,7 @@
         <v>806</v>
       </c>
       <c r="J1561" s="181" t="s">
-        <v>4469</v>
+        <v>4468</v>
       </c>
       <c r="K1561">
         <v>1562</v>
@@ -79638,7 +79679,7 @@
         <v>4438</v>
       </c>
       <c r="N1561" t="s">
-        <v>4473</v>
+        <v>4472</v>
       </c>
     </row>
     <row r="1562" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -79670,7 +79711,7 @@
         <v>806</v>
       </c>
       <c r="J1562" s="181" t="s">
-        <v>4470</v>
+        <v>4469</v>
       </c>
       <c r="K1562">
         <v>1563</v>
@@ -79679,7 +79720,7 @@
         <v>4438</v>
       </c>
       <c r="N1562" t="s">
-        <v>4474</v>
+        <v>4473</v>
       </c>
     </row>
     <row r="1563" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -79711,7 +79752,7 @@
         <v>806</v>
       </c>
       <c r="J1563" s="181" t="s">
-        <v>4471</v>
+        <v>4470</v>
       </c>
       <c r="K1563">
         <v>1564</v>
@@ -79720,7 +79761,176 @@
         <v>4438</v>
       </c>
       <c r="N1563" t="s">
+        <v>4474</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1564">
+        <v>91</v>
+      </c>
+      <c r="B1564" s="7">
+        <v>8066706</v>
+      </c>
+      <c r="C1564" s="182" t="s">
+        <v>3708</v>
+      </c>
+      <c r="D1564" s="182" t="s">
+        <v>628</v>
+      </c>
+      <c r="E1564" s="182" t="s">
+        <v>236</v>
+      </c>
+      <c r="F1564" s="29">
+        <v>46209</v>
+      </c>
+      <c r="G1564" s="56">
+        <v>3.1655092592592596E-2</v>
+      </c>
+      <c r="H1564" s="182" t="s">
         <v>4475</v>
+      </c>
+      <c r="I1564" s="182" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1564" s="63" t="s">
+        <v>4476</v>
+      </c>
+      <c r="K1564">
+        <v>1565</v>
+      </c>
+      <c r="M1564" s="179" t="s">
+        <v>4438</v>
+      </c>
+      <c r="N1564" t="s">
+        <v>4483</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1565">
+        <v>91</v>
+      </c>
+      <c r="B1565" s="7">
+        <v>22588035</v>
+      </c>
+      <c r="C1565" s="182" t="s">
+        <v>4465</v>
+      </c>
+      <c r="D1565" s="182" t="s">
+        <v>424</v>
+      </c>
+      <c r="E1565" s="182" t="s">
+        <v>4477</v>
+      </c>
+      <c r="F1565" s="29">
+        <v>46209</v>
+      </c>
+      <c r="G1565" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1565" s="182" t="s">
+        <v>4478</v>
+      </c>
+      <c r="I1565" s="182" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1565" s="63" t="s">
+        <v>4479</v>
+      </c>
+      <c r="K1565">
+        <v>1566</v>
+      </c>
+      <c r="M1565" s="179" t="s">
+        <v>4438</v>
+      </c>
+      <c r="N1565" t="s">
+        <v>4484</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1566">
+        <v>91</v>
+      </c>
+      <c r="B1566" s="7">
+        <v>11438699</v>
+      </c>
+      <c r="C1566" s="182" t="s">
+        <v>4480</v>
+      </c>
+      <c r="D1566" s="182" t="s">
+        <v>587</v>
+      </c>
+      <c r="E1566" s="182" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F1566" s="29">
+        <v>46209</v>
+      </c>
+      <c r="G1566" s="56">
+        <v>8.4965277777777778E-2</v>
+      </c>
+      <c r="H1566" s="182" t="s">
+        <v>815</v>
+      </c>
+      <c r="I1566" s="182" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1566" s="63" t="s">
+        <v>4481</v>
+      </c>
+      <c r="K1566">
+        <v>1567</v>
+      </c>
+      <c r="M1566" s="179" t="s">
+        <v>4438</v>
+      </c>
+      <c r="N1566" t="s">
+        <v>4485</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1567">
+        <v>91</v>
+      </c>
+      <c r="B1567" s="7">
+        <v>22611841</v>
+      </c>
+      <c r="C1567" s="182" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1567" s="182" t="s">
+        <v>272</v>
+      </c>
+      <c r="E1567" s="182" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1567" s="29">
+        <v>46209</v>
+      </c>
+      <c r="G1567" s="56">
+        <v>0.20128472222222224</v>
+      </c>
+      <c r="H1567" s="182" t="s">
+        <v>885</v>
+      </c>
+      <c r="I1567" s="182" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1567" s="63" t="s">
+        <v>4482</v>
+      </c>
+      <c r="K1567">
+        <v>1568</v>
+      </c>
+      <c r="M1567" s="179" t="s">
+        <v>4438</v>
+      </c>
+      <c r="N1567" t="s">
+        <v>4486</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K1568">
+        <v>1569</v>
       </c>
     </row>
   </sheetData>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13003" uniqueCount="4499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13115" uniqueCount="4535">
   <si>
     <t>Ņ</t>
   </si>
@@ -13343,9 +13343,6 @@
     <t>YQ</t>
   </si>
   <si>
-    <t>[o]</t>
-  </si>
-  <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1523259465996959764/id_YK.png?ex=6a4b756d&amp;is=6a4a23ed&amp;hm=e7fde05fa1bd11eb7e5321e5bb62f56aa5977d8b565fa205ad613e3d1e025e8d</t>
   </si>
   <si>
@@ -13524,6 +13521,117 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1524029416374538282/id_Yk.png?ex=6a4e427f&amp;is=6a4cf0ff&amp;hm=f07cdae00a0e27099d0d594f5ad513f62a63660d2417762d54cfc666d0b21649</t>
+  </si>
+  <si>
+    <t>Yl</t>
+  </si>
+  <si>
+    <t>Apostate of Ares(PBS)</t>
+  </si>
+  <si>
+    <t>Ym</t>
+  </si>
+  <si>
+    <t>Yn</t>
+  </si>
+  <si>
+    <t>Nest Guardian/Nest Keeper/Eris</t>
+  </si>
+  <si>
+    <t>Yt(failure)</t>
+  </si>
+  <si>
+    <t>Pentadrive</t>
+  </si>
+  <si>
+    <t>Yo</t>
+  </si>
+  <si>
+    <t>Yp</t>
+  </si>
+  <si>
+    <t>Yq</t>
+  </si>
+  <si>
+    <t>[sss+] kk</t>
+  </si>
+  <si>
+    <t>インフェルノシテ</t>
+  </si>
+  <si>
+    <t>Yr</t>
+  </si>
+  <si>
+    <t>Ys</t>
+  </si>
+  <si>
+    <t>Hyperprojector</t>
+  </si>
+  <si>
+    <t>Yt</t>
+  </si>
+  <si>
+    <t>Yu</t>
+  </si>
+  <si>
+    <t>Pollo Cansado &lt;3</t>
+  </si>
+  <si>
+    <t>Auto-Polluter</t>
+  </si>
+  <si>
+    <t>Yv</t>
+  </si>
+  <si>
+    <t>Yw</t>
+  </si>
+  <si>
+    <t>Yx</t>
+  </si>
+  <si>
+    <t>{Legends} Ch1ck3n &lt;3</t>
+  </si>
+  <si>
+    <t>catthing</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1524351645960372365/id_Yl.png?ex=6a4f6e99&amp;is=6a4e1d19&amp;hm=50a0cb75d8c8ce2e6cb1e3dbe0472a04926dff294e4c78b756af0b62bce43200</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1524351710133354506/id_Ym.png?ex=6a4f6ea8&amp;is=6a4e1d28&amp;hm=c0e5c191c51d2d95f0233b2274c36db7c883435b1e061a5b44a621b07e0a0bf9</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1524351839099682846/id_Yn.png?ex=6a4f6ec7&amp;is=6a4e1d47&amp;hm=0e66eec99bf1bc1c21dd599178f20a1efa45091f28a89f9dbe7c381b0fbe36e5</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1524351888110125086/id_Yo.jpg?ex=6a4f6ed3&amp;is=6a4e1d53&amp;hm=a6a190fe8123425c7ce244df6f92fa02253cdbf6be4467e25cd7135a0827401a</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1524351964354445403/id_Yp.jpg?ex=6a4f6ee5&amp;is=6a4e1d65&amp;hm=2dbabb16613536664e0f687615364d3336833030550f3965a9c9b4fc58840871</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1524352018750111875/id_Yq.jpg?ex=6a4f6ef2&amp;is=6a4e1d72&amp;hm=b6cd6c83e546424ea8c40d06f2faea4d55f19bc002232207527122ff571b254b</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1524352104204996638/id_Yr.png?ex=6a4f6f06&amp;is=6a4e1d86&amp;hm=022107235f856d7b7f9d72e120278e1936efe3a96b5577b62285fd4b73fcbd3c</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1524352169506242681/id_Ys.png?ex=6a4f6f16&amp;is=6a4e1d96&amp;hm=2e8aff6b0ce370b45651d104afe7c70b5bb8420760ff717668cfeaf2c1028283</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1524352231942389840/id_Yt.png?ex=6a4f6f25&amp;is=6a4e1da5&amp;hm=e1387aa0fe74a94b2a86cc80ee3541e5ecb7b07ed6f81062d46204748ecc100e</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1524352338469589152/id_Yu.png?ex=6a4f6f3e&amp;is=6a4e1dbe&amp;hm=d8abcec6f1ed6a8fd752bb8af4c8a525a5aac3462a9db01db97b2802fe56efb0</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1524352460410585219/id_Yv.png?ex=6a4f6f5b&amp;is=6a4e1ddb&amp;hm=dd03f790464419653aa13efbf996f7e02d7563c2fa326839c2aeefbad9e86c3b</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1524352545735180289/id_Yw.png?ex=6a4f6f70&amp;is=6a4e1df0&amp;hm=9e365f719c1714d920628bd8eb97dea7b61bf54d3209281d014c7d3bc64afe12</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1524352629382189088/id_Yx.png?ex=6a4f6f83&amp;is=6a4e1e03&amp;hm=3f88ea0f9022312fd4c471561d2aacaacaa24bc9a4ceae05f60e8f19c54fe7b8</t>
   </si>
 </sst>
 </file>
@@ -13535,11 +13643,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="131" x14ac:knownFonts="1">
+  <fonts count="132" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -14485,117 +14600,118 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="129" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="130" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="183">
+  <cellXfs count="184">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="128" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="128" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="127" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="127" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="126" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="126" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="125" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="124" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="123" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="122" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="120" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="119" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="128" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="112" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="127" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="111" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="126" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="118" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="112" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="119" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="113" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="109" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="108" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="97" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="97" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="96" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="96" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="97" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="96" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="97" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="96" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="93" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="93" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="94" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="94" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="96" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="97" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="130" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="129" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="92" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="131" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="91" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="130" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="90" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="90" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="89" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="89" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14604,18 +14720,18 @@
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="73" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="73" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="72" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="72" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="66" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14629,14 +14745,14 @@
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14681,8 +14797,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
@@ -14901,7 +15017,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1571"/>
+  <dimension ref="A1:O1584"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -16188,7 +16304,7 @@
         <v>60</v>
       </c>
       <c r="E30" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F30" s="29">
         <v>46000</v>
@@ -16570,7 +16686,7 @@
         <v>35</v>
       </c>
       <c r="E39" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F39" s="29">
         <v>45984</v>
@@ -19024,7 +19140,7 @@
         <v>5</v>
       </c>
       <c r="E96" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F96" s="30">
         <v>45756</v>
@@ -19757,7 +19873,7 @@
         <v>5</v>
       </c>
       <c r="E113" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F113" s="29">
         <v>45693</v>
@@ -19841,7 +19957,7 @@
         <v>60</v>
       </c>
       <c r="E115" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F115" s="30">
         <v>45741</v>
@@ -20791,7 +20907,7 @@
         <v>9</v>
       </c>
       <c r="E137" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F137" s="29">
         <v>46013</v>
@@ -21470,7 +21586,7 @@
         <v>5</v>
       </c>
       <c r="E153" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F153" s="29">
         <v>45779</v>
@@ -22284,7 +22400,7 @@
         <v>15</v>
       </c>
       <c r="E172" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F172" s="29">
         <v>45539</v>
@@ -22842,7 +22958,7 @@
         <v>60</v>
       </c>
       <c r="E185" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F185" s="30">
         <v>45773</v>
@@ -24163,7 +24279,7 @@
         <v>15</v>
       </c>
       <c r="E216" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F216" s="29">
         <v>46016</v>
@@ -27904,7 +28020,7 @@
         <v>465</v>
       </c>
       <c r="E305" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F305" s="29">
         <v>45999</v>
@@ -28201,7 +28317,7 @@
         <v>65</v>
       </c>
       <c r="E312" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F312" s="30">
         <v>45800</v>
@@ -28407,7 +28523,7 @@
         <v>5</v>
       </c>
       <c r="E317" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F317" s="29">
         <v>45712</v>
@@ -30601,7 +30717,7 @@
         <v>60</v>
       </c>
       <c r="E370" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F370" s="29">
         <v>45699</v>
@@ -33966,7 +34082,7 @@
         <v>60</v>
       </c>
       <c r="E451" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F451" s="29">
         <v>46033</v>
@@ -39069,7 +39185,7 @@
         <v>171</v>
       </c>
       <c r="E574" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F574" s="29">
         <v>45795</v>
@@ -40895,7 +41011,7 @@
         <v>570</v>
       </c>
       <c r="E618" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F618" s="29">
         <v>46046</v>
@@ -41513,7 +41629,7 @@
         <v>345</v>
       </c>
       <c r="E633" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F633" s="29">
         <v>45998</v>
@@ -42668,7 +42784,7 @@
         <v>372</v>
       </c>
       <c r="E661" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F661" s="29">
         <v>45998</v>
@@ -42750,7 +42866,7 @@
         <v>569</v>
       </c>
       <c r="E663" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F663" s="29">
         <v>46006</v>
@@ -43489,7 +43605,7 @@
         <v>333</v>
       </c>
       <c r="E681" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F681" s="29">
         <v>45996</v>
@@ -43530,7 +43646,7 @@
         <v>698</v>
       </c>
       <c r="E682" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F682" s="29">
         <v>46023</v>
@@ -46553,7 +46669,7 @@
         <v>334</v>
       </c>
       <c r="E755" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F755" s="29">
         <v>46010</v>
@@ -47335,7 +47451,7 @@
         <v>389</v>
       </c>
       <c r="E774" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F774" s="29">
         <v>46004</v>
@@ -47909,7 +48025,7 @@
         <v>506</v>
       </c>
       <c r="E788" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F788" s="29">
         <v>46018</v>
@@ -48363,7 +48479,7 @@
         <v>171</v>
       </c>
       <c r="E799" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F799" s="29">
         <v>46017</v>
@@ -49145,7 +49261,7 @@
         <v>334</v>
       </c>
       <c r="E818" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F818" s="29">
         <v>46004</v>
@@ -49432,7 +49548,7 @@
         <v>700</v>
       </c>
       <c r="E825" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F825" s="29">
         <v>46024</v>
@@ -50217,7 +50333,7 @@
         <v>564</v>
       </c>
       <c r="E844" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F844" s="29">
         <v>46012</v>
@@ -50463,7 +50579,7 @@
         <v>448</v>
       </c>
       <c r="E850" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F850" s="29">
         <v>45998</v>
@@ -50832,7 +50948,7 @@
         <v>333</v>
       </c>
       <c r="E859" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F859" s="29">
         <v>45808</v>
@@ -51163,7 +51279,7 @@
         <v>699</v>
       </c>
       <c r="E867" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F867" s="29">
         <v>46024</v>
@@ -51327,7 +51443,7 @@
         <v>171</v>
       </c>
       <c r="E871" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F871" s="29">
         <v>46033</v>
@@ -51655,7 +51771,7 @@
         <v>334</v>
       </c>
       <c r="E879" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F879" s="29">
         <v>45878</v>
@@ -53433,7 +53549,7 @@
         <v>760</v>
       </c>
       <c r="E922" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F922" s="29">
         <v>46039</v>
@@ -53802,7 +53918,7 @@
         <v>765</v>
       </c>
       <c r="E931" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F931" s="29">
         <v>46043</v>
@@ -54874,7 +54990,7 @@
         <v>572</v>
       </c>
       <c r="E957" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F957" s="29">
         <v>46007</v>
@@ -55038,7 +55154,7 @@
         <v>764</v>
       </c>
       <c r="E961" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F961" s="29">
         <v>46043</v>
@@ -56395,7 +56511,7 @@
         <v>590</v>
       </c>
       <c r="E994" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F994" s="29">
         <v>46008</v>
@@ -56518,7 +56634,7 @@
         <v>677</v>
       </c>
       <c r="E997" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F997" s="29">
         <v>46020</v>
@@ -56559,7 +56675,7 @@
         <v>701</v>
       </c>
       <c r="E998" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F998" s="29">
         <v>46024</v>
@@ -56641,7 +56757,7 @@
         <v>386</v>
       </c>
       <c r="E1000" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F1000" s="29">
         <v>46018</v>
@@ -57675,7 +57791,7 @@
         <v>573</v>
       </c>
       <c r="E1025" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F1025" s="29">
         <v>46007</v>
@@ -57798,7 +57914,7 @@
         <v>697</v>
       </c>
       <c r="E1028" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F1028" s="29">
         <v>46022</v>
@@ -58167,7 +58283,7 @@
         <v>783</v>
       </c>
       <c r="E1037" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F1037" s="29">
         <v>46046</v>
@@ -58296,7 +58412,7 @@
         <v>607</v>
       </c>
       <c r="E1040" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F1040" s="29">
         <v>46009</v>
@@ -58835,7 +58951,7 @@
         <v>517</v>
       </c>
       <c r="E1053" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F1053" s="29">
         <v>46019</v>
@@ -59164,7 +59280,7 @@
         <v>947</v>
       </c>
       <c r="E1061" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F1061" s="29">
         <v>46051</v>
@@ -60271,7 +60387,7 @@
         <v>1471</v>
       </c>
       <c r="E1088" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F1088" s="29">
         <v>46061</v>
@@ -60684,7 +60800,7 @@
         <v>1625</v>
       </c>
       <c r="E1098" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F1098" s="29">
         <v>46062</v>
@@ -60848,7 +60964,7 @@
         <v>1718</v>
       </c>
       <c r="E1102" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F1102" s="29">
         <v>46062</v>
@@ -61094,7 +61210,7 @@
         <v>60</v>
       </c>
       <c r="E1108" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F1108" s="29">
         <v>45759</v>
@@ -61545,7 +61661,7 @@
         <v>60</v>
       </c>
       <c r="E1119" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F1119" s="29">
         <v>46067</v>
@@ -62324,7 +62440,7 @@
         <v>35</v>
       </c>
       <c r="E1138" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F1138" s="29">
         <v>46072</v>
@@ -64046,7 +64162,7 @@
         <v>372</v>
       </c>
       <c r="E1180" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F1180" s="29">
         <v>46071</v>
@@ -66509,7 +66625,7 @@
         <v>66</v>
       </c>
       <c r="E1240" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F1240" s="29">
         <v>46090</v>
@@ -67206,7 +67322,7 @@
         <v>3641</v>
       </c>
       <c r="E1257" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F1257" s="29">
         <v>46095</v>
@@ -67288,7 +67404,7 @@
         <v>3645</v>
       </c>
       <c r="E1259" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F1259" s="29">
         <v>46093</v>
@@ -68846,7 +68962,7 @@
         <v>685</v>
       </c>
       <c r="E1297" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F1297" s="29">
         <v>46104</v>
@@ -68969,7 +69085,7 @@
         <v>3763</v>
       </c>
       <c r="E1300" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F1300" s="29">
         <v>46105</v>
@@ -69010,7 +69126,7 @@
         <v>3764</v>
       </c>
       <c r="E1301" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F1301" s="29">
         <v>46105</v>
@@ -69051,7 +69167,7 @@
         <v>3765</v>
       </c>
       <c r="E1302" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F1302" s="29">
         <v>46105</v>
@@ -69133,7 +69249,7 @@
         <v>3776</v>
       </c>
       <c r="E1304" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F1304" s="29">
         <v>46106</v>
@@ -69174,7 +69290,7 @@
         <v>3777</v>
       </c>
       <c r="E1305" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F1305" s="29">
         <v>46106</v>
@@ -69297,7 +69413,7 @@
         <v>3914</v>
       </c>
       <c r="E1308" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F1308" s="29">
         <v>46106</v>
@@ -69338,7 +69454,7 @@
         <v>3781</v>
       </c>
       <c r="E1309" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F1309" s="29">
         <v>46106</v>
@@ -71186,7 +71302,7 @@
         <v>3902</v>
       </c>
       <c r="E1354" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F1354" s="29">
         <v>46119</v>
@@ -75579,7 +75695,7 @@
         <v>313</v>
       </c>
       <c r="E1461" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F1461" s="29">
         <v>46145</v>
@@ -76030,7 +76146,7 @@
         <v>60</v>
       </c>
       <c r="E1472" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F1472" s="29">
         <v>46146</v>
@@ -76071,7 +76187,7 @@
         <v>4230</v>
       </c>
       <c r="E1473" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F1473" s="29">
         <v>46150</v>
@@ -76399,7 +76515,7 @@
         <v>4254</v>
       </c>
       <c r="E1481" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F1481" s="29">
         <v>46151</v>
@@ -76440,7 +76556,7 @@
         <v>4256</v>
       </c>
       <c r="E1482" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F1482" s="29">
         <v>46151</v>
@@ -76645,7 +76761,7 @@
         <v>4270</v>
       </c>
       <c r="E1487" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F1487" s="29">
         <v>46152</v>
@@ -76935,7 +77051,7 @@
         <v>4280</v>
       </c>
       <c r="E1494" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F1494" s="29">
         <v>46152</v>
@@ -77559,7 +77675,7 @@
         <v>4330</v>
       </c>
       <c r="E1509" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F1509" s="29">
         <v>46158</v>
@@ -77600,7 +77716,7 @@
         <v>3667</v>
       </c>
       <c r="E1510" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F1510" s="29">
         <v>46164</v>
@@ -79055,11 +79171,11 @@
       <c r="K1545">
         <v>1546</v>
       </c>
-      <c r="M1545" s="177" t="s">
+      <c r="M1545" s="56" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1545" t="s">
         <v>4438</v>
-      </c>
-      <c r="N1545" t="s">
-        <v>4439</v>
       </c>
     </row>
     <row r="1546" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -79096,11 +79212,11 @@
       <c r="K1546">
         <v>1547</v>
       </c>
-      <c r="M1546" s="177" t="s">
-        <v>4438</v>
+      <c r="M1546" s="56" t="s">
+        <v>854</v>
       </c>
       <c r="N1546" t="s">
-        <v>4440</v>
+        <v>4439</v>
       </c>
     </row>
     <row r="1547" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -79137,11 +79253,11 @@
       <c r="K1547">
         <v>1548</v>
       </c>
-      <c r="M1547" s="177" t="s">
-        <v>4438</v>
+      <c r="M1547" s="56" t="s">
+        <v>854</v>
       </c>
       <c r="N1547" t="s">
-        <v>4441</v>
+        <v>4440</v>
       </c>
     </row>
     <row r="1548" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -79178,11 +79294,11 @@
       <c r="K1548">
         <v>1549</v>
       </c>
-      <c r="M1548" s="177" t="s">
-        <v>4438</v>
+      <c r="M1548" s="56" t="s">
+        <v>854</v>
       </c>
       <c r="N1548" t="s">
-        <v>4442</v>
+        <v>4441</v>
       </c>
     </row>
     <row r="1549" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -79219,11 +79335,11 @@
       <c r="K1549">
         <v>1550</v>
       </c>
-      <c r="M1549" s="177" t="s">
-        <v>4438</v>
+      <c r="M1549" s="56" t="s">
+        <v>854</v>
       </c>
       <c r="N1549" t="s">
-        <v>4443</v>
+        <v>4442</v>
       </c>
     </row>
     <row r="1550" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -79240,7 +79356,7 @@
         <v>637</v>
       </c>
       <c r="E1550" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F1550" s="29">
         <v>46208</v>
@@ -79260,11 +79376,11 @@
       <c r="K1550">
         <v>1551</v>
       </c>
-      <c r="M1550" s="177" t="s">
-        <v>4438</v>
+      <c r="M1550" s="56" t="s">
+        <v>854</v>
       </c>
       <c r="N1550" t="s">
-        <v>4444</v>
+        <v>4443</v>
       </c>
     </row>
     <row r="1551" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -79301,11 +79417,11 @@
       <c r="K1551">
         <v>1552</v>
       </c>
-      <c r="M1551" s="177" t="s">
-        <v>4438</v>
+      <c r="M1551" s="56" t="s">
+        <v>854</v>
       </c>
       <c r="N1551" t="s">
-        <v>4445</v>
+        <v>4444</v>
       </c>
     </row>
     <row r="1552" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -79331,22 +79447,22 @@
         <v>0.12238425925925926</v>
       </c>
       <c r="H1552" s="178" t="s">
-        <v>4446</v>
+        <v>4445</v>
       </c>
       <c r="I1552" s="178" t="s">
         <v>806</v>
       </c>
       <c r="J1552" s="62" t="s">
-        <v>4448</v>
+        <v>4447</v>
       </c>
       <c r="K1552">
         <v>1553</v>
       </c>
-      <c r="M1552" s="178" t="s">
-        <v>4438</v>
+      <c r="M1552" s="56" t="s">
+        <v>854</v>
       </c>
       <c r="N1552" t="s">
-        <v>4456</v>
+        <v>4455</v>
       </c>
     </row>
     <row r="1553" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -79378,16 +79494,16 @@
         <v>806</v>
       </c>
       <c r="J1553" s="62" t="s">
-        <v>4449</v>
+        <v>4448</v>
       </c>
       <c r="K1553">
         <v>1554</v>
       </c>
-      <c r="M1553" s="178" t="s">
-        <v>4438</v>
+      <c r="M1553" s="56" t="s">
+        <v>854</v>
       </c>
       <c r="N1553" t="s">
-        <v>4457</v>
+        <v>4456</v>
       </c>
     </row>
     <row r="1554" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -79419,16 +79535,16 @@
         <v>806</v>
       </c>
       <c r="J1554" s="62" t="s">
-        <v>4447</v>
+        <v>4446</v>
       </c>
       <c r="K1554">
         <v>1555</v>
       </c>
-      <c r="M1554" s="178" t="s">
-        <v>4438</v>
+      <c r="M1554" s="56" t="s">
+        <v>854</v>
       </c>
       <c r="N1554" t="s">
-        <v>4458</v>
+        <v>4457</v>
       </c>
     </row>
     <row r="1555" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -79460,16 +79576,16 @@
         <v>806</v>
       </c>
       <c r="J1555" s="62" t="s">
-        <v>4450</v>
+        <v>4449</v>
       </c>
       <c r="K1555">
         <v>1556</v>
       </c>
-      <c r="M1555" s="178" t="s">
-        <v>4438</v>
+      <c r="M1555" s="56" t="s">
+        <v>854</v>
       </c>
       <c r="N1555" t="s">
-        <v>4459</v>
+        <v>4458</v>
       </c>
     </row>
     <row r="1556" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -79480,7 +79596,7 @@
         <v>15001077</v>
       </c>
       <c r="C1556" t="s">
-        <v>4451</v>
+        <v>4450</v>
       </c>
       <c r="D1556" t="s">
         <v>119</v>
@@ -79501,16 +79617,16 @@
         <v>806</v>
       </c>
       <c r="J1556" s="62" t="s">
-        <v>4452</v>
+        <v>4451</v>
       </c>
       <c r="K1556">
         <v>1557</v>
       </c>
-      <c r="M1556" s="178" t="s">
-        <v>4438</v>
+      <c r="M1556" s="56" t="s">
+        <v>854</v>
       </c>
       <c r="N1556" t="s">
-        <v>4460</v>
+        <v>4459</v>
       </c>
     </row>
     <row r="1557" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -79521,7 +79637,7 @@
         <v>11018920</v>
       </c>
       <c r="C1557" t="s">
-        <v>4451</v>
+        <v>4450</v>
       </c>
       <c r="D1557" t="s">
         <v>628</v>
@@ -79542,16 +79658,16 @@
         <v>806</v>
       </c>
       <c r="J1557" s="62" t="s">
-        <v>4453</v>
+        <v>4452</v>
       </c>
       <c r="K1557">
         <v>1558</v>
       </c>
-      <c r="M1557" s="178" t="s">
-        <v>4438</v>
+      <c r="M1557" s="56" t="s">
+        <v>854</v>
       </c>
       <c r="N1557" t="s">
-        <v>4461</v>
+        <v>4460</v>
       </c>
     </row>
     <row r="1558" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -79577,22 +79693,22 @@
         <v>6.1712962962962963E-2</v>
       </c>
       <c r="H1558" s="178" t="s">
+        <v>4453</v>
+      </c>
+      <c r="I1558" s="178" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1558" s="62" t="s">
         <v>4454</v>
-      </c>
-      <c r="I1558" s="178" t="s">
-        <v>806</v>
-      </c>
-      <c r="J1558" s="62" t="s">
-        <v>4455</v>
       </c>
       <c r="K1558">
         <v>1559</v>
       </c>
-      <c r="M1558" s="178" t="s">
-        <v>4438</v>
+      <c r="M1558" s="56" t="s">
+        <v>854</v>
       </c>
       <c r="N1558" t="s">
-        <v>4462</v>
+        <v>4461</v>
       </c>
     </row>
     <row r="1559" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -79603,7 +79719,7 @@
         <v>8021713</v>
       </c>
       <c r="C1559" s="179" t="s">
-        <v>4466</v>
+        <v>4465</v>
       </c>
       <c r="D1559" t="s">
         <v>501</v>
@@ -79624,16 +79740,16 @@
         <v>806</v>
       </c>
       <c r="J1559" s="62" t="s">
-        <v>4463</v>
+        <v>4462</v>
       </c>
       <c r="K1559">
         <v>1560</v>
       </c>
-      <c r="M1559" s="178" t="s">
-        <v>4438</v>
+      <c r="M1559" s="56" t="s">
+        <v>854</v>
       </c>
       <c r="N1559" t="s">
-        <v>4464</v>
+        <v>4463</v>
       </c>
     </row>
     <row r="1560" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -79644,13 +79760,13 @@
         <v>30281656</v>
       </c>
       <c r="C1560" t="s">
-        <v>4465</v>
+        <v>4464</v>
       </c>
       <c r="D1560" s="179" t="s">
         <v>13</v>
       </c>
       <c r="E1560" t="s">
-        <v>4477</v>
+        <v>4476</v>
       </c>
       <c r="F1560" s="29">
         <v>46208</v>
@@ -79665,16 +79781,16 @@
         <v>806</v>
       </c>
       <c r="J1560" s="180" t="s">
-        <v>4467</v>
+        <v>4466</v>
       </c>
       <c r="K1560">
         <v>1561</v>
       </c>
-      <c r="M1560" s="178" t="s">
-        <v>4438</v>
+      <c r="M1560" s="56" t="s">
+        <v>854</v>
       </c>
       <c r="N1560" t="s">
-        <v>4471</v>
+        <v>4470</v>
       </c>
     </row>
     <row r="1561" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -79706,16 +79822,16 @@
         <v>806</v>
       </c>
       <c r="J1561" s="180" t="s">
-        <v>4468</v>
+        <v>4467</v>
       </c>
       <c r="K1561">
         <v>1562</v>
       </c>
-      <c r="M1561" s="178" t="s">
-        <v>4438</v>
+      <c r="M1561" s="56" t="s">
+        <v>854</v>
       </c>
       <c r="N1561" t="s">
-        <v>4472</v>
+        <v>4471</v>
       </c>
     </row>
     <row r="1562" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -79747,16 +79863,16 @@
         <v>806</v>
       </c>
       <c r="J1562" s="180" t="s">
-        <v>4469</v>
+        <v>4468</v>
       </c>
       <c r="K1562">
         <v>1563</v>
       </c>
-      <c r="M1562" s="178" t="s">
-        <v>4438</v>
+      <c r="M1562" s="56" t="s">
+        <v>854</v>
       </c>
       <c r="N1562" t="s">
-        <v>4473</v>
+        <v>4472</v>
       </c>
     </row>
     <row r="1563" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -79788,16 +79904,16 @@
         <v>806</v>
       </c>
       <c r="J1563" s="180" t="s">
-        <v>4470</v>
+        <v>4469</v>
       </c>
       <c r="K1563">
         <v>1564</v>
       </c>
-      <c r="M1563" s="178" t="s">
-        <v>4438</v>
+      <c r="M1563" s="56" t="s">
+        <v>854</v>
       </c>
       <c r="N1563" t="s">
-        <v>4474</v>
+        <v>4473</v>
       </c>
     </row>
     <row r="1564" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -79823,22 +79939,22 @@
         <v>3.1655092592592596E-2</v>
       </c>
       <c r="H1564" s="181" t="s">
+        <v>4474</v>
+      </c>
+      <c r="I1564" s="181" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1564" s="62" t="s">
         <v>4475</v>
-      </c>
-      <c r="I1564" s="181" t="s">
-        <v>806</v>
-      </c>
-      <c r="J1564" s="62" t="s">
-        <v>4476</v>
       </c>
       <c r="K1564">
         <v>1565</v>
       </c>
-      <c r="M1564" s="178" t="s">
-        <v>4438</v>
+      <c r="M1564" s="56" t="s">
+        <v>854</v>
       </c>
       <c r="N1564" t="s">
-        <v>4483</v>
+        <v>4482</v>
       </c>
     </row>
     <row r="1565" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -79849,13 +79965,13 @@
         <v>22588035</v>
       </c>
       <c r="C1565" s="181" t="s">
-        <v>4465</v>
+        <v>4464</v>
       </c>
       <c r="D1565" s="181" t="s">
         <v>424</v>
       </c>
       <c r="E1565" s="181" t="s">
-        <v>4477</v>
+        <v>4476</v>
       </c>
       <c r="F1565" s="29">
         <v>46209</v>
@@ -79864,22 +79980,22 @@
         <v>11</v>
       </c>
       <c r="H1565" s="181" t="s">
+        <v>4477</v>
+      </c>
+      <c r="I1565" s="181" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1565" s="62" t="s">
         <v>4478</v>
-      </c>
-      <c r="I1565" s="181" t="s">
-        <v>806</v>
-      </c>
-      <c r="J1565" s="62" t="s">
-        <v>4479</v>
       </c>
       <c r="K1565">
         <v>1566</v>
       </c>
-      <c r="M1565" s="178" t="s">
-        <v>4438</v>
+      <c r="M1565" s="56" t="s">
+        <v>854</v>
       </c>
       <c r="N1565" t="s">
-        <v>4484</v>
+        <v>4483</v>
       </c>
     </row>
     <row r="1566" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -79889,8 +80005,8 @@
       <c r="B1566" s="7">
         <v>11438699</v>
       </c>
-      <c r="C1566" s="181" t="s">
-        <v>4480</v>
+      <c r="C1566" s="183" t="s">
+        <v>4479</v>
       </c>
       <c r="D1566" s="181" t="s">
         <v>587</v>
@@ -79911,16 +80027,16 @@
         <v>806</v>
       </c>
       <c r="J1566" s="62" t="s">
-        <v>4481</v>
+        <v>4480</v>
       </c>
       <c r="K1566">
         <v>1567</v>
       </c>
-      <c r="M1566" s="178" t="s">
-        <v>4438</v>
+      <c r="M1566" s="56" t="s">
+        <v>854</v>
       </c>
       <c r="N1566" t="s">
-        <v>4485</v>
+        <v>4484</v>
       </c>
     </row>
     <row r="1567" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -79952,16 +80068,16 @@
         <v>806</v>
       </c>
       <c r="J1567" s="62" t="s">
-        <v>4482</v>
+        <v>4481</v>
       </c>
       <c r="K1567">
         <v>1568</v>
       </c>
-      <c r="M1567" s="178" t="s">
-        <v>4438</v>
+      <c r="M1567" s="56" t="s">
+        <v>854</v>
       </c>
       <c r="N1567" t="s">
-        <v>4486</v>
+        <v>4485</v>
       </c>
     </row>
     <row r="1568" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -79978,7 +80094,7 @@
         <v>60</v>
       </c>
       <c r="E1568" t="s">
-        <v>4488</v>
+        <v>4487</v>
       </c>
       <c r="F1568" s="29">
         <v>46210</v>
@@ -79993,13 +80109,16 @@
         <v>806</v>
       </c>
       <c r="J1568" s="62" t="s">
-        <v>4487</v>
+        <v>4486</v>
       </c>
       <c r="K1568">
         <v>1569</v>
       </c>
+      <c r="M1568" s="56" t="s">
+        <v>854</v>
+      </c>
       <c r="N1568" t="s">
-        <v>4493</v>
+        <v>4492</v>
       </c>
     </row>
     <row r="1569" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -80025,19 +80144,22 @@
         <v>6.4548611111111112E-2</v>
       </c>
       <c r="H1569" s="182" t="s">
+        <v>4488</v>
+      </c>
+      <c r="I1569" s="182" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1569" s="62" t="s">
         <v>4489</v>
-      </c>
-      <c r="I1569" s="182" t="s">
-        <v>806</v>
-      </c>
-      <c r="J1569" s="62" t="s">
-        <v>4490</v>
       </c>
       <c r="K1569">
         <v>1570</v>
       </c>
+      <c r="M1569" s="56" t="s">
+        <v>854</v>
+      </c>
       <c r="N1569" t="s">
-        <v>4494</v>
+        <v>4493</v>
       </c>
     </row>
     <row r="1570" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -80048,7 +80170,7 @@
         <v>4226015</v>
       </c>
       <c r="C1570" t="s">
-        <v>4491</v>
+        <v>4490</v>
       </c>
       <c r="D1570" s="182" t="s">
         <v>203</v>
@@ -80069,13 +80191,16 @@
         <v>290</v>
       </c>
       <c r="J1570" s="62" t="s">
-        <v>4492</v>
+        <v>4491</v>
       </c>
       <c r="K1570">
         <v>1571</v>
       </c>
+      <c r="M1570" s="56" t="s">
+        <v>854</v>
+      </c>
       <c r="N1570" t="s">
-        <v>4495</v>
+        <v>4494</v>
       </c>
     </row>
     <row r="1571" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -80086,7 +80211,7 @@
         <v>16120000</v>
       </c>
       <c r="C1571" t="s">
-        <v>4496</v>
+        <v>4495</v>
       </c>
       <c r="D1571" s="182" t="s">
         <v>13</v>
@@ -80107,13 +80232,549 @@
         <v>806</v>
       </c>
       <c r="J1571" s="62" t="s">
-        <v>4497</v>
+        <v>4496</v>
       </c>
       <c r="K1571">
         <v>1572</v>
       </c>
+      <c r="M1571" s="56" t="s">
+        <v>854</v>
+      </c>
       <c r="N1571" t="s">
+        <v>4497</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1572">
+        <v>93</v>
+      </c>
+      <c r="B1572" s="7">
+        <v>15058035</v>
+      </c>
+      <c r="C1572" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1572" s="183" t="s">
+        <v>424</v>
+      </c>
+      <c r="E1572" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1572" s="29">
+        <v>46210</v>
+      </c>
+      <c r="G1572" s="55">
+        <v>9.0011574074074077E-2</v>
+      </c>
+      <c r="H1572" s="183" t="s">
+        <v>835</v>
+      </c>
+      <c r="I1572" s="183" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1572" s="62" t="s">
         <v>4498</v>
+      </c>
+      <c r="K1572">
+        <v>1573</v>
+      </c>
+      <c r="M1572" s="56" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1572" t="s">
+        <v>4522</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1573">
+        <v>93</v>
+      </c>
+      <c r="B1573" s="7">
+        <v>8417326</v>
+      </c>
+      <c r="C1573" t="s">
+        <v>4499</v>
+      </c>
+      <c r="D1573" s="183" t="s">
+        <v>434</v>
+      </c>
+      <c r="E1573" t="s">
+        <v>4476</v>
+      </c>
+      <c r="F1573" s="29">
+        <v>46210</v>
+      </c>
+      <c r="G1573" s="55">
+        <v>0.16842592592592595</v>
+      </c>
+      <c r="H1573" s="183" t="s">
+        <v>942</v>
+      </c>
+      <c r="I1573" s="183" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1573" s="62" t="s">
+        <v>4500</v>
+      </c>
+      <c r="K1573">
+        <v>1574</v>
+      </c>
+      <c r="M1573" s="56" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1573" t="s">
+        <v>4523</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1574">
+        <v>93</v>
+      </c>
+      <c r="B1574" s="7">
+        <v>23425907</v>
+      </c>
+      <c r="C1574" t="s">
+        <v>720</v>
+      </c>
+      <c r="D1574" s="183" t="s">
+        <v>277</v>
+      </c>
+      <c r="E1574" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F1574" s="29">
+        <v>46210</v>
+      </c>
+      <c r="G1574" s="55">
+        <v>0.16313657407407409</v>
+      </c>
+      <c r="H1574" s="183" t="s">
+        <v>4502</v>
+      </c>
+      <c r="I1574" s="183" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1574" s="62" t="s">
+        <v>4501</v>
+      </c>
+      <c r="K1574">
+        <v>1575</v>
+      </c>
+      <c r="M1574" s="56" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1574" t="s">
+        <v>4524</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1575">
+        <v>93</v>
+      </c>
+      <c r="B1575" s="7">
+        <v>1004126</v>
+      </c>
+      <c r="C1575" t="s">
+        <v>4503</v>
+      </c>
+      <c r="D1575" t="s">
+        <v>4504</v>
+      </c>
+      <c r="E1575" t="s">
+        <v>218</v>
+      </c>
+      <c r="F1575" s="29">
+        <v>46210</v>
+      </c>
+      <c r="G1575" s="55">
+        <v>0.11886574074074074</v>
+      </c>
+      <c r="H1575" s="183" t="s">
+        <v>805</v>
+      </c>
+      <c r="I1575" s="183" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1575" s="62" t="s">
+        <v>4505</v>
+      </c>
+      <c r="K1575">
+        <v>1576</v>
+      </c>
+      <c r="M1575" s="56" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1575" t="s">
+        <v>4525</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1576">
+        <v>93</v>
+      </c>
+      <c r="B1576" s="7">
+        <v>18160000</v>
+      </c>
+      <c r="C1576" t="s">
+        <v>4508</v>
+      </c>
+      <c r="D1576" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1576" t="s">
+        <v>4508</v>
+      </c>
+      <c r="F1576" s="29">
+        <v>46211</v>
+      </c>
+      <c r="G1576" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1576" s="183" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1576" s="183" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1576" s="62" t="s">
+        <v>4506</v>
+      </c>
+      <c r="K1576">
+        <v>1577</v>
+      </c>
+      <c r="M1576" s="56" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1576" t="s">
+        <v>4526</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1577">
+        <v>93</v>
+      </c>
+      <c r="B1577" s="7">
+        <v>18094997</v>
+      </c>
+      <c r="C1577" t="s">
+        <v>4509</v>
+      </c>
+      <c r="D1577" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1577" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1577" s="29">
+        <v>46211</v>
+      </c>
+      <c r="G1577" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1577" s="183" t="s">
+        <v>1313</v>
+      </c>
+      <c r="I1577" s="183" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1577" s="62" t="s">
+        <v>4507</v>
+      </c>
+      <c r="K1577">
+        <v>1578</v>
+      </c>
+      <c r="M1577" s="56" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1577" t="s">
+        <v>4527</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1578">
+        <v>93</v>
+      </c>
+      <c r="B1578" s="7">
+        <v>4098248</v>
+      </c>
+      <c r="C1578" t="s">
+        <v>4490</v>
+      </c>
+      <c r="D1578" t="s">
+        <v>203</v>
+      </c>
+      <c r="E1578" t="s">
+        <v>236</v>
+      </c>
+      <c r="F1578" s="29">
+        <v>46181</v>
+      </c>
+      <c r="G1578" s="55">
+        <v>5.2326388888888888E-2</v>
+      </c>
+      <c r="H1578" s="183" t="s">
+        <v>815</v>
+      </c>
+      <c r="I1578" s="183" t="s">
+        <v>290</v>
+      </c>
+      <c r="J1578" s="62" t="s">
+        <v>4510</v>
+      </c>
+      <c r="K1578">
+        <v>1579</v>
+      </c>
+      <c r="M1578" s="56" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1578" t="s">
+        <v>4528</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1579">
+        <v>93</v>
+      </c>
+      <c r="B1579" s="7">
+        <v>3957092</v>
+      </c>
+      <c r="C1579" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1579" t="s">
+        <v>4512</v>
+      </c>
+      <c r="E1579" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1579" s="29">
+        <v>46210</v>
+      </c>
+      <c r="G1579" s="55">
+        <v>5.9074074074074077E-2</v>
+      </c>
+      <c r="H1579" s="183" t="s">
+        <v>1321</v>
+      </c>
+      <c r="I1579" s="183" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1579" s="62" t="s">
+        <v>4511</v>
+      </c>
+      <c r="K1579">
+        <v>1580</v>
+      </c>
+      <c r="M1579" s="56" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1579" t="s">
+        <v>4529</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1580">
+        <v>93</v>
+      </c>
+      <c r="B1580" s="7">
+        <v>9008497</v>
+      </c>
+      <c r="C1580" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1580" t="s">
+        <v>431</v>
+      </c>
+      <c r="E1580" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1580" s="29">
+        <v>46210</v>
+      </c>
+      <c r="G1580" s="55">
+        <v>0.1925462962962963</v>
+      </c>
+      <c r="H1580" s="183" t="s">
+        <v>815</v>
+      </c>
+      <c r="I1580" s="183" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1580" s="62" t="s">
+        <v>4513</v>
+      </c>
+      <c r="K1580">
+        <v>1581</v>
+      </c>
+      <c r="M1580" s="56" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1580" t="s">
+        <v>4530</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1581">
+        <v>93</v>
+      </c>
+      <c r="B1581" s="7">
+        <v>14000000</v>
+      </c>
+      <c r="C1581" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1581" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1581" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1581" s="29">
+        <v>46210</v>
+      </c>
+      <c r="G1581" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1581" s="183" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1581" s="183" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1581" s="62" t="s">
+        <v>4514</v>
+      </c>
+      <c r="K1581">
+        <v>1582</v>
+      </c>
+      <c r="M1581" s="56" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1581" t="s">
+        <v>4531</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1582">
+        <v>93</v>
+      </c>
+      <c r="B1582" s="7">
+        <v>5476493</v>
+      </c>
+      <c r="C1582" t="s">
+        <v>4515</v>
+      </c>
+      <c r="D1582" t="s">
+        <v>4516</v>
+      </c>
+      <c r="E1582" t="s">
+        <v>648</v>
+      </c>
+      <c r="F1582" s="29">
+        <v>46210</v>
+      </c>
+      <c r="G1582" s="55">
+        <v>4.6018518518518514E-2</v>
+      </c>
+      <c r="H1582" s="183" t="s">
+        <v>832</v>
+      </c>
+      <c r="I1582" s="183" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1582" s="62" t="s">
+        <v>4517</v>
+      </c>
+      <c r="K1582">
+        <v>1583</v>
+      </c>
+      <c r="M1582" s="56" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1582" t="s">
+        <v>4532</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1583">
+        <v>93</v>
+      </c>
+      <c r="B1583" s="7">
+        <v>13417047</v>
+      </c>
+      <c r="C1583" t="s">
+        <v>4520</v>
+      </c>
+      <c r="D1583" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1583" t="s">
+        <v>648</v>
+      </c>
+      <c r="F1583" s="29">
+        <v>46211</v>
+      </c>
+      <c r="G1583" s="55">
+        <v>0.12850694444444444</v>
+      </c>
+      <c r="H1583" s="183" t="s">
+        <v>832</v>
+      </c>
+      <c r="I1583" s="183" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1583" s="62" t="s">
+        <v>4518</v>
+      </c>
+      <c r="K1583">
+        <v>1584</v>
+      </c>
+      <c r="M1583" s="56" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1583" t="s">
+        <v>4533</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1584">
+        <v>93</v>
+      </c>
+      <c r="B1584" s="7">
+        <v>14071835</v>
+      </c>
+      <c r="C1584" t="s">
+        <v>4521</v>
+      </c>
+      <c r="D1584" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1584" t="s">
+        <v>4435</v>
+      </c>
+      <c r="F1584" s="29">
+        <v>46211</v>
+      </c>
+      <c r="G1584" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1584" s="183" t="s">
+        <v>2030</v>
+      </c>
+      <c r="I1584" s="183" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1584" s="62" t="s">
+        <v>4519</v>
+      </c>
+      <c r="K1584">
+        <v>1585</v>
+      </c>
+      <c r="M1584" s="56" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1584" t="s">
+        <v>4534</v>
       </c>
     </row>
   </sheetData>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13115" uniqueCount="4535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13123" uniqueCount="4538">
   <si>
     <t>Ņ</t>
   </si>
@@ -13632,6 +13632,15 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1524352629382189088/id_Yx.png?ex=6a4f6f83&amp;is=6a4e1e03&amp;hm=3f88ea0f9022312fd4c471561d2aacaacaa24bc9a4ceae05f60e8f19c54fe7b8</t>
+  </si>
+  <si>
+    <t>Yy</t>
+  </si>
+  <si>
+    <t>Jon Siege</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1524448298633662695/id_Yy.png?ex=6a4fc89d&amp;is=6a4e771d&amp;hm=22ea17337c48d20ee8221c141499de4bef822b0d0a299a2e7fb6aebceadb3720</t>
   </si>
 </sst>
 </file>
@@ -13643,11 +13652,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="132" x14ac:knownFonts="1">
+  <fonts count="133" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -14600,117 +14616,118 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="130" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="131" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="184">
+  <cellXfs count="185">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="130" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="129" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="128" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="128" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="127" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="127" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="126" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="125" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="124" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="123" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="122" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="120" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="120" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="119" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="119" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="129" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="113" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="128" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="112" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="127" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="119" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="113" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="120" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="114" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="110" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="109" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="98" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="98" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="97" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="97" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="98" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="97" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="98" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="97" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="94" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="94" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="95" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="95" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="97" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="98" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="130" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="93" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="132" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="92" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="131" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="91" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="91" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="90" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="90" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14719,18 +14736,18 @@
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="74" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="74" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="73" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="73" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="68" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14744,14 +14761,14 @@
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14796,8 +14813,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -15017,7 +15034,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1584"/>
+  <dimension ref="A1:O1586"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -74468,7 +74485,7 @@
         <v>424</v>
       </c>
       <c r="E1431" t="s">
-        <v>1583</v>
+        <v>4536</v>
       </c>
       <c r="F1431" s="29">
         <v>46058</v>
@@ -77426,7 +77443,7 @@
         <v>372</v>
       </c>
       <c r="E1503" t="s">
-        <v>1583</v>
+        <v>4536</v>
       </c>
       <c r="F1503" s="29">
         <v>46156</v>
@@ -77634,7 +77651,7 @@
         <v>424</v>
       </c>
       <c r="E1508" t="s">
-        <v>1583</v>
+        <v>4536</v>
       </c>
       <c r="F1508" s="29">
         <v>46156</v>
@@ -77839,7 +77856,7 @@
         <v>424</v>
       </c>
       <c r="E1513" t="s">
-        <v>1583</v>
+        <v>4536</v>
       </c>
       <c r="F1513" s="29">
         <v>46124</v>
@@ -78413,7 +78430,7 @@
         <v>451</v>
       </c>
       <c r="E1527" t="s">
-        <v>1583</v>
+        <v>4536</v>
       </c>
       <c r="F1527" s="29">
         <v>46180</v>
@@ -78495,7 +78512,7 @@
         <v>223</v>
       </c>
       <c r="E1529" t="s">
-        <v>1583</v>
+        <v>4536</v>
       </c>
       <c r="F1529" s="29">
         <v>46182</v>
@@ -80776,6 +80793,50 @@
       <c r="N1584" t="s">
         <v>4534</v>
       </c>
+    </row>
+    <row r="1585" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1585">
+        <v>93</v>
+      </c>
+      <c r="B1585" s="7">
+        <v>11690105</v>
+      </c>
+      <c r="C1585" t="s">
+        <v>720</v>
+      </c>
+      <c r="D1585" t="s">
+        <v>451</v>
+      </c>
+      <c r="E1585" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F1585" s="29">
+        <v>46211</v>
+      </c>
+      <c r="G1585" s="55">
+        <v>0.12886574074074073</v>
+      </c>
+      <c r="H1585" s="184" t="s">
+        <v>830</v>
+      </c>
+      <c r="I1585" s="184" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1585" s="62" t="s">
+        <v>4535</v>
+      </c>
+      <c r="K1585">
+        <v>1586</v>
+      </c>
+      <c r="M1585" s="56" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1585" t="s">
+        <v>4537</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I1586" s="184"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N1">

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13123" uniqueCount="4538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13131" uniqueCount="4541">
   <si>
     <t>Ņ</t>
   </si>
@@ -13641,6 +13641,15 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1524448298633662695/id_Yy.png?ex=6a4fc89d&amp;is=6a4e771d&amp;hm=22ea17337c48d20ee8221c141499de4bef822b0d0a299a2e7fb6aebceadb3720</t>
+  </si>
+  <si>
+    <t>Yz</t>
+  </si>
+  <si>
+    <t>[o]</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1524457591290331177/id_Yz.png?ex=6a4fd144&amp;is=6a4e7fc4&amp;hm=373b425dc5a3e452a764d4b142d20f8ce51ac5cf33d4e956ab33611ed3f69881</t>
   </si>
 </sst>
 </file>
@@ -13652,11 +13661,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="133" x14ac:knownFonts="1">
+  <fonts count="134" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -14616,117 +14632,118 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="131" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="132" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="185">
+  <cellXfs count="186">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="131" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="130" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="130" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="129" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="129" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="128" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="128" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="127" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="126" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="126" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="125" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="124" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="123" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="122" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="120" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="119" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="130" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="114" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="129" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="113" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="128" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="120" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="114" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="121" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="115" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="111" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="110" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="99" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="99" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="98" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="98" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="99" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="98" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="99" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="98" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="95" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="95" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="96" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="96" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="98" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="99" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="132" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="131" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="94" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="93" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="132" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="92" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="92" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="91" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="91" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14735,18 +14752,18 @@
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="75" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="75" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="74" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="74" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="68" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="69" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14760,14 +14777,14 @@
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="52" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14812,8 +14829,8 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -80836,7 +80853,45 @@
       </c>
     </row>
     <row r="1586" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I1586" s="184"/>
+      <c r="A1586">
+        <v>93</v>
+      </c>
+      <c r="B1586" s="7">
+        <v>9049645</v>
+      </c>
+      <c r="C1586" t="s">
+        <v>4464</v>
+      </c>
+      <c r="D1586" t="s">
+        <v>501</v>
+      </c>
+      <c r="E1586" t="s">
+        <v>4476</v>
+      </c>
+      <c r="F1586" s="29">
+        <v>46211</v>
+      </c>
+      <c r="G1586" s="55">
+        <v>0.10804398148148148</v>
+      </c>
+      <c r="H1586" s="185" t="s">
+        <v>825</v>
+      </c>
+      <c r="I1586" s="185" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1586" s="62" t="s">
+        <v>4538</v>
+      </c>
+      <c r="K1586">
+        <v>1587</v>
+      </c>
+      <c r="M1586" s="185" t="s">
+        <v>4539</v>
+      </c>
+      <c r="N1586" t="s">
+        <v>4540</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N1">

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13131" uniqueCount="4541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13166" uniqueCount="4550">
   <si>
     <t>Ņ</t>
   </si>
@@ -13650,6 +13650,33 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1524457591290331177/id_Yz.png?ex=6a4fd144&amp;is=6a4e7fc4&amp;hm=373b425dc5a3e452a764d4b142d20f8ce51ac5cf33d4e956ab33611ed3f69881</t>
+  </si>
+  <si>
+    <t>Chad</t>
+  </si>
+  <si>
+    <t>Y0</t>
+  </si>
+  <si>
+    <t>Y1</t>
+  </si>
+  <si>
+    <t>Y2</t>
+  </si>
+  <si>
+    <t>Y3</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1524719605895921754/id_Y0.png?ex=6a50c549&amp;is=6a4f73c9&amp;hm=284d4b14b07feb5cf37fc565243336d5cc7da82a33ba9a2bb4af61b7a9a11e13</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1524719674577780886/id_Y1.png?ex=6a50c55a&amp;is=6a4f73da&amp;hm=65a46fb710ae35ffbdf427e5fb0e0c60baa4b7d6f922a616aab757e08a6659e4</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1524719751245467749/id_Y2.png?ex=6a50c56c&amp;is=6a4f73ec&amp;hm=e87a412f63af0187aec0f9ad4a7972012a0bb162621a93376fd9b3633d9e66ae</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1524719798016278618/id_Y3.jpg?ex=6a50c577&amp;is=6a4f73f7&amp;hm=50a48da36e15cccf4cfa4f2cb27f736844aad26d5b167486f148da7ff24a7349</t>
   </si>
 </sst>
 </file>
@@ -13661,11 +13688,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="134" x14ac:knownFonts="1">
+  <fonts count="135" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -14632,117 +14666,118 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="132" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="186">
+  <cellXfs count="187">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="132" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="131" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="131" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="130" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="130" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="129" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="129" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="128" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="127" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="127" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="126" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="126" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="125" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="124" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="123" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="122" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="120" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="119" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="131" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="115" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="130" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="114" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="129" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="121" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="115" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="122" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="116" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="112" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="111" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="100" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="100" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="99" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="99" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="100" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="99" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="100" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="99" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="96" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="96" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="97" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="97" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="99" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="100" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="132" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="95" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="134" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="94" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="133" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="93" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="93" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="92" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="92" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14751,18 +14786,18 @@
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="76" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="76" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="75" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="75" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="69" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14776,14 +14811,14 @@
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="53" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="52" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14828,8 +14863,8 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -15051,7 +15086,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1586"/>
+  <dimension ref="A1:O1590"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -80893,6 +80928,173 @@
         <v>4540</v>
       </c>
     </row>
+    <row r="1587" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1587">
+        <v>94</v>
+      </c>
+      <c r="B1587" s="7">
+        <v>101143784</v>
+      </c>
+      <c r="C1587" t="s">
+        <v>720</v>
+      </c>
+      <c r="D1587" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1587" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F1587" s="29">
+        <v>46212</v>
+      </c>
+      <c r="G1587" s="55">
+        <v>0.53726851851851853</v>
+      </c>
+      <c r="H1587" s="186" t="s">
+        <v>815</v>
+      </c>
+      <c r="I1587" s="186" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1587" s="62" t="s">
+        <v>4542</v>
+      </c>
+      <c r="K1587">
+        <v>1588</v>
+      </c>
+      <c r="L1587" t="s">
+        <v>4541</v>
+      </c>
+      <c r="M1587" s="186" t="s">
+        <v>4539</v>
+      </c>
+      <c r="N1587" t="s">
+        <v>4546</v>
+      </c>
+    </row>
+    <row r="1588" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1588">
+        <v>94</v>
+      </c>
+      <c r="B1588" s="7">
+        <v>62355908</v>
+      </c>
+      <c r="C1588" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1588" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1588" t="s">
+        <v>648</v>
+      </c>
+      <c r="F1588" s="29">
+        <v>46212</v>
+      </c>
+      <c r="G1588" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1588" s="186" t="s">
+        <v>830</v>
+      </c>
+      <c r="I1588" s="186" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1588" s="62" t="s">
+        <v>4543</v>
+      </c>
+      <c r="K1588">
+        <v>1589</v>
+      </c>
+      <c r="M1588" s="185" t="s">
+        <v>4539</v>
+      </c>
+      <c r="N1588" t="s">
+        <v>4547</v>
+      </c>
+    </row>
+    <row r="1589" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1589">
+        <v>94</v>
+      </c>
+      <c r="B1589" s="7">
+        <v>59618660</v>
+      </c>
+      <c r="C1589" t="s">
+        <v>641</v>
+      </c>
+      <c r="D1589" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1589" t="s">
+        <v>642</v>
+      </c>
+      <c r="F1589" s="29">
+        <v>46212</v>
+      </c>
+      <c r="G1589" s="55">
+        <v>0.3125</v>
+      </c>
+      <c r="H1589" s="186" t="s">
+        <v>886</v>
+      </c>
+      <c r="I1589" s="186" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1589" s="62" t="s">
+        <v>4544</v>
+      </c>
+      <c r="K1589">
+        <v>1590</v>
+      </c>
+      <c r="M1589" s="186" t="s">
+        <v>4539</v>
+      </c>
+      <c r="N1589" t="s">
+        <v>4548</v>
+      </c>
+    </row>
+    <row r="1590" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1590">
+        <v>94</v>
+      </c>
+      <c r="B1590" s="7">
+        <v>45209643</v>
+      </c>
+      <c r="C1590" t="s">
+        <v>4509</v>
+      </c>
+      <c r="D1590" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1590" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1590" s="29">
+        <v>46212</v>
+      </c>
+      <c r="G1590" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1590" s="186" t="s">
+        <v>1313</v>
+      </c>
+      <c r="I1590" s="186" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1590" s="62" t="s">
+        <v>4545</v>
+      </c>
+      <c r="K1590">
+        <v>1591</v>
+      </c>
+      <c r="M1590" s="185" t="s">
+        <v>4539</v>
+      </c>
+      <c r="N1590" t="s">
+        <v>4549</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N1">
     <sortState ref="A2:N1568">

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13166" uniqueCount="4550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13190" uniqueCount="4559">
   <si>
     <t>Ņ</t>
   </si>
@@ -13646,9 +13646,6 @@
     <t>Yz</t>
   </si>
   <si>
-    <t>[o]</t>
-  </si>
-  <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1524457591290331177/id_Yz.png?ex=6a4fd144&amp;is=6a4e7fc4&amp;hm=373b425dc5a3e452a764d4b142d20f8ce51ac5cf33d4e956ab33611ed3f69881</t>
   </si>
   <si>
@@ -13677,6 +13674,36 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1524719798016278618/id_Y3.jpg?ex=6a50c577&amp;is=6a4f73f7&amp;hm=50a48da36e15cccf4cfa4f2cb27f736844aad26d5b167486f148da7ff24a7349</t>
+  </si>
+  <si>
+    <t>Rebounder</t>
+  </si>
+  <si>
+    <t>Y4</t>
+  </si>
+  <si>
+    <t>Y5</t>
+  </si>
+  <si>
+    <t>10m speedrun</t>
+  </si>
+  <si>
+    <t>V= v0 + a-t</t>
+  </si>
+  <si>
+    <t>Auto-Integrator</t>
+  </si>
+  <si>
+    <t>Y6</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1524775370132295850/id_Y4.png?ex=6a50f939&amp;is=6a4fa7b9&amp;hm=a85b8355f205e06d83f325ccdee2fd09ee40fda3715493df2861b56a7cceef00</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1524775419423887380/id_Y5.png?ex=6a50f944&amp;is=6a4fa7c4&amp;hm=43f7fe89df0d332f60c47bd8cfd4080977ef44ba7ccf11d9879fb03dcbb12664</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1524775464638353538/id_Y6.png?ex=6a50f94f&amp;is=6a4fa7cf&amp;hm=338ab1207ce3254b1a8ad97489ca3f7a5747af917532c68d1961b7404ed1e7d9</t>
   </si>
 </sst>
 </file>
@@ -13688,11 +13715,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="135" x14ac:knownFonts="1">
+  <fonts count="136" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -14666,117 +14700,118 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="133" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="134" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="187">
+  <cellXfs count="189">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="132" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="132" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="131" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="131" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="130" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="130" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="129" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="128" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="128" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="127" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="127" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="126" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="125" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="124" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="123" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="122" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="120" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="119" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="132" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="116" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="131" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="115" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="130" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="122" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="116" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="123" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="117" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="113" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="112" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="101" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="101" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="100" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="100" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="101" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="100" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="101" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="100" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="97" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="97" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="98" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="98" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="100" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="101" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="134" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="133" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="96" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="95" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="134" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="94" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="94" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="93" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="93" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14785,18 +14820,18 @@
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="77" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="77" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="76" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="76" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="71" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14810,14 +14845,14 @@
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="53" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="52" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14862,14 +14897,15 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -15086,7 +15122,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1590"/>
+  <dimension ref="A1:O1593"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -80921,11 +80957,11 @@
       <c r="K1586">
         <v>1587</v>
       </c>
-      <c r="M1586" s="185" t="s">
+      <c r="M1586" s="56" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1586" t="s">
         <v>4539</v>
-      </c>
-      <c r="N1586" t="s">
-        <v>4540</v>
       </c>
     </row>
     <row r="1587" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -80957,19 +80993,19 @@
         <v>806</v>
       </c>
       <c r="J1587" s="62" t="s">
-        <v>4542</v>
+        <v>4541</v>
       </c>
       <c r="K1587">
         <v>1588</v>
       </c>
       <c r="L1587" t="s">
-        <v>4541</v>
-      </c>
-      <c r="M1587" s="186" t="s">
-        <v>4539</v>
+        <v>4540</v>
+      </c>
+      <c r="M1587" s="56" t="s">
+        <v>854</v>
       </c>
       <c r="N1587" t="s">
-        <v>4546</v>
+        <v>4545</v>
       </c>
     </row>
     <row r="1588" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -81001,16 +81037,16 @@
         <v>806</v>
       </c>
       <c r="J1588" s="62" t="s">
-        <v>4543</v>
+        <v>4542</v>
       </c>
       <c r="K1588">
         <v>1589</v>
       </c>
-      <c r="M1588" s="185" t="s">
-        <v>4539</v>
+      <c r="M1588" s="56" t="s">
+        <v>854</v>
       </c>
       <c r="N1588" t="s">
-        <v>4547</v>
+        <v>4546</v>
       </c>
     </row>
     <row r="1589" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -81042,16 +81078,16 @@
         <v>806</v>
       </c>
       <c r="J1589" s="62" t="s">
-        <v>4544</v>
+        <v>4543</v>
       </c>
       <c r="K1589">
         <v>1590</v>
       </c>
-      <c r="M1589" s="186" t="s">
-        <v>4539</v>
+      <c r="M1589" s="56" t="s">
+        <v>854</v>
       </c>
       <c r="N1589" t="s">
-        <v>4548</v>
+        <v>4547</v>
       </c>
     </row>
     <row r="1590" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -81073,8 +81109,8 @@
       <c r="F1590" s="29">
         <v>46212</v>
       </c>
-      <c r="G1590" s="55" t="s">
-        <v>11</v>
+      <c r="G1590" s="55">
+        <v>0.1875</v>
       </c>
       <c r="H1590" s="186" t="s">
         <v>1313</v>
@@ -81083,16 +81119,139 @@
         <v>806</v>
       </c>
       <c r="J1590" s="62" t="s">
-        <v>4545</v>
+        <v>4544</v>
       </c>
       <c r="K1590">
         <v>1591</v>
       </c>
-      <c r="M1590" s="185" t="s">
-        <v>4539</v>
+      <c r="M1590" s="56" t="s">
+        <v>854</v>
       </c>
       <c r="N1590" t="s">
+        <v>4548</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1591">
+        <v>94</v>
+      </c>
+      <c r="B1591" s="7">
+        <v>7737803</v>
+      </c>
+      <c r="C1591" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1591" t="s">
         <v>4549</v>
+      </c>
+      <c r="E1591" t="s">
+        <v>648</v>
+      </c>
+      <c r="F1591" s="29">
+        <v>46211</v>
+      </c>
+      <c r="G1591" s="55">
+        <v>5.2986111111111116E-2</v>
+      </c>
+      <c r="H1591" s="187" t="s">
+        <v>835</v>
+      </c>
+      <c r="I1591" s="187" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1591" s="62" t="s">
+        <v>4550</v>
+      </c>
+      <c r="K1591">
+        <v>1592</v>
+      </c>
+      <c r="M1591" s="56" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1591" t="s">
+        <v>4556</v>
+      </c>
+    </row>
+    <row r="1592" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1592">
+        <v>94</v>
+      </c>
+      <c r="B1592" s="7">
+        <v>24044313</v>
+      </c>
+      <c r="C1592" t="s">
+        <v>4552</v>
+      </c>
+      <c r="D1592" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1592" t="s">
+        <v>218</v>
+      </c>
+      <c r="F1592" s="29">
+        <v>46212</v>
+      </c>
+      <c r="G1592" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1592" s="187" t="s">
+        <v>1313</v>
+      </c>
+      <c r="I1592" s="187" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1592" s="62" t="s">
+        <v>4551</v>
+      </c>
+      <c r="K1592">
+        <v>1593</v>
+      </c>
+      <c r="M1592" s="56" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1592" t="s">
+        <v>4557</v>
+      </c>
+    </row>
+    <row r="1593" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1593">
+        <v>94</v>
+      </c>
+      <c r="B1593" s="7">
+        <v>3248319</v>
+      </c>
+      <c r="C1593" s="187" t="s">
+        <v>4553</v>
+      </c>
+      <c r="D1593" s="187" t="s">
+        <v>4554</v>
+      </c>
+      <c r="E1593" s="187" t="s">
+        <v>3847</v>
+      </c>
+      <c r="F1593" s="29">
+        <v>46110</v>
+      </c>
+      <c r="G1593" s="55">
+        <v>5.1631944444444446E-2</v>
+      </c>
+      <c r="H1593" s="187" t="s">
+        <v>885</v>
+      </c>
+      <c r="I1593" s="187" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1593" s="188" t="s">
+        <v>4555</v>
+      </c>
+      <c r="K1593">
+        <v>1594</v>
+      </c>
+      <c r="M1593" s="56" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1593" t="s">
+        <v>4558</v>
       </c>
     </row>
   </sheetData>

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13190" uniqueCount="4559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13256" uniqueCount="4581">
   <si>
     <t>Ņ</t>
   </si>
@@ -13704,6 +13704,95 @@
   </si>
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1524775464638353538/id_Y6.png?ex=6a50f94f&amp;is=6a4fa7cf&amp;hm=338ab1207ce3254b1a8ad97489ca3f7a5747af917532c68d1961b7404ed1e7d9</t>
+  </si>
+  <si>
+    <t>Y7</t>
+  </si>
+  <si>
+    <t>Y8</t>
+  </si>
+  <si>
+    <t>Joan of Arc</t>
+  </si>
+  <si>
+    <t>Virago</t>
+  </si>
+  <si>
+    <t>Y9</t>
+  </si>
+  <si>
+    <t>Pentateam[pol]</t>
+  </si>
+  <si>
+    <t>Pentateam</t>
+  </si>
+  <si>
+    <t>10m speed</t>
+  </si>
+  <si>
+    <t>Y(</t>
+  </si>
+  <si>
+    <t>Y)</t>
+  </si>
+  <si>
+    <t>ZA</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1525082799860613250/id_Y7.png?ex=6a52178a&amp;is=6a50c60a&amp;hm=fd5b34faae4530992dd84e8e3142e75909ea28121376c0b0cd2b859c7c43695a</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1525082944987861033/id_Y8.png?ex=6a5217ac&amp;is=6a50c62c&amp;hm=79af48d96274816a3f5384d4f8ed4fffb1a96f5d52b3cf45378d696bf3c19440</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1525083027414454332/id_Y9.png?ex=6a5217c0&amp;is=6a50c640&amp;hm=3f1c9fedd13878e1e122cb58511e7b3884a964d944240c5597abbc83323a60c8</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1525083568039133204/id_Y.png?ex=6a521841&amp;is=6a50c6c1&amp;hm=763798c71d3bb9e26225dbb9d3b0a488878035b005e902719f6e147e78a5f749</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1525083631608008774/id_Y.png?ex=6a521850&amp;is=6a50c6d0&amp;hm=7a8b7c77c668617307f647cc8e1c7955e061f6e73d7e3d650171eab1db99bb4d</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1525083698209361950/id_ZA.png?ex=6a521860&amp;is=6a50c6e0&amp;hm=f15f2943531a7e801d229e067ea2e8330fbbf0ae48125eeca4e748ea014b17bc</t>
+  </si>
+  <si>
+    <r>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>jm</t>
+    </r>
+  </si>
+  <si>
+    <t>ZB</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1525085091439579146/id_ZB.png?ex=6a5219ac&amp;is=6a50c82c&amp;hm=fe9d2f41947bdc69a7630b791ee2ff8b8a6ba3a307bb2e20ff64a9c0ad5f56e7</t>
+  </si>
+  <si>
+    <t>ZC</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1525087505664311336/id_ZC.png?ex=6a521bec&amp;is=6a50ca6c&amp;hm=544038f24fb8f00a2406f81c50c8fa0cb3a205dec86efd3605d820046ce668cb</t>
   </si>
 </sst>
 </file>
@@ -13715,11 +13804,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="136" x14ac:knownFonts="1">
+  <fonts count="138" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -14665,6 +14761,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -14700,117 +14804,118 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="134" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="189">
+  <cellXfs count="191">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="134" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="133" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="132" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="132" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="131" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="131" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="130" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="129" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="128" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="128" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="127" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="126" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="125" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="124" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="123" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="123" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="122" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="120" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="119" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="133" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="117" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="132" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="116" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="131" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="123" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="117" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="124" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="118" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="114" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="113" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="102" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="102" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="101" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="101" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="102" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="101" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="102" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="101" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="98" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="98" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="99" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="99" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="101" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="101" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="102" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="134" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="97" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="96" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="135" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="95" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="95" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="94" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="94" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14819,18 +14924,18 @@
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="77" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="77" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="71" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="72" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14844,14 +14949,14 @@
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="53" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14896,14 +15001,15 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
@@ -15122,7 +15228,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1593"/>
+  <dimension ref="A1:O1601"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -81254,6 +81360,334 @@
         <v>4558</v>
       </c>
     </row>
+    <row r="1594" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1594">
+        <v>95</v>
+      </c>
+      <c r="B1594" s="7">
+        <v>2505617</v>
+      </c>
+      <c r="C1594" s="187" t="s">
+        <v>4553</v>
+      </c>
+      <c r="D1594" s="189" t="s">
+        <v>613</v>
+      </c>
+      <c r="E1594" s="187" t="s">
+        <v>3847</v>
+      </c>
+      <c r="F1594" s="29">
+        <v>46110</v>
+      </c>
+      <c r="G1594" s="55">
+        <v>2.1527777777777781E-2</v>
+      </c>
+      <c r="H1594" s="189" t="s">
+        <v>1321</v>
+      </c>
+      <c r="I1594" s="189" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1594" s="62" t="s">
+        <v>4559</v>
+      </c>
+      <c r="K1594">
+        <v>1595</v>
+      </c>
+      <c r="M1594" s="56" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1594" t="s">
+        <v>4570</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1595">
+        <v>95</v>
+      </c>
+      <c r="B1595" s="7">
+        <v>2503151</v>
+      </c>
+      <c r="C1595" s="189" t="s">
+        <v>4561</v>
+      </c>
+      <c r="D1595" s="189" t="s">
+        <v>4562</v>
+      </c>
+      <c r="E1595" s="189" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1595" s="29">
+        <v>46212</v>
+      </c>
+      <c r="G1595" s="55">
+        <v>4.3807870370370372E-2</v>
+      </c>
+      <c r="H1595" s="189" t="s">
+        <v>815</v>
+      </c>
+      <c r="I1595" s="189" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1595" s="62" t="s">
+        <v>4560</v>
+      </c>
+      <c r="K1595">
+        <v>1596</v>
+      </c>
+      <c r="M1595" s="56" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1595" t="s">
+        <v>4571</v>
+      </c>
+    </row>
+    <row r="1596" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1596">
+        <v>95</v>
+      </c>
+      <c r="B1596" s="7">
+        <v>30114142</v>
+      </c>
+      <c r="C1596" s="189" t="s">
+        <v>236</v>
+      </c>
+      <c r="D1596" s="189" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1596" s="189" t="s">
+        <v>236</v>
+      </c>
+      <c r="F1596" s="29">
+        <v>46212</v>
+      </c>
+      <c r="G1596" s="55">
+        <v>0.15202546296296296</v>
+      </c>
+      <c r="H1596" s="189" t="s">
+        <v>2456</v>
+      </c>
+      <c r="I1596" s="189" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1596" s="62" t="s">
+        <v>4563</v>
+      </c>
+      <c r="K1596">
+        <v>1597</v>
+      </c>
+      <c r="M1596" s="56" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1596" t="s">
+        <v>4572</v>
+      </c>
+    </row>
+    <row r="1597" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1597">
+        <v>95</v>
+      </c>
+      <c r="B1597" s="7">
+        <v>11044241</v>
+      </c>
+      <c r="C1597" s="189" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1597" s="189" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1597" s="189" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1597" s="29">
+        <v>46212</v>
+      </c>
+      <c r="G1597" s="55">
+        <v>8.0555555555555561E-2</v>
+      </c>
+      <c r="H1597" s="189" t="s">
+        <v>1313</v>
+      </c>
+      <c r="I1597" s="189" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1597" s="62" t="s">
+        <v>4567</v>
+      </c>
+      <c r="K1597">
+        <v>1598</v>
+      </c>
+      <c r="M1597" s="56" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1597" t="s">
+        <v>4573</v>
+      </c>
+    </row>
+    <row r="1598" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1598">
+        <v>95</v>
+      </c>
+      <c r="B1598" s="7">
+        <v>18310000</v>
+      </c>
+      <c r="C1598" s="189" t="s">
+        <v>4564</v>
+      </c>
+      <c r="D1598" s="189" t="s">
+        <v>424</v>
+      </c>
+      <c r="E1598" s="189" t="s">
+        <v>4565</v>
+      </c>
+      <c r="F1598" s="29">
+        <v>46212</v>
+      </c>
+      <c r="G1598" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1598" s="189" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1598" s="189" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1598" s="62" t="s">
+        <v>4568</v>
+      </c>
+      <c r="K1598">
+        <v>1599</v>
+      </c>
+      <c r="M1598" s="56" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1598" t="s">
+        <v>4574</v>
+      </c>
+    </row>
+    <row r="1599" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1599">
+        <v>95</v>
+      </c>
+      <c r="B1599" s="7">
+        <v>34670000</v>
+      </c>
+      <c r="C1599" s="189" t="s">
+        <v>4566</v>
+      </c>
+      <c r="D1599" s="189" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1599" s="189" t="s">
+        <v>218</v>
+      </c>
+      <c r="F1599" s="29">
+        <v>46212</v>
+      </c>
+      <c r="G1599" s="55" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1599" s="189" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1599" s="189" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1599" s="62" t="s">
+        <v>4569</v>
+      </c>
+      <c r="K1599">
+        <v>1600</v>
+      </c>
+      <c r="M1599" s="56" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1599" t="s">
+        <v>4575</v>
+      </c>
+    </row>
+    <row r="1600" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1600">
+        <v>95</v>
+      </c>
+      <c r="B1600" s="7">
+        <v>11277051</v>
+      </c>
+      <c r="C1600" s="189" t="s">
+        <v>4576</v>
+      </c>
+      <c r="D1600" s="189" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1600" s="189" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1600" s="29">
+        <v>45684</v>
+      </c>
+      <c r="G1600" s="55">
+        <v>0.14509259259259258</v>
+      </c>
+      <c r="H1600" s="189" t="s">
+        <v>1321</v>
+      </c>
+      <c r="I1600" s="189" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1600" s="190" t="s">
+        <v>4577</v>
+      </c>
+      <c r="K1600">
+        <v>1601</v>
+      </c>
+      <c r="M1600" s="56" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1600" t="s">
+        <v>4578</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1601">
+        <v>95</v>
+      </c>
+      <c r="B1601" s="7">
+        <v>3905808</v>
+      </c>
+      <c r="C1601" s="189" t="s">
+        <v>236</v>
+      </c>
+      <c r="D1601" s="189" t="s">
+        <v>89</v>
+      </c>
+      <c r="E1601" s="189" t="s">
+        <v>236</v>
+      </c>
+      <c r="F1601" s="29">
+        <v>45834</v>
+      </c>
+      <c r="G1601" s="55">
+        <v>2.0879629629629626E-2</v>
+      </c>
+      <c r="H1601" s="189" t="s">
+        <v>835</v>
+      </c>
+      <c r="I1601" s="189" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1601" s="190" t="s">
+        <v>4579</v>
+      </c>
+      <c r="K1601">
+        <v>1602</v>
+      </c>
+      <c r="M1601" s="56" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1601" t="s">
+        <v>4580</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N1">
     <sortState ref="A2:N1568">

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13256" uniqueCount="4581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13264" uniqueCount="4584">
   <si>
     <t>Ņ</t>
   </si>
@@ -13794,6 +13794,15 @@
   <si>
     <t>https://cdn.discordapp.com/attachments/1466759427955888160/1525087505664311336/id_ZC.png?ex=6a521bec&amp;is=6a50ca6c&amp;hm=544038f24fb8f00a2406f81c50c8fa0cb3a205dec86efd3605d820046ce668cb</t>
   </si>
+  <si>
+    <t>Nest Warden/LC/Enchantress</t>
+  </si>
+  <si>
+    <t>ZD</t>
+  </si>
+  <si>
+    <t>https://cdn.discordapp.com/attachments/1466759427955888160/1526304925380775946/id_ZD.png?ex=6a5689bb&amp;is=6a55383b&amp;hm=50074992aa2452bdcb89990d3a4ccaac87eb470bb5107b3ad021b253f555fb0f</t>
+  </si>
 </sst>
 </file>
 
@@ -13804,11 +13813,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="138" x14ac:knownFonts="1">
+  <fonts count="139" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -14804,117 +14820,118 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="135" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="191">
+  <cellXfs count="192">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="134" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="134" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="133" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="133" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="132" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="132" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="131" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="130" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="130" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="129" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="129" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="128" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="127" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="126" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="125" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="124" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="123" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="122" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="120" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="119" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="134" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="118" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="133" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="117" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="132" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="124" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="118" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="125" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="119" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="115" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="114" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="103" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="103" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="102" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="102" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="103" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="102" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="103" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="102" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="99" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="99" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="100" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="100" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="102" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="102" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="102" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="103" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="135" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="98" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="97" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="136" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="96" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="96" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="95" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="95" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14923,18 +14940,18 @@
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="72" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="73" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14948,14 +14965,14 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -15000,18 +15017,18 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -15228,7 +15245,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1601"/>
+  <dimension ref="A1:O1602"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -81688,6 +81705,47 @@
         <v>4580</v>
       </c>
     </row>
+    <row r="1602" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1602">
+        <v>96</v>
+      </c>
+      <c r="B1602" s="7">
+        <v>12756666</v>
+      </c>
+      <c r="C1602" s="191" t="s">
+        <v>1583</v>
+      </c>
+      <c r="D1602" s="191" t="s">
+        <v>223</v>
+      </c>
+      <c r="E1602" s="191" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F1602" s="29">
+        <v>46216</v>
+      </c>
+      <c r="G1602" s="55">
+        <v>9.2199074074074072E-2</v>
+      </c>
+      <c r="H1602" s="191" t="s">
+        <v>4581</v>
+      </c>
+      <c r="I1602" s="191" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1602" s="62" t="s">
+        <v>4582</v>
+      </c>
+      <c r="K1602">
+        <v>1603</v>
+      </c>
+      <c r="M1602" s="56" t="s">
+        <v>854</v>
+      </c>
+      <c r="N1602" t="s">
+        <v>4583</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N1">
     <sortState ref="A2:N1568">

--- a/data/Olympus.xlsx
+++ b/data/Olympus.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13264" uniqueCount="4584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13264" uniqueCount="4583">
   <si>
     <t>Ņ</t>
   </si>
@@ -13488,9 +13488,6 @@
   </si>
   <si>
     <t>Yh</t>
-  </si>
-  <si>
-    <t>Schroldingongle</t>
   </si>
   <si>
     <t>Nest Warden/Nest Keeper/Kronos</t>
@@ -13813,11 +13810,18 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="139" x14ac:knownFonts="1">
+  <fonts count="140" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -14820,7 +14824,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="136" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="192">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14829,108 +14833,109 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="135" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="134" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="134" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="133" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="133" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="132" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="131" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="131" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="130" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="130" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="129" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="128" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="127" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="126" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="126" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="125" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="124" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="123" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="122" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="118" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="135" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="119" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="134" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="118" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="133" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="125" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="119" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="126" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="120" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="116" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="115" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="114" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="113" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="112" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="104" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="46" fontId="104" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="103" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="46" fontId="103" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="46" fontId="104" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="103" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="104" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="103" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="100" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="100" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="101" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="101" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="103" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="103" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="103" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="104" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="136" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="99" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="98" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="137" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="97" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="46" fontId="97" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="96" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="96" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14939,18 +14944,18 @@
     <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="46" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="79" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="78" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="46" fontId="73" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="46" fontId="74" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -14964,14 +14969,14 @@
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="57" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="55" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -15016,19 +15021,18 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -16532,7 +16536,7 @@
         <v>60</v>
       </c>
       <c r="E30" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F30" s="29">
         <v>46000</v>
@@ -16914,7 +16918,7 @@
         <v>35</v>
       </c>
       <c r="E39" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F39" s="29">
         <v>45984</v>
@@ -19368,7 +19372,7 @@
         <v>5</v>
       </c>
       <c r="E96" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F96" s="30">
         <v>45756</v>
@@ -20101,7 +20105,7 @@
         <v>5</v>
       </c>
       <c r="E113" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F113" s="29">
         <v>45693</v>
@@ -20185,7 +20189,7 @@
         <v>60</v>
       </c>
       <c r="E115" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F115" s="30">
         <v>45741</v>
@@ -21135,7 +21139,7 @@
         <v>9</v>
       </c>
       <c r="E137" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F137" s="29">
         <v>46013</v>
@@ -21814,7 +21818,7 @@
         <v>5</v>
       </c>
       <c r="E153" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F153" s="29">
         <v>45779</v>
@@ -22628,7 +22632,7 @@
         <v>15</v>
       </c>
       <c r="E172" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F172" s="29">
         <v>45539</v>
@@ -23186,7 +23190,7 @@
         <v>60</v>
       </c>
       <c r="E185" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F185" s="30">
         <v>45773</v>
@@ -24507,7 +24511,7 @@
         <v>15</v>
       </c>
       <c r="E216" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F216" s="29">
         <v>46016</v>
@@ -28248,7 +28252,7 @@
         <v>465</v>
       </c>
       <c r="E305" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F305" s="29">
         <v>45999</v>
@@ -28545,7 +28549,7 @@
         <v>65</v>
       </c>
       <c r="E312" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F312" s="30">
         <v>45800</v>
@@ -28751,7 +28755,7 @@
         <v>5</v>
       </c>
       <c r="E317" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F317" s="29">
         <v>45712</v>
@@ -30945,7 +30949,7 @@
         <v>60</v>
       </c>
       <c r="E370" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F370" s="29">
         <v>45699</v>
@@ -34310,7 +34314,7 @@
         <v>60</v>
       </c>
       <c r="E451" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F451" s="29">
         <v>46033</v>
@@ -39413,7 +39417,7 @@
         <v>171</v>
       </c>
       <c r="E574" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F574" s="29">
         <v>45795</v>
@@ -41239,7 +41243,7 @@
         <v>570</v>
       </c>
       <c r="E618" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F618" s="29">
         <v>46046</v>
@@ -41857,7 +41861,7 @@
         <v>345</v>
       </c>
       <c r="E633" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F633" s="29">
         <v>45998</v>
@@ -43012,7 +43016,7 @@
         <v>372</v>
       </c>
       <c r="E661" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F661" s="29">
         <v>45998</v>
@@ -43094,7 +43098,7 @@
         <v>569</v>
       </c>
       <c r="E663" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F663" s="29">
         <v>46006</v>
@@ -43833,7 +43837,7 @@
         <v>333</v>
       </c>
       <c r="E681" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F681" s="29">
         <v>45996</v>
@@ -43874,7 +43878,7 @@
         <v>698</v>
       </c>
       <c r="E682" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F682" s="29">
         <v>46023</v>
@@ -46897,7 +46901,7 @@
         <v>334</v>
       </c>
       <c r="E755" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F755" s="29">
         <v>46010</v>
@@ -47679,7 +47683,7 @@
         <v>389</v>
       </c>
       <c r="E774" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F774" s="29">
         <v>46004</v>
@@ -48253,7 +48257,7 @@
         <v>506</v>
       </c>
       <c r="E788" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F788" s="29">
         <v>46018</v>
@@ -48707,7 +48711,7 @@
         <v>171</v>
       </c>
       <c r="E799" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F799" s="29">
         <v>46017</v>
@@ -49489,7 +49493,7 @@
         <v>334</v>
       </c>
       <c r="E818" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F818" s="29">
         <v>46004</v>
@@ -49776,7 +49780,7 @@
         <v>700</v>
       </c>
       <c r="E825" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F825" s="29">
         <v>46024</v>
@@ -50561,7 +50565,7 @@
         <v>564</v>
       </c>
       <c r="E844" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F844" s="29">
         <v>46012</v>
@@ -50807,7 +50811,7 @@
         <v>448</v>
       </c>
       <c r="E850" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F850" s="29">
         <v>45998</v>
@@ -51176,7 +51180,7 @@
         <v>333</v>
       </c>
       <c r="E859" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F859" s="29">
         <v>45808</v>
@@ -51507,7 +51511,7 @@
         <v>699</v>
       </c>
       <c r="E867" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F867" s="29">
         <v>46024</v>
@@ -51671,7 +51675,7 @@
         <v>171</v>
       </c>
       <c r="E871" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F871" s="29">
         <v>46033</v>
@@ -51999,7 +52003,7 @@
         <v>334</v>
       </c>
       <c r="E879" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F879" s="29">
         <v>45878</v>
@@ -53777,7 +53781,7 @@
         <v>760</v>
       </c>
       <c r="E922" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F922" s="29">
         <v>46039</v>
@@ -54146,7 +54150,7 @@
         <v>765</v>
       </c>
       <c r="E931" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F931" s="29">
         <v>46043</v>
@@ -55218,7 +55222,7 @@
         <v>572</v>
       </c>
       <c r="E957" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F957" s="29">
         <v>46007</v>
@@ -55382,7 +55386,7 @@
         <v>764</v>
       </c>
       <c r="E961" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F961" s="29">
         <v>46043</v>
@@ -56739,7 +56743,7 @@
         <v>590</v>
       </c>
       <c r="E994" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F994" s="29">
         <v>46008</v>
@@ -56862,7 +56866,7 @@
         <v>677</v>
       </c>
       <c r="E997" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F997" s="29">
         <v>46020</v>
@@ -56903,7 +56907,7 @@
         <v>701</v>
       </c>
       <c r="E998" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F998" s="29">
         <v>46024</v>
@@ -56985,7 +56989,7 @@
         <v>386</v>
       </c>
       <c r="E1000" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F1000" s="29">
         <v>46018</v>
@@ -58019,7 +58023,7 @@
         <v>573</v>
       </c>
       <c r="E1025" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F1025" s="29">
         <v>46007</v>
@@ -58142,7 +58146,7 @@
         <v>697</v>
       </c>
       <c r="E1028" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F1028" s="29">
         <v>46022</v>
@@ -58511,7 +58515,7 @@
         <v>783</v>
       </c>
       <c r="E1037" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F1037" s="29">
         <v>46046</v>
@@ -58640,7 +58644,7 @@
         <v>607</v>
       </c>
       <c r="E1040" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F1040" s="29">
         <v>46009</v>
@@ -59179,7 +59183,7 @@
         <v>517</v>
       </c>
       <c r="E1053" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F1053" s="29">
         <v>46019</v>
@@ -59508,7 +59512,7 @@
         <v>947</v>
       </c>
       <c r="E1061" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F1061" s="29">
         <v>46051</v>
@@ -60615,7 +60619,7 @@
         <v>1471</v>
       </c>
       <c r="E1088" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F1088" s="29">
         <v>46061</v>
@@ -61028,7 +61032,7 @@
         <v>1625</v>
       </c>
       <c r="E1098" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F1098" s="29">
         <v>46062</v>
@@ -61192,7 +61196,7 @@
         <v>1718</v>
       </c>
       <c r="E1102" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F1102" s="29">
         <v>46062</v>
@@ -61438,7 +61442,7 @@
         <v>60</v>
       </c>
       <c r="E1108" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F1108" s="29">
         <v>45759</v>
@@ -61889,7 +61893,7 @@
         <v>60</v>
       </c>
       <c r="E1119" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F1119" s="29">
         <v>46067</v>
@@ -62668,7 +62672,7 @@
         <v>35</v>
       </c>
       <c r="E1138" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F1138" s="29">
         <v>46072</v>
@@ -64390,7 +64394,7 @@
         <v>372</v>
       </c>
       <c r="E1180" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F1180" s="29">
         <v>46071</v>
@@ -66853,7 +66857,7 @@
         <v>66</v>
       </c>
       <c r="E1240" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F1240" s="29">
         <v>46090</v>
@@ -67550,7 +67554,7 @@
         <v>3641</v>
       </c>
       <c r="E1257" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F1257" s="29">
         <v>46095</v>
@@ -67632,7 +67636,7 @@
         <v>3645</v>
       </c>
       <c r="E1259" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F1259" s="29">
         <v>46093</v>
@@ -69190,7 +69194,7 @@
         <v>685</v>
       </c>
       <c r="E1297" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F1297" s="29">
         <v>46104</v>
@@ -69313,7 +69317,7 @@
         <v>3763</v>
       </c>
       <c r="E1300" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F1300" s="29">
         <v>46105</v>
@@ -69354,7 +69358,7 @@
         <v>3764</v>
       </c>
       <c r="E1301" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F1301" s="29">
         <v>46105</v>
@@ -69395,7 +69399,7 @@
         <v>3765</v>
       </c>
       <c r="E1302" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F1302" s="29">
         <v>46105</v>
@@ -69477,7 +69481,7 @@
         <v>3776</v>
       </c>
       <c r="E1304" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F1304" s="29">
         <v>46106</v>
@@ -69518,7 +69522,7 @@
         <v>3777</v>
       </c>
       <c r="E1305" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F1305" s="29">
         <v>46106</v>
@@ -69641,7 +69645,7 @@
         <v>3914</v>
       </c>
       <c r="E1308" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F1308" s="29">
         <v>46106</v>
@@ -69682,7 +69686,7 @@
         <v>3781</v>
       </c>
       <c r="E1309" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F1309" s="29">
         <v>46106</v>
@@ -71530,7 +71534,7 @@
         <v>3902</v>
       </c>
       <c r="E1354" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F1354" s="29">
         <v>46119</v>
@@ -74696,7 +74700,7 @@
         <v>424</v>
       </c>
       <c r="E1431" t="s">
-        <v>4536</v>
+        <v>4535</v>
       </c>
       <c r="F1431" s="29">
         <v>46058</v>
@@ -75923,7 +75927,7 @@
         <v>313</v>
       </c>
       <c r="E1461" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F1461" s="29">
         <v>46145</v>
@@ -76374,7 +76378,7 @@
         <v>60</v>
       </c>
       <c r="E1472" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F1472" s="29">
         <v>46146</v>
@@ -76415,7 +76419,7 @@
         <v>4230</v>
       </c>
       <c r="E1473" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F1473" s="29">
         <v>46150</v>
@@ -76743,7 +76747,7 @@
         <v>4254</v>
       </c>
       <c r="E1481" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F1481" s="29">
         <v>46151</v>
@@ -76784,7 +76788,7 @@
         <v>4256</v>
       </c>
       <c r="E1482" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F1482" s="29">
         <v>46151</v>
@@ -76989,7 +76993,7 @@
         <v>4270</v>
       </c>
       <c r="E1487" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F1487" s="29">
         <v>46152</v>
@@ -77279,7 +77283,7 @@
         <v>4280</v>
       </c>
       <c r="E1494" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F1494" s="29">
         <v>46152</v>
@@ -77654,7 +77658,7 @@
         <v>372</v>
       </c>
       <c r="E1503" t="s">
-        <v>4536</v>
+        <v>4535</v>
       </c>
       <c r="F1503" s="29">
         <v>46156</v>
@@ -77862,7 +77866,7 @@
         <v>424</v>
       </c>
       <c r="E1508" t="s">
-        <v>4536</v>
+        <v>4535</v>
       </c>
       <c r="F1508" s="29">
         <v>46156</v>
@@ -77903,7 +77907,7 @@
         <v>4330</v>
       </c>
       <c r="E1509" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F1509" s="29">
         <v>46158</v>
@@ -77944,7 +77948,7 @@
         <v>3667</v>
       </c>
       <c r="E1510" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F1510" s="29">
         <v>46164</v>
@@ -78067,7 +78071,7 @@
         <v>424</v>
       </c>
       <c r="E1513" t="s">
-        <v>4536</v>
+        <v>4535</v>
       </c>
       <c r="F1513" s="29">
         <v>46124</v>
@@ -78641,7 +78645,7 @@
         <v>451</v>
       </c>
       <c r="E1527" t="s">
-        <v>4536</v>
+        <v>4535</v>
       </c>
       <c r="F1527" s="29">
         <v>46180</v>
@@ -78723,7 +78727,7 @@
         <v>223</v>
       </c>
       <c r="E1529" t="s">
-        <v>4536</v>
+        <v>4535</v>
       </c>
       <c r="F1529" s="29">
         <v>46182</v>
@@ -79584,7 +79588,7 @@
         <v>637</v>
       </c>
       <c r="E1550" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F1550" s="29">
         <v>46208</v>
@@ -80322,7 +80326,7 @@
         <v>60</v>
       </c>
       <c r="E1568" t="s">
-        <v>4487</v>
+        <v>331</v>
       </c>
       <c r="F1568" s="29">
         <v>46210</v>
@@ -80346,7 +80350,7 @@
         <v>854</v>
       </c>
       <c r="N1568" t="s">
-        <v>4492</v>
+        <v>4491</v>
       </c>
     </row>
     <row r="1569" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -80372,13 +80376,13 @@
         <v>6.4548611111111112E-2</v>
       </c>
       <c r="H1569" s="182" t="s">
+        <v>4487</v>
+      </c>
+      <c r="I1569" s="182" t="s">
+        <v>806</v>
+      </c>
+      <c r="J1569" s="62" t="s">
         <v>4488</v>
-      </c>
-      <c r="I1569" s="182" t="s">
-        <v>806</v>
-      </c>
-      <c r="J1569" s="62" t="s">
-        <v>4489</v>
       </c>
       <c r="K1569">
         <v>1570</v>
@@ -80387,7 +80391,7 @@
         <v>854</v>
       </c>
       <c r="N1569" t="s">
-        <v>4493</v>
+        <v>4492</v>
       </c>
     </row>
     <row r="1570" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -80398,7 +80402,7 @@
         <v>4226015</v>
       </c>
       <c r="C1570" t="s">
-        <v>4490</v>
+        <v>4489</v>
       </c>
       <c r="D1570" s="182" t="s">
         <v>203</v>
@@ -80419,7 +80423,7 @@
         <v>290</v>
       </c>
       <c r="J1570" s="62" t="s">
-        <v>4491</v>
+        <v>4490</v>
       </c>
       <c r="K1570">
         <v>1571</v>
@@ -80428,7 +80432,7 @@
         <v>854</v>
       </c>
       <c r="N1570" t="s">
-        <v>4494</v>
+        <v>4493</v>
       </c>
     </row>
     <row r="1571" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -80439,7 +80443,7 @@
         <v>16120000</v>
       </c>
       <c r="C1571" t="s">
-        <v>4495</v>
+        <v>4494</v>
       </c>
       <c r="D1571" s="182" t="s">
         <v>13</v>
@@ -80460,7 +80464,7 @@
         <v>806</v>
       </c>
       <c r="J1571" s="62" t="s">
-        <v>4496</v>
+        <v>4495</v>
       </c>
       <c r="K1571">
         <v>1572</v>
@@ -80469,7 +80473,7 @@
         <v>854</v>
       </c>
       <c r="N1571" t="s">
-        <v>4497</v>
+        <v>4496</v>
       </c>
     </row>
     <row r="1572" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -80501,7 +80505,7 @@
         <v>806</v>
       </c>
       <c r="J1572" s="62" t="s">
-        <v>4498</v>
+        <v>4497</v>
       </c>
       <c r="K1572">
         <v>1573</v>
@@ -80510,7 +80514,7 @@
         <v>854</v>
       </c>
       <c r="N1572" t="s">
-        <v>4522</v>
+        <v>4521</v>
       </c>
     </row>
     <row r="1573" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -80521,7 +80525,7 @@
         <v>8417326</v>
       </c>
       <c r="C1573" t="s">
-        <v>4499</v>
+        <v>4498</v>
       </c>
       <c r="D1573" s="183" t="s">
         <v>434</v>
@@ -80542,7 +80546,7 @@
         <v>806</v>
       </c>
       <c r="J1573" s="62" t="s">
-        <v>4500</v>
+        <v>4499</v>
       </c>
       <c r="K1573">
         <v>1574</v>
@@ -80551,7 +80555,7 @@
         <v>854</v>
       </c>
       <c r="N1573" t="s">
-        <v>4523</v>
+        <v>4522</v>
       </c>
     </row>
     <row r="1574" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -80577,13 +80581,13 @@
         <v>0.16313657407407409</v>
       </c>
       <c r="H1574" s="183" t="s">
-        <v>4502</v>
+        <v>4501</v>
       </c>
       <c r="I1574" s="183" t="s">
         <v>806</v>
       </c>
       <c r="J1574" s="62" t="s">
-        <v>4501</v>
+        <v>4500</v>
       </c>
       <c r="K1574">
         <v>1575</v>
@@ -80592,7 +80596,7 @@
         <v>854</v>
       </c>
       <c r="N1574" t="s">
-        <v>4524</v>
+        <v>4523</v>
       </c>
     </row>
     <row r="1575" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -80603,10 +80607,10 @@
         <v>1004126</v>
       </c>
       <c r="C1575" t="s">
+        <v>4502</v>
+      </c>
+      <c r="D1575" t="s">
         <v>4503</v>
-      </c>
-      <c r="D1575" t="s">
-        <v>4504</v>
       </c>
       <c r="E1575" t="s">
         <v>218</v>
@@ -80624,7 +80628,7 @@
         <v>806</v>
       </c>
       <c r="J1575" s="62" t="s">
-        <v>4505</v>
+        <v>4504</v>
       </c>
       <c r="K1575">
         <v>1576</v>
@@ -80633,7 +80637,7 @@
         <v>854</v>
       </c>
       <c r="N1575" t="s">
-        <v>4525</v>
+        <v>4524</v>
       </c>
     </row>
     <row r="1576" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -80644,13 +80648,13 @@
         <v>18160000</v>
       </c>
       <c r="C1576" t="s">
-        <v>4508</v>
+        <v>4507</v>
       </c>
       <c r="D1576" t="s">
         <v>65</v>
       </c>
       <c r="E1576" t="s">
-        <v>4508</v>
+        <v>4507</v>
       </c>
       <c r="F1576" s="29">
         <v>46211</v>
@@ -80665,7 +80669,7 @@
         <v>806</v>
       </c>
       <c r="J1576" s="62" t="s">
-        <v>4506</v>
+        <v>4505</v>
       </c>
       <c r="K1576">
         <v>1577</v>
@@ -80674,7 +80678,7 @@
         <v>854</v>
       </c>
       <c r="N1576" t="s">
-        <v>4526</v>
+        <v>4525</v>
       </c>
     </row>
     <row r="1577" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -80685,7 +80689,7 @@
         <v>18094997</v>
       </c>
       <c r="C1577" t="s">
-        <v>4509</v>
+        <v>4508</v>
       </c>
       <c r="D1577" t="s">
         <v>60</v>
@@ -80706,7 +80710,7 @@
         <v>806</v>
       </c>
       <c r="J1577" s="62" t="s">
-        <v>4507</v>
+        <v>4506</v>
       </c>
       <c r="K1577">
         <v>1578</v>
@@ -80715,7 +80719,7 @@
         <v>854</v>
       </c>
       <c r="N1577" t="s">
-        <v>4527</v>
+        <v>4526</v>
       </c>
     </row>
     <row r="1578" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -80726,7 +80730,7 @@
         <v>4098248</v>
       </c>
       <c r="C1578" t="s">
-        <v>4490</v>
+        <v>4489</v>
       </c>
       <c r="D1578" t="s">
         <v>203</v>
@@ -80747,7 +80751,7 @@
         <v>290</v>
       </c>
       <c r="J1578" s="62" t="s">
-        <v>4510</v>
+        <v>4509</v>
       </c>
       <c r="K1578">
         <v>1579</v>
@@ -80756,7 +80760,7 @@
         <v>854</v>
       </c>
       <c r="N1578" t="s">
-        <v>4528</v>
+        <v>4527</v>
       </c>
     </row>
     <row r="1579" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -80770,7 +80774,7 @@
         <v>32</v>
       </c>
       <c r="D1579" t="s">
-        <v>4512</v>
+        <v>4511</v>
       </c>
       <c r="E1579" t="s">
         <v>29</v>
@@ -80788,7 +80792,7 @@
         <v>806</v>
       </c>
       <c r="J1579" s="62" t="s">
-        <v>4511</v>
+        <v>4510</v>
       </c>
       <c r="K1579">
         <v>1580</v>
@@ -80797,7 +80801,7 @@
         <v>854</v>
       </c>
       <c r="N1579" t="s">
-        <v>4529</v>
+        <v>4528</v>
       </c>
     </row>
     <row r="1580" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -80829,7 +80833,7 @@
         <v>806</v>
       </c>
       <c r="J1580" s="62" t="s">
-        <v>4513</v>
+        <v>4512</v>
       </c>
       <c r="K1580">
         <v>1581</v>
@@ -80838,7 +80842,7 @@
         <v>854</v>
       </c>
       <c r="N1580" t="s">
-        <v>4530</v>
+        <v>4529</v>
       </c>
     </row>
     <row r="1581" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -80870,7 +80874,7 @@
         <v>806</v>
       </c>
       <c r="J1581" s="62" t="s">
-        <v>4514</v>
+        <v>4513</v>
       </c>
       <c r="K1581">
         <v>1582</v>
@@ -80879,7 +80883,7 @@
         <v>854</v>
       </c>
       <c r="N1581" t="s">
-        <v>4531</v>
+        <v>4530</v>
       </c>
     </row>
     <row r="1582" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -80890,10 +80894,10 @@
         <v>5476493</v>
       </c>
       <c r="C1582" t="s">
+        <v>4514</v>
+      </c>
+      <c r="D1582" t="s">
         <v>4515</v>
-      </c>
-      <c r="D1582" t="s">
-        <v>4516</v>
       </c>
       <c r="E1582" t="s">
         <v>648</v>
@@ -80911,7 +80915,7 @@
         <v>806</v>
       </c>
       <c r="J1582" s="62" t="s">
-        <v>4517</v>
+        <v>4516</v>
       </c>
       <c r="K1582">
         <v>1583</v>
@@ -80920,7 +80924,7 @@
         <v>854</v>
       </c>
       <c r="N1582" t="s">
-        <v>4532</v>
+        <v>4531</v>
       </c>
     </row>
     <row r="1583" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -80931,7 +80935,7 @@
         <v>13417047</v>
       </c>
       <c r="C1583" t="s">
-        <v>4520</v>
+        <v>4519</v>
       </c>
       <c r="D1583" t="s">
         <v>9</v>
@@ -80952,7 +80956,7 @@
         <v>806</v>
       </c>
       <c r="J1583" s="62" t="s">
-        <v>4518</v>
+        <v>4517</v>
       </c>
       <c r="K1583">
         <v>1584</v>
@@ -80961,7 +80965,7 @@
         <v>854</v>
       </c>
       <c r="N1583" t="s">
-        <v>4533</v>
+        <v>4532</v>
       </c>
     </row>
     <row r="1584" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -80972,7 +80976,7 @@
         <v>14071835</v>
       </c>
       <c r="C1584" t="s">
-        <v>4521</v>
+        <v>4520</v>
       </c>
       <c r="D1584" t="s">
         <v>13</v>
@@ -80993,7 +80997,7 @@
         <v>806</v>
       </c>
       <c r="J1584" s="62" t="s">
-        <v>4519</v>
+        <v>4518</v>
       </c>
       <c r="K1584">
         <v>1585</v>
@@ -81002,7 +81006,7 @@
         <v>854</v>
       </c>
       <c r="N1584" t="s">
-        <v>4534</v>
+        <v>4533</v>
       </c>
     </row>
     <row r="1585" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -81034,7